--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Seputeh Hills" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Developer Sales Status" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Klang Valley" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1809,7 +1809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM16"/>
+  <dimension ref="A1:BM17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1882,7 +1882,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Developer Sales Status — daily tracker</t>
+          <t>Klang Valley — daily tracker</t>
         </is>
       </c>
     </row>
@@ -2290,206 +2290,82 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>M AURORA</t>
+          <t>RESIDENSI WARISAN SALAK SELATAN</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>13262-2</t>
+          <t>31202-1</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>MAJORLAND DEVELOPMENT SDN BHD</t>
+          <t>EC VANTAGE SDN. BHD.</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>1544</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>321</v>
-      </c>
-      <c r="H5" s="11">
-        <f>G5/$E$5</f>
-        <v/>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>321</v>
-      </c>
-      <c r="K5" s="12">
-        <f>J5/$E$5</f>
-        <v/>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>321</v>
-      </c>
-      <c r="N5" s="12">
-        <f>M5/$E$5</f>
-        <v/>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q5" s="12">
-        <f>P5/$E$5</f>
-        <v/>
-      </c>
-      <c r="R5" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>319</v>
-      </c>
-      <c r="T5" s="12">
-        <f>S5/$E$5</f>
-        <v/>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v>306</v>
-      </c>
-      <c r="W5" s="12">
-        <f>V5/$E$5</f>
-        <v/>
-      </c>
-      <c r="X5" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y5" s="9" t="n">
-        <v>285</v>
-      </c>
-      <c r="Z5" s="12">
-        <f>Y5/$E$5</f>
-        <v/>
-      </c>
+        <v>1310</v>
+      </c>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="12" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="12" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="12" t="n"/>
       <c r="AA5" s="9" t="n"/>
       <c r="AB5" s="9" t="n"/>
       <c r="AC5" s="12" t="n"/>
-      <c r="AD5" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" s="9" t="n">
-        <v>269</v>
-      </c>
-      <c r="AF5" s="12">
-        <f>AE5/$E$5</f>
-        <v/>
-      </c>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="9" t="n"/>
+      <c r="AF5" s="12" t="n"/>
       <c r="AG5" s="9" t="n"/>
       <c r="AH5" s="9" t="n"/>
       <c r="AI5" s="12" t="n"/>
-      <c r="AJ5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK5" s="9" t="n">
-        <v>247</v>
-      </c>
-      <c r="AL5" s="12">
-        <f>AK5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN5" s="9" t="n">
-        <v>241</v>
-      </c>
-      <c r="AO5" s="12">
-        <f>AN5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ5" s="9" t="n">
-        <v>231</v>
-      </c>
-      <c r="AR5" s="12">
-        <f>AQ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT5" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="AU5" s="12">
-        <f>AT5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AV5" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="AW5" s="9" t="n">
-        <v>213</v>
-      </c>
-      <c r="AX5" s="12">
-        <f>AW5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AZ5" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="BA5" s="12">
-        <f>AZ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BB5" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC5" s="9" t="n">
-        <v>138</v>
-      </c>
-      <c r="BD5" s="12">
-        <f>BC5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BE5" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF5" s="9" t="n">
-        <v>123</v>
-      </c>
-      <c r="BG5" s="12">
-        <f>BF5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BH5" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BI5" s="9" t="n">
-        <v>109</v>
-      </c>
-      <c r="BJ5" s="12">
-        <f>BI5/$E$5</f>
-        <v/>
-      </c>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="9" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
+      <c r="AP5" s="9" t="n"/>
+      <c r="AQ5" s="9" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="9" t="n"/>
+      <c r="AX5" s="12" t="n"/>
+      <c r="AY5" s="9" t="n"/>
+      <c r="AZ5" s="9" t="n"/>
+      <c r="BA5" s="12" t="n"/>
+      <c r="BB5" s="9" t="n"/>
+      <c r="BC5" s="9" t="n"/>
+      <c r="BD5" s="12" t="n"/>
+      <c r="BE5" s="9" t="n"/>
+      <c r="BF5" s="9" t="n"/>
+      <c r="BG5" s="12" t="n"/>
+      <c r="BH5" s="9" t="n"/>
+      <c r="BI5" s="9" t="n"/>
+      <c r="BJ5" s="12" t="n"/>
       <c r="BK5" s="9" t="n"/>
-      <c r="BL5" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM5" s="12">
-        <f>BL5/$E$5</f>
-        <v/>
-      </c>
+      <c r="BL5" s="9" t="n"/>
+      <c r="BM5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2497,27 +2373,27 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>ARTE STAR  MILANO</t>
+          <t>M AURORA</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>30590-2</t>
+          <t>13262-2</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>SURIAMEGA DEVELOPMENT</t>
+          <t>MAJORLAND DEVELOPMENT SDN BHD</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>996</v>
+        <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>114</v>
+        <v>321</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
@@ -2527,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>113</v>
+        <v>321</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
@@ -2537,47 +2413,47 @@
         <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>113</v>
+        <v>321</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>113</v>
+        <v>321</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>112</v>
+        <v>319</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>106</v>
+        <v>306</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
@@ -2587,10 +2463,10 @@
       <c r="AB6" s="9" t="n"/>
       <c r="AC6" s="12" t="n"/>
       <c r="AD6" s="9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>94</v>
+        <v>269</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
@@ -2600,90 +2476,90 @@
       <c r="AH6" s="9" t="n"/>
       <c r="AI6" s="12" t="n"/>
       <c r="AJ6" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>73</v>
+        <v>220</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
       <c r="AY6" s="9" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="AZ6" s="9" t="n">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
       <c r="BB6" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BC6" s="9" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
@@ -2691,7 +2567,7 @@
       </c>
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
@@ -2704,27 +2580,27 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>M ASPIRA</t>
+          <t>ARTE STAR  MILANO</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>5911-33</t>
+          <t>30590-2</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>MAH SING GROUP BERHAD</t>
+          <t>SURIAMEGA DEVELOPMENT</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>1618</v>
+        <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>987</v>
+        <v>114</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -2734,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>986</v>
+        <v>113</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
@@ -2744,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>986</v>
+        <v>113</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
@@ -2754,37 +2630,37 @@
         <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>986</v>
+        <v>113</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>985</v>
+        <v>112</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>976</v>
+        <v>106</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>965</v>
+        <v>102</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
@@ -2794,10 +2670,10 @@
       <c r="AB7" s="9" t="n"/>
       <c r="AC7" s="12" t="n"/>
       <c r="AD7" s="9" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>951</v>
+        <v>94</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
@@ -2807,90 +2683,90 @@
       <c r="AH7" s="9" t="n"/>
       <c r="AI7" s="12" t="n"/>
       <c r="AJ7" s="9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>922</v>
+        <v>81</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>907</v>
+        <v>78</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>892</v>
+        <v>74</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>885</v>
+        <v>73</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
       <c r="AV7" s="9" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>878</v>
+        <v>67</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
       <c r="AY7" s="9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AZ7" s="9" t="n">
-        <v>854</v>
+        <v>61</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
         <v/>
       </c>
       <c r="BB7" s="9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="BC7" s="9" t="n">
-        <v>837</v>
+        <v>58</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>818</v>
+        <v>54</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>808</v>
+        <v>52</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
@@ -2898,7 +2774,7 @@
       </c>
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n">
-        <v>792</v>
+        <v>46</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
@@ -2911,27 +2787,27 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI DESA TIMUR A DESA</t>
+          <t>M ASPIRA</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>30363-2</t>
+          <t>5911-33</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>FITRAH RESOURCES SDN BHD</t>
+          <t>MAH SING GROUP BERHAD</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>1218</v>
+        <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1119</v>
+        <v>987</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
@@ -2941,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1119</v>
+        <v>986</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
@@ -2951,47 +2827,47 @@
         <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>1119</v>
+        <v>986</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1119</v>
+        <v>986</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>1119</v>
+        <v>985</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1117</v>
+        <v>976</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>1117</v>
+        <v>965</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
@@ -3001,10 +2877,10 @@
       <c r="AB8" s="9" t="n"/>
       <c r="AC8" s="12" t="n"/>
       <c r="AD8" s="9" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>1116</v>
+        <v>951</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
@@ -3014,90 +2890,90 @@
       <c r="AH8" s="9" t="n"/>
       <c r="AI8" s="12" t="n"/>
       <c r="AJ8" s="9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>1111</v>
+        <v>922</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>1109</v>
+        <v>907</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AQ8" s="9" t="n">
-        <v>1107</v>
+        <v>892</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>1106</v>
+        <v>885</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
       <c r="AV8" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>1102</v>
+        <v>878</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
       <c r="AY8" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AZ8" s="9" t="n">
-        <v>1096</v>
+        <v>854</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
         <v/>
       </c>
       <c r="BB8" s="9" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="BC8" s="9" t="n">
-        <v>1095</v>
+        <v>837</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>1093</v>
+        <v>10</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>1093</v>
+        <v>818</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>-1091</v>
+        <v>16</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
@@ -3105,7 +2981,7 @@
       </c>
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n">
-        <v>1091</v>
+        <v>792</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
@@ -3118,27 +2994,27 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>RADIUM ARENA RESIDENSI RADIUM</t>
+          <t>RESIDENSI DESA TIMUR A DESA</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>30821-1</t>
+          <t>30363-2</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>RADIUM GLOBAL SDN BHD</t>
+          <t>FITRAH RESOURCES SDN BHD</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>988</v>
+        <v>1218</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>492</v>
+        <v>1119</v>
       </c>
       <c r="H9" s="11">
         <f>G9/$E$9</f>
@@ -3148,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>491</v>
+        <v>1119</v>
       </c>
       <c r="K9" s="12">
         <f>J9/$E$9</f>
@@ -3158,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>491</v>
+        <v>1119</v>
       </c>
       <c r="N9" s="12">
         <f>M9/$E$9</f>
@@ -3168,37 +3044,37 @@
         <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>491</v>
+        <v>1119</v>
       </c>
       <c r="Q9" s="12">
         <f>P9/$E$9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>491</v>
+        <v>1119</v>
       </c>
       <c r="T9" s="12">
         <f>S9/$E$9</f>
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>485</v>
+        <v>1117</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>475</v>
+        <v>1117</v>
       </c>
       <c r="Z9" s="12">
         <f>Y9/$E$9</f>
@@ -3208,10 +3084,10 @@
       <c r="AB9" s="9" t="n"/>
       <c r="AC9" s="12" t="n"/>
       <c r="AD9" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>472</v>
+        <v>1116</v>
       </c>
       <c r="AF9" s="12">
         <f>AE9/$E$9</f>
@@ -3221,50 +3097,50 @@
       <c r="AH9" s="9" t="n"/>
       <c r="AI9" s="12" t="n"/>
       <c r="AJ9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>464</v>
+        <v>1111</v>
       </c>
       <c r="AL9" s="12">
         <f>AK9/$E$9</f>
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN9" s="9" t="n">
-        <v>463</v>
+        <v>1109</v>
       </c>
       <c r="AO9" s="12">
         <f>AN9/$E$9</f>
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" s="9" t="n">
-        <v>462</v>
+        <v>1107</v>
       </c>
       <c r="AR9" s="12">
         <f>AQ9/$E$9</f>
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT9" s="9" t="n">
-        <v>462</v>
+        <v>1106</v>
       </c>
       <c r="AU9" s="12">
         <f>AT9/$E$9</f>
         <v/>
       </c>
       <c r="AV9" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>460</v>
+        <v>1102</v>
       </c>
       <c r="AX9" s="12">
         <f>AW9/$E$9</f>
@@ -3274,34 +3150,34 @@
         <v>1</v>
       </c>
       <c r="AZ9" s="9" t="n">
-        <v>458</v>
+        <v>1096</v>
       </c>
       <c r="BA9" s="12">
         <f>AZ9/$E$9</f>
         <v/>
       </c>
       <c r="BB9" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BC9" s="9" t="n">
-        <v>457</v>
+        <v>1095</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>447</v>
+        <v>1093</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>447</v>
+        <v>1093</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>-446</v>
+        <v>-1091</v>
       </c>
       <c r="BI9" s="9" t="n">
         <v>0</v>
@@ -3312,7 +3188,7 @@
       </c>
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n">
-        <v>446</v>
+        <v>1091</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
@@ -3325,27 +3201,27 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI AMBIEN</t>
+          <t>RADIUM ARENA RESIDENSI RADIUM</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>30366-1</t>
+          <t>30821-1</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>FAITHVIEW RESOURCES SDN BHD</t>
+          <t>RADIUM GLOBAL SDN BHD</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>482</v>
+        <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -3355,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
@@ -3365,47 +3241,47 @@
         <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
@@ -3415,10 +3291,10 @@
       <c r="AB10" s="9" t="n"/>
       <c r="AC10" s="12" t="n"/>
       <c r="AD10" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
@@ -3428,7 +3304,7 @@
       <c r="AH10" s="9" t="n"/>
       <c r="AI10" s="12" t="n"/>
       <c r="AJ10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" s="9" t="n">
         <v>464</v>
@@ -3441,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
@@ -3451,44 +3327,44 @@
         <v>0</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT10" s="9" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
       <c r="AV10" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW10" s="9" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
       <c r="AY10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ10" s="9" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="BA10" s="12">
         <f>AZ10/$E$10</f>
         <v/>
       </c>
       <c r="BB10" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BC10" s="9" t="n">
         <v>457</v>
@@ -3498,20 +3374,20 @@
         <v/>
       </c>
       <c r="BE10" s="9" t="n">
-        <v>2</v>
+        <v>447</v>
       </c>
       <c r="BF10" s="9" t="n">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>2</v>
+        <v>-446</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
@@ -3519,7 +3395,7 @@
       </c>
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
@@ -3532,27 +3408,27 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI HANA</t>
+          <t>RESIDENSI AMBIEN</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>13074-4</t>
+          <t>30366-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>NATURAL DOMAIN SDN BHD</t>
+          <t>FAITHVIEW RESOURCES SDN BHD</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>299</v>
+        <v>482</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>235</v>
+        <v>466</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
@@ -3562,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>235</v>
+        <v>466</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
@@ -3572,27 +3448,27 @@
         <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>235</v>
+        <v>466</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>235</v>
+        <v>466</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>235</v>
+        <v>465</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
@@ -3602,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>234</v>
+        <v>465</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
@@ -3612,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>234</v>
+        <v>465</v>
       </c>
       <c r="Z11" s="12">
         <f>Y11/$E$11</f>
@@ -3622,10 +3498,10 @@
       <c r="AB11" s="9" t="n"/>
       <c r="AC11" s="12" t="n"/>
       <c r="AD11" s="9" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>234</v>
+        <v>465</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
@@ -3638,17 +3514,17 @@
         <v>0</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="AL11" s="12">
         <f>AK11/$E$11</f>
         <v/>
       </c>
       <c r="AM11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" s="9" t="n">
-        <v>236</v>
+        <v>464</v>
       </c>
       <c r="AO11" s="12">
         <f>AN11/$E$11</f>
@@ -3658,37 +3534,37 @@
         <v>0</v>
       </c>
       <c r="AQ11" s="9" t="n">
-        <v>236</v>
+        <v>463</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11" s="9" t="n">
-        <v>236</v>
+        <v>463</v>
       </c>
       <c r="AU11" s="12">
         <f>AT11/$E$11</f>
         <v/>
       </c>
       <c r="AV11" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW11" s="9" t="n">
-        <v>236</v>
+        <v>462</v>
       </c>
       <c r="AX11" s="12">
         <f>AW11/$E$11</f>
         <v/>
       </c>
       <c r="AY11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ11" s="9" t="n">
-        <v>236</v>
+        <v>459</v>
       </c>
       <c r="BA11" s="12">
         <f>AZ11/$E$11</f>
@@ -3698,27 +3574,27 @@
         <v>1</v>
       </c>
       <c r="BC11" s="9" t="n">
-        <v>236</v>
+        <v>457</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="BF11" s="9" t="n">
-        <v>235</v>
+        <v>456</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
         <v/>
       </c>
       <c r="BH11" s="9" t="n">
-        <v>-234</v>
+        <v>2</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
@@ -3726,7 +3602,7 @@
       </c>
       <c r="BK11" s="9" t="n"/>
       <c r="BL11" s="9" t="n">
-        <v>234</v>
+        <v>452</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
@@ -3739,37 +3615,37 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI SUNWAY COCHRANE</t>
+          <t>RESIDENSI HANA</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>8824-5</t>
+          <t>13074-4</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>SUNWAY COCHRANE SDN BHD</t>
+          <t>NATURAL DOMAIN SDN BHD</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1296</v>
+        <v>299</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>612</v>
+        <v>235</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>610</v>
+        <v>235</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
@@ -3779,47 +3655,47 @@
         <v>0</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>609</v>
+        <v>235</v>
       </c>
       <c r="N12" s="12">
         <f>M12/$E$12</f>
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>609</v>
+        <v>235</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>608</v>
+        <v>235</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>591</v>
+        <v>234</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>573</v>
+        <v>234</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
@@ -3829,10 +3705,10 @@
       <c r="AB12" s="9" t="n"/>
       <c r="AC12" s="12" t="n"/>
       <c r="AD12" s="9" t="n">
-        <v>84</v>
+        <v>-2</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>544</v>
+        <v>234</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
@@ -3842,87 +3718,87 @@
       <c r="AH12" s="9" t="n"/>
       <c r="AI12" s="12" t="n"/>
       <c r="AJ12" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>460</v>
+        <v>236</v>
       </c>
       <c r="AL12" s="12">
         <f>AK12/$E$12</f>
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="9" t="n">
-        <v>433</v>
+        <v>236</v>
       </c>
       <c r="AO12" s="12">
         <f>AN12/$E$12</f>
         <v/>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="9" t="n">
-        <v>421</v>
+        <v>236</v>
       </c>
       <c r="AR12" s="12">
         <f>AQ12/$E$12</f>
         <v/>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT12" s="9" t="n">
-        <v>412</v>
+        <v>236</v>
       </c>
       <c r="AU12" s="12">
         <f>AT12/$E$12</f>
         <v/>
       </c>
       <c r="AV12" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW12" s="9" t="n">
-        <v>401</v>
+        <v>236</v>
       </c>
       <c r="AX12" s="12">
         <f>AW12/$E$12</f>
         <v/>
       </c>
       <c r="AY12" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AZ12" s="9" t="n">
-        <v>389</v>
+        <v>236</v>
       </c>
       <c r="BA12" s="12">
         <f>AZ12/$E$12</f>
         <v/>
       </c>
       <c r="BB12" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC12" s="9" t="n">
-        <v>385</v>
+        <v>236</v>
       </c>
       <c r="BD12" s="12">
         <f>BC12/$E$12</f>
         <v/>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>381</v>
+        <v>235</v>
       </c>
       <c r="BF12" s="9" t="n">
-        <v>381</v>
+        <v>235</v>
       </c>
       <c r="BG12" s="12">
         <f>BF12/$E$12</f>
         <v/>
       </c>
       <c r="BH12" s="9" t="n">
-        <v>-379</v>
+        <v>-234</v>
       </c>
       <c r="BI12" s="9" t="n">
         <v>0</v>
@@ -3933,7 +3809,7 @@
       </c>
       <c r="BK12" s="9" t="n"/>
       <c r="BL12" s="9" t="n">
-        <v>379</v>
+        <v>234</v>
       </c>
       <c r="BM12" s="12">
         <f>BL12/$E$12</f>
@@ -3946,37 +3822,37 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI PLATINUM SAUJANA VIOLET 2 (PSV2)</t>
+          <t>RESIDENSI SUNWAY COCHRANE</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>20253-3</t>
+          <t>8824-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>PEMBINAAN SERTA HEBAT SDN.BHD</t>
+          <t>SUNWAY COCHRANE SDN BHD</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1500</v>
+        <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1140</v>
+        <v>612</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1140</v>
+        <v>610</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
@@ -3986,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>1140</v>
+        <v>609</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
@@ -3996,37 +3872,37 @@
         <v>1</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1140</v>
+        <v>609</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>1139</v>
+        <v>608</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1135</v>
+        <v>591</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>1129</v>
+        <v>573</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
@@ -4036,10 +3912,10 @@
       <c r="AB13" s="9" t="n"/>
       <c r="AC13" s="12" t="n"/>
       <c r="AD13" s="9" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>1126</v>
+        <v>544</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
@@ -4049,87 +3925,87 @@
       <c r="AH13" s="9" t="n"/>
       <c r="AI13" s="12" t="n"/>
       <c r="AJ13" s="9" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>1115</v>
+        <v>460</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN13" s="9" t="n">
-        <v>1110</v>
+        <v>433</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
       <c r="AP13" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AQ13" s="9" t="n">
-        <v>1100</v>
+        <v>421</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>1096</v>
+        <v>412</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
       <c r="AV13" s="9" t="n">
-        <v>1086</v>
+        <v>12</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>1086</v>
+        <v>401</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
       <c r="AY13" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AZ13" s="9" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
         <v/>
       </c>
       <c r="BB13" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC13" s="9" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>0</v>
+        <v>-379</v>
       </c>
       <c r="BI13" s="9" t="n">
         <v>0</v>
@@ -4140,7 +4016,7 @@
       </c>
       <c r="BK13" s="9" t="n"/>
       <c r="BL13" s="9" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
@@ -4153,27 +4029,27 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI VERIDIAN</t>
+          <t>RESIDENSI PLATINUM SAUJANA VIOLET 2 (PSV2)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>30876-1</t>
+          <t>20253-3</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>PERUMAHAN MASTERON SDN BHD</t>
+          <t>PEMBINAAN SERTA HEBAT SDN.BHD</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>551</v>
+        <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>123</v>
+        <v>1140</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
@@ -4183,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>124</v>
+        <v>1140</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
@@ -4193,37 +4069,37 @@
         <v>0</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>124</v>
+        <v>1140</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>124</v>
+        <v>1140</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>124</v>
+        <v>1139</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>121</v>
+        <v>1135</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
@@ -4233,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>121</v>
+        <v>1129</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
@@ -4243,10 +4119,10 @@
       <c r="AB14" s="9" t="n"/>
       <c r="AC14" s="12" t="n"/>
       <c r="AD14" s="9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>118</v>
+        <v>1126</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
@@ -4256,60 +4132,60 @@
       <c r="AH14" s="9" t="n"/>
       <c r="AI14" s="12" t="n"/>
       <c r="AJ14" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>96</v>
+        <v>1115</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>86</v>
+        <v>1110</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>82</v>
+        <v>1100</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>79</v>
+        <v>1096</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
       <c r="AV14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>76</v>
+        <v>1086</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
       <c r="AY14" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AZ14" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
@@ -4360,27 +4236,27 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>RESIDENSI AURUM</t>
+          <t>RESIDENSI VERIDIAN</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>30250-2</t>
+          <t>30876-1</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>AMBER HOMES SRI PETALING SDN BHD</t>
+          <t>PERUMAHAN MASTERON SDN BHD</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>661</v>
+        <v>551</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>659</v>
+        <v>123</v>
       </c>
       <c r="H15" s="11">
         <f>G15/$E$15</f>
@@ -4390,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>659</v>
+        <v>124</v>
       </c>
       <c r="K15" s="12">
         <f>J15/$E$15</f>
@@ -4400,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>659</v>
+        <v>124</v>
       </c>
       <c r="N15" s="12">
         <f>M15/$E$15</f>
@@ -4410,17 +4286,17 @@
         <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>659</v>
+        <v>124</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>659</v>
+        <v>124</v>
       </c>
       <c r="T15" s="12">
         <f>S15/$E$15</f>
@@ -4430,17 +4306,17 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>659</v>
+        <v>121</v>
       </c>
       <c r="W15" s="12">
         <f>V15/$E$15</f>
         <v/>
       </c>
       <c r="X15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>659</v>
+        <v>121</v>
       </c>
       <c r="Z15" s="12">
         <f>Y15/$E$15</f>
@@ -4450,10 +4326,10 @@
       <c r="AB15" s="9" t="n"/>
       <c r="AC15" s="12" t="n"/>
       <c r="AD15" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>659</v>
+        <v>118</v>
       </c>
       <c r="AF15" s="12">
         <f>AE15/$E$15</f>
@@ -4463,46 +4339,95 @@
       <c r="AH15" s="9" t="n"/>
       <c r="AI15" s="12" t="n"/>
       <c r="AJ15" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK15" s="9" t="n">
-        <v>659</v>
+        <v>96</v>
       </c>
       <c r="AL15" s="12">
         <f>AK15/$E$15</f>
         <v/>
       </c>
       <c r="AM15" s="9" t="n">
-        <v>659</v>
+        <v>4</v>
       </c>
       <c r="AN15" s="9" t="n">
-        <v>659</v>
+        <v>86</v>
       </c>
       <c r="AO15" s="12">
         <f>AN15/$E$15</f>
         <v/>
       </c>
-      <c r="AP15" s="9" t="n"/>
-      <c r="AQ15" s="9" t="n"/>
-      <c r="AR15" s="12" t="n"/>
-      <c r="AS15" s="9" t="n"/>
-      <c r="AT15" s="9" t="n"/>
-      <c r="AU15" s="12" t="n"/>
-      <c r="AV15" s="9" t="n"/>
-      <c r="AW15" s="9" t="n"/>
-      <c r="AX15" s="12" t="n"/>
-      <c r="AY15" s="9" t="n"/>
-      <c r="AZ15" s="9" t="n"/>
-      <c r="BA15" s="12" t="n"/>
-      <c r="BB15" s="9" t="n"/>
-      <c r="BC15" s="9" t="n"/>
-      <c r="BD15" s="12" t="n"/>
-      <c r="BE15" s="9" t="n"/>
-      <c r="BF15" s="9" t="n"/>
-      <c r="BG15" s="12" t="n"/>
-      <c r="BH15" s="9" t="n"/>
-      <c r="BI15" s="9" t="n"/>
-      <c r="BJ15" s="12" t="n"/>
+      <c r="AP15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ15" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="AR15" s="12">
+        <f>AQ15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AS15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT15" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="AU15" s="12">
+        <f>AT15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AV15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="AX15" s="12">
+        <f>AW15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AY15" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="AZ15" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="BA15" s="12">
+        <f>AZ15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BB15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" s="12">
+        <f>BC15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BE15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" s="12">
+        <f>BF15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BH15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="12">
+        <f>BI15/$E$15</f>
+        <v/>
+      </c>
       <c r="BK15" s="9" t="n"/>
       <c r="BL15" s="9" t="n">
         <v>0</v>
@@ -4518,58 +4443,128 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>THE SHANG RESIDENCE</t>
+          <t>RESIDENSI AURUM</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30250-2</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>SHANG HEIGHT REALTY SDN. BHD.</t>
+          <t>AMBER HOMES SRI PETALING SDN BHD</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>449</v>
-      </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="11" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="9" t="n"/>
-      <c r="S16" s="9" t="n"/>
-      <c r="T16" s="12" t="n"/>
-      <c r="U16" s="9" t="n"/>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="12" t="n"/>
+        <v>661</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>659</v>
+      </c>
+      <c r="H16" s="11">
+        <f>G16/$E$16</f>
+        <v/>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="K16" s="12">
+        <f>J16/$E$16</f>
+        <v/>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="N16" s="12">
+        <f>M16/$E$16</f>
+        <v/>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="Q16" s="12">
+        <f>P16/$E$16</f>
+        <v/>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="T16" s="12">
+        <f>S16/$E$16</f>
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="W16" s="12">
+        <f>V16/$E$16</f>
+        <v/>
+      </c>
+      <c r="X16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="Z16" s="12">
+        <f>Y16/$E$16</f>
+        <v/>
+      </c>
       <c r="AA16" s="9" t="n"/>
       <c r="AB16" s="9" t="n"/>
       <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="9" t="n"/>
-      <c r="AE16" s="9" t="n"/>
-      <c r="AF16" s="12" t="n"/>
+      <c r="AD16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AF16" s="12">
+        <f>AE16/$E$16</f>
+        <v/>
+      </c>
       <c r="AG16" s="9" t="n"/>
       <c r="AH16" s="9" t="n"/>
       <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AN16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
       <c r="AP16" s="9" t="n"/>
       <c r="AQ16" s="9" t="n"/>
       <c r="AR16" s="12" t="n"/>
@@ -4592,8 +4587,96 @@
       <c r="BI16" s="9" t="n"/>
       <c r="BJ16" s="12" t="n"/>
       <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n"/>
-      <c r="BM16" s="12" t="n"/>
+      <c r="BL16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" s="12">
+        <f>BL16/$E$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>THE SHANG RESIDENCE</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>SHANG HEIGHT REALTY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>449</v>
+      </c>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="12" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="9" t="n"/>
+      <c r="AE17" s="9" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="9" t="n"/>
+      <c r="AK17" s="9" t="n"/>
+      <c r="AL17" s="12" t="n"/>
+      <c r="AM17" s="9" t="n"/>
+      <c r="AN17" s="9" t="n"/>
+      <c r="AO17" s="12" t="n"/>
+      <c r="AP17" s="9" t="n"/>
+      <c r="AQ17" s="9" t="n"/>
+      <c r="AR17" s="12" t="n"/>
+      <c r="AS17" s="9" t="n"/>
+      <c r="AT17" s="9" t="n"/>
+      <c r="AU17" s="12" t="n"/>
+      <c r="AV17" s="9" t="n"/>
+      <c r="AW17" s="9" t="n"/>
+      <c r="AX17" s="12" t="n"/>
+      <c r="AY17" s="9" t="n"/>
+      <c r="AZ17" s="9" t="n"/>
+      <c r="BA17" s="12" t="n"/>
+      <c r="BB17" s="9" t="n"/>
+      <c r="BC17" s="9" t="n"/>
+      <c r="BD17" s="12" t="n"/>
+      <c r="BE17" s="9" t="n"/>
+      <c r="BF17" s="9" t="n"/>
+      <c r="BG17" s="12" t="n"/>
+      <c r="BH17" s="9" t="n"/>
+      <c r="BI17" s="9" t="n"/>
+      <c r="BJ17" s="12" t="n"/>
+      <c r="BK17" s="9" t="n"/>
+      <c r="BL17" s="9" t="n"/>
+      <c r="BM17" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -1258,10 +1258,10 @@
         <v>490</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -1669,10 +1669,10 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -2307,8 +2307,13 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n"/>
-      <c r="G5" s="10" t="n"/>
-      <c r="H5" s="11" t="n"/>
+      <c r="G5" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="H5" s="11">
+        <f>G5/$E$5</f>
+        <v/>
+      </c>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="12" t="n"/>
@@ -2390,10 +2395,10 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
@@ -2597,10 +2602,10 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -2804,10 +2809,10 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
@@ -3011,10 +3016,10 @@
         <v>1218</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H9" s="11">
         <f>G9/$E$9</f>
@@ -3218,10 +3223,10 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -3425,10 +3430,10 @@
         <v>482</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
@@ -3839,10 +3844,10 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
@@ -4046,10 +4051,10 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Seputeh Hills" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Klang Valley" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Johor" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,37 +573,37 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>46242</v>
+        <v>46234</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>46241</v>
+        <v>46227</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46220</v>
+        <v>46213</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>46219</v>
+        <v>46206</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>46213</v>
+        <v>46205</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>46205</v>
+        <v>46199</v>
       </c>
       <c r="AM3" s="4" t="n">
         <v>46198</v>
@@ -994,7 +995,7 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>42</v>
@@ -1004,40 +1005,33 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
-      <c r="R5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="T5" s="12">
-        <f>S5/$E$5</f>
-        <v/>
-      </c>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="12" t="n"/>
       <c r="U5" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
@@ -1046,11 +1040,9 @@
       <c r="X5" s="9" t="n"/>
       <c r="Y5" s="9" t="n"/>
       <c r="Z5" s="12" t="n"/>
-      <c r="AA5" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="AA5" s="9" t="n"/>
       <c r="AB5" s="9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
@@ -1060,13 +1052,8 @@
       <c r="AE5" s="9" t="n"/>
       <c r="AF5" s="12" t="n"/>
       <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI5" s="12">
-        <f>AH5/$E$5</f>
-        <v/>
-      </c>
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="12" t="n"/>
       <c r="AJ5" s="9" t="n"/>
       <c r="AK5" s="9" t="n"/>
       <c r="AL5" s="12" t="n"/>
@@ -1160,18 +1147,11 @@
         <f>P6/$E$6</f>
         <v/>
       </c>
-      <c r="R6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="T6" s="12">
-        <f>S6/$E$6</f>
-        <v/>
-      </c>
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="12" t="n"/>
       <c r="U6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>33</v>
@@ -1183,11 +1163,9 @@
       <c r="X6" s="9" t="n"/>
       <c r="Y6" s="9" t="n"/>
       <c r="Z6" s="12" t="n"/>
-      <c r="AA6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA6" s="9" t="n"/>
       <c r="AB6" s="9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
@@ -1197,13 +1175,8 @@
       <c r="AE6" s="9" t="n"/>
       <c r="AF6" s="12" t="n"/>
       <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
       <c r="AJ6" s="9" t="n"/>
       <c r="AK6" s="9" t="n"/>
       <c r="AL6" s="12" t="n"/>
@@ -1268,7 +1241,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>44</v>
@@ -1278,40 +1251,33 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
-      <c r="R7" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="S7" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="T7" s="12">
-        <f>S7/$E$7</f>
-        <v/>
-      </c>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="12" t="n"/>
       <c r="U7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
@@ -1320,11 +1286,9 @@
       <c r="X7" s="9" t="n"/>
       <c r="Y7" s="9" t="n"/>
       <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="AA7" s="9" t="n"/>
       <c r="AB7" s="9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
@@ -1334,13 +1298,8 @@
       <c r="AE7" s="9" t="n"/>
       <c r="AF7" s="12" t="n"/>
       <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
       <c r="AJ7" s="9" t="n"/>
       <c r="AK7" s="9" t="n"/>
       <c r="AL7" s="12" t="n"/>
@@ -1434,16 +1393,9 @@
         <f>P8/$E$8</f>
         <v/>
       </c>
-      <c r="R8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="T8" s="12">
-        <f>S8/$E$8</f>
-        <v/>
-      </c>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="12" t="n"/>
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1409,7 @@
       <c r="X8" s="9" t="n"/>
       <c r="Y8" s="9" t="n"/>
       <c r="Z8" s="12" t="n"/>
-      <c r="AA8" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA8" s="9" t="n"/>
       <c r="AB8" s="9" t="n">
         <v>45</v>
       </c>
@@ -1471,13 +1421,8 @@
       <c r="AE8" s="9" t="n"/>
       <c r="AF8" s="12" t="n"/>
       <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
       <c r="AJ8" s="9" t="n"/>
       <c r="AK8" s="9" t="n"/>
       <c r="AL8" s="12" t="n"/>
@@ -1562,7 +1507,7 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>1</v>
@@ -1571,21 +1516,14 @@
         <f>P9/$E$9</f>
         <v/>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="12">
-        <f>S9/$E$9</f>
-        <v/>
-      </c>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="12" t="n"/>
       <c r="U9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
@@ -1594,9 +1532,7 @@
       <c r="X9" s="9" t="n"/>
       <c r="Y9" s="9" t="n"/>
       <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA9" s="9" t="n"/>
       <c r="AB9" s="9" t="n">
         <v>0</v>
       </c>
@@ -1608,13 +1544,8 @@
       <c r="AE9" s="9" t="n"/>
       <c r="AF9" s="12" t="n"/>
       <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
       <c r="AJ9" s="9" t="n"/>
       <c r="AK9" s="9" t="n"/>
       <c r="AL9" s="12" t="n"/>
@@ -1679,7 +1610,7 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>271</v>
@@ -1689,40 +1620,31 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>271</v>
+        <v>214</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
-      <c r="R10" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>262</v>
-      </c>
-      <c r="T10" s="12">
-        <f>S10/$E$10</f>
-        <v/>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v>182</v>
-      </c>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="12" t="n"/>
+      <c r="U10" s="9" t="n"/>
       <c r="V10" s="9" t="n">
-        <v>214</v>
+        <v>32</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
@@ -1732,13 +1654,8 @@
       <c r="Y10" s="9" t="n"/>
       <c r="Z10" s="12" t="n"/>
       <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC10" s="12">
-        <f>AB10/$E$10</f>
-        <v/>
-      </c>
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="12" t="n"/>
       <c r="AD10" s="9" t="n"/>
       <c r="AE10" s="9" t="n"/>
       <c r="AF10" s="12" t="n"/>
@@ -1895,37 +1812,37 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>46242</v>
+        <v>46234</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>46241</v>
+        <v>46227</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46220</v>
+        <v>46213</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>46219</v>
+        <v>46206</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>46213</v>
+        <v>46205</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>46205</v>
+        <v>46199</v>
       </c>
       <c r="AM3" s="4" t="n">
         <v>46198</v>
@@ -2405,7 +2322,7 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>321</v>
@@ -2415,50 +2332,43 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="V6" s="9" t="n">
-        <v>306</v>
-      </c>
-      <c r="W6" s="12">
-        <f>V6/$E$6</f>
-        <v/>
-      </c>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="12" t="n"/>
       <c r="X6" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
@@ -2467,29 +2377,22 @@
       <c r="AA6" s="9" t="n"/>
       <c r="AB6" s="9" t="n"/>
       <c r="AC6" s="12" t="n"/>
-      <c r="AD6" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE6" s="9" t="n">
-        <v>269</v>
-      </c>
-      <c r="AF6" s="12">
-        <f>AE6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AH6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
       <c r="AM6" s="9" t="n">
         <v>10</v>
       </c>
@@ -2612,7 +2515,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>113</v>
@@ -2622,50 +2525,43 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>106</v>
-      </c>
-      <c r="W7" s="12">
-        <f>V7/$E$7</f>
-        <v/>
-      </c>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="12" t="n"/>
       <c r="X7" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
@@ -2674,29 +2570,22 @@
       <c r="AA7" s="9" t="n"/>
       <c r="AB7" s="9" t="n"/>
       <c r="AC7" s="12" t="n"/>
-      <c r="AD7" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE7" s="9" t="n">
-        <v>94</v>
-      </c>
-      <c r="AF7" s="12">
-        <f>AE7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AH7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
       <c r="AM7" s="9" t="n">
         <v>4</v>
       </c>
@@ -2819,7 +2708,7 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>986</v>
@@ -2829,50 +2718,43 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>986</v>
+        <v>976</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>985</v>
+        <v>965</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
-      <c r="U8" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v>976</v>
-      </c>
-      <c r="W8" s="12">
-        <f>V8/$E$8</f>
-        <v/>
-      </c>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="12" t="n"/>
       <c r="X8" s="9" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>965</v>
+        <v>951</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
@@ -2881,29 +2763,22 @@
       <c r="AA8" s="9" t="n"/>
       <c r="AB8" s="9" t="n"/>
       <c r="AC8" s="12" t="n"/>
-      <c r="AD8" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE8" s="9" t="n">
-        <v>951</v>
-      </c>
-      <c r="AF8" s="12">
-        <f>AE8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AH8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
       <c r="AM8" s="9" t="n">
         <v>15</v>
       </c>
@@ -3036,7 +2911,7 @@
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>1119</v>
@@ -3049,37 +2924,30 @@
         <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="Q9" s="12">
         <f>P9/$E$9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="T9" s="12">
         <f>S9/$E$9</f>
         <v/>
       </c>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v>1117</v>
-      </c>
-      <c r="W9" s="12">
-        <f>V9/$E$9</f>
-        <v/>
-      </c>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="12" t="n"/>
       <c r="X9" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="Z9" s="12">
         <f>Y9/$E$9</f>
@@ -3088,29 +2956,22 @@
       <c r="AA9" s="9" t="n"/>
       <c r="AB9" s="9" t="n"/>
       <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="9" t="n">
-        <v>1116</v>
-      </c>
-      <c r="AF9" s="12">
-        <f>AE9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
+      <c r="AD9" s="9" t="n"/>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AH9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
       <c r="AM9" s="9" t="n">
         <v>2</v>
       </c>
@@ -3243,7 +3104,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>491</v>
@@ -3253,40 +3114,33 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
-      <c r="U10" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="V10" s="9" t="n">
-        <v>485</v>
-      </c>
-      <c r="W10" s="12">
-        <f>V10/$E$10</f>
-        <v/>
-      </c>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="12" t="n"/>
       <c r="X10" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
@@ -3295,29 +3149,22 @@
       <c r="AA10" s="9" t="n"/>
       <c r="AB10" s="9" t="n"/>
       <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE10" s="9" t="n">
-        <v>472</v>
-      </c>
-      <c r="AF10" s="12">
-        <f>AE10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AD10" s="9" t="n"/>
+      <c r="AE10" s="9" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AH10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
       <c r="AM10" s="9" t="n">
         <v>1</v>
       </c>
@@ -3440,7 +3287,7 @@
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>466</v>
@@ -3453,17 +3300,17 @@
         <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
@@ -3479,18 +3326,11 @@
         <f>S11/$E$11</f>
         <v/>
       </c>
-      <c r="U11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="9" t="n">
-        <v>465</v>
-      </c>
-      <c r="W11" s="12">
-        <f>V11/$E$11</f>
-        <v/>
-      </c>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="12" t="n"/>
       <c r="X11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>465</v>
@@ -3502,29 +3342,22 @@
       <c r="AA11" s="9" t="n"/>
       <c r="AB11" s="9" t="n"/>
       <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="9" t="n">
-        <v>465</v>
-      </c>
-      <c r="AF11" s="12">
-        <f>AE11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AD11" s="9" t="n"/>
+      <c r="AE11" s="9" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
       <c r="AM11" s="9" t="n">
         <v>1</v>
       </c>
@@ -3657,7 +3490,7 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>235</v>
@@ -3670,34 +3503,27 @@
         <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v>234</v>
-      </c>
-      <c r="W12" s="12">
-        <f>V12/$E$12</f>
-        <v/>
-      </c>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="9" t="n"/>
+      <c r="W12" s="12" t="n"/>
       <c r="X12" s="9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>234</v>
@@ -3709,29 +3535,22 @@
       <c r="AA12" s="9" t="n"/>
       <c r="AB12" s="9" t="n"/>
       <c r="AC12" s="12" t="n"/>
-      <c r="AD12" s="9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE12" s="9" t="n">
-        <v>234</v>
-      </c>
-      <c r="AF12" s="12">
-        <f>AE12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AD12" s="9" t="n"/>
+      <c r="AE12" s="9" t="n"/>
+      <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
       <c r="AM12" s="9" t="n">
         <v>0</v>
       </c>
@@ -3844,7 +3663,7 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>613</v>
@@ -3857,57 +3676,50 @@
         <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>608</v>
+        <v>573</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
-      <c r="U13" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v>591</v>
-      </c>
-      <c r="W13" s="12">
-        <f>V13/$E$13</f>
-        <v/>
-      </c>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="12" t="n"/>
       <c r="X13" s="9" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
@@ -3916,29 +3728,22 @@
       <c r="AA13" s="9" t="n"/>
       <c r="AB13" s="9" t="n"/>
       <c r="AC13" s="12" t="n"/>
-      <c r="AD13" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="AE13" s="9" t="n">
-        <v>544</v>
-      </c>
-      <c r="AF13" s="12">
-        <f>AE13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AD13" s="9" t="n"/>
+      <c r="AE13" s="9" t="n"/>
+      <c r="AF13" s="12" t="n"/>
+      <c r="AG13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AH13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
       <c r="AM13" s="9" t="n">
         <v>12</v>
       </c>
@@ -4061,7 +3866,7 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>1140</v>
@@ -4071,50 +3876,43 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1139</v>
+        <v>1129</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
-      <c r="U14" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v>1135</v>
-      </c>
-      <c r="W14" s="12">
-        <f>V14/$E$14</f>
-        <v/>
-      </c>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="9" t="n"/>
+      <c r="W14" s="12" t="n"/>
       <c r="X14" s="9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
@@ -4123,29 +3921,22 @@
       <c r="AA14" s="9" t="n"/>
       <c r="AB14" s="9" t="n"/>
       <c r="AC14" s="12" t="n"/>
-      <c r="AD14" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE14" s="9" t="n">
-        <v>1126</v>
-      </c>
-      <c r="AF14" s="12">
-        <f>AE14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
+      <c r="AD14" s="9" t="n"/>
+      <c r="AE14" s="9" t="n"/>
+      <c r="AF14" s="12" t="n"/>
+      <c r="AG14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AH14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
       <c r="AM14" s="9" t="n">
         <v>10</v>
       </c>
@@ -4278,7 +4069,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" s="9" t="n">
         <v>124</v>
@@ -4291,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
@@ -4301,27 +4092,20 @@
         <v>3</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="T15" s="12">
         <f>S15/$E$15</f>
         <v/>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="W15" s="12">
-        <f>V15/$E$15</f>
-        <v/>
-      </c>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="12" t="n"/>
       <c r="X15" s="9" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Z15" s="12">
         <f>Y15/$E$15</f>
@@ -4330,29 +4114,22 @@
       <c r="AA15" s="9" t="n"/>
       <c r="AB15" s="9" t="n"/>
       <c r="AC15" s="12" t="n"/>
-      <c r="AD15" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE15" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="AF15" s="12">
-        <f>AE15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AG15" s="9" t="n"/>
-      <c r="AH15" s="9" t="n"/>
-      <c r="AI15" s="12" t="n"/>
-      <c r="AJ15" s="9" t="n">
+      <c r="AD15" s="9" t="n"/>
+      <c r="AE15" s="9" t="n"/>
+      <c r="AF15" s="12" t="n"/>
+      <c r="AG15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AK15" s="9" t="n">
+      <c r="AH15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AL15" s="12">
-        <f>AK15/$E$15</f>
-        <v/>
-      </c>
+      <c r="AI15" s="12">
+        <f>AH15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="9" t="n"/>
+      <c r="AK15" s="9" t="n"/>
+      <c r="AL15" s="12" t="n"/>
       <c r="AM15" s="9" t="n">
         <v>4</v>
       </c>
@@ -4514,16 +4291,9 @@
         <f>S16/$E$16</f>
         <v/>
       </c>
-      <c r="U16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>659</v>
-      </c>
-      <c r="W16" s="12">
-        <f>V16/$E$16</f>
-        <v/>
-      </c>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="12" t="n"/>
       <c r="X16" s="9" t="n">
         <v>0</v>
       </c>
@@ -4537,29 +4307,22 @@
       <c r="AA16" s="9" t="n"/>
       <c r="AB16" s="9" t="n"/>
       <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="9" t="n">
+      <c r="AD16" s="9" t="n"/>
+      <c r="AE16" s="9" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AF16" s="12">
-        <f>AE16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="9" t="n">
-        <v>659</v>
-      </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
       <c r="AM16" s="9" t="n">
         <v>659</v>
       </c>
@@ -4708,4 +4471,2467 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BM18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+    <col width="9" customWidth="1" min="39" max="39"/>
+    <col width="9" customWidth="1" min="40" max="40"/>
+    <col width="9" customWidth="1" min="41" max="41"/>
+    <col width="9" customWidth="1" min="42" max="42"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="9" customWidth="1" min="44" max="44"/>
+    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="9" customWidth="1" min="46" max="46"/>
+    <col width="9" customWidth="1" min="47" max="47"/>
+    <col width="9" customWidth="1" min="48" max="48"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="9" customWidth="1" min="52" max="52"/>
+    <col width="9" customWidth="1" min="53" max="53"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="55" max="55"/>
+    <col width="9" customWidth="1" min="56" max="56"/>
+    <col width="9" customWidth="1" min="57" max="57"/>
+    <col width="9" customWidth="1" min="58" max="58"/>
+    <col width="9" customWidth="1" min="59" max="59"/>
+    <col width="9" customWidth="1" min="60" max="60"/>
+    <col width="9" customWidth="1" min="61" max="61"/>
+    <col width="9" customWidth="1" min="62" max="62"/>
+    <col width="9" customWidth="1" min="63" max="63"/>
+    <col width="9" customWidth="1" min="64" max="64"/>
+    <col width="9" customWidth="1" min="65" max="65"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Johor — daily tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Every day the tracker has run, newest first. Generated 11/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="F3" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>46242</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>46220</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>46219</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>46213</v>
+      </c>
+      <c r="AD3" s="4" t="n">
+        <v>46206</v>
+      </c>
+      <c r="AG3" s="4" t="n">
+        <v>46205</v>
+      </c>
+      <c r="AJ3" s="4" t="n">
+        <v>46199</v>
+      </c>
+      <c r="AM3" s="4" t="n">
+        <v>46198</v>
+      </c>
+      <c r="AP3" s="4" t="n">
+        <v>46192</v>
+      </c>
+      <c r="AS3" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="AV3" s="4" t="n">
+        <v>46170</v>
+      </c>
+      <c r="AY3" s="4" t="n">
+        <v>46163</v>
+      </c>
+      <c r="BB3" s="4" t="n">
+        <v>46156</v>
+      </c>
+      <c r="BE3" s="4" t="n">
+        <v>46149</v>
+      </c>
+      <c r="BH3" s="4" t="n">
+        <v>46142</v>
+      </c>
+      <c r="BK3" s="4" t="n">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>PROJECT 
+CODE</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>DEVELOPER</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL 
+UNITS</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AC4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AD4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AE4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AF4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AG4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AH4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AI4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AJ4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AK4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AL4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AM4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AN4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AO4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AP4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AQ4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AR4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AS4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AT4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AU4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AV4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AW4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AX4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AY4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AZ4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BA4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BB4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BC4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BD4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BE4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BF4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BG4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BH4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BI4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BJ4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BK4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BL4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BM4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>The Straits View Duo</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>835-14</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>BRDB</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>715</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>295</v>
+      </c>
+      <c r="H5" s="11">
+        <f>G5/$E$5</f>
+        <v/>
+      </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>293</v>
+      </c>
+      <c r="N5" s="12">
+        <f>M5/$E$5</f>
+        <v/>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q5" s="12">
+        <f>P5/$E$5</f>
+        <v/>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="T5" s="12">
+        <f>S5/$E$5</f>
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="W5" s="12">
+        <f>V5/$E$5</f>
+        <v/>
+      </c>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="12" t="n"/>
+      <c r="AA5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AG5" s="9" t="n"/>
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK5" s="9" t="n">
+        <v>286</v>
+      </c>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
+      <c r="AP5" s="9" t="n"/>
+      <c r="AQ5" s="9" t="n">
+        <v>275</v>
+      </c>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="9" t="n"/>
+      <c r="AX5" s="12" t="n"/>
+      <c r="AY5" s="9" t="n"/>
+      <c r="AZ5" s="9" t="n"/>
+      <c r="BA5" s="12" t="n"/>
+      <c r="BB5" s="9" t="n"/>
+      <c r="BC5" s="9" t="n"/>
+      <c r="BD5" s="12" t="n"/>
+      <c r="BE5" s="9" t="n"/>
+      <c r="BF5" s="9" t="n"/>
+      <c r="BG5" s="12" t="n"/>
+      <c r="BH5" s="9" t="n"/>
+      <c r="BI5" s="9" t="n"/>
+      <c r="BJ5" s="12" t="n"/>
+      <c r="BK5" s="9" t="n"/>
+      <c r="BL5" s="9" t="n"/>
+      <c r="BM5" s="12" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Permas Heights</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>30946-1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>MB World</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>937</v>
+      </c>
+      <c r="H6" s="11">
+        <f>G6/$E$6</f>
+        <v/>
+      </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>935</v>
+      </c>
+      <c r="N6" s="12">
+        <f>M6/$E$6</f>
+        <v/>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>925</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>P6/$E$6</f>
+        <v/>
+      </c>
+      <c r="R6" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>916</v>
+      </c>
+      <c r="T6" s="12">
+        <f>S6/$E$6</f>
+        <v/>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="W6" s="12">
+        <f>V6/$E$6</f>
+        <v/>
+      </c>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="12" t="n"/>
+      <c r="AA6" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>901</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n">
+        <v>842</v>
+      </c>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n"/>
+      <c r="BF6" s="9" t="n"/>
+      <c r="BG6" s="12" t="n"/>
+      <c r="BH6" s="9" t="n"/>
+      <c r="BI6" s="9" t="n"/>
+      <c r="BJ6" s="12" t="n"/>
+      <c r="BK6" s="9" t="n"/>
+      <c r="BL6" s="9" t="n"/>
+      <c r="BM6" s="12" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>HillView Senibong Cove</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>14523-4</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>WM Senibong</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>416</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="H7" s="11">
+        <f>G7/$E$7</f>
+        <v/>
+      </c>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="N7" s="12">
+        <f>M7/$E$7</f>
+        <v/>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="12">
+        <f>P7/$E$7</f>
+        <v/>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="T7" s="12">
+        <f>S7/$E$7</f>
+        <v/>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="W7" s="12">
+        <f>V7/$E$7</f>
+        <v/>
+      </c>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="12" t="n"/>
+      <c r="AA7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n"/>
+      <c r="BF7" s="9" t="n"/>
+      <c r="BG7" s="12" t="n"/>
+      <c r="BH7" s="9" t="n"/>
+      <c r="BI7" s="9" t="n"/>
+      <c r="BJ7" s="12" t="n"/>
+      <c r="BK7" s="9" t="n"/>
+      <c r="BL7" s="9" t="n"/>
+      <c r="BM7" s="12" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Parkland by the River</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>30635-1</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Parkland</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>2156</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>1051</v>
+      </c>
+      <c r="H8" s="11">
+        <f>G8/$E$8</f>
+        <v/>
+      </c>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>1051</v>
+      </c>
+      <c r="N8" s="12">
+        <f>M8/$E$8</f>
+        <v/>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q8" s="12">
+        <f>P8/$E$8</f>
+        <v/>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>1045</v>
+      </c>
+      <c r="T8" s="12">
+        <f>S8/$E$8</f>
+        <v/>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="W8" s="12">
+        <f>V8/$E$8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB8" s="9" t="n">
+        <v>1033</v>
+      </c>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AD8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="9" t="n">
+        <v>1012</v>
+      </c>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n">
+        <v>1010</v>
+      </c>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n"/>
+      <c r="BF8" s="9" t="n"/>
+      <c r="BG8" s="12" t="n"/>
+      <c r="BH8" s="9" t="n"/>
+      <c r="BI8" s="9" t="n"/>
+      <c r="BJ8" s="12" t="n"/>
+      <c r="BK8" s="9" t="n"/>
+      <c r="BL8" s="9" t="n"/>
+      <c r="BM8" s="12" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>The Asteriaz</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>31007-1</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Exsim</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>848</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>845</v>
+      </c>
+      <c r="H9" s="11">
+        <f>G9/$E$9</f>
+        <v/>
+      </c>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>845</v>
+      </c>
+      <c r="N9" s="12">
+        <f>M9/$E$9</f>
+        <v/>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>845</v>
+      </c>
+      <c r="Q9" s="12">
+        <f>P9/$E$9</f>
+        <v/>
+      </c>
+      <c r="R9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" s="9" t="n">
+        <v>845</v>
+      </c>
+      <c r="T9" s="12">
+        <f>S9/$E$9</f>
+        <v/>
+      </c>
+      <c r="U9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="W9" s="12">
+        <f>V9/$E$9</f>
+        <v/>
+      </c>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="9" t="n"/>
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
+      <c r="BE9" s="9" t="n"/>
+      <c r="BF9" s="9" t="n"/>
+      <c r="BG9" s="12" t="n"/>
+      <c r="BH9" s="9" t="n"/>
+      <c r="BI9" s="9" t="n"/>
+      <c r="BJ9" s="12" t="n"/>
+      <c r="BK9" s="9" t="n"/>
+      <c r="BL9" s="9" t="n"/>
+      <c r="BM9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Causewayz Square</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>31100-1</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Exsim</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>3692</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>1409</v>
+      </c>
+      <c r="H10" s="11">
+        <f>G10/$E$10</f>
+        <v/>
+      </c>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>1406</v>
+      </c>
+      <c r="N10" s="12">
+        <f>M10/$E$10</f>
+        <v/>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>1403</v>
+      </c>
+      <c r="Q10" s="12">
+        <f>P10/$E$10</f>
+        <v/>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="T10" s="12">
+        <f>S10/$E$10</f>
+        <v/>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="W10" s="12">
+        <f>V10/$E$10</f>
+        <v/>
+      </c>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>1364</v>
+      </c>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AD10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AF10" s="12">
+        <f>AE10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK10" s="9" t="n">
+        <v>1341</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="9" t="n">
+        <v>1334</v>
+      </c>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n"/>
+      <c r="BD10" s="12" t="n"/>
+      <c r="BE10" s="9" t="n"/>
+      <c r="BF10" s="9" t="n"/>
+      <c r="BG10" s="12" t="n"/>
+      <c r="BH10" s="9" t="n"/>
+      <c r="BI10" s="9" t="n"/>
+      <c r="BJ10" s="12" t="n"/>
+      <c r="BK10" s="9" t="n"/>
+      <c r="BL10" s="9" t="n"/>
+      <c r="BM10" s="12" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>The Address</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>31074-1</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Maxim Global</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>2743</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>991</v>
+      </c>
+      <c r="H11" s="11">
+        <f>G11/$E$11</f>
+        <v/>
+      </c>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="N11" s="12">
+        <f>M11/$E$11</f>
+        <v/>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>989</v>
+      </c>
+      <c r="Q11" s="12">
+        <f>P11/$E$11</f>
+        <v/>
+      </c>
+      <c r="R11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" s="9" t="n">
+        <v>976</v>
+      </c>
+      <c r="T11" s="12">
+        <f>S11/$E$11</f>
+        <v/>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="W11" s="12">
+        <f>V11/$E$11</f>
+        <v/>
+      </c>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB11" s="9" t="n">
+        <v>963</v>
+      </c>
+      <c r="AC11" s="12">
+        <f>AB11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AF11" s="12">
+        <f>AE11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK11" s="9" t="n">
+        <v>943</v>
+      </c>
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n"/>
+      <c r="AQ11" s="9" t="n">
+        <v>936</v>
+      </c>
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="9" t="n"/>
+      <c r="AZ11" s="9" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="9" t="n"/>
+      <c r="BC11" s="9" t="n"/>
+      <c r="BD11" s="12" t="n"/>
+      <c r="BE11" s="9" t="n"/>
+      <c r="BF11" s="9" t="n"/>
+      <c r="BG11" s="12" t="n"/>
+      <c r="BH11" s="9" t="n"/>
+      <c r="BI11" s="9" t="n"/>
+      <c r="BJ11" s="12" t="n"/>
+      <c r="BK11" s="9" t="n"/>
+      <c r="BL11" s="9" t="n"/>
+      <c r="BM11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>M Grand Minori</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>9600-6</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Mah Sing</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>1733</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>726</v>
+      </c>
+      <c r="H12" s="11">
+        <f>G12/$E$12</f>
+        <v/>
+      </c>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>724</v>
+      </c>
+      <c r="N12" s="12">
+        <f>M12/$E$12</f>
+        <v/>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>714</v>
+      </c>
+      <c r="Q12" s="12">
+        <f>P12/$E$12</f>
+        <v/>
+      </c>
+      <c r="R12" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="S12" s="9" t="n">
+        <v>692</v>
+      </c>
+      <c r="T12" s="12">
+        <f>S12/$E$12</f>
+        <v/>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="W12" s="12">
+        <f>V12/$E$12</f>
+        <v/>
+      </c>
+      <c r="X12" s="9" t="n"/>
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="12" t="n"/>
+      <c r="AA12" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB12" s="9" t="n">
+        <v>665</v>
+      </c>
+      <c r="AC12" s="12">
+        <f>AB12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AF12" s="12">
+        <f>AE12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="9" t="n"/>
+      <c r="AH12" s="9" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK12" s="9" t="n">
+        <v>616</v>
+      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
+      <c r="AP12" s="9" t="n"/>
+      <c r="AQ12" s="9" t="n">
+        <v>610</v>
+      </c>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="12" t="n"/>
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="12" t="n"/>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="12" t="n"/>
+      <c r="BE12" s="9" t="n"/>
+      <c r="BF12" s="9" t="n"/>
+      <c r="BG12" s="12" t="n"/>
+      <c r="BH12" s="9" t="n"/>
+      <c r="BI12" s="9" t="n"/>
+      <c r="BJ12" s="12" t="n"/>
+      <c r="BK12" s="9" t="n"/>
+      <c r="BL12" s="9" t="n"/>
+      <c r="BM12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Skyline One</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>31031-1</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>TS Law</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1623</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>1391</v>
+      </c>
+      <c r="H13" s="11">
+        <f>G13/$E$13</f>
+        <v/>
+      </c>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>1389</v>
+      </c>
+      <c r="N13" s="12">
+        <f>M13/$E$13</f>
+        <v/>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>1387</v>
+      </c>
+      <c r="Q13" s="12">
+        <f>P13/$E$13</f>
+        <v/>
+      </c>
+      <c r="R13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" s="9" t="n">
+        <v>1381</v>
+      </c>
+      <c r="T13" s="12">
+        <f>S13/$E$13</f>
+        <v/>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="W13" s="12">
+        <f>V13/$E$13</f>
+        <v/>
+      </c>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="12" t="n"/>
+      <c r="AA13" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AC13" s="12">
+        <f>AB13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AF13" s="12">
+        <f>AE13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK13" s="9" t="n">
+        <v>1354</v>
+      </c>
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n"/>
+      <c r="AQ13" s="9" t="n">
+        <v>1351</v>
+      </c>
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="9" t="n"/>
+      <c r="AW13" s="9" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="9" t="n"/>
+      <c r="BC13" s="9" t="n"/>
+      <c r="BD13" s="12" t="n"/>
+      <c r="BE13" s="9" t="n"/>
+      <c r="BF13" s="9" t="n"/>
+      <c r="BG13" s="12" t="n"/>
+      <c r="BH13" s="9" t="n"/>
+      <c r="BI13" s="9" t="n"/>
+      <c r="BJ13" s="12" t="n"/>
+      <c r="BK13" s="9" t="n"/>
+      <c r="BL13" s="9" t="n"/>
+      <c r="BM13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Gen Sphere</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>30828-3</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Majestic Gen</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>996</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>901</v>
+      </c>
+      <c r="H14" s="11">
+        <f>G14/$E$14</f>
+        <v/>
+      </c>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>898</v>
+      </c>
+      <c r="N14" s="12">
+        <f>M14/$E$14</f>
+        <v/>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>898</v>
+      </c>
+      <c r="Q14" s="12">
+        <f>P14/$E$14</f>
+        <v/>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>890</v>
+      </c>
+      <c r="T14" s="12">
+        <f>S14/$E$14</f>
+        <v/>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="W14" s="12">
+        <f>V14/$E$14</f>
+        <v/>
+      </c>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="12" t="n"/>
+      <c r="AA14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>887</v>
+      </c>
+      <c r="AC14" s="12">
+        <f>AB14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AF14" s="12">
+        <f>AE14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK14" s="9" t="n">
+        <v>877</v>
+      </c>
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n">
+        <v>873</v>
+      </c>
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="9" t="n"/>
+      <c r="AZ14" s="9" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="9" t="n"/>
+      <c r="BC14" s="9" t="n"/>
+      <c r="BD14" s="12" t="n"/>
+      <c r="BE14" s="9" t="n"/>
+      <c r="BF14" s="9" t="n"/>
+      <c r="BG14" s="12" t="n"/>
+      <c r="BH14" s="9" t="n"/>
+      <c r="BI14" s="9" t="n"/>
+      <c r="BJ14" s="12" t="n"/>
+      <c r="BK14" s="9" t="n"/>
+      <c r="BL14" s="9" t="n"/>
+      <c r="BM14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>The Eclipse</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Chin Hin</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1116</v>
+      </c>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="12" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="12" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="12" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="12" t="n"/>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="9" t="n"/>
+      <c r="AC15" s="12" t="n"/>
+      <c r="AD15" s="9" t="n"/>
+      <c r="AE15" s="9" t="n"/>
+      <c r="AF15" s="12" t="n"/>
+      <c r="AG15" s="9" t="n"/>
+      <c r="AH15" s="9" t="n"/>
+      <c r="AI15" s="12" t="n"/>
+      <c r="AJ15" s="9" t="n"/>
+      <c r="AK15" s="9" t="n"/>
+      <c r="AL15" s="12" t="n"/>
+      <c r="AM15" s="9" t="n"/>
+      <c r="AN15" s="9" t="n"/>
+      <c r="AO15" s="12" t="n"/>
+      <c r="AP15" s="9" t="n"/>
+      <c r="AQ15" s="9" t="n"/>
+      <c r="AR15" s="12" t="n"/>
+      <c r="AS15" s="9" t="n"/>
+      <c r="AT15" s="9" t="n"/>
+      <c r="AU15" s="12" t="n"/>
+      <c r="AV15" s="9" t="n"/>
+      <c r="AW15" s="9" t="n"/>
+      <c r="AX15" s="12" t="n"/>
+      <c r="AY15" s="9" t="n"/>
+      <c r="AZ15" s="9" t="n"/>
+      <c r="BA15" s="12" t="n"/>
+      <c r="BB15" s="9" t="n"/>
+      <c r="BC15" s="9" t="n"/>
+      <c r="BD15" s="12" t="n"/>
+      <c r="BE15" s="9" t="n"/>
+      <c r="BF15" s="9" t="n"/>
+      <c r="BG15" s="12" t="n"/>
+      <c r="BH15" s="9" t="n"/>
+      <c r="BI15" s="9" t="n"/>
+      <c r="BJ15" s="12" t="n"/>
+      <c r="BK15" s="9" t="n"/>
+      <c r="BL15" s="9" t="n"/>
+      <c r="BM15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Amberwood</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>13531-2</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Chin Hin</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>824</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>710</v>
+      </c>
+      <c r="H16" s="11">
+        <f>G16/$E$16</f>
+        <v/>
+      </c>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>710</v>
+      </c>
+      <c r="N16" s="12">
+        <f>M16/$E$16</f>
+        <v/>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>707</v>
+      </c>
+      <c r="Q16" s="12">
+        <f>P16/$E$16</f>
+        <v/>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>700</v>
+      </c>
+      <c r="T16" s="12">
+        <f>S16/$E$16</f>
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="W16" s="12">
+        <f>V16/$E$16</f>
+        <v/>
+      </c>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>692</v>
+      </c>
+      <c r="AC16" s="12">
+        <f>AB16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AF16" s="12">
+        <f>AE16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>682</v>
+      </c>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n">
+        <v>684</v>
+      </c>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="12" t="n"/>
+      <c r="BE16" s="9" t="n"/>
+      <c r="BF16" s="9" t="n"/>
+      <c r="BG16" s="12" t="n"/>
+      <c r="BH16" s="9" t="n"/>
+      <c r="BI16" s="9" t="n"/>
+      <c r="BJ16" s="12" t="n"/>
+      <c r="BK16" s="9" t="n"/>
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Sunway Majestic</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>31034-1</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Sunway/Majestic Gen</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>384</v>
+      </c>
+      <c r="H17" s="11">
+        <f>G17/$E$17</f>
+        <v/>
+      </c>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>382</v>
+      </c>
+      <c r="N17" s="12">
+        <f>M17/$E$17</f>
+        <v/>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q17" s="12">
+        <f>P17/$E$17</f>
+        <v/>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" s="9" t="n">
+        <v>373</v>
+      </c>
+      <c r="T17" s="12">
+        <f>S17/$E$17</f>
+        <v/>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="W17" s="12">
+        <f>V17/$E$17</f>
+        <v/>
+      </c>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="12" t="n"/>
+      <c r="AA17" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AC17" s="12">
+        <f>AB17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AF17" s="12">
+        <f>AE17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AL17" s="12">
+        <f>AK17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AM17" s="9" t="n"/>
+      <c r="AN17" s="9" t="n"/>
+      <c r="AO17" s="12" t="n"/>
+      <c r="AP17" s="9" t="n"/>
+      <c r="AQ17" s="9" t="n">
+        <v>358</v>
+      </c>
+      <c r="AR17" s="12">
+        <f>AQ17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AS17" s="9" t="n"/>
+      <c r="AT17" s="9" t="n"/>
+      <c r="AU17" s="12" t="n"/>
+      <c r="AV17" s="9" t="n"/>
+      <c r="AW17" s="9" t="n"/>
+      <c r="AX17" s="12" t="n"/>
+      <c r="AY17" s="9" t="n"/>
+      <c r="AZ17" s="9" t="n"/>
+      <c r="BA17" s="12" t="n"/>
+      <c r="BB17" s="9" t="n"/>
+      <c r="BC17" s="9" t="n"/>
+      <c r="BD17" s="12" t="n"/>
+      <c r="BE17" s="9" t="n"/>
+      <c r="BF17" s="9" t="n"/>
+      <c r="BG17" s="12" t="n"/>
+      <c r="BH17" s="9" t="n"/>
+      <c r="BI17" s="9" t="n"/>
+      <c r="BJ17" s="12" t="n"/>
+      <c r="BK17" s="9" t="n"/>
+      <c r="BL17" s="9" t="n"/>
+      <c r="BM17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Calia</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>31149-1</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>PGB</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>1274</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>285</v>
+      </c>
+      <c r="H18" s="11">
+        <f>G18/$E$18</f>
+        <v/>
+      </c>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="N18" s="12">
+        <f>M18/$E$18</f>
+        <v/>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q18" s="12">
+        <f>P18/$E$18</f>
+        <v/>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" s="9" t="n">
+        <v>275</v>
+      </c>
+      <c r="T18" s="12">
+        <f>S18/$E$18</f>
+        <v/>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="W18" s="12">
+        <f>V18/$E$18</f>
+        <v/>
+      </c>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="12" t="n"/>
+      <c r="AA18" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB18" s="9" t="n">
+        <v>266</v>
+      </c>
+      <c r="AC18" s="12">
+        <f>AB18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AF18" s="12">
+        <f>AE18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="9" t="n"/>
+      <c r="AI18" s="12" t="n"/>
+      <c r="AJ18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AL18" s="12">
+        <f>AK18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="9" t="n"/>
+      <c r="AO18" s="12" t="n"/>
+      <c r="AP18" s="9" t="n"/>
+      <c r="AQ18" s="9" t="n">
+        <v>249</v>
+      </c>
+      <c r="AR18" s="12">
+        <f>AQ18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="9" t="n"/>
+      <c r="AU18" s="12" t="n"/>
+      <c r="AV18" s="9" t="n"/>
+      <c r="AW18" s="9" t="n"/>
+      <c r="AX18" s="12" t="n"/>
+      <c r="AY18" s="9" t="n"/>
+      <c r="AZ18" s="9" t="n"/>
+      <c r="BA18" s="12" t="n"/>
+      <c r="BB18" s="9" t="n"/>
+      <c r="BC18" s="9" t="n"/>
+      <c r="BD18" s="12" t="n"/>
+      <c r="BE18" s="9" t="n"/>
+      <c r="BF18" s="9" t="n"/>
+      <c r="BG18" s="12" t="n"/>
+      <c r="BH18" s="9" t="n"/>
+      <c r="BI18" s="9" t="n"/>
+      <c r="BJ18" s="12" t="n"/>
+      <c r="BK18" s="9" t="n"/>
+      <c r="BL18" s="9" t="n"/>
+      <c r="BM18" s="12" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="BB3:BD3"/>
+    <mergeCell ref="AV3:AX3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="BH3:BJ3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 11/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 12/08/2026</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -1806,7 +1806,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 11/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
@@ -2698,10 +2698,10 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
@@ -2891,10 +2891,10 @@
         <v>1218</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H9" s="11">
         <f>G9/$E$9</f>
@@ -3084,10 +3084,10 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -3470,10 +3470,10 @@
         <v>299</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
@@ -4559,7 +4559,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 11/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 12/08/2026</t>
         </is>
       </c>
     </row>
@@ -4977,10 +4977,10 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
@@ -5409,10 +5409,10 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
@@ -5697,10 +5697,10 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -5985,10 +5985,10 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
@@ -6788,10 +6788,10 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>416</v>
+        <v>1500</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>0</v>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -555,6 +555,9 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,63 +576,66 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46246</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -957,6 +963,21 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BN4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BO4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -995,7 +1016,7 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>42</v>
@@ -1008,49 +1029,56 @@
         <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="12" t="n"/>
-      <c r="U5" s="9" t="n">
+      <c r="R5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="T5" s="12">
+        <f>S5/$E$5</f>
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="Y5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="W5" s="12">
-        <f>V5/$E$5</f>
-        <v/>
-      </c>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="12" t="n"/>
+      <c r="Z5" s="12">
+        <f>Y5/$E$5</f>
+        <v/>
+      </c>
       <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n">
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="12" t="n"/>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AC5" s="12">
-        <f>AB5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="12" t="n"/>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
       <c r="AG5" s="9" t="n"/>
       <c r="AH5" s="9" t="n"/>
       <c r="AI5" s="12" t="n"/>
@@ -1084,6 +1112,9 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n"/>
+      <c r="BO5" s="9" t="n"/>
+      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1147,33 +1178,40 @@
         <f>P6/$E$6</f>
         <v/>
       </c>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="9" t="n">
+      <c r="R6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="T6" s="12">
+        <f>S6/$E$6</f>
+        <v/>
+      </c>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="Y6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="W6" s="12">
-        <f>V6/$E$6</f>
-        <v/>
-      </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
       <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n">
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
       <c r="AG6" s="9" t="n"/>
       <c r="AH6" s="9" t="n"/>
       <c r="AI6" s="12" t="n"/>
@@ -1207,6 +1245,9 @@
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n"/>
+      <c r="BP6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1231,7 +1272,7 @@
         <v>490</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>45</v>
@@ -1241,62 +1282,69 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="12" t="n"/>
-      <c r="U7" s="9" t="n">
+      <c r="R7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="T7" s="12">
+        <f>S7/$E$7</f>
+        <v/>
+      </c>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="Y7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="W7" s="12">
-        <f>V7/$E$7</f>
-        <v/>
-      </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
       <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n">
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
       <c r="AG7" s="9" t="n"/>
       <c r="AH7" s="9" t="n"/>
       <c r="AI7" s="12" t="n"/>
@@ -1330,6 +1378,9 @@
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n"/>
+      <c r="BP7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1393,33 +1444,40 @@
         <f>P8/$E$8</f>
         <v/>
       </c>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="12" t="n"/>
-      <c r="U8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="9" t="n">
+      <c r="R8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="W8" s="12">
-        <f>V8/$E$8</f>
-        <v/>
-      </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
+      <c r="T8" s="12">
+        <f>S8/$E$8</f>
+        <v/>
+      </c>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
       <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n">
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
       <c r="AG8" s="9" t="n"/>
       <c r="AH8" s="9" t="n"/>
       <c r="AI8" s="12" t="n"/>
@@ -1453,6 +1511,9 @@
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n"/>
+      <c r="BP8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1507,7 +1568,7 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>1</v>
@@ -1516,33 +1577,40 @@
         <f>P9/$E$9</f>
         <v/>
       </c>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="12" t="n"/>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="12">
-        <f>V9/$E$9</f>
-        <v/>
-      </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
+      <c r="R9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="12">
+        <f>S9/$E$9</f>
+        <v/>
+      </c>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
       <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
       <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
+      <c r="AE9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
       <c r="AG9" s="9" t="n"/>
       <c r="AH9" s="9" t="n"/>
       <c r="AI9" s="12" t="n"/>
@@ -1576,6 +1644,9 @@
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n"/>
+      <c r="BP9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1600,59 +1671,66 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="9" t="n"/>
-      <c r="T10" s="12" t="n"/>
+      <c r="R10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="T10" s="12">
+        <f>S10/$E$10</f>
+        <v/>
+      </c>
       <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="W10" s="12">
-        <f>V10/$E$10</f>
-        <v/>
-      </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
       <c r="AA10" s="9" t="n"/>
       <c r="AB10" s="9" t="n"/>
       <c r="AC10" s="12" t="n"/>
@@ -1692,9 +1770,13 @@
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n"/>
       <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n"/>
+      <c r="BP10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -1726,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1794,6 +1876,9 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1812,63 +1897,66 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46246</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2196,6 +2284,21 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BN4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BO4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2223,17 +2326,24 @@
       <c r="E5" s="9" t="n">
         <v>1310</v>
       </c>
-      <c r="F5" s="10" t="n"/>
+      <c r="F5" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="G5" s="10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
       <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="12" t="n"/>
+      <c r="J5" s="9" t="n">
+        <v>174</v>
+      </c>
+      <c r="K5" s="12">
+        <f>J5/$E$5</f>
+        <v/>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="12" t="n"/>
@@ -2288,6 +2398,9 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n"/>
+      <c r="BO5" s="9" t="n"/>
+      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2312,173 +2425,183 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="12" t="n"/>
-      <c r="X6" s="9" t="n">
+      <c r="U6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="W6" s="12">
+        <f>V6/$E$6</f>
+        <v/>
+      </c>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="12" t="n"/>
+      <c r="AA6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="AB6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="Z6" s="12">
-        <f>Y6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
       <c r="AD6" s="9" t="n"/>
       <c r="AE6" s="9" t="n"/>
       <c r="AF6" s="12" t="n"/>
-      <c r="AG6" s="9" t="n">
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
       <c r="AY6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AZ6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
       <c r="BB6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BC6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
-      <c r="BK6" s="9" t="n"/>
+      <c r="BK6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="BL6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="BP6" s="12">
+        <f>BO6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -2505,7 +2628,7 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>116</v>
@@ -2515,102 +2638,102 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="9" t="n">
+      <c r="U7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="W7" s="12">
+        <f>V7/$E$7</f>
+        <v/>
+      </c>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="12" t="n"/>
+      <c r="AA7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="AB7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="Z7" s="12">
-        <f>Y7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
       <c r="AD7" s="9" t="n"/>
       <c r="AE7" s="9" t="n"/>
       <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="9" t="n">
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AH7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
@@ -2620,58 +2743,68 @@
         <v>6</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
       <c r="AY7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AZ7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
         <v/>
       </c>
       <c r="BB7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
-      <c r="BK7" s="9" t="n"/>
+      <c r="BK7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="BL7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BP7" s="12">
+        <f>BO7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -2698,102 +2831,102 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="12" t="n"/>
-      <c r="X8" s="9" t="n">
+      <c r="U8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="W8" s="12">
+        <f>V8/$E$8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="AB8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="Z8" s="12">
-        <f>Y8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
       <c r="AD8" s="9" t="n"/>
       <c r="AE8" s="9" t="n"/>
       <c r="AF8" s="12" t="n"/>
-      <c r="AG8" s="9" t="n">
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AH8" s="9" t="n">
+      <c r="AK8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AQ8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
@@ -2803,68 +2936,78 @@
         <v>7</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
       <c r="AV8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
       <c r="AY8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AZ8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
         <v/>
       </c>
       <c r="BB8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BC8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
-      <c r="BK8" s="9" t="n"/>
+      <c r="BK8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="BL8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="BP8" s="12">
+        <f>BO8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -2894,24 +3037,24 @@
         <v>2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="H9" s="11">
         <f>G9/$E$9</f>
         <v/>
       </c>
       <c r="I9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K9" s="12">
         <f>J9/$E$9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>1119</v>
@@ -2921,17 +3064,17 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="Q9" s="12">
         <f>P9/$E$9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>1117</v>
@@ -2940,124 +3083,134 @@
         <f>S9/$E$9</f>
         <v/>
       </c>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="9" t="n">
+      <c r="U9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="W9" s="12">
+        <f>V9/$E$9</f>
+        <v/>
+      </c>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="9" t="n">
+      <c r="AB9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="Z9" s="12">
-        <f>Y9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
       <c r="AD9" s="9" t="n"/>
       <c r="AE9" s="9" t="n"/>
       <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="9" t="n">
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AH9" s="9" t="n">
+      <c r="AK9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AQ9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AP9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="AR9" s="12">
         <f>AQ9/$E$9</f>
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AU9" s="12">
         <f>AT9/$E$9</f>
         <v/>
       </c>
       <c r="AV9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="AX9" s="12">
         <f>AW9/$E$9</f>
         <v/>
       </c>
       <c r="AY9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AZ9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BA9" s="12">
         <f>AZ9/$E$9</f>
         <v/>
       </c>
       <c r="BB9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
-      <c r="BK9" s="9" t="n"/>
+      <c r="BK9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="BL9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="BP9" s="12">
+        <f>BO9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3084,27 +3237,27 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>491</v>
@@ -3114,79 +3267,79 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
-      <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
-      <c r="W10" s="12" t="n"/>
-      <c r="X10" s="9" t="n">
+      <c r="U10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="W10" s="12">
+        <f>V10/$E$10</f>
+        <v/>
+      </c>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="AB10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="Z10" s="12">
-        <f>Y10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
       <c r="AD10" s="9" t="n"/>
       <c r="AE10" s="9" t="n"/>
       <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="9" t="n">
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH10" s="9" t="n">
+      <c r="AK10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AI10" s="12">
-        <f>AH10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AQ10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT10" s="9" t="n">
         <v>462</v>
@@ -3199,58 +3352,68 @@
         <v>2</v>
       </c>
       <c r="AW10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
       <c r="AY10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BA10" s="12">
         <f>AZ10/$E$10</f>
         <v/>
       </c>
       <c r="BB10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BC10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BD10" s="12">
         <f>BC10/$E$10</f>
         <v/>
       </c>
       <c r="BE10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BF10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
-      <c r="BK10" s="9" t="n"/>
+      <c r="BK10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="BL10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="BP10" s="12">
+        <f>BO10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -3277,7 +3440,7 @@
         <v>482</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>467</v>
@@ -3290,17 +3453,17 @@
         <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
@@ -3326,60 +3489,60 @@
         <f>S11/$E$11</f>
         <v/>
       </c>
-      <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
-      <c r="W11" s="12" t="n"/>
-      <c r="X11" s="9" t="n">
+      <c r="U11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="W11" s="12">
+        <f>V11/$E$11</f>
+        <v/>
+      </c>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="AB11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="Z11" s="12">
-        <f>Y11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="12" t="n"/>
+      <c r="AC11" s="12">
+        <f>AB11/$E$11</f>
+        <v/>
+      </c>
       <c r="AD11" s="9" t="n"/>
       <c r="AE11" s="9" t="n"/>
       <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="9" t="n">
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AI11" s="12">
-        <f>AH11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AQ11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" s="9" t="n">
         <v>463</v>
@@ -3389,40 +3552,40 @@
         <v/>
       </c>
       <c r="AV11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AX11" s="12">
         <f>AW11/$E$11</f>
         <v/>
       </c>
       <c r="AY11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BA11" s="12">
         <f>AZ11/$E$11</f>
         <v/>
       </c>
       <c r="BB11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
@@ -3432,18 +3595,28 @@
         <v>2</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
         <v/>
       </c>
-      <c r="BK11" s="9" t="n"/>
+      <c r="BK11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="BL11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BN11" s="9" t="n"/>
+      <c r="BO11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="BP11" s="12">
+        <f>BO11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -3470,7 +3643,7 @@
         <v>299</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>236</v>
@@ -3480,17 +3653,17 @@
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>235</v>
@@ -3500,10 +3673,10 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
@@ -3519,48 +3692,48 @@
         <f>S12/$E$12</f>
         <v/>
       </c>
-      <c r="U12" s="9" t="n"/>
-      <c r="V12" s="9" t="n"/>
-      <c r="W12" s="12" t="n"/>
-      <c r="X12" s="9" t="n">
+      <c r="U12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="W12" s="12">
+        <f>V12/$E$12</f>
+        <v/>
+      </c>
+      <c r="X12" s="9" t="n"/>
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="12" t="n"/>
+      <c r="AA12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="Y12" s="9" t="n">
+      <c r="AB12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="Z12" s="12">
-        <f>Y12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="9" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="12" t="n"/>
+      <c r="AC12" s="12">
+        <f>AB12/$E$12</f>
+        <v/>
+      </c>
       <c r="AD12" s="9" t="n"/>
       <c r="AE12" s="9" t="n"/>
       <c r="AF12" s="12" t="n"/>
-      <c r="AG12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="9" t="n">
+      <c r="AG12" s="9" t="n"/>
+      <c r="AH12" s="9" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AI12" s="12">
-        <f>AH12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
       <c r="AP12" s="9" t="n">
         <v>0</v>
       </c>
@@ -3602,7 +3775,7 @@
         <v/>
       </c>
       <c r="BB12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC12" s="9" t="n">
         <v>236</v>
@@ -3612,31 +3785,41 @@
         <v/>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BF12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BG12" s="12">
         <f>BF12/$E$12</f>
         <v/>
       </c>
       <c r="BH12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="BI12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BJ12" s="12">
         <f>BI12/$E$12</f>
         <v/>
       </c>
-      <c r="BK12" s="9" t="n"/>
+      <c r="BK12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="BL12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="BM12" s="12">
         <f>BL12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BN12" s="9" t="n"/>
+      <c r="BO12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BP12" s="12">
+        <f>BO12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -3663,132 +3846,132 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
-      <c r="U13" s="9" t="n"/>
-      <c r="V13" s="9" t="n"/>
-      <c r="W13" s="12" t="n"/>
-      <c r="X13" s="9" t="n">
+      <c r="U13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="W13" s="12">
+        <f>V13/$E$13</f>
+        <v/>
+      </c>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="12" t="n"/>
+      <c r="AA13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="AB13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="Z13" s="12">
-        <f>Y13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="12" t="n"/>
+      <c r="AC13" s="12">
+        <f>AB13/$E$13</f>
+        <v/>
+      </c>
       <c r="AD13" s="9" t="n"/>
       <c r="AE13" s="9" t="n"/>
       <c r="AF13" s="12" t="n"/>
-      <c r="AG13" s="9" t="n">
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AH13" s="9" t="n">
+      <c r="AK13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AI13" s="12">
-        <f>AH13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AQ13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AP13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
       <c r="AV13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
       <c r="AY13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AZ13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
@@ -3798,38 +3981,48 @@
         <v>4</v>
       </c>
       <c r="BC13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
-      <c r="BK13" s="9" t="n"/>
+      <c r="BK13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="BL13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BN13" s="9" t="n"/>
+      <c r="BO13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="BP13" s="12">
+        <f>BO13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -3856,7 +4049,7 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1142</v>
@@ -3866,122 +4059,122 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
-      <c r="U14" s="9" t="n"/>
-      <c r="V14" s="9" t="n"/>
-      <c r="W14" s="12" t="n"/>
-      <c r="X14" s="9" t="n">
+      <c r="U14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="W14" s="12">
+        <f>V14/$E$14</f>
+        <v/>
+      </c>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="12" t="n"/>
+      <c r="AA14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="Y14" s="9" t="n">
+      <c r="AB14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="Z14" s="12">
-        <f>Y14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="9" t="n"/>
-      <c r="AB14" s="9" t="n"/>
-      <c r="AC14" s="12" t="n"/>
+      <c r="AC14" s="12">
+        <f>AB14/$E$14</f>
+        <v/>
+      </c>
       <c r="AD14" s="9" t="n"/>
       <c r="AE14" s="9" t="n"/>
       <c r="AF14" s="12" t="n"/>
-      <c r="AG14" s="9" t="n">
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AH14" s="9" t="n">
+      <c r="AK14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AI14" s="12">
-        <f>AH14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AQ14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AP14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
       <c r="AV14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
       <c r="AY14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="AZ14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
@@ -4017,12 +4210,22 @@
         <f>BI14/$E$14</f>
         <v/>
       </c>
-      <c r="BK14" s="9" t="n"/>
+      <c r="BK14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BL14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BM14" s="12">
         <f>BL14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BN14" s="9" t="n"/>
+      <c r="BO14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" s="12">
+        <f>BO14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -4049,27 +4252,27 @@
         <v>551</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H15" s="11">
         <f>G15/$E$15</f>
         <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K15" s="12">
         <f>J15/$E$15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
         <v>124</v>
@@ -4079,17 +4282,17 @@
         <v/>
       </c>
       <c r="O15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>121</v>
@@ -4098,53 +4301,53 @@
         <f>S15/$E$15</f>
         <v/>
       </c>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="9" t="n"/>
-      <c r="W15" s="12" t="n"/>
-      <c r="X15" s="9" t="n">
+      <c r="U15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="W15" s="12">
+        <f>V15/$E$15</f>
+        <v/>
+      </c>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="12" t="n"/>
+      <c r="AA15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="AB15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="Z15" s="12">
-        <f>Y15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AA15" s="9" t="n"/>
-      <c r="AB15" s="9" t="n"/>
-      <c r="AC15" s="12" t="n"/>
+      <c r="AC15" s="12">
+        <f>AB15/$E$15</f>
+        <v/>
+      </c>
       <c r="AD15" s="9" t="n"/>
       <c r="AE15" s="9" t="n"/>
       <c r="AF15" s="12" t="n"/>
-      <c r="AG15" s="9" t="n">
+      <c r="AG15" s="9" t="n"/>
+      <c r="AH15" s="9" t="n"/>
+      <c r="AI15" s="12" t="n"/>
+      <c r="AJ15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AH15" s="9" t="n">
+      <c r="AK15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AI15" s="12">
-        <f>AH15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="9" t="n"/>
-      <c r="AK15" s="9" t="n"/>
-      <c r="AL15" s="12" t="n"/>
-      <c r="AM15" s="9" t="n">
+      <c r="AL15" s="12">
+        <f>AK15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AM15" s="9" t="n"/>
+      <c r="AN15" s="9" t="n"/>
+      <c r="AO15" s="12" t="n"/>
+      <c r="AP15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN15" s="9" t="n">
+      <c r="AQ15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="AO15" s="12">
-        <f>AN15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AP15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="AR15" s="12">
         <f>AQ15/$E$15</f>
@@ -4154,24 +4357,24 @@
         <v>3</v>
       </c>
       <c r="AT15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AU15" s="12">
         <f>AT15/$E$15</f>
         <v/>
       </c>
       <c r="AV15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AX15" s="12">
         <f>AW15/$E$15</f>
         <v/>
       </c>
       <c r="AY15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AZ15" s="9" t="n">
         <v>76</v>
@@ -4181,10 +4384,10 @@
         <v/>
       </c>
       <c r="BB15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BC15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BD15" s="12">
         <f>BC15/$E$15</f>
@@ -4210,12 +4413,22 @@
         <f>BI15/$E$15</f>
         <v/>
       </c>
-      <c r="BK15" s="9" t="n"/>
+      <c r="BK15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BL15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BM15" s="12">
         <f>BL15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BN15" s="9" t="n"/>
+      <c r="BO15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="12">
+        <f>BO15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -4291,51 +4504,58 @@
         <f>S16/$E$16</f>
         <v/>
       </c>
-      <c r="U16" s="9" t="n"/>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="9" t="n">
+      <c r="U16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="Z16" s="12">
-        <f>Y16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="9" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="12" t="n"/>
+      <c r="W16" s="12">
+        <f>V16/$E$16</f>
+        <v/>
+      </c>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AC16" s="12">
+        <f>AB16/$E$16</f>
+        <v/>
+      </c>
       <c r="AD16" s="9" t="n"/>
       <c r="AE16" s="9" t="n"/>
       <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="9" t="n">
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AI16" s="12">
-        <f>AH16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AQ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
       <c r="AS16" s="9" t="n"/>
       <c r="AT16" s="9" t="n"/>
       <c r="AU16" s="12" t="n"/>
@@ -4355,11 +4575,14 @@
       <c r="BI16" s="9" t="n"/>
       <c r="BJ16" s="12" t="n"/>
       <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" s="12">
-        <f>BL16/$E$16</f>
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n"/>
+      <c r="BO16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" s="12">
+        <f>BO16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -4445,9 +4668,13 @@
       <c r="BK17" s="9" t="n"/>
       <c r="BL17" s="9" t="n"/>
       <c r="BM17" s="12" t="n"/>
+      <c r="BN17" s="9" t="n"/>
+      <c r="BO17" s="9" t="n"/>
+      <c r="BP17" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -4479,7 +4706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM18"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4547,6 +4774,9 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4565,63 +4795,66 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46246</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -4949,6 +5182,21 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BN4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BO4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -4977,7 +5225,7 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>296</v>
@@ -4986,99 +5234,106 @@
         <f>G5/$E$5</f>
         <v/>
       </c>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="9" t="n">
+      <c r="I5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="K5" s="12">
+        <f>J5/$E$5</f>
+        <v/>
+      </c>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="P5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="N5" s="12">
-        <f>M5/$E$5</f>
-        <v/>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="12" t="n"/>
-      <c r="AA5" s="9" t="n">
+      <c r="X5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="Z5" s="12">
+        <f>Y5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="12" t="n"/>
+      <c r="AD5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="9" t="n">
+      <c r="AE5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AC5" s="12">
-        <f>AB5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AE5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
-      <c r="AJ5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="9" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AN5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="AL5" s="12">
-        <f>AK5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
       <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n">
+      <c r="AQ5" s="9" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="AR5" s="12">
-        <f>AQ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
       <c r="AV5" s="9" t="n"/>
       <c r="AW5" s="9" t="n"/>
       <c r="AX5" s="12" t="n"/>
@@ -5097,6 +5352,9 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n"/>
+      <c r="BO5" s="9" t="n"/>
+      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -5121,108 +5379,115 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="9" t="n">
+      <c r="I6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>937</v>
+      </c>
+      <c r="K6" s="12">
+        <f>J6/$E$6</f>
+        <v/>
+      </c>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="P6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="N6" s="12">
-        <f>M6/$E$6</f>
-        <v/>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
-      <c r="AA6" s="9" t="n">
+      <c r="X6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AB6" s="9" t="n">
+      <c r="AE6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AD6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AN6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
       <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n">
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
       <c r="AV6" s="9" t="n"/>
       <c r="AW6" s="9" t="n"/>
       <c r="AX6" s="12" t="n"/>
@@ -5241,6 +5506,9 @@
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n"/>
+      <c r="BP6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -5274,99 +5542,106 @@
         <f>G7/$E$7</f>
         <v/>
       </c>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="9" t="n">
+      <c r="I7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="K7" s="12">
+        <f>J7/$E$7</f>
+        <v/>
+      </c>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="P7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="N7" s="12">
-        <f>M7/$E$7</f>
-        <v/>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="9" t="n">
+      <c r="X7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AB7" s="9" t="n">
+      <c r="Y7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AD7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AN7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
       <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n">
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
       <c r="AV7" s="9" t="n"/>
       <c r="AW7" s="9" t="n"/>
       <c r="AX7" s="12" t="n"/>
@@ -5385,6 +5660,9 @@
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n"/>
+      <c r="BP7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5409,7 +5687,7 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1052</v>
@@ -5418,99 +5696,106 @@
         <f>G8/$E$8</f>
         <v/>
       </c>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="9" t="n">
+      <c r="I8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="J8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="K8" s="12">
+        <f>J8/$E$8</f>
+        <v/>
+      </c>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="N8" s="12">
-        <f>M8/$E$8</f>
-        <v/>
-      </c>
-      <c r="O8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
-      <c r="AA8" s="9" t="n">
+      <c r="X8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AB8" s="9" t="n">
+      <c r="AE8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AD8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AN8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
       <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n">
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
       <c r="AV8" s="9" t="n"/>
       <c r="AW8" s="9" t="n"/>
       <c r="AX8" s="12" t="n"/>
@@ -5529,6 +5814,9 @@
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n"/>
+      <c r="BP8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -5562,19 +5850,19 @@
         <f>G9/$E$9</f>
         <v/>
       </c>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9" t="n">
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="N9" s="12">
-        <f>M9/$E$9</f>
-        <v/>
-      </c>
+      <c r="K9" s="12">
+        <f>J9/$E$9</f>
+        <v/>
+      </c>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5586,7 +5874,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>845</v>
@@ -5596,28 +5884,28 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
         <v/>
       </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9" t="n">
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
       <c r="AD9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5628,33 +5916,40 @@
         <f>AE9/$E$9</f>
         <v/>
       </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AG9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
       <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n">
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
       <c r="AV9" s="9" t="n"/>
       <c r="AW9" s="9" t="n"/>
       <c r="AX9" s="12" t="n"/>
@@ -5673,6 +5968,9 @@
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n"/>
+      <c r="BP9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -5697,108 +5995,115 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="9" t="n">
+      <c r="I10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1411</v>
+      </c>
+      <c r="K10" s="12">
+        <f>J10/$E$10</f>
+        <v/>
+      </c>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="P10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="N10" s="12">
-        <f>M10/$E$10</f>
-        <v/>
-      </c>
-      <c r="O10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="P10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="9" t="n">
+      <c r="X10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AB10" s="9" t="n">
+      <c r="AE10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AC10" s="12">
-        <f>AB10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AD10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AG10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AH10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
       <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n">
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
       <c r="AV10" s="9" t="n"/>
       <c r="AW10" s="9" t="n"/>
       <c r="AX10" s="12" t="n"/>
@@ -5817,6 +6122,9 @@
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n"/>
       <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n"/>
+      <c r="BP10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -5841,108 +6149,115 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
         <v/>
       </c>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="9" t="n">
+      <c r="I11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="J11" s="9" t="n">
+        <v>991</v>
+      </c>
+      <c r="K11" s="12">
+        <f>J11/$E$11</f>
+        <v/>
+      </c>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="N11" s="12">
-        <f>M11/$E$11</f>
-        <v/>
-      </c>
-      <c r="O11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="P11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
         <v/>
       </c>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="9" t="n">
+      <c r="X11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="Z11" s="12">
+        <f>Y11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AB11" s="9" t="n">
+      <c r="AE11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AC11" s="12">
-        <f>AB11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AD11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
         <v/>
       </c>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AN11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
       <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n">
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="AR11" s="12">
-        <f>AQ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
       <c r="AV11" s="9" t="n"/>
       <c r="AW11" s="9" t="n"/>
       <c r="AX11" s="12" t="n"/>
@@ -5961,6 +6276,9 @@
       <c r="BK11" s="9" t="n"/>
       <c r="BL11" s="9" t="n"/>
       <c r="BM11" s="12" t="n"/>
+      <c r="BN11" s="9" t="n"/>
+      <c r="BO11" s="9" t="n"/>
+      <c r="BP11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -5985,108 +6303,115 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
         <v/>
       </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="9" t="n">
+      <c r="I12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>727</v>
+      </c>
+      <c r="K12" s="12">
+        <f>J12/$E$12</f>
+        <v/>
+      </c>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="P12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="N12" s="12">
-        <f>M12/$E$12</f>
-        <v/>
-      </c>
-      <c r="O12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="9" t="n"/>
-      <c r="Z12" s="12" t="n"/>
-      <c r="AA12" s="9" t="n">
+      <c r="X12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="Z12" s="12">
+        <f>Y12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="9" t="n"/>
+      <c r="AC12" s="12" t="n"/>
+      <c r="AD12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AB12" s="9" t="n">
+      <c r="AE12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AC12" s="12">
-        <f>AB12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AD12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AN12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
       <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n">
+      <c r="AQ12" s="9" t="n"/>
+      <c r="AR12" s="12" t="n"/>
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="AR12" s="12">
-        <f>AQ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
       <c r="AV12" s="9" t="n"/>
       <c r="AW12" s="9" t="n"/>
       <c r="AX12" s="12" t="n"/>
@@ -6105,6 +6430,9 @@
       <c r="BK12" s="9" t="n"/>
       <c r="BL12" s="9" t="n"/>
       <c r="BM12" s="12" t="n"/>
+      <c r="BN12" s="9" t="n"/>
+      <c r="BO12" s="9" t="n"/>
+      <c r="BP12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -6129,7 +6457,7 @@
         <v>1623</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>1391</v>
@@ -6138,99 +6466,106 @@
         <f>G13/$E$13</f>
         <v/>
       </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="9" t="n">
+      <c r="I13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="J13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="K13" s="12">
+        <f>J13/$E$13</f>
+        <v/>
+      </c>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="N13" s="12">
-        <f>M13/$E$13</f>
-        <v/>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="9" t="n">
+      <c r="X13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="Z13" s="12">
+        <f>Y13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="12" t="n"/>
+      <c r="AD13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AB13" s="9" t="n">
+      <c r="AE13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AC13" s="12">
-        <f>AB13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
+      <c r="AM13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AN13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
       <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n">
+      <c r="AQ13" s="9" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="AR13" s="12">
-        <f>AQ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
       <c r="AV13" s="9" t="n"/>
       <c r="AW13" s="9" t="n"/>
       <c r="AX13" s="12" t="n"/>
@@ -6249,6 +6584,9 @@
       <c r="BK13" s="9" t="n"/>
       <c r="BL13" s="9" t="n"/>
       <c r="BM13" s="12" t="n"/>
+      <c r="BN13" s="9" t="n"/>
+      <c r="BO13" s="9" t="n"/>
+      <c r="BP13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -6273,30 +6611,30 @@
         <v>996</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
         <v/>
       </c>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="N14" s="12">
-        <f>M14/$E$14</f>
-        <v/>
-      </c>
+      <c r="I14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>901</v>
+      </c>
+      <c r="K14" s="12">
+        <f>J14/$E$14</f>
+        <v/>
+      </c>
+      <c r="L14" s="9" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>898</v>
@@ -6306,75 +6644,82 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="9" t="n"/>
-      <c r="Z14" s="12" t="n"/>
-      <c r="AA14" s="9" t="n">
+      <c r="X14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="Z14" s="12">
+        <f>Y14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="9" t="n"/>
+      <c r="AC14" s="12" t="n"/>
+      <c r="AD14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AB14" s="9" t="n">
+      <c r="AE14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AC14" s="12">
-        <f>AB14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AD14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
+      <c r="AG14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AH14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
+      <c r="AM14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
       <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n">
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="AR14" s="12">
-        <f>AQ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
       <c r="AV14" s="9" t="n"/>
       <c r="AW14" s="9" t="n"/>
       <c r="AX14" s="12" t="n"/>
@@ -6393,6 +6738,9 @@
       <c r="BK14" s="9" t="n"/>
       <c r="BL14" s="9" t="n"/>
       <c r="BM14" s="12" t="n"/>
+      <c r="BN14" s="9" t="n"/>
+      <c r="BO14" s="9" t="n"/>
+      <c r="BP14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -6476,6 +6824,9 @@
       <c r="BK15" s="9" t="n"/>
       <c r="BL15" s="9" t="n"/>
       <c r="BM15" s="12" t="n"/>
+      <c r="BN15" s="9" t="n"/>
+      <c r="BO15" s="9" t="n"/>
+      <c r="BP15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -6500,108 +6851,115 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H16" s="11">
         <f>G16/$E$16</f>
         <v/>
       </c>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="9" t="n">
+      <c r="I16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>710</v>
+      </c>
+      <c r="K16" s="12">
+        <f>J16/$E$16</f>
+        <v/>
+      </c>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="P16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="N16" s="12">
-        <f>M16/$E$16</f>
-        <v/>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/$E$16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="T16" s="12">
         <f>S16/$E$16</f>
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
         <v/>
       </c>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="9" t="n">
+      <c r="X16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="Z16" s="12">
+        <f>Y16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AB16" s="9" t="n">
+      <c r="AE16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AC16" s="12">
-        <f>AB16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AN16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
       <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n">
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
       <c r="AV16" s="9" t="n"/>
       <c r="AW16" s="9" t="n"/>
       <c r="AX16" s="12" t="n"/>
@@ -6620,6 +6978,9 @@
       <c r="BK16" s="9" t="n"/>
       <c r="BL16" s="9" t="n"/>
       <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n"/>
+      <c r="BO16" s="9" t="n"/>
+      <c r="BP16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -6644,7 +7005,7 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>384</v>
@@ -6653,99 +7014,106 @@
         <f>G17/$E$17</f>
         <v/>
       </c>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="9" t="n">
+      <c r="I17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="J17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="K17" s="12">
+        <f>J17/$E$17</f>
+        <v/>
+      </c>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="N17" s="12">
-        <f>M17/$E$17</f>
-        <v/>
-      </c>
-      <c r="O17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/$E$17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="T17" s="12">
         <f>S17/$E$17</f>
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
         <v/>
       </c>
-      <c r="X17" s="9" t="n"/>
-      <c r="Y17" s="9" t="n"/>
-      <c r="Z17" s="12" t="n"/>
-      <c r="AA17" s="9" t="n">
+      <c r="X17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="Z17" s="12">
+        <f>Y17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AB17" s="9" t="n">
+      <c r="AE17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AC17" s="12">
-        <f>AB17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AD17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AF17" s="12">
         <f>AE17/$E$17</f>
         <v/>
       </c>
-      <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="9" t="n"/>
-      <c r="AI17" s="12" t="n"/>
-      <c r="AJ17" s="9" t="n">
+      <c r="AG17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AI17" s="12">
+        <f>AH17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="9" t="n"/>
+      <c r="AK17" s="9" t="n"/>
+      <c r="AL17" s="12" t="n"/>
+      <c r="AM17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AK17" s="9" t="n">
+      <c r="AN17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="AL17" s="12">
-        <f>AK17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AM17" s="9" t="n"/>
-      <c r="AN17" s="9" t="n"/>
-      <c r="AO17" s="12" t="n"/>
+      <c r="AO17" s="12">
+        <f>AN17/$E$17</f>
+        <v/>
+      </c>
       <c r="AP17" s="9" t="n"/>
-      <c r="AQ17" s="9" t="n">
+      <c r="AQ17" s="9" t="n"/>
+      <c r="AR17" s="12" t="n"/>
+      <c r="AS17" s="9" t="n"/>
+      <c r="AT17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="AR17" s="12">
-        <f>AQ17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AS17" s="9" t="n"/>
-      <c r="AT17" s="9" t="n"/>
-      <c r="AU17" s="12" t="n"/>
+      <c r="AU17" s="12">
+        <f>AT17/$E$17</f>
+        <v/>
+      </c>
       <c r="AV17" s="9" t="n"/>
       <c r="AW17" s="9" t="n"/>
       <c r="AX17" s="12" t="n"/>
@@ -6764,6 +7132,9 @@
       <c r="BK17" s="9" t="n"/>
       <c r="BL17" s="9" t="n"/>
       <c r="BM17" s="12" t="n"/>
+      <c r="BN17" s="9" t="n"/>
+      <c r="BO17" s="9" t="n"/>
+      <c r="BP17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6791,105 +7162,112 @@
         <v>2</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="9" t="n">
+      <c r="I18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>286</v>
+      </c>
+      <c r="K18" s="12">
+        <f>J18/$E$18</f>
+        <v/>
+      </c>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="P18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="N18" s="12">
-        <f>M18/$E$18</f>
-        <v/>
-      </c>
-      <c r="O18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
-      <c r="X18" s="9" t="n"/>
-      <c r="Y18" s="9" t="n"/>
-      <c r="Z18" s="12" t="n"/>
-      <c r="AA18" s="9" t="n">
+      <c r="X18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="Z18" s="12">
+        <f>Y18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="9" t="n"/>
+      <c r="AC18" s="12" t="n"/>
+      <c r="AD18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AB18" s="9" t="n">
+      <c r="AE18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AC18" s="12">
-        <f>AB18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AD18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
-      <c r="AG18" s="9" t="n"/>
-      <c r="AH18" s="9" t="n"/>
-      <c r="AI18" s="12" t="n"/>
-      <c r="AJ18" s="9" t="n">
+      <c r="AG18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AI18" s="12">
+        <f>AH18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="9" t="n"/>
+      <c r="AL18" s="12" t="n"/>
+      <c r="AM18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK18" s="9" t="n">
+      <c r="AN18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="AL18" s="12">
-        <f>AK18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AM18" s="9" t="n"/>
-      <c r="AN18" s="9" t="n"/>
-      <c r="AO18" s="12" t="n"/>
+      <c r="AO18" s="12">
+        <f>AN18/$E$18</f>
+        <v/>
+      </c>
       <c r="AP18" s="9" t="n"/>
-      <c r="AQ18" s="9" t="n">
+      <c r="AQ18" s="9" t="n"/>
+      <c r="AR18" s="12" t="n"/>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="AR18" s="12">
-        <f>AQ18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AS18" s="9" t="n"/>
-      <c r="AT18" s="9" t="n"/>
-      <c r="AU18" s="12" t="n"/>
+      <c r="AU18" s="12">
+        <f>AT18/$E$18</f>
+        <v/>
+      </c>
       <c r="AV18" s="9" t="n"/>
       <c r="AW18" s="9" t="n"/>
       <c r="AX18" s="12" t="n"/>
@@ -6908,9 +7286,13 @@
       <c r="BK18" s="9" t="n"/>
       <c r="BL18" s="9" t="n"/>
       <c r="BM18" s="12" t="n"/>
+      <c r="BN18" s="9" t="n"/>
+      <c r="BO18" s="9" t="n"/>
+      <c r="BP18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -555,9 +555,6 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
-    <col width="9" customWidth="1" min="66" max="66"/>
-    <col width="9" customWidth="1" min="67" max="67"/>
-    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 12/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 13/08/2026</t>
         </is>
       </c>
     </row>
@@ -579,63 +576,60 @@
         <v>46247</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>46205</v>
+        <v>46199</v>
       </c>
       <c r="AM3" s="4" t="n">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="AP3" s="4" t="n">
-        <v>46198</v>
+        <v>46192</v>
       </c>
       <c r="AS3" s="4" t="n">
-        <v>46192</v>
+        <v>46184</v>
       </c>
       <c r="AV3" s="4" t="n">
-        <v>46184</v>
+        <v>46170</v>
       </c>
       <c r="AY3" s="4" t="n">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="BB3" s="4" t="n">
-        <v>46163</v>
+        <v>46156</v>
       </c>
       <c r="BE3" s="4" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="BH3" s="4" t="n">
-        <v>46149</v>
+        <v>46142</v>
       </c>
       <c r="BK3" s="4" t="n">
-        <v>46142</v>
-      </c>
-      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -963,21 +957,6 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="BN4" s="5" t="inlineStr">
-        <is>
-          <t>NEW SALES</t>
-        </is>
-      </c>
-      <c r="BO4" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL SOLD</t>
-        </is>
-      </c>
-      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1016,7 +995,7 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>42</v>
@@ -1029,56 +1008,49 @@
         <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
-      <c r="R5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="T5" s="12">
-        <f>S5/$E$5</f>
-        <v/>
-      </c>
-      <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
-      <c r="W5" s="12" t="n"/>
-      <c r="X5" s="9" t="n">
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="12" t="n"/>
+      <c r="U5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="V5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="Z5" s="12">
-        <f>Y5/$E$5</f>
-        <v/>
-      </c>
+      <c r="W5" s="12">
+        <f>V5/$E$5</f>
+        <v/>
+      </c>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="12" t="n"/>
       <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="12" t="n"/>
+      <c r="AB5" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
       <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF5" s="12">
-        <f>AE5/$E$5</f>
-        <v/>
-      </c>
+      <c r="AE5" s="9" t="n"/>
+      <c r="AF5" s="12" t="n"/>
       <c r="AG5" s="9" t="n"/>
       <c r="AH5" s="9" t="n"/>
       <c r="AI5" s="12" t="n"/>
@@ -1112,9 +1084,6 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
-      <c r="BN5" s="9" t="n"/>
-      <c r="BO5" s="9" t="n"/>
-      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1178,40 +1147,33 @@
         <f>P6/$E$6</f>
         <v/>
       </c>
-      <c r="R6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="9" t="n">
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="T6" s="12">
-        <f>S6/$E$6</f>
-        <v/>
-      </c>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="12" t="n"/>
-      <c r="X6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z6" s="12">
-        <f>Y6/$E$6</f>
-        <v/>
-      </c>
+      <c r="W6" s="12">
+        <f>V6/$E$6</f>
+        <v/>
+      </c>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="12" t="n"/>
       <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
+      <c r="AB6" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
       <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF6" s="12">
-        <f>AE6/$E$6</f>
-        <v/>
-      </c>
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="12" t="n"/>
       <c r="AG6" s="9" t="n"/>
       <c r="AH6" s="9" t="n"/>
       <c r="AI6" s="12" t="n"/>
@@ -1245,9 +1207,6 @@
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
-      <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n"/>
-      <c r="BP6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1272,7 +1231,7 @@
         <v>490</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>45</v>
@@ -1282,69 +1241,62 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
-      <c r="R7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S7" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="T7" s="12">
-        <f>S7/$E$7</f>
-        <v/>
-      </c>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="9" t="n">
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="12" t="n"/>
+      <c r="U7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="V7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="Z7" s="12">
-        <f>Y7/$E$7</f>
-        <v/>
-      </c>
+      <c r="W7" s="12">
+        <f>V7/$E$7</f>
+        <v/>
+      </c>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="12" t="n"/>
       <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
+      <c r="AB7" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
       <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" s="12">
-        <f>AE7/$E$7</f>
-        <v/>
-      </c>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="12" t="n"/>
       <c r="AG7" s="9" t="n"/>
       <c r="AH7" s="9" t="n"/>
       <c r="AI7" s="12" t="n"/>
@@ -1378,9 +1330,6 @@
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
-      <c r="BN7" s="9" t="n"/>
-      <c r="BO7" s="9" t="n"/>
-      <c r="BP7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1444,40 +1393,33 @@
         <f>P8/$E$8</f>
         <v/>
       </c>
-      <c r="R8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9" t="n">
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="T8" s="12">
-        <f>S8/$E$8</f>
-        <v/>
-      </c>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="12" t="n"/>
-      <c r="X8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="9" t="n">
+      <c r="W8" s="12">
+        <f>V8/$E$8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="Z8" s="12">
-        <f>Y8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
       <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="AF8" s="12">
-        <f>AE8/$E$8</f>
-        <v/>
-      </c>
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="12" t="n"/>
       <c r="AG8" s="9" t="n"/>
       <c r="AH8" s="9" t="n"/>
       <c r="AI8" s="12" t="n"/>
@@ -1511,9 +1453,6 @@
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
-      <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n"/>
-      <c r="BP8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1568,7 +1507,7 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>1</v>
@@ -1577,40 +1516,33 @@
         <f>P9/$E$9</f>
         <v/>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="12">
-        <f>S9/$E$9</f>
-        <v/>
-      </c>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="12">
-        <f>Y9/$E$9</f>
-        <v/>
-      </c>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="12" t="n"/>
+      <c r="U9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="12">
+        <f>V9/$E$9</f>
+        <v/>
+      </c>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="12" t="n"/>
       <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
+      <c r="AB9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
       <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="12">
-        <f>AE9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="12" t="n"/>
       <c r="AG9" s="9" t="n"/>
       <c r="AH9" s="9" t="n"/>
       <c r="AI9" s="12" t="n"/>
@@ -1644,9 +1576,6 @@
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
-      <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n"/>
-      <c r="BP9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1671,7 +1600,7 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>293</v>
@@ -1681,56 +1610,49 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
-      <c r="R10" s="9" t="n">
-        <v>182</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>214</v>
-      </c>
-      <c r="T10" s="12">
-        <f>S10/$E$10</f>
-        <v/>
-      </c>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="12" t="n"/>
       <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
-      <c r="W10" s="12" t="n"/>
+      <c r="V10" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="W10" s="12">
+        <f>V10/$E$10</f>
+        <v/>
+      </c>
       <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z10" s="12">
-        <f>Y10/$E$10</f>
-        <v/>
-      </c>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="12" t="n"/>
       <c r="AA10" s="9" t="n"/>
       <c r="AB10" s="9" t="n"/>
       <c r="AC10" s="12" t="n"/>
@@ -1770,13 +1692,9 @@
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n"/>
       <c r="BM10" s="12" t="n"/>
-      <c r="BN10" s="9" t="n"/>
-      <c r="BO10" s="9" t="n"/>
-      <c r="BP10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="BN3:BP3"/>
+  <mergeCells count="20">
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -1808,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP17"/>
+  <dimension ref="A1:BM17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1876,9 +1794,6 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
-    <col width="9" customWidth="1" min="66" max="66"/>
-    <col width="9" customWidth="1" min="67" max="67"/>
-    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1891,7 +1806,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 12/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 13/08/2026</t>
         </is>
       </c>
     </row>
@@ -1900,63 +1815,60 @@
         <v>46247</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>46205</v>
+        <v>46199</v>
       </c>
       <c r="AM3" s="4" t="n">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="AP3" s="4" t="n">
-        <v>46198</v>
+        <v>46192</v>
       </c>
       <c r="AS3" s="4" t="n">
-        <v>46192</v>
+        <v>46184</v>
       </c>
       <c r="AV3" s="4" t="n">
-        <v>46184</v>
+        <v>46170</v>
       </c>
       <c r="AY3" s="4" t="n">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="BB3" s="4" t="n">
-        <v>46163</v>
+        <v>46156</v>
       </c>
       <c r="BE3" s="4" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="BH3" s="4" t="n">
-        <v>46149</v>
+        <v>46142</v>
       </c>
       <c r="BK3" s="4" t="n">
-        <v>46142</v>
-      </c>
-      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2284,21 +2196,6 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="BN4" s="5" t="inlineStr">
-        <is>
-          <t>NEW SALES</t>
-        </is>
-      </c>
-      <c r="BO4" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL SOLD</t>
-        </is>
-      </c>
-      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2326,9 +2223,7 @@
       <c r="E5" s="9" t="n">
         <v>1310</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n">
         <v>175</v>
       </c>
@@ -2337,13 +2232,8 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n">
-        <v>174</v>
-      </c>
-      <c r="K5" s="12">
-        <f>J5/$E$5</f>
-        <v/>
-      </c>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="12" t="n"/>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="12" t="n"/>
@@ -2398,9 +2288,6 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
-      <c r="BN5" s="9" t="n"/>
-      <c r="BO5" s="9" t="n"/>
-      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2425,7 +2312,7 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>328</v>
@@ -2435,173 +2322,163 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="V6" s="9" t="n">
-        <v>285</v>
-      </c>
-      <c r="W6" s="12">
-        <f>V6/$E$6</f>
-        <v/>
-      </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
-      <c r="AA6" s="9" t="n">
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AB6" s="9" t="n">
+      <c r="Y6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
       <c r="AD6" s="9" t="n"/>
       <c r="AE6" s="9" t="n"/>
       <c r="AF6" s="12" t="n"/>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AH6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>241</v>
+      </c>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
       <c r="AP6" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
       <c r="AY6" s="9" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="AZ6" s="9" t="n">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
       <c r="BB6" s="9" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="BC6" s="9" t="n">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
-      <c r="BK6" s="9" t="n">
-        <v>24</v>
-      </c>
+      <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="BP6" s="12">
-        <f>BO6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -2628,7 +2505,7 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>116</v>
@@ -2638,102 +2515,102 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>102</v>
-      </c>
-      <c r="W7" s="12">
-        <f>V7/$E$7</f>
-        <v/>
-      </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="9" t="n">
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AB7" s="9" t="n">
+      <c r="Y7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
       <c r="AD7" s="9" t="n"/>
       <c r="AE7" s="9" t="n"/>
       <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AH7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
       <c r="AP7" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
@@ -2743,68 +2620,58 @@
         <v>6</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
       <c r="AY7" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AZ7" s="9" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
         <v/>
       </c>
       <c r="BB7" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC7" s="9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
-      <c r="BK7" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BN7" s="9" t="n"/>
-      <c r="BO7" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="BP7" s="12">
-        <f>BO7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -2831,7 +2698,7 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>993</v>
@@ -2841,92 +2708,92 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
-      <c r="U8" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v>965</v>
-      </c>
-      <c r="W8" s="12">
-        <f>V8/$E$8</f>
-        <v/>
-      </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
-      <c r="AA8" s="9" t="n">
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AB8" s="9" t="n">
+      <c r="Y8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
       <c r="AD8" s="9" t="n"/>
       <c r="AE8" s="9" t="n"/>
       <c r="AF8" s="12" t="n"/>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AH8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>907</v>
+      </c>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
       <c r="AP8" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AQ8" s="9" t="n">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
@@ -2936,78 +2803,68 @@
         <v>7</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
       <c r="AV8" s="9" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
       <c r="AY8" s="9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ8" s="9" t="n">
-        <v>878</v>
+        <v>854</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
         <v/>
       </c>
       <c r="BB8" s="9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC8" s="9" t="n">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
-      <c r="BK8" s="9" t="n">
-        <v>16</v>
-      </c>
+      <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n">
-        <v>792</v>
-      </c>
-      <c r="BP8" s="12">
-        <f>BO8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +2891,7 @@
         <v>1218</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>1123</v>
@@ -3044,17 +2901,17 @@
         <v/>
       </c>
       <c r="I9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="K9" s="12">
         <f>J9/$E$9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>1119</v>
@@ -3064,17 +2921,17 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="Q9" s="12">
         <f>P9/$E$9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>1117</v>
@@ -3083,134 +2940,124 @@
         <f>S9/$E$9</f>
         <v/>
       </c>
-      <c r="U9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v>1117</v>
-      </c>
-      <c r="W9" s="12">
-        <f>V9/$E$9</f>
-        <v/>
-      </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="9" t="n">
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AB9" s="9" t="n">
+      <c r="Y9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
       <c r="AD9" s="9" t="n"/>
       <c r="AE9" s="9" t="n"/>
       <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
+      <c r="AG9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AH9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>1109</v>
+      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
       <c r="AP9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ9" s="9" t="n">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="AR9" s="12">
         <f>AQ9/$E$9</f>
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AT9" s="9" t="n">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AU9" s="12">
         <f>AT9/$E$9</f>
         <v/>
       </c>
       <c r="AV9" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="AX9" s="12">
         <f>AW9/$E$9</f>
         <v/>
       </c>
       <c r="AY9" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AZ9" s="9" t="n">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="BA9" s="12">
         <f>AZ9/$E$9</f>
         <v/>
       </c>
       <c r="BB9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC9" s="9" t="n">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>2</v>
+        <v>1093</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>1093</v>
+        <v>-1091</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>1093</v>
+        <v>0</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
-      <c r="BK9" s="9" t="n">
-        <v>-1091</v>
-      </c>
+      <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n">
-        <v>0</v>
+        <v>1091</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n">
-        <v>1091</v>
-      </c>
-      <c r="BP9" s="12">
-        <f>BO9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3237,7 +3084,7 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>498</v>
@@ -3247,17 +3094,17 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>491</v>
@@ -3267,79 +3114,79 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
-      <c r="U10" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" s="9" t="n">
-        <v>475</v>
-      </c>
-      <c r="W10" s="12">
-        <f>V10/$E$10</f>
-        <v/>
-      </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="9" t="n">
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AB10" s="9" t="n">
+      <c r="Y10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AC10" s="12">
-        <f>AB10/$E$10</f>
-        <v/>
-      </c>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="12" t="n"/>
       <c r="AD10" s="9" t="n"/>
       <c r="AE10" s="9" t="n"/>
       <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AG10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AH10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="9" t="n">
+        <v>463</v>
+      </c>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
       <c r="AP10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT10" s="9" t="n">
         <v>462</v>
@@ -3352,68 +3199,58 @@
         <v>2</v>
       </c>
       <c r="AW10" s="9" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
       <c r="AY10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ10" s="9" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="BA10" s="12">
         <f>AZ10/$E$10</f>
         <v/>
       </c>
       <c r="BB10" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BC10" s="9" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="BD10" s="12">
         <f>BC10/$E$10</f>
         <v/>
       </c>
       <c r="BE10" s="9" t="n">
-        <v>10</v>
+        <v>447</v>
       </c>
       <c r="BF10" s="9" t="n">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>447</v>
+        <v>-446</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
-      <c r="BK10" s="9" t="n">
-        <v>-446</v>
-      </c>
+      <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BN10" s="9" t="n"/>
-      <c r="BO10" s="9" t="n">
-        <v>446</v>
-      </c>
-      <c r="BP10" s="12">
-        <f>BO10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -3440,7 +3277,7 @@
         <v>482</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>467</v>
@@ -3453,17 +3290,17 @@
         <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
@@ -3489,60 +3326,60 @@
         <f>S11/$E$11</f>
         <v/>
       </c>
-      <c r="U11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="9" t="n">
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="12" t="n"/>
+      <c r="X11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="W11" s="12">
-        <f>V11/$E$11</f>
-        <v/>
-      </c>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="9" t="n">
-        <v>465</v>
-      </c>
-      <c r="AC11" s="12">
-        <f>AB11/$E$11</f>
-        <v/>
-      </c>
+      <c r="Z11" s="12">
+        <f>Y11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="12" t="n"/>
       <c r="AD11" s="9" t="n"/>
       <c r="AE11" s="9" t="n"/>
       <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" s="9" t="n">
+        <v>464</v>
+      </c>
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
       <c r="AP11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="9" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11" s="9" t="n">
         <v>463</v>
@@ -3552,40 +3389,40 @@
         <v/>
       </c>
       <c r="AV11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW11" s="9" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AX11" s="12">
         <f>AW11/$E$11</f>
         <v/>
       </c>
       <c r="AY11" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ11" s="9" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="BA11" s="12">
         <f>AZ11/$E$11</f>
         <v/>
       </c>
       <c r="BB11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC11" s="9" t="n">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF11" s="9" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
@@ -3595,28 +3432,18 @@
         <v>2</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
         <v/>
       </c>
-      <c r="BK11" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="BK11" s="9" t="n"/>
       <c r="BL11" s="9" t="n">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BN11" s="9" t="n"/>
-      <c r="BO11" s="9" t="n">
-        <v>452</v>
-      </c>
-      <c r="BP11" s="12">
-        <f>BO11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -3643,7 +3470,7 @@
         <v>299</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>236</v>
@@ -3653,17 +3480,17 @@
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>235</v>
@@ -3673,10 +3500,10 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
@@ -3692,48 +3519,48 @@
         <f>S12/$E$12</f>
         <v/>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="9" t="n"/>
+      <c r="W12" s="12" t="n"/>
+      <c r="X12" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="W12" s="12">
-        <f>V12/$E$12</f>
-        <v/>
-      </c>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="9" t="n"/>
-      <c r="Z12" s="12" t="n"/>
-      <c r="AA12" s="9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB12" s="9" t="n">
-        <v>234</v>
-      </c>
-      <c r="AC12" s="12">
-        <f>AB12/$E$12</f>
-        <v/>
-      </c>
+      <c r="Z12" s="12">
+        <f>Y12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="9" t="n"/>
+      <c r="AC12" s="12" t="n"/>
       <c r="AD12" s="9" t="n"/>
       <c r="AE12" s="9" t="n"/>
       <c r="AF12" s="12" t="n"/>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="9" t="n">
+        <v>236</v>
+      </c>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
       <c r="AP12" s="9" t="n">
         <v>0</v>
       </c>
@@ -3775,7 +3602,7 @@
         <v/>
       </c>
       <c r="BB12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC12" s="9" t="n">
         <v>236</v>
@@ -3785,41 +3612,31 @@
         <v/>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="BF12" s="9" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BG12" s="12">
         <f>BF12/$E$12</f>
         <v/>
       </c>
       <c r="BH12" s="9" t="n">
-        <v>235</v>
+        <v>-234</v>
       </c>
       <c r="BI12" s="9" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="BJ12" s="12">
         <f>BI12/$E$12</f>
         <v/>
       </c>
-      <c r="BK12" s="9" t="n">
-        <v>-234</v>
-      </c>
+      <c r="BK12" s="9" t="n"/>
       <c r="BL12" s="9" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="BM12" s="12">
         <f>BL12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BN12" s="9" t="n"/>
-      <c r="BO12" s="9" t="n">
-        <v>234</v>
-      </c>
-      <c r="BP12" s="12">
-        <f>BO12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -3846,7 +3663,7 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>614</v>
@@ -3856,122 +3673,122 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
-      <c r="U13" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v>573</v>
-      </c>
-      <c r="W13" s="12">
-        <f>V13/$E$13</f>
-        <v/>
-      </c>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="9" t="n">
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="12" t="n"/>
+      <c r="X13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AB13" s="9" t="n">
+      <c r="Y13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AC13" s="12">
-        <f>AB13/$E$13</f>
-        <v/>
-      </c>
+      <c r="Z13" s="12">
+        <f>Y13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="12" t="n"/>
       <c r="AD13" s="9" t="n"/>
       <c r="AE13" s="9" t="n"/>
       <c r="AF13" s="12" t="n"/>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AH13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
+      <c r="AM13" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN13" s="9" t="n">
+        <v>433</v>
+      </c>
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
       <c r="AP13" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ13" s="9" t="n">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
       <c r="AV13" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
       <c r="AY13" s="9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AZ13" s="9" t="n">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
@@ -3981,48 +3798,38 @@
         <v>4</v>
       </c>
       <c r="BC13" s="9" t="n">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>4</v>
+        <v>381</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>381</v>
+        <v>-379</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
-      <c r="BK13" s="9" t="n">
-        <v>-379</v>
-      </c>
+      <c r="BK13" s="9" t="n"/>
       <c r="BL13" s="9" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BN13" s="9" t="n"/>
-      <c r="BO13" s="9" t="n">
-        <v>379</v>
-      </c>
-      <c r="BP13" s="12">
-        <f>BO13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -4049,7 +3856,7 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1142</v>
@@ -4059,122 +3866,122 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
-      <c r="U14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v>1129</v>
-      </c>
-      <c r="W14" s="12">
-        <f>V14/$E$14</f>
-        <v/>
-      </c>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="9" t="n"/>
-      <c r="Z14" s="12" t="n"/>
-      <c r="AA14" s="9" t="n">
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="9" t="n"/>
+      <c r="W14" s="12" t="n"/>
+      <c r="X14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AB14" s="9" t="n">
+      <c r="Y14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AC14" s="12">
-        <f>AB14/$E$14</f>
-        <v/>
-      </c>
+      <c r="Z14" s="12">
+        <f>Y14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="9" t="n"/>
+      <c r="AC14" s="12" t="n"/>
       <c r="AD14" s="9" t="n"/>
       <c r="AE14" s="9" t="n"/>
       <c r="AF14" s="12" t="n"/>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
+      <c r="AG14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AH14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
+      <c r="AM14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="9" t="n">
+        <v>1110</v>
+      </c>
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
       <c r="AP14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
       <c r="AV14" s="9" t="n">
-        <v>10</v>
+        <v>1086</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
       <c r="AY14" s="9" t="n">
-        <v>1086</v>
+        <v>0</v>
       </c>
       <c r="AZ14" s="9" t="n">
-        <v>1086</v>
+        <v>0</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
@@ -4210,22 +4017,12 @@
         <f>BI14/$E$14</f>
         <v/>
       </c>
-      <c r="BK14" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="BK14" s="9" t="n"/>
       <c r="BL14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BM14" s="12">
         <f>BL14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BN14" s="9" t="n"/>
-      <c r="BO14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" s="12">
-        <f>BO14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -4252,7 +4049,7 @@
         <v>551</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>124</v>
@@ -4262,17 +4059,17 @@
         <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K15" s="12">
         <f>J15/$E$15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" s="9" t="n">
         <v>124</v>
@@ -4282,17 +4079,17 @@
         <v/>
       </c>
       <c r="O15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>121</v>
@@ -4301,53 +4098,53 @@
         <f>S15/$E$15</f>
         <v/>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="9" t="n">
-        <v>121</v>
-      </c>
-      <c r="W15" s="12">
-        <f>V15/$E$15</f>
-        <v/>
-      </c>
-      <c r="X15" s="9" t="n"/>
-      <c r="Y15" s="9" t="n"/>
-      <c r="Z15" s="12" t="n"/>
-      <c r="AA15" s="9" t="n">
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="12" t="n"/>
+      <c r="X15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AB15" s="9" t="n">
+      <c r="Y15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AC15" s="12">
-        <f>AB15/$E$15</f>
-        <v/>
-      </c>
+      <c r="Z15" s="12">
+        <f>Y15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="9" t="n"/>
+      <c r="AC15" s="12" t="n"/>
       <c r="AD15" s="9" t="n"/>
       <c r="AE15" s="9" t="n"/>
       <c r="AF15" s="12" t="n"/>
-      <c r="AG15" s="9" t="n"/>
-      <c r="AH15" s="9" t="n"/>
-      <c r="AI15" s="12" t="n"/>
-      <c r="AJ15" s="9" t="n">
+      <c r="AG15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AK15" s="9" t="n">
+      <c r="AH15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AL15" s="12">
-        <f>AK15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AM15" s="9" t="n"/>
-      <c r="AN15" s="9" t="n"/>
-      <c r="AO15" s="12" t="n"/>
+      <c r="AI15" s="12">
+        <f>AH15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="9" t="n"/>
+      <c r="AK15" s="9" t="n"/>
+      <c r="AL15" s="12" t="n"/>
+      <c r="AM15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO15" s="12">
+        <f>AN15/$E$15</f>
+        <v/>
+      </c>
       <c r="AP15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ15" s="9" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AR15" s="12">
         <f>AQ15/$E$15</f>
@@ -4357,24 +4154,24 @@
         <v>3</v>
       </c>
       <c r="AT15" s="9" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AU15" s="12">
         <f>AT15/$E$15</f>
         <v/>
       </c>
       <c r="AV15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AX15" s="12">
         <f>AW15/$E$15</f>
         <v/>
       </c>
       <c r="AY15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AZ15" s="9" t="n">
         <v>76</v>
@@ -4384,10 +4181,10 @@
         <v/>
       </c>
       <c r="BB15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BC15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BD15" s="12">
         <f>BC15/$E$15</f>
@@ -4413,22 +4210,12 @@
         <f>BI15/$E$15</f>
         <v/>
       </c>
-      <c r="BK15" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="BK15" s="9" t="n"/>
       <c r="BL15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BM15" s="12">
         <f>BL15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BN15" s="9" t="n"/>
-      <c r="BO15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP15" s="12">
-        <f>BO15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -4504,58 +4291,51 @@
         <f>S16/$E$16</f>
         <v/>
       </c>
-      <c r="U16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="9" t="n">
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="W16" s="12">
-        <f>V16/$E$16</f>
-        <v/>
-      </c>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="9" t="n">
-        <v>659</v>
-      </c>
-      <c r="AC16" s="12">
-        <f>AB16/$E$16</f>
-        <v/>
-      </c>
+      <c r="Z16" s="12">
+        <f>Y16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="12" t="n"/>
       <c r="AD16" s="9" t="n"/>
       <c r="AE16" s="9" t="n"/>
       <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
-      <c r="AP16" s="9" t="n">
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AQ16" s="9" t="n">
+      <c r="AN16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
       <c r="AS16" s="9" t="n"/>
       <c r="AT16" s="9" t="n"/>
       <c r="AU16" s="12" t="n"/>
@@ -4575,14 +4355,11 @@
       <c r="BI16" s="9" t="n"/>
       <c r="BJ16" s="12" t="n"/>
       <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n"/>
-      <c r="BM16" s="12" t="n"/>
-      <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" s="12">
-        <f>BO16/$E$16</f>
+      <c r="BL16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" s="12">
+        <f>BL16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -4668,13 +4445,9 @@
       <c r="BK17" s="9" t="n"/>
       <c r="BL17" s="9" t="n"/>
       <c r="BM17" s="12" t="n"/>
-      <c r="BN17" s="9" t="n"/>
-      <c r="BO17" s="9" t="n"/>
-      <c r="BP17" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="BN3:BP3"/>
+  <mergeCells count="20">
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -4706,7 +4479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BM18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4774,9 +4547,6 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
-    <col width="9" customWidth="1" min="66" max="66"/>
-    <col width="9" customWidth="1" min="67" max="67"/>
-    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4789,7 +4559,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 12/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 13/08/2026</t>
         </is>
       </c>
     </row>
@@ -4798,63 +4568,60 @@
         <v>46247</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46227</v>
+        <v>46220</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="AG3" s="4" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="AJ3" s="4" t="n">
-        <v>46205</v>
+        <v>46199</v>
       </c>
       <c r="AM3" s="4" t="n">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="AP3" s="4" t="n">
-        <v>46198</v>
+        <v>46192</v>
       </c>
       <c r="AS3" s="4" t="n">
-        <v>46192</v>
+        <v>46184</v>
       </c>
       <c r="AV3" s="4" t="n">
-        <v>46184</v>
+        <v>46170</v>
       </c>
       <c r="AY3" s="4" t="n">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="BB3" s="4" t="n">
-        <v>46163</v>
+        <v>46156</v>
       </c>
       <c r="BE3" s="4" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="BH3" s="4" t="n">
-        <v>46149</v>
+        <v>46142</v>
       </c>
       <c r="BK3" s="4" t="n">
-        <v>46142</v>
-      </c>
-      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -5182,21 +4949,6 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="BN4" s="5" t="inlineStr">
-        <is>
-          <t>NEW SALES</t>
-        </is>
-      </c>
-      <c r="BO4" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL SOLD</t>
-        </is>
-      </c>
-      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -5225,7 +4977,7 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>296</v>
@@ -5234,106 +4986,99 @@
         <f>G5/$E$5</f>
         <v/>
       </c>
-      <c r="I5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>296</v>
-      </c>
-      <c r="K5" s="12">
-        <f>J5/$E$5</f>
-        <v/>
-      </c>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="12" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>293</v>
+      </c>
+      <c r="N5" s="12">
+        <f>M5/$E$5</f>
+        <v/>
+      </c>
       <c r="O5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
-      <c r="X5" s="9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y5" s="9" t="n">
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="12" t="n"/>
+      <c r="AA5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE5" s="9" t="n">
         <v>283</v>
-      </c>
-      <c r="Z5" s="12">
-        <f>Y5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="12" t="n"/>
-      <c r="AD5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE5" s="9" t="n">
-        <v>285</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
-      <c r="AG5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AH5" s="9" t="n">
-        <v>283</v>
-      </c>
-      <c r="AI5" s="12">
-        <f>AH5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
-      <c r="AM5" s="9" t="n">
+      <c r="AG5" s="9" t="n"/>
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AN5" s="9" t="n">
+      <c r="AK5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="AO5" s="12">
-        <f>AN5/$E$5</f>
-        <v/>
-      </c>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
       <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="12" t="n"/>
+      <c r="AQ5" s="9" t="n">
+        <v>275</v>
+      </c>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
       <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n">
-        <v>275</v>
-      </c>
-      <c r="AU5" s="12">
-        <f>AT5/$E$5</f>
-        <v/>
-      </c>
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
       <c r="AV5" s="9" t="n"/>
       <c r="AW5" s="9" t="n"/>
       <c r="AX5" s="12" t="n"/>
@@ -5352,9 +5097,6 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
-      <c r="BN5" s="9" t="n"/>
-      <c r="BO5" s="9" t="n"/>
-      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -5379,7 +5121,7 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>938</v>
@@ -5388,106 +5130,99 @@
         <f>G6/$E$6</f>
         <v/>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>937</v>
-      </c>
-      <c r="K6" s="12">
-        <f>J6/$E$6</f>
-        <v/>
-      </c>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="12" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>935</v>
+      </c>
+      <c r="N6" s="12">
+        <f>M6/$E$6</f>
+        <v/>
+      </c>
       <c r="O6" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>916</v>
+        <v>905</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
-      <c r="X6" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y6" s="9" t="n">
-        <v>905</v>
-      </c>
-      <c r="Z6" s="12">
-        <f>Y6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="12" t="n"/>
+      <c r="AA6" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>901</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
       <c r="AD6" s="9" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>901</v>
+        <v>853</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
-      <c r="AG6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH6" s="9" t="n">
-        <v>853</v>
-      </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
       <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
+      <c r="AQ6" s="9" t="n">
+        <v>842</v>
+      </c>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
       <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n">
-        <v>842</v>
-      </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
       <c r="AV6" s="9" t="n"/>
       <c r="AW6" s="9" t="n"/>
       <c r="AX6" s="12" t="n"/>
@@ -5506,9 +5241,6 @@
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
-      <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n"/>
-      <c r="BP6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -5542,106 +5274,99 @@
         <f>G7/$E$7</f>
         <v/>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9" t="n">
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M7" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="K7" s="12">
-        <f>J7/$E$7</f>
-        <v/>
-      </c>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="12" t="n"/>
+      <c r="N7" s="12">
+        <f>M7/$E$7</f>
+        <v/>
+      </c>
       <c r="O7" s="9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
-      <c r="X7" s="9" t="n">
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="12" t="n"/>
+      <c r="AA7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z7" s="12">
-        <f>Y7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
+      <c r="AB7" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
       <c r="AD7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
-      <c r="AG7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
       <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
+      <c r="AQ7" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
       <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
       <c r="AV7" s="9" t="n"/>
       <c r="AW7" s="9" t="n"/>
       <c r="AX7" s="12" t="n"/>
@@ -5660,9 +5385,6 @@
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
-      <c r="BN7" s="9" t="n"/>
-      <c r="BO7" s="9" t="n"/>
-      <c r="BP7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5687,7 +5409,7 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1052</v>
@@ -5696,106 +5418,99 @@
         <f>G8/$E$8</f>
         <v/>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="9" t="n">
-        <v>1052</v>
-      </c>
-      <c r="K8" s="12">
-        <f>J8/$E$8</f>
-        <v/>
-      </c>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="12" t="n"/>
+      <c r="M8" s="9" t="n">
+        <v>1051</v>
+      </c>
+      <c r="N8" s="12">
+        <f>M8/$E$8</f>
+        <v/>
+      </c>
       <c r="O8" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
-      <c r="X8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>1037</v>
-      </c>
-      <c r="Z8" s="12">
-        <f>Y8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB8" s="9" t="n">
+        <v>1033</v>
+      </c>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
       <c r="AD8" s="9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH8" s="9" t="n">
-        <v>1018</v>
-      </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AK8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
       <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
+      <c r="AQ8" s="9" t="n">
+        <v>1010</v>
+      </c>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
       <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n">
-        <v>1010</v>
-      </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
       <c r="AV8" s="9" t="n"/>
       <c r="AW8" s="9" t="n"/>
       <c r="AX8" s="12" t="n"/>
@@ -5814,9 +5529,6 @@
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
-      <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n"/>
-      <c r="BP8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -5850,19 +5562,19 @@
         <f>G9/$E$9</f>
         <v/>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9" t="n">
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="K9" s="12">
-        <f>J9/$E$9</f>
-        <v/>
-      </c>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="12" t="n"/>
+      <c r="N9" s="12">
+        <f>M9/$E$9</f>
+        <v/>
+      </c>
       <c r="O9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5874,7 +5586,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>845</v>
@@ -5884,28 +5596,28 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
         <v/>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9" t="n">
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="Z9" s="12">
-        <f>Y9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
       <c r="AD9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5916,40 +5628,33 @@
         <f>AE9/$E$9</f>
         <v/>
       </c>
-      <c r="AG9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="9" t="n">
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
       <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n">
-        <v>843</v>
-      </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
       <c r="AV9" s="9" t="n"/>
       <c r="AW9" s="9" t="n"/>
       <c r="AX9" s="12" t="n"/>
@@ -5968,9 +5673,6 @@
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
-      <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n"/>
-      <c r="BP9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -5995,7 +5697,7 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>1413</v>
@@ -6004,106 +5706,99 @@
         <f>G10/$E$10</f>
         <v/>
       </c>
-      <c r="I10" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>1411</v>
-      </c>
-      <c r="K10" s="12">
-        <f>J10/$E$10</f>
-        <v/>
-      </c>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="12" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>1406</v>
+      </c>
+      <c r="N10" s="12">
+        <f>M10/$E$10</f>
+        <v/>
+      </c>
       <c r="O10" s="9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>1403</v>
+        <v>1391</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1391</v>
+        <v>1372</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="9" t="n">
-        <v>1372</v>
-      </c>
-      <c r="Z10" s="12">
-        <f>Y10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>1364</v>
+      </c>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
       <c r="AD10" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>1364</v>
+        <v>1348</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
-      <c r="AG10" s="9" t="n">
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AH10" s="9" t="n">
-        <v>1348</v>
-      </c>
-      <c r="AI10" s="12">
-        <f>AH10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AK10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
       <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
+      <c r="AQ10" s="9" t="n">
+        <v>1334</v>
+      </c>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
       <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n">
-        <v>1334</v>
-      </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
       <c r="AV10" s="9" t="n"/>
       <c r="AW10" s="9" t="n"/>
       <c r="AX10" s="12" t="n"/>
@@ -6122,9 +5817,6 @@
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n"/>
       <c r="BM10" s="12" t="n"/>
-      <c r="BN10" s="9" t="n"/>
-      <c r="BO10" s="9" t="n"/>
-      <c r="BP10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -6149,7 +5841,7 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>990</v>
@@ -6158,106 +5850,99 @@
         <f>G11/$E$11</f>
         <v/>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="9" t="n">
-        <v>991</v>
-      </c>
-      <c r="K11" s="12">
-        <f>J11/$E$11</f>
-        <v/>
-      </c>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="12" t="n"/>
+      <c r="M11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="N11" s="12">
+        <f>M11/$E$11</f>
+        <v/>
+      </c>
       <c r="O11" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>989</v>
+        <v>976</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
         <v/>
       </c>
-      <c r="X11" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y11" s="9" t="n">
-        <v>968</v>
-      </c>
-      <c r="Z11" s="12">
-        <f>Y11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="12" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB11" s="9" t="n">
+        <v>963</v>
+      </c>
+      <c r="AC11" s="12">
+        <f>AB11/$E$11</f>
+        <v/>
+      </c>
       <c r="AD11" s="9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
         <v/>
       </c>
-      <c r="AG11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH11" s="9" t="n">
-        <v>949</v>
-      </c>
-      <c r="AI11" s="12">
-        <f>AH11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AK11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
       <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n"/>
-      <c r="AR11" s="12" t="n"/>
+      <c r="AQ11" s="9" t="n">
+        <v>936</v>
+      </c>
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
       <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n">
-        <v>936</v>
-      </c>
-      <c r="AU11" s="12">
-        <f>AT11/$E$11</f>
-        <v/>
-      </c>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
       <c r="AV11" s="9" t="n"/>
       <c r="AW11" s="9" t="n"/>
       <c r="AX11" s="12" t="n"/>
@@ -6276,9 +5961,6 @@
       <c r="BK11" s="9" t="n"/>
       <c r="BL11" s="9" t="n"/>
       <c r="BM11" s="12" t="n"/>
-      <c r="BN11" s="9" t="n"/>
-      <c r="BO11" s="9" t="n"/>
-      <c r="BP11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -6303,7 +5985,7 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>728</v>
@@ -6312,106 +5994,99 @@
         <f>G12/$E$12</f>
         <v/>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>727</v>
-      </c>
-      <c r="K12" s="12">
-        <f>J12/$E$12</f>
-        <v/>
-      </c>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="12" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>724</v>
+      </c>
+      <c r="N12" s="12">
+        <f>M12/$E$12</f>
+        <v/>
+      </c>
       <c r="O12" s="9" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
-      <c r="X12" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>676</v>
-      </c>
-      <c r="Z12" s="12">
-        <f>Y12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="9" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="12" t="n"/>
+      <c r="X12" s="9" t="n"/>
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="12" t="n"/>
+      <c r="AA12" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB12" s="9" t="n">
+        <v>665</v>
+      </c>
+      <c r="AC12" s="12">
+        <f>AB12/$E$12</f>
+        <v/>
+      </c>
       <c r="AD12" s="9" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>665</v>
+        <v>637</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
-      <c r="AG12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH12" s="9" t="n">
-        <v>637</v>
-      </c>
-      <c r="AI12" s="12">
-        <f>AH12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
+      <c r="AG12" s="9" t="n"/>
+      <c r="AH12" s="9" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AK12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
       <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n"/>
-      <c r="AR12" s="12" t="n"/>
+      <c r="AQ12" s="9" t="n">
+        <v>610</v>
+      </c>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
       <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n">
-        <v>610</v>
-      </c>
-      <c r="AU12" s="12">
-        <f>AT12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
       <c r="AV12" s="9" t="n"/>
       <c r="AW12" s="9" t="n"/>
       <c r="AX12" s="12" t="n"/>
@@ -6430,9 +6105,6 @@
       <c r="BK12" s="9" t="n"/>
       <c r="BL12" s="9" t="n"/>
       <c r="BM12" s="12" t="n"/>
-      <c r="BN12" s="9" t="n"/>
-      <c r="BO12" s="9" t="n"/>
-      <c r="BP12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -6457,7 +6129,7 @@
         <v>1623</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>1391</v>
@@ -6466,106 +6138,99 @@
         <f>G13/$E$13</f>
         <v/>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="9" t="n">
-        <v>1391</v>
-      </c>
-      <c r="K13" s="12">
-        <f>J13/$E$13</f>
-        <v/>
-      </c>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="12" t="n"/>
+      <c r="M13" s="9" t="n">
+        <v>1389</v>
+      </c>
+      <c r="N13" s="12">
+        <f>M13/$E$13</f>
+        <v/>
+      </c>
       <c r="O13" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
-      <c r="X13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y13" s="9" t="n">
-        <v>1376</v>
-      </c>
-      <c r="Z13" s="12">
-        <f>Y13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="12" t="n"/>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="12" t="n"/>
+      <c r="AA13" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AC13" s="12">
+        <f>AB13/$E$13</f>
+        <v/>
+      </c>
       <c r="AD13" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>1372</v>
+        <v>1356</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
-      <c r="AG13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" s="9" t="n">
-        <v>1356</v>
-      </c>
-      <c r="AI13" s="12">
-        <f>AH13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AK13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
       <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n"/>
-      <c r="AR13" s="12" t="n"/>
+      <c r="AQ13" s="9" t="n">
+        <v>1351</v>
+      </c>
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
       <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n">
-        <v>1351</v>
-      </c>
-      <c r="AU13" s="12">
-        <f>AT13/$E$13</f>
-        <v/>
-      </c>
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
       <c r="AV13" s="9" t="n"/>
       <c r="AW13" s="9" t="n"/>
       <c r="AX13" s="12" t="n"/>
@@ -6584,9 +6249,6 @@
       <c r="BK13" s="9" t="n"/>
       <c r="BL13" s="9" t="n"/>
       <c r="BM13" s="12" t="n"/>
-      <c r="BN13" s="9" t="n"/>
-      <c r="BO13" s="9" t="n"/>
-      <c r="BP13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -6611,7 +6273,7 @@
         <v>996</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>902</v>
@@ -6620,21 +6282,21 @@
         <f>G14/$E$14</f>
         <v/>
       </c>
-      <c r="I14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>901</v>
-      </c>
-      <c r="K14" s="12">
-        <f>J14/$E$14</f>
-        <v/>
-      </c>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="12" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>898</v>
+      </c>
+      <c r="N14" s="12">
+        <f>M14/$E$14</f>
+        <v/>
+      </c>
       <c r="O14" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>898</v>
@@ -6644,82 +6306,75 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
-      <c r="X14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>888</v>
-      </c>
-      <c r="Z14" s="12">
-        <f>Y14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="9" t="n"/>
-      <c r="AB14" s="9" t="n"/>
-      <c r="AC14" s="12" t="n"/>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="12" t="n"/>
+      <c r="AA14" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>887</v>
+      </c>
+      <c r="AC14" s="12">
+        <f>AB14/$E$14</f>
+        <v/>
+      </c>
       <c r="AD14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
-      <c r="AG14" s="9" t="n">
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AH14" s="9" t="n">
-        <v>881</v>
-      </c>
-      <c r="AI14" s="12">
-        <f>AH14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AK14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
       <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n"/>
-      <c r="AR14" s="12" t="n"/>
+      <c r="AQ14" s="9" t="n">
+        <v>873</v>
+      </c>
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
       <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n">
-        <v>873</v>
-      </c>
-      <c r="AU14" s="12">
-        <f>AT14/$E$14</f>
-        <v/>
-      </c>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
       <c r="AV14" s="9" t="n"/>
       <c r="AW14" s="9" t="n"/>
       <c r="AX14" s="12" t="n"/>
@@ -6738,9 +6393,6 @@
       <c r="BK14" s="9" t="n"/>
       <c r="BL14" s="9" t="n"/>
       <c r="BM14" s="12" t="n"/>
-      <c r="BN14" s="9" t="n"/>
-      <c r="BO14" s="9" t="n"/>
-      <c r="BP14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -6824,9 +6476,6 @@
       <c r="BK15" s="9" t="n"/>
       <c r="BL15" s="9" t="n"/>
       <c r="BM15" s="12" t="n"/>
-      <c r="BN15" s="9" t="n"/>
-      <c r="BO15" s="9" t="n"/>
-      <c r="BP15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -6860,106 +6509,99 @@
         <f>G16/$E$16</f>
         <v/>
       </c>
-      <c r="I16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9" t="n">
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="9" t="n">
         <v>710</v>
       </c>
-      <c r="K16" s="12">
-        <f>J16/$E$16</f>
-        <v/>
-      </c>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="12" t="n"/>
+      <c r="N16" s="12">
+        <f>M16/$E$16</f>
+        <v/>
+      </c>
       <c r="O16" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/$E$16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="T16" s="12">
         <f>S16/$E$16</f>
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
         <v/>
       </c>
-      <c r="X16" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y16" s="9" t="n">
-        <v>698</v>
-      </c>
-      <c r="Z16" s="12">
-        <f>Y16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="9" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="12" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>692</v>
+      </c>
+      <c r="AC16" s="12">
+        <f>AB16/$E$16</f>
+        <v/>
+      </c>
       <c r="AD16" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
-      <c r="AG16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH16" s="9" t="n">
-        <v>685</v>
-      </c>
-      <c r="AI16" s="12">
-        <f>AH16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AK16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
       <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
+      <c r="AQ16" s="9" t="n">
+        <v>684</v>
+      </c>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
       <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n">
-        <v>684</v>
-      </c>
-      <c r="AU16" s="12">
-        <f>AT16/$E$16</f>
-        <v/>
-      </c>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
       <c r="AV16" s="9" t="n"/>
       <c r="AW16" s="9" t="n"/>
       <c r="AX16" s="12" t="n"/>
@@ -6978,9 +6620,6 @@
       <c r="BK16" s="9" t="n"/>
       <c r="BL16" s="9" t="n"/>
       <c r="BM16" s="12" t="n"/>
-      <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n"/>
-      <c r="BP16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -7005,7 +6644,7 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>384</v>
@@ -7014,106 +6653,99 @@
         <f>G17/$E$17</f>
         <v/>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="9" t="n">
-        <v>384</v>
-      </c>
-      <c r="K17" s="12">
-        <f>J17/$E$17</f>
-        <v/>
-      </c>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="12" t="n"/>
+      <c r="M17" s="9" t="n">
+        <v>382</v>
+      </c>
+      <c r="N17" s="12">
+        <f>M17/$E$17</f>
+        <v/>
+      </c>
       <c r="O17" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/$E$17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="T17" s="12">
         <f>S17/$E$17</f>
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
         <v/>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="9" t="n">
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="12" t="n"/>
+      <c r="AA17" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="9" t="n">
         <v>370</v>
       </c>
-      <c r="Z17" s="12">
-        <f>Y17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AA17" s="9" t="n"/>
-      <c r="AB17" s="9" t="n"/>
-      <c r="AC17" s="12" t="n"/>
+      <c r="AC17" s="12">
+        <f>AB17/$E$17</f>
+        <v/>
+      </c>
       <c r="AD17" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AF17" s="12">
         <f>AE17/$E$17</f>
         <v/>
       </c>
-      <c r="AG17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="9" t="n">
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="AI17" s="12">
-        <f>AH17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="9" t="n"/>
-      <c r="AK17" s="9" t="n"/>
-      <c r="AL17" s="12" t="n"/>
-      <c r="AM17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN17" s="9" t="n">
-        <v>365</v>
-      </c>
-      <c r="AO17" s="12">
-        <f>AN17/$E$17</f>
-        <v/>
-      </c>
+      <c r="AL17" s="12">
+        <f>AK17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AM17" s="9" t="n"/>
+      <c r="AN17" s="9" t="n"/>
+      <c r="AO17" s="12" t="n"/>
       <c r="AP17" s="9" t="n"/>
-      <c r="AQ17" s="9" t="n"/>
-      <c r="AR17" s="12" t="n"/>
+      <c r="AQ17" s="9" t="n">
+        <v>358</v>
+      </c>
+      <c r="AR17" s="12">
+        <f>AQ17/$E$17</f>
+        <v/>
+      </c>
       <c r="AS17" s="9" t="n"/>
-      <c r="AT17" s="9" t="n">
-        <v>358</v>
-      </c>
-      <c r="AU17" s="12">
-        <f>AT17/$E$17</f>
-        <v/>
-      </c>
+      <c r="AT17" s="9" t="n"/>
+      <c r="AU17" s="12" t="n"/>
       <c r="AV17" s="9" t="n"/>
       <c r="AW17" s="9" t="n"/>
       <c r="AX17" s="12" t="n"/>
@@ -7132,9 +6764,6 @@
       <c r="BK17" s="9" t="n"/>
       <c r="BL17" s="9" t="n"/>
       <c r="BM17" s="12" t="n"/>
-      <c r="BN17" s="9" t="n"/>
-      <c r="BO17" s="9" t="n"/>
-      <c r="BP17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -7159,7 +6788,7 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>288</v>
@@ -7168,106 +6797,99 @@
         <f>G18/$E$18</f>
         <v/>
       </c>
-      <c r="I18" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>286</v>
-      </c>
-      <c r="K18" s="12">
-        <f>J18/$E$18</f>
-        <v/>
-      </c>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="12" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="N18" s="12">
+        <f>M18/$E$18</f>
+        <v/>
+      </c>
       <c r="O18" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
-      <c r="X18" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="9" t="n">
-        <v>270</v>
-      </c>
-      <c r="Z18" s="12">
-        <f>Y18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AA18" s="9" t="n"/>
-      <c r="AB18" s="9" t="n"/>
-      <c r="AC18" s="12" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="12" t="n"/>
+      <c r="AA18" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB18" s="9" t="n">
+        <v>266</v>
+      </c>
+      <c r="AC18" s="12">
+        <f>AB18/$E$18</f>
+        <v/>
+      </c>
       <c r="AD18" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="9" t="n">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
-      <c r="AG18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="9" t="n">
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="9" t="n"/>
+      <c r="AI18" s="12" t="n"/>
+      <c r="AJ18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="AI18" s="12">
-        <f>AH18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="9" t="n"/>
-      <c r="AK18" s="9" t="n"/>
-      <c r="AL18" s="12" t="n"/>
-      <c r="AM18" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN18" s="9" t="n">
-        <v>251</v>
-      </c>
-      <c r="AO18" s="12">
-        <f>AN18/$E$18</f>
-        <v/>
-      </c>
+      <c r="AL18" s="12">
+        <f>AK18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="9" t="n"/>
+      <c r="AO18" s="12" t="n"/>
       <c r="AP18" s="9" t="n"/>
-      <c r="AQ18" s="9" t="n"/>
-      <c r="AR18" s="12" t="n"/>
+      <c r="AQ18" s="9" t="n">
+        <v>249</v>
+      </c>
+      <c r="AR18" s="12">
+        <f>AQ18/$E$18</f>
+        <v/>
+      </c>
       <c r="AS18" s="9" t="n"/>
-      <c r="AT18" s="9" t="n">
-        <v>249</v>
-      </c>
-      <c r="AU18" s="12">
-        <f>AT18/$E$18</f>
-        <v/>
-      </c>
+      <c r="AT18" s="9" t="n"/>
+      <c r="AU18" s="12" t="n"/>
       <c r="AV18" s="9" t="n"/>
       <c r="AW18" s="9" t="n"/>
       <c r="AX18" s="12" t="n"/>
@@ -7286,13 +6908,9 @@
       <c r="BK18" s="9" t="n"/>
       <c r="BL18" s="9" t="n"/>
       <c r="BM18" s="12" t="n"/>
-      <c r="BN18" s="9" t="n"/>
-      <c r="BO18" s="9" t="n"/>
-      <c r="BP18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="BN3:BP3"/>
+  <mergeCells count="20">
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -555,6 +555,9 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -573,63 +576,66 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -957,6 +963,21 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BN4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BO4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -985,17 +1006,17 @@
         <v>146</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>42</v>
@@ -1008,49 +1029,56 @@
         <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="12" t="n"/>
-      <c r="U5" s="9" t="n">
+      <c r="R5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="T5" s="12">
+        <f>S5/$E$5</f>
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="Y5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="W5" s="12">
-        <f>V5/$E$5</f>
-        <v/>
-      </c>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="12" t="n"/>
+      <c r="Z5" s="12">
+        <f>Y5/$E$5</f>
+        <v/>
+      </c>
       <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n">
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="12" t="n"/>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AC5" s="12">
-        <f>AB5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="12" t="n"/>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
       <c r="AG5" s="9" t="n"/>
       <c r="AH5" s="9" t="n"/>
       <c r="AI5" s="12" t="n"/>
@@ -1084,6 +1112,9 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n"/>
+      <c r="BO5" s="9" t="n"/>
+      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1147,33 +1178,40 @@
         <f>P6/$E$6</f>
         <v/>
       </c>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="9" t="n">
+      <c r="R6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="T6" s="12">
+        <f>S6/$E$6</f>
+        <v/>
+      </c>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="Y6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="W6" s="12">
-        <f>V6/$E$6</f>
-        <v/>
-      </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
       <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n">
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
       <c r="AG6" s="9" t="n"/>
       <c r="AH6" s="9" t="n"/>
       <c r="AI6" s="12" t="n"/>
@@ -1207,6 +1245,9 @@
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n"/>
+      <c r="BP6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1231,7 +1272,7 @@
         <v>490</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>45</v>
@@ -1241,62 +1282,69 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="12" t="n"/>
-      <c r="U7" s="9" t="n">
+      <c r="R7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="T7" s="12">
+        <f>S7/$E$7</f>
+        <v/>
+      </c>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="Y7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="W7" s="12">
-        <f>V7/$E$7</f>
-        <v/>
-      </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
       <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n">
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
       <c r="AG7" s="9" t="n"/>
       <c r="AH7" s="9" t="n"/>
       <c r="AI7" s="12" t="n"/>
@@ -1330,6 +1378,9 @@
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n"/>
+      <c r="BP7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1393,33 +1444,40 @@
         <f>P8/$E$8</f>
         <v/>
       </c>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="12" t="n"/>
-      <c r="U8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="9" t="n">
+      <c r="R8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="W8" s="12">
-        <f>V8/$E$8</f>
-        <v/>
-      </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
+      <c r="T8" s="12">
+        <f>S8/$E$8</f>
+        <v/>
+      </c>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
       <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n">
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
       <c r="AG8" s="9" t="n"/>
       <c r="AH8" s="9" t="n"/>
       <c r="AI8" s="12" t="n"/>
@@ -1453,6 +1511,9 @@
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n"/>
+      <c r="BP8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1507,7 +1568,7 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>1</v>
@@ -1516,33 +1577,40 @@
         <f>P9/$E$9</f>
         <v/>
       </c>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="12" t="n"/>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="12">
-        <f>V9/$E$9</f>
-        <v/>
-      </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
+      <c r="R9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="12">
+        <f>S9/$E$9</f>
+        <v/>
+      </c>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
       <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
       <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
+      <c r="AE9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
       <c r="AG9" s="9" t="n"/>
       <c r="AH9" s="9" t="n"/>
       <c r="AI9" s="12" t="n"/>
@@ -1576,6 +1644,9 @@
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n"/>
+      <c r="BP9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1600,59 +1671,66 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="9" t="n"/>
-      <c r="T10" s="12" t="n"/>
+      <c r="R10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="T10" s="12">
+        <f>S10/$E$10</f>
+        <v/>
+      </c>
       <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="W10" s="12">
-        <f>V10/$E$10</f>
-        <v/>
-      </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
       <c r="AA10" s="9" t="n"/>
       <c r="AB10" s="9" t="n"/>
       <c r="AC10" s="12" t="n"/>
@@ -1692,9 +1770,13 @@
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n"/>
       <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n"/>
+      <c r="BP10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -1726,7 +1808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1794,6 +1876,9 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1812,63 +1897,66 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2196,6 +2284,21 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BN4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BO4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2223,17 +2326,24 @@
       <c r="E5" s="9" t="n">
         <v>1310</v>
       </c>
-      <c r="F5" s="10" t="n"/>
+      <c r="F5" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="G5" s="10" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
       <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="12" t="n"/>
+      <c r="J5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="K5" s="12">
+        <f>J5/$E$5</f>
+        <v/>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="12" t="n"/>
@@ -2288,6 +2398,9 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n"/>
+      <c r="BO5" s="9" t="n"/>
+      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2312,173 +2425,183 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="12" t="n"/>
-      <c r="X6" s="9" t="n">
+      <c r="U6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="W6" s="12">
+        <f>V6/$E$6</f>
+        <v/>
+      </c>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="12" t="n"/>
+      <c r="AA6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="AB6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="Z6" s="12">
-        <f>Y6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
       <c r="AD6" s="9" t="n"/>
       <c r="AE6" s="9" t="n"/>
       <c r="AF6" s="12" t="n"/>
-      <c r="AG6" s="9" t="n">
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
       <c r="AY6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AZ6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
       <c r="BB6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BC6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
-      <c r="BK6" s="9" t="n"/>
+      <c r="BK6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="BL6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="BP6" s="12">
+        <f>BO6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -2508,109 +2631,109 @@
         <v>3</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="9" t="n">
+      <c r="U7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="W7" s="12">
+        <f>V7/$E$7</f>
+        <v/>
+      </c>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="12" t="n"/>
+      <c r="AA7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="AB7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="Z7" s="12">
-        <f>Y7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
       <c r="AD7" s="9" t="n"/>
       <c r="AE7" s="9" t="n"/>
       <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="9" t="n">
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AH7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
@@ -2620,58 +2743,68 @@
         <v>6</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
       <c r="AY7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AZ7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
         <v/>
       </c>
       <c r="BB7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
-      <c r="BK7" s="9" t="n"/>
+      <c r="BK7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="BL7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BP7" s="12">
+        <f>BO7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -2698,102 +2831,102 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="12" t="n"/>
-      <c r="X8" s="9" t="n">
+      <c r="U8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="W8" s="12">
+        <f>V8/$E$8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="AB8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="Z8" s="12">
-        <f>Y8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
       <c r="AD8" s="9" t="n"/>
       <c r="AE8" s="9" t="n"/>
       <c r="AF8" s="12" t="n"/>
-      <c r="AG8" s="9" t="n">
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AH8" s="9" t="n">
+      <c r="AK8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AQ8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
@@ -2803,68 +2936,78 @@
         <v>7</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
       <c r="AV8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
       <c r="AY8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AZ8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
         <v/>
       </c>
       <c r="BB8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BC8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
-      <c r="BK8" s="9" t="n"/>
+      <c r="BK8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="BL8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="BP8" s="12">
+        <f>BO8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -2891,27 +3034,27 @@
         <v>1218</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="H9" s="11">
         <f>G9/$E$9</f>
         <v/>
       </c>
       <c r="I9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="K9" s="12">
         <f>J9/$E$9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>1119</v>
@@ -2921,17 +3064,17 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="Q9" s="12">
         <f>P9/$E$9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>1117</v>
@@ -2940,124 +3083,134 @@
         <f>S9/$E$9</f>
         <v/>
       </c>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="9" t="n">
+      <c r="U9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="W9" s="12">
+        <f>V9/$E$9</f>
+        <v/>
+      </c>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="9" t="n">
+      <c r="AB9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="Z9" s="12">
-        <f>Y9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
       <c r="AD9" s="9" t="n"/>
       <c r="AE9" s="9" t="n"/>
       <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="9" t="n">
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AH9" s="9" t="n">
+      <c r="AK9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AQ9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AP9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="AR9" s="12">
         <f>AQ9/$E$9</f>
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AU9" s="12">
         <f>AT9/$E$9</f>
         <v/>
       </c>
       <c r="AV9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="AX9" s="12">
         <f>AW9/$E$9</f>
         <v/>
       </c>
       <c r="AY9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AZ9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BA9" s="12">
         <f>AZ9/$E$9</f>
         <v/>
       </c>
       <c r="BB9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
-      <c r="BK9" s="9" t="n"/>
+      <c r="BK9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="BL9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="BP9" s="12">
+        <f>BO9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3084,27 +3237,27 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>491</v>
@@ -3114,79 +3267,79 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
-      <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
-      <c r="W10" s="12" t="n"/>
-      <c r="X10" s="9" t="n">
+      <c r="U10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="W10" s="12">
+        <f>V10/$E$10</f>
+        <v/>
+      </c>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="AB10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="Z10" s="12">
-        <f>Y10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
       <c r="AD10" s="9" t="n"/>
       <c r="AE10" s="9" t="n"/>
       <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="9" t="n">
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH10" s="9" t="n">
+      <c r="AK10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AI10" s="12">
-        <f>AH10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AQ10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT10" s="9" t="n">
         <v>462</v>
@@ -3199,58 +3352,68 @@
         <v>2</v>
       </c>
       <c r="AW10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
       <c r="AY10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BA10" s="12">
         <f>AZ10/$E$10</f>
         <v/>
       </c>
       <c r="BB10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BC10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BD10" s="12">
         <f>BC10/$E$10</f>
         <v/>
       </c>
       <c r="BE10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BF10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
-      <c r="BK10" s="9" t="n"/>
+      <c r="BK10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="BL10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="BP10" s="12">
+        <f>BO10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -3277,7 +3440,7 @@
         <v>482</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>467</v>
@@ -3290,17 +3453,17 @@
         <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
@@ -3326,60 +3489,60 @@
         <f>S11/$E$11</f>
         <v/>
       </c>
-      <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
-      <c r="W11" s="12" t="n"/>
-      <c r="X11" s="9" t="n">
+      <c r="U11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="W11" s="12">
+        <f>V11/$E$11</f>
+        <v/>
+      </c>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="AB11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="Z11" s="12">
-        <f>Y11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="12" t="n"/>
+      <c r="AC11" s="12">
+        <f>AB11/$E$11</f>
+        <v/>
+      </c>
       <c r="AD11" s="9" t="n"/>
       <c r="AE11" s="9" t="n"/>
       <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="9" t="n">
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AI11" s="12">
-        <f>AH11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AQ11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" s="9" t="n">
         <v>463</v>
@@ -3389,40 +3552,40 @@
         <v/>
       </c>
       <c r="AV11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AX11" s="12">
         <f>AW11/$E$11</f>
         <v/>
       </c>
       <c r="AY11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BA11" s="12">
         <f>AZ11/$E$11</f>
         <v/>
       </c>
       <c r="BB11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
@@ -3432,18 +3595,28 @@
         <v>2</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
         <v/>
       </c>
-      <c r="BK11" s="9" t="n"/>
+      <c r="BK11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="BL11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BN11" s="9" t="n"/>
+      <c r="BO11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="BP11" s="12">
+        <f>BO11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -3470,7 +3643,7 @@
         <v>299</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>236</v>
@@ -3480,17 +3653,17 @@
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>235</v>
@@ -3500,10 +3673,10 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
@@ -3519,48 +3692,48 @@
         <f>S12/$E$12</f>
         <v/>
       </c>
-      <c r="U12" s="9" t="n"/>
-      <c r="V12" s="9" t="n"/>
-      <c r="W12" s="12" t="n"/>
-      <c r="X12" s="9" t="n">
+      <c r="U12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="W12" s="12">
+        <f>V12/$E$12</f>
+        <v/>
+      </c>
+      <c r="X12" s="9" t="n"/>
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="12" t="n"/>
+      <c r="AA12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="Y12" s="9" t="n">
+      <c r="AB12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="Z12" s="12">
-        <f>Y12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="9" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="12" t="n"/>
+      <c r="AC12" s="12">
+        <f>AB12/$E$12</f>
+        <v/>
+      </c>
       <c r="AD12" s="9" t="n"/>
       <c r="AE12" s="9" t="n"/>
       <c r="AF12" s="12" t="n"/>
-      <c r="AG12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="9" t="n">
+      <c r="AG12" s="9" t="n"/>
+      <c r="AH12" s="9" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AI12" s="12">
-        <f>AH12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
       <c r="AP12" s="9" t="n">
         <v>0</v>
       </c>
@@ -3602,7 +3775,7 @@
         <v/>
       </c>
       <c r="BB12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC12" s="9" t="n">
         <v>236</v>
@@ -3612,31 +3785,41 @@
         <v/>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BF12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BG12" s="12">
         <f>BF12/$E$12</f>
         <v/>
       </c>
       <c r="BH12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="BI12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BJ12" s="12">
         <f>BI12/$E$12</f>
         <v/>
       </c>
-      <c r="BK12" s="9" t="n"/>
+      <c r="BK12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="BL12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="BM12" s="12">
         <f>BL12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BN12" s="9" t="n"/>
+      <c r="BO12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BP12" s="12">
+        <f>BO12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -3663,132 +3846,132 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
-      <c r="U13" s="9" t="n"/>
-      <c r="V13" s="9" t="n"/>
-      <c r="W13" s="12" t="n"/>
-      <c r="X13" s="9" t="n">
+      <c r="U13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="W13" s="12">
+        <f>V13/$E$13</f>
+        <v/>
+      </c>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="12" t="n"/>
+      <c r="AA13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="AB13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="Z13" s="12">
-        <f>Y13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="12" t="n"/>
+      <c r="AC13" s="12">
+        <f>AB13/$E$13</f>
+        <v/>
+      </c>
       <c r="AD13" s="9" t="n"/>
       <c r="AE13" s="9" t="n"/>
       <c r="AF13" s="12" t="n"/>
-      <c r="AG13" s="9" t="n">
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AH13" s="9" t="n">
+      <c r="AK13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AI13" s="12">
-        <f>AH13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AQ13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AP13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
       <c r="AV13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
       <c r="AY13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AZ13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
@@ -3798,38 +3981,48 @@
         <v>4</v>
       </c>
       <c r="BC13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
-      <c r="BK13" s="9" t="n"/>
+      <c r="BK13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="BL13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BN13" s="9" t="n"/>
+      <c r="BO13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="BP13" s="12">
+        <f>BO13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -3856,7 +4049,7 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1142</v>
@@ -3866,122 +4059,122 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
-      <c r="U14" s="9" t="n"/>
-      <c r="V14" s="9" t="n"/>
-      <c r="W14" s="12" t="n"/>
-      <c r="X14" s="9" t="n">
+      <c r="U14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="W14" s="12">
+        <f>V14/$E$14</f>
+        <v/>
+      </c>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="12" t="n"/>
+      <c r="AA14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="Y14" s="9" t="n">
+      <c r="AB14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="Z14" s="12">
-        <f>Y14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AA14" s="9" t="n"/>
-      <c r="AB14" s="9" t="n"/>
-      <c r="AC14" s="12" t="n"/>
+      <c r="AC14" s="12">
+        <f>AB14/$E$14</f>
+        <v/>
+      </c>
       <c r="AD14" s="9" t="n"/>
       <c r="AE14" s="9" t="n"/>
       <c r="AF14" s="12" t="n"/>
-      <c r="AG14" s="9" t="n">
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AH14" s="9" t="n">
+      <c r="AK14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AI14" s="12">
-        <f>AH14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AQ14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AP14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
       <c r="AV14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
       <c r="AY14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="AZ14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
@@ -4017,12 +4210,22 @@
         <f>BI14/$E$14</f>
         <v/>
       </c>
-      <c r="BK14" s="9" t="n"/>
+      <c r="BK14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BL14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BM14" s="12">
         <f>BL14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BN14" s="9" t="n"/>
+      <c r="BO14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" s="12">
+        <f>BO14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -4049,10 +4252,10 @@
         <v>551</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H15" s="11">
         <f>G15/$E$15</f>
@@ -4069,7 +4272,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
         <v>124</v>
@@ -4079,17 +4282,17 @@
         <v/>
       </c>
       <c r="O15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>121</v>
@@ -4098,53 +4301,53 @@
         <f>S15/$E$15</f>
         <v/>
       </c>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="9" t="n"/>
-      <c r="W15" s="12" t="n"/>
-      <c r="X15" s="9" t="n">
+      <c r="U15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="W15" s="12">
+        <f>V15/$E$15</f>
+        <v/>
+      </c>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="12" t="n"/>
+      <c r="AA15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="AB15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="Z15" s="12">
-        <f>Y15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AA15" s="9" t="n"/>
-      <c r="AB15" s="9" t="n"/>
-      <c r="AC15" s="12" t="n"/>
+      <c r="AC15" s="12">
+        <f>AB15/$E$15</f>
+        <v/>
+      </c>
       <c r="AD15" s="9" t="n"/>
       <c r="AE15" s="9" t="n"/>
       <c r="AF15" s="12" t="n"/>
-      <c r="AG15" s="9" t="n">
+      <c r="AG15" s="9" t="n"/>
+      <c r="AH15" s="9" t="n"/>
+      <c r="AI15" s="12" t="n"/>
+      <c r="AJ15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AH15" s="9" t="n">
+      <c r="AK15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AI15" s="12">
-        <f>AH15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="9" t="n"/>
-      <c r="AK15" s="9" t="n"/>
-      <c r="AL15" s="12" t="n"/>
-      <c r="AM15" s="9" t="n">
+      <c r="AL15" s="12">
+        <f>AK15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AM15" s="9" t="n"/>
+      <c r="AN15" s="9" t="n"/>
+      <c r="AO15" s="12" t="n"/>
+      <c r="AP15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN15" s="9" t="n">
+      <c r="AQ15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="AO15" s="12">
-        <f>AN15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AP15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="AR15" s="12">
         <f>AQ15/$E$15</f>
@@ -4154,24 +4357,24 @@
         <v>3</v>
       </c>
       <c r="AT15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AU15" s="12">
         <f>AT15/$E$15</f>
         <v/>
       </c>
       <c r="AV15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AX15" s="12">
         <f>AW15/$E$15</f>
         <v/>
       </c>
       <c r="AY15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AZ15" s="9" t="n">
         <v>76</v>
@@ -4181,10 +4384,10 @@
         <v/>
       </c>
       <c r="BB15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BC15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BD15" s="12">
         <f>BC15/$E$15</f>
@@ -4210,12 +4413,22 @@
         <f>BI15/$E$15</f>
         <v/>
       </c>
-      <c r="BK15" s="9" t="n"/>
+      <c r="BK15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BL15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BM15" s="12">
         <f>BL15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BN15" s="9" t="n"/>
+      <c r="BO15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="12">
+        <f>BO15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -4291,51 +4504,58 @@
         <f>S16/$E$16</f>
         <v/>
       </c>
-      <c r="U16" s="9" t="n"/>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="9" t="n">
+      <c r="U16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="Z16" s="12">
-        <f>Y16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="9" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="12" t="n"/>
+      <c r="W16" s="12">
+        <f>V16/$E$16</f>
+        <v/>
+      </c>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AC16" s="12">
+        <f>AB16/$E$16</f>
+        <v/>
+      </c>
       <c r="AD16" s="9" t="n"/>
       <c r="AE16" s="9" t="n"/>
       <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="9" t="n">
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AI16" s="12">
-        <f>AH16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AQ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
       <c r="AS16" s="9" t="n"/>
       <c r="AT16" s="9" t="n"/>
       <c r="AU16" s="12" t="n"/>
@@ -4355,11 +4575,14 @@
       <c r="BI16" s="9" t="n"/>
       <c r="BJ16" s="12" t="n"/>
       <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" s="12">
-        <f>BL16/$E$16</f>
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n"/>
+      <c r="BO16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" s="12">
+        <f>BO16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -4445,9 +4668,13 @@
       <c r="BK17" s="9" t="n"/>
       <c r="BL17" s="9" t="n"/>
       <c r="BM17" s="12" t="n"/>
+      <c r="BN17" s="9" t="n"/>
+      <c r="BO17" s="9" t="n"/>
+      <c r="BP17" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -4479,7 +4706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM18"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4547,6 +4774,9 @@
     <col width="9" customWidth="1" min="63" max="63"/>
     <col width="9" customWidth="1" min="64" max="64"/>
     <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="9" customWidth="1" min="66" max="66"/>
+    <col width="9" customWidth="1" min="67" max="67"/>
+    <col width="9" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4565,63 +4795,66 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -4949,6 +5182,21 @@
         </is>
       </c>
       <c r="BM4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BN4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BO4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -4977,108 +5225,115 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="9" t="n">
+      <c r="I5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="K5" s="12">
+        <f>J5/$E$5</f>
+        <v/>
+      </c>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="P5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="N5" s="12">
-        <f>M5/$E$5</f>
-        <v/>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="12" t="n"/>
-      <c r="AA5" s="9" t="n">
+      <c r="X5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="Z5" s="12">
+        <f>Y5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="12" t="n"/>
+      <c r="AD5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="9" t="n">
+      <c r="AE5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AC5" s="12">
-        <f>AB5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AE5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
-      <c r="AJ5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="9" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AN5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="AL5" s="12">
-        <f>AK5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
       <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n">
+      <c r="AQ5" s="9" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="AR5" s="12">
-        <f>AQ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
       <c r="AV5" s="9" t="n"/>
       <c r="AW5" s="9" t="n"/>
       <c r="AX5" s="12" t="n"/>
@@ -5097,6 +5352,9 @@
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n"/>
+      <c r="BO5" s="9" t="n"/>
+      <c r="BP5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -5121,108 +5379,115 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="9" t="n">
+      <c r="I6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="K6" s="12">
+        <f>J6/$E$6</f>
+        <v/>
+      </c>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="P6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="N6" s="12">
-        <f>M6/$E$6</f>
-        <v/>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
-      <c r="AA6" s="9" t="n">
+      <c r="X6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AB6" s="9" t="n">
+      <c r="AE6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AD6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AN6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
       <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n">
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
       <c r="AV6" s="9" t="n"/>
       <c r="AW6" s="9" t="n"/>
       <c r="AX6" s="12" t="n"/>
@@ -5241,6 +5506,9 @@
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n"/>
+      <c r="BP6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -5274,99 +5542,106 @@
         <f>G7/$E$7</f>
         <v/>
       </c>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="9" t="n">
+      <c r="I7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="K7" s="12">
+        <f>J7/$E$7</f>
+        <v/>
+      </c>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="P7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="N7" s="12">
-        <f>M7/$E$7</f>
-        <v/>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="9" t="n">
+      <c r="X7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AB7" s="9" t="n">
+      <c r="Y7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AD7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AN7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
       <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n">
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
       <c r="AV7" s="9" t="n"/>
       <c r="AW7" s="9" t="n"/>
       <c r="AX7" s="12" t="n"/>
@@ -5385,6 +5660,9 @@
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n"/>
+      <c r="BP7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5409,7 +5687,7 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1052</v>
@@ -5418,99 +5696,106 @@
         <f>G8/$E$8</f>
         <v/>
       </c>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="9" t="n">
+      <c r="I8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="J8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="K8" s="12">
+        <f>J8/$E$8</f>
+        <v/>
+      </c>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="N8" s="12">
-        <f>M8/$E$8</f>
-        <v/>
-      </c>
-      <c r="O8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
-      <c r="AA8" s="9" t="n">
+      <c r="X8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AB8" s="9" t="n">
+      <c r="AE8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AD8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AN8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
       <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n">
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
       <c r="AV8" s="9" t="n"/>
       <c r="AW8" s="9" t="n"/>
       <c r="AX8" s="12" t="n"/>
@@ -5529,6 +5814,9 @@
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n"/>
+      <c r="BP8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -5562,19 +5850,19 @@
         <f>G9/$E$9</f>
         <v/>
       </c>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9" t="n">
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="N9" s="12">
-        <f>M9/$E$9</f>
-        <v/>
-      </c>
+      <c r="K9" s="12">
+        <f>J9/$E$9</f>
+        <v/>
+      </c>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="12" t="n"/>
       <c r="O9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5586,7 +5874,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>845</v>
@@ -5596,28 +5884,28 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
         <v/>
       </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9" t="n">
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
       <c r="AD9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5628,33 +5916,40 @@
         <f>AE9/$E$9</f>
         <v/>
       </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AG9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
       <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n">
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
       <c r="AV9" s="9" t="n"/>
       <c r="AW9" s="9" t="n"/>
       <c r="AX9" s="12" t="n"/>
@@ -5673,6 +5968,9 @@
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n"/>
+      <c r="BP9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -5697,108 +5995,115 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="9" t="n">
+      <c r="I10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="K10" s="12">
+        <f>J10/$E$10</f>
+        <v/>
+      </c>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="P10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="N10" s="12">
-        <f>M10/$E$10</f>
-        <v/>
-      </c>
-      <c r="O10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="P10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="9" t="n">
+      <c r="X10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AB10" s="9" t="n">
+      <c r="AE10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AC10" s="12">
-        <f>AB10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AD10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AG10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AH10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
       <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n">
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
       <c r="AV10" s="9" t="n"/>
       <c r="AW10" s="9" t="n"/>
       <c r="AX10" s="12" t="n"/>
@@ -5817,6 +6122,9 @@
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n"/>
       <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n"/>
+      <c r="BP10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -5850,99 +6158,106 @@
         <f>G11/$E$11</f>
         <v/>
       </c>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="9" t="n">
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="K11" s="12">
+        <f>J11/$E$11</f>
+        <v/>
+      </c>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="P11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="N11" s="12">
-        <f>M11/$E$11</f>
-        <v/>
-      </c>
-      <c r="O11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="P11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
         <v/>
       </c>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="9" t="n">
+      <c r="X11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="Z11" s="12">
+        <f>Y11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AB11" s="9" t="n">
+      <c r="AE11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AC11" s="12">
-        <f>AB11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AD11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
         <v/>
       </c>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AN11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
       <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n">
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="AR11" s="12">
-        <f>AQ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
       <c r="AV11" s="9" t="n"/>
       <c r="AW11" s="9" t="n"/>
       <c r="AX11" s="12" t="n"/>
@@ -5961,6 +6276,9 @@
       <c r="BK11" s="9" t="n"/>
       <c r="BL11" s="9" t="n"/>
       <c r="BM11" s="12" t="n"/>
+      <c r="BN11" s="9" t="n"/>
+      <c r="BO11" s="9" t="n"/>
+      <c r="BP11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -5985,108 +6303,115 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
         <v/>
       </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="9" t="n">
+      <c r="I12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="K12" s="12">
+        <f>J12/$E$12</f>
+        <v/>
+      </c>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="P12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="N12" s="12">
-        <f>M12/$E$12</f>
-        <v/>
-      </c>
-      <c r="O12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="9" t="n"/>
-      <c r="Z12" s="12" t="n"/>
-      <c r="AA12" s="9" t="n">
+      <c r="X12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="Z12" s="12">
+        <f>Y12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="9" t="n"/>
+      <c r="AC12" s="12" t="n"/>
+      <c r="AD12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AB12" s="9" t="n">
+      <c r="AE12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AC12" s="12">
-        <f>AB12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AD12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AN12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
       <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n">
+      <c r="AQ12" s="9" t="n"/>
+      <c r="AR12" s="12" t="n"/>
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="AR12" s="12">
-        <f>AQ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
       <c r="AV12" s="9" t="n"/>
       <c r="AW12" s="9" t="n"/>
       <c r="AX12" s="12" t="n"/>
@@ -6105,6 +6430,9 @@
       <c r="BK12" s="9" t="n"/>
       <c r="BL12" s="9" t="n"/>
       <c r="BM12" s="12" t="n"/>
+      <c r="BN12" s="9" t="n"/>
+      <c r="BO12" s="9" t="n"/>
+      <c r="BP12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -6129,7 +6457,7 @@
         <v>1623</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>1391</v>
@@ -6138,99 +6466,106 @@
         <f>G13/$E$13</f>
         <v/>
       </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="9" t="n">
+      <c r="I13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="J13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="K13" s="12">
+        <f>J13/$E$13</f>
+        <v/>
+      </c>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="N13" s="12">
-        <f>M13/$E$13</f>
-        <v/>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="9" t="n">
+      <c r="X13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="Z13" s="12">
+        <f>Y13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="12" t="n"/>
+      <c r="AD13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AB13" s="9" t="n">
+      <c r="AE13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AC13" s="12">
-        <f>AB13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
+      <c r="AM13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AN13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
       <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n">
+      <c r="AQ13" s="9" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="AR13" s="12">
-        <f>AQ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
       <c r="AV13" s="9" t="n"/>
       <c r="AW13" s="9" t="n"/>
       <c r="AX13" s="12" t="n"/>
@@ -6249,6 +6584,9 @@
       <c r="BK13" s="9" t="n"/>
       <c r="BL13" s="9" t="n"/>
       <c r="BM13" s="12" t="n"/>
+      <c r="BN13" s="9" t="n"/>
+      <c r="BO13" s="9" t="n"/>
+      <c r="BP13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -6273,7 +6611,7 @@
         <v>996</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>902</v>
@@ -6282,21 +6620,21 @@
         <f>G14/$E$14</f>
         <v/>
       </c>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="N14" s="12">
-        <f>M14/$E$14</f>
-        <v/>
-      </c>
+      <c r="I14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="K14" s="12">
+        <f>J14/$E$14</f>
+        <v/>
+      </c>
+      <c r="L14" s="9" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="12" t="n"/>
       <c r="O14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>898</v>
@@ -6306,75 +6644,82 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="9" t="n"/>
-      <c r="Z14" s="12" t="n"/>
-      <c r="AA14" s="9" t="n">
+      <c r="X14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="Z14" s="12">
+        <f>Y14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="9" t="n"/>
+      <c r="AC14" s="12" t="n"/>
+      <c r="AD14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AB14" s="9" t="n">
+      <c r="AE14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AC14" s="12">
-        <f>AB14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AD14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
+      <c r="AG14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AH14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
+      <c r="AM14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
       <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n">
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="AR14" s="12">
-        <f>AQ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
       <c r="AV14" s="9" t="n"/>
       <c r="AW14" s="9" t="n"/>
       <c r="AX14" s="12" t="n"/>
@@ -6393,6 +6738,9 @@
       <c r="BK14" s="9" t="n"/>
       <c r="BL14" s="9" t="n"/>
       <c r="BM14" s="12" t="n"/>
+      <c r="BN14" s="9" t="n"/>
+      <c r="BO14" s="9" t="n"/>
+      <c r="BP14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -6476,6 +6824,9 @@
       <c r="BK15" s="9" t="n"/>
       <c r="BL15" s="9" t="n"/>
       <c r="BM15" s="12" t="n"/>
+      <c r="BN15" s="9" t="n"/>
+      <c r="BO15" s="9" t="n"/>
+      <c r="BP15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -6500,108 +6851,115 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="H16" s="11">
         <f>G16/$E$16</f>
         <v/>
       </c>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="9" t="n">
+      <c r="I16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="K16" s="12">
+        <f>J16/$E$16</f>
+        <v/>
+      </c>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="P16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="N16" s="12">
-        <f>M16/$E$16</f>
-        <v/>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/$E$16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="T16" s="12">
         <f>S16/$E$16</f>
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
         <v/>
       </c>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="9" t="n">
+      <c r="X16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="Z16" s="12">
+        <f>Y16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AB16" s="9" t="n">
+      <c r="AE16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AC16" s="12">
-        <f>AB16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AN16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
       <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n">
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
       <c r="AV16" s="9" t="n"/>
       <c r="AW16" s="9" t="n"/>
       <c r="AX16" s="12" t="n"/>
@@ -6620,6 +6978,9 @@
       <c r="BK16" s="9" t="n"/>
       <c r="BL16" s="9" t="n"/>
       <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n"/>
+      <c r="BO16" s="9" t="n"/>
+      <c r="BP16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -6644,108 +7005,115 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H17" s="11">
         <f>G17/$E$17</f>
         <v/>
       </c>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="9" t="n">
+      <c r="I17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="J17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="K17" s="12">
+        <f>J17/$E$17</f>
+        <v/>
+      </c>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="N17" s="12">
-        <f>M17/$E$17</f>
-        <v/>
-      </c>
-      <c r="O17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/$E$17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="T17" s="12">
         <f>S17/$E$17</f>
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
         <v/>
       </c>
-      <c r="X17" s="9" t="n"/>
-      <c r="Y17" s="9" t="n"/>
-      <c r="Z17" s="12" t="n"/>
-      <c r="AA17" s="9" t="n">
+      <c r="X17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="Z17" s="12">
+        <f>Y17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AB17" s="9" t="n">
+      <c r="AE17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AC17" s="12">
-        <f>AB17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AD17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AF17" s="12">
         <f>AE17/$E$17</f>
         <v/>
       </c>
-      <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="9" t="n"/>
-      <c r="AI17" s="12" t="n"/>
-      <c r="AJ17" s="9" t="n">
+      <c r="AG17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AI17" s="12">
+        <f>AH17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="9" t="n"/>
+      <c r="AK17" s="9" t="n"/>
+      <c r="AL17" s="12" t="n"/>
+      <c r="AM17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AK17" s="9" t="n">
+      <c r="AN17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="AL17" s="12">
-        <f>AK17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AM17" s="9" t="n"/>
-      <c r="AN17" s="9" t="n"/>
-      <c r="AO17" s="12" t="n"/>
+      <c r="AO17" s="12">
+        <f>AN17/$E$17</f>
+        <v/>
+      </c>
       <c r="AP17" s="9" t="n"/>
-      <c r="AQ17" s="9" t="n">
+      <c r="AQ17" s="9" t="n"/>
+      <c r="AR17" s="12" t="n"/>
+      <c r="AS17" s="9" t="n"/>
+      <c r="AT17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="AR17" s="12">
-        <f>AQ17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AS17" s="9" t="n"/>
-      <c r="AT17" s="9" t="n"/>
-      <c r="AU17" s="12" t="n"/>
+      <c r="AU17" s="12">
+        <f>AT17/$E$17</f>
+        <v/>
+      </c>
       <c r="AV17" s="9" t="n"/>
       <c r="AW17" s="9" t="n"/>
       <c r="AX17" s="12" t="n"/>
@@ -6764,6 +7132,9 @@
       <c r="BK17" s="9" t="n"/>
       <c r="BL17" s="9" t="n"/>
       <c r="BM17" s="12" t="n"/>
+      <c r="BN17" s="9" t="n"/>
+      <c r="BO17" s="9" t="n"/>
+      <c r="BP17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6788,108 +7159,115 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="9" t="n">
+      <c r="I18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="K18" s="12">
+        <f>J18/$E$18</f>
+        <v/>
+      </c>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="P18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="N18" s="12">
-        <f>M18/$E$18</f>
-        <v/>
-      </c>
-      <c r="O18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
-      <c r="X18" s="9" t="n"/>
-      <c r="Y18" s="9" t="n"/>
-      <c r="Z18" s="12" t="n"/>
-      <c r="AA18" s="9" t="n">
+      <c r="X18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="Z18" s="12">
+        <f>Y18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="9" t="n"/>
+      <c r="AC18" s="12" t="n"/>
+      <c r="AD18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AB18" s="9" t="n">
+      <c r="AE18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AC18" s="12">
-        <f>AB18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AD18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
-      <c r="AG18" s="9" t="n"/>
-      <c r="AH18" s="9" t="n"/>
-      <c r="AI18" s="12" t="n"/>
-      <c r="AJ18" s="9" t="n">
+      <c r="AG18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AI18" s="12">
+        <f>AH18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="9" t="n"/>
+      <c r="AL18" s="12" t="n"/>
+      <c r="AM18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK18" s="9" t="n">
+      <c r="AN18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="AL18" s="12">
-        <f>AK18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AM18" s="9" t="n"/>
-      <c r="AN18" s="9" t="n"/>
-      <c r="AO18" s="12" t="n"/>
+      <c r="AO18" s="12">
+        <f>AN18/$E$18</f>
+        <v/>
+      </c>
       <c r="AP18" s="9" t="n"/>
-      <c r="AQ18" s="9" t="n">
+      <c r="AQ18" s="9" t="n"/>
+      <c r="AR18" s="12" t="n"/>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="AR18" s="12">
-        <f>AQ18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AS18" s="9" t="n"/>
-      <c r="AT18" s="9" t="n"/>
-      <c r="AU18" s="12" t="n"/>
+      <c r="AU18" s="12">
+        <f>AT18/$E$18</f>
+        <v/>
+      </c>
       <c r="AV18" s="9" t="n"/>
       <c r="AW18" s="9" t="n"/>
       <c r="AX18" s="12" t="n"/>
@@ -6908,9 +7286,13 @@
       <c r="BK18" s="9" t="n"/>
       <c r="BL18" s="9" t="n"/>
       <c r="BM18" s="12" t="n"/>
+      <c r="BN18" s="9" t="n"/>
+      <c r="BO18" s="9" t="n"/>
+      <c r="BP18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -570,7 +570,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 13/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 14/08/2026</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 13/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 14/08/2026</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 13/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 14/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -558,6 +558,9 @@
     <col width="9" customWidth="1" min="66" max="66"/>
     <col width="9" customWidth="1" min="67" max="67"/>
     <col width="9" customWidth="1" min="68" max="68"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="9" customWidth="1" min="70" max="70"/>
+    <col width="9" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,66 +579,69 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -978,6 +984,21 @@
         </is>
       </c>
       <c r="BP4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BQ4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BR4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BS4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1006,7 +1027,7 @@
         <v>146</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>43</v>
@@ -1016,17 +1037,17 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>42</v>
@@ -1039,49 +1060,56 @@
         <v>1</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
-      <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
-      <c r="W5" s="12" t="n"/>
-      <c r="X5" s="9" t="n">
+      <c r="U5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="W5" s="12">
+        <f>V5/$E$5</f>
+        <v/>
+      </c>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="12" t="n"/>
+      <c r="AA5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="AB5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="Z5" s="12">
-        <f>Y5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="12" t="n"/>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
       <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n">
+      <c r="AE5" s="9" t="n"/>
+      <c r="AF5" s="12" t="n"/>
+      <c r="AG5" s="9" t="n"/>
+      <c r="AH5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AF5" s="12">
-        <f>AE5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
       <c r="AJ5" s="9" t="n"/>
       <c r="AK5" s="9" t="n"/>
       <c r="AL5" s="12" t="n"/>
@@ -1115,6 +1143,9 @@
       <c r="BN5" s="9" t="n"/>
       <c r="BO5" s="9" t="n"/>
       <c r="BP5" s="12" t="n"/>
+      <c r="BQ5" s="9" t="n"/>
+      <c r="BR5" s="9" t="n"/>
+      <c r="BS5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1188,33 +1219,40 @@
         <f>S6/$E$6</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="12" t="n"/>
-      <c r="X6" s="9" t="n">
+      <c r="U6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="W6" s="12">
+        <f>V6/$E$6</f>
+        <v/>
+      </c>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="12" t="n"/>
+      <c r="AA6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="AB6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="Z6" s="12">
-        <f>Y6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
       <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n">
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AF6" s="12">
-        <f>AE6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
       <c r="AJ6" s="9" t="n"/>
       <c r="AK6" s="9" t="n"/>
       <c r="AL6" s="12" t="n"/>
@@ -1248,6 +1286,9 @@
       <c r="BN6" s="9" t="n"/>
       <c r="BO6" s="9" t="n"/>
       <c r="BP6" s="12" t="n"/>
+      <c r="BQ6" s="9" t="n"/>
+      <c r="BR6" s="9" t="n"/>
+      <c r="BS6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1282,7 +1323,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>45</v>
@@ -1292,62 +1333,69 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="9" t="n">
+      <c r="U7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="W7" s="12">
+        <f>V7/$E$7</f>
+        <v/>
+      </c>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="12" t="n"/>
+      <c r="AA7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="AB7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="Z7" s="12">
-        <f>Y7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
       <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n">
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AF7" s="12">
-        <f>AE7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
       <c r="AJ7" s="9" t="n"/>
       <c r="AK7" s="9" t="n"/>
       <c r="AL7" s="12" t="n"/>
@@ -1381,6 +1429,9 @@
       <c r="BN7" s="9" t="n"/>
       <c r="BO7" s="9" t="n"/>
       <c r="BP7" s="12" t="n"/>
+      <c r="BQ7" s="9" t="n"/>
+      <c r="BR7" s="9" t="n"/>
+      <c r="BS7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1454,33 +1505,40 @@
         <f>S8/$E$8</f>
         <v/>
       </c>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="12" t="n"/>
-      <c r="X8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="9" t="n">
+      <c r="U8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="Z8" s="12">
-        <f>Y8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
+      <c r="W8" s="12">
+        <f>V8/$E$8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
       <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n">
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AF8" s="12">
-        <f>AE8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
       <c r="AJ8" s="9" t="n"/>
       <c r="AK8" s="9" t="n"/>
       <c r="AL8" s="12" t="n"/>
@@ -1514,6 +1572,9 @@
       <c r="BN8" s="9" t="n"/>
       <c r="BO8" s="9" t="n"/>
       <c r="BP8" s="12" t="n"/>
+      <c r="BQ8" s="9" t="n"/>
+      <c r="BR8" s="9" t="n"/>
+      <c r="BS8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1578,7 +1639,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>1</v>
@@ -1587,33 +1648,40 @@
         <f>S9/$E$9</f>
         <v/>
       </c>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="12">
-        <f>Y9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
+      <c r="U9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="12">
+        <f>V9/$E$9</f>
+        <v/>
+      </c>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="12" t="n"/>
+      <c r="AA9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
       <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="12">
-        <f>AE9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="12" t="n"/>
       <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
+      <c r="AH9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
       <c r="AJ9" s="9" t="n"/>
       <c r="AK9" s="9" t="n"/>
       <c r="AL9" s="12" t="n"/>
@@ -1647,6 +1715,9 @@
       <c r="BN9" s="9" t="n"/>
       <c r="BO9" s="9" t="n"/>
       <c r="BP9" s="12" t="n"/>
+      <c r="BQ9" s="9" t="n"/>
+      <c r="BR9" s="9" t="n"/>
+      <c r="BS9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1671,69 +1742,76 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
-      <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
-      <c r="W10" s="12" t="n"/>
+      <c r="U10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="W10" s="12">
+        <f>V10/$E$10</f>
+        <v/>
+      </c>
       <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n">
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="Z10" s="12">
-        <f>Y10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
       <c r="AD10" s="9" t="n"/>
       <c r="AE10" s="9" t="n"/>
       <c r="AF10" s="12" t="n"/>
@@ -1773,15 +1851,19 @@
       <c r="BN10" s="9" t="n"/>
       <c r="BO10" s="9" t="n"/>
       <c r="BP10" s="12" t="n"/>
+      <c r="BQ10" s="9" t="n"/>
+      <c r="BR10" s="9" t="n"/>
+      <c r="BS10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
@@ -1808,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP17"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1879,6 +1961,9 @@
     <col width="9" customWidth="1" min="66" max="66"/>
     <col width="9" customWidth="1" min="67" max="67"/>
     <col width="9" customWidth="1" min="68" max="68"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="9" customWidth="1" min="70" max="70"/>
+    <col width="9" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1897,66 +1982,69 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2299,6 +2387,21 @@
         </is>
       </c>
       <c r="BP4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BQ4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BR4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BS4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2327,7 +2430,7 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>177</v>
@@ -2336,17 +2439,24 @@
         <f>G5/$E$5</f>
         <v/>
       </c>
-      <c r="I5" s="9" t="n"/>
+      <c r="I5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="J5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
         <v/>
       </c>
       <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="12" t="n"/>
+      <c r="M5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="N5" s="12">
+        <f>M5/$E$5</f>
+        <v/>
+      </c>
       <c r="O5" s="9" t="n"/>
       <c r="P5" s="9" t="n"/>
       <c r="Q5" s="12" t="n"/>
@@ -2401,6 +2511,9 @@
       <c r="BN5" s="9" t="n"/>
       <c r="BO5" s="9" t="n"/>
       <c r="BP5" s="12" t="n"/>
+      <c r="BQ5" s="9" t="n"/>
+      <c r="BR5" s="9" t="n"/>
+      <c r="BS5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2425,183 +2538,193 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
-      <c r="AA6" s="9" t="n">
+      <c r="X6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AB6" s="9" t="n">
+      <c r="AE6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
       <c r="AG6" s="9" t="n"/>
       <c r="AH6" s="9" t="n"/>
       <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AN6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
-      <c r="AP6" s="9" t="n">
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AQ6" s="9" t="n">
+      <c r="AT6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
       <c r="AY6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="AZ6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
       <c r="BB6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BC6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
       <c r="BK6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BL6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
         <v/>
       </c>
-      <c r="BN6" s="9" t="n"/>
+      <c r="BN6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="BO6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BQ6" s="9" t="n"/>
+      <c r="BR6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="BS6" s="12">
+        <f>BR6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -2628,7 +2751,7 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>119</v>
@@ -2641,109 +2764,109 @@
         <v>3</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="9" t="n">
+      <c r="X7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AB7" s="9" t="n">
+      <c r="AE7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
       <c r="AG7" s="9" t="n"/>
       <c r="AH7" s="9" t="n"/>
       <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AN7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
-      <c r="AP7" s="9" t="n">
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AQ7" s="9" t="n">
+      <c r="AT7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
       <c r="AV7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
@@ -2753,58 +2876,68 @@
         <v>6</v>
       </c>
       <c r="AZ7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
         <v/>
       </c>
       <c r="BB7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BC7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
       <c r="BK7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BL7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
         <v/>
       </c>
-      <c r="BN7" s="9" t="n"/>
+      <c r="BN7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="BO7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BQ7" s="9" t="n"/>
+      <c r="BR7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS7" s="12">
+        <f>BR7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -2831,112 +2964,112 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
-      <c r="AA8" s="9" t="n">
+      <c r="X8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AB8" s="9" t="n">
+      <c r="AE8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
       <c r="AG8" s="9" t="n"/>
       <c r="AH8" s="9" t="n"/>
       <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AN8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
-      <c r="AP8" s="9" t="n">
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AQ8" s="9" t="n">
+      <c r="AT8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
@@ -2946,68 +3079,78 @@
         <v>7</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
       <c r="AY8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AZ8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
         <v/>
       </c>
       <c r="BB8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BC8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
       <c r="BK8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BL8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
         <v/>
       </c>
-      <c r="BN8" s="9" t="n"/>
+      <c r="BN8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="BO8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BQ8" s="9" t="n"/>
+      <c r="BR8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="BS8" s="12">
+        <f>BR8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3034,7 +3177,7 @@
         <v>1218</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>1125</v>
@@ -3044,27 +3187,27 @@
         <v/>
       </c>
       <c r="I9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="K9" s="12">
         <f>J9/$E$9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="N9" s="12">
         <f>M9/$E$9</f>
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>1119</v>
@@ -3074,17 +3217,17 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="T9" s="12">
         <f>S9/$E$9</f>
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>1117</v>
@@ -3093,124 +3236,134 @@
         <f>V9/$E$9</f>
         <v/>
       </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="9" t="n">
+      <c r="X9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
+      <c r="AD9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AB9" s="9" t="n">
+      <c r="AE9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
       <c r="AG9" s="9" t="n"/>
       <c r="AH9" s="9" t="n"/>
       <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AN9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
-      <c r="AP9" s="9" t="n">
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ9" s="9" t="n">
+      <c r="AT9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AS9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="AU9" s="12">
         <f>AT9/$E$9</f>
         <v/>
       </c>
       <c r="AV9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AX9" s="12">
         <f>AW9/$E$9</f>
         <v/>
       </c>
       <c r="AY9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BA9" s="12">
         <f>AZ9/$E$9</f>
         <v/>
       </c>
       <c r="BB9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BC9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
       <c r="BK9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="BL9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
         <v/>
       </c>
-      <c r="BN9" s="9" t="n"/>
+      <c r="BN9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="BO9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BQ9" s="9" t="n"/>
+      <c r="BR9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="BS9" s="12">
+        <f>BR9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3237,37 +3390,37 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>491</v>
@@ -3277,79 +3430,79 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="9" t="n">
+      <c r="X10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AB10" s="9" t="n">
+      <c r="AE10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AC10" s="12">
-        <f>AB10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n"/>
-      <c r="AF10" s="12" t="n"/>
+      <c r="AF10" s="12">
+        <f>AE10/$E$10</f>
+        <v/>
+      </c>
       <c r="AG10" s="9" t="n"/>
       <c r="AH10" s="9" t="n"/>
       <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AN10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
-      <c r="AP10" s="9" t="n">
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" s="9" t="n">
+      <c r="AT10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
       <c r="AV10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW10" s="9" t="n">
         <v>462</v>
@@ -3362,58 +3515,68 @@
         <v>2</v>
       </c>
       <c r="AZ10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BA10" s="12">
         <f>AZ10/$E$10</f>
         <v/>
       </c>
       <c r="BB10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BD10" s="12">
         <f>BC10/$E$10</f>
         <v/>
       </c>
       <c r="BE10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BF10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
       <c r="BK10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="BL10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
         <v/>
       </c>
-      <c r="BN10" s="9" t="n"/>
+      <c r="BN10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="BO10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="BP10" s="12">
         <f>BO10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BQ10" s="9" t="n"/>
+      <c r="BR10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="BS10" s="12">
+        <f>BR10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -3450,7 +3613,7 @@
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>467</v>
@@ -3463,17 +3626,17 @@
         <v>1</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
@@ -3499,60 +3662,60 @@
         <f>V11/$E$11</f>
         <v/>
       </c>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="9" t="n">
+      <c r="X11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="Z11" s="12">
+        <f>Y11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB11" s="9" t="n">
+      <c r="AE11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AC11" s="12">
-        <f>AB11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="9" t="n"/>
-      <c r="AF11" s="12" t="n"/>
+      <c r="AF11" s="12">
+        <f>AE11/$E$11</f>
+        <v/>
+      </c>
       <c r="AG11" s="9" t="n"/>
       <c r="AH11" s="9" t="n"/>
       <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
-      <c r="AP11" s="9" t="n">
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AP11" s="9" t="n"/>
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ11" s="9" t="n">
+      <c r="AT11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="AR11" s="12">
-        <f>AQ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="AU11" s="12">
         <f>AT11/$E$11</f>
         <v/>
       </c>
       <c r="AV11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW11" s="9" t="n">
         <v>463</v>
@@ -3562,40 +3725,40 @@
         <v/>
       </c>
       <c r="AY11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BA11" s="12">
         <f>AZ11/$E$11</f>
         <v/>
       </c>
       <c r="BB11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
         <v/>
       </c>
       <c r="BH11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
@@ -3605,18 +3768,28 @@
         <v>2</v>
       </c>
       <c r="BL11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
         <v/>
       </c>
-      <c r="BN11" s="9" t="n"/>
+      <c r="BN11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="BO11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BP11" s="12">
         <f>BO11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BQ11" s="9" t="n"/>
+      <c r="BR11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="BS11" s="12">
+        <f>BR11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -3653,7 +3826,7 @@
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>236</v>
@@ -3663,17 +3836,17 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N12" s="12">
         <f>M12/$E$12</f>
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>235</v>
@@ -3683,10 +3856,10 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
@@ -3702,48 +3875,48 @@
         <f>V12/$E$12</f>
         <v/>
       </c>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="9" t="n"/>
-      <c r="Z12" s="12" t="n"/>
-      <c r="AA12" s="9" t="n">
+      <c r="X12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="Z12" s="12">
+        <f>Y12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="9" t="n"/>
+      <c r="AC12" s="12" t="n"/>
+      <c r="AD12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AB12" s="9" t="n">
+      <c r="AE12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AC12" s="12">
-        <f>AB12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AD12" s="9" t="n"/>
-      <c r="AE12" s="9" t="n"/>
-      <c r="AF12" s="12" t="n"/>
+      <c r="AF12" s="12">
+        <f>AE12/$E$12</f>
+        <v/>
+      </c>
       <c r="AG12" s="9" t="n"/>
       <c r="AH12" s="9" t="n"/>
       <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
-      <c r="AP12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="AR12" s="12">
-        <f>AQ12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AP12" s="9" t="n"/>
+      <c r="AQ12" s="9" t="n"/>
+      <c r="AR12" s="12" t="n"/>
       <c r="AS12" s="9" t="n">
         <v>0</v>
       </c>
@@ -3785,7 +3958,7 @@
         <v/>
       </c>
       <c r="BE12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF12" s="9" t="n">
         <v>236</v>
@@ -3795,31 +3968,41 @@
         <v/>
       </c>
       <c r="BH12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BI12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BJ12" s="12">
         <f>BI12/$E$12</f>
         <v/>
       </c>
       <c r="BK12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="BL12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BM12" s="12">
         <f>BL12/$E$12</f>
         <v/>
       </c>
-      <c r="BN12" s="9" t="n"/>
+      <c r="BN12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="BO12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="BP12" s="12">
         <f>BO12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BQ12" s="9" t="n"/>
+      <c r="BR12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BS12" s="12">
+        <f>BR12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -3846,142 +4029,142 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="9" t="n">
+      <c r="X13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="Z13" s="12">
+        <f>Y13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="12" t="n"/>
+      <c r="AD13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AB13" s="9" t="n">
+      <c r="AE13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AC13" s="12">
-        <f>AB13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="9" t="n"/>
-      <c r="AE13" s="9" t="n"/>
-      <c r="AF13" s="12" t="n"/>
+      <c r="AF13" s="12">
+        <f>AE13/$E$13</f>
+        <v/>
+      </c>
       <c r="AG13" s="9" t="n"/>
       <c r="AH13" s="9" t="n"/>
       <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
+      <c r="AM13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AN13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
-      <c r="AP13" s="9" t="n">
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AP13" s="9" t="n"/>
+      <c r="AQ13" s="9" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AQ13" s="9" t="n">
+      <c r="AT13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="AR13" s="12">
-        <f>AQ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AS13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
       <c r="AV13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
       <c r="AY13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
         <v/>
       </c>
       <c r="BB13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BC13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
@@ -3991,38 +4174,48 @@
         <v>4</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
       <c r="BK13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="BL13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
         <v/>
       </c>
-      <c r="BN13" s="9" t="n"/>
+      <c r="BN13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="BO13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BQ13" s="9" t="n"/>
+      <c r="BR13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="BS13" s="12">
+        <f>BR13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -4049,17 +4242,17 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>1142</v>
@@ -4069,122 +4262,122 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="9" t="n"/>
-      <c r="Z14" s="12" t="n"/>
-      <c r="AA14" s="9" t="n">
+      <c r="X14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="Z14" s="12">
+        <f>Y14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="9" t="n"/>
+      <c r="AC14" s="12" t="n"/>
+      <c r="AD14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AB14" s="9" t="n">
+      <c r="AE14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AC14" s="12">
-        <f>AB14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AD14" s="9" t="n"/>
-      <c r="AE14" s="9" t="n"/>
-      <c r="AF14" s="12" t="n"/>
+      <c r="AF14" s="12">
+        <f>AE14/$E$14</f>
+        <v/>
+      </c>
       <c r="AG14" s="9" t="n"/>
       <c r="AH14" s="9" t="n"/>
       <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
+      <c r="AM14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AN14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
-      <c r="AP14" s="9" t="n">
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AQ14" s="9" t="n">
+      <c r="AT14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="AR14" s="12">
-        <f>AQ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AS14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
       <c r="AV14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
       <c r="AY14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="AZ14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
         <v/>
       </c>
       <c r="BB14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BC14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BD14" s="12">
         <f>BC14/$E$14</f>
@@ -4220,12 +4413,22 @@
         <f>BL14/$E$14</f>
         <v/>
       </c>
-      <c r="BN14" s="9" t="n"/>
+      <c r="BN14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BO14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BP14" s="12">
         <f>BO14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BQ14" s="9" t="n"/>
+      <c r="BR14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" s="12">
+        <f>BR14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -4255,17 +4458,17 @@
         <v>1</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11">
         <f>G15/$E$15</f>
         <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K15" s="12">
         <f>J15/$E$15</f>
@@ -4282,7 +4485,7 @@
         <v/>
       </c>
       <c r="O15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>124</v>
@@ -4292,17 +4495,17 @@
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="T15" s="12">
         <f>S15/$E$15</f>
         <v/>
       </c>
       <c r="U15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>121</v>
@@ -4311,53 +4514,53 @@
         <f>V15/$E$15</f>
         <v/>
       </c>
-      <c r="X15" s="9" t="n"/>
-      <c r="Y15" s="9" t="n"/>
-      <c r="Z15" s="12" t="n"/>
-      <c r="AA15" s="9" t="n">
+      <c r="X15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="Z15" s="12">
+        <f>Y15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="9" t="n"/>
+      <c r="AC15" s="12" t="n"/>
+      <c r="AD15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AB15" s="9" t="n">
+      <c r="AE15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AC15" s="12">
-        <f>AB15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AD15" s="9" t="n"/>
-      <c r="AE15" s="9" t="n"/>
-      <c r="AF15" s="12" t="n"/>
+      <c r="AF15" s="12">
+        <f>AE15/$E$15</f>
+        <v/>
+      </c>
       <c r="AG15" s="9" t="n"/>
       <c r="AH15" s="9" t="n"/>
       <c r="AI15" s="12" t="n"/>
-      <c r="AJ15" s="9" t="n">
+      <c r="AJ15" s="9" t="n"/>
+      <c r="AK15" s="9" t="n"/>
+      <c r="AL15" s="12" t="n"/>
+      <c r="AM15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AK15" s="9" t="n">
+      <c r="AN15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AL15" s="12">
-        <f>AK15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AM15" s="9" t="n"/>
-      <c r="AN15" s="9" t="n"/>
-      <c r="AO15" s="12" t="n"/>
-      <c r="AP15" s="9" t="n">
+      <c r="AO15" s="12">
+        <f>AN15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AP15" s="9" t="n"/>
+      <c r="AQ15" s="9" t="n"/>
+      <c r="AR15" s="12" t="n"/>
+      <c r="AS15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AQ15" s="9" t="n">
+      <c r="AT15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="AR15" s="12">
-        <f>AQ15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AS15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="AU15" s="12">
         <f>AT15/$E$15</f>
@@ -4367,24 +4570,24 @@
         <v>3</v>
       </c>
       <c r="AW15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AX15" s="12">
         <f>AW15/$E$15</f>
         <v/>
       </c>
       <c r="AY15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BA15" s="12">
         <f>AZ15/$E$15</f>
         <v/>
       </c>
       <c r="BB15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BC15" s="9" t="n">
         <v>76</v>
@@ -4394,10 +4597,10 @@
         <v/>
       </c>
       <c r="BE15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BF15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BG15" s="12">
         <f>BF15/$E$15</f>
@@ -4423,12 +4626,22 @@
         <f>BL15/$E$15</f>
         <v/>
       </c>
-      <c r="BN15" s="9" t="n"/>
+      <c r="BN15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BO15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BP15" s="12">
         <f>BO15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BQ15" s="9" t="n"/>
+      <c r="BR15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" s="12">
+        <f>BR15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -4514,51 +4727,58 @@
         <f>V16/$E$16</f>
         <v/>
       </c>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="9" t="n">
+      <c r="X16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AC16" s="12">
-        <f>AB16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="9" t="n"/>
-      <c r="AE16" s="9" t="n"/>
-      <c r="AF16" s="12" t="n"/>
+      <c r="Z16" s="12">
+        <f>Y16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AF16" s="12">
+        <f>AE16/$E$16</f>
+        <v/>
+      </c>
       <c r="AG16" s="9" t="n"/>
       <c r="AH16" s="9" t="n"/>
       <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
-      <c r="AP16" s="9" t="n">
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AQ16" s="9" t="n">
+      <c r="AT16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
       <c r="AV16" s="9" t="n"/>
       <c r="AW16" s="9" t="n"/>
       <c r="AX16" s="12" t="n"/>
@@ -4578,11 +4798,14 @@
       <c r="BL16" s="9" t="n"/>
       <c r="BM16" s="12" t="n"/>
       <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" s="12">
-        <f>BO16/$E$16</f>
+      <c r="BO16" s="9" t="n"/>
+      <c r="BP16" s="12" t="n"/>
+      <c r="BQ16" s="9" t="n"/>
+      <c r="BR16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" s="12">
+        <f>BR16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -4671,15 +4894,19 @@
       <c r="BN17" s="9" t="n"/>
       <c r="BO17" s="9" t="n"/>
       <c r="BP17" s="12" t="n"/>
+      <c r="BQ17" s="9" t="n"/>
+      <c r="BR17" s="9" t="n"/>
+      <c r="BS17" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
@@ -4706,7 +4933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4777,6 +5004,9 @@
     <col width="9" customWidth="1" min="66" max="66"/>
     <col width="9" customWidth="1" min="67" max="67"/>
     <col width="9" customWidth="1" min="68" max="68"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="9" customWidth="1" min="70" max="70"/>
+    <col width="9" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4795,66 +5025,69 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -5197,6 +5430,21 @@
         </is>
       </c>
       <c r="BP4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BQ4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BR4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BS4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -5228,115 +5476,122 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
         <v/>
       </c>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="9" t="n">
+      <c r="L5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="N5" s="12">
+        <f>M5/$E$5</f>
+        <v/>
+      </c>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="12" t="n"/>
+      <c r="R5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="S5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="Q5" s="12">
-        <f>P5/$E$5</f>
-        <v/>
-      </c>
-      <c r="R5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
-      <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="12" t="n"/>
-      <c r="AD5" s="9" t="n">
+      <c r="AA5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="9" t="n"/>
+      <c r="AF5" s="12" t="n"/>
+      <c r="AG5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AE5" s="9" t="n">
+      <c r="AH5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AF5" s="12">
-        <f>AE5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AG5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AH5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
-      <c r="AM5" s="9" t="n">
+      <c r="AJ5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AK5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
+      <c r="AP5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AN5" s="9" t="n">
+      <c r="AQ5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="AO5" s="12">
-        <f>AN5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="12" t="n"/>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
       <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n">
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="AU5" s="12">
-        <f>AT5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n"/>
-      <c r="AX5" s="12" t="n"/>
+      <c r="AX5" s="12">
+        <f>AW5/$E$5</f>
+        <v/>
+      </c>
       <c r="AY5" s="9" t="n"/>
       <c r="AZ5" s="9" t="n"/>
       <c r="BA5" s="12" t="n"/>
@@ -5355,6 +5610,9 @@
       <c r="BN5" s="9" t="n"/>
       <c r="BO5" s="9" t="n"/>
       <c r="BP5" s="12" t="n"/>
+      <c r="BQ5" s="9" t="n"/>
+      <c r="BR5" s="9" t="n"/>
+      <c r="BS5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -5379,118 +5637,125 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="9" t="n">
+      <c r="L6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="N6" s="12">
+        <f>M6/$E$6</f>
+        <v/>
+      </c>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="S6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="Q6" s="12">
-        <f>P6/$E$6</f>
-        <v/>
-      </c>
-      <c r="R6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="S6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
-      <c r="AD6" s="9" t="n">
+      <c r="AA6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AH6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AF6" s="12">
-        <f>AE6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AG6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AJ6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
       <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n">
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
       <c r="AY6" s="9" t="n"/>
       <c r="AZ6" s="9" t="n"/>
       <c r="BA6" s="12" t="n"/>
@@ -5509,6 +5774,9 @@
       <c r="BN6" s="9" t="n"/>
       <c r="BO6" s="9" t="n"/>
       <c r="BP6" s="12" t="n"/>
+      <c r="BQ6" s="9" t="n"/>
+      <c r="BR6" s="9" t="n"/>
+      <c r="BS6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -5552,99 +5820,106 @@
         <f>J7/$E$7</f>
         <v/>
       </c>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="O7" s="9" t="n">
+      <c r="L7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="N7" s="12">
+        <f>M7/$E$7</f>
+        <v/>
+      </c>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="12" t="n"/>
+      <c r="R7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="P7" s="9" t="n">
+      <c r="S7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="Q7" s="12">
-        <f>P7/$E$7</f>
-        <v/>
-      </c>
-      <c r="R7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
-      <c r="AD7" s="9" t="n">
+      <c r="AA7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AE7" s="9" t="n">
+      <c r="AB7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AF7" s="12">
-        <f>AE7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AG7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AJ7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
       <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n">
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
       <c r="AY7" s="9" t="n"/>
       <c r="AZ7" s="9" t="n"/>
       <c r="BA7" s="12" t="n"/>
@@ -5663,6 +5938,9 @@
       <c r="BN7" s="9" t="n"/>
       <c r="BO7" s="9" t="n"/>
       <c r="BP7" s="12" t="n"/>
+      <c r="BQ7" s="9" t="n"/>
+      <c r="BR7" s="9" t="n"/>
+      <c r="BS7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5687,17 +5965,17 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1052</v>
@@ -5706,99 +5984,106 @@
         <f>J8/$E$8</f>
         <v/>
       </c>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="9" t="n">
+      <c r="L8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="P8" s="9" t="n">
+      <c r="M8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="N8" s="12">
+        <f>M8/$E$8</f>
+        <v/>
+      </c>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="12" t="n"/>
+      <c r="R8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="Q8" s="12">
-        <f>P8/$E$8</f>
-        <v/>
-      </c>
-      <c r="R8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
-      <c r="AD8" s="9" t="n">
+      <c r="AA8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AE8" s="9" t="n">
+      <c r="AH8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AF8" s="12">
-        <f>AE8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AG8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AJ8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AQ8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
       <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n">
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
       <c r="AY8" s="9" t="n"/>
       <c r="AZ8" s="9" t="n"/>
       <c r="BA8" s="12" t="n"/>
@@ -5817,6 +6102,9 @@
       <c r="BN8" s="9" t="n"/>
       <c r="BO8" s="9" t="n"/>
       <c r="BP8" s="12" t="n"/>
+      <c r="BQ8" s="9" t="n"/>
+      <c r="BR8" s="9" t="n"/>
+      <c r="BS8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -5860,19 +6148,19 @@
         <f>J9/$E$9</f>
         <v/>
       </c>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9" t="n">
+      <c r="L9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="Q9" s="12">
-        <f>P9/$E$9</f>
-        <v/>
-      </c>
+      <c r="N9" s="12">
+        <f>M9/$E$9</f>
+        <v/>
+      </c>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="12" t="n"/>
       <c r="R9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5884,7 +6172,7 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>845</v>
@@ -5894,28 +6182,28 @@
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="Z9" s="12">
         <f>Y9/$E$9</f>
         <v/>
       </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="9" t="n">
+      <c r="AA9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AF9" s="12">
-        <f>AE9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9" t="n"/>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="12" t="n"/>
       <c r="AG9" s="9" t="n">
         <v>0</v>
       </c>
@@ -5926,33 +6214,40 @@
         <f>AH9/$E$9</f>
         <v/>
       </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AJ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
       <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n">
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
       <c r="AY9" s="9" t="n"/>
       <c r="AZ9" s="9" t="n"/>
       <c r="BA9" s="12" t="n"/>
@@ -5971,6 +6266,9 @@
       <c r="BN9" s="9" t="n"/>
       <c r="BO9" s="9" t="n"/>
       <c r="BP9" s="12" t="n"/>
+      <c r="BQ9" s="9" t="n"/>
+      <c r="BR9" s="9" t="n"/>
+      <c r="BS9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -5995,118 +6293,125 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="9" t="n">
+      <c r="L10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="N10" s="12">
+        <f>M10/$E$10</f>
+        <v/>
+      </c>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="S10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="Q10" s="12">
-        <f>P10/$E$10</f>
-        <v/>
-      </c>
-      <c r="R10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="9" t="n">
+      <c r="AA10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AD10" s="9" t="n"/>
+      <c r="AE10" s="9" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AE10" s="9" t="n">
+      <c r="AH10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AF10" s="12">
-        <f>AE10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AG10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
+      <c r="AJ10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AK10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
       <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n">
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
       <c r="AY10" s="9" t="n"/>
       <c r="AZ10" s="9" t="n"/>
       <c r="BA10" s="12" t="n"/>
@@ -6125,6 +6430,9 @@
       <c r="BN10" s="9" t="n"/>
       <c r="BO10" s="9" t="n"/>
       <c r="BP10" s="12" t="n"/>
+      <c r="BQ10" s="9" t="n"/>
+      <c r="BR10" s="9" t="n"/>
+      <c r="BS10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -6149,10 +6457,10 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
@@ -6168,99 +6476,106 @@
         <f>J11/$E$11</f>
         <v/>
       </c>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="9" t="n">
+      <c r="L11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="N11" s="12">
+        <f>M11/$E$11</f>
+        <v/>
+      </c>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="12" t="n"/>
+      <c r="R11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="S11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="Q11" s="12">
-        <f>P11/$E$11</f>
-        <v/>
-      </c>
-      <c r="R11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="S11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
         <v/>
       </c>
       <c r="X11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="Z11" s="12">
         <f>Y11/$E$11</f>
         <v/>
       </c>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="9" t="n">
+      <c r="AA11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AC11" s="12">
+        <f>AB11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9" t="n"/>
+      <c r="AE11" s="9" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AH11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AF11" s="12">
-        <f>AE11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AG11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AI11" s="12">
         <f>AH11/$E$11</f>
         <v/>
       </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
+      <c r="AJ11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AQ11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n"/>
-      <c r="AR11" s="12" t="n"/>
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
       <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n">
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="AU11" s="12">
-        <f>AT11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n"/>
-      <c r="AX11" s="12" t="n"/>
+      <c r="AX11" s="12">
+        <f>AW11/$E$11</f>
+        <v/>
+      </c>
       <c r="AY11" s="9" t="n"/>
       <c r="AZ11" s="9" t="n"/>
       <c r="BA11" s="12" t="n"/>
@@ -6279,6 +6594,9 @@
       <c r="BN11" s="9" t="n"/>
       <c r="BO11" s="9" t="n"/>
       <c r="BP11" s="12" t="n"/>
+      <c r="BQ11" s="9" t="n"/>
+      <c r="BR11" s="9" t="n"/>
+      <c r="BS11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -6303,118 +6621,125 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
         <v/>
       </c>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="9" t="n">
+      <c r="L12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="N12" s="12">
+        <f>M12/$E$12</f>
+        <v/>
+      </c>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="12" t="n"/>
+      <c r="R12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="P12" s="9" t="n">
+      <c r="S12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="Q12" s="12">
-        <f>P12/$E$12</f>
-        <v/>
-      </c>
-      <c r="R12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="S12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
         <v/>
       </c>
-      <c r="AA12" s="9" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="12" t="n"/>
-      <c r="AD12" s="9" t="n">
+      <c r="AA12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AC12" s="12">
+        <f>AB12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="9" t="n"/>
+      <c r="AE12" s="9" t="n"/>
+      <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AE12" s="9" t="n">
+      <c r="AH12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AF12" s="12">
-        <f>AE12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AG12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AI12" s="12">
         <f>AH12/$E$12</f>
         <v/>
       </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
+      <c r="AJ12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
+      <c r="AP12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AQ12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n"/>
-      <c r="AR12" s="12" t="n"/>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
       <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n">
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="AU12" s="12">
-        <f>AT12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="12" t="n"/>
+      <c r="AX12" s="12">
+        <f>AW12/$E$12</f>
+        <v/>
+      </c>
       <c r="AY12" s="9" t="n"/>
       <c r="AZ12" s="9" t="n"/>
       <c r="BA12" s="12" t="n"/>
@@ -6433,6 +6758,9 @@
       <c r="BN12" s="9" t="n"/>
       <c r="BO12" s="9" t="n"/>
       <c r="BP12" s="12" t="n"/>
+      <c r="BQ12" s="9" t="n"/>
+      <c r="BR12" s="9" t="n"/>
+      <c r="BS12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -6467,7 +6795,7 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>1391</v>
@@ -6476,99 +6804,106 @@
         <f>J13/$E$13</f>
         <v/>
       </c>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="9" t="n">
+      <c r="L13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="M13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="N13" s="12">
+        <f>M13/$E$13</f>
+        <v/>
+      </c>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="12" t="n"/>
+      <c r="R13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="Q13" s="12">
-        <f>P13/$E$13</f>
-        <v/>
-      </c>
-      <c r="R13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="12" t="n"/>
-      <c r="AD13" s="9" t="n">
+      <c r="AA13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AC13" s="12">
+        <f>AB13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="9" t="n"/>
+      <c r="AE13" s="9" t="n"/>
+      <c r="AF13" s="12" t="n"/>
+      <c r="AG13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AE13" s="9" t="n">
+      <c r="AH13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AF13" s="12">
-        <f>AE13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AG13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AJ13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AQ13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n"/>
-      <c r="AR13" s="12" t="n"/>
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
       <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n">
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="9" t="n"/>
+      <c r="AW13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="AU13" s="12">
-        <f>AT13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n"/>
-      <c r="AX13" s="12" t="n"/>
+      <c r="AX13" s="12">
+        <f>AW13/$E$13</f>
+        <v/>
+      </c>
       <c r="AY13" s="9" t="n"/>
       <c r="AZ13" s="9" t="n"/>
       <c r="BA13" s="12" t="n"/>
@@ -6587,6 +6922,9 @@
       <c r="BN13" s="9" t="n"/>
       <c r="BO13" s="9" t="n"/>
       <c r="BP13" s="12" t="n"/>
+      <c r="BQ13" s="9" t="n"/>
+      <c r="BR13" s="9" t="n"/>
+      <c r="BS13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -6621,7 +6959,7 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>902</v>
@@ -6630,21 +6968,21 @@
         <f>J14/$E$14</f>
         <v/>
       </c>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="Q14" s="12">
-        <f>P14/$E$14</f>
-        <v/>
-      </c>
+      <c r="L14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="N14" s="12">
+        <f>M14/$E$14</f>
+        <v/>
+      </c>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="12" t="n"/>
       <c r="R14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>898</v>
@@ -6654,75 +6992,82 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
         <v/>
       </c>
-      <c r="AA14" s="9" t="n"/>
-      <c r="AB14" s="9" t="n"/>
-      <c r="AC14" s="12" t="n"/>
-      <c r="AD14" s="9" t="n">
+      <c r="AA14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AC14" s="12">
+        <f>AB14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="9" t="n"/>
+      <c r="AE14" s="9" t="n"/>
+      <c r="AF14" s="12" t="n"/>
+      <c r="AG14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AE14" s="9" t="n">
+      <c r="AH14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AF14" s="12">
-        <f>AE14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AG14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
+      <c r="AJ14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AK14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n"/>
-      <c r="AR14" s="12" t="n"/>
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
       <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n">
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="AU14" s="12">
-        <f>AT14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n"/>
-      <c r="AX14" s="12" t="n"/>
+      <c r="AX14" s="12">
+        <f>AW14/$E$14</f>
+        <v/>
+      </c>
       <c r="AY14" s="9" t="n"/>
       <c r="AZ14" s="9" t="n"/>
       <c r="BA14" s="12" t="n"/>
@@ -6741,6 +7086,9 @@
       <c r="BN14" s="9" t="n"/>
       <c r="BO14" s="9" t="n"/>
       <c r="BP14" s="12" t="n"/>
+      <c r="BQ14" s="9" t="n"/>
+      <c r="BR14" s="9" t="n"/>
+      <c r="BS14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -6827,6 +7175,9 @@
       <c r="BN15" s="9" t="n"/>
       <c r="BO15" s="9" t="n"/>
       <c r="BP15" s="12" t="n"/>
+      <c r="BQ15" s="9" t="n"/>
+      <c r="BR15" s="9" t="n"/>
+      <c r="BS15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -6851,118 +7202,125 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H16" s="11">
         <f>G16/$E$16</f>
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="K16" s="12">
         <f>J16/$E$16</f>
         <v/>
       </c>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="9" t="n">
+      <c r="L16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="N16" s="12">
+        <f>M16/$E$16</f>
+        <v/>
+      </c>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="12" t="n"/>
+      <c r="R16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="P16" s="9" t="n">
+      <c r="S16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="Q16" s="12">
-        <f>P16/$E$16</f>
-        <v/>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="T16" s="12">
         <f>S16/$E$16</f>
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
         <v/>
       </c>
       <c r="X16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="Z16" s="12">
         <f>Y16/$E$16</f>
         <v/>
       </c>
-      <c r="AA16" s="9" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="9" t="n">
+      <c r="AA16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AC16" s="12">
+        <f>AB16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="9" t="n"/>
+      <c r="AE16" s="9" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AE16" s="9" t="n">
+      <c r="AH16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AF16" s="12">
-        <f>AE16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AG16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AI16" s="12">
         <f>AH16/$E$16</f>
         <v/>
       </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
+      <c r="AJ16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AQ16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
       <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n">
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="AU16" s="12">
-        <f>AT16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
       <c r="AY16" s="9" t="n"/>
       <c r="AZ16" s="9" t="n"/>
       <c r="BA16" s="12" t="n"/>
@@ -6981,6 +7339,9 @@
       <c r="BN16" s="9" t="n"/>
       <c r="BO16" s="9" t="n"/>
       <c r="BP16" s="12" t="n"/>
+      <c r="BQ16" s="9" t="n"/>
+      <c r="BR16" s="9" t="n"/>
+      <c r="BS16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -7005,7 +7366,7 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>385</v>
@@ -7015,108 +7376,115 @@
         <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K17" s="12">
         <f>J17/$E$17</f>
         <v/>
       </c>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="9" t="n">
+      <c r="L17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="P17" s="9" t="n">
+      <c r="M17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="N17" s="12">
+        <f>M17/$E$17</f>
+        <v/>
+      </c>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="12" t="n"/>
+      <c r="R17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="Q17" s="12">
-        <f>P17/$E$17</f>
-        <v/>
-      </c>
-      <c r="R17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="S17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="T17" s="12">
         <f>S17/$E$17</f>
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
         <v/>
       </c>
       <c r="X17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Z17" s="12">
         <f>Y17/$E$17</f>
         <v/>
       </c>
-      <c r="AA17" s="9" t="n"/>
-      <c r="AB17" s="9" t="n"/>
-      <c r="AC17" s="12" t="n"/>
-      <c r="AD17" s="9" t="n">
+      <c r="AA17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AC17" s="12">
+        <f>AB17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="9" t="n"/>
+      <c r="AE17" s="9" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AE17" s="9" t="n">
+      <c r="AH17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AF17" s="12">
-        <f>AE17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AG17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AI17" s="12">
         <f>AH17/$E$17</f>
         <v/>
       </c>
-      <c r="AJ17" s="9" t="n"/>
-      <c r="AK17" s="9" t="n"/>
-      <c r="AL17" s="12" t="n"/>
-      <c r="AM17" s="9" t="n">
+      <c r="AJ17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AL17" s="12">
+        <f>AK17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AM17" s="9" t="n"/>
+      <c r="AN17" s="9" t="n"/>
+      <c r="AO17" s="12" t="n"/>
+      <c r="AP17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AN17" s="9" t="n">
+      <c r="AQ17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="AO17" s="12">
-        <f>AN17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AP17" s="9" t="n"/>
-      <c r="AQ17" s="9" t="n"/>
-      <c r="AR17" s="12" t="n"/>
+      <c r="AR17" s="12">
+        <f>AQ17/$E$17</f>
+        <v/>
+      </c>
       <c r="AS17" s="9" t="n"/>
-      <c r="AT17" s="9" t="n">
+      <c r="AT17" s="9" t="n"/>
+      <c r="AU17" s="12" t="n"/>
+      <c r="AV17" s="9" t="n"/>
+      <c r="AW17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="AU17" s="12">
-        <f>AT17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AV17" s="9" t="n"/>
-      <c r="AW17" s="9" t="n"/>
-      <c r="AX17" s="12" t="n"/>
+      <c r="AX17" s="12">
+        <f>AW17/$E$17</f>
+        <v/>
+      </c>
       <c r="AY17" s="9" t="n"/>
       <c r="AZ17" s="9" t="n"/>
       <c r="BA17" s="12" t="n"/>
@@ -7135,6 +7503,9 @@
       <c r="BN17" s="9" t="n"/>
       <c r="BO17" s="9" t="n"/>
       <c r="BP17" s="12" t="n"/>
+      <c r="BQ17" s="9" t="n"/>
+      <c r="BR17" s="9" t="n"/>
+      <c r="BS17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -7159,118 +7530,125 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="9" t="n">
+      <c r="L18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="N18" s="12">
+        <f>M18/$E$18</f>
+        <v/>
+      </c>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="12" t="n"/>
+      <c r="R18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="S18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="Q18" s="12">
-        <f>P18/$E$18</f>
-        <v/>
-      </c>
-      <c r="R18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
       <c r="X18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Z18" s="12">
         <f>Y18/$E$18</f>
         <v/>
       </c>
-      <c r="AA18" s="9" t="n"/>
-      <c r="AB18" s="9" t="n"/>
-      <c r="AC18" s="12" t="n"/>
-      <c r="AD18" s="9" t="n">
+      <c r="AA18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AC18" s="12">
+        <f>AB18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="9" t="n"/>
+      <c r="AE18" s="9" t="n"/>
+      <c r="AF18" s="12" t="n"/>
+      <c r="AG18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AH18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AF18" s="12">
-        <f>AE18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AG18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AI18" s="12">
         <f>AH18/$E$18</f>
         <v/>
       </c>
-      <c r="AJ18" s="9" t="n"/>
-      <c r="AK18" s="9" t="n"/>
-      <c r="AL18" s="12" t="n"/>
-      <c r="AM18" s="9" t="n">
+      <c r="AJ18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AL18" s="12">
+        <f>AK18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="9" t="n"/>
+      <c r="AO18" s="12" t="n"/>
+      <c r="AP18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN18" s="9" t="n">
+      <c r="AQ18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="AO18" s="12">
-        <f>AN18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AP18" s="9" t="n"/>
-      <c r="AQ18" s="9" t="n"/>
-      <c r="AR18" s="12" t="n"/>
+      <c r="AR18" s="12">
+        <f>AQ18/$E$18</f>
+        <v/>
+      </c>
       <c r="AS18" s="9" t="n"/>
-      <c r="AT18" s="9" t="n">
+      <c r="AT18" s="9" t="n"/>
+      <c r="AU18" s="12" t="n"/>
+      <c r="AV18" s="9" t="n"/>
+      <c r="AW18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="AU18" s="12">
-        <f>AT18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AV18" s="9" t="n"/>
-      <c r="AW18" s="9" t="n"/>
-      <c r="AX18" s="12" t="n"/>
+      <c r="AX18" s="12">
+        <f>AW18/$E$18</f>
+        <v/>
+      </c>
       <c r="AY18" s="9" t="n"/>
       <c r="AZ18" s="9" t="n"/>
       <c r="BA18" s="12" t="n"/>
@@ -7289,15 +7667,19 @@
       <c r="BN18" s="9" t="n"/>
       <c r="BO18" s="9" t="n"/>
       <c r="BP18" s="12" t="n"/>
+      <c r="BQ18" s="9" t="n"/>
+      <c r="BR18" s="9" t="n"/>
+      <c r="BS18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 14/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 15/08/2026</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 14/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 15/08/2026</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 14/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 15/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,9 @@
     <col width="9" customWidth="1" min="69" max="69"/>
     <col width="9" customWidth="1" min="70" max="70"/>
     <col width="9" customWidth="1" min="71" max="71"/>
+    <col width="9" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="9" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -579,69 +582,72 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -999,6 +1005,21 @@
         </is>
       </c>
       <c r="BS4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BT4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BU4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BV4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1037,7 +1058,7 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>43</v>
@@ -1047,17 +1068,17 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>42</v>
@@ -1070,49 +1091,56 @@
         <v>1</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="12" t="n"/>
-      <c r="AA5" s="9" t="n">
+      <c r="X5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z5" s="12">
+        <f>Y5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="12" t="n"/>
+      <c r="AD5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AB5" s="9" t="n">
+      <c r="AE5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AC5" s="12">
-        <f>AB5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="12" t="n"/>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
       <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n">
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AI5" s="12">
-        <f>AH5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
       <c r="AM5" s="9" t="n"/>
       <c r="AN5" s="9" t="n"/>
       <c r="AO5" s="12" t="n"/>
@@ -1146,6 +1174,9 @@
       <c r="BQ5" s="9" t="n"/>
       <c r="BR5" s="9" t="n"/>
       <c r="BS5" s="12" t="n"/>
+      <c r="BT5" s="9" t="n"/>
+      <c r="BU5" s="9" t="n"/>
+      <c r="BV5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1229,33 +1260,40 @@
         <f>V6/$E$6</f>
         <v/>
       </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
-      <c r="AA6" s="9" t="n">
+      <c r="X6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" s="9" t="n">
+      <c r="AE6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
       <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n">
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
       <c r="AM6" s="9" t="n"/>
       <c r="AN6" s="9" t="n"/>
       <c r="AO6" s="12" t="n"/>
@@ -1289,6 +1327,9 @@
       <c r="BQ6" s="9" t="n"/>
       <c r="BR6" s="9" t="n"/>
       <c r="BS6" s="12" t="n"/>
+      <c r="BT6" s="9" t="n"/>
+      <c r="BU6" s="9" t="n"/>
+      <c r="BV6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1333,7 +1374,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>45</v>
@@ -1343,62 +1384,69 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="9" t="n">
+      <c r="X7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AB7" s="9" t="n">
+      <c r="AE7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
       <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n">
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
       <c r="AM7" s="9" t="n"/>
       <c r="AN7" s="9" t="n"/>
       <c r="AO7" s="12" t="n"/>
@@ -1432,6 +1480,9 @@
       <c r="BQ7" s="9" t="n"/>
       <c r="BR7" s="9" t="n"/>
       <c r="BS7" s="12" t="n"/>
+      <c r="BT7" s="9" t="n"/>
+      <c r="BU7" s="9" t="n"/>
+      <c r="BV7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1515,33 +1566,40 @@
         <f>V8/$E$8</f>
         <v/>
       </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
-      <c r="AA8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="9" t="n">
+      <c r="X8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
       <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n">
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
       <c r="AM8" s="9" t="n"/>
       <c r="AN8" s="9" t="n"/>
       <c r="AO8" s="12" t="n"/>
@@ -1575,6 +1633,9 @@
       <c r="BQ8" s="9" t="n"/>
       <c r="BR8" s="9" t="n"/>
       <c r="BS8" s="12" t="n"/>
+      <c r="BT8" s="9" t="n"/>
+      <c r="BU8" s="9" t="n"/>
+      <c r="BV8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1649,7 +1710,7 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>1</v>
@@ -1658,33 +1719,40 @@
         <f>V9/$E$9</f>
         <v/>
       </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
+      <c r="X9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
+      <c r="AD9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
       <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
       <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
+      <c r="AK9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
       <c r="AM9" s="9" t="n"/>
       <c r="AN9" s="9" t="n"/>
       <c r="AO9" s="12" t="n"/>
@@ -1718,6 +1786,9 @@
       <c r="BQ9" s="9" t="n"/>
       <c r="BR9" s="9" t="n"/>
       <c r="BS9" s="12" t="n"/>
+      <c r="BT9" s="9" t="n"/>
+      <c r="BU9" s="9" t="n"/>
+      <c r="BV9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1742,7 +1813,7 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>311</v>
@@ -1752,69 +1823,76 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
+      <c r="X10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
       <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n">
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="9" t="n"/>
+      <c r="AE10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AC10" s="12">
-        <f>AB10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n"/>
-      <c r="AF10" s="12" t="n"/>
+      <c r="AF10" s="12">
+        <f>AE10/$E$10</f>
+        <v/>
+      </c>
       <c r="AG10" s="9" t="n"/>
       <c r="AH10" s="9" t="n"/>
       <c r="AI10" s="12" t="n"/>
@@ -1854,14 +1932,18 @@
       <c r="BQ10" s="9" t="n"/>
       <c r="BR10" s="9" t="n"/>
       <c r="BS10" s="12" t="n"/>
+      <c r="BT10" s="9" t="n"/>
+      <c r="BU10" s="9" t="n"/>
+      <c r="BV10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
+    <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
@@ -1890,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BV17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1964,6 +2046,9 @@
     <col width="9" customWidth="1" min="69" max="69"/>
     <col width="9" customWidth="1" min="70" max="70"/>
     <col width="9" customWidth="1" min="71" max="71"/>
+    <col width="9" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="9" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1982,69 +2067,72 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2402,6 +2490,21 @@
         </is>
       </c>
       <c r="BS4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BT4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BU4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BV4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2440,7 +2543,7 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>177</v>
@@ -2449,17 +2552,24 @@
         <f>J5/$E$5</f>
         <v/>
       </c>
-      <c r="L5" s="9" t="n"/>
+      <c r="L5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="M5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="12" t="n"/>
+      <c r="P5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q5" s="12">
+        <f>P5/$E$5</f>
+        <v/>
+      </c>
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="n"/>
       <c r="T5" s="12" t="n"/>
@@ -2514,6 +2624,9 @@
       <c r="BQ5" s="9" t="n"/>
       <c r="BR5" s="9" t="n"/>
       <c r="BS5" s="12" t="n"/>
+      <c r="BT5" s="9" t="n"/>
+      <c r="BU5" s="9" t="n"/>
+      <c r="BV5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2538,7 +2651,7 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>335</v>
@@ -2548,183 +2661,193 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
-      <c r="AD6" s="9" t="n">
+      <c r="AA6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AH6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AF6" s="12">
-        <f>AE6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
       <c r="AJ6" s="9" t="n"/>
       <c r="AK6" s="9" t="n"/>
       <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
-      <c r="AS6" s="9" t="n">
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AT6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
       <c r="AY6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
       <c r="BB6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BC6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
       <c r="BK6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BL6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
         <v/>
       </c>
       <c r="BN6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BO6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
         <v/>
       </c>
-      <c r="BQ6" s="9" t="n"/>
+      <c r="BQ6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="BR6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BT6" s="9" t="n"/>
+      <c r="BU6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="BV6" s="12">
+        <f>BU6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -2761,7 +2884,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>119</v>
@@ -2774,109 +2897,109 @@
         <v>3</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
-      <c r="AD7" s="9" t="n">
+      <c r="AA7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AE7" s="9" t="n">
+      <c r="AH7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AF7" s="12">
-        <f>AE7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
       <c r="AJ7" s="9" t="n"/>
       <c r="AK7" s="9" t="n"/>
       <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
-      <c r="AS7" s="9" t="n">
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AT7" s="9" t="n">
+      <c r="AW7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
       <c r="AY7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AZ7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
@@ -2886,58 +3009,68 @@
         <v>6</v>
       </c>
       <c r="BC7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
       <c r="BK7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
         <v/>
       </c>
       <c r="BN7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BO7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
         <v/>
       </c>
-      <c r="BQ7" s="9" t="n"/>
+      <c r="BQ7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="BR7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BT7" s="9" t="n"/>
+      <c r="BU7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BV7" s="12">
+        <f>BU7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -2964,7 +3097,7 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>998</v>
@@ -2974,112 +3107,112 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
-      <c r="AD8" s="9" t="n">
+      <c r="AA8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AE8" s="9" t="n">
+      <c r="AH8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AF8" s="12">
-        <f>AE8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
       <c r="AJ8" s="9" t="n"/>
       <c r="AK8" s="9" t="n"/>
       <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AQ8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
-      <c r="AS8" s="9" t="n">
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AT8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
@@ -3089,68 +3222,78 @@
         <v>7</v>
       </c>
       <c r="AZ8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
         <v/>
       </c>
       <c r="BB8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BC8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
       <c r="BK8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BL8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
         <v/>
       </c>
       <c r="BN8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BO8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
         <v/>
       </c>
-      <c r="BQ8" s="9" t="n"/>
+      <c r="BQ8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="BR8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BT8" s="9" t="n"/>
+      <c r="BU8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="BV8" s="12">
+        <f>BU8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3187,7 +3330,7 @@
         <v/>
       </c>
       <c r="I9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>1125</v>
@@ -3197,27 +3340,27 @@
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="N9" s="12">
         <f>M9/$E$9</f>
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="Q9" s="12">
         <f>P9/$E$9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>1119</v>
@@ -3227,17 +3370,17 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>1117</v>
@@ -3246,124 +3389,134 @@
         <f>Y9/$E$9</f>
         <v/>
       </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="9" t="n">
+      <c r="AA9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9" t="n"/>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AE9" s="9" t="n">
+      <c r="AH9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AF9" s="12">
-        <f>AE9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
       <c r="AJ9" s="9" t="n"/>
       <c r="AK9" s="9" t="n"/>
       <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AQ9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
-      <c r="AS9" s="9" t="n">
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AT9" s="9" t="n">
+      <c r="AW9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AV9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="AX9" s="12">
         <f>AW9/$E$9</f>
         <v/>
       </c>
       <c r="AY9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AZ9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BA9" s="12">
         <f>AZ9/$E$9</f>
         <v/>
       </c>
       <c r="BB9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
       <c r="BK9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BL9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
         <v/>
       </c>
       <c r="BN9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="BO9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
         <v/>
       </c>
-      <c r="BQ9" s="9" t="n"/>
+      <c r="BQ9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="BR9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BT9" s="9" t="n"/>
+      <c r="BU9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="BV9" s="12">
+        <f>BU9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3390,7 +3543,7 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>502</v>
@@ -3400,37 +3553,37 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>491</v>
@@ -3440,79 +3593,79 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="9" t="n">
+      <c r="AA10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AD10" s="9" t="n"/>
+      <c r="AE10" s="9" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AE10" s="9" t="n">
+      <c r="AH10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AF10" s="12">
-        <f>AE10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
       <c r="AJ10" s="9" t="n"/>
       <c r="AK10" s="9" t="n"/>
       <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AQ10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
-      <c r="AS10" s="9" t="n">
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AT10" s="9" t="n">
+      <c r="AW10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AV10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
       <c r="AY10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ10" s="9" t="n">
         <v>462</v>
@@ -3525,58 +3678,68 @@
         <v>2</v>
       </c>
       <c r="BC10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BD10" s="12">
         <f>BC10/$E$10</f>
         <v/>
       </c>
       <c r="BE10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
       <c r="BK10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BL10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
         <v/>
       </c>
       <c r="BN10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="BO10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="BP10" s="12">
         <f>BO10/$E$10</f>
         <v/>
       </c>
-      <c r="BQ10" s="9" t="n"/>
+      <c r="BQ10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="BR10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="BS10" s="12">
         <f>BR10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BT10" s="9" t="n"/>
+      <c r="BU10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="BV10" s="12">
+        <f>BU10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -3623,7 +3786,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>467</v>
@@ -3636,17 +3799,17 @@
         <v>1</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
@@ -3672,60 +3835,60 @@
         <f>Y11/$E$11</f>
         <v/>
       </c>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="9" t="n">
+      <c r="AA11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AC11" s="12">
+        <f>AB11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9" t="n"/>
+      <c r="AE11" s="9" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AH11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AF11" s="12">
-        <f>AE11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
       <c r="AJ11" s="9" t="n"/>
       <c r="AK11" s="9" t="n"/>
       <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n"/>
-      <c r="AR11" s="12" t="n"/>
-      <c r="AS11" s="9" t="n">
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AT11" s="9" t="n">
+      <c r="AW11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="AU11" s="12">
-        <f>AT11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AV11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="AX11" s="12">
         <f>AW11/$E$11</f>
         <v/>
       </c>
       <c r="AY11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ11" s="9" t="n">
         <v>463</v>
@@ -3735,40 +3898,40 @@
         <v/>
       </c>
       <c r="BB11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BF11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
         <v/>
       </c>
       <c r="BH11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
         <v/>
       </c>
       <c r="BK11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
@@ -3778,18 +3941,28 @@
         <v>2</v>
       </c>
       <c r="BO11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BP11" s="12">
         <f>BO11/$E$11</f>
         <v/>
       </c>
-      <c r="BQ11" s="9" t="n"/>
+      <c r="BQ11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="BR11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BS11" s="12">
         <f>BR11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BT11" s="9" t="n"/>
+      <c r="BU11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="BV11" s="12">
+        <f>BU11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -3836,7 +4009,7 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>236</v>
@@ -3846,17 +4019,17 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
         <v>235</v>
@@ -3866,10 +4039,10 @@
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
@@ -3885,48 +4058,48 @@
         <f>Y12/$E$12</f>
         <v/>
       </c>
-      <c r="AA12" s="9" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="12" t="n"/>
-      <c r="AD12" s="9" t="n">
+      <c r="AA12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AC12" s="12">
+        <f>AB12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="9" t="n"/>
+      <c r="AE12" s="9" t="n"/>
+      <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AE12" s="9" t="n">
+      <c r="AH12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AF12" s="12">
-        <f>AE12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
       <c r="AJ12" s="9" t="n"/>
       <c r="AK12" s="9" t="n"/>
       <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
+      <c r="AP12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n"/>
-      <c r="AR12" s="12" t="n"/>
-      <c r="AS12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="AU12" s="12">
-        <f>AT12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
       <c r="AV12" s="9" t="n">
         <v>0</v>
       </c>
@@ -3968,7 +4141,7 @@
         <v/>
       </c>
       <c r="BH12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI12" s="9" t="n">
         <v>236</v>
@@ -3978,31 +4151,41 @@
         <v/>
       </c>
       <c r="BK12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BL12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BM12" s="12">
         <f>BL12/$E$12</f>
         <v/>
       </c>
       <c r="BN12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="BO12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BP12" s="12">
         <f>BO12/$E$12</f>
         <v/>
       </c>
-      <c r="BQ12" s="9" t="n"/>
+      <c r="BQ12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="BR12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="BS12" s="12">
         <f>BR12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BT12" s="9" t="n"/>
+      <c r="BU12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BV12" s="12">
+        <f>BU12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -4029,7 +4212,7 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>621</v>
@@ -4039,142 +4222,142 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="12" t="n"/>
-      <c r="AD13" s="9" t="n">
+      <c r="AA13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AC13" s="12">
+        <f>AB13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="9" t="n"/>
+      <c r="AE13" s="9" t="n"/>
+      <c r="AF13" s="12" t="n"/>
+      <c r="AG13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AE13" s="9" t="n">
+      <c r="AH13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AF13" s="12">
-        <f>AE13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
       <c r="AJ13" s="9" t="n"/>
       <c r="AK13" s="9" t="n"/>
       <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AQ13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n"/>
-      <c r="AR13" s="12" t="n"/>
-      <c r="AS13" s="9" t="n">
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AT13" s="9" t="n">
+      <c r="AW13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="AU13" s="12">
-        <f>AT13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AV13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
       <c r="AY13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
         <v/>
       </c>
       <c r="BB13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
@@ -4184,38 +4367,48 @@
         <v>4</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
       <c r="BK13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BL13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
         <v/>
       </c>
       <c r="BN13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="BO13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
         <v/>
       </c>
-      <c r="BQ13" s="9" t="n"/>
+      <c r="BQ13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="BR13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BT13" s="9" t="n"/>
+      <c r="BU13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="BV13" s="12">
+        <f>BU13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -4242,7 +4435,7 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1145</v>
@@ -4252,17 +4445,17 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>1142</v>
@@ -4272,122 +4465,122 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
         <v/>
       </c>
-      <c r="AA14" s="9" t="n"/>
-      <c r="AB14" s="9" t="n"/>
-      <c r="AC14" s="12" t="n"/>
-      <c r="AD14" s="9" t="n">
+      <c r="AA14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AC14" s="12">
+        <f>AB14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="9" t="n"/>
+      <c r="AE14" s="9" t="n"/>
+      <c r="AF14" s="12" t="n"/>
+      <c r="AG14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AE14" s="9" t="n">
+      <c r="AH14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AF14" s="12">
-        <f>AE14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
       <c r="AJ14" s="9" t="n"/>
       <c r="AK14" s="9" t="n"/>
       <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AQ14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n"/>
-      <c r="AR14" s="12" t="n"/>
-      <c r="AS14" s="9" t="n">
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AT14" s="9" t="n">
+      <c r="AW14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="AU14" s="12">
-        <f>AT14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AV14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
       <c r="AY14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AZ14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
         <v/>
       </c>
       <c r="BB14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BC14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BD14" s="12">
         <f>BC14/$E$14</f>
         <v/>
       </c>
       <c r="BE14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BF14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BG14" s="12">
         <f>BF14/$E$14</f>
@@ -4423,12 +4616,22 @@
         <f>BO14/$E$14</f>
         <v/>
       </c>
-      <c r="BQ14" s="9" t="n"/>
+      <c r="BQ14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BR14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BS14" s="12">
         <f>BR14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BT14" s="9" t="n"/>
+      <c r="BU14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" s="12">
+        <f>BU14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -4455,7 +4658,7 @@
         <v>551</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>126</v>
@@ -4468,17 +4671,17 @@
         <v>1</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K15" s="12">
         <f>J15/$E$15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N15" s="12">
         <f>M15/$E$15</f>
@@ -4495,7 +4698,7 @@
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>124</v>
@@ -4505,17 +4708,17 @@
         <v/>
       </c>
       <c r="U15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="W15" s="12">
         <f>V15/$E$15</f>
         <v/>
       </c>
       <c r="X15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>121</v>
@@ -4524,53 +4727,53 @@
         <f>Y15/$E$15</f>
         <v/>
       </c>
-      <c r="AA15" s="9" t="n"/>
-      <c r="AB15" s="9" t="n"/>
-      <c r="AC15" s="12" t="n"/>
-      <c r="AD15" s="9" t="n">
+      <c r="AA15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AC15" s="12">
+        <f>AB15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="9" t="n"/>
+      <c r="AE15" s="9" t="n"/>
+      <c r="AF15" s="12" t="n"/>
+      <c r="AG15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AE15" s="9" t="n">
+      <c r="AH15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AF15" s="12">
-        <f>AE15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AG15" s="9" t="n"/>
-      <c r="AH15" s="9" t="n"/>
-      <c r="AI15" s="12" t="n"/>
+      <c r="AI15" s="12">
+        <f>AH15/$E$15</f>
+        <v/>
+      </c>
       <c r="AJ15" s="9" t="n"/>
       <c r="AK15" s="9" t="n"/>
       <c r="AL15" s="12" t="n"/>
-      <c r="AM15" s="9" t="n">
+      <c r="AM15" s="9" t="n"/>
+      <c r="AN15" s="9" t="n"/>
+      <c r="AO15" s="12" t="n"/>
+      <c r="AP15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AN15" s="9" t="n">
+      <c r="AQ15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AO15" s="12">
-        <f>AN15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AP15" s="9" t="n"/>
-      <c r="AQ15" s="9" t="n"/>
-      <c r="AR15" s="12" t="n"/>
-      <c r="AS15" s="9" t="n">
+      <c r="AR15" s="12">
+        <f>AQ15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AS15" s="9" t="n"/>
+      <c r="AT15" s="9" t="n"/>
+      <c r="AU15" s="12" t="n"/>
+      <c r="AV15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AT15" s="9" t="n">
+      <c r="AW15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="AU15" s="12">
-        <f>AT15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AV15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="AX15" s="12">
         <f>AW15/$E$15</f>
@@ -4580,24 +4783,24 @@
         <v>3</v>
       </c>
       <c r="AZ15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BA15" s="12">
         <f>AZ15/$E$15</f>
         <v/>
       </c>
       <c r="BB15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BD15" s="12">
         <f>BC15/$E$15</f>
         <v/>
       </c>
       <c r="BE15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BF15" s="9" t="n">
         <v>76</v>
@@ -4607,10 +4810,10 @@
         <v/>
       </c>
       <c r="BH15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BI15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BJ15" s="12">
         <f>BI15/$E$15</f>
@@ -4636,12 +4839,22 @@
         <f>BO15/$E$15</f>
         <v/>
       </c>
-      <c r="BQ15" s="9" t="n"/>
+      <c r="BQ15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BR15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BS15" s="12">
         <f>BR15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BT15" s="9" t="n"/>
+      <c r="BU15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" s="12">
+        <f>BU15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -4737,51 +4950,58 @@
         <f>Y16/$E$16</f>
         <v/>
       </c>
-      <c r="AA16" s="9" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="9" t="n">
+      <c r="AA16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AF16" s="12">
-        <f>AE16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
+      <c r="AC16" s="12">
+        <f>AB16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="9" t="n"/>
+      <c r="AE16" s="9" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
       <c r="AJ16" s="9" t="n"/>
       <c r="AK16" s="9" t="n"/>
       <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
-      <c r="AS16" s="9" t="n">
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AT16" s="9" t="n">
+      <c r="AW16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AU16" s="12">
-        <f>AT16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
       <c r="AY16" s="9" t="n"/>
       <c r="AZ16" s="9" t="n"/>
       <c r="BA16" s="12" t="n"/>
@@ -4801,11 +5021,14 @@
       <c r="BO16" s="9" t="n"/>
       <c r="BP16" s="12" t="n"/>
       <c r="BQ16" s="9" t="n"/>
-      <c r="BR16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" s="12">
-        <f>BR16/$E$16</f>
+      <c r="BR16" s="9" t="n"/>
+      <c r="BS16" s="12" t="n"/>
+      <c r="BT16" s="9" t="n"/>
+      <c r="BU16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" s="12">
+        <f>BU16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -4897,14 +5120,18 @@
       <c r="BQ17" s="9" t="n"/>
       <c r="BR17" s="9" t="n"/>
       <c r="BS17" s="12" t="n"/>
+      <c r="BT17" s="9" t="n"/>
+      <c r="BU17" s="9" t="n"/>
+      <c r="BV17" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
+    <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
@@ -4933,7 +5160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5007,6 +5234,9 @@
     <col width="9" customWidth="1" min="69" max="69"/>
     <col width="9" customWidth="1" min="70" max="70"/>
     <col width="9" customWidth="1" min="71" max="71"/>
+    <col width="9" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="9" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5025,69 +5255,72 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -5445,6 +5678,21 @@
         </is>
       </c>
       <c r="BS4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BT4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BU4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BV4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -5473,7 +5721,7 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>298</v>
@@ -5486,115 +5734,122 @@
         <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
-      <c r="O5" s="9" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="12" t="n"/>
-      <c r="R5" s="9" t="n">
+      <c r="O5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q5" s="12">
+        <f>P5/$E$5</f>
+        <v/>
+      </c>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="12" t="n"/>
+      <c r="U5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="V5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="T5" s="12">
-        <f>S5/$E$5</f>
-        <v/>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="12" t="n"/>
-      <c r="AG5" s="9" t="n">
+      <c r="AD5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AG5" s="9" t="n"/>
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AH5" s="9" t="n">
+      <c r="AK5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AI5" s="12">
-        <f>AH5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AK5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
-      <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
-      <c r="AP5" s="9" t="n">
+      <c r="AM5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AN5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AP5" s="9" t="n"/>
+      <c r="AQ5" s="9" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AQ5" s="9" t="n">
+      <c r="AT5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="AR5" s="12">
-        <f>AQ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
       <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n">
+      <c r="AW5" s="9" t="n"/>
+      <c r="AX5" s="12" t="n"/>
+      <c r="AY5" s="9" t="n"/>
+      <c r="AZ5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="AX5" s="12">
-        <f>AW5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n"/>
-      <c r="BA5" s="12" t="n"/>
+      <c r="BA5" s="12">
+        <f>AZ5/$E$5</f>
+        <v/>
+      </c>
       <c r="BB5" s="9" t="n"/>
       <c r="BC5" s="9" t="n"/>
       <c r="BD5" s="12" t="n"/>
@@ -5613,6 +5868,9 @@
       <c r="BQ5" s="9" t="n"/>
       <c r="BR5" s="9" t="n"/>
       <c r="BS5" s="12" t="n"/>
+      <c r="BT5" s="9" t="n"/>
+      <c r="BU5" s="9" t="n"/>
+      <c r="BV5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -5637,7 +5895,7 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>950</v>
@@ -5647,118 +5905,125 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="12" t="n"/>
-      <c r="R6" s="9" t="n">
+      <c r="O6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>P6/$E$6</f>
+        <v/>
+      </c>
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="V6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="T6" s="12">
-        <f>S6/$E$6</f>
-        <v/>
-      </c>
-      <c r="U6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="V6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
-      <c r="AG6" s="9" t="n">
+      <c r="AD6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
-      <c r="AP6" s="9" t="n">
+      <c r="AM6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ6" s="9" t="n">
+      <c r="AT6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
       <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n">
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
       <c r="BB6" s="9" t="n"/>
       <c r="BC6" s="9" t="n"/>
       <c r="BD6" s="12" t="n"/>
@@ -5777,6 +6042,9 @@
       <c r="BQ6" s="9" t="n"/>
       <c r="BR6" s="9" t="n"/>
       <c r="BS6" s="12" t="n"/>
+      <c r="BT6" s="9" t="n"/>
+      <c r="BU6" s="9" t="n"/>
+      <c r="BV6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -5830,99 +6098,106 @@
         <f>M7/$E$7</f>
         <v/>
       </c>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="12" t="n"/>
-      <c r="R7" s="9" t="n">
+      <c r="O7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q7" s="12">
+        <f>P7/$E$7</f>
+        <v/>
+      </c>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="12" t="n"/>
+      <c r="U7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="V7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="T7" s="12">
-        <f>S7/$E$7</f>
-        <v/>
-      </c>
-      <c r="U7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="9" t="n">
+      <c r="AD7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AH7" s="9" t="n">
+      <c r="AE7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
-      <c r="AP7" s="9" t="n">
+      <c r="AM7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AQ7" s="9" t="n">
+      <c r="AT7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
       <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n">
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
       <c r="BB7" s="9" t="n"/>
       <c r="BC7" s="9" t="n"/>
       <c r="BD7" s="12" t="n"/>
@@ -5941,6 +6216,9 @@
       <c r="BQ7" s="9" t="n"/>
       <c r="BR7" s="9" t="n"/>
       <c r="BS7" s="12" t="n"/>
+      <c r="BT7" s="9" t="n"/>
+      <c r="BU7" s="9" t="n"/>
+      <c r="BV7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5965,7 +6243,7 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1054</v>
@@ -5975,17 +6253,17 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>1052</v>
@@ -5994,99 +6272,106 @@
         <f>M8/$E$8</f>
         <v/>
       </c>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="12" t="n"/>
-      <c r="R8" s="9" t="n">
+      <c r="O8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="P8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="Q8" s="12">
+        <f>P8/$E$8</f>
+        <v/>
+      </c>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="T8" s="12">
-        <f>S8/$E$8</f>
-        <v/>
-      </c>
-      <c r="U8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
-      <c r="AG8" s="9" t="n">
+      <c r="AD8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AH8" s="9" t="n">
+      <c r="AK8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
-      <c r="AP8" s="9" t="n">
+      <c r="AM8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ8" s="9" t="n">
+      <c r="AT8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
       <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n">
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
       <c r="BB8" s="9" t="n"/>
       <c r="BC8" s="9" t="n"/>
       <c r="BD8" s="12" t="n"/>
@@ -6105,6 +6390,9 @@
       <c r="BQ8" s="9" t="n"/>
       <c r="BR8" s="9" t="n"/>
       <c r="BS8" s="12" t="n"/>
+      <c r="BT8" s="9" t="n"/>
+      <c r="BU8" s="9" t="n"/>
+      <c r="BV8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -6158,19 +6446,19 @@
         <f>M9/$E$9</f>
         <v/>
       </c>
-      <c r="O9" s="9" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="9" t="n">
+      <c r="O9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="T9" s="12">
-        <f>S9/$E$9</f>
-        <v/>
-      </c>
+      <c r="Q9" s="12">
+        <f>P9/$E$9</f>
+        <v/>
+      </c>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="12" t="n"/>
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
@@ -6182,7 +6470,7 @@
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>845</v>
@@ -6192,28 +6480,28 @@
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AC9" s="12">
         <f>AB9/$E$9</f>
         <v/>
       </c>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="9" t="n">
+      <c r="AD9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
       <c r="AJ9" s="9" t="n">
         <v>0</v>
       </c>
@@ -6224,33 +6512,40 @@
         <f>AK9/$E$9</f>
         <v/>
       </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
-      <c r="AP9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="9" t="n">
+      <c r="AM9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
       <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n">
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
       <c r="BB9" s="9" t="n"/>
       <c r="BC9" s="9" t="n"/>
       <c r="BD9" s="12" t="n"/>
@@ -6269,6 +6564,9 @@
       <c r="BQ9" s="9" t="n"/>
       <c r="BR9" s="9" t="n"/>
       <c r="BS9" s="12" t="n"/>
+      <c r="BT9" s="9" t="n"/>
+      <c r="BU9" s="9" t="n"/>
+      <c r="BV9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -6293,7 +6591,7 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>1418</v>
@@ -6303,118 +6601,125 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
-      <c r="O10" s="9" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="9" t="n">
+      <c r="O10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="Q10" s="12">
+        <f>P10/$E$10</f>
+        <v/>
+      </c>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="12" t="n"/>
+      <c r="U10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="V10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="T10" s="12">
-        <f>S10/$E$10</f>
-        <v/>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="V10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="9" t="n">
+      <c r="AD10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AF10" s="12">
+        <f>AE10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AH10" s="9" t="n">
+      <c r="AK10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AI10" s="12">
-        <f>AH10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
-      <c r="AP10" s="9" t="n">
+      <c r="AM10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AQ10" s="9" t="n">
+      <c r="AN10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
       <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n">
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="AX10" s="12">
-        <f>AW10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
       <c r="BB10" s="9" t="n"/>
       <c r="BC10" s="9" t="n"/>
       <c r="BD10" s="12" t="n"/>
@@ -6433,6 +6738,9 @@
       <c r="BQ10" s="9" t="n"/>
       <c r="BR10" s="9" t="n"/>
       <c r="BS10" s="12" t="n"/>
+      <c r="BT10" s="9" t="n"/>
+      <c r="BU10" s="9" t="n"/>
+      <c r="BV10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -6457,7 +6765,7 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>992</v>
@@ -6467,10 +6775,10 @@
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
@@ -6486,99 +6794,106 @@
         <f>M11/$E$11</f>
         <v/>
       </c>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="12" t="n"/>
-      <c r="R11" s="9" t="n">
+      <c r="O11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="Q11" s="12">
+        <f>P11/$E$11</f>
+        <v/>
+      </c>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="12" t="n"/>
+      <c r="U11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="V11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="T11" s="12">
-        <f>S11/$E$11</f>
-        <v/>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="V11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
         <v/>
       </c>
       <c r="X11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="Z11" s="12">
         <f>Y11/$E$11</f>
         <v/>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AC11" s="12">
         <f>AB11/$E$11</f>
         <v/>
       </c>
-      <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="9" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="9" t="n">
+      <c r="AD11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AF11" s="12">
+        <f>AE11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AH11" s="9" t="n">
+      <c r="AK11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AI11" s="12">
-        <f>AH11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AL11" s="12">
         <f>AK11/$E$11</f>
         <v/>
       </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
-      <c r="AP11" s="9" t="n">
+      <c r="AM11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AP11" s="9" t="n"/>
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AQ11" s="9" t="n">
+      <c r="AT11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="AR11" s="12">
-        <f>AQ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
       <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n">
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="9" t="n"/>
+      <c r="AZ11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="AX11" s="12">
-        <f>AW11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n"/>
-      <c r="BA11" s="12" t="n"/>
+      <c r="BA11" s="12">
+        <f>AZ11/$E$11</f>
+        <v/>
+      </c>
       <c r="BB11" s="9" t="n"/>
       <c r="BC11" s="9" t="n"/>
       <c r="BD11" s="12" t="n"/>
@@ -6597,6 +6912,9 @@
       <c r="BQ11" s="9" t="n"/>
       <c r="BR11" s="9" t="n"/>
       <c r="BS11" s="12" t="n"/>
+      <c r="BT11" s="9" t="n"/>
+      <c r="BU11" s="9" t="n"/>
+      <c r="BV11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -6621,7 +6939,7 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>737</v>
@@ -6631,118 +6949,125 @@
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="N12" s="12">
         <f>M12/$E$12</f>
         <v/>
       </c>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="12" t="n"/>
-      <c r="R12" s="9" t="n">
+      <c r="O12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="Q12" s="12">
+        <f>P12/$E$12</f>
+        <v/>
+      </c>
+      <c r="R12" s="9" t="n"/>
+      <c r="S12" s="9" t="n"/>
+      <c r="T12" s="12" t="n"/>
+      <c r="U12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="V12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="T12" s="12">
-        <f>S12/$E$12</f>
-        <v/>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AC12" s="12">
         <f>AB12/$E$12</f>
         <v/>
       </c>
-      <c r="AD12" s="9" t="n"/>
-      <c r="AE12" s="9" t="n"/>
-      <c r="AF12" s="12" t="n"/>
-      <c r="AG12" s="9" t="n">
+      <c r="AD12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AF12" s="12">
+        <f>AE12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="9" t="n"/>
+      <c r="AH12" s="9" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AH12" s="9" t="n">
+      <c r="AK12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AI12" s="12">
-        <f>AH12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AL12" s="12">
         <f>AK12/$E$12</f>
         <v/>
       </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
-      <c r="AP12" s="9" t="n">
+      <c r="AM12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AP12" s="9" t="n"/>
+      <c r="AQ12" s="9" t="n"/>
+      <c r="AR12" s="12" t="n"/>
+      <c r="AS12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AQ12" s="9" t="n">
+      <c r="AT12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="AR12" s="12">
-        <f>AQ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
       <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n">
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="12" t="n"/>
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="AX12" s="12">
-        <f>AW12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n"/>
-      <c r="BA12" s="12" t="n"/>
+      <c r="BA12" s="12">
+        <f>AZ12/$E$12</f>
+        <v/>
+      </c>
       <c r="BB12" s="9" t="n"/>
       <c r="BC12" s="9" t="n"/>
       <c r="BD12" s="12" t="n"/>
@@ -6761,6 +7086,9 @@
       <c r="BQ12" s="9" t="n"/>
       <c r="BR12" s="9" t="n"/>
       <c r="BS12" s="12" t="n"/>
+      <c r="BT12" s="9" t="n"/>
+      <c r="BU12" s="9" t="n"/>
+      <c r="BV12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -6805,7 +7133,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>1391</v>
@@ -6814,99 +7142,106 @@
         <f>M13/$E$13</f>
         <v/>
       </c>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="12" t="n"/>
-      <c r="R13" s="9" t="n">
+      <c r="O13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="P13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="Q13" s="12">
+        <f>P13/$E$13</f>
+        <v/>
+      </c>
+      <c r="R13" s="9" t="n"/>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="12" t="n"/>
+      <c r="U13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="T13" s="12">
-        <f>S13/$E$13</f>
-        <v/>
-      </c>
-      <c r="U13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
-      <c r="AD13" s="9" t="n"/>
-      <c r="AE13" s="9" t="n"/>
-      <c r="AF13" s="12" t="n"/>
-      <c r="AG13" s="9" t="n">
+      <c r="AD13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AF13" s="12">
+        <f>AE13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AH13" s="9" t="n">
+      <c r="AK13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AI13" s="12">
-        <f>AH13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
-      <c r="AP13" s="9" t="n">
+      <c r="AM13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AP13" s="9" t="n"/>
+      <c r="AQ13" s="9" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AQ13" s="9" t="n">
+      <c r="AT13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="AR13" s="12">
-        <f>AQ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
       <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n">
+      <c r="AW13" s="9" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="AX13" s="12">
-        <f>AW13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n"/>
-      <c r="BA13" s="12" t="n"/>
+      <c r="BA13" s="12">
+        <f>AZ13/$E$13</f>
+        <v/>
+      </c>
       <c r="BB13" s="9" t="n"/>
       <c r="BC13" s="9" t="n"/>
       <c r="BD13" s="12" t="n"/>
@@ -6925,6 +7260,9 @@
       <c r="BQ13" s="9" t="n"/>
       <c r="BR13" s="9" t="n"/>
       <c r="BS13" s="12" t="n"/>
+      <c r="BT13" s="9" t="n"/>
+      <c r="BU13" s="9" t="n"/>
+      <c r="BV13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -6969,7 +7307,7 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>902</v>
@@ -6978,21 +7316,21 @@
         <f>M14/$E$14</f>
         <v/>
       </c>
-      <c r="O14" s="9" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="12" t="n"/>
-      <c r="R14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="T14" s="12">
-        <f>S14/$E$14</f>
-        <v/>
-      </c>
+      <c r="O14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="Q14" s="12">
+        <f>P14/$E$14</f>
+        <v/>
+      </c>
+      <c r="R14" s="9" t="n"/>
+      <c r="S14" s="9" t="n"/>
+      <c r="T14" s="12" t="n"/>
       <c r="U14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>898</v>
@@ -7002,75 +7340,82 @@
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AC14" s="12">
         <f>AB14/$E$14</f>
         <v/>
       </c>
-      <c r="AD14" s="9" t="n"/>
-      <c r="AE14" s="9" t="n"/>
-      <c r="AF14" s="12" t="n"/>
-      <c r="AG14" s="9" t="n">
+      <c r="AD14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AF14" s="12">
+        <f>AE14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AH14" s="9" t="n">
+      <c r="AK14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AI14" s="12">
-        <f>AH14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
-      <c r="AP14" s="9" t="n">
+      <c r="AM14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AQ14" s="9" t="n">
+      <c r="AN14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="AR14" s="12">
-        <f>AQ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
       <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n">
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="9" t="n"/>
+      <c r="AZ14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="AX14" s="12">
-        <f>AW14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n"/>
-      <c r="BA14" s="12" t="n"/>
+      <c r="BA14" s="12">
+        <f>AZ14/$E$14</f>
+        <v/>
+      </c>
       <c r="BB14" s="9" t="n"/>
       <c r="BC14" s="9" t="n"/>
       <c r="BD14" s="12" t="n"/>
@@ -7089,6 +7434,9 @@
       <c r="BQ14" s="9" t="n"/>
       <c r="BR14" s="9" t="n"/>
       <c r="BS14" s="12" t="n"/>
+      <c r="BT14" s="9" t="n"/>
+      <c r="BU14" s="9" t="n"/>
+      <c r="BV14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -7178,6 +7526,9 @@
       <c r="BQ15" s="9" t="n"/>
       <c r="BR15" s="9" t="n"/>
       <c r="BS15" s="12" t="n"/>
+      <c r="BT15" s="9" t="n"/>
+      <c r="BU15" s="9" t="n"/>
+      <c r="BV15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -7202,7 +7553,7 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>715</v>
@@ -7212,118 +7563,125 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="K16" s="12">
         <f>J16/$E$16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="N16" s="12">
         <f>M16/$E$16</f>
         <v/>
       </c>
-      <c r="O16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="12" t="n"/>
-      <c r="R16" s="9" t="n">
+      <c r="O16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="Q16" s="12">
+        <f>P16/$E$16</f>
+        <v/>
+      </c>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="12" t="n"/>
+      <c r="U16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="S16" s="9" t="n">
+      <c r="V16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="T16" s="12">
-        <f>S16/$E$16</f>
-        <v/>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
         <v/>
       </c>
       <c r="X16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="Z16" s="12">
         <f>Y16/$E$16</f>
         <v/>
       </c>
       <c r="AA16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AC16" s="12">
         <f>AB16/$E$16</f>
         <v/>
       </c>
-      <c r="AD16" s="9" t="n"/>
-      <c r="AE16" s="9" t="n"/>
-      <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="9" t="n">
+      <c r="AD16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AF16" s="12">
+        <f>AE16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AH16" s="9" t="n">
+      <c r="AK16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AI16" s="12">
-        <f>AH16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AL16" s="12">
         <f>AK16/$E$16</f>
         <v/>
       </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
-      <c r="AP16" s="9" t="n">
+      <c r="AM16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AQ16" s="9" t="n">
+      <c r="AT16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
       <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n">
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="AX16" s="12">
-        <f>AW16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
       <c r="BB16" s="9" t="n"/>
       <c r="BC16" s="9" t="n"/>
       <c r="BD16" s="12" t="n"/>
@@ -7342,6 +7700,9 @@
       <c r="BQ16" s="9" t="n"/>
       <c r="BR16" s="9" t="n"/>
       <c r="BS16" s="12" t="n"/>
+      <c r="BT16" s="9" t="n"/>
+      <c r="BU16" s="9" t="n"/>
+      <c r="BV16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -7376,7 +7737,7 @@
         <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>385</v>
@@ -7386,108 +7747,115 @@
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N17" s="12">
         <f>M17/$E$17</f>
         <v/>
       </c>
-      <c r="O17" s="9" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="12" t="n"/>
-      <c r="R17" s="9" t="n">
+      <c r="O17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="P17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q17" s="12">
+        <f>P17/$E$17</f>
+        <v/>
+      </c>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="12" t="n"/>
+      <c r="U17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="T17" s="12">
-        <f>S17/$E$17</f>
-        <v/>
-      </c>
-      <c r="U17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
         <v/>
       </c>
       <c r="X17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="Z17" s="12">
         <f>Y17/$E$17</f>
         <v/>
       </c>
       <c r="AA17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AC17" s="12">
         <f>AB17/$E$17</f>
         <v/>
       </c>
-      <c r="AD17" s="9" t="n"/>
-      <c r="AE17" s="9" t="n"/>
-      <c r="AF17" s="12" t="n"/>
-      <c r="AG17" s="9" t="n">
+      <c r="AD17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF17" s="12">
+        <f>AE17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AH17" s="9" t="n">
+      <c r="AK17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AI17" s="12">
-        <f>AH17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AL17" s="12">
         <f>AK17/$E$17</f>
         <v/>
       </c>
-      <c r="AM17" s="9" t="n"/>
-      <c r="AN17" s="9" t="n"/>
-      <c r="AO17" s="12" t="n"/>
-      <c r="AP17" s="9" t="n">
+      <c r="AM17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AO17" s="12">
+        <f>AN17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AP17" s="9" t="n"/>
+      <c r="AQ17" s="9" t="n"/>
+      <c r="AR17" s="12" t="n"/>
+      <c r="AS17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AQ17" s="9" t="n">
+      <c r="AT17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="AR17" s="12">
-        <f>AQ17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AS17" s="9" t="n"/>
-      <c r="AT17" s="9" t="n"/>
-      <c r="AU17" s="12" t="n"/>
+      <c r="AU17" s="12">
+        <f>AT17/$E$17</f>
+        <v/>
+      </c>
       <c r="AV17" s="9" t="n"/>
-      <c r="AW17" s="9" t="n">
+      <c r="AW17" s="9" t="n"/>
+      <c r="AX17" s="12" t="n"/>
+      <c r="AY17" s="9" t="n"/>
+      <c r="AZ17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="AX17" s="12">
-        <f>AW17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AY17" s="9" t="n"/>
-      <c r="AZ17" s="9" t="n"/>
-      <c r="BA17" s="12" t="n"/>
+      <c r="BA17" s="12">
+        <f>AZ17/$E$17</f>
+        <v/>
+      </c>
       <c r="BB17" s="9" t="n"/>
       <c r="BC17" s="9" t="n"/>
       <c r="BD17" s="12" t="n"/>
@@ -7506,6 +7874,9 @@
       <c r="BQ17" s="9" t="n"/>
       <c r="BR17" s="9" t="n"/>
       <c r="BS17" s="12" t="n"/>
+      <c r="BT17" s="9" t="n"/>
+      <c r="BU17" s="9" t="n"/>
+      <c r="BV17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -7530,7 +7901,7 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>292</v>
@@ -7540,118 +7911,125 @@
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
         <v/>
       </c>
-      <c r="O18" s="9" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="12" t="n"/>
-      <c r="R18" s="9" t="n">
+      <c r="O18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q18" s="12">
+        <f>P18/$E$18</f>
+        <v/>
+      </c>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="9" t="n"/>
+      <c r="T18" s="12" t="n"/>
+      <c r="U18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="V18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="T18" s="12">
-        <f>S18/$E$18</f>
-        <v/>
-      </c>
-      <c r="U18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
       <c r="X18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Z18" s="12">
         <f>Y18/$E$18</f>
         <v/>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AC18" s="12">
         <f>AB18/$E$18</f>
         <v/>
       </c>
-      <c r="AD18" s="9" t="n"/>
-      <c r="AE18" s="9" t="n"/>
-      <c r="AF18" s="12" t="n"/>
-      <c r="AG18" s="9" t="n">
+      <c r="AD18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF18" s="12">
+        <f>AE18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="9" t="n"/>
+      <c r="AI18" s="12" t="n"/>
+      <c r="AJ18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AH18" s="9" t="n">
+      <c r="AK18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AI18" s="12">
-        <f>AH18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AL18" s="12">
         <f>AK18/$E$18</f>
         <v/>
       </c>
-      <c r="AM18" s="9" t="n"/>
-      <c r="AN18" s="9" t="n"/>
-      <c r="AO18" s="12" t="n"/>
-      <c r="AP18" s="9" t="n">
+      <c r="AM18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AO18" s="12">
+        <f>AN18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AP18" s="9" t="n"/>
+      <c r="AQ18" s="9" t="n"/>
+      <c r="AR18" s="12" t="n"/>
+      <c r="AS18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ18" s="9" t="n">
+      <c r="AT18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="AR18" s="12">
-        <f>AQ18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AS18" s="9" t="n"/>
-      <c r="AT18" s="9" t="n"/>
-      <c r="AU18" s="12" t="n"/>
+      <c r="AU18" s="12">
+        <f>AT18/$E$18</f>
+        <v/>
+      </c>
       <c r="AV18" s="9" t="n"/>
-      <c r="AW18" s="9" t="n">
+      <c r="AW18" s="9" t="n"/>
+      <c r="AX18" s="12" t="n"/>
+      <c r="AY18" s="9" t="n"/>
+      <c r="AZ18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="AX18" s="12">
-        <f>AW18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AY18" s="9" t="n"/>
-      <c r="AZ18" s="9" t="n"/>
-      <c r="BA18" s="12" t="n"/>
+      <c r="BA18" s="12">
+        <f>AZ18/$E$18</f>
+        <v/>
+      </c>
       <c r="BB18" s="9" t="n"/>
       <c r="BC18" s="9" t="n"/>
       <c r="BD18" s="12" t="n"/>
@@ -7670,14 +8048,18 @@
       <c r="BQ18" s="9" t="n"/>
       <c r="BR18" s="9" t="n"/>
       <c r="BS18" s="12" t="n"/>
+      <c r="BT18" s="9" t="n"/>
+      <c r="BU18" s="9" t="n"/>
+      <c r="BV18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="U3:W3"/>
+    <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 15/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 16/08/2026</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 15/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 16/08/2026</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 15/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 16/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -1972,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV17"/>
+  <dimension ref="A1:BV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5123,6 +5123,103 @@
       <c r="BT17" s="9" t="n"/>
       <c r="BU17" s="9" t="n"/>
       <c r="BV17" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>BINASTRA COCHRANE</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>31332-1</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>BINASTRA SYNERGY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>830</v>
+      </c>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="H18" s="11">
+        <f>G18/$E$18</f>
+        <v/>
+      </c>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="12" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="9" t="n"/>
+      <c r="T18" s="12" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="12" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="12" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="9" t="n"/>
+      <c r="AC18" s="12" t="n"/>
+      <c r="AD18" s="9" t="n"/>
+      <c r="AE18" s="9" t="n"/>
+      <c r="AF18" s="12" t="n"/>
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="9" t="n"/>
+      <c r="AI18" s="12" t="n"/>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="9" t="n"/>
+      <c r="AL18" s="12" t="n"/>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="9" t="n"/>
+      <c r="AO18" s="12" t="n"/>
+      <c r="AP18" s="9" t="n"/>
+      <c r="AQ18" s="9" t="n"/>
+      <c r="AR18" s="12" t="n"/>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="9" t="n"/>
+      <c r="AU18" s="12" t="n"/>
+      <c r="AV18" s="9" t="n"/>
+      <c r="AW18" s="9" t="n"/>
+      <c r="AX18" s="12" t="n"/>
+      <c r="AY18" s="9" t="n"/>
+      <c r="AZ18" s="9" t="n"/>
+      <c r="BA18" s="12" t="n"/>
+      <c r="BB18" s="9" t="n"/>
+      <c r="BC18" s="9" t="n"/>
+      <c r="BD18" s="12" t="n"/>
+      <c r="BE18" s="9" t="n"/>
+      <c r="BF18" s="9" t="n"/>
+      <c r="BG18" s="12" t="n"/>
+      <c r="BH18" s="9" t="n"/>
+      <c r="BI18" s="9" t="n"/>
+      <c r="BJ18" s="12" t="n"/>
+      <c r="BK18" s="9" t="n"/>
+      <c r="BL18" s="9" t="n"/>
+      <c r="BM18" s="12" t="n"/>
+      <c r="BN18" s="9" t="n"/>
+      <c r="BO18" s="9" t="n"/>
+      <c r="BP18" s="12" t="n"/>
+      <c r="BQ18" s="9" t="n"/>
+      <c r="BR18" s="9" t="n"/>
+      <c r="BS18" s="12" t="n"/>
+      <c r="BT18" s="9" t="n"/>
+      <c r="BU18" s="9" t="n"/>
+      <c r="BV18" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -564,6 +564,9 @@
     <col width="9" customWidth="1" min="72" max="72"/>
     <col width="9" customWidth="1" min="73" max="73"/>
     <col width="9" customWidth="1" min="74" max="74"/>
+    <col width="9" customWidth="1" min="75" max="75"/>
+    <col width="9" customWidth="1" min="76" max="76"/>
+    <col width="9" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,72 +585,75 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1020,6 +1026,21 @@
         </is>
       </c>
       <c r="BV4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BW4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BX4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BY4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1068,7 +1089,7 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>43</v>
@@ -1078,17 +1099,17 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
         <v>42</v>
@@ -1101,49 +1122,56 @@
         <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
-      <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="12" t="n"/>
-      <c r="AD5" s="9" t="n">
+      <c r="AA5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="9" t="n"/>
+      <c r="AF5" s="12" t="n"/>
+      <c r="AG5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AE5" s="9" t="n">
+      <c r="AH5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AF5" s="12">
-        <f>AE5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
       <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n">
+      <c r="AK5" s="9" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AL5" s="12">
-        <f>AK5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
       <c r="AP5" s="9" t="n"/>
       <c r="AQ5" s="9" t="n"/>
       <c r="AR5" s="12" t="n"/>
@@ -1177,6 +1205,9 @@
       <c r="BT5" s="9" t="n"/>
       <c r="BU5" s="9" t="n"/>
       <c r="BV5" s="12" t="n"/>
+      <c r="BW5" s="9" t="n"/>
+      <c r="BX5" s="9" t="n"/>
+      <c r="BY5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1270,33 +1301,40 @@
         <f>Y6/$E$6</f>
         <v/>
       </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
-      <c r="AD6" s="9" t="n">
+      <c r="AA6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AH6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AF6" s="12">
-        <f>AE6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
       <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n">
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
       <c r="AP6" s="9" t="n"/>
       <c r="AQ6" s="9" t="n"/>
       <c r="AR6" s="12" t="n"/>
@@ -1330,6 +1368,9 @@
       <c r="BT6" s="9" t="n"/>
       <c r="BU6" s="9" t="n"/>
       <c r="BV6" s="12" t="n"/>
+      <c r="BW6" s="9" t="n"/>
+      <c r="BX6" s="9" t="n"/>
+      <c r="BY6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1384,7 +1425,7 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>45</v>
@@ -1394,62 +1435,69 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
-      <c r="AD7" s="9" t="n">
+      <c r="AA7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AE7" s="9" t="n">
+      <c r="AH7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AF7" s="12">
-        <f>AE7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
       <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n">
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
       <c r="AP7" s="9" t="n"/>
       <c r="AQ7" s="9" t="n"/>
       <c r="AR7" s="12" t="n"/>
@@ -1483,6 +1531,9 @@
       <c r="BT7" s="9" t="n"/>
       <c r="BU7" s="9" t="n"/>
       <c r="BV7" s="12" t="n"/>
+      <c r="BW7" s="9" t="n"/>
+      <c r="BX7" s="9" t="n"/>
+      <c r="BY7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1576,33 +1627,40 @@
         <f>Y8/$E$8</f>
         <v/>
       </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
-      <c r="AD8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="9" t="n">
+      <c r="AA8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AF8" s="12">
-        <f>AE8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
       <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n">
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
       <c r="AP8" s="9" t="n"/>
       <c r="AQ8" s="9" t="n"/>
       <c r="AR8" s="12" t="n"/>
@@ -1636,6 +1694,9 @@
       <c r="BT8" s="9" t="n"/>
       <c r="BU8" s="9" t="n"/>
       <c r="BV8" s="12" t="n"/>
+      <c r="BW8" s="9" t="n"/>
+      <c r="BX8" s="9" t="n"/>
+      <c r="BY8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1720,7 +1781,7 @@
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>1</v>
@@ -1729,33 +1790,40 @@
         <f>Y9/$E$9</f>
         <v/>
       </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="12">
-        <f>AE9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
+      <c r="AA9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9" t="n"/>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
       <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
       <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
+      <c r="AN9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
       <c r="AP9" s="9" t="n"/>
       <c r="AQ9" s="9" t="n"/>
       <c r="AR9" s="12" t="n"/>
@@ -1789,6 +1857,9 @@
       <c r="BT9" s="9" t="n"/>
       <c r="BU9" s="9" t="n"/>
       <c r="BV9" s="12" t="n"/>
+      <c r="BW9" s="9" t="n"/>
+      <c r="BX9" s="9" t="n"/>
+      <c r="BY9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1813,17 +1884,17 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>311</v>
@@ -1833,69 +1904,76 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
+      <c r="AA10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
       <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n">
+      <c r="AE10" s="9" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AF10" s="12">
-        <f>AE10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
       <c r="AJ10" s="9" t="n"/>
       <c r="AK10" s="9" t="n"/>
       <c r="AL10" s="12" t="n"/>
@@ -1935,9 +2013,12 @@
       <c r="BT10" s="9" t="n"/>
       <c r="BU10" s="9" t="n"/>
       <c r="BV10" s="12" t="n"/>
+      <c r="BW10" s="9" t="n"/>
+      <c r="BX10" s="9" t="n"/>
+      <c r="BY10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
@@ -1947,6 +2028,7 @@
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
+    <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AM3:AO3"/>
@@ -1972,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV18"/>
+  <dimension ref="A1:BY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2131,9 @@
     <col width="9" customWidth="1" min="72" max="72"/>
     <col width="9" customWidth="1" min="73" max="73"/>
     <col width="9" customWidth="1" min="74" max="74"/>
+    <col width="9" customWidth="1" min="75" max="75"/>
+    <col width="9" customWidth="1" min="76" max="76"/>
+    <col width="9" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2067,72 +2152,75 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2505,6 +2593,21 @@
         </is>
       </c>
       <c r="BV4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BW4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BX4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BY4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2553,7 +2656,7 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>177</v>
@@ -2562,17 +2665,24 @@
         <f>M5/$E$5</f>
         <v/>
       </c>
-      <c r="O5" s="9" t="n"/>
+      <c r="O5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="P5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="12" t="n"/>
+      <c r="S5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="T5" s="12">
+        <f>S5/$E$5</f>
+        <v/>
+      </c>
       <c r="U5" s="9" t="n"/>
       <c r="V5" s="9" t="n"/>
       <c r="W5" s="12" t="n"/>
@@ -2627,6 +2737,9 @@
       <c r="BT5" s="9" t="n"/>
       <c r="BU5" s="9" t="n"/>
       <c r="BV5" s="12" t="n"/>
+      <c r="BW5" s="9" t="n"/>
+      <c r="BX5" s="9" t="n"/>
+      <c r="BY5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2661,7 +2774,7 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>335</v>
@@ -2671,183 +2784,193 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
-      <c r="AG6" s="9" t="n">
+      <c r="AD6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
       <c r="AM6" s="9" t="n"/>
       <c r="AN6" s="9" t="n"/>
       <c r="AO6" s="12" t="n"/>
-      <c r="AP6" s="9" t="n">
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AQ6" s="9" t="n">
+      <c r="AT6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
-      <c r="AV6" s="9" t="n">
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="AZ6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
       <c r="BB6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BC6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
       <c r="BK6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BL6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
         <v/>
       </c>
       <c r="BN6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BO6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
         <v/>
       </c>
       <c r="BQ6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BR6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
         <v/>
       </c>
-      <c r="BT6" s="9" t="n"/>
+      <c r="BT6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="BU6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BW6" s="9" t="n"/>
+      <c r="BX6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY6" s="12">
+        <f>BX6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -2874,10 +2997,10 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -2894,7 +3017,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>119</v>
@@ -2907,109 +3030,109 @@
         <v>3</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="9" t="n">
+      <c r="AD7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AH7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
       <c r="AM7" s="9" t="n"/>
       <c r="AN7" s="9" t="n"/>
       <c r="AO7" s="12" t="n"/>
-      <c r="AP7" s="9" t="n">
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AQ7" s="9" t="n">
+      <c r="AT7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="9" t="n">
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AW7" s="9" t="n">
+      <c r="AZ7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
         <v/>
       </c>
       <c r="BB7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BC7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
@@ -3019,58 +3142,68 @@
         <v>6</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
       <c r="BK7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
         <v/>
       </c>
       <c r="BN7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BO7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
         <v/>
       </c>
       <c r="BQ7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BR7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
         <v/>
       </c>
-      <c r="BT7" s="9" t="n"/>
+      <c r="BT7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="BU7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BW7" s="9" t="n"/>
+      <c r="BX7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY7" s="12">
+        <f>BX7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -3107,7 +3240,7 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>998</v>
@@ -3117,112 +3250,112 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
-      <c r="AG8" s="9" t="n">
+      <c r="AD8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AH8" s="9" t="n">
+      <c r="AK8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
       <c r="AM8" s="9" t="n"/>
       <c r="AN8" s="9" t="n"/>
       <c r="AO8" s="12" t="n"/>
-      <c r="AP8" s="9" t="n">
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AQ8" s="9" t="n">
+      <c r="AT8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
-      <c r="AV8" s="9" t="n">
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AW8" s="9" t="n">
+      <c r="AZ8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
@@ -3232,68 +3365,78 @@
         <v>7</v>
       </c>
       <c r="BC8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
       <c r="BE8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
       <c r="BK8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BL8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
         <v/>
       </c>
       <c r="BN8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BO8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
         <v/>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BR8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
         <v/>
       </c>
-      <c r="BT8" s="9" t="n"/>
+      <c r="BT8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="BU8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BW8" s="9" t="n"/>
+      <c r="BX8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="BY8" s="12">
+        <f>BX8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3340,7 +3483,7 @@
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>1125</v>
@@ -3350,27 +3493,27 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="Q9" s="12">
         <f>P9/$E$9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="T9" s="12">
         <f>S9/$E$9</f>
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>1119</v>
@@ -3380,17 +3523,17 @@
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="Z9" s="12">
         <f>Y9/$E$9</f>
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="9" t="n">
         <v>1117</v>
@@ -3399,124 +3542,134 @@
         <f>AB9/$E$9</f>
         <v/>
       </c>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="9" t="n">
+      <c r="AD9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AH9" s="9" t="n">
+      <c r="AK9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
       <c r="AM9" s="9" t="n"/>
       <c r="AN9" s="9" t="n"/>
       <c r="AO9" s="12" t="n"/>
-      <c r="AP9" s="9" t="n">
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ9" s="9" t="n">
+      <c r="AT9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
-      <c r="AV9" s="9" t="n">
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AW9" s="9" t="n">
+      <c r="AZ9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BA9" s="12">
         <f>AZ9/$E$9</f>
         <v/>
       </c>
       <c r="BB9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
       <c r="BK9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
         <v/>
       </c>
       <c r="BN9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BO9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
         <v/>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="BR9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
         <v/>
       </c>
-      <c r="BT9" s="9" t="n"/>
+      <c r="BT9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="BU9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BW9" s="9" t="n"/>
+      <c r="BX9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="BY9" s="12">
+        <f>BX9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3553,7 +3706,7 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>502</v>
@@ -3563,37 +3716,37 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>491</v>
@@ -3603,79 +3756,79 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="9" t="n">
+      <c r="AD10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AF10" s="12">
+        <f>AE10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AH10" s="9" t="n">
+      <c r="AK10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AI10" s="12">
-        <f>AH10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
       <c r="AM10" s="9" t="n"/>
       <c r="AN10" s="9" t="n"/>
       <c r="AO10" s="12" t="n"/>
-      <c r="AP10" s="9" t="n">
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" s="9" t="n">
+      <c r="AT10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="9" t="n">
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AW10" s="9" t="n">
+      <c r="AZ10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="AX10" s="12">
-        <f>AW10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BA10" s="12">
         <f>AZ10/$E$10</f>
         <v/>
       </c>
       <c r="BB10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BC10" s="9" t="n">
         <v>462</v>
@@ -3688,58 +3841,68 @@
         <v>2</v>
       </c>
       <c r="BF10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
       <c r="BK10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BL10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
         <v/>
       </c>
       <c r="BN10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BO10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BP10" s="12">
         <f>BO10/$E$10</f>
         <v/>
       </c>
       <c r="BQ10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="BR10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="BS10" s="12">
         <f>BR10/$E$10</f>
         <v/>
       </c>
-      <c r="BT10" s="9" t="n"/>
+      <c r="BT10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="BU10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="BV10" s="12">
         <f>BU10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BW10" s="9" t="n"/>
+      <c r="BX10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="BY10" s="12">
+        <f>BX10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -3796,7 +3959,7 @@
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>467</v>
@@ -3809,17 +3972,17 @@
         <v>1</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
@@ -3845,60 +4008,60 @@
         <f>AB11/$E$11</f>
         <v/>
       </c>
-      <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="9" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="9" t="n">
+      <c r="AD11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AF11" s="12">
+        <f>AE11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" s="9" t="n">
+      <c r="AK11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AI11" s="12">
-        <f>AH11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
       <c r="AM11" s="9" t="n"/>
       <c r="AN11" s="9" t="n"/>
       <c r="AO11" s="12" t="n"/>
-      <c r="AP11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="9" t="n">
+      <c r="AP11" s="9" t="n"/>
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AR11" s="12">
-        <f>AQ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
-      <c r="AV11" s="9" t="n">
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AW11" s="9" t="n">
+      <c r="AZ11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="AX11" s="12">
-        <f>AW11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BA11" s="12">
         <f>AZ11/$E$11</f>
         <v/>
       </c>
       <c r="BB11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC11" s="9" t="n">
         <v>463</v>
@@ -3908,40 +4071,40 @@
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BF11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
         <v/>
       </c>
       <c r="BH11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
         <v/>
       </c>
       <c r="BK11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
         <v/>
       </c>
       <c r="BN11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BP11" s="12">
         <f>BO11/$E$11</f>
@@ -3951,18 +4114,28 @@
         <v>2</v>
       </c>
       <c r="BR11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BS11" s="12">
         <f>BR11/$E$11</f>
         <v/>
       </c>
-      <c r="BT11" s="9" t="n"/>
+      <c r="BT11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="BU11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BV11" s="12">
         <f>BU11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BW11" s="9" t="n"/>
+      <c r="BX11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="BY11" s="12">
+        <f>BX11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -4019,7 +4192,7 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>236</v>
@@ -4029,17 +4202,17 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>235</v>
@@ -4049,10 +4222,10 @@
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
@@ -4068,48 +4241,48 @@
         <f>AB12/$E$12</f>
         <v/>
       </c>
-      <c r="AD12" s="9" t="n"/>
-      <c r="AE12" s="9" t="n"/>
-      <c r="AF12" s="12" t="n"/>
-      <c r="AG12" s="9" t="n">
+      <c r="AD12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AF12" s="12">
+        <f>AE12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="9" t="n"/>
+      <c r="AH12" s="9" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AH12" s="9" t="n">
+      <c r="AK12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AI12" s="12">
-        <f>AH12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
       <c r="AM12" s="9" t="n"/>
       <c r="AN12" s="9" t="n"/>
       <c r="AO12" s="12" t="n"/>
-      <c r="AP12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="9" t="n">
+      <c r="AP12" s="9" t="n"/>
+      <c r="AQ12" s="9" t="n"/>
+      <c r="AR12" s="12" t="n"/>
+      <c r="AS12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AR12" s="12">
-        <f>AQ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
-      <c r="AV12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="AX12" s="12">
-        <f>AW12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="12" t="n"/>
       <c r="AY12" s="9" t="n">
         <v>0</v>
       </c>
@@ -4151,7 +4324,7 @@
         <v/>
       </c>
       <c r="BK12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL12" s="9" t="n">
         <v>236</v>
@@ -4161,31 +4334,41 @@
         <v/>
       </c>
       <c r="BN12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BO12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BP12" s="12">
         <f>BO12/$E$12</f>
         <v/>
       </c>
       <c r="BQ12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="BR12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BS12" s="12">
         <f>BR12/$E$12</f>
         <v/>
       </c>
-      <c r="BT12" s="9" t="n"/>
+      <c r="BT12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="BU12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="BV12" s="12">
         <f>BU12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BW12" s="9" t="n"/>
+      <c r="BX12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BY12" s="12">
+        <f>BX12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -4222,7 +4405,7 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>621</v>
@@ -4232,142 +4415,142 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
-      <c r="AD13" s="9" t="n"/>
-      <c r="AE13" s="9" t="n"/>
-      <c r="AF13" s="12" t="n"/>
-      <c r="AG13" s="9" t="n">
+      <c r="AD13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AF13" s="12">
+        <f>AE13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AH13" s="9" t="n">
+      <c r="AK13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AI13" s="12">
-        <f>AH13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
       <c r="AM13" s="9" t="n"/>
       <c r="AN13" s="9" t="n"/>
       <c r="AO13" s="12" t="n"/>
-      <c r="AP13" s="9" t="n">
+      <c r="AP13" s="9" t="n"/>
+      <c r="AQ13" s="9" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AQ13" s="9" t="n">
+      <c r="AT13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AR13" s="12">
-        <f>AQ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="9" t="n">
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AV13" s="9" t="n"/>
+      <c r="AW13" s="9" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AW13" s="9" t="n">
+      <c r="AZ13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="AX13" s="12">
-        <f>AW13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
         <v/>
       </c>
       <c r="BB13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
@@ -4377,38 +4560,48 @@
         <v>4</v>
       </c>
       <c r="BL13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
         <v/>
       </c>
       <c r="BN13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BO13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
         <v/>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="BR13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
         <v/>
       </c>
-      <c r="BT13" s="9" t="n"/>
+      <c r="BT13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="BU13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BW13" s="9" t="n"/>
+      <c r="BX13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="BY13" s="12">
+        <f>BX13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -4445,7 +4638,7 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>1145</v>
@@ -4455,17 +4648,17 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>1142</v>
@@ -4475,122 +4668,122 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AC14" s="12">
         <f>AB14/$E$14</f>
         <v/>
       </c>
-      <c r="AD14" s="9" t="n"/>
-      <c r="AE14" s="9" t="n"/>
-      <c r="AF14" s="12" t="n"/>
-      <c r="AG14" s="9" t="n">
+      <c r="AD14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AF14" s="12">
+        <f>AE14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AH14" s="9" t="n">
+      <c r="AK14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AI14" s="12">
-        <f>AH14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
       <c r="AM14" s="9" t="n"/>
       <c r="AN14" s="9" t="n"/>
       <c r="AO14" s="12" t="n"/>
-      <c r="AP14" s="9" t="n">
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AQ14" s="9" t="n">
+      <c r="AT14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AR14" s="12">
-        <f>AQ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
-      <c r="AV14" s="9" t="n">
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AW14" s="9" t="n">
+      <c r="AZ14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="AX14" s="12">
-        <f>AW14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
         <v/>
       </c>
       <c r="BB14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BC14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BD14" s="12">
         <f>BC14/$E$14</f>
         <v/>
       </c>
       <c r="BE14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BF14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BG14" s="12">
         <f>BF14/$E$14</f>
         <v/>
       </c>
       <c r="BH14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BI14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BJ14" s="12">
         <f>BI14/$E$14</f>
@@ -4626,12 +4819,22 @@
         <f>BR14/$E$14</f>
         <v/>
       </c>
-      <c r="BT14" s="9" t="n"/>
+      <c r="BT14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BU14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BV14" s="12">
         <f>BU14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BW14" s="9" t="n"/>
+      <c r="BX14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" s="12">
+        <f>BX14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -4668,7 +4871,7 @@
         <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>126</v>
@@ -4681,17 +4884,17 @@
         <v>1</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="12">
         <f>M15/$E$15</f>
         <v/>
       </c>
       <c r="O15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
@@ -4708,7 +4911,7 @@
         <v/>
       </c>
       <c r="U15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>124</v>
@@ -4718,17 +4921,17 @@
         <v/>
       </c>
       <c r="X15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Z15" s="12">
         <f>Y15/$E$15</f>
         <v/>
       </c>
       <c r="AA15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="9" t="n">
         <v>121</v>
@@ -4737,53 +4940,53 @@
         <f>AB15/$E$15</f>
         <v/>
       </c>
-      <c r="AD15" s="9" t="n"/>
-      <c r="AE15" s="9" t="n"/>
-      <c r="AF15" s="12" t="n"/>
-      <c r="AG15" s="9" t="n">
+      <c r="AD15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF15" s="12">
+        <f>AE15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AG15" s="9" t="n"/>
+      <c r="AH15" s="9" t="n"/>
+      <c r="AI15" s="12" t="n"/>
+      <c r="AJ15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AH15" s="9" t="n">
+      <c r="AK15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AI15" s="12">
-        <f>AH15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="9" t="n"/>
-      <c r="AK15" s="9" t="n"/>
-      <c r="AL15" s="12" t="n"/>
+      <c r="AL15" s="12">
+        <f>AK15/$E$15</f>
+        <v/>
+      </c>
       <c r="AM15" s="9" t="n"/>
       <c r="AN15" s="9" t="n"/>
       <c r="AO15" s="12" t="n"/>
-      <c r="AP15" s="9" t="n">
+      <c r="AP15" s="9" t="n"/>
+      <c r="AQ15" s="9" t="n"/>
+      <c r="AR15" s="12" t="n"/>
+      <c r="AS15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AQ15" s="9" t="n">
+      <c r="AT15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AR15" s="12">
-        <f>AQ15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AS15" s="9" t="n"/>
-      <c r="AT15" s="9" t="n"/>
-      <c r="AU15" s="12" t="n"/>
-      <c r="AV15" s="9" t="n">
+      <c r="AU15" s="12">
+        <f>AT15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AV15" s="9" t="n"/>
+      <c r="AW15" s="9" t="n"/>
+      <c r="AX15" s="12" t="n"/>
+      <c r="AY15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AW15" s="9" t="n">
+      <c r="AZ15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="AX15" s="12">
-        <f>AW15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AY15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BA15" s="12">
         <f>AZ15/$E$15</f>
@@ -4793,24 +4996,24 @@
         <v>3</v>
       </c>
       <c r="BC15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BD15" s="12">
         <f>BC15/$E$15</f>
         <v/>
       </c>
       <c r="BE15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BF15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BG15" s="12">
         <f>BF15/$E$15</f>
         <v/>
       </c>
       <c r="BH15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BI15" s="9" t="n">
         <v>76</v>
@@ -4820,10 +5023,10 @@
         <v/>
       </c>
       <c r="BK15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BL15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BM15" s="12">
         <f>BL15/$E$15</f>
@@ -4849,12 +5052,22 @@
         <f>BR15/$E$15</f>
         <v/>
       </c>
-      <c r="BT15" s="9" t="n"/>
+      <c r="BT15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BU15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BV15" s="12">
         <f>BU15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BW15" s="9" t="n"/>
+      <c r="BX15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" s="12">
+        <f>BX15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -4960,51 +5173,58 @@
         <f>AB16/$E$16</f>
         <v/>
       </c>
-      <c r="AD16" s="9" t="n"/>
-      <c r="AE16" s="9" t="n"/>
-      <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="9" t="n">
+      <c r="AD16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AI16" s="12">
-        <f>AH16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
+      <c r="AF16" s="12">
+        <f>AE16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
       <c r="AM16" s="9" t="n"/>
       <c r="AN16" s="9" t="n"/>
       <c r="AO16" s="12" t="n"/>
-      <c r="AP16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="9" t="n">
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="9" t="n">
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AW16" s="9" t="n">
+      <c r="AZ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AX16" s="12">
-        <f>AW16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
       <c r="BB16" s="9" t="n"/>
       <c r="BC16" s="9" t="n"/>
       <c r="BD16" s="12" t="n"/>
@@ -5024,11 +5244,14 @@
       <c r="BR16" s="9" t="n"/>
       <c r="BS16" s="12" t="n"/>
       <c r="BT16" s="9" t="n"/>
-      <c r="BU16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" s="12">
-        <f>BU16/$E$16</f>
+      <c r="BU16" s="9" t="n"/>
+      <c r="BV16" s="12" t="n"/>
+      <c r="BW16" s="9" t="n"/>
+      <c r="BX16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" s="12">
+        <f>BX16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -5123,6 +5346,9 @@
       <c r="BT17" s="9" t="n"/>
       <c r="BU17" s="9" t="n"/>
       <c r="BV17" s="12" t="n"/>
+      <c r="BW17" s="9" t="n"/>
+      <c r="BX17" s="9" t="n"/>
+      <c r="BY17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -5146,7 +5372,9 @@
       <c r="E18" s="9" t="n">
         <v>830</v>
       </c>
-      <c r="F18" s="10" t="n"/>
+      <c r="F18" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G18" s="10" t="n">
         <v>139</v>
       </c>
@@ -5155,8 +5383,13 @@
         <v/>
       </c>
       <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="12" t="n"/>
+      <c r="J18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="K18" s="12">
+        <f>J18/$E$18</f>
+        <v/>
+      </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="9" t="n"/>
       <c r="N18" s="12" t="n"/>
@@ -5220,9 +5453,12 @@
       <c r="BT18" s="9" t="n"/>
       <c r="BU18" s="9" t="n"/>
       <c r="BV18" s="12" t="n"/>
+      <c r="BW18" s="9" t="n"/>
+      <c r="BX18" s="9" t="n"/>
+      <c r="BY18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
@@ -5232,6 +5468,7 @@
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
+    <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AM3:AO3"/>
@@ -5257,7 +5494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV18"/>
+  <dimension ref="A1:BY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5334,6 +5571,9 @@
     <col width="9" customWidth="1" min="72" max="72"/>
     <col width="9" customWidth="1" min="73" max="73"/>
     <col width="9" customWidth="1" min="74" max="74"/>
+    <col width="9" customWidth="1" min="75" max="75"/>
+    <col width="9" customWidth="1" min="76" max="76"/>
+    <col width="9" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5352,72 +5592,75 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -5790,6 +6033,21 @@
         </is>
       </c>
       <c r="BV4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BW4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BX4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BY4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -5828,7 +6086,7 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>298</v>
@@ -5841,115 +6099,122 @@
         <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="12" t="n"/>
-      <c r="U5" s="9" t="n">
+      <c r="R5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="T5" s="12">
+        <f>S5/$E$5</f>
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="12" t="n"/>
+      <c r="X5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="Y5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="W5" s="12">
-        <f>V5/$E$5</f>
-        <v/>
-      </c>
-      <c r="X5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
-      <c r="AJ5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="9" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AN5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AL5" s="12">
-        <f>AK5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AN5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AO5" s="12">
         <f>AN5/$E$5</f>
         <v/>
       </c>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="12" t="n"/>
-      <c r="AS5" s="9" t="n">
+      <c r="AP5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AQ5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
+      <c r="AV5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AT5" s="9" t="n">
+      <c r="AW5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="AU5" s="12">
-        <f>AT5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n"/>
-      <c r="AX5" s="12" t="n"/>
+      <c r="AX5" s="12">
+        <f>AW5/$E$5</f>
+        <v/>
+      </c>
       <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n">
+      <c r="AZ5" s="9" t="n"/>
+      <c r="BA5" s="12" t="n"/>
+      <c r="BB5" s="9" t="n"/>
+      <c r="BC5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="BA5" s="12">
-        <f>AZ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BB5" s="9" t="n"/>
-      <c r="BC5" s="9" t="n"/>
-      <c r="BD5" s="12" t="n"/>
+      <c r="BD5" s="12">
+        <f>BC5/$E$5</f>
+        <v/>
+      </c>
       <c r="BE5" s="9" t="n"/>
       <c r="BF5" s="9" t="n"/>
       <c r="BG5" s="12" t="n"/>
@@ -5968,6 +6233,9 @@
       <c r="BT5" s="9" t="n"/>
       <c r="BU5" s="9" t="n"/>
       <c r="BV5" s="12" t="n"/>
+      <c r="BW5" s="9" t="n"/>
+      <c r="BX5" s="9" t="n"/>
+      <c r="BY5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -6002,7 +6270,7 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>950</v>
@@ -6012,118 +6280,125 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="9" t="n">
+      <c r="R6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="T6" s="12">
+        <f>S6/$E$6</f>
+        <v/>
+      </c>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="Y6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="W6" s="12">
-        <f>V6/$E$6</f>
-        <v/>
-      </c>
-      <c r="X6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AN6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
-      <c r="AS6" s="9" t="n">
+      <c r="AP6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AT6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
       <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n">
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="12" t="n"/>
+      <c r="BD6" s="12">
+        <f>BC6/$E$6</f>
+        <v/>
+      </c>
       <c r="BE6" s="9" t="n"/>
       <c r="BF6" s="9" t="n"/>
       <c r="BG6" s="12" t="n"/>
@@ -6142,6 +6417,9 @@
       <c r="BT6" s="9" t="n"/>
       <c r="BU6" s="9" t="n"/>
       <c r="BV6" s="12" t="n"/>
+      <c r="BW6" s="9" t="n"/>
+      <c r="BX6" s="9" t="n"/>
+      <c r="BY6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -6205,99 +6483,106 @@
         <f>P7/$E$7</f>
         <v/>
       </c>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="12" t="n"/>
-      <c r="U7" s="9" t="n">
+      <c r="R7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="T7" s="12">
+        <f>S7/$E$7</f>
+        <v/>
+      </c>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="Y7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="W7" s="12">
-        <f>V7/$E$7</f>
-        <v/>
-      </c>
-      <c r="X7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AH7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
-      <c r="AS7" s="9" t="n">
+      <c r="AP7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AT7" s="9" t="n">
+      <c r="AW7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
       <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n">
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="12" t="n"/>
+      <c r="BD7" s="12">
+        <f>BC7/$E$7</f>
+        <v/>
+      </c>
       <c r="BE7" s="9" t="n"/>
       <c r="BF7" s="9" t="n"/>
       <c r="BG7" s="12" t="n"/>
@@ -6316,6 +6601,9 @@
       <c r="BT7" s="9" t="n"/>
       <c r="BU7" s="9" t="n"/>
       <c r="BV7" s="12" t="n"/>
+      <c r="BW7" s="9" t="n"/>
+      <c r="BX7" s="9" t="n"/>
+      <c r="BY7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -6350,7 +6638,7 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1054</v>
@@ -6360,17 +6648,17 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>1052</v>
@@ -6379,99 +6667,106 @@
         <f>P8/$E$8</f>
         <v/>
       </c>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="12" t="n"/>
-      <c r="U8" s="9" t="n">
+      <c r="R8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="S8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="T8" s="12">
+        <f>S8/$E$8</f>
+        <v/>
+      </c>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="12" t="n"/>
+      <c r="X8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="W8" s="12">
-        <f>V8/$E$8</f>
-        <v/>
-      </c>
-      <c r="X8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AN8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
-      <c r="AS8" s="9" t="n">
+      <c r="AP8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AT8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
       <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n">
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="12" t="n"/>
+      <c r="BD8" s="12">
+        <f>BC8/$E$8</f>
+        <v/>
+      </c>
       <c r="BE8" s="9" t="n"/>
       <c r="BF8" s="9" t="n"/>
       <c r="BG8" s="12" t="n"/>
@@ -6490,6 +6785,9 @@
       <c r="BT8" s="9" t="n"/>
       <c r="BU8" s="9" t="n"/>
       <c r="BV8" s="12" t="n"/>
+      <c r="BW8" s="9" t="n"/>
+      <c r="BX8" s="9" t="n"/>
+      <c r="BY8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -6553,19 +6851,19 @@
         <f>P9/$E$9</f>
         <v/>
       </c>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="12" t="n"/>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="9" t="n">
+      <c r="R9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="W9" s="12">
-        <f>V9/$E$9</f>
-        <v/>
-      </c>
+      <c r="T9" s="12">
+        <f>S9/$E$9</f>
+        <v/>
+      </c>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="12" t="n"/>
       <c r="X9" s="9" t="n">
         <v>0</v>
       </c>
@@ -6577,7 +6875,7 @@
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="9" t="n">
         <v>845</v>
@@ -6587,28 +6885,28 @@
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AF9" s="12">
         <f>AE9/$E$9</f>
         <v/>
       </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AG9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
       <c r="AM9" s="9" t="n">
         <v>0</v>
       </c>
@@ -6619,33 +6917,40 @@
         <f>AN9/$E$9</f>
         <v/>
       </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
-      <c r="AS9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="9" t="n">
+      <c r="AP9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
       <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n">
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="9" t="n"/>
+      <c r="BC9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="12" t="n"/>
+      <c r="BD9" s="12">
+        <f>BC9/$E$9</f>
+        <v/>
+      </c>
       <c r="BE9" s="9" t="n"/>
       <c r="BF9" s="9" t="n"/>
       <c r="BG9" s="12" t="n"/>
@@ -6664,6 +6969,9 @@
       <c r="BT9" s="9" t="n"/>
       <c r="BU9" s="9" t="n"/>
       <c r="BV9" s="12" t="n"/>
+      <c r="BW9" s="9" t="n"/>
+      <c r="BX9" s="9" t="n"/>
+      <c r="BY9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -6698,7 +7006,7 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>1418</v>
@@ -6708,118 +7016,125 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="9" t="n"/>
-      <c r="T10" s="12" t="n"/>
-      <c r="U10" s="9" t="n">
+      <c r="R10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="T10" s="12">
+        <f>S10/$E$10</f>
+        <v/>
+      </c>
+      <c r="U10" s="9" t="n"/>
+      <c r="V10" s="9" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="Y10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="W10" s="12">
-        <f>V10/$E$10</f>
-        <v/>
-      </c>
-      <c r="X10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AG10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AN10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
-      <c r="AS10" s="9" t="n">
+      <c r="AP10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AT10" s="9" t="n">
+      <c r="AQ10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
       <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n">
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="BA10" s="12">
-        <f>AZ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BB10" s="9" t="n"/>
-      <c r="BC10" s="9" t="n"/>
-      <c r="BD10" s="12" t="n"/>
+      <c r="BD10" s="12">
+        <f>BC10/$E$10</f>
+        <v/>
+      </c>
       <c r="BE10" s="9" t="n"/>
       <c r="BF10" s="9" t="n"/>
       <c r="BG10" s="12" t="n"/>
@@ -6838,6 +7153,9 @@
       <c r="BT10" s="9" t="n"/>
       <c r="BU10" s="9" t="n"/>
       <c r="BV10" s="12" t="n"/>
+      <c r="BW10" s="9" t="n"/>
+      <c r="BX10" s="9" t="n"/>
+      <c r="BY10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -6872,7 +7190,7 @@
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>992</v>
@@ -6882,10 +7200,10 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
@@ -6901,99 +7219,106 @@
         <f>P11/$E$11</f>
         <v/>
       </c>
-      <c r="R11" s="9" t="n"/>
-      <c r="S11" s="9" t="n"/>
-      <c r="T11" s="12" t="n"/>
-      <c r="U11" s="9" t="n">
+      <c r="R11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="T11" s="12">
+        <f>S11/$E$11</f>
+        <v/>
+      </c>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="12" t="n"/>
+      <c r="X11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="Y11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="W11" s="12">
-        <f>V11/$E$11</f>
-        <v/>
-      </c>
-      <c r="X11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="Z11" s="12">
         <f>Y11/$E$11</f>
         <v/>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="AC11" s="12">
         <f>AB11/$E$11</f>
         <v/>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
         <v/>
       </c>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AN11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AO11" s="12">
         <f>AN11/$E$11</f>
         <v/>
       </c>
-      <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n"/>
-      <c r="AR11" s="12" t="n"/>
-      <c r="AS11" s="9" t="n">
+      <c r="AP11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AT11" s="9" t="n">
+      <c r="AW11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="AU11" s="12">
-        <f>AT11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n"/>
-      <c r="AX11" s="12" t="n"/>
+      <c r="AX11" s="12">
+        <f>AW11/$E$11</f>
+        <v/>
+      </c>
       <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n">
+      <c r="AZ11" s="9" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="9" t="n"/>
+      <c r="BC11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="BA11" s="12">
-        <f>AZ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BB11" s="9" t="n"/>
-      <c r="BC11" s="9" t="n"/>
-      <c r="BD11" s="12" t="n"/>
+      <c r="BD11" s="12">
+        <f>BC11/$E$11</f>
+        <v/>
+      </c>
       <c r="BE11" s="9" t="n"/>
       <c r="BF11" s="9" t="n"/>
       <c r="BG11" s="12" t="n"/>
@@ -7012,6 +7337,9 @@
       <c r="BT11" s="9" t="n"/>
       <c r="BU11" s="9" t="n"/>
       <c r="BV11" s="12" t="n"/>
+      <c r="BW11" s="9" t="n"/>
+      <c r="BX11" s="9" t="n"/>
+      <c r="BY11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -7046,7 +7374,7 @@
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>737</v>
@@ -7056,118 +7384,125 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="N12" s="12">
         <f>M12/$E$12</f>
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
-      <c r="R12" s="9" t="n"/>
-      <c r="S12" s="9" t="n"/>
-      <c r="T12" s="12" t="n"/>
-      <c r="U12" s="9" t="n">
+      <c r="R12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="T12" s="12">
+        <f>S12/$E$12</f>
+        <v/>
+      </c>
+      <c r="U12" s="9" t="n"/>
+      <c r="V12" s="9" t="n"/>
+      <c r="W12" s="12" t="n"/>
+      <c r="X12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="Y12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="W12" s="12">
-        <f>V12/$E$12</f>
-        <v/>
-      </c>
-      <c r="X12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="AC12" s="12">
         <f>AB12/$E$12</f>
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AN12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AM12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AN12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AO12" s="12">
         <f>AN12/$E$12</f>
         <v/>
       </c>
-      <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n"/>
-      <c r="AR12" s="12" t="n"/>
-      <c r="AS12" s="9" t="n">
+      <c r="AP12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
+      <c r="AV12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AT12" s="9" t="n">
+      <c r="AW12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="AU12" s="12">
-        <f>AT12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="12" t="n"/>
+      <c r="AX12" s="12">
+        <f>AW12/$E$12</f>
+        <v/>
+      </c>
       <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n">
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="12" t="n"/>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="BA12" s="12">
-        <f>AZ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BB12" s="9" t="n"/>
-      <c r="BC12" s="9" t="n"/>
-      <c r="BD12" s="12" t="n"/>
+      <c r="BD12" s="12">
+        <f>BC12/$E$12</f>
+        <v/>
+      </c>
       <c r="BE12" s="9" t="n"/>
       <c r="BF12" s="9" t="n"/>
       <c r="BG12" s="12" t="n"/>
@@ -7186,6 +7521,9 @@
       <c r="BT12" s="9" t="n"/>
       <c r="BU12" s="9" t="n"/>
       <c r="BV12" s="12" t="n"/>
+      <c r="BW12" s="9" t="n"/>
+      <c r="BX12" s="9" t="n"/>
+      <c r="BY12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -7240,7 +7578,7 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>1391</v>
@@ -7249,99 +7587,106 @@
         <f>P13/$E$13</f>
         <v/>
       </c>
-      <c r="R13" s="9" t="n"/>
-      <c r="S13" s="9" t="n"/>
-      <c r="T13" s="12" t="n"/>
-      <c r="U13" s="9" t="n">
+      <c r="R13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="S13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="T13" s="12">
+        <f>S13/$E$13</f>
+        <v/>
+      </c>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n"/>
+      <c r="W13" s="12" t="n"/>
+      <c r="X13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="W13" s="12">
-        <f>V13/$E$13</f>
-        <v/>
-      </c>
-      <c r="X13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
+      <c r="AM13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AN13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AM13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
-      <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n"/>
-      <c r="AR13" s="12" t="n"/>
-      <c r="AS13" s="9" t="n">
+      <c r="AP13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AT13" s="9" t="n">
+      <c r="AW13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="AU13" s="12">
-        <f>AT13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n"/>
-      <c r="AX13" s="12" t="n"/>
+      <c r="AX13" s="12">
+        <f>AW13/$E$13</f>
+        <v/>
+      </c>
       <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n">
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="9" t="n"/>
+      <c r="BC13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="BA13" s="12">
-        <f>AZ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BB13" s="9" t="n"/>
-      <c r="BC13" s="9" t="n"/>
-      <c r="BD13" s="12" t="n"/>
+      <c r="BD13" s="12">
+        <f>BC13/$E$13</f>
+        <v/>
+      </c>
       <c r="BE13" s="9" t="n"/>
       <c r="BF13" s="9" t="n"/>
       <c r="BG13" s="12" t="n"/>
@@ -7360,6 +7705,9 @@
       <c r="BT13" s="9" t="n"/>
       <c r="BU13" s="9" t="n"/>
       <c r="BV13" s="12" t="n"/>
+      <c r="BW13" s="9" t="n"/>
+      <c r="BX13" s="9" t="n"/>
+      <c r="BY13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -7414,7 +7762,7 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>902</v>
@@ -7423,21 +7771,21 @@
         <f>P14/$E$14</f>
         <v/>
       </c>
-      <c r="R14" s="9" t="n"/>
-      <c r="S14" s="9" t="n"/>
-      <c r="T14" s="12" t="n"/>
-      <c r="U14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="W14" s="12">
-        <f>V14/$E$14</f>
-        <v/>
-      </c>
+      <c r="R14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="T14" s="12">
+        <f>S14/$E$14</f>
+        <v/>
+      </c>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="9" t="n"/>
+      <c r="W14" s="12" t="n"/>
       <c r="X14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>898</v>
@@ -7447,75 +7795,82 @@
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="AC14" s="12">
         <f>AB14/$E$14</f>
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
+      <c r="AG14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
+      <c r="AM14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AN14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AM14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
-      <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n"/>
-      <c r="AR14" s="12" t="n"/>
-      <c r="AS14" s="9" t="n">
+      <c r="AP14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AT14" s="9" t="n">
+      <c r="AQ14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="AU14" s="12">
-        <f>AT14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n"/>
-      <c r="AX14" s="12" t="n"/>
+      <c r="AX14" s="12">
+        <f>AW14/$E$14</f>
+        <v/>
+      </c>
       <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n">
+      <c r="AZ14" s="9" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="9" t="n"/>
+      <c r="BC14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="BA14" s="12">
-        <f>AZ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BB14" s="9" t="n"/>
-      <c r="BC14" s="9" t="n"/>
-      <c r="BD14" s="12" t="n"/>
+      <c r="BD14" s="12">
+        <f>BC14/$E$14</f>
+        <v/>
+      </c>
       <c r="BE14" s="9" t="n"/>
       <c r="BF14" s="9" t="n"/>
       <c r="BG14" s="12" t="n"/>
@@ -7534,6 +7889,9 @@
       <c r="BT14" s="9" t="n"/>
       <c r="BU14" s="9" t="n"/>
       <c r="BV14" s="12" t="n"/>
+      <c r="BW14" s="9" t="n"/>
+      <c r="BX14" s="9" t="n"/>
+      <c r="BY14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -7626,6 +7984,9 @@
       <c r="BT15" s="9" t="n"/>
       <c r="BU15" s="9" t="n"/>
       <c r="BV15" s="12" t="n"/>
+      <c r="BW15" s="9" t="n"/>
+      <c r="BX15" s="9" t="n"/>
+      <c r="BY15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -7660,7 +8021,7 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>715</v>
@@ -7670,118 +8031,125 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N16" s="12">
         <f>M16/$E$16</f>
         <v/>
       </c>
       <c r="O16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/$E$16</f>
         <v/>
       </c>
-      <c r="R16" s="9" t="n"/>
-      <c r="S16" s="9" t="n"/>
-      <c r="T16" s="12" t="n"/>
-      <c r="U16" s="9" t="n">
+      <c r="R16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="T16" s="12">
+        <f>S16/$E$16</f>
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="12" t="n"/>
+      <c r="X16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="Y16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="W16" s="12">
-        <f>V16/$E$16</f>
-        <v/>
-      </c>
-      <c r="X16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="Z16" s="12">
         <f>Y16/$E$16</f>
         <v/>
       </c>
       <c r="AA16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AC16" s="12">
         <f>AB16/$E$16</f>
         <v/>
       </c>
       <c r="AD16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AN16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AM16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AO16" s="12">
         <f>AN16/$E$16</f>
         <v/>
       </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
-      <c r="AS16" s="9" t="n">
+      <c r="AP16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AT16" s="9" t="n">
+      <c r="AW16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="AU16" s="12">
-        <f>AT16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
       <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n">
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="BA16" s="12">
-        <f>AZ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BB16" s="9" t="n"/>
-      <c r="BC16" s="9" t="n"/>
-      <c r="BD16" s="12" t="n"/>
+      <c r="BD16" s="12">
+        <f>BC16/$E$16</f>
+        <v/>
+      </c>
       <c r="BE16" s="9" t="n"/>
       <c r="BF16" s="9" t="n"/>
       <c r="BG16" s="12" t="n"/>
@@ -7800,6 +8168,9 @@
       <c r="BT16" s="9" t="n"/>
       <c r="BU16" s="9" t="n"/>
       <c r="BV16" s="12" t="n"/>
+      <c r="BW16" s="9" t="n"/>
+      <c r="BX16" s="9" t="n"/>
+      <c r="BY16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -7824,10 +8195,10 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H17" s="11">
         <f>G17/$E$17</f>
@@ -7844,7 +8215,7 @@
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
         <v>385</v>
@@ -7854,108 +8225,115 @@
         <v/>
       </c>
       <c r="O17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/$E$17</f>
         <v/>
       </c>
-      <c r="R17" s="9" t="n"/>
-      <c r="S17" s="9" t="n"/>
-      <c r="T17" s="12" t="n"/>
-      <c r="U17" s="9" t="n">
+      <c r="R17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="S17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="T17" s="12">
+        <f>S17/$E$17</f>
+        <v/>
+      </c>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="12" t="n"/>
+      <c r="X17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="W17" s="12">
-        <f>V17/$E$17</f>
-        <v/>
-      </c>
-      <c r="X17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="Z17" s="12">
         <f>Y17/$E$17</f>
         <v/>
       </c>
       <c r="AA17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AB17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AC17" s="12">
         <f>AB17/$E$17</f>
         <v/>
       </c>
       <c r="AD17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AF17" s="12">
         <f>AE17/$E$17</f>
         <v/>
       </c>
-      <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="9" t="n"/>
-      <c r="AI17" s="12" t="n"/>
-      <c r="AJ17" s="9" t="n">
+      <c r="AG17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AI17" s="12">
+        <f>AH17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="9" t="n"/>
+      <c r="AK17" s="9" t="n"/>
+      <c r="AL17" s="12" t="n"/>
+      <c r="AM17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AK17" s="9" t="n">
+      <c r="AN17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AL17" s="12">
-        <f>AK17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AM17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AO17" s="12">
         <f>AN17/$E$17</f>
         <v/>
       </c>
-      <c r="AP17" s="9" t="n"/>
-      <c r="AQ17" s="9" t="n"/>
-      <c r="AR17" s="12" t="n"/>
-      <c r="AS17" s="9" t="n">
+      <c r="AP17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AR17" s="12">
+        <f>AQ17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AS17" s="9" t="n"/>
+      <c r="AT17" s="9" t="n"/>
+      <c r="AU17" s="12" t="n"/>
+      <c r="AV17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AT17" s="9" t="n">
+      <c r="AW17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="AU17" s="12">
-        <f>AT17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AV17" s="9" t="n"/>
-      <c r="AW17" s="9" t="n"/>
-      <c r="AX17" s="12" t="n"/>
+      <c r="AX17" s="12">
+        <f>AW17/$E$17</f>
+        <v/>
+      </c>
       <c r="AY17" s="9" t="n"/>
-      <c r="AZ17" s="9" t="n">
+      <c r="AZ17" s="9" t="n"/>
+      <c r="BA17" s="12" t="n"/>
+      <c r="BB17" s="9" t="n"/>
+      <c r="BC17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="BA17" s="12">
-        <f>AZ17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BB17" s="9" t="n"/>
-      <c r="BC17" s="9" t="n"/>
-      <c r="BD17" s="12" t="n"/>
+      <c r="BD17" s="12">
+        <f>BC17/$E$17</f>
+        <v/>
+      </c>
       <c r="BE17" s="9" t="n"/>
       <c r="BF17" s="9" t="n"/>
       <c r="BG17" s="12" t="n"/>
@@ -7974,6 +8352,9 @@
       <c r="BT17" s="9" t="n"/>
       <c r="BU17" s="9" t="n"/>
       <c r="BV17" s="12" t="n"/>
+      <c r="BW17" s="9" t="n"/>
+      <c r="BX17" s="9" t="n"/>
+      <c r="BY17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -8008,7 +8389,7 @@
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>292</v>
@@ -8018,118 +8399,125 @@
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
-      <c r="R18" s="9" t="n"/>
-      <c r="S18" s="9" t="n"/>
-      <c r="T18" s="12" t="n"/>
-      <c r="U18" s="9" t="n">
+      <c r="R18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="T18" s="12">
+        <f>S18/$E$18</f>
+        <v/>
+      </c>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="12" t="n"/>
+      <c r="X18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="Y18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="W18" s="12">
-        <f>V18/$E$18</f>
-        <v/>
-      </c>
-      <c r="X18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="Z18" s="12">
         <f>Y18/$E$18</f>
         <v/>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AC18" s="12">
         <f>AB18/$E$18</f>
         <v/>
       </c>
       <c r="AD18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
-      <c r="AG18" s="9" t="n"/>
-      <c r="AH18" s="9" t="n"/>
-      <c r="AI18" s="12" t="n"/>
-      <c r="AJ18" s="9" t="n">
+      <c r="AG18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AI18" s="12">
+        <f>AH18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="9" t="n"/>
+      <c r="AL18" s="12" t="n"/>
+      <c r="AM18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AK18" s="9" t="n">
+      <c r="AN18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AL18" s="12">
-        <f>AK18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AM18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AO18" s="12">
         <f>AN18/$E$18</f>
         <v/>
       </c>
-      <c r="AP18" s="9" t="n"/>
-      <c r="AQ18" s="9" t="n"/>
-      <c r="AR18" s="12" t="n"/>
-      <c r="AS18" s="9" t="n">
+      <c r="AP18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AR18" s="12">
+        <f>AQ18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="9" t="n"/>
+      <c r="AU18" s="12" t="n"/>
+      <c r="AV18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AT18" s="9" t="n">
+      <c r="AW18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="AU18" s="12">
-        <f>AT18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AV18" s="9" t="n"/>
-      <c r="AW18" s="9" t="n"/>
-      <c r="AX18" s="12" t="n"/>
+      <c r="AX18" s="12">
+        <f>AW18/$E$18</f>
+        <v/>
+      </c>
       <c r="AY18" s="9" t="n"/>
-      <c r="AZ18" s="9" t="n">
+      <c r="AZ18" s="9" t="n"/>
+      <c r="BA18" s="12" t="n"/>
+      <c r="BB18" s="9" t="n"/>
+      <c r="BC18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="BA18" s="12">
-        <f>AZ18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BB18" s="9" t="n"/>
-      <c r="BC18" s="9" t="n"/>
-      <c r="BD18" s="12" t="n"/>
+      <c r="BD18" s="12">
+        <f>BC18/$E$18</f>
+        <v/>
+      </c>
       <c r="BE18" s="9" t="n"/>
       <c r="BF18" s="9" t="n"/>
       <c r="BG18" s="12" t="n"/>
@@ -8148,9 +8536,12 @@
       <c r="BT18" s="9" t="n"/>
       <c r="BU18" s="9" t="n"/>
       <c r="BV18" s="12" t="n"/>
+      <c r="BW18" s="9" t="n"/>
+      <c r="BX18" s="9" t="n"/>
+      <c r="BY18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
@@ -8160,6 +8551,7 @@
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
+    <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AM3:AO3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -579,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 16/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 17/08/2026</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 16/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 17/08/2026</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 16/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 17/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -567,6 +567,9 @@
     <col width="9" customWidth="1" min="75" max="75"/>
     <col width="9" customWidth="1" min="76" max="76"/>
     <col width="9" customWidth="1" min="77" max="77"/>
+    <col width="9" customWidth="1" min="78" max="78"/>
+    <col width="9" customWidth="1" min="79" max="79"/>
+    <col width="9" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,75 +588,78 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1041,6 +1047,21 @@
         </is>
       </c>
       <c r="BY4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BZ4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CA4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CB4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1099,7 +1120,7 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>43</v>
@@ -1109,17 +1130,17 @@
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>42</v>
@@ -1132,49 +1153,56 @@
         <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="12" t="n"/>
-      <c r="AG5" s="9" t="n">
+      <c r="AD5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AG5" s="9" t="n"/>
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AH5" s="9" t="n">
+      <c r="AK5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AI5" s="12">
-        <f>AH5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
       <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n">
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
+      <c r="AP5" s="9" t="n"/>
+      <c r="AQ5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AO5" s="12">
-        <f>AN5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="12" t="n"/>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
       <c r="AS5" s="9" t="n"/>
       <c r="AT5" s="9" t="n"/>
       <c r="AU5" s="12" t="n"/>
@@ -1208,6 +1236,9 @@
       <c r="BW5" s="9" t="n"/>
       <c r="BX5" s="9" t="n"/>
       <c r="BY5" s="12" t="n"/>
+      <c r="BZ5" s="9" t="n"/>
+      <c r="CA5" s="9" t="n"/>
+      <c r="CB5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1232,10 +1263,10 @@
         <v>154</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
@@ -1311,33 +1342,40 @@
         <f>AB6/$E$6</f>
         <v/>
       </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
-      <c r="AG6" s="9" t="n">
+      <c r="AD6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
       <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n">
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
       <c r="AS6" s="9" t="n"/>
       <c r="AT6" s="9" t="n"/>
       <c r="AU6" s="12" t="n"/>
@@ -1371,6 +1409,9 @@
       <c r="BW6" s="9" t="n"/>
       <c r="BX6" s="9" t="n"/>
       <c r="BY6" s="12" t="n"/>
+      <c r="BZ6" s="9" t="n"/>
+      <c r="CA6" s="9" t="n"/>
+      <c r="CB6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1395,10 +1436,10 @@
         <v>490</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -1435,7 +1476,7 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>45</v>
@@ -1445,62 +1486,69 @@
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="9" t="n">
+      <c r="AD7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AH7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
       <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n">
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
       <c r="AS7" s="9" t="n"/>
       <c r="AT7" s="9" t="n"/>
       <c r="AU7" s="12" t="n"/>
@@ -1534,6 +1582,9 @@
       <c r="BW7" s="9" t="n"/>
       <c r="BX7" s="9" t="n"/>
       <c r="BY7" s="12" t="n"/>
+      <c r="BZ7" s="9" t="n"/>
+      <c r="CA7" s="9" t="n"/>
+      <c r="CB7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1637,33 +1688,40 @@
         <f>AB8/$E$8</f>
         <v/>
       </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
-      <c r="AG8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="9" t="n">
+      <c r="AD8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
       <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n">
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
       <c r="AS8" s="9" t="n"/>
       <c r="AT8" s="9" t="n"/>
       <c r="AU8" s="12" t="n"/>
@@ -1697,6 +1755,9 @@
       <c r="BW8" s="9" t="n"/>
       <c r="BX8" s="9" t="n"/>
       <c r="BY8" s="12" t="n"/>
+      <c r="BZ8" s="9" t="n"/>
+      <c r="CA8" s="9" t="n"/>
+      <c r="CB8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1791,7 +1852,7 @@
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="9" t="n">
         <v>1</v>
@@ -1800,33 +1861,40 @@
         <f>AB9/$E$9</f>
         <v/>
       </c>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
+      <c r="AD9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
       <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
       <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
+      <c r="AQ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
       <c r="AS9" s="9" t="n"/>
       <c r="AT9" s="9" t="n"/>
       <c r="AU9" s="12" t="n"/>
@@ -1860,6 +1928,9 @@
       <c r="BW9" s="9" t="n"/>
       <c r="BX9" s="9" t="n"/>
       <c r="BY9" s="12" t="n"/>
+      <c r="BZ9" s="9" t="n"/>
+      <c r="CA9" s="9" t="n"/>
+      <c r="CB9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1884,27 +1955,27 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>311</v>
@@ -1914,69 +1985,76 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n"/>
-      <c r="AF10" s="12" t="n"/>
+      <c r="AD10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AF10" s="12">
+        <f>AE10/$E$10</f>
+        <v/>
+      </c>
       <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n">
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AI10" s="12">
-        <f>AH10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
       <c r="AM10" s="9" t="n"/>
       <c r="AN10" s="9" t="n"/>
       <c r="AO10" s="12" t="n"/>
@@ -2016,10 +2094,14 @@
       <c r="BW10" s="9" t="n"/>
       <c r="BX10" s="9" t="n"/>
       <c r="BY10" s="12" t="n"/>
+      <c r="BZ10" s="9" t="n"/>
+      <c r="CA10" s="9" t="n"/>
+      <c r="CB10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -2054,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY18"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2134,6 +2216,9 @@
     <col width="9" customWidth="1" min="75" max="75"/>
     <col width="9" customWidth="1" min="76" max="76"/>
     <col width="9" customWidth="1" min="77" max="77"/>
+    <col width="9" customWidth="1" min="78" max="78"/>
+    <col width="9" customWidth="1" min="79" max="79"/>
+    <col width="9" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2152,75 +2237,78 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2608,6 +2696,21 @@
         </is>
       </c>
       <c r="BY4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BZ4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CA4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CB4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2636,10 +2739,10 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
@@ -2666,7 +2769,7 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>177</v>
@@ -2675,17 +2778,24 @@
         <f>P5/$E$5</f>
         <v/>
       </c>
-      <c r="R5" s="9" t="n"/>
+      <c r="R5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="S5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
-      <c r="W5" s="12" t="n"/>
+      <c r="V5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="W5" s="12">
+        <f>V5/$E$5</f>
+        <v/>
+      </c>
       <c r="X5" s="9" t="n"/>
       <c r="Y5" s="9" t="n"/>
       <c r="Z5" s="12" t="n"/>
@@ -2740,6 +2850,9 @@
       <c r="BW5" s="9" t="n"/>
       <c r="BX5" s="9" t="n"/>
       <c r="BY5" s="12" t="n"/>
+      <c r="BZ5" s="9" t="n"/>
+      <c r="CA5" s="9" t="n"/>
+      <c r="CB5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2764,10 +2877,10 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
@@ -2784,7 +2897,7 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>335</v>
@@ -2794,183 +2907,193 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AN6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
       <c r="AP6" s="9" t="n"/>
       <c r="AQ6" s="9" t="n"/>
       <c r="AR6" s="12" t="n"/>
-      <c r="AS6" s="9" t="n">
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AT6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
-      <c r="AY6" s="9" t="n">
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AZ6" s="9" t="n">
+      <c r="BC6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
       <c r="BE6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BF6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
       <c r="BK6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BL6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
         <v/>
       </c>
       <c r="BN6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BO6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
         <v/>
       </c>
       <c r="BQ6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BR6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
         <v/>
       </c>
       <c r="BT6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BU6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
         <v/>
       </c>
-      <c r="BW6" s="9" t="n"/>
+      <c r="BW6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="BX6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="BY6" s="12">
         <f>BX6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BZ6" s="9" t="n"/>
+      <c r="CA6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="CB6" s="12">
+        <f>CA6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -2997,7 +3120,7 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>120</v>
@@ -3007,10 +3130,10 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
@@ -3027,7 +3150,7 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>119</v>
@@ -3040,109 +3163,109 @@
         <v>3</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AN7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
       <c r="AP7" s="9" t="n"/>
       <c r="AQ7" s="9" t="n"/>
       <c r="AR7" s="12" t="n"/>
-      <c r="AS7" s="9" t="n">
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AT7" s="9" t="n">
+      <c r="AW7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
-      <c r="AY7" s="9" t="n">
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AZ7" s="9" t="n">
+      <c r="BC7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
       <c r="BE7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BF7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
@@ -3152,58 +3275,68 @@
         <v>6</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
       <c r="BK7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
         <v/>
       </c>
       <c r="BN7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
         <v/>
       </c>
       <c r="BQ7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
         <v/>
       </c>
       <c r="BT7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BU7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
         <v/>
       </c>
-      <c r="BW7" s="9" t="n"/>
+      <c r="BW7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="BX7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="BY7" s="12">
         <f>BX7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BZ7" s="9" t="n"/>
+      <c r="CA7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CB7" s="12">
+        <f>CA7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -3250,7 +3383,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>998</v>
@@ -3260,112 +3393,112 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AN8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
       <c r="AP8" s="9" t="n"/>
       <c r="AQ8" s="9" t="n"/>
       <c r="AR8" s="12" t="n"/>
-      <c r="AS8" s="9" t="n">
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AT8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
-      <c r="AY8" s="9" t="n">
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AZ8" s="9" t="n">
+      <c r="BC8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
@@ -3375,68 +3508,78 @@
         <v>7</v>
       </c>
       <c r="BF8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
       <c r="BH8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
       <c r="BK8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BL8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
         <v/>
       </c>
       <c r="BN8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BO8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
         <v/>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BR8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
         <v/>
       </c>
       <c r="BT8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
         <v/>
       </c>
-      <c r="BW8" s="9" t="n"/>
+      <c r="BW8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="BX8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="BY8" s="12">
         <f>BX8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BZ8" s="9" t="n"/>
+      <c r="CA8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="CB8" s="12">
+        <f>CA8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3493,7 +3636,7 @@
         <v/>
       </c>
       <c r="O9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>1125</v>
@@ -3503,27 +3646,27 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="T9" s="12">
         <f>S9/$E$9</f>
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>1119</v>
@@ -3533,17 +3676,17 @@
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AC9" s="12">
         <f>AB9/$E$9</f>
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="9" t="n">
         <v>1117</v>
@@ -3552,124 +3695,134 @@
         <f>AE9/$E$9</f>
         <v/>
       </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
+      <c r="AG9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AN9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
       <c r="AP9" s="9" t="n"/>
       <c r="AQ9" s="9" t="n"/>
       <c r="AR9" s="12" t="n"/>
-      <c r="AS9" s="9" t="n">
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AT9" s="9" t="n">
+      <c r="AW9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
-      <c r="AY9" s="9" t="n">
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AZ9" s="9" t="n">
+      <c r="BC9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BB9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BD9" s="12">
         <f>BC9/$E$9</f>
         <v/>
       </c>
       <c r="BE9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BF9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
       <c r="BK9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
         <v/>
       </c>
       <c r="BN9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
         <v/>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BR9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
         <v/>
       </c>
       <c r="BT9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
         <v/>
       </c>
-      <c r="BW9" s="9" t="n"/>
+      <c r="BW9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="BX9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="BY9" s="12">
         <f>BX9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BZ9" s="9" t="n"/>
+      <c r="CA9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CB9" s="12">
+        <f>CA9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3696,10 +3849,10 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -3716,7 +3869,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>502</v>
@@ -3726,37 +3879,37 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>491</v>
@@ -3766,79 +3919,79 @@
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AG10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AN10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
       <c r="AP10" s="9" t="n"/>
       <c r="AQ10" s="9" t="n"/>
       <c r="AR10" s="12" t="n"/>
-      <c r="AS10" s="9" t="n">
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AT10" s="9" t="n">
+      <c r="AW10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
-      <c r="AY10" s="9" t="n">
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AZ10" s="9" t="n">
+      <c r="BC10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="BA10" s="12">
-        <f>AZ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BB10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BD10" s="12">
         <f>BC10/$E$10</f>
         <v/>
       </c>
       <c r="BE10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF10" s="9" t="n">
         <v>462</v>
@@ -3851,58 +4004,68 @@
         <v>2</v>
       </c>
       <c r="BI10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
       <c r="BK10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
         <v/>
       </c>
       <c r="BN10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BO10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BP10" s="12">
         <f>BO10/$E$10</f>
         <v/>
       </c>
       <c r="BQ10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BR10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BS10" s="12">
         <f>BR10/$E$10</f>
         <v/>
       </c>
       <c r="BT10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="BU10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="BV10" s="12">
         <f>BU10/$E$10</f>
         <v/>
       </c>
-      <c r="BW10" s="9" t="n"/>
+      <c r="BW10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="BX10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="BY10" s="12">
         <f>BX10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BZ10" s="9" t="n"/>
+      <c r="CA10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="CB10" s="12">
+        <f>CA10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -3969,7 +4132,7 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
         <v>467</v>
@@ -3982,17 +4145,17 @@
         <v>1</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
         <v/>
       </c>
       <c r="X11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z11" s="12">
         <f>Y11/$E$11</f>
@@ -4018,60 +4181,60 @@
         <f>AE11/$E$11</f>
         <v/>
       </c>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AN11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
       <c r="AP11" s="9" t="n"/>
       <c r="AQ11" s="9" t="n"/>
       <c r="AR11" s="12" t="n"/>
-      <c r="AS11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="9" t="n">
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AU11" s="12">
-        <f>AT11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n"/>
-      <c r="AX11" s="12" t="n"/>
-      <c r="AY11" s="9" t="n">
+      <c r="AX11" s="12">
+        <f>AW11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="9" t="n"/>
+      <c r="AZ11" s="9" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AZ11" s="9" t="n">
+      <c r="BC11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="BA11" s="12">
-        <f>AZ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BB11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
       <c r="BE11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF11" s="9" t="n">
         <v>463</v>
@@ -4081,40 +4244,40 @@
         <v/>
       </c>
       <c r="BH11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BI11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
         <v/>
       </c>
       <c r="BK11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
         <v/>
       </c>
       <c r="BN11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BP11" s="12">
         <f>BO11/$E$11</f>
         <v/>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BS11" s="12">
         <f>BR11/$E$11</f>
@@ -4124,18 +4287,28 @@
         <v>2</v>
       </c>
       <c r="BU11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BV11" s="12">
         <f>BU11/$E$11</f>
         <v/>
       </c>
-      <c r="BW11" s="9" t="n"/>
+      <c r="BW11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="BX11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BY11" s="12">
         <f>BX11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BZ11" s="9" t="n"/>
+      <c r="CA11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="CB11" s="12">
+        <f>CA11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -4202,7 +4375,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
         <v>236</v>
@@ -4212,17 +4385,17 @@
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>235</v>
@@ -4232,10 +4405,10 @@
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AC12" s="12">
         <f>AB12/$E$12</f>
@@ -4251,48 +4424,48 @@
         <f>AE12/$E$12</f>
         <v/>
       </c>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AN12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
       <c r="AP12" s="9" t="n"/>
       <c r="AQ12" s="9" t="n"/>
       <c r="AR12" s="12" t="n"/>
-      <c r="AS12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="9" t="n">
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
+      <c r="AV12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AU12" s="12">
-        <f>AT12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="12" t="n"/>
-      <c r="AY12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="BA12" s="12">
-        <f>AZ12/$E$12</f>
-        <v/>
-      </c>
+      <c r="AX12" s="12">
+        <f>AW12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="12" t="n"/>
       <c r="BB12" s="9" t="n">
         <v>0</v>
       </c>
@@ -4334,7 +4507,7 @@
         <v/>
       </c>
       <c r="BN12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO12" s="9" t="n">
         <v>236</v>
@@ -4344,31 +4517,41 @@
         <v/>
       </c>
       <c r="BQ12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BR12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BS12" s="12">
         <f>BR12/$E$12</f>
         <v/>
       </c>
       <c r="BT12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="BU12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BV12" s="12">
         <f>BU12/$E$12</f>
         <v/>
       </c>
-      <c r="BW12" s="9" t="n"/>
+      <c r="BW12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="BX12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="BY12" s="12">
         <f>BX12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BZ12" s="9" t="n"/>
+      <c r="CA12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="CB12" s="12">
+        <f>CA12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -4395,10 +4578,10 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
@@ -4415,7 +4598,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>621</v>
@@ -4425,142 +4608,142 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
+      <c r="AM13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AN13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
       <c r="AP13" s="9" t="n"/>
       <c r="AQ13" s="9" t="n"/>
       <c r="AR13" s="12" t="n"/>
-      <c r="AS13" s="9" t="n">
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AT13" s="9" t="n">
+      <c r="AW13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AU13" s="12">
-        <f>AT13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n"/>
-      <c r="AX13" s="12" t="n"/>
-      <c r="AY13" s="9" t="n">
+      <c r="AX13" s="12">
+        <f>AW13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AZ13" s="9" t="n">
+      <c r="BC13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="BA13" s="12">
-        <f>AZ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BB13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
       <c r="BE13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BF13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
       <c r="BK13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BL13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
@@ -4570,38 +4753,48 @@
         <v>4</v>
       </c>
       <c r="BO13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
         <v/>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BR13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
         <v/>
       </c>
       <c r="BT13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
         <v/>
       </c>
-      <c r="BW13" s="9" t="n"/>
+      <c r="BW13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="BX13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="BY13" s="12">
         <f>BX13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BZ13" s="9" t="n"/>
+      <c r="CA13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="CB13" s="12">
+        <f>CA13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -4628,10 +4821,10 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
@@ -4648,7 +4841,7 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>1145</v>
@@ -4658,17 +4851,17 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>1142</v>
@@ -4678,122 +4871,122 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="AC14" s="12">
         <f>AB14/$E$14</f>
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
+      <c r="AG14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
+      <c r="AM14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AK14" s="9" t="n">
+      <c r="AN14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
       <c r="AP14" s="9" t="n"/>
       <c r="AQ14" s="9" t="n"/>
       <c r="AR14" s="12" t="n"/>
-      <c r="AS14" s="9" t="n">
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AT14" s="9" t="n">
+      <c r="AW14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AU14" s="12">
-        <f>AT14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n"/>
-      <c r="AX14" s="12" t="n"/>
-      <c r="AY14" s="9" t="n">
+      <c r="AX14" s="12">
+        <f>AW14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="9" t="n"/>
+      <c r="AZ14" s="9" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AZ14" s="9" t="n">
+      <c r="BC14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="BA14" s="12">
-        <f>AZ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BB14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BD14" s="12">
         <f>BC14/$E$14</f>
         <v/>
       </c>
       <c r="BE14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BF14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BG14" s="12">
         <f>BF14/$E$14</f>
         <v/>
       </c>
       <c r="BH14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BI14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BJ14" s="12">
         <f>BI14/$E$14</f>
         <v/>
       </c>
       <c r="BK14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BL14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BM14" s="12">
         <f>BL14/$E$14</f>
@@ -4829,12 +5022,22 @@
         <f>BU14/$E$14</f>
         <v/>
       </c>
-      <c r="BW14" s="9" t="n"/>
+      <c r="BW14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BX14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BY14" s="12">
         <f>BX14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BZ14" s="9" t="n"/>
+      <c r="CA14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" s="12">
+        <f>CA14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -4881,7 +5084,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
         <v>126</v>
@@ -4894,17 +5097,17 @@
         <v>1</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T15" s="12">
         <f>S15/$E$15</f>
@@ -4921,7 +5124,7 @@
         <v/>
       </c>
       <c r="X15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>124</v>
@@ -4931,17 +5134,17 @@
         <v/>
       </c>
       <c r="AA15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AC15" s="12">
         <f>AB15/$E$15</f>
         <v/>
       </c>
       <c r="AD15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="9" t="n">
         <v>121</v>
@@ -4950,53 +5153,53 @@
         <f>AE15/$E$15</f>
         <v/>
       </c>
-      <c r="AG15" s="9" t="n"/>
-      <c r="AH15" s="9" t="n"/>
-      <c r="AI15" s="12" t="n"/>
-      <c r="AJ15" s="9" t="n">
+      <c r="AG15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AI15" s="12">
+        <f>AH15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="9" t="n"/>
+      <c r="AK15" s="9" t="n"/>
+      <c r="AL15" s="12" t="n"/>
+      <c r="AM15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AK15" s="9" t="n">
+      <c r="AN15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AL15" s="12">
-        <f>AK15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AM15" s="9" t="n"/>
-      <c r="AN15" s="9" t="n"/>
-      <c r="AO15" s="12" t="n"/>
+      <c r="AO15" s="12">
+        <f>AN15/$E$15</f>
+        <v/>
+      </c>
       <c r="AP15" s="9" t="n"/>
       <c r="AQ15" s="9" t="n"/>
       <c r="AR15" s="12" t="n"/>
-      <c r="AS15" s="9" t="n">
+      <c r="AS15" s="9" t="n"/>
+      <c r="AT15" s="9" t="n"/>
+      <c r="AU15" s="12" t="n"/>
+      <c r="AV15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AT15" s="9" t="n">
+      <c r="AW15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AU15" s="12">
-        <f>AT15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AV15" s="9" t="n"/>
-      <c r="AW15" s="9" t="n"/>
-      <c r="AX15" s="12" t="n"/>
-      <c r="AY15" s="9" t="n">
+      <c r="AX15" s="12">
+        <f>AW15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AY15" s="9" t="n"/>
+      <c r="AZ15" s="9" t="n"/>
+      <c r="BA15" s="12" t="n"/>
+      <c r="BB15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AZ15" s="9" t="n">
+      <c r="BC15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="BA15" s="12">
-        <f>AZ15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BB15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BD15" s="12">
         <f>BC15/$E$15</f>
@@ -5006,24 +5209,24 @@
         <v>3</v>
       </c>
       <c r="BF15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BG15" s="12">
         <f>BF15/$E$15</f>
         <v/>
       </c>
       <c r="BH15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BJ15" s="12">
         <f>BI15/$E$15</f>
         <v/>
       </c>
       <c r="BK15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BL15" s="9" t="n">
         <v>76</v>
@@ -5033,10 +5236,10 @@
         <v/>
       </c>
       <c r="BN15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BO15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BP15" s="12">
         <f>BO15/$E$15</f>
@@ -5062,12 +5265,22 @@
         <f>BU15/$E$15</f>
         <v/>
       </c>
-      <c r="BW15" s="9" t="n"/>
+      <c r="BW15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="BX15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="BY15" s="12">
         <f>BX15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BZ15" s="9" t="n"/>
+      <c r="CA15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" s="12">
+        <f>CA15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -5183,51 +5396,58 @@
         <f>AE16/$E$16</f>
         <v/>
       </c>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
       <c r="AP16" s="9" t="n"/>
       <c r="AQ16" s="9" t="n"/>
       <c r="AR16" s="12" t="n"/>
-      <c r="AS16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" s="9" t="n">
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AU16" s="12">
-        <f>AT16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
-      <c r="AY16" s="9" t="n">
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AZ16" s="9" t="n">
+      <c r="BC16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BA16" s="12">
-        <f>AZ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BB16" s="9" t="n"/>
-      <c r="BC16" s="9" t="n"/>
-      <c r="BD16" s="12" t="n"/>
+      <c r="BD16" s="12">
+        <f>BC16/$E$16</f>
+        <v/>
+      </c>
       <c r="BE16" s="9" t="n"/>
       <c r="BF16" s="9" t="n"/>
       <c r="BG16" s="12" t="n"/>
@@ -5247,11 +5467,14 @@
       <c r="BU16" s="9" t="n"/>
       <c r="BV16" s="12" t="n"/>
       <c r="BW16" s="9" t="n"/>
-      <c r="BX16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" s="12">
-        <f>BX16/$E$16</f>
+      <c r="BX16" s="9" t="n"/>
+      <c r="BY16" s="12" t="n"/>
+      <c r="BZ16" s="9" t="n"/>
+      <c r="CA16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" s="12">
+        <f>CA16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -5349,6 +5572,9 @@
       <c r="BW17" s="9" t="n"/>
       <c r="BX17" s="9" t="n"/>
       <c r="BY17" s="12" t="n"/>
+      <c r="BZ17" s="9" t="n"/>
+      <c r="CA17" s="9" t="n"/>
+      <c r="CB17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -5373,16 +5599,18 @@
         <v>830</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
-      <c r="I18" s="9" t="n"/>
+      <c r="I18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="J18" s="9" t="n">
         <v>139</v>
       </c>
@@ -5391,8 +5619,13 @@
         <v/>
       </c>
       <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="12" t="n"/>
+      <c r="M18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="N18" s="12">
+        <f>M18/$E$18</f>
+        <v/>
+      </c>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
       <c r="Q18" s="12" t="n"/>
@@ -5456,10 +5689,14 @@
       <c r="BW18" s="9" t="n"/>
       <c r="BX18" s="9" t="n"/>
       <c r="BY18" s="12" t="n"/>
+      <c r="BZ18" s="9" t="n"/>
+      <c r="CA18" s="9" t="n"/>
+      <c r="CB18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
@@ -5494,7 +5731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY18"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5574,6 +5811,9 @@
     <col width="9" customWidth="1" min="75" max="75"/>
     <col width="9" customWidth="1" min="76" max="76"/>
     <col width="9" customWidth="1" min="77" max="77"/>
+    <col width="9" customWidth="1" min="78" max="78"/>
+    <col width="9" customWidth="1" min="79" max="79"/>
+    <col width="9" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5592,75 +5832,78 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -6048,6 +6291,21 @@
         </is>
       </c>
       <c r="BY4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BZ4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CA4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CB4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -6096,7 +6354,7 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>298</v>
@@ -6109,115 +6367,122 @@
         <v>1</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
-      <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
-      <c r="W5" s="12" t="n"/>
-      <c r="X5" s="9" t="n">
+      <c r="U5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="W5" s="12">
+        <f>V5/$E$5</f>
+        <v/>
+      </c>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="12" t="n"/>
+      <c r="AA5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="AB5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="Z5" s="12">
-        <f>Y5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AA5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
-      <c r="AM5" s="9" t="n">
+      <c r="AJ5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
+      <c r="AP5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN5" s="9" t="n">
+      <c r="AQ5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AO5" s="12">
-        <f>AN5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AQ5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AR5" s="12">
         <f>AQ5/$E$5</f>
         <v/>
       </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
-      <c r="AV5" s="9" t="n">
+      <c r="AS5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AT5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="9" t="n"/>
+      <c r="AX5" s="12" t="n"/>
+      <c r="AY5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AW5" s="9" t="n">
+      <c r="AZ5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="AX5" s="12">
-        <f>AW5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n"/>
-      <c r="BA5" s="12" t="n"/>
+      <c r="BA5" s="12">
+        <f>AZ5/$E$5</f>
+        <v/>
+      </c>
       <c r="BB5" s="9" t="n"/>
-      <c r="BC5" s="9" t="n">
+      <c r="BC5" s="9" t="n"/>
+      <c r="BD5" s="12" t="n"/>
+      <c r="BE5" s="9" t="n"/>
+      <c r="BF5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="BD5" s="12">
-        <f>BC5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BE5" s="9" t="n"/>
-      <c r="BF5" s="9" t="n"/>
-      <c r="BG5" s="12" t="n"/>
+      <c r="BG5" s="12">
+        <f>BF5/$E$5</f>
+        <v/>
+      </c>
       <c r="BH5" s="9" t="n"/>
       <c r="BI5" s="9" t="n"/>
       <c r="BJ5" s="12" t="n"/>
@@ -6236,6 +6501,9 @@
       <c r="BW5" s="9" t="n"/>
       <c r="BX5" s="9" t="n"/>
       <c r="BY5" s="12" t="n"/>
+      <c r="BZ5" s="9" t="n"/>
+      <c r="CA5" s="9" t="n"/>
+      <c r="CB5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -6260,10 +6528,10 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
@@ -6280,7 +6548,7 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>950</v>
@@ -6290,118 +6558,125 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="12" t="n"/>
-      <c r="X6" s="9" t="n">
+      <c r="U6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="W6" s="12">
+        <f>V6/$E$6</f>
+        <v/>
+      </c>
+      <c r="X6" s="9" t="n"/>
+      <c r="Y6" s="9" t="n"/>
+      <c r="Z6" s="12" t="n"/>
+      <c r="AA6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="AB6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="Z6" s="12">
-        <f>Y6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AA6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AJ6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
-      <c r="AV6" s="9" t="n">
+      <c r="AS6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="AZ6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
       <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n">
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n"/>
+      <c r="BF6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="BD6" s="12">
-        <f>BC6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="12" t="n"/>
+      <c r="BG6" s="12">
+        <f>BF6/$E$6</f>
+        <v/>
+      </c>
       <c r="BH6" s="9" t="n"/>
       <c r="BI6" s="9" t="n"/>
       <c r="BJ6" s="12" t="n"/>
@@ -6420,6 +6695,9 @@
       <c r="BW6" s="9" t="n"/>
       <c r="BX6" s="9" t="n"/>
       <c r="BY6" s="12" t="n"/>
+      <c r="BZ6" s="9" t="n"/>
+      <c r="CA6" s="9" t="n"/>
+      <c r="CB6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -6493,99 +6771,106 @@
         <f>S7/$E$7</f>
         <v/>
       </c>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="12" t="n"/>
-      <c r="X7" s="9" t="n">
+      <c r="U7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="W7" s="12">
+        <f>V7/$E$7</f>
+        <v/>
+      </c>
+      <c r="X7" s="9" t="n"/>
+      <c r="Y7" s="9" t="n"/>
+      <c r="Z7" s="12" t="n"/>
+      <c r="AA7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="AB7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="Z7" s="12">
-        <f>Y7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AA7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AJ7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="9" t="n">
+      <c r="AS7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AW7" s="9" t="n">
+      <c r="AZ7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
       <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n">
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n"/>
+      <c r="BF7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BD7" s="12">
-        <f>BC7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="12" t="n"/>
+      <c r="BG7" s="12">
+        <f>BF7/$E$7</f>
+        <v/>
+      </c>
       <c r="BH7" s="9" t="n"/>
       <c r="BI7" s="9" t="n"/>
       <c r="BJ7" s="12" t="n"/>
@@ -6604,6 +6889,9 @@
       <c r="BW7" s="9" t="n"/>
       <c r="BX7" s="9" t="n"/>
       <c r="BY7" s="12" t="n"/>
+      <c r="BZ7" s="9" t="n"/>
+      <c r="CA7" s="9" t="n"/>
+      <c r="CB7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -6648,7 +6936,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>1054</v>
@@ -6658,17 +6946,17 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>1052</v>
@@ -6677,99 +6965,106 @@
         <f>S8/$E$8</f>
         <v/>
       </c>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="12" t="n"/>
-      <c r="X8" s="9" t="n">
+      <c r="U8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="V8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="W8" s="12">
+        <f>V8/$E$8</f>
+        <v/>
+      </c>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="12" t="n"/>
+      <c r="AA8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="Z8" s="12">
-        <f>Y8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AJ8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AQ8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
-      <c r="AV8" s="9" t="n">
+      <c r="AS8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AW8" s="9" t="n">
+      <c r="AZ8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
       <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n">
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n"/>
+      <c r="BF8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="BD8" s="12">
-        <f>BC8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="12" t="n"/>
+      <c r="BG8" s="12">
+        <f>BF8/$E$8</f>
+        <v/>
+      </c>
       <c r="BH8" s="9" t="n"/>
       <c r="BI8" s="9" t="n"/>
       <c r="BJ8" s="12" t="n"/>
@@ -6788,6 +7083,9 @@
       <c r="BW8" s="9" t="n"/>
       <c r="BX8" s="9" t="n"/>
       <c r="BY8" s="12" t="n"/>
+      <c r="BZ8" s="9" t="n"/>
+      <c r="CA8" s="9" t="n"/>
+      <c r="CB8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -6861,19 +7159,19 @@
         <f>S9/$E$9</f>
         <v/>
       </c>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="9" t="n">
+      <c r="U9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="Z9" s="12">
-        <f>Y9/$E$9</f>
-        <v/>
-      </c>
+      <c r="W9" s="12">
+        <f>V9/$E$9</f>
+        <v/>
+      </c>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="12" t="n"/>
       <c r="AA9" s="9" t="n">
         <v>0</v>
       </c>
@@ -6885,7 +7183,7 @@
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="9" t="n">
         <v>845</v>
@@ -6895,28 +7193,28 @@
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AI9" s="12">
         <f>AH9/$E$9</f>
         <v/>
       </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AJ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
       <c r="AP9" s="9" t="n">
         <v>0</v>
       </c>
@@ -6927,33 +7225,40 @@
         <f>AQ9/$E$9</f>
         <v/>
       </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
-      <c r="AV9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="9" t="n">
+      <c r="AS9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
       <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n">
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
+      <c r="BE9" s="9" t="n"/>
+      <c r="BF9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BD9" s="12">
-        <f>BC9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="12" t="n"/>
+      <c r="BG9" s="12">
+        <f>BF9/$E$9</f>
+        <v/>
+      </c>
       <c r="BH9" s="9" t="n"/>
       <c r="BI9" s="9" t="n"/>
       <c r="BJ9" s="12" t="n"/>
@@ -6972,6 +7277,9 @@
       <c r="BW9" s="9" t="n"/>
       <c r="BX9" s="9" t="n"/>
       <c r="BY9" s="12" t="n"/>
+      <c r="BZ9" s="9" t="n"/>
+      <c r="CA9" s="9" t="n"/>
+      <c r="CB9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -7016,7 +7324,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>1418</v>
@@ -7026,118 +7334,125 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
-      <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
-      <c r="W10" s="12" t="n"/>
-      <c r="X10" s="9" t="n">
+      <c r="U10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="W10" s="12">
+        <f>V10/$E$10</f>
+        <v/>
+      </c>
+      <c r="X10" s="9" t="n"/>
+      <c r="Y10" s="9" t="n"/>
+      <c r="Z10" s="12" t="n"/>
+      <c r="AA10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="AB10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="Z10" s="12">
-        <f>Y10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AA10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
+      <c r="AJ10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AQ10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="9" t="n">
+      <c r="AS10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AW10" s="9" t="n">
+      <c r="AT10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="AX10" s="12">
-        <f>AW10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
       <c r="BB10" s="9" t="n"/>
-      <c r="BC10" s="9" t="n">
+      <c r="BC10" s="9" t="n"/>
+      <c r="BD10" s="12" t="n"/>
+      <c r="BE10" s="9" t="n"/>
+      <c r="BF10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="BD10" s="12">
-        <f>BC10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BE10" s="9" t="n"/>
-      <c r="BF10" s="9" t="n"/>
-      <c r="BG10" s="12" t="n"/>
+      <c r="BG10" s="12">
+        <f>BF10/$E$10</f>
+        <v/>
+      </c>
       <c r="BH10" s="9" t="n"/>
       <c r="BI10" s="9" t="n"/>
       <c r="BJ10" s="12" t="n"/>
@@ -7156,6 +7471,9 @@
       <c r="BW10" s="9" t="n"/>
       <c r="BX10" s="9" t="n"/>
       <c r="BY10" s="12" t="n"/>
+      <c r="BZ10" s="9" t="n"/>
+      <c r="CA10" s="9" t="n"/>
+      <c r="CB10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -7180,10 +7498,10 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
@@ -7200,7 +7518,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>992</v>
@@ -7210,10 +7528,10 @@
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
@@ -7229,99 +7547,106 @@
         <f>S11/$E$11</f>
         <v/>
       </c>
-      <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
-      <c r="W11" s="12" t="n"/>
-      <c r="X11" s="9" t="n">
+      <c r="U11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="W11" s="12">
+        <f>V11/$E$11</f>
+        <v/>
+      </c>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="12" t="n"/>
+      <c r="AA11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="AB11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="Z11" s="12">
-        <f>Y11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AA11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="AC11" s="12">
         <f>AB11/$E$11</f>
         <v/>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
         <v/>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AH11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AI11" s="12">
         <f>AH11/$E$11</f>
         <v/>
       </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
+      <c r="AJ11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AQ11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
-      <c r="AV11" s="9" t="n">
+      <c r="AS11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AW11" s="9" t="n">
+      <c r="AZ11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="AX11" s="12">
-        <f>AW11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n"/>
-      <c r="BA11" s="12" t="n"/>
+      <c r="BA11" s="12">
+        <f>AZ11/$E$11</f>
+        <v/>
+      </c>
       <c r="BB11" s="9" t="n"/>
-      <c r="BC11" s="9" t="n">
+      <c r="BC11" s="9" t="n"/>
+      <c r="BD11" s="12" t="n"/>
+      <c r="BE11" s="9" t="n"/>
+      <c r="BF11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="BD11" s="12">
-        <f>BC11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BE11" s="9" t="n"/>
-      <c r="BF11" s="9" t="n"/>
-      <c r="BG11" s="12" t="n"/>
+      <c r="BG11" s="12">
+        <f>BF11/$E$11</f>
+        <v/>
+      </c>
       <c r="BH11" s="9" t="n"/>
       <c r="BI11" s="9" t="n"/>
       <c r="BJ11" s="12" t="n"/>
@@ -7340,6 +7665,9 @@
       <c r="BW11" s="9" t="n"/>
       <c r="BX11" s="9" t="n"/>
       <c r="BY11" s="12" t="n"/>
+      <c r="BZ11" s="9" t="n"/>
+      <c r="CA11" s="9" t="n"/>
+      <c r="CB11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -7384,7 +7712,7 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>737</v>
@@ -7394,118 +7722,125 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
-      <c r="U12" s="9" t="n"/>
-      <c r="V12" s="9" t="n"/>
-      <c r="W12" s="12" t="n"/>
-      <c r="X12" s="9" t="n">
+      <c r="U12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="W12" s="12">
+        <f>V12/$E$12</f>
+        <v/>
+      </c>
+      <c r="X12" s="9" t="n"/>
+      <c r="Y12" s="9" t="n"/>
+      <c r="Z12" s="12" t="n"/>
+      <c r="AA12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="Y12" s="9" t="n">
+      <c r="AB12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="Z12" s="12">
-        <f>Y12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AA12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="AC12" s="12">
         <f>AB12/$E$12</f>
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AI12" s="12">
         <f>AH12/$E$12</f>
         <v/>
       </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
+      <c r="AJ12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
+      <c r="AP12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AQ12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AP12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AR12" s="12">
         <f>AQ12/$E$12</f>
         <v/>
       </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
-      <c r="AV12" s="9" t="n">
+      <c r="AS12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="12" t="n"/>
+      <c r="AY12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AW12" s="9" t="n">
+      <c r="AZ12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="AX12" s="12">
-        <f>AW12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n"/>
-      <c r="BA12" s="12" t="n"/>
+      <c r="BA12" s="12">
+        <f>AZ12/$E$12</f>
+        <v/>
+      </c>
       <c r="BB12" s="9" t="n"/>
-      <c r="BC12" s="9" t="n">
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="12" t="n"/>
+      <c r="BE12" s="9" t="n"/>
+      <c r="BF12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="BD12" s="12">
-        <f>BC12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BE12" s="9" t="n"/>
-      <c r="BF12" s="9" t="n"/>
-      <c r="BG12" s="12" t="n"/>
+      <c r="BG12" s="12">
+        <f>BF12/$E$12</f>
+        <v/>
+      </c>
       <c r="BH12" s="9" t="n"/>
       <c r="BI12" s="9" t="n"/>
       <c r="BJ12" s="12" t="n"/>
@@ -7524,6 +7859,9 @@
       <c r="BW12" s="9" t="n"/>
       <c r="BX12" s="9" t="n"/>
       <c r="BY12" s="12" t="n"/>
+      <c r="BZ12" s="9" t="n"/>
+      <c r="CA12" s="9" t="n"/>
+      <c r="CB12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -7548,10 +7886,10 @@
         <v>1623</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
@@ -7588,7 +7926,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
         <v>1391</v>
@@ -7597,99 +7935,106 @@
         <f>S13/$E$13</f>
         <v/>
       </c>
-      <c r="U13" s="9" t="n"/>
-      <c r="V13" s="9" t="n"/>
-      <c r="W13" s="12" t="n"/>
-      <c r="X13" s="9" t="n">
+      <c r="U13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="V13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="W13" s="12">
+        <f>V13/$E$13</f>
+        <v/>
+      </c>
+      <c r="X13" s="9" t="n"/>
+      <c r="Y13" s="9" t="n"/>
+      <c r="Z13" s="12" t="n"/>
+      <c r="AA13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="Z13" s="12">
-        <f>Y13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AA13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AJ13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AQ13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AP13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="9" t="n">
+      <c r="AS13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AV13" s="9" t="n"/>
+      <c r="AW13" s="9" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AW13" s="9" t="n">
+      <c r="AZ13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="AX13" s="12">
-        <f>AW13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n"/>
-      <c r="BA13" s="12" t="n"/>
+      <c r="BA13" s="12">
+        <f>AZ13/$E$13</f>
+        <v/>
+      </c>
       <c r="BB13" s="9" t="n"/>
-      <c r="BC13" s="9" t="n">
+      <c r="BC13" s="9" t="n"/>
+      <c r="BD13" s="12" t="n"/>
+      <c r="BE13" s="9" t="n"/>
+      <c r="BF13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="BD13" s="12">
-        <f>BC13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BE13" s="9" t="n"/>
-      <c r="BF13" s="9" t="n"/>
-      <c r="BG13" s="12" t="n"/>
+      <c r="BG13" s="12">
+        <f>BF13/$E$13</f>
+        <v/>
+      </c>
       <c r="BH13" s="9" t="n"/>
       <c r="BI13" s="9" t="n"/>
       <c r="BJ13" s="12" t="n"/>
@@ -7708,6 +8053,9 @@
       <c r="BW13" s="9" t="n"/>
       <c r="BX13" s="9" t="n"/>
       <c r="BY13" s="12" t="n"/>
+      <c r="BZ13" s="9" t="n"/>
+      <c r="CA13" s="9" t="n"/>
+      <c r="CB13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -7732,10 +8080,10 @@
         <v>996</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
@@ -7772,7 +8120,7 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>902</v>
@@ -7781,21 +8129,21 @@
         <f>S14/$E$14</f>
         <v/>
       </c>
-      <c r="U14" s="9" t="n"/>
-      <c r="V14" s="9" t="n"/>
-      <c r="W14" s="12" t="n"/>
-      <c r="X14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="Z14" s="12">
-        <f>Y14/$E$14</f>
-        <v/>
-      </c>
+      <c r="U14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="W14" s="12">
+        <f>V14/$E$14</f>
+        <v/>
+      </c>
+      <c r="X14" s="9" t="n"/>
+      <c r="Y14" s="9" t="n"/>
+      <c r="Z14" s="12" t="n"/>
       <c r="AA14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="9" t="n">
         <v>898</v>
@@ -7805,75 +8153,82 @@
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
+      <c r="AJ14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AQ14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AP14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
-      <c r="AV14" s="9" t="n">
+      <c r="AS14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AW14" s="9" t="n">
+      <c r="AT14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="AX14" s="12">
-        <f>AW14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n"/>
-      <c r="BA14" s="12" t="n"/>
+      <c r="BA14" s="12">
+        <f>AZ14/$E$14</f>
+        <v/>
+      </c>
       <c r="BB14" s="9" t="n"/>
-      <c r="BC14" s="9" t="n">
+      <c r="BC14" s="9" t="n"/>
+      <c r="BD14" s="12" t="n"/>
+      <c r="BE14" s="9" t="n"/>
+      <c r="BF14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="BD14" s="12">
-        <f>BC14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BE14" s="9" t="n"/>
-      <c r="BF14" s="9" t="n"/>
-      <c r="BG14" s="12" t="n"/>
+      <c r="BG14" s="12">
+        <f>BF14/$E$14</f>
+        <v/>
+      </c>
       <c r="BH14" s="9" t="n"/>
       <c r="BI14" s="9" t="n"/>
       <c r="BJ14" s="12" t="n"/>
@@ -7892,6 +8247,9 @@
       <c r="BW14" s="9" t="n"/>
       <c r="BX14" s="9" t="n"/>
       <c r="BY14" s="12" t="n"/>
+      <c r="BZ14" s="9" t="n"/>
+      <c r="CA14" s="9" t="n"/>
+      <c r="CB14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -7987,6 +8345,9 @@
       <c r="BW15" s="9" t="n"/>
       <c r="BX15" s="9" t="n"/>
       <c r="BY15" s="12" t="n"/>
+      <c r="BZ15" s="9" t="n"/>
+      <c r="CA15" s="9" t="n"/>
+      <c r="CB15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -8011,10 +8372,10 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H16" s="11">
         <f>G16/$E$16</f>
@@ -8031,7 +8392,7 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>715</v>
@@ -8041,118 +8402,125 @@
         <v/>
       </c>
       <c r="O16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/$E$16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="T16" s="12">
         <f>S16/$E$16</f>
         <v/>
       </c>
-      <c r="U16" s="9" t="n"/>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="12" t="n"/>
-      <c r="X16" s="9" t="n">
+      <c r="U16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="W16" s="12">
+        <f>V16/$E$16</f>
+        <v/>
+      </c>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="12" t="n"/>
+      <c r="AA16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Y16" s="9" t="n">
+      <c r="AB16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="Z16" s="12">
-        <f>Y16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AA16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="AC16" s="12">
         <f>AB16/$E$16</f>
         <v/>
       </c>
       <c r="AD16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AH16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AI16" s="12">
         <f>AH16/$E$16</f>
         <v/>
       </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
+      <c r="AJ16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AQ16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AP16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AR16" s="12">
         <f>AQ16/$E$16</f>
         <v/>
       </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="9" t="n">
+      <c r="AS16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AW16" s="9" t="n">
+      <c r="AZ16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="AX16" s="12">
-        <f>AW16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
       <c r="BB16" s="9" t="n"/>
-      <c r="BC16" s="9" t="n">
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="12" t="n"/>
+      <c r="BE16" s="9" t="n"/>
+      <c r="BF16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="BD16" s="12">
-        <f>BC16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BE16" s="9" t="n"/>
-      <c r="BF16" s="9" t="n"/>
-      <c r="BG16" s="12" t="n"/>
+      <c r="BG16" s="12">
+        <f>BF16/$E$16</f>
+        <v/>
+      </c>
       <c r="BH16" s="9" t="n"/>
       <c r="BI16" s="9" t="n"/>
       <c r="BJ16" s="12" t="n"/>
@@ -8171,6 +8539,9 @@
       <c r="BW16" s="9" t="n"/>
       <c r="BX16" s="9" t="n"/>
       <c r="BY16" s="12" t="n"/>
+      <c r="BZ16" s="9" t="n"/>
+      <c r="CA16" s="9" t="n"/>
+      <c r="CB16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -8195,20 +8566,20 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H17" s="11">
         <f>G17/$E$17</f>
         <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K17" s="12">
         <f>J17/$E$17</f>
@@ -8225,7 +8596,7 @@
         <v/>
       </c>
       <c r="O17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>385</v>
@@ -8235,108 +8606,115 @@
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T17" s="12">
         <f>S17/$E$17</f>
         <v/>
       </c>
-      <c r="U17" s="9" t="n"/>
-      <c r="V17" s="9" t="n"/>
-      <c r="W17" s="12" t="n"/>
-      <c r="X17" s="9" t="n">
+      <c r="U17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Y17" s="9" t="n">
+      <c r="V17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="W17" s="12">
+        <f>V17/$E$17</f>
+        <v/>
+      </c>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="12" t="n"/>
+      <c r="AA17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="Z17" s="12">
-        <f>Y17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AA17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="AC17" s="12">
         <f>AB17/$E$17</f>
         <v/>
       </c>
       <c r="AD17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AF17" s="12">
         <f>AE17/$E$17</f>
         <v/>
       </c>
       <c r="AG17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AI17" s="12">
         <f>AH17/$E$17</f>
         <v/>
       </c>
-      <c r="AJ17" s="9" t="n"/>
-      <c r="AK17" s="9" t="n"/>
-      <c r="AL17" s="12" t="n"/>
-      <c r="AM17" s="9" t="n">
+      <c r="AJ17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AL17" s="12">
+        <f>AK17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AM17" s="9" t="n"/>
+      <c r="AN17" s="9" t="n"/>
+      <c r="AO17" s="12" t="n"/>
+      <c r="AP17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AN17" s="9" t="n">
+      <c r="AQ17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AO17" s="12">
-        <f>AN17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AP17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AR17" s="12">
         <f>AQ17/$E$17</f>
         <v/>
       </c>
-      <c r="AS17" s="9" t="n"/>
-      <c r="AT17" s="9" t="n"/>
-      <c r="AU17" s="12" t="n"/>
-      <c r="AV17" s="9" t="n">
+      <c r="AS17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AU17" s="12">
+        <f>AT17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AV17" s="9" t="n"/>
+      <c r="AW17" s="9" t="n"/>
+      <c r="AX17" s="12" t="n"/>
+      <c r="AY17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AW17" s="9" t="n">
+      <c r="AZ17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="AX17" s="12">
-        <f>AW17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AY17" s="9" t="n"/>
-      <c r="AZ17" s="9" t="n"/>
-      <c r="BA17" s="12" t="n"/>
+      <c r="BA17" s="12">
+        <f>AZ17/$E$17</f>
+        <v/>
+      </c>
       <c r="BB17" s="9" t="n"/>
-      <c r="BC17" s="9" t="n">
+      <c r="BC17" s="9" t="n"/>
+      <c r="BD17" s="12" t="n"/>
+      <c r="BE17" s="9" t="n"/>
+      <c r="BF17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="BD17" s="12">
-        <f>BC17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BE17" s="9" t="n"/>
-      <c r="BF17" s="9" t="n"/>
-      <c r="BG17" s="12" t="n"/>
+      <c r="BG17" s="12">
+        <f>BF17/$E$17</f>
+        <v/>
+      </c>
       <c r="BH17" s="9" t="n"/>
       <c r="BI17" s="9" t="n"/>
       <c r="BJ17" s="12" t="n"/>
@@ -8355,6 +8733,9 @@
       <c r="BW17" s="9" t="n"/>
       <c r="BX17" s="9" t="n"/>
       <c r="BY17" s="12" t="n"/>
+      <c r="BZ17" s="9" t="n"/>
+      <c r="CA17" s="9" t="n"/>
+      <c r="CB17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -8399,7 +8780,7 @@
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
         <v>292</v>
@@ -8409,118 +8790,125 @@
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
-      <c r="U18" s="9" t="n"/>
-      <c r="V18" s="9" t="n"/>
-      <c r="W18" s="12" t="n"/>
-      <c r="X18" s="9" t="n">
+      <c r="U18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="W18" s="12">
+        <f>V18/$E$18</f>
+        <v/>
+      </c>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="12" t="n"/>
+      <c r="AA18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="AB18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="Z18" s="12">
-        <f>Y18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AA18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="AC18" s="12">
         <f>AB18/$E$18</f>
         <v/>
       </c>
       <c r="AD18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
       <c r="AG18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AI18" s="12">
         <f>AH18/$E$18</f>
         <v/>
       </c>
-      <c r="AJ18" s="9" t="n"/>
-      <c r="AK18" s="9" t="n"/>
-      <c r="AL18" s="12" t="n"/>
-      <c r="AM18" s="9" t="n">
+      <c r="AJ18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AL18" s="12">
+        <f>AK18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="9" t="n"/>
+      <c r="AO18" s="12" t="n"/>
+      <c r="AP18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AN18" s="9" t="n">
+      <c r="AQ18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AO18" s="12">
-        <f>AN18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AP18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AR18" s="12">
         <f>AQ18/$E$18</f>
         <v/>
       </c>
-      <c r="AS18" s="9" t="n"/>
-      <c r="AT18" s="9" t="n"/>
-      <c r="AU18" s="12" t="n"/>
-      <c r="AV18" s="9" t="n">
+      <c r="AS18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AU18" s="12">
+        <f>AT18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AV18" s="9" t="n"/>
+      <c r="AW18" s="9" t="n"/>
+      <c r="AX18" s="12" t="n"/>
+      <c r="AY18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AW18" s="9" t="n">
+      <c r="AZ18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="AX18" s="12">
-        <f>AW18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AY18" s="9" t="n"/>
-      <c r="AZ18" s="9" t="n"/>
-      <c r="BA18" s="12" t="n"/>
+      <c r="BA18" s="12">
+        <f>AZ18/$E$18</f>
+        <v/>
+      </c>
       <c r="BB18" s="9" t="n"/>
-      <c r="BC18" s="9" t="n">
+      <c r="BC18" s="9" t="n"/>
+      <c r="BD18" s="12" t="n"/>
+      <c r="BE18" s="9" t="n"/>
+      <c r="BF18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="BD18" s="12">
-        <f>BC18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BE18" s="9" t="n"/>
-      <c r="BF18" s="9" t="n"/>
-      <c r="BG18" s="12" t="n"/>
+      <c r="BG18" s="12">
+        <f>BF18/$E$18</f>
+        <v/>
+      </c>
       <c r="BH18" s="9" t="n"/>
       <c r="BI18" s="9" t="n"/>
       <c r="BJ18" s="12" t="n"/>
@@ -8539,10 +8927,14 @@
       <c r="BW18" s="9" t="n"/>
       <c r="BX18" s="9" t="n"/>
       <c r="BY18" s="12" t="n"/>
+      <c r="BZ18" s="9" t="n"/>
+      <c r="CA18" s="9" t="n"/>
+      <c r="CB18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -582,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 17/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 18/08/2026</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 17/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 18/08/2026</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 17/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 18/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -570,6 +570,9 @@
     <col width="9" customWidth="1" min="78" max="78"/>
     <col width="9" customWidth="1" min="79" max="79"/>
     <col width="9" customWidth="1" min="80" max="80"/>
+    <col width="9" customWidth="1" min="81" max="81"/>
+    <col width="9" customWidth="1" min="82" max="82"/>
+    <col width="9" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,78 +591,81 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1062,6 +1068,21 @@
         </is>
       </c>
       <c r="CB4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CC4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CD4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CE4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1130,7 +1151,7 @@
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
         <v>43</v>
@@ -1140,17 +1161,17 @@
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>42</v>
@@ -1163,49 +1184,56 @@
         <v>1</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
-      <c r="AJ5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="9" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AN5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AL5" s="12">
-        <f>AK5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
       <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n">
+      <c r="AQ5" s="9" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AR5" s="12">
-        <f>AQ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
       <c r="AV5" s="9" t="n"/>
       <c r="AW5" s="9" t="n"/>
       <c r="AX5" s="12" t="n"/>
@@ -1239,6 +1267,9 @@
       <c r="BZ5" s="9" t="n"/>
       <c r="CA5" s="9" t="n"/>
       <c r="CB5" s="12" t="n"/>
+      <c r="CC5" s="9" t="n"/>
+      <c r="CD5" s="9" t="n"/>
+      <c r="CE5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1263,7 +1294,7 @@
         <v>154</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>34</v>
@@ -1273,10 +1304,10 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
@@ -1352,33 +1383,40 @@
         <f>AE6/$E$6</f>
         <v/>
       </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AN6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
       <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n">
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
       <c r="AV6" s="9" t="n"/>
       <c r="AW6" s="9" t="n"/>
       <c r="AX6" s="12" t="n"/>
@@ -1412,6 +1450,9 @@
       <c r="BZ6" s="9" t="n"/>
       <c r="CA6" s="9" t="n"/>
       <c r="CB6" s="12" t="n"/>
+      <c r="CC6" s="9" t="n"/>
+      <c r="CD6" s="9" t="n"/>
+      <c r="CE6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1439,17 +1480,17 @@
         <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
@@ -1486,7 +1527,7 @@
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>45</v>
@@ -1496,62 +1537,69 @@
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AN7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
       <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n">
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
       <c r="AV7" s="9" t="n"/>
       <c r="AW7" s="9" t="n"/>
       <c r="AX7" s="12" t="n"/>
@@ -1585,6 +1633,9 @@
       <c r="BZ7" s="9" t="n"/>
       <c r="CA7" s="9" t="n"/>
       <c r="CB7" s="12" t="n"/>
+      <c r="CC7" s="9" t="n"/>
+      <c r="CD7" s="9" t="n"/>
+      <c r="CE7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1698,33 +1749,40 @@
         <f>AE8/$E$8</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
       <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n">
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
       <c r="AV8" s="9" t="n"/>
       <c r="AW8" s="9" t="n"/>
       <c r="AX8" s="12" t="n"/>
@@ -1758,6 +1816,9 @@
       <c r="BZ8" s="9" t="n"/>
       <c r="CA8" s="9" t="n"/>
       <c r="CB8" s="12" t="n"/>
+      <c r="CC8" s="9" t="n"/>
+      <c r="CD8" s="9" t="n"/>
+      <c r="CE8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1862,7 +1923,7 @@
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="9" t="n">
         <v>1</v>
@@ -1871,33 +1932,40 @@
         <f>AE9/$E$9</f>
         <v/>
       </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
+      <c r="AG9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
+      <c r="AM9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
       <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
       <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
+      <c r="AT9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
       <c r="AV9" s="9" t="n"/>
       <c r="AW9" s="9" t="n"/>
       <c r="AX9" s="12" t="n"/>
@@ -1931,6 +1999,9 @@
       <c r="BZ9" s="9" t="n"/>
       <c r="CA9" s="9" t="n"/>
       <c r="CB9" s="12" t="n"/>
+      <c r="CC9" s="9" t="n"/>
+      <c r="CD9" s="9" t="n"/>
+      <c r="CE9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1955,37 +2026,37 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>311</v>
@@ -1995,69 +2066,76 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
+      <c r="AG10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AH10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
       <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n">
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
       <c r="AP10" s="9" t="n"/>
       <c r="AQ10" s="9" t="n"/>
       <c r="AR10" s="12" t="n"/>
@@ -2097,9 +2175,12 @@
       <c r="BZ10" s="9" t="n"/>
       <c r="CA10" s="9" t="n"/>
       <c r="CB10" s="12" t="n"/>
+      <c r="CC10" s="9" t="n"/>
+      <c r="CD10" s="9" t="n"/>
+      <c r="CE10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -2115,6 +2196,7 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="CC3:CE3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="BE3:BG3"/>
@@ -2136,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2219,6 +2301,9 @@
     <col width="9" customWidth="1" min="78" max="78"/>
     <col width="9" customWidth="1" min="79" max="79"/>
     <col width="9" customWidth="1" min="80" max="80"/>
+    <col width="9" customWidth="1" min="81" max="81"/>
+    <col width="9" customWidth="1" min="82" max="82"/>
+    <col width="9" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2237,78 +2322,81 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2711,6 +2799,21 @@
         </is>
       </c>
       <c r="CB4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CC4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CD4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CE4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2739,7 +2842,7 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>178</v>
@@ -2749,10 +2852,10 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
@@ -2779,7 +2882,7 @@
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
         <v>177</v>
@@ -2788,17 +2891,24 @@
         <f>S5/$E$5</f>
         <v/>
       </c>
-      <c r="U5" s="9" t="n"/>
+      <c r="U5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="V5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
       <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="12" t="n"/>
+      <c r="Y5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="Z5" s="12">
+        <f>Y5/$E$5</f>
+        <v/>
+      </c>
       <c r="AA5" s="9" t="n"/>
       <c r="AB5" s="9" t="n"/>
       <c r="AC5" s="12" t="n"/>
@@ -2853,6 +2963,9 @@
       <c r="BZ5" s="9" t="n"/>
       <c r="CA5" s="9" t="n"/>
       <c r="CB5" s="12" t="n"/>
+      <c r="CC5" s="9" t="n"/>
+      <c r="CD5" s="9" t="n"/>
+      <c r="CE5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2877,20 +2990,20 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
@@ -2907,7 +3020,7 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>335</v>
@@ -2917,183 +3030,193 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AJ6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
       <c r="AS6" s="9" t="n"/>
       <c r="AT6" s="9" t="n"/>
       <c r="AU6" s="12" t="n"/>
-      <c r="AV6" s="9" t="n">
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="AZ6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
-      <c r="BB6" s="9" t="n">
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BC6" s="9" t="n">
+      <c r="BF6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="BD6" s="12">
-        <f>BC6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BE6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
       <c r="BH6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BI6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
       <c r="BK6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BL6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
         <v/>
       </c>
       <c r="BN6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BO6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
         <v/>
       </c>
       <c r="BQ6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BR6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
         <v/>
       </c>
       <c r="BT6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BU6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
         <v/>
       </c>
       <c r="BW6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BX6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BY6" s="12">
         <f>BX6/$E$6</f>
         <v/>
       </c>
-      <c r="BZ6" s="9" t="n"/>
+      <c r="BZ6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="CA6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="CB6" s="12">
         <f>CA6/$E$6</f>
+        <v/>
+      </c>
+      <c r="CC6" s="9" t="n"/>
+      <c r="CD6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="CE6" s="12">
+        <f>CD6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -3130,7 +3253,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>120</v>
@@ -3140,10 +3263,10 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
@@ -3160,7 +3283,7 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>119</v>
@@ -3173,109 +3296,109 @@
         <v>3</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AJ7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
       <c r="AS7" s="9" t="n"/>
       <c r="AT7" s="9" t="n"/>
       <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="9" t="n">
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AW7" s="9" t="n">
+      <c r="AZ7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
-      <c r="BB7" s="9" t="n">
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BC7" s="9" t="n">
+      <c r="BF7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="BD7" s="12">
-        <f>BC7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BE7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
       <c r="BH7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BI7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
@@ -3285,58 +3408,68 @@
         <v>6</v>
       </c>
       <c r="BL7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
         <v/>
       </c>
       <c r="BN7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
         <v/>
       </c>
       <c r="BQ7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
         <v/>
       </c>
       <c r="BT7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
         <v/>
       </c>
       <c r="BW7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BX7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="BY7" s="12">
         <f>BX7/$E$7</f>
         <v/>
       </c>
-      <c r="BZ7" s="9" t="n"/>
+      <c r="BZ7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="CA7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CB7" s="12">
         <f>CA7/$E$7</f>
+        <v/>
+      </c>
+      <c r="CC7" s="9" t="n"/>
+      <c r="CD7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CE7" s="12">
+        <f>CD7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -3363,10 +3496,10 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
@@ -3393,7 +3526,7 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>998</v>
@@ -3403,112 +3536,112 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AJ8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AQ8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
       <c r="AS8" s="9" t="n"/>
       <c r="AT8" s="9" t="n"/>
       <c r="AU8" s="12" t="n"/>
-      <c r="AV8" s="9" t="n">
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AW8" s="9" t="n">
+      <c r="AZ8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
-      <c r="BB8" s="9" t="n">
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BC8" s="9" t="n">
+      <c r="BF8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="BD8" s="12">
-        <f>BC8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BE8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
@@ -3518,68 +3651,78 @@
         <v>7</v>
       </c>
       <c r="BI8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
         <v/>
       </c>
       <c r="BK8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BL8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
         <v/>
       </c>
       <c r="BN8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BO8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
         <v/>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BR8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
         <v/>
       </c>
       <c r="BT8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
         <v/>
       </c>
       <c r="BW8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BX8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="BY8" s="12">
         <f>BX8/$E$8</f>
         <v/>
       </c>
-      <c r="BZ8" s="9" t="n"/>
+      <c r="BZ8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="CA8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="CB8" s="12">
         <f>CA8/$E$8</f>
+        <v/>
+      </c>
+      <c r="CC8" s="9" t="n"/>
+      <c r="CD8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="CE8" s="12">
+        <f>CD8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3646,7 +3789,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>1125</v>
@@ -3656,27 +3799,27 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="W9" s="12">
         <f>V9/$E$9</f>
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="Z9" s="12">
         <f>Y9/$E$9</f>
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="9" t="n">
         <v>1119</v>
@@ -3686,17 +3829,17 @@
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AF9" s="12">
         <f>AE9/$E$9</f>
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="9" t="n">
         <v>1117</v>
@@ -3705,124 +3848,134 @@
         <f>AH9/$E$9</f>
         <v/>
       </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
+      <c r="AJ9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AQ9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
       <c r="AS9" s="9" t="n"/>
       <c r="AT9" s="9" t="n"/>
       <c r="AU9" s="12" t="n"/>
-      <c r="AV9" s="9" t="n">
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AW9" s="9" t="n">
+      <c r="AZ9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
-      <c r="BB9" s="9" t="n">
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="9" t="n"/>
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
+      <c r="BE9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BC9" s="9" t="n">
+      <c r="BF9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="BD9" s="12">
-        <f>BC9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BE9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BG9" s="12">
         <f>BF9/$E$9</f>
         <v/>
       </c>
       <c r="BH9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BI9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
       <c r="BK9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BL9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
         <v/>
       </c>
       <c r="BN9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BO9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
         <v/>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
         <v/>
       </c>
       <c r="BT9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
         <v/>
       </c>
       <c r="BW9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="BX9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="BY9" s="12">
         <f>BX9/$E$9</f>
         <v/>
       </c>
-      <c r="BZ9" s="9" t="n"/>
+      <c r="BZ9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="CA9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="CB9" s="12">
         <f>CA9/$E$9</f>
+        <v/>
+      </c>
+      <c r="CC9" s="9" t="n"/>
+      <c r="CD9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CE9" s="12">
+        <f>CD9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -3849,7 +4002,7 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>504</v>
@@ -3859,10 +4012,10 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
@@ -3879,7 +4032,7 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>502</v>
@@ -3889,37 +4042,37 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="9" t="n">
         <v>491</v>
@@ -3929,79 +4082,79 @@
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
+      <c r="AJ10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AQ10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
       <c r="AS10" s="9" t="n"/>
       <c r="AT10" s="9" t="n"/>
       <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="9" t="n">
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AW10" s="9" t="n">
+      <c r="AZ10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AX10" s="12">
-        <f>AW10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
-      <c r="BB10" s="9" t="n">
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n"/>
+      <c r="BD10" s="12" t="n"/>
+      <c r="BE10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BC10" s="9" t="n">
+      <c r="BF10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="BD10" s="12">
-        <f>BC10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BE10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
       <c r="BH10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI10" s="9" t="n">
         <v>462</v>
@@ -4014,58 +4167,68 @@
         <v>2</v>
       </c>
       <c r="BL10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
         <v/>
       </c>
       <c r="BN10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BO10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BP10" s="12">
         <f>BO10/$E$10</f>
         <v/>
       </c>
       <c r="BQ10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BR10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BS10" s="12">
         <f>BR10/$E$10</f>
         <v/>
       </c>
       <c r="BT10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BU10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BV10" s="12">
         <f>BU10/$E$10</f>
         <v/>
       </c>
       <c r="BW10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="BX10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="BY10" s="12">
         <f>BX10/$E$10</f>
         <v/>
       </c>
-      <c r="BZ10" s="9" t="n"/>
+      <c r="BZ10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="CA10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="CB10" s="12">
         <f>CA10/$E$10</f>
+        <v/>
+      </c>
+      <c r="CC10" s="9" t="n"/>
+      <c r="CD10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="CE10" s="12">
+        <f>CD10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -4142,7 +4305,7 @@
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>467</v>
@@ -4155,17 +4318,17 @@
         <v>1</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z11" s="12">
         <f>Y11/$E$11</f>
         <v/>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AC11" s="12">
         <f>AB11/$E$11</f>
@@ -4191,60 +4354,60 @@
         <f>AH11/$E$11</f>
         <v/>
       </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
+      <c r="AJ11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AQ11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n"/>
-      <c r="AR11" s="12" t="n"/>
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
       <c r="AS11" s="9" t="n"/>
       <c r="AT11" s="9" t="n"/>
       <c r="AU11" s="12" t="n"/>
-      <c r="AV11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="9" t="n">
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="AX11" s="12">
-        <f>AW11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n"/>
-      <c r="BA11" s="12" t="n"/>
-      <c r="BB11" s="9" t="n">
+      <c r="BA11" s="12">
+        <f>AZ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="9" t="n"/>
+      <c r="BC11" s="9" t="n"/>
+      <c r="BD11" s="12" t="n"/>
+      <c r="BE11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BC11" s="9" t="n">
+      <c r="BF11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="BD11" s="12">
-        <f>BC11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BE11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
         <v/>
       </c>
       <c r="BH11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI11" s="9" t="n">
         <v>463</v>
@@ -4254,40 +4417,40 @@
         <v/>
       </c>
       <c r="BK11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
         <v/>
       </c>
       <c r="BN11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BP11" s="12">
         <f>BO11/$E$11</f>
         <v/>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BS11" s="12">
         <f>BR11/$E$11</f>
         <v/>
       </c>
       <c r="BT11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BV11" s="12">
         <f>BU11/$E$11</f>
@@ -4297,18 +4460,28 @@
         <v>2</v>
       </c>
       <c r="BX11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BY11" s="12">
         <f>BX11/$E$11</f>
         <v/>
       </c>
-      <c r="BZ11" s="9" t="n"/>
+      <c r="BZ11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="CA11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CB11" s="12">
         <f>CA11/$E$11</f>
+        <v/>
+      </c>
+      <c r="CC11" s="9" t="n"/>
+      <c r="CD11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="CE11" s="12">
+        <f>CD11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -4385,7 +4558,7 @@
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>236</v>
@@ -4395,17 +4568,17 @@
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="9" t="n">
         <v>235</v>
@@ -4415,10 +4588,10 @@
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
@@ -4434,48 +4607,48 @@
         <f>AH12/$E$12</f>
         <v/>
       </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
+      <c r="AJ12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
+      <c r="AP12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AQ12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n"/>
-      <c r="AR12" s="12" t="n"/>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
       <c r="AS12" s="9" t="n"/>
       <c r="AT12" s="9" t="n"/>
       <c r="AU12" s="12" t="n"/>
-      <c r="AV12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="9" t="n">
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="12" t="n"/>
+      <c r="AY12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="AX12" s="12">
-        <f>AW12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n"/>
-      <c r="BA12" s="12" t="n"/>
-      <c r="BB12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="BD12" s="12">
-        <f>BC12/$E$12</f>
-        <v/>
-      </c>
+      <c r="BA12" s="12">
+        <f>AZ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="12" t="n"/>
       <c r="BE12" s="9" t="n">
         <v>0</v>
       </c>
@@ -4517,7 +4690,7 @@
         <v/>
       </c>
       <c r="BQ12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR12" s="9" t="n">
         <v>236</v>
@@ -4527,31 +4700,41 @@
         <v/>
       </c>
       <c r="BT12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BU12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BV12" s="12">
         <f>BU12/$E$12</f>
         <v/>
       </c>
       <c r="BW12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="BX12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="BY12" s="12">
         <f>BX12/$E$12</f>
         <v/>
       </c>
-      <c r="BZ12" s="9" t="n"/>
+      <c r="BZ12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="CA12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="CB12" s="12">
         <f>CA12/$E$12</f>
+        <v/>
+      </c>
+      <c r="CC12" s="9" t="n"/>
+      <c r="CD12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="CE12" s="12">
+        <f>CD12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -4578,7 +4761,7 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>622</v>
@@ -4588,10 +4771,10 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
@@ -4608,7 +4791,7 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>621</v>
@@ -4618,142 +4801,142 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AJ13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AQ13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n"/>
-      <c r="AR13" s="12" t="n"/>
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
       <c r="AS13" s="9" t="n"/>
       <c r="AT13" s="9" t="n"/>
       <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="9" t="n">
+      <c r="AV13" s="9" t="n"/>
+      <c r="AW13" s="9" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AW13" s="9" t="n">
+      <c r="AZ13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="AX13" s="12">
-        <f>AW13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n"/>
-      <c r="BA13" s="12" t="n"/>
-      <c r="BB13" s="9" t="n">
+      <c r="BA13" s="12">
+        <f>AZ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="9" t="n"/>
+      <c r="BC13" s="9" t="n"/>
+      <c r="BD13" s="12" t="n"/>
+      <c r="BE13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="BC13" s="9" t="n">
+      <c r="BF13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="BD13" s="12">
-        <f>BC13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BE13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
       <c r="BH13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BI13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
       <c r="BK13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BL13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
         <v/>
       </c>
       <c r="BN13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BO13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
@@ -4763,38 +4946,48 @@
         <v>4</v>
       </c>
       <c r="BR13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
         <v/>
       </c>
       <c r="BT13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
         <v/>
       </c>
       <c r="BW13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="BX13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="BY13" s="12">
         <f>BX13/$E$13</f>
         <v/>
       </c>
-      <c r="BZ13" s="9" t="n"/>
+      <c r="BZ13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="CA13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="CB13" s="12">
         <f>CA13/$E$13</f>
+        <v/>
+      </c>
+      <c r="CC13" s="9" t="n"/>
+      <c r="CD13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="CE13" s="12">
+        <f>CD13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -4821,7 +5014,7 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1146</v>
@@ -4831,10 +5024,10 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
@@ -4851,7 +5044,7 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>1145</v>
@@ -4861,17 +5054,17 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>1142</v>
@@ -4881,122 +5074,122 @@
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AC14" s="12">
         <f>AB14/$E$14</f>
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
+      <c r="AJ14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AN14" s="9" t="n">
+      <c r="AQ14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n"/>
-      <c r="AR14" s="12" t="n"/>
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
       <c r="AS14" s="9" t="n"/>
       <c r="AT14" s="9" t="n"/>
       <c r="AU14" s="12" t="n"/>
-      <c r="AV14" s="9" t="n">
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AW14" s="9" t="n">
+      <c r="AZ14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="AX14" s="12">
-        <f>AW14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n"/>
-      <c r="BA14" s="12" t="n"/>
-      <c r="BB14" s="9" t="n">
+      <c r="BA14" s="12">
+        <f>AZ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="9" t="n"/>
+      <c r="BC14" s="9" t="n"/>
+      <c r="BD14" s="12" t="n"/>
+      <c r="BE14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BC14" s="9" t="n">
+      <c r="BF14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="BD14" s="12">
-        <f>BC14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BE14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BG14" s="12">
         <f>BF14/$E$14</f>
         <v/>
       </c>
       <c r="BH14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BI14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BJ14" s="12">
         <f>BI14/$E$14</f>
         <v/>
       </c>
       <c r="BK14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BL14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BM14" s="12">
         <f>BL14/$E$14</f>
         <v/>
       </c>
       <c r="BN14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BO14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BP14" s="12">
         <f>BO14/$E$14</f>
@@ -5032,12 +5225,22 @@
         <f>BX14/$E$14</f>
         <v/>
       </c>
-      <c r="BZ14" s="9" t="n"/>
+      <c r="BZ14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CA14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CB14" s="12">
         <f>CA14/$E$14</f>
+        <v/>
+      </c>
+      <c r="CC14" s="9" t="n"/>
+      <c r="CD14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" s="12">
+        <f>CD14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -5094,7 +5297,7 @@
         <v/>
       </c>
       <c r="O15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>126</v>
@@ -5107,17 +5310,17 @@
         <v>1</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="T15" s="12">
         <f>S15/$E$15</f>
         <v/>
       </c>
       <c r="U15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="W15" s="12">
         <f>V15/$E$15</f>
@@ -5134,7 +5337,7 @@
         <v/>
       </c>
       <c r="AA15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="9" t="n">
         <v>124</v>
@@ -5144,17 +5347,17 @@
         <v/>
       </c>
       <c r="AD15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AF15" s="12">
         <f>AE15/$E$15</f>
         <v/>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="9" t="n">
         <v>121</v>
@@ -5163,53 +5366,53 @@
         <f>AH15/$E$15</f>
         <v/>
       </c>
-      <c r="AJ15" s="9" t="n"/>
-      <c r="AK15" s="9" t="n"/>
-      <c r="AL15" s="12" t="n"/>
-      <c r="AM15" s="9" t="n">
+      <c r="AJ15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AL15" s="12">
+        <f>AK15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AM15" s="9" t="n"/>
+      <c r="AN15" s="9" t="n"/>
+      <c r="AO15" s="12" t="n"/>
+      <c r="AP15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AN15" s="9" t="n">
+      <c r="AQ15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AO15" s="12">
-        <f>AN15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AP15" s="9" t="n"/>
-      <c r="AQ15" s="9" t="n"/>
-      <c r="AR15" s="12" t="n"/>
+      <c r="AR15" s="12">
+        <f>AQ15/$E$15</f>
+        <v/>
+      </c>
       <c r="AS15" s="9" t="n"/>
       <c r="AT15" s="9" t="n"/>
       <c r="AU15" s="12" t="n"/>
-      <c r="AV15" s="9" t="n">
+      <c r="AV15" s="9" t="n"/>
+      <c r="AW15" s="9" t="n"/>
+      <c r="AX15" s="12" t="n"/>
+      <c r="AY15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AW15" s="9" t="n">
+      <c r="AZ15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="AX15" s="12">
-        <f>AW15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AY15" s="9" t="n"/>
-      <c r="AZ15" s="9" t="n"/>
-      <c r="BA15" s="12" t="n"/>
-      <c r="BB15" s="9" t="n">
+      <c r="BA15" s="12">
+        <f>AZ15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BB15" s="9" t="n"/>
+      <c r="BC15" s="9" t="n"/>
+      <c r="BD15" s="12" t="n"/>
+      <c r="BE15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BC15" s="9" t="n">
+      <c r="BF15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="BD15" s="12">
-        <f>BC15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BE15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BG15" s="12">
         <f>BF15/$E$15</f>
@@ -5219,24 +5422,24 @@
         <v>3</v>
       </c>
       <c r="BI15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BJ15" s="12">
         <f>BI15/$E$15</f>
         <v/>
       </c>
       <c r="BK15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BM15" s="12">
         <f>BL15/$E$15</f>
         <v/>
       </c>
       <c r="BN15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BO15" s="9" t="n">
         <v>76</v>
@@ -5246,10 +5449,10 @@
         <v/>
       </c>
       <c r="BQ15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BR15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BS15" s="12">
         <f>BR15/$E$15</f>
@@ -5275,12 +5478,22 @@
         <f>BX15/$E$15</f>
         <v/>
       </c>
-      <c r="BZ15" s="9" t="n"/>
+      <c r="BZ15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CA15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CB15" s="12">
         <f>CA15/$E$15</f>
+        <v/>
+      </c>
+      <c r="CC15" s="9" t="n"/>
+      <c r="CD15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" s="12">
+        <f>CD15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -5406,51 +5619,58 @@
         <f>AH16/$E$16</f>
         <v/>
       </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AJ16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
       <c r="AS16" s="9" t="n"/>
       <c r="AT16" s="9" t="n"/>
       <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" s="9" t="n">
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AX16" s="12">
-        <f>AW16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
-      <c r="BB16" s="9" t="n">
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="12" t="n"/>
+      <c r="BE16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BC16" s="9" t="n">
+      <c r="BF16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BD16" s="12">
-        <f>BC16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BE16" s="9" t="n"/>
-      <c r="BF16" s="9" t="n"/>
-      <c r="BG16" s="12" t="n"/>
+      <c r="BG16" s="12">
+        <f>BF16/$E$16</f>
+        <v/>
+      </c>
       <c r="BH16" s="9" t="n"/>
       <c r="BI16" s="9" t="n"/>
       <c r="BJ16" s="12" t="n"/>
@@ -5470,11 +5690,14 @@
       <c r="BX16" s="9" t="n"/>
       <c r="BY16" s="12" t="n"/>
       <c r="BZ16" s="9" t="n"/>
-      <c r="CA16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" s="12">
-        <f>CA16/$E$16</f>
+      <c r="CA16" s="9" t="n"/>
+      <c r="CB16" s="12" t="n"/>
+      <c r="CC16" s="9" t="n"/>
+      <c r="CD16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" s="12">
+        <f>CD16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -5575,6 +5798,9 @@
       <c r="BZ17" s="9" t="n"/>
       <c r="CA17" s="9" t="n"/>
       <c r="CB17" s="12" t="n"/>
+      <c r="CC17" s="9" t="n"/>
+      <c r="CD17" s="9" t="n"/>
+      <c r="CE17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -5599,26 +5825,28 @@
         <v>830</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
-      <c r="L18" s="9" t="n"/>
+      <c r="L18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" s="9" t="n">
         <v>139</v>
       </c>
@@ -5627,8 +5855,13 @@
         <v/>
       </c>
       <c r="O18" s="9" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="12" t="n"/>
+      <c r="P18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q18" s="12">
+        <f>P18/$E$18</f>
+        <v/>
+      </c>
       <c r="R18" s="9" t="n"/>
       <c r="S18" s="9" t="n"/>
       <c r="T18" s="12" t="n"/>
@@ -5692,9 +5925,12 @@
       <c r="BZ18" s="9" t="n"/>
       <c r="CA18" s="9" t="n"/>
       <c r="CB18" s="12" t="n"/>
+      <c r="CC18" s="9" t="n"/>
+      <c r="CD18" s="9" t="n"/>
+      <c r="CE18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -5710,6 +5946,7 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="CC3:CE3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="BE3:BG3"/>
@@ -5731,7 +5968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5814,6 +6051,9 @@
     <col width="9" customWidth="1" min="78" max="78"/>
     <col width="9" customWidth="1" min="79" max="79"/>
     <col width="9" customWidth="1" min="80" max="80"/>
+    <col width="9" customWidth="1" min="81" max="81"/>
+    <col width="9" customWidth="1" min="82" max="82"/>
+    <col width="9" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5832,78 +6072,81 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -6306,6 +6549,21 @@
         </is>
       </c>
       <c r="CB4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CC4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CD4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CE4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -6334,10 +6592,10 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
@@ -6364,7 +6622,7 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>298</v>
@@ -6377,115 +6635,122 @@
         <v>1</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="12" t="n"/>
-      <c r="AA5" s="9" t="n">
+      <c r="X5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="Z5" s="12">
+        <f>Y5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="12" t="n"/>
+      <c r="AD5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="9" t="n">
+      <c r="AE5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="AC5" s="12">
-        <f>AB5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
       <c r="AJ5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
-      <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
-      <c r="AP5" s="9" t="n">
+      <c r="AM5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AN5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AP5" s="9" t="n"/>
+      <c r="AQ5" s="9" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ5" s="9" t="n">
+      <c r="AT5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AR5" s="12">
-        <f>AQ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AT5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AU5" s="12">
         <f>AT5/$E$5</f>
         <v/>
       </c>
-      <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n"/>
-      <c r="AX5" s="12" t="n"/>
-      <c r="AY5" s="9" t="n">
+      <c r="AV5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AW5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AX5" s="12">
+        <f>AW5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AY5" s="9" t="n"/>
+      <c r="AZ5" s="9" t="n"/>
+      <c r="BA5" s="12" t="n"/>
+      <c r="BB5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AZ5" s="9" t="n">
+      <c r="BC5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="BA5" s="12">
-        <f>AZ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BB5" s="9" t="n"/>
-      <c r="BC5" s="9" t="n"/>
-      <c r="BD5" s="12" t="n"/>
+      <c r="BD5" s="12">
+        <f>BC5/$E$5</f>
+        <v/>
+      </c>
       <c r="BE5" s="9" t="n"/>
-      <c r="BF5" s="9" t="n">
+      <c r="BF5" s="9" t="n"/>
+      <c r="BG5" s="12" t="n"/>
+      <c r="BH5" s="9" t="n"/>
+      <c r="BI5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="BG5" s="12">
-        <f>BF5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BH5" s="9" t="n"/>
-      <c r="BI5" s="9" t="n"/>
-      <c r="BJ5" s="12" t="n"/>
+      <c r="BJ5" s="12">
+        <f>BI5/$E$5</f>
+        <v/>
+      </c>
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
@@ -6504,6 +6769,9 @@
       <c r="BZ5" s="9" t="n"/>
       <c r="CA5" s="9" t="n"/>
       <c r="CB5" s="12" t="n"/>
+      <c r="CC5" s="9" t="n"/>
+      <c r="CD5" s="9" t="n"/>
+      <c r="CE5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -6528,20 +6796,20 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
@@ -6558,7 +6826,7 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>950</v>
@@ -6568,118 +6836,125 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="12" t="n"/>
-      <c r="AA6" s="9" t="n">
+      <c r="X6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="Z6" s="12">
+        <f>Y6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="9" t="n"/>
+      <c r="AC6" s="12" t="n"/>
+      <c r="AD6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AB6" s="9" t="n">
+      <c r="AE6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="AC6" s="12">
-        <f>AB6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AD6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
-      <c r="AP6" s="9" t="n">
+      <c r="AM6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AQ6" s="9" t="n">
+      <c r="AT6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
-      <c r="AY6" s="9" t="n">
+      <c r="AV6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AZ6" s="9" t="n">
+      <c r="BC6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="12" t="n"/>
+      <c r="BD6" s="12">
+        <f>BC6/$E$6</f>
+        <v/>
+      </c>
       <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n">
+      <c r="BF6" s="9" t="n"/>
+      <c r="BG6" s="12" t="n"/>
+      <c r="BH6" s="9" t="n"/>
+      <c r="BI6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="BG6" s="12">
-        <f>BF6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n"/>
-      <c r="BJ6" s="12" t="n"/>
+      <c r="BJ6" s="12">
+        <f>BI6/$E$6</f>
+        <v/>
+      </c>
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
@@ -6698,6 +6973,9 @@
       <c r="BZ6" s="9" t="n"/>
       <c r="CA6" s="9" t="n"/>
       <c r="CB6" s="12" t="n"/>
+      <c r="CC6" s="9" t="n"/>
+      <c r="CD6" s="9" t="n"/>
+      <c r="CE6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -6781,99 +7059,106 @@
         <f>V7/$E$7</f>
         <v/>
       </c>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="12" t="n"/>
-      <c r="AA7" s="9" t="n">
+      <c r="X7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z7" s="12">
+        <f>Y7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="9" t="n"/>
+      <c r="AC7" s="12" t="n"/>
+      <c r="AD7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="AB7" s="9" t="n">
+      <c r="AE7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="AC7" s="12">
-        <f>AB7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AD7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
-      <c r="AP7" s="9" t="n">
+      <c r="AM7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AQ7" s="9" t="n">
+      <c r="AN7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
-      <c r="AY7" s="9" t="n">
+      <c r="AV7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AZ7" s="9" t="n">
+      <c r="BC7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="12" t="n"/>
+      <c r="BD7" s="12">
+        <f>BC7/$E$7</f>
+        <v/>
+      </c>
       <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n">
+      <c r="BF7" s="9" t="n"/>
+      <c r="BG7" s="12" t="n"/>
+      <c r="BH7" s="9" t="n"/>
+      <c r="BI7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BG7" s="12">
-        <f>BF7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BH7" s="9" t="n"/>
-      <c r="BI7" s="9" t="n"/>
-      <c r="BJ7" s="12" t="n"/>
+      <c r="BJ7" s="12">
+        <f>BI7/$E$7</f>
+        <v/>
+      </c>
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
@@ -6892,6 +7177,9 @@
       <c r="BZ7" s="9" t="n"/>
       <c r="CA7" s="9" t="n"/>
       <c r="CB7" s="12" t="n"/>
+      <c r="CC7" s="9" t="n"/>
+      <c r="CD7" s="9" t="n"/>
+      <c r="CE7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -6916,10 +7204,10 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
@@ -6946,7 +7234,7 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>1054</v>
@@ -6956,17 +7244,17 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>1052</v>
@@ -6975,99 +7263,106 @@
         <f>V8/$E$8</f>
         <v/>
       </c>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="12" t="n"/>
-      <c r="AA8" s="9" t="n">
+      <c r="X8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB8" s="9" t="n">
+      <c r="Y8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="Z8" s="12">
+        <f>Y8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="12" t="n"/>
+      <c r="AD8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="AC8" s="12">
-        <f>AB8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AD8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
-      <c r="AP8" s="9" t="n">
+      <c r="AM8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AQ8" s="9" t="n">
+      <c r="AT8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
-      <c r="AY8" s="9" t="n">
+      <c r="AV8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AZ8" s="9" t="n">
+      <c r="BC8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="12" t="n"/>
+      <c r="BD8" s="12">
+        <f>BC8/$E$8</f>
+        <v/>
+      </c>
       <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n">
+      <c r="BF8" s="9" t="n"/>
+      <c r="BG8" s="12" t="n"/>
+      <c r="BH8" s="9" t="n"/>
+      <c r="BI8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="BG8" s="12">
-        <f>BF8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="9" t="n"/>
-      <c r="BJ8" s="12" t="n"/>
+      <c r="BJ8" s="12">
+        <f>BI8/$E$8</f>
+        <v/>
+      </c>
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
@@ -7086,6 +7381,9 @@
       <c r="BZ8" s="9" t="n"/>
       <c r="CA8" s="9" t="n"/>
       <c r="CB8" s="12" t="n"/>
+      <c r="CC8" s="9" t="n"/>
+      <c r="CD8" s="9" t="n"/>
+      <c r="CE8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -7169,19 +7467,19 @@
         <f>V9/$E$9</f>
         <v/>
       </c>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="12" t="n"/>
-      <c r="AA9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9" t="n">
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="AC9" s="12">
-        <f>AB9/$E$9</f>
-        <v/>
-      </c>
+      <c r="Z9" s="12">
+        <f>Y9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="9" t="n"/>
+      <c r="AC9" s="12" t="n"/>
       <c r="AD9" s="9" t="n">
         <v>0</v>
       </c>
@@ -7193,7 +7491,7 @@
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="9" t="n">
         <v>845</v>
@@ -7203,28 +7501,28 @@
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AL9" s="12">
         <f>AK9/$E$9</f>
         <v/>
       </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
-      <c r="AP9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="9" t="n">
+      <c r="AM9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
       <c r="AS9" s="9" t="n">
         <v>0</v>
       </c>
@@ -7235,33 +7533,40 @@
         <f>AT9/$E$9</f>
         <v/>
       </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
-      <c r="AY9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="9" t="n">
+      <c r="AV9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="12" t="n"/>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="BD9" s="12">
+        <f>BC9/$E$9</f>
+        <v/>
+      </c>
       <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n">
+      <c r="BF9" s="9" t="n"/>
+      <c r="BG9" s="12" t="n"/>
+      <c r="BH9" s="9" t="n"/>
+      <c r="BI9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BG9" s="12">
-        <f>BF9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n"/>
-      <c r="BJ9" s="12" t="n"/>
+      <c r="BJ9" s="12">
+        <f>BI9/$E$9</f>
+        <v/>
+      </c>
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
@@ -7280,6 +7585,9 @@
       <c r="BZ9" s="9" t="n"/>
       <c r="CA9" s="9" t="n"/>
       <c r="CB9" s="12" t="n"/>
+      <c r="CC9" s="9" t="n"/>
+      <c r="CD9" s="9" t="n"/>
+      <c r="CE9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -7304,10 +7612,10 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -7334,7 +7642,7 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>1418</v>
@@ -7344,118 +7652,125 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="12" t="n"/>
-      <c r="AA10" s="9" t="n">
+      <c r="X10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="Z10" s="12">
+        <f>Y10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="9" t="n"/>
+      <c r="AC10" s="12" t="n"/>
+      <c r="AD10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AB10" s="9" t="n">
+      <c r="AE10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="AC10" s="12">
-        <f>AB10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AD10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
-      <c r="AP10" s="9" t="n">
+      <c r="AM10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AQ10" s="9" t="n">
+      <c r="AT10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
-      <c r="AY10" s="9" t="n">
+      <c r="AV10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AZ10" s="9" t="n">
+      <c r="AW10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="BA10" s="12">
-        <f>AZ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BB10" s="9" t="n"/>
-      <c r="BC10" s="9" t="n"/>
-      <c r="BD10" s="12" t="n"/>
+      <c r="BD10" s="12">
+        <f>BC10/$E$10</f>
+        <v/>
+      </c>
       <c r="BE10" s="9" t="n"/>
-      <c r="BF10" s="9" t="n">
+      <c r="BF10" s="9" t="n"/>
+      <c r="BG10" s="12" t="n"/>
+      <c r="BH10" s="9" t="n"/>
+      <c r="BI10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="BG10" s="12">
-        <f>BF10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BH10" s="9" t="n"/>
-      <c r="BI10" s="9" t="n"/>
-      <c r="BJ10" s="12" t="n"/>
+      <c r="BJ10" s="12">
+        <f>BI10/$E$10</f>
+        <v/>
+      </c>
       <c r="BK10" s="9" t="n"/>
       <c r="BL10" s="9" t="n"/>
       <c r="BM10" s="12" t="n"/>
@@ -7474,6 +7789,9 @@
       <c r="BZ10" s="9" t="n"/>
       <c r="CA10" s="9" t="n"/>
       <c r="CB10" s="12" t="n"/>
+      <c r="CC10" s="9" t="n"/>
+      <c r="CD10" s="9" t="n"/>
+      <c r="CE10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -7498,20 +7816,20 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
@@ -7528,7 +7846,7 @@
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>992</v>
@@ -7538,10 +7856,10 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
@@ -7557,99 +7875,106 @@
         <f>V11/$E$11</f>
         <v/>
       </c>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="12" t="n"/>
-      <c r="AA11" s="9" t="n">
+      <c r="X11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="Z11" s="12">
+        <f>Y11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="12" t="n"/>
+      <c r="AD11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AB11" s="9" t="n">
+      <c r="AE11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="AC11" s="12">
-        <f>AB11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AD11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
         <v/>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AH11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="AI11" s="12">
         <f>AH11/$E$11</f>
         <v/>
       </c>
       <c r="AJ11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AL11" s="12">
         <f>AK11/$E$11</f>
         <v/>
       </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
-      <c r="AP11" s="9" t="n">
+      <c r="AM11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AP11" s="9" t="n"/>
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AQ11" s="9" t="n">
+      <c r="AT11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AR11" s="12">
-        <f>AQ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AU11" s="12">
         <f>AT11/$E$11</f>
         <v/>
       </c>
-      <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n"/>
-      <c r="AX11" s="12" t="n"/>
-      <c r="AY11" s="9" t="n">
+      <c r="AV11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AX11" s="12">
+        <f>AW11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="9" t="n"/>
+      <c r="AZ11" s="9" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AZ11" s="9" t="n">
+      <c r="BC11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="BA11" s="12">
-        <f>AZ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BB11" s="9" t="n"/>
-      <c r="BC11" s="9" t="n"/>
-      <c r="BD11" s="12" t="n"/>
+      <c r="BD11" s="12">
+        <f>BC11/$E$11</f>
+        <v/>
+      </c>
       <c r="BE11" s="9" t="n"/>
-      <c r="BF11" s="9" t="n">
+      <c r="BF11" s="9" t="n"/>
+      <c r="BG11" s="12" t="n"/>
+      <c r="BH11" s="9" t="n"/>
+      <c r="BI11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="BG11" s="12">
-        <f>BF11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BH11" s="9" t="n"/>
-      <c r="BI11" s="9" t="n"/>
-      <c r="BJ11" s="12" t="n"/>
+      <c r="BJ11" s="12">
+        <f>BI11/$E$11</f>
+        <v/>
+      </c>
       <c r="BK11" s="9" t="n"/>
       <c r="BL11" s="9" t="n"/>
       <c r="BM11" s="12" t="n"/>
@@ -7668,6 +7993,9 @@
       <c r="BZ11" s="9" t="n"/>
       <c r="CA11" s="9" t="n"/>
       <c r="CB11" s="12" t="n"/>
+      <c r="CC11" s="9" t="n"/>
+      <c r="CD11" s="9" t="n"/>
+      <c r="CE11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -7692,10 +8020,10 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
@@ -7722,7 +8050,7 @@
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>737</v>
@@ -7732,118 +8060,125 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="9" t="n"/>
-      <c r="Z12" s="12" t="n"/>
-      <c r="AA12" s="9" t="n">
+      <c r="X12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="Z12" s="12">
+        <f>Y12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="9" t="n"/>
+      <c r="AC12" s="12" t="n"/>
+      <c r="AD12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AB12" s="9" t="n">
+      <c r="AE12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="AC12" s="12">
-        <f>AB12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AD12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="AI12" s="12">
         <f>AH12/$E$12</f>
         <v/>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AL12" s="12">
         <f>AK12/$E$12</f>
         <v/>
       </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
-      <c r="AP12" s="9" t="n">
+      <c r="AM12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AP12" s="9" t="n"/>
+      <c r="AQ12" s="9" t="n"/>
+      <c r="AR12" s="12" t="n"/>
+      <c r="AS12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AQ12" s="9" t="n">
+      <c r="AT12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AR12" s="12">
-        <f>AQ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AS12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AU12" s="12">
         <f>AT12/$E$12</f>
         <v/>
       </c>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="12" t="n"/>
-      <c r="AY12" s="9" t="n">
+      <c r="AV12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="AX12" s="12">
+        <f>AW12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="12" t="n"/>
+      <c r="BB12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AZ12" s="9" t="n">
+      <c r="BC12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="BA12" s="12">
-        <f>AZ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BB12" s="9" t="n"/>
-      <c r="BC12" s="9" t="n"/>
-      <c r="BD12" s="12" t="n"/>
+      <c r="BD12" s="12">
+        <f>BC12/$E$12</f>
+        <v/>
+      </c>
       <c r="BE12" s="9" t="n"/>
-      <c r="BF12" s="9" t="n">
+      <c r="BF12" s="9" t="n"/>
+      <c r="BG12" s="12" t="n"/>
+      <c r="BH12" s="9" t="n"/>
+      <c r="BI12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="BG12" s="12">
-        <f>BF12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BH12" s="9" t="n"/>
-      <c r="BI12" s="9" t="n"/>
-      <c r="BJ12" s="12" t="n"/>
+      <c r="BJ12" s="12">
+        <f>BI12/$E$12</f>
+        <v/>
+      </c>
       <c r="BK12" s="9" t="n"/>
       <c r="BL12" s="9" t="n"/>
       <c r="BM12" s="12" t="n"/>
@@ -7862,6 +8197,9 @@
       <c r="BZ12" s="9" t="n"/>
       <c r="CA12" s="9" t="n"/>
       <c r="CB12" s="12" t="n"/>
+      <c r="CC12" s="9" t="n"/>
+      <c r="CD12" s="9" t="n"/>
+      <c r="CE12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -7886,20 +8224,20 @@
         <v>1623</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
@@ -7936,7 +8274,7 @@
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>1391</v>
@@ -7945,99 +8283,106 @@
         <f>V13/$E$13</f>
         <v/>
       </c>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="12" t="n"/>
-      <c r="AA13" s="9" t="n">
+      <c r="X13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AB13" s="9" t="n">
+      <c r="Y13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="Z13" s="12">
+        <f>Y13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="9" t="n"/>
+      <c r="AC13" s="12" t="n"/>
+      <c r="AD13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="AC13" s="12">
-        <f>AB13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AD13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
-      <c r="AP13" s="9" t="n">
+      <c r="AM13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AP13" s="9" t="n"/>
+      <c r="AQ13" s="9" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AQ13" s="9" t="n">
+      <c r="AT13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AR13" s="12">
-        <f>AQ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AS13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
-      <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n"/>
-      <c r="AX13" s="12" t="n"/>
-      <c r="AY13" s="9" t="n">
+      <c r="AV13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AX13" s="12">
+        <f>AW13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AZ13" s="9" t="n">
+      <c r="BC13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="BA13" s="12">
-        <f>AZ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BB13" s="9" t="n"/>
-      <c r="BC13" s="9" t="n"/>
-      <c r="BD13" s="12" t="n"/>
+      <c r="BD13" s="12">
+        <f>BC13/$E$13</f>
+        <v/>
+      </c>
       <c r="BE13" s="9" t="n"/>
-      <c r="BF13" s="9" t="n">
+      <c r="BF13" s="9" t="n"/>
+      <c r="BG13" s="12" t="n"/>
+      <c r="BH13" s="9" t="n"/>
+      <c r="BI13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="BG13" s="12">
-        <f>BF13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BH13" s="9" t="n"/>
-      <c r="BI13" s="9" t="n"/>
-      <c r="BJ13" s="12" t="n"/>
+      <c r="BJ13" s="12">
+        <f>BI13/$E$13</f>
+        <v/>
+      </c>
       <c r="BK13" s="9" t="n"/>
       <c r="BL13" s="9" t="n"/>
       <c r="BM13" s="12" t="n"/>
@@ -8056,6 +8401,9 @@
       <c r="BZ13" s="9" t="n"/>
       <c r="CA13" s="9" t="n"/>
       <c r="CB13" s="12" t="n"/>
+      <c r="CC13" s="9" t="n"/>
+      <c r="CD13" s="9" t="n"/>
+      <c r="CE13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -8080,7 +8428,7 @@
         <v>996</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>904</v>
@@ -8090,10 +8438,10 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
@@ -8130,7 +8478,7 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>902</v>
@@ -8139,21 +8487,21 @@
         <f>V14/$E$14</f>
         <v/>
       </c>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="9" t="n"/>
-      <c r="Z14" s="12" t="n"/>
-      <c r="AA14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="AC14" s="12">
-        <f>AB14/$E$14</f>
-        <v/>
-      </c>
+      <c r="X14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="Z14" s="12">
+        <f>Y14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="9" t="n"/>
+      <c r="AC14" s="12" t="n"/>
       <c r="AD14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="9" t="n">
         <v>898</v>
@@ -8163,75 +8511,82 @@
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
-      <c r="AP14" s="9" t="n">
+      <c r="AM14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AQ14" s="9" t="n">
+      <c r="AT14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AR14" s="12">
-        <f>AQ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AS14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
-      <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n"/>
-      <c r="AX14" s="12" t="n"/>
-      <c r="AY14" s="9" t="n">
+      <c r="AV14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AZ14" s="9" t="n">
+      <c r="AW14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AX14" s="12">
+        <f>AW14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="9" t="n"/>
+      <c r="AZ14" s="9" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="BA14" s="12">
-        <f>AZ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BB14" s="9" t="n"/>
-      <c r="BC14" s="9" t="n"/>
-      <c r="BD14" s="12" t="n"/>
+      <c r="BD14" s="12">
+        <f>BC14/$E$14</f>
+        <v/>
+      </c>
       <c r="BE14" s="9" t="n"/>
-      <c r="BF14" s="9" t="n">
+      <c r="BF14" s="9" t="n"/>
+      <c r="BG14" s="12" t="n"/>
+      <c r="BH14" s="9" t="n"/>
+      <c r="BI14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="BG14" s="12">
-        <f>BF14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BH14" s="9" t="n"/>
-      <c r="BI14" s="9" t="n"/>
-      <c r="BJ14" s="12" t="n"/>
+      <c r="BJ14" s="12">
+        <f>BI14/$E$14</f>
+        <v/>
+      </c>
       <c r="BK14" s="9" t="n"/>
       <c r="BL14" s="9" t="n"/>
       <c r="BM14" s="12" t="n"/>
@@ -8250,6 +8605,9 @@
       <c r="BZ14" s="9" t="n"/>
       <c r="CA14" s="9" t="n"/>
       <c r="CB14" s="12" t="n"/>
+      <c r="CC14" s="9" t="n"/>
+      <c r="CD14" s="9" t="n"/>
+      <c r="CE14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -8348,6 +8706,9 @@
       <c r="BZ15" s="9" t="n"/>
       <c r="CA15" s="9" t="n"/>
       <c r="CB15" s="12" t="n"/>
+      <c r="CC15" s="9" t="n"/>
+      <c r="CD15" s="9" t="n"/>
+      <c r="CE15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -8372,7 +8733,7 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>717</v>
@@ -8382,10 +8743,10 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="K16" s="12">
         <f>J16/$E$16</f>
@@ -8402,7 +8763,7 @@
         <v/>
       </c>
       <c r="O16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>715</v>
@@ -8412,118 +8773,125 @@
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="T16" s="12">
         <f>S16/$E$16</f>
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
         <v/>
       </c>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="12" t="n"/>
-      <c r="AA16" s="9" t="n">
+      <c r="X16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="Z16" s="12">
+        <f>Y16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="12" t="n"/>
+      <c r="AD16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AB16" s="9" t="n">
+      <c r="AE16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="AC16" s="12">
-        <f>AB16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AD16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AH16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AI16" s="12">
         <f>AH16/$E$16</f>
         <v/>
       </c>
       <c r="AJ16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AL16" s="12">
         <f>AK16/$E$16</f>
         <v/>
       </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
-      <c r="AP16" s="9" t="n">
+      <c r="AM16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AQ16" s="9" t="n">
+      <c r="AT16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AS16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AU16" s="12">
         <f>AT16/$E$16</f>
         <v/>
       </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
-      <c r="AY16" s="9" t="n">
+      <c r="AV16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AZ16" s="9" t="n">
+      <c r="BC16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="BA16" s="12">
-        <f>AZ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BB16" s="9" t="n"/>
-      <c r="BC16" s="9" t="n"/>
-      <c r="BD16" s="12" t="n"/>
+      <c r="BD16" s="12">
+        <f>BC16/$E$16</f>
+        <v/>
+      </c>
       <c r="BE16" s="9" t="n"/>
-      <c r="BF16" s="9" t="n">
+      <c r="BF16" s="9" t="n"/>
+      <c r="BG16" s="12" t="n"/>
+      <c r="BH16" s="9" t="n"/>
+      <c r="BI16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="BG16" s="12">
-        <f>BF16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BH16" s="9" t="n"/>
-      <c r="BI16" s="9" t="n"/>
-      <c r="BJ16" s="12" t="n"/>
+      <c r="BJ16" s="12">
+        <f>BI16/$E$16</f>
+        <v/>
+      </c>
       <c r="BK16" s="9" t="n"/>
       <c r="BL16" s="9" t="n"/>
       <c r="BM16" s="12" t="n"/>
@@ -8542,6 +8910,9 @@
       <c r="BZ16" s="9" t="n"/>
       <c r="CA16" s="9" t="n"/>
       <c r="CB16" s="12" t="n"/>
+      <c r="CC16" s="9" t="n"/>
+      <c r="CD16" s="9" t="n"/>
+      <c r="CE16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -8566,7 +8937,7 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>388</v>
@@ -8576,20 +8947,20 @@
         <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K17" s="12">
         <f>J17/$E$17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N17" s="12">
         <f>M17/$E$17</f>
@@ -8606,7 +8977,7 @@
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
         <v>385</v>
@@ -8616,108 +8987,115 @@
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
         <v/>
       </c>
-      <c r="X17" s="9" t="n"/>
-      <c r="Y17" s="9" t="n"/>
-      <c r="Z17" s="12" t="n"/>
-      <c r="AA17" s="9" t="n">
+      <c r="X17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AB17" s="9" t="n">
+      <c r="Y17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="Z17" s="12">
+        <f>Y17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="12" t="n"/>
+      <c r="AD17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="AC17" s="12">
-        <f>AB17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AD17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="AF17" s="12">
         <f>AE17/$E$17</f>
         <v/>
       </c>
       <c r="AG17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AH17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AI17" s="12">
         <f>AH17/$E$17</f>
         <v/>
       </c>
       <c r="AJ17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AL17" s="12">
         <f>AK17/$E$17</f>
         <v/>
       </c>
-      <c r="AM17" s="9" t="n"/>
-      <c r="AN17" s="9" t="n"/>
-      <c r="AO17" s="12" t="n"/>
-      <c r="AP17" s="9" t="n">
+      <c r="AM17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AO17" s="12">
+        <f>AN17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AP17" s="9" t="n"/>
+      <c r="AQ17" s="9" t="n"/>
+      <c r="AR17" s="12" t="n"/>
+      <c r="AS17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AQ17" s="9" t="n">
+      <c r="AT17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AR17" s="12">
-        <f>AQ17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AS17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AU17" s="12">
         <f>AT17/$E$17</f>
         <v/>
       </c>
-      <c r="AV17" s="9" t="n"/>
-      <c r="AW17" s="9" t="n"/>
-      <c r="AX17" s="12" t="n"/>
-      <c r="AY17" s="9" t="n">
+      <c r="AV17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="AX17" s="12">
+        <f>AW17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AY17" s="9" t="n"/>
+      <c r="AZ17" s="9" t="n"/>
+      <c r="BA17" s="12" t="n"/>
+      <c r="BB17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AZ17" s="9" t="n">
+      <c r="BC17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="BA17" s="12">
-        <f>AZ17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BB17" s="9" t="n"/>
-      <c r="BC17" s="9" t="n"/>
-      <c r="BD17" s="12" t="n"/>
+      <c r="BD17" s="12">
+        <f>BC17/$E$17</f>
+        <v/>
+      </c>
       <c r="BE17" s="9" t="n"/>
-      <c r="BF17" s="9" t="n">
+      <c r="BF17" s="9" t="n"/>
+      <c r="BG17" s="12" t="n"/>
+      <c r="BH17" s="9" t="n"/>
+      <c r="BI17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="BG17" s="12">
-        <f>BF17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BH17" s="9" t="n"/>
-      <c r="BI17" s="9" t="n"/>
-      <c r="BJ17" s="12" t="n"/>
+      <c r="BJ17" s="12">
+        <f>BI17/$E$17</f>
+        <v/>
+      </c>
       <c r="BK17" s="9" t="n"/>
       <c r="BL17" s="9" t="n"/>
       <c r="BM17" s="12" t="n"/>
@@ -8736,6 +9114,9 @@
       <c r="BZ17" s="9" t="n"/>
       <c r="CA17" s="9" t="n"/>
       <c r="CB17" s="12" t="n"/>
+      <c r="CC17" s="9" t="n"/>
+      <c r="CD17" s="9" t="n"/>
+      <c r="CE17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -8790,7 +9171,7 @@
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>292</v>
@@ -8800,118 +9181,125 @@
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
-      <c r="X18" s="9" t="n"/>
-      <c r="Y18" s="9" t="n"/>
-      <c r="Z18" s="12" t="n"/>
-      <c r="AA18" s="9" t="n">
+      <c r="X18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="Z18" s="12">
+        <f>Y18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="9" t="n"/>
+      <c r="AC18" s="12" t="n"/>
+      <c r="AD18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AB18" s="9" t="n">
+      <c r="AE18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="AC18" s="12">
-        <f>AB18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AD18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
       <c r="AG18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AI18" s="12">
         <f>AH18/$E$18</f>
         <v/>
       </c>
       <c r="AJ18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AL18" s="12">
         <f>AK18/$E$18</f>
         <v/>
       </c>
-      <c r="AM18" s="9" t="n"/>
-      <c r="AN18" s="9" t="n"/>
-      <c r="AO18" s="12" t="n"/>
-      <c r="AP18" s="9" t="n">
+      <c r="AM18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AO18" s="12">
+        <f>AN18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AP18" s="9" t="n"/>
+      <c r="AQ18" s="9" t="n"/>
+      <c r="AR18" s="12" t="n"/>
+      <c r="AS18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AQ18" s="9" t="n">
+      <c r="AT18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AR18" s="12">
-        <f>AQ18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AS18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AU18" s="12">
         <f>AT18/$E$18</f>
         <v/>
       </c>
-      <c r="AV18" s="9" t="n"/>
-      <c r="AW18" s="9" t="n"/>
-      <c r="AX18" s="12" t="n"/>
-      <c r="AY18" s="9" t="n">
+      <c r="AV18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="AX18" s="12">
+        <f>AW18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AY18" s="9" t="n"/>
+      <c r="AZ18" s="9" t="n"/>
+      <c r="BA18" s="12" t="n"/>
+      <c r="BB18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AZ18" s="9" t="n">
+      <c r="BC18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="BA18" s="12">
-        <f>AZ18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BB18" s="9" t="n"/>
-      <c r="BC18" s="9" t="n"/>
-      <c r="BD18" s="12" t="n"/>
+      <c r="BD18" s="12">
+        <f>BC18/$E$18</f>
+        <v/>
+      </c>
       <c r="BE18" s="9" t="n"/>
-      <c r="BF18" s="9" t="n">
+      <c r="BF18" s="9" t="n"/>
+      <c r="BG18" s="12" t="n"/>
+      <c r="BH18" s="9" t="n"/>
+      <c r="BI18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="BG18" s="12">
-        <f>BF18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BH18" s="9" t="n"/>
-      <c r="BI18" s="9" t="n"/>
-      <c r="BJ18" s="12" t="n"/>
+      <c r="BJ18" s="12">
+        <f>BI18/$E$18</f>
+        <v/>
+      </c>
       <c r="BK18" s="9" t="n"/>
       <c r="BL18" s="9" t="n"/>
       <c r="BM18" s="12" t="n"/>
@@ -8930,9 +9318,12 @@
       <c r="BZ18" s="9" t="n"/>
       <c r="CA18" s="9" t="n"/>
       <c r="CB18" s="12" t="n"/>
+      <c r="CC18" s="9" t="n"/>
+      <c r="CD18" s="9" t="n"/>
+      <c r="CE18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -8948,6 +9339,7 @@
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="CC3:CE3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="BE3:BG3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 18/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 19/08/2026</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 18/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 19/08/2026</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 18/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 19/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -573,6 +573,9 @@
     <col width="9" customWidth="1" min="81" max="81"/>
     <col width="9" customWidth="1" min="82" max="82"/>
     <col width="9" customWidth="1" min="83" max="83"/>
+    <col width="9" customWidth="1" min="84" max="84"/>
+    <col width="9" customWidth="1" min="85" max="85"/>
+    <col width="9" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,81 +594,84 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1083,6 +1089,21 @@
         </is>
       </c>
       <c r="CE4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CF4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CG4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CH4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1161,7 +1182,7 @@
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>43</v>
@@ -1171,17 +1192,17 @@
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="9" t="n">
         <v>42</v>
@@ -1194,49 +1215,56 @@
         <v>1</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
-      <c r="AM5" s="9" t="n">
+      <c r="AJ5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
+      <c r="AP5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AN5" s="9" t="n">
+      <c r="AQ5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AO5" s="12">
-        <f>AN5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="12" t="n"/>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
       <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n">
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AU5" s="12">
-        <f>AT5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n"/>
-      <c r="AX5" s="12" t="n"/>
+      <c r="AX5" s="12">
+        <f>AW5/$E$5</f>
+        <v/>
+      </c>
       <c r="AY5" s="9" t="n"/>
       <c r="AZ5" s="9" t="n"/>
       <c r="BA5" s="12" t="n"/>
@@ -1270,6 +1298,9 @@
       <c r="CC5" s="9" t="n"/>
       <c r="CD5" s="9" t="n"/>
       <c r="CE5" s="12" t="n"/>
+      <c r="CF5" s="9" t="n"/>
+      <c r="CG5" s="9" t="n"/>
+      <c r="CH5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1294,17 +1325,17 @@
         <v>154</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>34</v>
@@ -1314,10 +1345,10 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
@@ -1393,33 +1424,40 @@
         <f>AH6/$E$6</f>
         <v/>
       </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AJ6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
       <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n">
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
       <c r="AY6" s="9" t="n"/>
       <c r="AZ6" s="9" t="n"/>
       <c r="BA6" s="12" t="n"/>
@@ -1453,6 +1491,9 @@
       <c r="CC6" s="9" t="n"/>
       <c r="CD6" s="9" t="n"/>
       <c r="CE6" s="12" t="n"/>
+      <c r="CF6" s="9" t="n"/>
+      <c r="CG6" s="9" t="n"/>
+      <c r="CH6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1480,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -1490,17 +1531,17 @@
         <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
@@ -1537,7 +1578,7 @@
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>45</v>
@@ -1547,62 +1588,69 @@
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AJ7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
       <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n">
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
       <c r="AY7" s="9" t="n"/>
       <c r="AZ7" s="9" t="n"/>
       <c r="BA7" s="12" t="n"/>
@@ -1636,6 +1684,9 @@
       <c r="CC7" s="9" t="n"/>
       <c r="CD7" s="9" t="n"/>
       <c r="CE7" s="12" t="n"/>
+      <c r="CF7" s="9" t="n"/>
+      <c r="CG7" s="9" t="n"/>
+      <c r="CH7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1759,33 +1810,40 @@
         <f>AH8/$E$8</f>
         <v/>
       </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AJ8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
       <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n">
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
       <c r="AY8" s="9" t="n"/>
       <c r="AZ8" s="9" t="n"/>
       <c r="BA8" s="12" t="n"/>
@@ -1819,6 +1877,9 @@
       <c r="CC8" s="9" t="n"/>
       <c r="CD8" s="9" t="n"/>
       <c r="CE8" s="12" t="n"/>
+      <c r="CF8" s="9" t="n"/>
+      <c r="CG8" s="9" t="n"/>
+      <c r="CH8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1933,7 +1994,7 @@
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="9" t="n">
         <v>1</v>
@@ -1942,33 +2003,40 @@
         <f>AH9/$E$9</f>
         <v/>
       </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
+      <c r="AJ9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
       <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
       <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
+      <c r="AW9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
       <c r="AY9" s="9" t="n"/>
       <c r="AZ9" s="9" t="n"/>
       <c r="BA9" s="12" t="n"/>
@@ -2002,6 +2070,9 @@
       <c r="CC9" s="9" t="n"/>
       <c r="CD9" s="9" t="n"/>
       <c r="CE9" s="12" t="n"/>
+      <c r="CF9" s="9" t="n"/>
+      <c r="CG9" s="9" t="n"/>
+      <c r="CH9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2026,47 +2097,47 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>311</v>
@@ -2076,69 +2147,76 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
       <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n">
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
       <c r="AS10" s="9" t="n"/>
       <c r="AT10" s="9" t="n"/>
       <c r="AU10" s="12" t="n"/>
@@ -2178,9 +2256,12 @@
       <c r="CC10" s="9" t="n"/>
       <c r="CD10" s="9" t="n"/>
       <c r="CE10" s="12" t="n"/>
+      <c r="CF10" s="9" t="n"/>
+      <c r="CG10" s="9" t="n"/>
+      <c r="CH10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -2189,6 +2270,7 @@
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="CF3:CH3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="BW3:BY3"/>
@@ -2218,7 +2300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE18"/>
+  <dimension ref="A1:CH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2304,6 +2386,9 @@
     <col width="9" customWidth="1" min="81" max="81"/>
     <col width="9" customWidth="1" min="82" max="82"/>
     <col width="9" customWidth="1" min="83" max="83"/>
+    <col width="9" customWidth="1" min="84" max="84"/>
+    <col width="9" customWidth="1" min="85" max="85"/>
+    <col width="9" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2322,81 +2407,84 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2814,6 +2902,21 @@
         </is>
       </c>
       <c r="CE4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CF4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CG4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CH4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2842,17 +2945,17 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>178</v>
@@ -2862,10 +2965,10 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
@@ -2892,7 +2995,7 @@
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>177</v>
@@ -2901,17 +3004,24 @@
         <f>V5/$E$5</f>
         <v/>
       </c>
-      <c r="X5" s="9" t="n"/>
+      <c r="X5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="Y5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
       <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="12" t="n"/>
+      <c r="AB5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
       <c r="AD5" s="9" t="n"/>
       <c r="AE5" s="9" t="n"/>
       <c r="AF5" s="12" t="n"/>
@@ -2966,6 +3076,9 @@
       <c r="CC5" s="9" t="n"/>
       <c r="CD5" s="9" t="n"/>
       <c r="CE5" s="12" t="n"/>
+      <c r="CF5" s="9" t="n"/>
+      <c r="CG5" s="9" t="n"/>
+      <c r="CH5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2990,30 +3103,30 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
@@ -3030,7 +3143,7 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
         <v>335</v>
@@ -3040,183 +3153,193 @@
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
-      <c r="AP6" s="9" t="n">
+      <c r="AM6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AQ6" s="9" t="n">
+      <c r="AT6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
       <c r="AV6" s="9" t="n"/>
       <c r="AW6" s="9" t="n"/>
       <c r="AX6" s="12" t="n"/>
-      <c r="AY6" s="9" t="n">
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AZ6" s="9" t="n">
+      <c r="BC6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="12" t="n"/>
-      <c r="BE6" s="9" t="n">
+      <c r="BD6" s="12">
+        <f>BC6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BE6" s="9" t="n"/>
+      <c r="BF6" s="9" t="n"/>
+      <c r="BG6" s="12" t="n"/>
+      <c r="BH6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BF6" s="9" t="n">
+      <c r="BI6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="BG6" s="12">
-        <f>BF6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BH6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BI6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BJ6" s="12">
         <f>BI6/$E$6</f>
         <v/>
       </c>
       <c r="BK6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BL6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
         <v/>
       </c>
       <c r="BN6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BO6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
         <v/>
       </c>
       <c r="BQ6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BR6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
         <v/>
       </c>
       <c r="BT6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BU6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
         <v/>
       </c>
       <c r="BW6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="BY6" s="12">
         <f>BX6/$E$6</f>
         <v/>
       </c>
       <c r="BZ6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CA6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="CB6" s="12">
         <f>CA6/$E$6</f>
         <v/>
       </c>
-      <c r="CC6" s="9" t="n"/>
+      <c r="CC6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="CD6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="CE6" s="12">
         <f>CD6/$E$6</f>
+        <v/>
+      </c>
+      <c r="CF6" s="9" t="n"/>
+      <c r="CG6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="CH6" s="12">
+        <f>CG6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -3263,7 +3386,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>120</v>
@@ -3273,10 +3396,10 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
@@ -3293,7 +3416,7 @@
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>119</v>
@@ -3306,109 +3429,109 @@
         <v>3</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
-      <c r="AP7" s="9" t="n">
+      <c r="AM7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AQ7" s="9" t="n">
+      <c r="AT7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
       <c r="AV7" s="9" t="n"/>
       <c r="AW7" s="9" t="n"/>
       <c r="AX7" s="12" t="n"/>
-      <c r="AY7" s="9" t="n">
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AZ7" s="9" t="n">
+      <c r="BC7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="12" t="n"/>
-      <c r="BE7" s="9" t="n">
+      <c r="BD7" s="12">
+        <f>BC7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BE7" s="9" t="n"/>
+      <c r="BF7" s="9" t="n"/>
+      <c r="BG7" s="12" t="n"/>
+      <c r="BH7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BF7" s="9" t="n">
+      <c r="BI7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="BG7" s="12">
-        <f>BF7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BH7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BJ7" s="12">
         <f>BI7/$E$7</f>
         <v/>
       </c>
       <c r="BK7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BL7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
@@ -3418,58 +3541,68 @@
         <v>6</v>
       </c>
       <c r="BO7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
         <v/>
       </c>
       <c r="BQ7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BR7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
         <v/>
       </c>
       <c r="BT7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
         <v/>
       </c>
       <c r="BW7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BX7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="BY7" s="12">
         <f>BX7/$E$7</f>
         <v/>
       </c>
       <c r="BZ7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CA7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CB7" s="12">
         <f>CA7/$E$7</f>
         <v/>
       </c>
-      <c r="CC7" s="9" t="n"/>
+      <c r="CC7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="CD7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CE7" s="12">
         <f>CD7/$E$7</f>
+        <v/>
+      </c>
+      <c r="CF7" s="9" t="n"/>
+      <c r="CG7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CH7" s="12">
+        <f>CG7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3629,7 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1000</v>
@@ -3506,10 +3639,10 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
@@ -3536,7 +3669,7 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>998</v>
@@ -3546,112 +3679,112 @@
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
-      <c r="AP8" s="9" t="n">
+      <c r="AM8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AQ8" s="9" t="n">
+      <c r="AT8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
       <c r="AV8" s="9" t="n"/>
       <c r="AW8" s="9" t="n"/>
       <c r="AX8" s="12" t="n"/>
-      <c r="AY8" s="9" t="n">
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AZ8" s="9" t="n">
+      <c r="BC8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="12" t="n"/>
-      <c r="BE8" s="9" t="n">
+      <c r="BD8" s="12">
+        <f>BC8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BE8" s="9" t="n"/>
+      <c r="BF8" s="9" t="n"/>
+      <c r="BG8" s="12" t="n"/>
+      <c r="BH8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BF8" s="9" t="n">
+      <c r="BI8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="BG8" s="12">
-        <f>BF8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BH8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BJ8" s="12">
         <f>BI8/$E$8</f>
@@ -3661,68 +3794,78 @@
         <v>7</v>
       </c>
       <c r="BL8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
         <v/>
       </c>
       <c r="BN8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BO8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
         <v/>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BR8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
         <v/>
       </c>
       <c r="BT8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
         <v/>
       </c>
       <c r="BW8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BX8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="BY8" s="12">
         <f>BX8/$E$8</f>
         <v/>
       </c>
       <c r="BZ8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CA8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="CB8" s="12">
         <f>CA8/$E$8</f>
         <v/>
       </c>
-      <c r="CC8" s="9" t="n"/>
+      <c r="CC8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="CD8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="CE8" s="12">
         <f>CD8/$E$8</f>
+        <v/>
+      </c>
+      <c r="CF8" s="9" t="n"/>
+      <c r="CG8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="CH8" s="12">
+        <f>CG8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3799,7 +3942,7 @@
         <v/>
       </c>
       <c r="U9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
         <v>1125</v>
@@ -3809,27 +3952,27 @@
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="Z9" s="12">
         <f>Y9/$E$9</f>
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="AC9" s="12">
         <f>AB9/$E$9</f>
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="9" t="n">
         <v>1119</v>
@@ -3839,17 +3982,17 @@
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AI9" s="12">
         <f>AH9/$E$9</f>
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="9" t="n">
         <v>1117</v>
@@ -3858,124 +4001,134 @@
         <f>AK9/$E$9</f>
         <v/>
       </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
-      <c r="AP9" s="9" t="n">
+      <c r="AM9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AQ9" s="9" t="n">
+      <c r="AT9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
       <c r="AV9" s="9" t="n"/>
       <c r="AW9" s="9" t="n"/>
       <c r="AX9" s="12" t="n"/>
-      <c r="AY9" s="9" t="n">
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AZ9" s="9" t="n">
+      <c r="BC9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="12" t="n"/>
-      <c r="BE9" s="9" t="n">
+      <c r="BD9" s="12">
+        <f>BC9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BE9" s="9" t="n"/>
+      <c r="BF9" s="9" t="n"/>
+      <c r="BG9" s="12" t="n"/>
+      <c r="BH9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BF9" s="9" t="n">
+      <c r="BI9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="BG9" s="12">
-        <f>BF9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BH9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BJ9" s="12">
         <f>BI9/$E$9</f>
         <v/>
       </c>
       <c r="BK9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
         <v/>
       </c>
       <c r="BN9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
         <v/>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BR9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
         <v/>
       </c>
       <c r="BT9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
         <v/>
       </c>
       <c r="BW9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="BX9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="BY9" s="12">
         <f>BX9/$E$9</f>
         <v/>
       </c>
       <c r="BZ9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="CA9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="CB9" s="12">
         <f>CA9/$E$9</f>
         <v/>
       </c>
-      <c r="CC9" s="9" t="n"/>
+      <c r="CC9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="CD9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="CE9" s="12">
         <f>CD9/$E$9</f>
+        <v/>
+      </c>
+      <c r="CF9" s="9" t="n"/>
+      <c r="CG9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CH9" s="12">
+        <f>CG9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -4002,17 +4155,17 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>504</v>
@@ -4022,10 +4175,10 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
@@ -4042,7 +4195,7 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>502</v>
@@ -4052,37 +4205,37 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="9" t="n">
         <v>491</v>
@@ -4092,79 +4245,79 @@
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
-      <c r="AP10" s="9" t="n">
+      <c r="AM10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AP10" s="9" t="n"/>
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AQ10" s="9" t="n">
+      <c r="AT10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
       <c r="AV10" s="9" t="n"/>
       <c r="AW10" s="9" t="n"/>
       <c r="AX10" s="12" t="n"/>
-      <c r="AY10" s="9" t="n">
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AZ10" s="9" t="n">
+      <c r="BC10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BA10" s="12">
-        <f>AZ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BB10" s="9" t="n"/>
-      <c r="BC10" s="9" t="n"/>
-      <c r="BD10" s="12" t="n"/>
-      <c r="BE10" s="9" t="n">
+      <c r="BD10" s="12">
+        <f>BC10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BE10" s="9" t="n"/>
+      <c r="BF10" s="9" t="n"/>
+      <c r="BG10" s="12" t="n"/>
+      <c r="BH10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BF10" s="9" t="n">
+      <c r="BI10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="BG10" s="12">
-        <f>BF10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BH10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BJ10" s="12">
         <f>BI10/$E$10</f>
         <v/>
       </c>
       <c r="BK10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL10" s="9" t="n">
         <v>462</v>
@@ -4177,58 +4330,68 @@
         <v>2</v>
       </c>
       <c r="BO10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BP10" s="12">
         <f>BO10/$E$10</f>
         <v/>
       </c>
       <c r="BQ10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BS10" s="12">
         <f>BR10/$E$10</f>
         <v/>
       </c>
       <c r="BT10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BU10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BV10" s="12">
         <f>BU10/$E$10</f>
         <v/>
       </c>
       <c r="BW10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="BX10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="BY10" s="12">
         <f>BX10/$E$10</f>
         <v/>
       </c>
       <c r="BZ10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="CA10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="CB10" s="12">
         <f>CA10/$E$10</f>
         <v/>
       </c>
-      <c r="CC10" s="9" t="n"/>
+      <c r="CC10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="CD10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="CE10" s="12">
         <f>CD10/$E$10</f>
+        <v/>
+      </c>
+      <c r="CF10" s="9" t="n"/>
+      <c r="CG10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="CH10" s="12">
+        <f>CG10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -4315,7 +4478,7 @@
         <v/>
       </c>
       <c r="X11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>467</v>
@@ -4328,17 +4491,17 @@
         <v>1</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AC11" s="12">
         <f>AB11/$E$11</f>
         <v/>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
@@ -4364,60 +4527,60 @@
         <f>AK11/$E$11</f>
         <v/>
       </c>
-      <c r="AM11" s="9" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="12" t="n"/>
-      <c r="AP11" s="9" t="n">
+      <c r="AM11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AO11" s="12">
+        <f>AN11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AP11" s="9" t="n"/>
+      <c r="AQ11" s="9" t="n"/>
+      <c r="AR11" s="12" t="n"/>
+      <c r="AS11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ11" s="9" t="n">
+      <c r="AT11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AR11" s="12">
-        <f>AQ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
       <c r="AV11" s="9" t="n"/>
       <c r="AW11" s="9" t="n"/>
       <c r="AX11" s="12" t="n"/>
-      <c r="AY11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="9" t="n">
+      <c r="AY11" s="9" t="n"/>
+      <c r="AZ11" s="9" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BA11" s="12">
-        <f>AZ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BB11" s="9" t="n"/>
-      <c r="BC11" s="9" t="n"/>
-      <c r="BD11" s="12" t="n"/>
-      <c r="BE11" s="9" t="n">
+      <c r="BD11" s="12">
+        <f>BC11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BE11" s="9" t="n"/>
+      <c r="BF11" s="9" t="n"/>
+      <c r="BG11" s="12" t="n"/>
+      <c r="BH11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BF11" s="9" t="n">
+      <c r="BI11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="BG11" s="12">
-        <f>BF11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BH11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BJ11" s="12">
         <f>BI11/$E$11</f>
         <v/>
       </c>
       <c r="BK11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL11" s="9" t="n">
         <v>463</v>
@@ -4427,40 +4590,40 @@
         <v/>
       </c>
       <c r="BN11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BO11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BP11" s="12">
         <f>BO11/$E$11</f>
         <v/>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BS11" s="12">
         <f>BR11/$E$11</f>
         <v/>
       </c>
       <c r="BT11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BV11" s="12">
         <f>BU11/$E$11</f>
         <v/>
       </c>
       <c r="BW11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BX11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BY11" s="12">
         <f>BX11/$E$11</f>
@@ -4470,18 +4633,28 @@
         <v>2</v>
       </c>
       <c r="CA11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CB11" s="12">
         <f>CA11/$E$11</f>
         <v/>
       </c>
-      <c r="CC11" s="9" t="n"/>
+      <c r="CC11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="CD11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CE11" s="12">
         <f>CD11/$E$11</f>
+        <v/>
+      </c>
+      <c r="CF11" s="9" t="n"/>
+      <c r="CG11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="CH11" s="12">
+        <f>CG11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -4568,7 +4741,7 @@
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>236</v>
@@ -4578,17 +4751,17 @@
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AC12" s="12">
         <f>AB12/$E$12</f>
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="9" t="n">
         <v>235</v>
@@ -4598,10 +4771,10 @@
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AI12" s="12">
         <f>AH12/$E$12</f>
@@ -4617,48 +4790,48 @@
         <f>AK12/$E$12</f>
         <v/>
       </c>
-      <c r="AM12" s="9" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="12" t="n"/>
-      <c r="AP12" s="9" t="n">
+      <c r="AM12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AO12" s="12">
+        <f>AN12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AP12" s="9" t="n"/>
+      <c r="AQ12" s="9" t="n"/>
+      <c r="AR12" s="12" t="n"/>
+      <c r="AS12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AQ12" s="9" t="n">
+      <c r="AT12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AR12" s="12">
-        <f>AQ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
       <c r="AV12" s="9" t="n"/>
       <c r="AW12" s="9" t="n"/>
       <c r="AX12" s="12" t="n"/>
-      <c r="AY12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="9" t="n">
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="12" t="n"/>
+      <c r="BB12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="BA12" s="12">
-        <f>AZ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BB12" s="9" t="n"/>
-      <c r="BC12" s="9" t="n"/>
-      <c r="BD12" s="12" t="n"/>
-      <c r="BE12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="BG12" s="12">
-        <f>BF12/$E$12</f>
-        <v/>
-      </c>
+      <c r="BD12" s="12">
+        <f>BC12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BE12" s="9" t="n"/>
+      <c r="BF12" s="9" t="n"/>
+      <c r="BG12" s="12" t="n"/>
       <c r="BH12" s="9" t="n">
         <v>0</v>
       </c>
@@ -4700,7 +4873,7 @@
         <v/>
       </c>
       <c r="BT12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU12" s="9" t="n">
         <v>236</v>
@@ -4710,31 +4883,41 @@
         <v/>
       </c>
       <c r="BW12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="BX12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BY12" s="12">
         <f>BX12/$E$12</f>
         <v/>
       </c>
       <c r="BZ12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="CA12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="CB12" s="12">
         <f>CA12/$E$12</f>
         <v/>
       </c>
-      <c r="CC12" s="9" t="n"/>
+      <c r="CC12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="CD12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="CE12" s="12">
         <f>CD12/$E$12</f>
+        <v/>
+      </c>
+      <c r="CF12" s="9" t="n"/>
+      <c r="CG12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="CH12" s="12">
+        <f>CG12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -4761,17 +4944,17 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>622</v>
@@ -4781,10 +4964,10 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
@@ -4801,7 +4984,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
         <v>621</v>
@@ -4811,142 +4994,142 @@
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
-      <c r="AM13" s="9" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="12" t="n"/>
-      <c r="AP13" s="9" t="n">
+      <c r="AM13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AO13" s="12">
+        <f>AN13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AP13" s="9" t="n"/>
+      <c r="AQ13" s="9" t="n"/>
+      <c r="AR13" s="12" t="n"/>
+      <c r="AS13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AQ13" s="9" t="n">
+      <c r="AT13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AR13" s="12">
-        <f>AQ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
       <c r="AV13" s="9" t="n"/>
       <c r="AW13" s="9" t="n"/>
       <c r="AX13" s="12" t="n"/>
-      <c r="AY13" s="9" t="n">
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AZ13" s="9" t="n">
+      <c r="BC13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="BA13" s="12">
-        <f>AZ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BB13" s="9" t="n"/>
-      <c r="BC13" s="9" t="n"/>
-      <c r="BD13" s="12" t="n"/>
-      <c r="BE13" s="9" t="n">
+      <c r="BD13" s="12">
+        <f>BC13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BE13" s="9" t="n"/>
+      <c r="BF13" s="9" t="n"/>
+      <c r="BG13" s="12" t="n"/>
+      <c r="BH13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="BF13" s="9" t="n">
+      <c r="BI13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="BG13" s="12">
-        <f>BF13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BH13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BJ13" s="12">
         <f>BI13/$E$13</f>
         <v/>
       </c>
       <c r="BK13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BL13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
         <v/>
       </c>
       <c r="BN13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BO13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
         <v/>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BR13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
@@ -4956,38 +5139,48 @@
         <v>4</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
         <v/>
       </c>
       <c r="BW13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="BX13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BY13" s="12">
         <f>BX13/$E$13</f>
         <v/>
       </c>
       <c r="BZ13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="CA13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="CB13" s="12">
         <f>CA13/$E$13</f>
         <v/>
       </c>
-      <c r="CC13" s="9" t="n"/>
+      <c r="CC13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="CD13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="CE13" s="12">
         <f>CD13/$E$13</f>
+        <v/>
+      </c>
+      <c r="CF13" s="9" t="n"/>
+      <c r="CG13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="CH13" s="12">
+        <f>CG13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -5014,17 +5207,17 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>1146</v>
@@ -5034,10 +5227,10 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
@@ -5054,7 +5247,7 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>1145</v>
@@ -5064,17 +5257,17 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>1142</v>
@@ -5084,122 +5277,122 @@
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="AC14" s="12">
         <f>AB14/$E$14</f>
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
-      <c r="AM14" s="9" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="12" t="n"/>
-      <c r="AP14" s="9" t="n">
+      <c r="AM14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AO14" s="12">
+        <f>AN14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="12" t="n"/>
+      <c r="AS14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AQ14" s="9" t="n">
+      <c r="AT14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AR14" s="12">
-        <f>AQ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
       <c r="AV14" s="9" t="n"/>
       <c r="AW14" s="9" t="n"/>
       <c r="AX14" s="12" t="n"/>
-      <c r="AY14" s="9" t="n">
+      <c r="AY14" s="9" t="n"/>
+      <c r="AZ14" s="9" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AZ14" s="9" t="n">
+      <c r="BC14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="BA14" s="12">
-        <f>AZ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BB14" s="9" t="n"/>
-      <c r="BC14" s="9" t="n"/>
-      <c r="BD14" s="12" t="n"/>
-      <c r="BE14" s="9" t="n">
+      <c r="BD14" s="12">
+        <f>BC14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BE14" s="9" t="n"/>
+      <c r="BF14" s="9" t="n"/>
+      <c r="BG14" s="12" t="n"/>
+      <c r="BH14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BF14" s="9" t="n">
+      <c r="BI14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="BG14" s="12">
-        <f>BF14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BH14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BJ14" s="12">
         <f>BI14/$E$14</f>
         <v/>
       </c>
       <c r="BK14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BL14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BM14" s="12">
         <f>BL14/$E$14</f>
         <v/>
       </c>
       <c r="BN14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BO14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BP14" s="12">
         <f>BO14/$E$14</f>
         <v/>
       </c>
       <c r="BQ14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BR14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BS14" s="12">
         <f>BR14/$E$14</f>
@@ -5235,12 +5428,22 @@
         <f>CA14/$E$14</f>
         <v/>
       </c>
-      <c r="CC14" s="9" t="n"/>
+      <c r="CC14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CD14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CE14" s="12">
         <f>CD14/$E$14</f>
+        <v/>
+      </c>
+      <c r="CF14" s="9" t="n"/>
+      <c r="CG14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" s="12">
+        <f>CG14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -5307,7 +5510,7 @@
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>126</v>
@@ -5320,17 +5523,17 @@
         <v>1</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W15" s="12">
         <f>V15/$E$15</f>
         <v/>
       </c>
       <c r="X15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Z15" s="12">
         <f>Y15/$E$15</f>
@@ -5347,7 +5550,7 @@
         <v/>
       </c>
       <c r="AD15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="9" t="n">
         <v>124</v>
@@ -5357,17 +5560,17 @@
         <v/>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AI15" s="12">
         <f>AH15/$E$15</f>
         <v/>
       </c>
       <c r="AJ15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="9" t="n">
         <v>121</v>
@@ -5376,53 +5579,53 @@
         <f>AK15/$E$15</f>
         <v/>
       </c>
-      <c r="AM15" s="9" t="n"/>
-      <c r="AN15" s="9" t="n"/>
-      <c r="AO15" s="12" t="n"/>
-      <c r="AP15" s="9" t="n">
+      <c r="AM15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AO15" s="12">
+        <f>AN15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AP15" s="9" t="n"/>
+      <c r="AQ15" s="9" t="n"/>
+      <c r="AR15" s="12" t="n"/>
+      <c r="AS15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AQ15" s="9" t="n">
+      <c r="AT15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AR15" s="12">
-        <f>AQ15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AS15" s="9" t="n"/>
-      <c r="AT15" s="9" t="n"/>
-      <c r="AU15" s="12" t="n"/>
+      <c r="AU15" s="12">
+        <f>AT15/$E$15</f>
+        <v/>
+      </c>
       <c r="AV15" s="9" t="n"/>
       <c r="AW15" s="9" t="n"/>
       <c r="AX15" s="12" t="n"/>
-      <c r="AY15" s="9" t="n">
+      <c r="AY15" s="9" t="n"/>
+      <c r="AZ15" s="9" t="n"/>
+      <c r="BA15" s="12" t="n"/>
+      <c r="BB15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AZ15" s="9" t="n">
+      <c r="BC15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="BA15" s="12">
-        <f>AZ15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BB15" s="9" t="n"/>
-      <c r="BC15" s="9" t="n"/>
-      <c r="BD15" s="12" t="n"/>
-      <c r="BE15" s="9" t="n">
+      <c r="BD15" s="12">
+        <f>BC15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BE15" s="9" t="n"/>
+      <c r="BF15" s="9" t="n"/>
+      <c r="BG15" s="12" t="n"/>
+      <c r="BH15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BF15" s="9" t="n">
+      <c r="BI15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="BG15" s="12">
-        <f>BF15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BH15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BJ15" s="12">
         <f>BI15/$E$15</f>
@@ -5432,24 +5635,24 @@
         <v>3</v>
       </c>
       <c r="BL15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BM15" s="12">
         <f>BL15/$E$15</f>
         <v/>
       </c>
       <c r="BN15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BO15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BP15" s="12">
         <f>BO15/$E$15</f>
         <v/>
       </c>
       <c r="BQ15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BR15" s="9" t="n">
         <v>76</v>
@@ -5459,10 +5662,10 @@
         <v/>
       </c>
       <c r="BT15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BU15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BV15" s="12">
         <f>BU15/$E$15</f>
@@ -5488,12 +5691,22 @@
         <f>CA15/$E$15</f>
         <v/>
       </c>
-      <c r="CC15" s="9" t="n"/>
+      <c r="CC15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CD15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CE15" s="12">
         <f>CD15/$E$15</f>
+        <v/>
+      </c>
+      <c r="CF15" s="9" t="n"/>
+      <c r="CG15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" s="12">
+        <f>CG15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -5629,51 +5842,58 @@
         <f>AK16/$E$16</f>
         <v/>
       </c>
-      <c r="AM16" s="9" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="12" t="n"/>
-      <c r="AP16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="9" t="n">
+      <c r="AM16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AR16" s="12">
-        <f>AQ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
+      <c r="AO16" s="12">
+        <f>AN16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AP16" s="9" t="n"/>
+      <c r="AQ16" s="9" t="n"/>
+      <c r="AR16" s="12" t="n"/>
+      <c r="AS16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
       <c r="AV16" s="9" t="n"/>
       <c r="AW16" s="9" t="n"/>
       <c r="AX16" s="12" t="n"/>
-      <c r="AY16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="9" t="n">
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BA16" s="12">
-        <f>AZ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BB16" s="9" t="n"/>
-      <c r="BC16" s="9" t="n"/>
-      <c r="BD16" s="12" t="n"/>
-      <c r="BE16" s="9" t="n">
+      <c r="BD16" s="12">
+        <f>BC16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BE16" s="9" t="n"/>
+      <c r="BF16" s="9" t="n"/>
+      <c r="BG16" s="12" t="n"/>
+      <c r="BH16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BF16" s="9" t="n">
+      <c r="BI16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BG16" s="12">
-        <f>BF16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BH16" s="9" t="n"/>
-      <c r="BI16" s="9" t="n"/>
-      <c r="BJ16" s="12" t="n"/>
+      <c r="BJ16" s="12">
+        <f>BI16/$E$16</f>
+        <v/>
+      </c>
       <c r="BK16" s="9" t="n"/>
       <c r="BL16" s="9" t="n"/>
       <c r="BM16" s="12" t="n"/>
@@ -5693,11 +5913,14 @@
       <c r="CA16" s="9" t="n"/>
       <c r="CB16" s="12" t="n"/>
       <c r="CC16" s="9" t="n"/>
-      <c r="CD16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" s="12">
-        <f>CD16/$E$16</f>
+      <c r="CD16" s="9" t="n"/>
+      <c r="CE16" s="12" t="n"/>
+      <c r="CF16" s="9" t="n"/>
+      <c r="CG16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" s="12">
+        <f>CG16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -5801,6 +6024,9 @@
       <c r="CC17" s="9" t="n"/>
       <c r="CD17" s="9" t="n"/>
       <c r="CE17" s="12" t="n"/>
+      <c r="CF17" s="9" t="n"/>
+      <c r="CG17" s="9" t="n"/>
+      <c r="CH17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -5825,36 +6051,38 @@
         <v>830</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
         <v/>
       </c>
-      <c r="O18" s="9" t="n"/>
+      <c r="O18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="P18" s="9" t="n">
         <v>139</v>
       </c>
@@ -5863,8 +6091,13 @@
         <v/>
       </c>
       <c r="R18" s="9" t="n"/>
-      <c r="S18" s="9" t="n"/>
-      <c r="T18" s="12" t="n"/>
+      <c r="S18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="T18" s="12">
+        <f>S18/$E$18</f>
+        <v/>
+      </c>
       <c r="U18" s="9" t="n"/>
       <c r="V18" s="9" t="n"/>
       <c r="W18" s="12" t="n"/>
@@ -5928,9 +6161,12 @@
       <c r="CC18" s="9" t="n"/>
       <c r="CD18" s="9" t="n"/>
       <c r="CE18" s="12" t="n"/>
+      <c r="CF18" s="9" t="n"/>
+      <c r="CG18" s="9" t="n"/>
+      <c r="CH18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -5939,6 +6175,7 @@
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="CF3:CH3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="BW3:BY3"/>
@@ -5968,7 +6205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE18"/>
+  <dimension ref="A1:CH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6054,6 +6291,9 @@
     <col width="9" customWidth="1" min="81" max="81"/>
     <col width="9" customWidth="1" min="82" max="82"/>
     <col width="9" customWidth="1" min="83" max="83"/>
+    <col width="9" customWidth="1" min="84" max="84"/>
+    <col width="9" customWidth="1" min="85" max="85"/>
+    <col width="9" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6072,81 +6312,84 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -6564,6 +6807,21 @@
         </is>
       </c>
       <c r="CE4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CF4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CG4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CH4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -6592,7 +6850,7 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>302</v>
@@ -6602,10 +6860,10 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
@@ -6632,7 +6890,7 @@
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
         <v>298</v>
@@ -6645,115 +6903,122 @@
         <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
-      <c r="AA5" s="9" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="12" t="n"/>
-      <c r="AD5" s="9" t="n">
+      <c r="AA5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>AB5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="9" t="n"/>
+      <c r="AE5" s="9" t="n"/>
+      <c r="AF5" s="12" t="n"/>
+      <c r="AG5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AE5" s="9" t="n">
+      <c r="AH5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="AF5" s="12">
-        <f>AE5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AG5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
       <c r="AJ5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
       <c r="AM5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AN5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO5" s="12">
         <f>AN5/$E$5</f>
         <v/>
       </c>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="12" t="n"/>
-      <c r="AS5" s="9" t="n">
+      <c r="AP5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AQ5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
+      <c r="AV5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AT5" s="9" t="n">
+      <c r="AW5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AU5" s="12">
-        <f>AT5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AV5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AW5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="AX5" s="12">
         <f>AW5/$E$5</f>
         <v/>
       </c>
-      <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n"/>
-      <c r="BA5" s="12" t="n"/>
-      <c r="BB5" s="9" t="n">
+      <c r="AY5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AZ5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="BA5" s="12">
+        <f>AZ5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BB5" s="9" t="n"/>
+      <c r="BC5" s="9" t="n"/>
+      <c r="BD5" s="12" t="n"/>
+      <c r="BE5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="BC5" s="9" t="n">
+      <c r="BF5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="BD5" s="12">
-        <f>BC5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BE5" s="9" t="n"/>
-      <c r="BF5" s="9" t="n"/>
-      <c r="BG5" s="12" t="n"/>
+      <c r="BG5" s="12">
+        <f>BF5/$E$5</f>
+        <v/>
+      </c>
       <c r="BH5" s="9" t="n"/>
-      <c r="BI5" s="9" t="n">
+      <c r="BI5" s="9" t="n"/>
+      <c r="BJ5" s="12" t="n"/>
+      <c r="BK5" s="9" t="n"/>
+      <c r="BL5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="BJ5" s="12">
-        <f>BI5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BK5" s="9" t="n"/>
-      <c r="BL5" s="9" t="n"/>
-      <c r="BM5" s="12" t="n"/>
+      <c r="BM5" s="12">
+        <f>BL5/$E$5</f>
+        <v/>
+      </c>
       <c r="BN5" s="9" t="n"/>
       <c r="BO5" s="9" t="n"/>
       <c r="BP5" s="12" t="n"/>
@@ -6772,6 +7037,9 @@
       <c r="CC5" s="9" t="n"/>
       <c r="CD5" s="9" t="n"/>
       <c r="CE5" s="12" t="n"/>
+      <c r="CF5" s="9" t="n"/>
+      <c r="CG5" s="9" t="n"/>
+      <c r="CH5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -6796,7 +7064,7 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>953</v>
@@ -6806,20 +7074,20 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
@@ -6836,7 +7104,7 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
         <v>950</v>
@@ -6846,118 +7114,125 @@
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="12" t="n"/>
-      <c r="AD6" s="9" t="n">
+      <c r="AA6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>AB6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="9" t="n"/>
+      <c r="AE6" s="9" t="n"/>
+      <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AH6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="AF6" s="12">
-        <f>AE6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AG6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
-      <c r="AS6" s="9" t="n">
+      <c r="AP6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AT6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
-      <c r="BB6" s="9" t="n">
+      <c r="AY6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BC6" s="9" t="n">
+      <c r="BF6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BD6" s="12">
-        <f>BC6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="12" t="n"/>
+      <c r="BG6" s="12">
+        <f>BF6/$E$6</f>
+        <v/>
+      </c>
       <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n">
+      <c r="BI6" s="9" t="n"/>
+      <c r="BJ6" s="12" t="n"/>
+      <c r="BK6" s="9" t="n"/>
+      <c r="BL6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="BJ6" s="12">
-        <f>BI6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BK6" s="9" t="n"/>
-      <c r="BL6" s="9" t="n"/>
-      <c r="BM6" s="12" t="n"/>
+      <c r="BM6" s="12">
+        <f>BL6/$E$6</f>
+        <v/>
+      </c>
       <c r="BN6" s="9" t="n"/>
       <c r="BO6" s="9" t="n"/>
       <c r="BP6" s="12" t="n"/>
@@ -6976,6 +7251,9 @@
       <c r="CC6" s="9" t="n"/>
       <c r="CD6" s="9" t="n"/>
       <c r="CE6" s="12" t="n"/>
+      <c r="CF6" s="9" t="n"/>
+      <c r="CG6" s="9" t="n"/>
+      <c r="CH6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -7000,10 +7278,10 @@
         <v>1500</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -7069,99 +7347,106 @@
         <f>Y7/$E$7</f>
         <v/>
       </c>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="12" t="n"/>
-      <c r="AD7" s="9" t="n">
+      <c r="AA7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC7" s="12">
+        <f>AB7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AD7" s="9" t="n"/>
+      <c r="AE7" s="9" t="n"/>
+      <c r="AF7" s="12" t="n"/>
+      <c r="AG7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="AE7" s="9" t="n">
+      <c r="AH7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="AF7" s="12">
-        <f>AE7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AG7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
-      <c r="AS7" s="9" t="n">
+      <c r="AP7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AT7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
-      <c r="BB7" s="9" t="n">
+      <c r="AY7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BC7" s="9" t="n">
+      <c r="BF7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="BD7" s="12">
-        <f>BC7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="12" t="n"/>
+      <c r="BG7" s="12">
+        <f>BF7/$E$7</f>
+        <v/>
+      </c>
       <c r="BH7" s="9" t="n"/>
-      <c r="BI7" s="9" t="n">
+      <c r="BI7" s="9" t="n"/>
+      <c r="BJ7" s="12" t="n"/>
+      <c r="BK7" s="9" t="n"/>
+      <c r="BL7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BJ7" s="12">
-        <f>BI7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BK7" s="9" t="n"/>
-      <c r="BL7" s="9" t="n"/>
-      <c r="BM7" s="12" t="n"/>
+      <c r="BM7" s="12">
+        <f>BL7/$E$7</f>
+        <v/>
+      </c>
       <c r="BN7" s="9" t="n"/>
       <c r="BO7" s="9" t="n"/>
       <c r="BP7" s="12" t="n"/>
@@ -7180,6 +7465,9 @@
       <c r="CC7" s="9" t="n"/>
       <c r="CD7" s="9" t="n"/>
       <c r="CE7" s="12" t="n"/>
+      <c r="CF7" s="9" t="n"/>
+      <c r="CG7" s="9" t="n"/>
+      <c r="CH7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -7204,7 +7492,7 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1056</v>
@@ -7214,10 +7502,10 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
@@ -7244,7 +7532,7 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>1054</v>
@@ -7254,17 +7542,17 @@
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>1052</v>
@@ -7273,99 +7561,106 @@
         <f>Y8/$E$8</f>
         <v/>
       </c>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="12" t="n"/>
-      <c r="AD8" s="9" t="n">
+      <c r="AA8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AE8" s="9" t="n">
+      <c r="AB8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="AC8" s="12">
+        <f>AB8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AD8" s="9" t="n"/>
+      <c r="AE8" s="9" t="n"/>
+      <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="AF8" s="12">
-        <f>AE8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AG8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
-      <c r="AS8" s="9" t="n">
+      <c r="AP8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AT8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
-      <c r="BB8" s="9" t="n">
+      <c r="AY8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BC8" s="9" t="n">
+      <c r="BF8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="BD8" s="12">
-        <f>BC8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="12" t="n"/>
+      <c r="BG8" s="12">
+        <f>BF8/$E$8</f>
+        <v/>
+      </c>
       <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="9" t="n">
+      <c r="BI8" s="9" t="n"/>
+      <c r="BJ8" s="12" t="n"/>
+      <c r="BK8" s="9" t="n"/>
+      <c r="BL8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="BJ8" s="12">
-        <f>BI8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BK8" s="9" t="n"/>
-      <c r="BL8" s="9" t="n"/>
-      <c r="BM8" s="12" t="n"/>
+      <c r="BM8" s="12">
+        <f>BL8/$E$8</f>
+        <v/>
+      </c>
       <c r="BN8" s="9" t="n"/>
       <c r="BO8" s="9" t="n"/>
       <c r="BP8" s="12" t="n"/>
@@ -7384,6 +7679,9 @@
       <c r="CC8" s="9" t="n"/>
       <c r="CD8" s="9" t="n"/>
       <c r="CE8" s="12" t="n"/>
+      <c r="CF8" s="9" t="n"/>
+      <c r="CG8" s="9" t="n"/>
+      <c r="CH8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -7477,19 +7775,19 @@
         <f>Y9/$E$9</f>
         <v/>
       </c>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="12" t="n"/>
-      <c r="AD9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="9" t="n">
+      <c r="AA9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="AF9" s="12">
-        <f>AE9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AC9" s="12">
+        <f>AB9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="9" t="n"/>
+      <c r="AE9" s="9" t="n"/>
+      <c r="AF9" s="12" t="n"/>
       <c r="AG9" s="9" t="n">
         <v>0</v>
       </c>
@@ -7501,7 +7799,7 @@
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="9" t="n">
         <v>845</v>
@@ -7511,28 +7809,28 @@
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AO9" s="12">
         <f>AN9/$E$9</f>
         <v/>
       </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
-      <c r="AS9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="9" t="n">
+      <c r="AP9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
       <c r="AV9" s="9" t="n">
         <v>0</v>
       </c>
@@ -7543,33 +7841,40 @@
         <f>AW9/$E$9</f>
         <v/>
       </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
-      <c r="BB9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" s="9" t="n">
+      <c r="AY9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BD9" s="12">
-        <f>BC9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="12" t="n"/>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="9" t="n"/>
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
+      <c r="BE9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="BG9" s="12">
+        <f>BF9/$E$9</f>
+        <v/>
+      </c>
       <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n">
+      <c r="BI9" s="9" t="n"/>
+      <c r="BJ9" s="12" t="n"/>
+      <c r="BK9" s="9" t="n"/>
+      <c r="BL9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BJ9" s="12">
-        <f>BI9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BK9" s="9" t="n"/>
-      <c r="BL9" s="9" t="n"/>
-      <c r="BM9" s="12" t="n"/>
+      <c r="BM9" s="12">
+        <f>BL9/$E$9</f>
+        <v/>
+      </c>
       <c r="BN9" s="9" t="n"/>
       <c r="BO9" s="9" t="n"/>
       <c r="BP9" s="12" t="n"/>
@@ -7588,6 +7893,9 @@
       <c r="CC9" s="9" t="n"/>
       <c r="CD9" s="9" t="n"/>
       <c r="CE9" s="12" t="n"/>
+      <c r="CF9" s="9" t="n"/>
+      <c r="CG9" s="9" t="n"/>
+      <c r="CH9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -7615,17 +7923,17 @@
         <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
@@ -7652,7 +7960,7 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>1418</v>
@@ -7662,118 +7970,125 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="12" t="n"/>
-      <c r="AD10" s="9" t="n">
+      <c r="AA10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="AC10" s="12">
+        <f>AB10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AD10" s="9" t="n"/>
+      <c r="AE10" s="9" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AE10" s="9" t="n">
+      <c r="AH10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="AF10" s="12">
-        <f>AE10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AG10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
-      <c r="AS10" s="9" t="n">
+      <c r="AP10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AT10" s="9" t="n">
+      <c r="AW10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AV10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
-      <c r="BB10" s="9" t="n">
+      <c r="AY10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BC10" s="9" t="n">
+      <c r="AZ10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n"/>
+      <c r="BD10" s="12" t="n"/>
+      <c r="BE10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="BD10" s="12">
-        <f>BC10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BE10" s="9" t="n"/>
-      <c r="BF10" s="9" t="n"/>
-      <c r="BG10" s="12" t="n"/>
+      <c r="BG10" s="12">
+        <f>BF10/$E$10</f>
+        <v/>
+      </c>
       <c r="BH10" s="9" t="n"/>
-      <c r="BI10" s="9" t="n">
+      <c r="BI10" s="9" t="n"/>
+      <c r="BJ10" s="12" t="n"/>
+      <c r="BK10" s="9" t="n"/>
+      <c r="BL10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="BJ10" s="12">
-        <f>BI10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BK10" s="9" t="n"/>
-      <c r="BL10" s="9" t="n"/>
-      <c r="BM10" s="12" t="n"/>
+      <c r="BM10" s="12">
+        <f>BL10/$E$10</f>
+        <v/>
+      </c>
       <c r="BN10" s="9" t="n"/>
       <c r="BO10" s="9" t="n"/>
       <c r="BP10" s="12" t="n"/>
@@ -7792,6 +8107,9 @@
       <c r="CC10" s="9" t="n"/>
       <c r="CD10" s="9" t="n"/>
       <c r="CE10" s="12" t="n"/>
+      <c r="CF10" s="9" t="n"/>
+      <c r="CG10" s="9" t="n"/>
+      <c r="CH10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -7819,27 +8137,27 @@
         <v>3</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
@@ -7856,7 +8174,7 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
         <v>992</v>
@@ -7866,10 +8184,10 @@
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
@@ -7885,99 +8203,106 @@
         <f>Y11/$E$11</f>
         <v/>
       </c>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="12" t="n"/>
-      <c r="AD11" s="9" t="n">
+      <c r="AA11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AC11" s="12">
+        <f>AB11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AD11" s="9" t="n"/>
+      <c r="AE11" s="9" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AH11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="AF11" s="12">
-        <f>AE11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AG11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="AI11" s="12">
         <f>AH11/$E$11</f>
         <v/>
       </c>
       <c r="AJ11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="AL11" s="12">
         <f>AK11/$E$11</f>
         <v/>
       </c>
       <c r="AM11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AO11" s="12">
         <f>AN11/$E$11</f>
         <v/>
       </c>
-      <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n"/>
-      <c r="AR11" s="12" t="n"/>
-      <c r="AS11" s="9" t="n">
+      <c r="AP11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AT11" s="9" t="n">
+      <c r="AW11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AU11" s="12">
-        <f>AT11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AV11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="AX11" s="12">
         <f>AW11/$E$11</f>
         <v/>
       </c>
-      <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n"/>
-      <c r="BA11" s="12" t="n"/>
-      <c r="BB11" s="9" t="n">
+      <c r="AY11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="BA11" s="12">
+        <f>AZ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="9" t="n"/>
+      <c r="BC11" s="9" t="n"/>
+      <c r="BD11" s="12" t="n"/>
+      <c r="BE11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BC11" s="9" t="n">
+      <c r="BF11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="BD11" s="12">
-        <f>BC11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BE11" s="9" t="n"/>
-      <c r="BF11" s="9" t="n"/>
-      <c r="BG11" s="12" t="n"/>
+      <c r="BG11" s="12">
+        <f>BF11/$E$11</f>
+        <v/>
+      </c>
       <c r="BH11" s="9" t="n"/>
-      <c r="BI11" s="9" t="n">
+      <c r="BI11" s="9" t="n"/>
+      <c r="BJ11" s="12" t="n"/>
+      <c r="BK11" s="9" t="n"/>
+      <c r="BL11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="BJ11" s="12">
-        <f>BI11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BK11" s="9" t="n"/>
-      <c r="BL11" s="9" t="n"/>
-      <c r="BM11" s="12" t="n"/>
+      <c r="BM11" s="12">
+        <f>BL11/$E$11</f>
+        <v/>
+      </c>
       <c r="BN11" s="9" t="n"/>
       <c r="BO11" s="9" t="n"/>
       <c r="BP11" s="12" t="n"/>
@@ -7996,6 +8321,9 @@
       <c r="CC11" s="9" t="n"/>
       <c r="CD11" s="9" t="n"/>
       <c r="CE11" s="12" t="n"/>
+      <c r="CF11" s="9" t="n"/>
+      <c r="CG11" s="9" t="n"/>
+      <c r="CH11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -8023,17 +8351,17 @@
         <v>1</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
@@ -8060,7 +8388,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
         <v>737</v>
@@ -8070,118 +8398,125 @@
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="W12" s="12">
         <f>V12/$E$12</f>
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
         <v/>
       </c>
-      <c r="AA12" s="9" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="12" t="n"/>
-      <c r="AD12" s="9" t="n">
+      <c r="AA12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="AC12" s="12">
+        <f>AB12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="9" t="n"/>
+      <c r="AE12" s="9" t="n"/>
+      <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AE12" s="9" t="n">
+      <c r="AH12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="AF12" s="12">
-        <f>AE12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AG12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="AI12" s="12">
         <f>AH12/$E$12</f>
         <v/>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="AL12" s="12">
         <f>AK12/$E$12</f>
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AN12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AO12" s="12">
         <f>AN12/$E$12</f>
         <v/>
       </c>
-      <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n"/>
-      <c r="AR12" s="12" t="n"/>
-      <c r="AS12" s="9" t="n">
+      <c r="AP12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
+      <c r="AV12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AT12" s="9" t="n">
+      <c r="AW12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AU12" s="12">
-        <f>AT12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AV12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="AX12" s="12">
         <f>AW12/$E$12</f>
         <v/>
       </c>
-      <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n"/>
-      <c r="BA12" s="12" t="n"/>
-      <c r="BB12" s="9" t="n">
+      <c r="AY12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="BA12" s="12">
+        <f>AZ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="12" t="n"/>
+      <c r="BE12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BC12" s="9" t="n">
+      <c r="BF12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="BD12" s="12">
-        <f>BC12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BE12" s="9" t="n"/>
-      <c r="BF12" s="9" t="n"/>
-      <c r="BG12" s="12" t="n"/>
+      <c r="BG12" s="12">
+        <f>BF12/$E$12</f>
+        <v/>
+      </c>
       <c r="BH12" s="9" t="n"/>
-      <c r="BI12" s="9" t="n">
+      <c r="BI12" s="9" t="n"/>
+      <c r="BJ12" s="12" t="n"/>
+      <c r="BK12" s="9" t="n"/>
+      <c r="BL12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="BJ12" s="12">
-        <f>BI12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BK12" s="9" t="n"/>
-      <c r="BL12" s="9" t="n"/>
-      <c r="BM12" s="12" t="n"/>
+      <c r="BM12" s="12">
+        <f>BL12/$E$12</f>
+        <v/>
+      </c>
       <c r="BN12" s="9" t="n"/>
       <c r="BO12" s="9" t="n"/>
       <c r="BP12" s="12" t="n"/>
@@ -8200,6 +8535,9 @@
       <c r="CC12" s="9" t="n"/>
       <c r="CD12" s="9" t="n"/>
       <c r="CE12" s="12" t="n"/>
+      <c r="CF12" s="9" t="n"/>
+      <c r="CG12" s="9" t="n"/>
+      <c r="CH12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -8224,7 +8562,7 @@
         <v>1623</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>1394</v>
@@ -8234,20 +8572,20 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
@@ -8284,7 +8622,7 @@
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>1391</v>
@@ -8293,99 +8631,106 @@
         <f>Y13/$E$13</f>
         <v/>
       </c>
-      <c r="AA13" s="9" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="12" t="n"/>
-      <c r="AD13" s="9" t="n">
+      <c r="AA13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AE13" s="9" t="n">
+      <c r="AB13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="AC13" s="12">
+        <f>AB13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="9" t="n"/>
+      <c r="AE13" s="9" t="n"/>
+      <c r="AF13" s="12" t="n"/>
+      <c r="AG13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="AF13" s="12">
-        <f>AE13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AG13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
-      <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n"/>
-      <c r="AR13" s="12" t="n"/>
-      <c r="AS13" s="9" t="n">
+      <c r="AP13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AT13" s="9" t="n">
+      <c r="AW13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AU13" s="12">
-        <f>AT13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AV13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
-      <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n"/>
-      <c r="BA13" s="12" t="n"/>
-      <c r="BB13" s="9" t="n">
+      <c r="AY13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="BA13" s="12">
+        <f>AZ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="9" t="n"/>
+      <c r="BC13" s="9" t="n"/>
+      <c r="BD13" s="12" t="n"/>
+      <c r="BE13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BC13" s="9" t="n">
+      <c r="BF13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="BD13" s="12">
-        <f>BC13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BE13" s="9" t="n"/>
-      <c r="BF13" s="9" t="n"/>
-      <c r="BG13" s="12" t="n"/>
+      <c r="BG13" s="12">
+        <f>BF13/$E$13</f>
+        <v/>
+      </c>
       <c r="BH13" s="9" t="n"/>
-      <c r="BI13" s="9" t="n">
+      <c r="BI13" s="9" t="n"/>
+      <c r="BJ13" s="12" t="n"/>
+      <c r="BK13" s="9" t="n"/>
+      <c r="BL13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="BJ13" s="12">
-        <f>BI13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BK13" s="9" t="n"/>
-      <c r="BL13" s="9" t="n"/>
-      <c r="BM13" s="12" t="n"/>
+      <c r="BM13" s="12">
+        <f>BL13/$E$13</f>
+        <v/>
+      </c>
       <c r="BN13" s="9" t="n"/>
       <c r="BO13" s="9" t="n"/>
       <c r="BP13" s="12" t="n"/>
@@ -8404,6 +8749,9 @@
       <c r="CC13" s="9" t="n"/>
       <c r="CD13" s="9" t="n"/>
       <c r="CE13" s="12" t="n"/>
+      <c r="CF13" s="9" t="n"/>
+      <c r="CG13" s="9" t="n"/>
+      <c r="CH13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -8428,17 +8776,17 @@
         <v>996</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>904</v>
@@ -8448,10 +8796,10 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
@@ -8488,7 +8836,7 @@
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>902</v>
@@ -8497,21 +8845,21 @@
         <f>Y14/$E$14</f>
         <v/>
       </c>
-      <c r="AA14" s="9" t="n"/>
-      <c r="AB14" s="9" t="n"/>
-      <c r="AC14" s="12" t="n"/>
-      <c r="AD14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="AF14" s="12">
-        <f>AE14/$E$14</f>
-        <v/>
-      </c>
+      <c r="AA14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="AC14" s="12">
+        <f>AB14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="9" t="n"/>
+      <c r="AE14" s="9" t="n"/>
+      <c r="AF14" s="12" t="n"/>
       <c r="AG14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="9" t="n">
         <v>898</v>
@@ -8521,75 +8869,82 @@
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
-      <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n"/>
-      <c r="AR14" s="12" t="n"/>
-      <c r="AS14" s="9" t="n">
+      <c r="AP14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AT14" s="9" t="n">
+      <c r="AW14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AU14" s="12">
-        <f>AT14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AV14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
-      <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n"/>
-      <c r="BA14" s="12" t="n"/>
-      <c r="BB14" s="9" t="n">
+      <c r="AY14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BC14" s="9" t="n">
+      <c r="AZ14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="BA14" s="12">
+        <f>AZ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="9" t="n"/>
+      <c r="BC14" s="9" t="n"/>
+      <c r="BD14" s="12" t="n"/>
+      <c r="BE14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="BD14" s="12">
-        <f>BC14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BE14" s="9" t="n"/>
-      <c r="BF14" s="9" t="n"/>
-      <c r="BG14" s="12" t="n"/>
+      <c r="BG14" s="12">
+        <f>BF14/$E$14</f>
+        <v/>
+      </c>
       <c r="BH14" s="9" t="n"/>
-      <c r="BI14" s="9" t="n">
+      <c r="BI14" s="9" t="n"/>
+      <c r="BJ14" s="12" t="n"/>
+      <c r="BK14" s="9" t="n"/>
+      <c r="BL14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="BJ14" s="12">
-        <f>BI14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BK14" s="9" t="n"/>
-      <c r="BL14" s="9" t="n"/>
-      <c r="BM14" s="12" t="n"/>
+      <c r="BM14" s="12">
+        <f>BL14/$E$14</f>
+        <v/>
+      </c>
       <c r="BN14" s="9" t="n"/>
       <c r="BO14" s="9" t="n"/>
       <c r="BP14" s="12" t="n"/>
@@ -8608,6 +8963,9 @@
       <c r="CC14" s="9" t="n"/>
       <c r="CD14" s="9" t="n"/>
       <c r="CE14" s="12" t="n"/>
+      <c r="CF14" s="9" t="n"/>
+      <c r="CG14" s="9" t="n"/>
+      <c r="CH14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -8709,6 +9067,9 @@
       <c r="CC15" s="9" t="n"/>
       <c r="CD15" s="9" t="n"/>
       <c r="CE15" s="12" t="n"/>
+      <c r="CF15" s="9" t="n"/>
+      <c r="CG15" s="9" t="n"/>
+      <c r="CH15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -8733,17 +9094,17 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H16" s="11">
         <f>G16/$E$16</f>
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>717</v>
@@ -8753,10 +9114,10 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="N16" s="12">
         <f>M16/$E$16</f>
@@ -8773,7 +9134,7 @@
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="9" t="n">
         <v>715</v>
@@ -8783,118 +9144,125 @@
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
         <v/>
       </c>
       <c r="X16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="Z16" s="12">
         <f>Y16/$E$16</f>
         <v/>
       </c>
-      <c r="AA16" s="9" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="12" t="n"/>
-      <c r="AD16" s="9" t="n">
+      <c r="AA16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="AC16" s="12">
+        <f>AB16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="9" t="n"/>
+      <c r="AE16" s="9" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AE16" s="9" t="n">
+      <c r="AH16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="AF16" s="12">
-        <f>AE16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AG16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="AI16" s="12">
         <f>AH16/$E$16</f>
         <v/>
       </c>
       <c r="AJ16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AK16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AL16" s="12">
         <f>AK16/$E$16</f>
         <v/>
       </c>
       <c r="AM16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AN16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AO16" s="12">
         <f>AN16/$E$16</f>
         <v/>
       </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
-      <c r="AS16" s="9" t="n">
+      <c r="AP16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AT16" s="9" t="n">
+      <c r="AW16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AU16" s="12">
-        <f>AT16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AV16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="AX16" s="12">
         <f>AW16/$E$16</f>
         <v/>
       </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
-      <c r="BB16" s="9" t="n">
+      <c r="AY16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="12" t="n"/>
+      <c r="BE16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="BC16" s="9" t="n">
+      <c r="BF16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="BD16" s="12">
-        <f>BC16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BE16" s="9" t="n"/>
-      <c r="BF16" s="9" t="n"/>
-      <c r="BG16" s="12" t="n"/>
+      <c r="BG16" s="12">
+        <f>BF16/$E$16</f>
+        <v/>
+      </c>
       <c r="BH16" s="9" t="n"/>
-      <c r="BI16" s="9" t="n">
+      <c r="BI16" s="9" t="n"/>
+      <c r="BJ16" s="12" t="n"/>
+      <c r="BK16" s="9" t="n"/>
+      <c r="BL16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="BJ16" s="12">
-        <f>BI16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n"/>
-      <c r="BM16" s="12" t="n"/>
+      <c r="BM16" s="12">
+        <f>BL16/$E$16</f>
+        <v/>
+      </c>
       <c r="BN16" s="9" t="n"/>
       <c r="BO16" s="9" t="n"/>
       <c r="BP16" s="12" t="n"/>
@@ -8913,6 +9281,9 @@
       <c r="CC16" s="9" t="n"/>
       <c r="CD16" s="9" t="n"/>
       <c r="CE16" s="12" t="n"/>
+      <c r="CF16" s="9" t="n"/>
+      <c r="CG16" s="9" t="n"/>
+      <c r="CH16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -8937,17 +9308,17 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H17" s="11">
         <f>G17/$E$17</f>
         <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>388</v>
@@ -8957,20 +9328,20 @@
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N17" s="12">
         <f>M17/$E$17</f>
         <v/>
       </c>
       <c r="O17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/$E$17</f>
@@ -8987,7 +9358,7 @@
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>385</v>
@@ -8997,108 +9368,115 @@
         <v/>
       </c>
       <c r="X17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z17" s="12">
         <f>Y17/$E$17</f>
         <v/>
       </c>
-      <c r="AA17" s="9" t="n"/>
-      <c r="AB17" s="9" t="n"/>
-      <c r="AC17" s="12" t="n"/>
-      <c r="AD17" s="9" t="n">
+      <c r="AA17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AE17" s="9" t="n">
+      <c r="AB17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="AC17" s="12">
+        <f>AB17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="9" t="n"/>
+      <c r="AE17" s="9" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="AF17" s="12">
-        <f>AE17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AG17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="AI17" s="12">
         <f>AH17/$E$17</f>
         <v/>
       </c>
       <c r="AJ17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AK17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AL17" s="12">
         <f>AK17/$E$17</f>
         <v/>
       </c>
       <c r="AM17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AO17" s="12">
         <f>AN17/$E$17</f>
         <v/>
       </c>
-      <c r="AP17" s="9" t="n"/>
-      <c r="AQ17" s="9" t="n"/>
-      <c r="AR17" s="12" t="n"/>
-      <c r="AS17" s="9" t="n">
+      <c r="AP17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AR17" s="12">
+        <f>AQ17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AS17" s="9" t="n"/>
+      <c r="AT17" s="9" t="n"/>
+      <c r="AU17" s="12" t="n"/>
+      <c r="AV17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AT17" s="9" t="n">
+      <c r="AW17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AU17" s="12">
-        <f>AT17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AV17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="AX17" s="12">
         <f>AW17/$E$17</f>
         <v/>
       </c>
-      <c r="AY17" s="9" t="n"/>
-      <c r="AZ17" s="9" t="n"/>
-      <c r="BA17" s="12" t="n"/>
-      <c r="BB17" s="9" t="n">
+      <c r="AY17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="BA17" s="12">
+        <f>AZ17/$E$17</f>
+        <v/>
+      </c>
+      <c r="BB17" s="9" t="n"/>
+      <c r="BC17" s="9" t="n"/>
+      <c r="BD17" s="12" t="n"/>
+      <c r="BE17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BC17" s="9" t="n">
+      <c r="BF17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="BD17" s="12">
-        <f>BC17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BE17" s="9" t="n"/>
-      <c r="BF17" s="9" t="n"/>
-      <c r="BG17" s="12" t="n"/>
+      <c r="BG17" s="12">
+        <f>BF17/$E$17</f>
+        <v/>
+      </c>
       <c r="BH17" s="9" t="n"/>
-      <c r="BI17" s="9" t="n">
+      <c r="BI17" s="9" t="n"/>
+      <c r="BJ17" s="12" t="n"/>
+      <c r="BK17" s="9" t="n"/>
+      <c r="BL17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="BJ17" s="12">
-        <f>BI17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BK17" s="9" t="n"/>
-      <c r="BL17" s="9" t="n"/>
-      <c r="BM17" s="12" t="n"/>
+      <c r="BM17" s="12">
+        <f>BL17/$E$17</f>
+        <v/>
+      </c>
       <c r="BN17" s="9" t="n"/>
       <c r="BO17" s="9" t="n"/>
       <c r="BP17" s="12" t="n"/>
@@ -9117,6 +9495,9 @@
       <c r="CC17" s="9" t="n"/>
       <c r="CD17" s="9" t="n"/>
       <c r="CE17" s="12" t="n"/>
+      <c r="CF17" s="9" t="n"/>
+      <c r="CG17" s="9" t="n"/>
+      <c r="CH17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -9141,10 +9522,10 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
@@ -9181,7 +9562,7 @@
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="9" t="n">
         <v>292</v>
@@ -9191,118 +9572,125 @@
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
       <c r="X18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Z18" s="12">
         <f>Y18/$E$18</f>
         <v/>
       </c>
-      <c r="AA18" s="9" t="n"/>
-      <c r="AB18" s="9" t="n"/>
-      <c r="AC18" s="12" t="n"/>
-      <c r="AD18" s="9" t="n">
+      <c r="AA18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="AC18" s="12">
+        <f>AB18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="9" t="n"/>
+      <c r="AE18" s="9" t="n"/>
+      <c r="AF18" s="12" t="n"/>
+      <c r="AG18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AH18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="AF18" s="12">
-        <f>AE18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AG18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="AI18" s="12">
         <f>AH18/$E$18</f>
         <v/>
       </c>
       <c r="AJ18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL18" s="12">
         <f>AK18/$E$18</f>
         <v/>
       </c>
       <c r="AM18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO18" s="12">
         <f>AN18/$E$18</f>
         <v/>
       </c>
-      <c r="AP18" s="9" t="n"/>
-      <c r="AQ18" s="9" t="n"/>
-      <c r="AR18" s="12" t="n"/>
-      <c r="AS18" s="9" t="n">
+      <c r="AP18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AR18" s="12">
+        <f>AQ18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="9" t="n"/>
+      <c r="AU18" s="12" t="n"/>
+      <c r="AV18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AT18" s="9" t="n">
+      <c r="AW18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AU18" s="12">
-        <f>AT18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AV18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="AX18" s="12">
         <f>AW18/$E$18</f>
         <v/>
       </c>
-      <c r="AY18" s="9" t="n"/>
-      <c r="AZ18" s="9" t="n"/>
-      <c r="BA18" s="12" t="n"/>
-      <c r="BB18" s="9" t="n">
+      <c r="AY18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="BA18" s="12">
+        <f>AZ18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BB18" s="9" t="n"/>
+      <c r="BC18" s="9" t="n"/>
+      <c r="BD18" s="12" t="n"/>
+      <c r="BE18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BC18" s="9" t="n">
+      <c r="BF18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="BD18" s="12">
-        <f>BC18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BE18" s="9" t="n"/>
-      <c r="BF18" s="9" t="n"/>
-      <c r="BG18" s="12" t="n"/>
+      <c r="BG18" s="12">
+        <f>BF18/$E$18</f>
+        <v/>
+      </c>
       <c r="BH18" s="9" t="n"/>
-      <c r="BI18" s="9" t="n">
+      <c r="BI18" s="9" t="n"/>
+      <c r="BJ18" s="12" t="n"/>
+      <c r="BK18" s="9" t="n"/>
+      <c r="BL18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="BJ18" s="12">
-        <f>BI18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BK18" s="9" t="n"/>
-      <c r="BL18" s="9" t="n"/>
-      <c r="BM18" s="12" t="n"/>
+      <c r="BM18" s="12">
+        <f>BL18/$E$18</f>
+        <v/>
+      </c>
       <c r="BN18" s="9" t="n"/>
       <c r="BO18" s="9" t="n"/>
       <c r="BP18" s="12" t="n"/>
@@ -9321,9 +9709,12 @@
       <c r="CC18" s="9" t="n"/>
       <c r="CD18" s="9" t="n"/>
       <c r="CE18" s="12" t="n"/>
+      <c r="CF18" s="9" t="n"/>
+      <c r="CG18" s="9" t="n"/>
+      <c r="CH18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -9332,6 +9723,7 @@
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
+    <mergeCell ref="CF3:CH3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="BW3:BY3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 19/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 20/08/2026</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 19/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 20/08/2026</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 19/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 20/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,9 @@
     <col width="9" customWidth="1" min="84" max="84"/>
     <col width="9" customWidth="1" min="85" max="85"/>
     <col width="9" customWidth="1" min="86" max="86"/>
+    <col width="9" customWidth="1" min="87" max="87"/>
+    <col width="9" customWidth="1" min="88" max="88"/>
+    <col width="9" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -594,84 +597,87 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1104,6 +1110,21 @@
         </is>
       </c>
       <c r="CH4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CI4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CJ4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CK4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1192,7 +1213,7 @@
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>43</v>
@@ -1202,17 +1223,17 @@
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="9" t="n">
         <v>42</v>
@@ -1225,49 +1246,56 @@
         <v>1</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
       <c r="AJ5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
-      <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
-      <c r="AP5" s="9" t="n">
+      <c r="AM5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AP5" s="9" t="n"/>
+      <c r="AQ5" s="9" t="n"/>
+      <c r="AR5" s="12" t="n"/>
+      <c r="AS5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AQ5" s="9" t="n">
+      <c r="AT5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AR5" s="12">
-        <f>AQ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
       <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n">
+      <c r="AW5" s="9" t="n"/>
+      <c r="AX5" s="12" t="n"/>
+      <c r="AY5" s="9" t="n"/>
+      <c r="AZ5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AX5" s="12">
-        <f>AW5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n"/>
-      <c r="BA5" s="12" t="n"/>
+      <c r="BA5" s="12">
+        <f>AZ5/$E$5</f>
+        <v/>
+      </c>
       <c r="BB5" s="9" t="n"/>
       <c r="BC5" s="9" t="n"/>
       <c r="BD5" s="12" t="n"/>
@@ -1301,6 +1329,9 @@
       <c r="CF5" s="9" t="n"/>
       <c r="CG5" s="9" t="n"/>
       <c r="CH5" s="12" t="n"/>
+      <c r="CI5" s="9" t="n"/>
+      <c r="CJ5" s="9" t="n"/>
+      <c r="CK5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1325,7 +1356,7 @@
         <v>154</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>35</v>
@@ -1335,17 +1366,17 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>34</v>
@@ -1355,10 +1386,10 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
@@ -1434,33 +1465,40 @@
         <f>AK6/$E$6</f>
         <v/>
       </c>
-      <c r="AM6" s="9" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="12" t="n"/>
-      <c r="AP6" s="9" t="n">
+      <c r="AM6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AO6" s="12">
+        <f>AN6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AP6" s="9" t="n"/>
+      <c r="AQ6" s="9" t="n"/>
+      <c r="AR6" s="12" t="n"/>
+      <c r="AS6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AQ6" s="9" t="n">
+      <c r="AT6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AR6" s="12">
-        <f>AQ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
       <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n">
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
       <c r="BB6" s="9" t="n"/>
       <c r="BC6" s="9" t="n"/>
       <c r="BD6" s="12" t="n"/>
@@ -1494,6 +1532,9 @@
       <c r="CF6" s="9" t="n"/>
       <c r="CG6" s="9" t="n"/>
       <c r="CH6" s="12" t="n"/>
+      <c r="CI6" s="9" t="n"/>
+      <c r="CJ6" s="9" t="n"/>
+      <c r="CK6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1518,7 +1559,7 @@
         <v>490</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>48</v>
@@ -1531,7 +1572,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
@@ -1541,17 +1582,17 @@
         <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
@@ -1588,7 +1629,7 @@
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="9" t="n">
         <v>45</v>
@@ -1598,62 +1639,69 @@
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
-      <c r="AM7" s="9" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="12" t="n"/>
-      <c r="AP7" s="9" t="n">
+      <c r="AM7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO7" s="12">
+        <f>AN7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AP7" s="9" t="n"/>
+      <c r="AQ7" s="9" t="n"/>
+      <c r="AR7" s="12" t="n"/>
+      <c r="AS7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ7" s="9" t="n">
+      <c r="AT7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AR7" s="12">
-        <f>AQ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
       <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n">
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
       <c r="BB7" s="9" t="n"/>
       <c r="BC7" s="9" t="n"/>
       <c r="BD7" s="12" t="n"/>
@@ -1687,6 +1735,9 @@
       <c r="CF7" s="9" t="n"/>
       <c r="CG7" s="9" t="n"/>
       <c r="CH7" s="12" t="n"/>
+      <c r="CI7" s="9" t="n"/>
+      <c r="CJ7" s="9" t="n"/>
+      <c r="CK7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1820,33 +1871,40 @@
         <f>AK8/$E$8</f>
         <v/>
       </c>
-      <c r="AM8" s="9" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="12" t="n"/>
-      <c r="AP8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="9" t="n">
+      <c r="AM8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AR8" s="12">
-        <f>AQ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
+      <c r="AO8" s="12">
+        <f>AN8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AP8" s="9" t="n"/>
+      <c r="AQ8" s="9" t="n"/>
+      <c r="AR8" s="12" t="n"/>
+      <c r="AS8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
       <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n">
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
       <c r="BB8" s="9" t="n"/>
       <c r="BC8" s="9" t="n"/>
       <c r="BD8" s="12" t="n"/>
@@ -1880,6 +1938,9 @@
       <c r="CF8" s="9" t="n"/>
       <c r="CG8" s="9" t="n"/>
       <c r="CH8" s="12" t="n"/>
+      <c r="CI8" s="9" t="n"/>
+      <c r="CJ8" s="9" t="n"/>
+      <c r="CK8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2004,7 +2065,7 @@
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="9" t="n">
         <v>1</v>
@@ -2013,33 +2074,40 @@
         <f>AK9/$E$9</f>
         <v/>
       </c>
-      <c r="AM9" s="9" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="12" t="n"/>
-      <c r="AP9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="12">
-        <f>AQ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
+      <c r="AM9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="12">
+        <f>AN9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AP9" s="9" t="n"/>
+      <c r="AQ9" s="9" t="n"/>
+      <c r="AR9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
       <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
       <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
+      <c r="AZ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
       <c r="BB9" s="9" t="n"/>
       <c r="BC9" s="9" t="n"/>
       <c r="BD9" s="12" t="n"/>
@@ -2073,6 +2141,9 @@
       <c r="CF9" s="9" t="n"/>
       <c r="CG9" s="9" t="n"/>
       <c r="CH9" s="12" t="n"/>
+      <c r="CI9" s="9" t="n"/>
+      <c r="CJ9" s="9" t="n"/>
+      <c r="CK9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2100,54 +2171,54 @@
         <v>8</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>311</v>
@@ -2157,69 +2228,76 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
-      <c r="AM10" s="9" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AN10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AO10" s="12">
+        <f>AN10/$E$10</f>
+        <v/>
+      </c>
       <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n">
+      <c r="AQ10" s="9" t="n"/>
+      <c r="AR10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AR10" s="12">
-        <f>AQ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
       <c r="AV10" s="9" t="n"/>
       <c r="AW10" s="9" t="n"/>
       <c r="AX10" s="12" t="n"/>
@@ -2259,9 +2337,12 @@
       <c r="CF10" s="9" t="n"/>
       <c r="CG10" s="9" t="n"/>
       <c r="CH10" s="12" t="n"/>
+      <c r="CI10" s="9" t="n"/>
+      <c r="CJ10" s="9" t="n"/>
+      <c r="CK10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -2276,6 +2357,7 @@
     <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="CI3:CK3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="CC3:CE3"/>
@@ -2300,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH18"/>
+  <dimension ref="A1:CK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2389,6 +2471,9 @@
     <col width="9" customWidth="1" min="84" max="84"/>
     <col width="9" customWidth="1" min="85" max="85"/>
     <col width="9" customWidth="1" min="86" max="86"/>
+    <col width="9" customWidth="1" min="87" max="87"/>
+    <col width="9" customWidth="1" min="88" max="88"/>
+    <col width="9" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2407,84 +2492,87 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -2917,6 +3005,21 @@
         </is>
       </c>
       <c r="CH4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CI4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CJ4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CK4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2945,27 +3048,27 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>178</v>
@@ -2975,10 +3078,10 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
@@ -3005,7 +3108,7 @@
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>177</v>
@@ -3014,17 +3117,24 @@
         <f>Y5/$E$5</f>
         <v/>
       </c>
-      <c r="AA5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="AB5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
       <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="12" t="n"/>
+      <c r="AE5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
       <c r="AG5" s="9" t="n"/>
       <c r="AH5" s="9" t="n"/>
       <c r="AI5" s="12" t="n"/>
@@ -3079,6 +3189,9 @@
       <c r="CF5" s="9" t="n"/>
       <c r="CG5" s="9" t="n"/>
       <c r="CH5" s="12" t="n"/>
+      <c r="CI5" s="9" t="n"/>
+      <c r="CJ5" s="9" t="n"/>
+      <c r="CK5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -3103,40 +3216,40 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
@@ -3153,7 +3266,7 @@
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>335</v>
@@ -3163,183 +3276,193 @@
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
-      <c r="AS6" s="9" t="n">
+      <c r="AP6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AT6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
       <c r="AY6" s="9" t="n"/>
       <c r="AZ6" s="9" t="n"/>
       <c r="BA6" s="12" t="n"/>
-      <c r="BB6" s="9" t="n">
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BC6" s="9" t="n">
+      <c r="BF6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="BD6" s="12">
-        <f>BC6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="12" t="n"/>
-      <c r="BH6" s="9" t="n">
+      <c r="BG6" s="12">
+        <f>BF6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BH6" s="9" t="n"/>
+      <c r="BI6" s="9" t="n"/>
+      <c r="BJ6" s="12" t="n"/>
+      <c r="BK6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BI6" s="9" t="n">
+      <c r="BL6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="BJ6" s="12">
-        <f>BI6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BK6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BL6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BM6" s="12">
         <f>BL6/$E$6</f>
         <v/>
       </c>
       <c r="BN6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BO6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
         <v/>
       </c>
       <c r="BQ6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BR6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
         <v/>
       </c>
       <c r="BT6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BU6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
         <v/>
       </c>
       <c r="BW6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="BX6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="BY6" s="12">
         <f>BX6/$E$6</f>
         <v/>
       </c>
       <c r="BZ6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CA6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="CB6" s="12">
         <f>CA6/$E$6</f>
         <v/>
       </c>
       <c r="CC6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CD6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="CE6" s="12">
         <f>CD6/$E$6</f>
         <v/>
       </c>
-      <c r="CF6" s="9" t="n"/>
+      <c r="CF6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="CG6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="CH6" s="12">
         <f>CG6/$E$6</f>
+        <v/>
+      </c>
+      <c r="CI6" s="9" t="n"/>
+      <c r="CJ6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="CK6" s="12">
+        <f>CJ6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -3366,10 +3489,10 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H7" s="11">
         <f>G7/$E$7</f>
@@ -3396,7 +3519,7 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>120</v>
@@ -3406,10 +3529,10 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
@@ -3426,7 +3549,7 @@
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>119</v>
@@ -3439,109 +3562,109 @@
         <v>3</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
-      <c r="AS7" s="9" t="n">
+      <c r="AP7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AT7" s="9" t="n">
+      <c r="AW7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
       <c r="AY7" s="9" t="n"/>
       <c r="AZ7" s="9" t="n"/>
       <c r="BA7" s="12" t="n"/>
-      <c r="BB7" s="9" t="n">
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BC7" s="9" t="n">
+      <c r="BF7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="BD7" s="12">
-        <f>BC7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="12" t="n"/>
-      <c r="BH7" s="9" t="n">
+      <c r="BG7" s="12">
+        <f>BF7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BH7" s="9" t="n"/>
+      <c r="BI7" s="9" t="n"/>
+      <c r="BJ7" s="12" t="n"/>
+      <c r="BK7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BI7" s="9" t="n">
+      <c r="BL7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="BJ7" s="12">
-        <f>BI7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BK7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BM7" s="12">
         <f>BL7/$E$7</f>
         <v/>
       </c>
       <c r="BN7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BO7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
@@ -3551,58 +3674,68 @@
         <v>6</v>
       </c>
       <c r="BR7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
         <v/>
       </c>
       <c r="BT7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BU7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
         <v/>
       </c>
       <c r="BW7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BX7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BY7" s="12">
         <f>BX7/$E$7</f>
         <v/>
       </c>
       <c r="BZ7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CA7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CB7" s="12">
         <f>CA7/$E$7</f>
         <v/>
       </c>
       <c r="CC7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CD7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CE7" s="12">
         <f>CD7/$E$7</f>
         <v/>
       </c>
-      <c r="CF7" s="9" t="n"/>
+      <c r="CF7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="CG7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CH7" s="12">
         <f>CG7/$E$7</f>
+        <v/>
+      </c>
+      <c r="CI7" s="9" t="n"/>
+      <c r="CJ7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CK7" s="12">
+        <f>CJ7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -3629,17 +3762,17 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1000</v>
@@ -3649,10 +3782,10 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
@@ -3679,7 +3812,7 @@
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>998</v>
@@ -3689,112 +3822,112 @@
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
-      <c r="AS8" s="9" t="n">
+      <c r="AP8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AT8" s="9" t="n">
+      <c r="AW8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
       <c r="AY8" s="9" t="n"/>
       <c r="AZ8" s="9" t="n"/>
       <c r="BA8" s="12" t="n"/>
-      <c r="BB8" s="9" t="n">
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BC8" s="9" t="n">
+      <c r="BF8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="BD8" s="12">
-        <f>BC8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="12" t="n"/>
-      <c r="BH8" s="9" t="n">
+      <c r="BG8" s="12">
+        <f>BF8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BH8" s="9" t="n"/>
+      <c r="BI8" s="9" t="n"/>
+      <c r="BJ8" s="12" t="n"/>
+      <c r="BK8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BI8" s="9" t="n">
+      <c r="BL8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="BJ8" s="12">
-        <f>BI8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BK8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BM8" s="12">
         <f>BL8/$E$8</f>
@@ -3804,68 +3937,78 @@
         <v>7</v>
       </c>
       <c r="BO8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
         <v/>
       </c>
       <c r="BQ8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BR8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
         <v/>
       </c>
       <c r="BT8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
         <v/>
       </c>
       <c r="BW8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BX8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="BY8" s="12">
         <f>BX8/$E$8</f>
         <v/>
       </c>
       <c r="BZ8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="CA8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="CB8" s="12">
         <f>CA8/$E$8</f>
         <v/>
       </c>
       <c r="CC8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CD8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="CE8" s="12">
         <f>CD8/$E$8</f>
         <v/>
       </c>
-      <c r="CF8" s="9" t="n"/>
+      <c r="CF8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="CG8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="CH8" s="12">
         <f>CG8/$E$8</f>
+        <v/>
+      </c>
+      <c r="CI8" s="9" t="n"/>
+      <c r="CJ8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="CK8" s="12">
+        <f>CJ8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -3952,7 +4095,7 @@
         <v/>
       </c>
       <c r="X9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>1125</v>
@@ -3962,27 +4105,27 @@
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AC9" s="12">
         <f>AB9/$E$9</f>
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="AF9" s="12">
         <f>AE9/$E$9</f>
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="9" t="n">
         <v>1119</v>
@@ -3992,17 +4135,17 @@
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AL9" s="12">
         <f>AK9/$E$9</f>
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="9" t="n">
         <v>1117</v>
@@ -4011,124 +4154,134 @@
         <f>AN9/$E$9</f>
         <v/>
       </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
-      <c r="AS9" s="9" t="n">
+      <c r="AP9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AT9" s="9" t="n">
+      <c r="AW9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
       <c r="AY9" s="9" t="n"/>
       <c r="AZ9" s="9" t="n"/>
       <c r="BA9" s="12" t="n"/>
-      <c r="BB9" s="9" t="n">
+      <c r="BB9" s="9" t="n"/>
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
+      <c r="BE9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BC9" s="9" t="n">
+      <c r="BF9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="BD9" s="12">
-        <f>BC9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="12" t="n"/>
-      <c r="BH9" s="9" t="n">
+      <c r="BG9" s="12">
+        <f>BF9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BH9" s="9" t="n"/>
+      <c r="BI9" s="9" t="n"/>
+      <c r="BJ9" s="12" t="n"/>
+      <c r="BK9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BI9" s="9" t="n">
+      <c r="BL9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="BJ9" s="12">
-        <f>BI9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BK9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BM9" s="12">
         <f>BL9/$E$9</f>
         <v/>
       </c>
       <c r="BN9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BO9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
         <v/>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BR9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
         <v/>
       </c>
       <c r="BT9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
         <v/>
       </c>
       <c r="BW9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BX9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="BY9" s="12">
         <f>BX9/$E$9</f>
         <v/>
       </c>
       <c r="BZ9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="CA9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="CB9" s="12">
         <f>CA9/$E$9</f>
         <v/>
       </c>
       <c r="CC9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="CD9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="CE9" s="12">
         <f>CD9/$E$9</f>
         <v/>
       </c>
-      <c r="CF9" s="9" t="n"/>
+      <c r="CF9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="CG9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="CH9" s="12">
         <f>CG9/$E$9</f>
+        <v/>
+      </c>
+      <c r="CI9" s="9" t="n"/>
+      <c r="CJ9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CK9" s="12">
+        <f>CJ9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -4155,27 +4308,27 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>504</v>
@@ -4185,10 +4338,10 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
@@ -4205,7 +4358,7 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>502</v>
@@ -4215,37 +4368,37 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="9" t="n">
         <v>491</v>
@@ -4255,79 +4408,79 @@
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
-      <c r="AS10" s="9" t="n">
+      <c r="AP10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AS10" s="9" t="n"/>
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AT10" s="9" t="n">
+      <c r="AW10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
       <c r="AY10" s="9" t="n"/>
       <c r="AZ10" s="9" t="n"/>
       <c r="BA10" s="12" t="n"/>
-      <c r="BB10" s="9" t="n">
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n"/>
+      <c r="BD10" s="12" t="n"/>
+      <c r="BE10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BC10" s="9" t="n">
+      <c r="BF10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BD10" s="12">
-        <f>BC10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BE10" s="9" t="n"/>
-      <c r="BF10" s="9" t="n"/>
-      <c r="BG10" s="12" t="n"/>
-      <c r="BH10" s="9" t="n">
+      <c r="BG10" s="12">
+        <f>BF10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BH10" s="9" t="n"/>
+      <c r="BI10" s="9" t="n"/>
+      <c r="BJ10" s="12" t="n"/>
+      <c r="BK10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BI10" s="9" t="n">
+      <c r="BL10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="BJ10" s="12">
-        <f>BI10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BK10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BM10" s="12">
         <f>BL10/$E$10</f>
         <v/>
       </c>
       <c r="BN10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BO10" s="9" t="n">
         <v>462</v>
@@ -4340,58 +4493,68 @@
         <v>2</v>
       </c>
       <c r="BR10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BS10" s="12">
         <f>BR10/$E$10</f>
         <v/>
       </c>
       <c r="BT10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BV10" s="12">
         <f>BU10/$E$10</f>
         <v/>
       </c>
       <c r="BW10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BX10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BY10" s="12">
         <f>BX10/$E$10</f>
         <v/>
       </c>
       <c r="BZ10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="CA10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="CB10" s="12">
         <f>CA10/$E$10</f>
         <v/>
       </c>
       <c r="CC10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="CD10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="CE10" s="12">
         <f>CD10/$E$10</f>
         <v/>
       </c>
-      <c r="CF10" s="9" t="n"/>
+      <c r="CF10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="CG10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="CH10" s="12">
         <f>CG10/$E$10</f>
+        <v/>
+      </c>
+      <c r="CI10" s="9" t="n"/>
+      <c r="CJ10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="CK10" s="12">
+        <f>CJ10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -4488,7 +4651,7 @@
         <v/>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="9" t="n">
         <v>467</v>
@@ -4501,17 +4664,17 @@
         <v>1</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
         <v/>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AI11" s="12">
         <f>AH11/$E$11</f>
@@ -4537,60 +4700,60 @@
         <f>AN11/$E$11</f>
         <v/>
       </c>
-      <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="9" t="n"/>
-      <c r="AR11" s="12" t="n"/>
-      <c r="AS11" s="9" t="n">
+      <c r="AP11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AR11" s="12">
+        <f>AQ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AS11" s="9" t="n"/>
+      <c r="AT11" s="9" t="n"/>
+      <c r="AU11" s="12" t="n"/>
+      <c r="AV11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AT11" s="9" t="n">
+      <c r="AW11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AU11" s="12">
-        <f>AT11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n"/>
-      <c r="AX11" s="12" t="n"/>
+      <c r="AX11" s="12">
+        <f>AW11/$E$11</f>
+        <v/>
+      </c>
       <c r="AY11" s="9" t="n"/>
       <c r="AZ11" s="9" t="n"/>
       <c r="BA11" s="12" t="n"/>
-      <c r="BB11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" s="9" t="n">
+      <c r="BB11" s="9" t="n"/>
+      <c r="BC11" s="9" t="n"/>
+      <c r="BD11" s="12" t="n"/>
+      <c r="BE11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BD11" s="12">
-        <f>BC11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BE11" s="9" t="n"/>
-      <c r="BF11" s="9" t="n"/>
-      <c r="BG11" s="12" t="n"/>
-      <c r="BH11" s="9" t="n">
+      <c r="BG11" s="12">
+        <f>BF11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BH11" s="9" t="n"/>
+      <c r="BI11" s="9" t="n"/>
+      <c r="BJ11" s="12" t="n"/>
+      <c r="BK11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BI11" s="9" t="n">
+      <c r="BL11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="BJ11" s="12">
-        <f>BI11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BK11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BM11" s="12">
         <f>BL11/$E$11</f>
         <v/>
       </c>
       <c r="BN11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO11" s="9" t="n">
         <v>463</v>
@@ -4600,40 +4763,40 @@
         <v/>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BS11" s="12">
         <f>BR11/$E$11</f>
         <v/>
       </c>
       <c r="BT11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BV11" s="12">
         <f>BU11/$E$11</f>
         <v/>
       </c>
       <c r="BW11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BX11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BY11" s="12">
         <f>BX11/$E$11</f>
         <v/>
       </c>
       <c r="BZ11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CA11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="CB11" s="12">
         <f>CA11/$E$11</f>
@@ -4643,18 +4806,28 @@
         <v>2</v>
       </c>
       <c r="CD11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CE11" s="12">
         <f>CD11/$E$11</f>
         <v/>
       </c>
-      <c r="CF11" s="9" t="n"/>
+      <c r="CF11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="CG11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CH11" s="12">
         <f>CG11/$E$11</f>
+        <v/>
+      </c>
+      <c r="CI11" s="9" t="n"/>
+      <c r="CJ11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="CK11" s="12">
+        <f>CJ11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -4751,7 +4924,7 @@
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="9" t="n">
         <v>236</v>
@@ -4761,17 +4934,17 @@
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" s="9" t="n">
         <v>235</v>
@@ -4781,10 +4954,10 @@
         <v/>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL12" s="12">
         <f>AK12/$E$12</f>
@@ -4800,48 +4973,48 @@
         <f>AN12/$E$12</f>
         <v/>
       </c>
-      <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="9" t="n"/>
-      <c r="AR12" s="12" t="n"/>
-      <c r="AS12" s="9" t="n">
+      <c r="AP12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AR12" s="12">
+        <f>AQ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AS12" s="9" t="n"/>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="12" t="n"/>
+      <c r="AV12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AT12" s="9" t="n">
+      <c r="AW12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AU12" s="12">
-        <f>AT12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="12" t="n"/>
+      <c r="AX12" s="12">
+        <f>AW12/$E$12</f>
+        <v/>
+      </c>
       <c r="AY12" s="9" t="n"/>
       <c r="AZ12" s="9" t="n"/>
       <c r="BA12" s="12" t="n"/>
-      <c r="BB12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="9" t="n">
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="12" t="n"/>
+      <c r="BE12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="BD12" s="12">
-        <f>BC12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BE12" s="9" t="n"/>
-      <c r="BF12" s="9" t="n"/>
-      <c r="BG12" s="12" t="n"/>
-      <c r="BH12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="BJ12" s="12">
-        <f>BI12/$E$12</f>
-        <v/>
-      </c>
+      <c r="BG12" s="12">
+        <f>BF12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BH12" s="9" t="n"/>
+      <c r="BI12" s="9" t="n"/>
+      <c r="BJ12" s="12" t="n"/>
       <c r="BK12" s="9" t="n">
         <v>0</v>
       </c>
@@ -4883,7 +5056,7 @@
         <v/>
       </c>
       <c r="BW12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX12" s="9" t="n">
         <v>236</v>
@@ -4893,31 +5066,41 @@
         <v/>
       </c>
       <c r="BZ12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="CA12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="CB12" s="12">
         <f>CA12/$E$12</f>
         <v/>
       </c>
       <c r="CC12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="CD12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="CE12" s="12">
         <f>CD12/$E$12</f>
         <v/>
       </c>
-      <c r="CF12" s="9" t="n"/>
+      <c r="CF12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="CG12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="CH12" s="12">
         <f>CG12/$E$12</f>
+        <v/>
+      </c>
+      <c r="CI12" s="9" t="n"/>
+      <c r="CJ12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="CK12" s="12">
+        <f>CJ12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -4944,27 +5127,27 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>622</v>
@@ -4974,10 +5157,10 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
@@ -4994,7 +5177,7 @@
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>621</v>
@@ -5004,142 +5187,142 @@
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AN13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
-      <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="9" t="n"/>
-      <c r="AR13" s="12" t="n"/>
-      <c r="AS13" s="9" t="n">
+      <c r="AP13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AR13" s="12">
+        <f>AQ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AS13" s="9" t="n"/>
+      <c r="AT13" s="9" t="n"/>
+      <c r="AU13" s="12" t="n"/>
+      <c r="AV13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AT13" s="9" t="n">
+      <c r="AW13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AU13" s="12">
-        <f>AT13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n"/>
-      <c r="AX13" s="12" t="n"/>
+      <c r="AX13" s="12">
+        <f>AW13/$E$13</f>
+        <v/>
+      </c>
       <c r="AY13" s="9" t="n"/>
       <c r="AZ13" s="9" t="n"/>
       <c r="BA13" s="12" t="n"/>
-      <c r="BB13" s="9" t="n">
+      <c r="BB13" s="9" t="n"/>
+      <c r="BC13" s="9" t="n"/>
+      <c r="BD13" s="12" t="n"/>
+      <c r="BE13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="BC13" s="9" t="n">
+      <c r="BF13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="BD13" s="12">
-        <f>BC13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BE13" s="9" t="n"/>
-      <c r="BF13" s="9" t="n"/>
-      <c r="BG13" s="12" t="n"/>
-      <c r="BH13" s="9" t="n">
+      <c r="BG13" s="12">
+        <f>BF13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BH13" s="9" t="n"/>
+      <c r="BI13" s="9" t="n"/>
+      <c r="BJ13" s="12" t="n"/>
+      <c r="BK13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="BI13" s="9" t="n">
+      <c r="BL13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="BJ13" s="12">
-        <f>BI13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BK13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BL13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BM13" s="12">
         <f>BL13/$E$13</f>
         <v/>
       </c>
       <c r="BN13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BO13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
         <v/>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BR13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
         <v/>
       </c>
       <c r="BT13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
@@ -5149,38 +5332,48 @@
         <v>4</v>
       </c>
       <c r="BX13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BY13" s="12">
         <f>BX13/$E$13</f>
         <v/>
       </c>
       <c r="BZ13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="CA13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="CB13" s="12">
         <f>CA13/$E$13</f>
         <v/>
       </c>
       <c r="CC13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="CD13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="CE13" s="12">
         <f>CD13/$E$13</f>
         <v/>
       </c>
-      <c r="CF13" s="9" t="n"/>
+      <c r="CF13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="CG13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="CH13" s="12">
         <f>CG13/$E$13</f>
+        <v/>
+      </c>
+      <c r="CI13" s="9" t="n"/>
+      <c r="CJ13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="CK13" s="12">
+        <f>CJ13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -5207,27 +5400,27 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>1146</v>
@@ -5237,10 +5430,10 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
@@ -5257,7 +5450,7 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>1145</v>
@@ -5267,17 +5460,17 @@
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="9" t="n">
         <v>1142</v>
@@ -5287,122 +5480,122 @@
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
-      <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="9" t="n"/>
-      <c r="AR14" s="12" t="n"/>
-      <c r="AS14" s="9" t="n">
+      <c r="AP14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AR14" s="12">
+        <f>AQ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AS14" s="9" t="n"/>
+      <c r="AT14" s="9" t="n"/>
+      <c r="AU14" s="12" t="n"/>
+      <c r="AV14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AT14" s="9" t="n">
+      <c r="AW14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AU14" s="12">
-        <f>AT14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n"/>
-      <c r="AX14" s="12" t="n"/>
+      <c r="AX14" s="12">
+        <f>AW14/$E$14</f>
+        <v/>
+      </c>
       <c r="AY14" s="9" t="n"/>
       <c r="AZ14" s="9" t="n"/>
       <c r="BA14" s="12" t="n"/>
-      <c r="BB14" s="9" t="n">
+      <c r="BB14" s="9" t="n"/>
+      <c r="BC14" s="9" t="n"/>
+      <c r="BD14" s="12" t="n"/>
+      <c r="BE14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="BC14" s="9" t="n">
+      <c r="BF14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="BD14" s="12">
-        <f>BC14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BE14" s="9" t="n"/>
-      <c r="BF14" s="9" t="n"/>
-      <c r="BG14" s="12" t="n"/>
-      <c r="BH14" s="9" t="n">
+      <c r="BG14" s="12">
+        <f>BF14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BH14" s="9" t="n"/>
+      <c r="BI14" s="9" t="n"/>
+      <c r="BJ14" s="12" t="n"/>
+      <c r="BK14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BI14" s="9" t="n">
+      <c r="BL14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="BJ14" s="12">
-        <f>BI14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BK14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BM14" s="12">
         <f>BL14/$E$14</f>
         <v/>
       </c>
       <c r="BN14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BO14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BP14" s="12">
         <f>BO14/$E$14</f>
         <v/>
       </c>
       <c r="BQ14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BR14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BS14" s="12">
         <f>BR14/$E$14</f>
         <v/>
       </c>
       <c r="BT14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BU14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BV14" s="12">
         <f>BU14/$E$14</f>
@@ -5438,12 +5631,22 @@
         <f>CD14/$E$14</f>
         <v/>
       </c>
-      <c r="CF14" s="9" t="n"/>
+      <c r="CF14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CG14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CH14" s="12">
         <f>CG14/$E$14</f>
+        <v/>
+      </c>
+      <c r="CI14" s="9" t="n"/>
+      <c r="CJ14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" s="12">
+        <f>CJ14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -5470,10 +5673,10 @@
         <v>551</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H15" s="11">
         <f>G15/$E$15</f>
@@ -5520,7 +5723,7 @@
         <v/>
       </c>
       <c r="U15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>126</v>
@@ -5533,17 +5736,17 @@
         <v>1</v>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Z15" s="12">
         <f>Y15/$E$15</f>
         <v/>
       </c>
       <c r="AA15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AC15" s="12">
         <f>AB15/$E$15</f>
@@ -5560,7 +5763,7 @@
         <v/>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="9" t="n">
         <v>124</v>
@@ -5570,17 +5773,17 @@
         <v/>
       </c>
       <c r="AJ15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AL15" s="12">
         <f>AK15/$E$15</f>
         <v/>
       </c>
       <c r="AM15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN15" s="9" t="n">
         <v>121</v>
@@ -5589,53 +5792,53 @@
         <f>AN15/$E$15</f>
         <v/>
       </c>
-      <c r="AP15" s="9" t="n"/>
-      <c r="AQ15" s="9" t="n"/>
-      <c r="AR15" s="12" t="n"/>
-      <c r="AS15" s="9" t="n">
+      <c r="AP15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AR15" s="12">
+        <f>AQ15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AS15" s="9" t="n"/>
+      <c r="AT15" s="9" t="n"/>
+      <c r="AU15" s="12" t="n"/>
+      <c r="AV15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AT15" s="9" t="n">
+      <c r="AW15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AU15" s="12">
-        <f>AT15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AV15" s="9" t="n"/>
-      <c r="AW15" s="9" t="n"/>
-      <c r="AX15" s="12" t="n"/>
+      <c r="AX15" s="12">
+        <f>AW15/$E$15</f>
+        <v/>
+      </c>
       <c r="AY15" s="9" t="n"/>
       <c r="AZ15" s="9" t="n"/>
       <c r="BA15" s="12" t="n"/>
-      <c r="BB15" s="9" t="n">
+      <c r="BB15" s="9" t="n"/>
+      <c r="BC15" s="9" t="n"/>
+      <c r="BD15" s="12" t="n"/>
+      <c r="BE15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BC15" s="9" t="n">
+      <c r="BF15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="BD15" s="12">
-        <f>BC15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BE15" s="9" t="n"/>
-      <c r="BF15" s="9" t="n"/>
-      <c r="BG15" s="12" t="n"/>
-      <c r="BH15" s="9" t="n">
+      <c r="BG15" s="12">
+        <f>BF15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BH15" s="9" t="n"/>
+      <c r="BI15" s="9" t="n"/>
+      <c r="BJ15" s="12" t="n"/>
+      <c r="BK15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BI15" s="9" t="n">
+      <c r="BL15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="BJ15" s="12">
-        <f>BI15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BK15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BM15" s="12">
         <f>BL15/$E$15</f>
@@ -5645,24 +5848,24 @@
         <v>3</v>
       </c>
       <c r="BO15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BP15" s="12">
         <f>BO15/$E$15</f>
         <v/>
       </c>
       <c r="BQ15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BS15" s="12">
         <f>BR15/$E$15</f>
         <v/>
       </c>
       <c r="BT15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BU15" s="9" t="n">
         <v>76</v>
@@ -5672,10 +5875,10 @@
         <v/>
       </c>
       <c r="BW15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BX15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="BY15" s="12">
         <f>BX15/$E$15</f>
@@ -5701,12 +5904,22 @@
         <f>CD15/$E$15</f>
         <v/>
       </c>
-      <c r="CF15" s="9" t="n"/>
+      <c r="CF15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CG15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CH15" s="12">
         <f>CG15/$E$15</f>
+        <v/>
+      </c>
+      <c r="CI15" s="9" t="n"/>
+      <c r="CJ15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" s="12">
+        <f>CJ15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -5852,51 +6065,58 @@
         <f>AN16/$E$16</f>
         <v/>
       </c>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="9" t="n"/>
-      <c r="AR16" s="12" t="n"/>
-      <c r="AS16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" s="9" t="n">
+      <c r="AP16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AU16" s="12">
-        <f>AT16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
+      <c r="AR16" s="12">
+        <f>AQ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AS16" s="9" t="n"/>
+      <c r="AT16" s="9" t="n"/>
+      <c r="AU16" s="12" t="n"/>
+      <c r="AV16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
       <c r="AY16" s="9" t="n"/>
       <c r="AZ16" s="9" t="n"/>
       <c r="BA16" s="12" t="n"/>
-      <c r="BB16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" s="9" t="n">
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="12" t="n"/>
+      <c r="BE16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BD16" s="12">
-        <f>BC16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BE16" s="9" t="n"/>
-      <c r="BF16" s="9" t="n"/>
-      <c r="BG16" s="12" t="n"/>
-      <c r="BH16" s="9" t="n">
+      <c r="BG16" s="12">
+        <f>BF16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BH16" s="9" t="n"/>
+      <c r="BI16" s="9" t="n"/>
+      <c r="BJ16" s="12" t="n"/>
+      <c r="BK16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BI16" s="9" t="n">
+      <c r="BL16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BJ16" s="12">
-        <f>BI16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n"/>
-      <c r="BM16" s="12" t="n"/>
+      <c r="BM16" s="12">
+        <f>BL16/$E$16</f>
+        <v/>
+      </c>
       <c r="BN16" s="9" t="n"/>
       <c r="BO16" s="9" t="n"/>
       <c r="BP16" s="12" t="n"/>
@@ -5916,11 +6136,14 @@
       <c r="CD16" s="9" t="n"/>
       <c r="CE16" s="12" t="n"/>
       <c r="CF16" s="9" t="n"/>
-      <c r="CG16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" s="12">
-        <f>CG16/$E$16</f>
+      <c r="CG16" s="9" t="n"/>
+      <c r="CH16" s="12" t="n"/>
+      <c r="CI16" s="9" t="n"/>
+      <c r="CJ16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" s="12">
+        <f>CJ16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -6027,6 +6250,9 @@
       <c r="CF17" s="9" t="n"/>
       <c r="CG17" s="9" t="n"/>
       <c r="CH17" s="12" t="n"/>
+      <c r="CI17" s="9" t="n"/>
+      <c r="CJ17" s="9" t="n"/>
+      <c r="CK17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6051,46 +6277,48 @@
         <v>830</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
-      <c r="R18" s="9" t="n"/>
+      <c r="R18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="S18" s="9" t="n">
         <v>139</v>
       </c>
@@ -6099,8 +6327,13 @@
         <v/>
       </c>
       <c r="U18" s="9" t="n"/>
-      <c r="V18" s="9" t="n"/>
-      <c r="W18" s="12" t="n"/>
+      <c r="V18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="W18" s="12">
+        <f>V18/$E$18</f>
+        <v/>
+      </c>
       <c r="X18" s="9" t="n"/>
       <c r="Y18" s="9" t="n"/>
       <c r="Z18" s="12" t="n"/>
@@ -6164,9 +6397,12 @@
       <c r="CF18" s="9" t="n"/>
       <c r="CG18" s="9" t="n"/>
       <c r="CH18" s="12" t="n"/>
+      <c r="CI18" s="9" t="n"/>
+      <c r="CJ18" s="9" t="n"/>
+      <c r="CK18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -6181,6 +6417,7 @@
     <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="CI3:CK3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="CC3:CE3"/>
@@ -6205,7 +6442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH18"/>
+  <dimension ref="A1:CK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6294,6 +6531,9 @@
     <col width="9" customWidth="1" min="84" max="84"/>
     <col width="9" customWidth="1" min="85" max="85"/>
     <col width="9" customWidth="1" min="86" max="86"/>
+    <col width="9" customWidth="1" min="87" max="87"/>
+    <col width="9" customWidth="1" min="88" max="88"/>
+    <col width="9" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6312,84 +6552,87 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -6822,6 +7065,21 @@
         </is>
       </c>
       <c r="CH4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CI4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CJ4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CK4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -6860,7 +7118,7 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>302</v>
@@ -6870,10 +7128,10 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
@@ -6900,7 +7158,7 @@
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>298</v>
@@ -6913,115 +7171,122 @@
         <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="12" t="n"/>
-      <c r="AG5" s="9" t="n">
+      <c r="AD5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="AF5" s="12">
+        <f>AE5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AG5" s="9" t="n"/>
+      <c r="AH5" s="9" t="n"/>
+      <c r="AI5" s="12" t="n"/>
+      <c r="AJ5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AH5" s="9" t="n">
+      <c r="AK5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="AI5" s="12">
-        <f>AH5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
       <c r="AM5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AO5" s="12">
         <f>AN5/$E$5</f>
         <v/>
       </c>
       <c r="AP5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AQ5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AR5" s="12">
         <f>AQ5/$E$5</f>
         <v/>
       </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
-      <c r="AV5" s="9" t="n">
+      <c r="AS5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AT5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="9" t="n"/>
+      <c r="AX5" s="12" t="n"/>
+      <c r="AY5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AW5" s="9" t="n">
+      <c r="AZ5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="AX5" s="12">
-        <f>AW5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AZ5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="BA5" s="12">
         <f>AZ5/$E$5</f>
         <v/>
       </c>
-      <c r="BB5" s="9" t="n"/>
-      <c r="BC5" s="9" t="n"/>
-      <c r="BD5" s="12" t="n"/>
-      <c r="BE5" s="9" t="n">
+      <c r="BB5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BC5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="BD5" s="12">
+        <f>BC5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BE5" s="9" t="n"/>
+      <c r="BF5" s="9" t="n"/>
+      <c r="BG5" s="12" t="n"/>
+      <c r="BH5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="BF5" s="9" t="n">
+      <c r="BI5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="BG5" s="12">
-        <f>BF5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BH5" s="9" t="n"/>
-      <c r="BI5" s="9" t="n"/>
-      <c r="BJ5" s="12" t="n"/>
+      <c r="BJ5" s="12">
+        <f>BI5/$E$5</f>
+        <v/>
+      </c>
       <c r="BK5" s="9" t="n"/>
-      <c r="BL5" s="9" t="n">
+      <c r="BL5" s="9" t="n"/>
+      <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n"/>
+      <c r="BO5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="BM5" s="12">
-        <f>BL5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BN5" s="9" t="n"/>
-      <c r="BO5" s="9" t="n"/>
-      <c r="BP5" s="12" t="n"/>
+      <c r="BP5" s="12">
+        <f>BO5/$E$5</f>
+        <v/>
+      </c>
       <c r="BQ5" s="9" t="n"/>
       <c r="BR5" s="9" t="n"/>
       <c r="BS5" s="12" t="n"/>
@@ -7040,6 +7305,9 @@
       <c r="CF5" s="9" t="n"/>
       <c r="CG5" s="9" t="n"/>
       <c r="CH5" s="12" t="n"/>
+      <c r="CI5" s="9" t="n"/>
+      <c r="CJ5" s="9" t="n"/>
+      <c r="CK5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -7064,17 +7332,17 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>953</v>
@@ -7084,20 +7352,20 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
@@ -7114,7 +7382,7 @@
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>950</v>
@@ -7124,118 +7392,125 @@
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="12" t="n"/>
-      <c r="AG6" s="9" t="n">
+      <c r="AD6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="AF6" s="12">
+        <f>AE6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AG6" s="9" t="n"/>
+      <c r="AH6" s="9" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AK6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="AI6" s="12">
-        <f>AH6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
-      <c r="AV6" s="9" t="n">
+      <c r="AS6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="AZ6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="BA6" s="12">
         <f>AZ6/$E$6</f>
         <v/>
       </c>
-      <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="12" t="n"/>
-      <c r="BE6" s="9" t="n">
+      <c r="BB6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="BD6" s="12">
+        <f>BC6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BE6" s="9" t="n"/>
+      <c r="BF6" s="9" t="n"/>
+      <c r="BG6" s="12" t="n"/>
+      <c r="BH6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BF6" s="9" t="n">
+      <c r="BI6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BG6" s="12">
-        <f>BF6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n"/>
-      <c r="BJ6" s="12" t="n"/>
+      <c r="BJ6" s="12">
+        <f>BI6/$E$6</f>
+        <v/>
+      </c>
       <c r="BK6" s="9" t="n"/>
-      <c r="BL6" s="9" t="n">
+      <c r="BL6" s="9" t="n"/>
+      <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="BM6" s="12">
-        <f>BL6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n"/>
-      <c r="BP6" s="12" t="n"/>
+      <c r="BP6" s="12">
+        <f>BO6/$E$6</f>
+        <v/>
+      </c>
       <c r="BQ6" s="9" t="n"/>
       <c r="BR6" s="9" t="n"/>
       <c r="BS6" s="12" t="n"/>
@@ -7254,6 +7529,9 @@
       <c r="CF6" s="9" t="n"/>
       <c r="CG6" s="9" t="n"/>
       <c r="CH6" s="12" t="n"/>
+      <c r="CI6" s="9" t="n"/>
+      <c r="CJ6" s="9" t="n"/>
+      <c r="CK6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -7278,7 +7556,7 @@
         <v>1500</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>48</v>
@@ -7288,10 +7566,10 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
@@ -7357,99 +7635,106 @@
         <f>AB7/$E$7</f>
         <v/>
       </c>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="12" t="n"/>
-      <c r="AG7" s="9" t="n">
+      <c r="AD7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="AF7" s="12">
+        <f>AE7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AG7" s="9" t="n"/>
+      <c r="AH7" s="9" t="n"/>
+      <c r="AI7" s="12" t="n"/>
+      <c r="AJ7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="AH7" s="9" t="n">
+      <c r="AK7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="AI7" s="12">
-        <f>AH7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="9" t="n">
+      <c r="AS7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AW7" s="9" t="n">
+      <c r="AT7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="BA7" s="12">
         <f>AZ7/$E$7</f>
         <v/>
       </c>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="12" t="n"/>
-      <c r="BE7" s="9" t="n">
+      <c r="BB7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="BD7" s="12">
+        <f>BC7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BE7" s="9" t="n"/>
+      <c r="BF7" s="9" t="n"/>
+      <c r="BG7" s="12" t="n"/>
+      <c r="BH7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BF7" s="9" t="n">
+      <c r="BI7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="BG7" s="12">
-        <f>BF7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BH7" s="9" t="n"/>
-      <c r="BI7" s="9" t="n"/>
-      <c r="BJ7" s="12" t="n"/>
+      <c r="BJ7" s="12">
+        <f>BI7/$E$7</f>
+        <v/>
+      </c>
       <c r="BK7" s="9" t="n"/>
-      <c r="BL7" s="9" t="n">
+      <c r="BL7" s="9" t="n"/>
+      <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BM7" s="12">
-        <f>BL7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BN7" s="9" t="n"/>
-      <c r="BO7" s="9" t="n"/>
-      <c r="BP7" s="12" t="n"/>
+      <c r="BP7" s="12">
+        <f>BO7/$E$7</f>
+        <v/>
+      </c>
       <c r="BQ7" s="9" t="n"/>
       <c r="BR7" s="9" t="n"/>
       <c r="BS7" s="12" t="n"/>
@@ -7468,6 +7753,9 @@
       <c r="CF7" s="9" t="n"/>
       <c r="CG7" s="9" t="n"/>
       <c r="CH7" s="12" t="n"/>
+      <c r="CI7" s="9" t="n"/>
+      <c r="CJ7" s="9" t="n"/>
+      <c r="CK7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -7492,17 +7780,17 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1056</v>
@@ -7512,10 +7800,10 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
@@ -7542,7 +7830,7 @@
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>1054</v>
@@ -7552,17 +7840,17 @@
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="Z8" s="12">
         <f>Y8/$E$8</f>
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="9" t="n">
         <v>1052</v>
@@ -7571,99 +7859,106 @@
         <f>AB8/$E$8</f>
         <v/>
       </c>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="12" t="n"/>
-      <c r="AG8" s="9" t="n">
+      <c r="AD8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH8" s="9" t="n">
+      <c r="AE8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="AF8" s="12">
+        <f>AE8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AG8" s="9" t="n"/>
+      <c r="AH8" s="9" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="AI8" s="12">
-        <f>AH8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AQ8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
-      <c r="AV8" s="9" t="n">
+      <c r="AS8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AW8" s="9" t="n">
+      <c r="AZ8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="BA8" s="12">
         <f>AZ8/$E$8</f>
         <v/>
       </c>
-      <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="12" t="n"/>
-      <c r="BE8" s="9" t="n">
+      <c r="BB8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BD8" s="12">
+        <f>BC8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BE8" s="9" t="n"/>
+      <c r="BF8" s="9" t="n"/>
+      <c r="BG8" s="12" t="n"/>
+      <c r="BH8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BF8" s="9" t="n">
+      <c r="BI8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="BG8" s="12">
-        <f>BF8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="9" t="n"/>
-      <c r="BJ8" s="12" t="n"/>
+      <c r="BJ8" s="12">
+        <f>BI8/$E$8</f>
+        <v/>
+      </c>
       <c r="BK8" s="9" t="n"/>
-      <c r="BL8" s="9" t="n">
+      <c r="BL8" s="9" t="n"/>
+      <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="BM8" s="12">
-        <f>BL8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n"/>
-      <c r="BP8" s="12" t="n"/>
+      <c r="BP8" s="12">
+        <f>BO8/$E$8</f>
+        <v/>
+      </c>
       <c r="BQ8" s="9" t="n"/>
       <c r="BR8" s="9" t="n"/>
       <c r="BS8" s="12" t="n"/>
@@ -7682,6 +7977,9 @@
       <c r="CF8" s="9" t="n"/>
       <c r="CG8" s="9" t="n"/>
       <c r="CH8" s="12" t="n"/>
+      <c r="CI8" s="9" t="n"/>
+      <c r="CJ8" s="9" t="n"/>
+      <c r="CK8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -7785,19 +8083,19 @@
         <f>AB9/$E$9</f>
         <v/>
       </c>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="9" t="n">
+      <c r="AD9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="AI9" s="12">
-        <f>AH9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AF9" s="12">
+        <f>AE9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AG9" s="9" t="n"/>
+      <c r="AH9" s="9" t="n"/>
+      <c r="AI9" s="12" t="n"/>
       <c r="AJ9" s="9" t="n">
         <v>0</v>
       </c>
@@ -7809,7 +8107,7 @@
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="9" t="n">
         <v>845</v>
@@ -7819,28 +8117,28 @@
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AR9" s="12">
         <f>AQ9/$E$9</f>
         <v/>
       </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
-      <c r="AV9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="9" t="n">
+      <c r="AS9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
       <c r="AY9" s="9" t="n">
         <v>0</v>
       </c>
@@ -7851,33 +8149,40 @@
         <f>AZ9/$E$9</f>
         <v/>
       </c>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="12" t="n"/>
-      <c r="BE9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" s="9" t="n">
+      <c r="BB9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BG9" s="12">
-        <f>BF9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n"/>
-      <c r="BJ9" s="12" t="n"/>
+      <c r="BD9" s="12">
+        <f>BC9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BE9" s="9" t="n"/>
+      <c r="BF9" s="9" t="n"/>
+      <c r="BG9" s="12" t="n"/>
+      <c r="BH9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="BJ9" s="12">
+        <f>BI9/$E$9</f>
+        <v/>
+      </c>
       <c r="BK9" s="9" t="n"/>
-      <c r="BL9" s="9" t="n">
+      <c r="BL9" s="9" t="n"/>
+      <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BM9" s="12">
-        <f>BL9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n"/>
-      <c r="BP9" s="12" t="n"/>
+      <c r="BP9" s="12">
+        <f>BO9/$E$9</f>
+        <v/>
+      </c>
       <c r="BQ9" s="9" t="n"/>
       <c r="BR9" s="9" t="n"/>
       <c r="BS9" s="12" t="n"/>
@@ -7896,6 +8201,9 @@
       <c r="CF9" s="9" t="n"/>
       <c r="CG9" s="9" t="n"/>
       <c r="CH9" s="12" t="n"/>
+      <c r="CI9" s="9" t="n"/>
+      <c r="CJ9" s="9" t="n"/>
+      <c r="CK9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -7923,7 +8231,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
@@ -7933,17 +8241,17 @@
         <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
@@ -7970,7 +8278,7 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>1418</v>
@@ -7980,118 +8288,125 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="9" t="n">
+      <c r="AD10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="AF10" s="12">
+        <f>AE10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AG10" s="9" t="n"/>
+      <c r="AH10" s="9" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AH10" s="9" t="n">
+      <c r="AK10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="AI10" s="12">
-        <f>AH10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="9" t="n">
+      <c r="AS10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AW10" s="9" t="n">
+      <c r="AZ10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="AX10" s="12">
-        <f>AW10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="BA10" s="12">
         <f>AZ10/$E$10</f>
         <v/>
       </c>
-      <c r="BB10" s="9" t="n"/>
-      <c r="BC10" s="9" t="n"/>
-      <c r="BD10" s="12" t="n"/>
-      <c r="BE10" s="9" t="n">
+      <c r="BB10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BF10" s="9" t="n">
+      <c r="BC10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="BD10" s="12">
+        <f>BC10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BE10" s="9" t="n"/>
+      <c r="BF10" s="9" t="n"/>
+      <c r="BG10" s="12" t="n"/>
+      <c r="BH10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="BG10" s="12">
-        <f>BF10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BH10" s="9" t="n"/>
-      <c r="BI10" s="9" t="n"/>
-      <c r="BJ10" s="12" t="n"/>
+      <c r="BJ10" s="12">
+        <f>BI10/$E$10</f>
+        <v/>
+      </c>
       <c r="BK10" s="9" t="n"/>
-      <c r="BL10" s="9" t="n">
+      <c r="BL10" s="9" t="n"/>
+      <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="BM10" s="12">
-        <f>BL10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BN10" s="9" t="n"/>
-      <c r="BO10" s="9" t="n"/>
-      <c r="BP10" s="12" t="n"/>
+      <c r="BP10" s="12">
+        <f>BO10/$E$10</f>
+        <v/>
+      </c>
       <c r="BQ10" s="9" t="n"/>
       <c r="BR10" s="9" t="n"/>
       <c r="BS10" s="12" t="n"/>
@@ -8110,6 +8425,9 @@
       <c r="CF10" s="9" t="n"/>
       <c r="CG10" s="9" t="n"/>
       <c r="CH10" s="12" t="n"/>
+      <c r="CI10" s="9" t="n"/>
+      <c r="CJ10" s="9" t="n"/>
+      <c r="CK10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -8134,10 +8452,10 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
@@ -8147,27 +8465,27 @@
         <v>3</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
@@ -8184,7 +8502,7 @@
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>992</v>
@@ -8194,10 +8512,10 @@
         <v/>
       </c>
       <c r="X11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="Z11" s="12">
         <f>Y11/$E$11</f>
@@ -8213,99 +8531,106 @@
         <f>AB11/$E$11</f>
         <v/>
       </c>
-      <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="9" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="9" t="n">
+      <c r="AD11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AF11" s="12">
+        <f>AE11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AG11" s="9" t="n"/>
+      <c r="AH11" s="9" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" s="9" t="n">
+      <c r="AK11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="AI11" s="12">
-        <f>AH11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="AL11" s="12">
         <f>AK11/$E$11</f>
         <v/>
       </c>
       <c r="AM11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AN11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="AO11" s="12">
         <f>AN11/$E$11</f>
         <v/>
       </c>
       <c r="AP11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
-      <c r="AV11" s="9" t="n">
+      <c r="AS11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AW11" s="9" t="n">
+      <c r="AZ11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="AX11" s="12">
-        <f>AW11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="BA11" s="12">
         <f>AZ11/$E$11</f>
         <v/>
       </c>
-      <c r="BB11" s="9" t="n"/>
-      <c r="BC11" s="9" t="n"/>
-      <c r="BD11" s="12" t="n"/>
-      <c r="BE11" s="9" t="n">
+      <c r="BB11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="BD11" s="12">
+        <f>BC11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BE11" s="9" t="n"/>
+      <c r="BF11" s="9" t="n"/>
+      <c r="BG11" s="12" t="n"/>
+      <c r="BH11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BF11" s="9" t="n">
+      <c r="BI11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="BG11" s="12">
-        <f>BF11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BH11" s="9" t="n"/>
-      <c r="BI11" s="9" t="n"/>
-      <c r="BJ11" s="12" t="n"/>
+      <c r="BJ11" s="12">
+        <f>BI11/$E$11</f>
+        <v/>
+      </c>
       <c r="BK11" s="9" t="n"/>
-      <c r="BL11" s="9" t="n">
+      <c r="BL11" s="9" t="n"/>
+      <c r="BM11" s="12" t="n"/>
+      <c r="BN11" s="9" t="n"/>
+      <c r="BO11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="BM11" s="12">
-        <f>BL11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BN11" s="9" t="n"/>
-      <c r="BO11" s="9" t="n"/>
-      <c r="BP11" s="12" t="n"/>
+      <c r="BP11" s="12">
+        <f>BO11/$E$11</f>
+        <v/>
+      </c>
       <c r="BQ11" s="9" t="n"/>
       <c r="BR11" s="9" t="n"/>
       <c r="BS11" s="12" t="n"/>
@@ -8324,6 +8649,9 @@
       <c r="CF11" s="9" t="n"/>
       <c r="CG11" s="9" t="n"/>
       <c r="CH11" s="12" t="n"/>
+      <c r="CI11" s="9" t="n"/>
+      <c r="CJ11" s="9" t="n"/>
+      <c r="CK11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -8348,10 +8676,10 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
@@ -8361,17 +8689,17 @@
         <v>1</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N12" s="12">
         <f>M12/$E$12</f>
@@ -8398,7 +8726,7 @@
         <v/>
       </c>
       <c r="U12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>737</v>
@@ -8408,118 +8736,125 @@
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="Z12" s="12">
         <f>Y12/$E$12</f>
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AC12" s="12">
         <f>AB12/$E$12</f>
         <v/>
       </c>
-      <c r="AD12" s="9" t="n"/>
-      <c r="AE12" s="9" t="n"/>
-      <c r="AF12" s="12" t="n"/>
-      <c r="AG12" s="9" t="n">
+      <c r="AD12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="AF12" s="12">
+        <f>AE12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AG12" s="9" t="n"/>
+      <c r="AH12" s="9" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AH12" s="9" t="n">
+      <c r="AK12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="AI12" s="12">
-        <f>AH12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AJ12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="AL12" s="12">
         <f>AK12/$E$12</f>
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AN12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="AO12" s="12">
         <f>AN12/$E$12</f>
         <v/>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AQ12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AR12" s="12">
         <f>AQ12/$E$12</f>
         <v/>
       </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
-      <c r="AV12" s="9" t="n">
+      <c r="AS12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="12" t="n"/>
+      <c r="AY12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AW12" s="9" t="n">
+      <c r="AZ12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="AX12" s="12">
-        <f>AW12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AY12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="BA12" s="12">
         <f>AZ12/$E$12</f>
         <v/>
       </c>
-      <c r="BB12" s="9" t="n"/>
-      <c r="BC12" s="9" t="n"/>
-      <c r="BD12" s="12" t="n"/>
-      <c r="BE12" s="9" t="n">
+      <c r="BB12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="BD12" s="12">
+        <f>BC12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BE12" s="9" t="n"/>
+      <c r="BF12" s="9" t="n"/>
+      <c r="BG12" s="12" t="n"/>
+      <c r="BH12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BF12" s="9" t="n">
+      <c r="BI12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="BG12" s="12">
-        <f>BF12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BH12" s="9" t="n"/>
-      <c r="BI12" s="9" t="n"/>
-      <c r="BJ12" s="12" t="n"/>
+      <c r="BJ12" s="12">
+        <f>BI12/$E$12</f>
+        <v/>
+      </c>
       <c r="BK12" s="9" t="n"/>
-      <c r="BL12" s="9" t="n">
+      <c r="BL12" s="9" t="n"/>
+      <c r="BM12" s="12" t="n"/>
+      <c r="BN12" s="9" t="n"/>
+      <c r="BO12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="BM12" s="12">
-        <f>BL12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BN12" s="9" t="n"/>
-      <c r="BO12" s="9" t="n"/>
-      <c r="BP12" s="12" t="n"/>
+      <c r="BP12" s="12">
+        <f>BO12/$E$12</f>
+        <v/>
+      </c>
       <c r="BQ12" s="9" t="n"/>
       <c r="BR12" s="9" t="n"/>
       <c r="BS12" s="12" t="n"/>
@@ -8538,6 +8873,9 @@
       <c r="CF12" s="9" t="n"/>
       <c r="CG12" s="9" t="n"/>
       <c r="CH12" s="12" t="n"/>
+      <c r="CI12" s="9" t="n"/>
+      <c r="CJ12" s="9" t="n"/>
+      <c r="CK12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -8572,7 +8910,7 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>1394</v>
@@ -8582,20 +8920,20 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
@@ -8632,7 +8970,7 @@
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="9" t="n">
         <v>1391</v>
@@ -8641,99 +8979,106 @@
         <f>AB13/$E$13</f>
         <v/>
       </c>
-      <c r="AD13" s="9" t="n"/>
-      <c r="AE13" s="9" t="n"/>
-      <c r="AF13" s="12" t="n"/>
-      <c r="AG13" s="9" t="n">
+      <c r="AD13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AH13" s="9" t="n">
+      <c r="AE13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="AF13" s="12">
+        <f>AE13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AG13" s="9" t="n"/>
+      <c r="AH13" s="9" t="n"/>
+      <c r="AI13" s="12" t="n"/>
+      <c r="AJ13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="AI13" s="12">
-        <f>AH13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AJ13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
       <c r="AP13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="9" t="n">
+      <c r="AS13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AV13" s="9" t="n"/>
+      <c r="AW13" s="9" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AW13" s="9" t="n">
+      <c r="AZ13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="AX13" s="12">
-        <f>AW13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="BA13" s="12">
         <f>AZ13/$E$13</f>
         <v/>
       </c>
-      <c r="BB13" s="9" t="n"/>
-      <c r="BC13" s="9" t="n"/>
-      <c r="BD13" s="12" t="n"/>
-      <c r="BE13" s="9" t="n">
+      <c r="BB13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="BD13" s="12">
+        <f>BC13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BE13" s="9" t="n"/>
+      <c r="BF13" s="9" t="n"/>
+      <c r="BG13" s="12" t="n"/>
+      <c r="BH13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BF13" s="9" t="n">
+      <c r="BI13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="BG13" s="12">
-        <f>BF13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BH13" s="9" t="n"/>
-      <c r="BI13" s="9" t="n"/>
-      <c r="BJ13" s="12" t="n"/>
+      <c r="BJ13" s="12">
+        <f>BI13/$E$13</f>
+        <v/>
+      </c>
       <c r="BK13" s="9" t="n"/>
-      <c r="BL13" s="9" t="n">
+      <c r="BL13" s="9" t="n"/>
+      <c r="BM13" s="12" t="n"/>
+      <c r="BN13" s="9" t="n"/>
+      <c r="BO13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="BM13" s="12">
-        <f>BL13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BN13" s="9" t="n"/>
-      <c r="BO13" s="9" t="n"/>
-      <c r="BP13" s="12" t="n"/>
+      <c r="BP13" s="12">
+        <f>BO13/$E$13</f>
+        <v/>
+      </c>
       <c r="BQ13" s="9" t="n"/>
       <c r="BR13" s="9" t="n"/>
       <c r="BS13" s="12" t="n"/>
@@ -8752,6 +9097,9 @@
       <c r="CF13" s="9" t="n"/>
       <c r="CG13" s="9" t="n"/>
       <c r="CH13" s="12" t="n"/>
+      <c r="CI13" s="9" t="n"/>
+      <c r="CJ13" s="9" t="n"/>
+      <c r="CK13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -8779,24 +9127,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>904</v>
@@ -8806,10 +9154,10 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
@@ -8846,7 +9194,7 @@
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="9" t="n">
         <v>902</v>
@@ -8855,21 +9203,21 @@
         <f>AB14/$E$14</f>
         <v/>
       </c>
-      <c r="AD14" s="9" t="n"/>
-      <c r="AE14" s="9" t="n"/>
-      <c r="AF14" s="12" t="n"/>
-      <c r="AG14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="AI14" s="12">
-        <f>AH14/$E$14</f>
-        <v/>
-      </c>
+      <c r="AD14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="AF14" s="12">
+        <f>AE14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="12" t="n"/>
       <c r="AJ14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="9" t="n">
         <v>898</v>
@@ -8879,75 +9227,82 @@
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
-      <c r="AV14" s="9" t="n">
+      <c r="AS14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AW14" s="9" t="n">
+      <c r="AZ14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="AX14" s="12">
-        <f>AW14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="BA14" s="12">
         <f>AZ14/$E$14</f>
         <v/>
       </c>
-      <c r="BB14" s="9" t="n"/>
-      <c r="BC14" s="9" t="n"/>
-      <c r="BD14" s="12" t="n"/>
-      <c r="BE14" s="9" t="n">
+      <c r="BB14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BF14" s="9" t="n">
+      <c r="BC14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="BD14" s="12">
+        <f>BC14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BE14" s="9" t="n"/>
+      <c r="BF14" s="9" t="n"/>
+      <c r="BG14" s="12" t="n"/>
+      <c r="BH14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="BG14" s="12">
-        <f>BF14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BH14" s="9" t="n"/>
-      <c r="BI14" s="9" t="n"/>
-      <c r="BJ14" s="12" t="n"/>
+      <c r="BJ14" s="12">
+        <f>BI14/$E$14</f>
+        <v/>
+      </c>
       <c r="BK14" s="9" t="n"/>
-      <c r="BL14" s="9" t="n">
+      <c r="BL14" s="9" t="n"/>
+      <c r="BM14" s="12" t="n"/>
+      <c r="BN14" s="9" t="n"/>
+      <c r="BO14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="BM14" s="12">
-        <f>BL14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BN14" s="9" t="n"/>
-      <c r="BO14" s="9" t="n"/>
-      <c r="BP14" s="12" t="n"/>
+      <c r="BP14" s="12">
+        <f>BO14/$E$14</f>
+        <v/>
+      </c>
       <c r="BQ14" s="9" t="n"/>
       <c r="BR14" s="9" t="n"/>
       <c r="BS14" s="12" t="n"/>
@@ -8966,6 +9321,9 @@
       <c r="CF14" s="9" t="n"/>
       <c r="CG14" s="9" t="n"/>
       <c r="CH14" s="12" t="n"/>
+      <c r="CI14" s="9" t="n"/>
+      <c r="CJ14" s="9" t="n"/>
+      <c r="CK14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -9070,6 +9428,9 @@
       <c r="CF15" s="9" t="n"/>
       <c r="CG15" s="9" t="n"/>
       <c r="CH15" s="12" t="n"/>
+      <c r="CI15" s="9" t="n"/>
+      <c r="CJ15" s="9" t="n"/>
+      <c r="CK15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -9094,27 +9455,27 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H16" s="11">
         <f>G16/$E$16</f>
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="K16" s="12">
         <f>J16/$E$16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>717</v>
@@ -9124,10 +9485,10 @@
         <v/>
       </c>
       <c r="O16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/$E$16</f>
@@ -9144,7 +9505,7 @@
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>715</v>
@@ -9154,118 +9515,125 @@
         <v/>
       </c>
       <c r="X16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z16" s="12">
         <f>Y16/$E$16</f>
         <v/>
       </c>
       <c r="AA16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="AC16" s="12">
         <f>AB16/$E$16</f>
         <v/>
       </c>
-      <c r="AD16" s="9" t="n"/>
-      <c r="AE16" s="9" t="n"/>
-      <c r="AF16" s="12" t="n"/>
-      <c r="AG16" s="9" t="n">
+      <c r="AD16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="AF16" s="12">
+        <f>AE16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AH16" s="9" t="n">
+      <c r="AK16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="AI16" s="12">
-        <f>AH16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="AL16" s="12">
         <f>AK16/$E$16</f>
         <v/>
       </c>
       <c r="AM16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AN16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AO16" s="12">
         <f>AN16/$E$16</f>
         <v/>
       </c>
       <c r="AP16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AQ16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AR16" s="12">
         <f>AQ16/$E$16</f>
         <v/>
       </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="9" t="n">
+      <c r="AS16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AW16" s="9" t="n">
+      <c r="AZ16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="AX16" s="12">
-        <f>AW16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="BA16" s="12">
         <f>AZ16/$E$16</f>
         <v/>
       </c>
-      <c r="BB16" s="9" t="n"/>
-      <c r="BC16" s="9" t="n"/>
-      <c r="BD16" s="12" t="n"/>
-      <c r="BE16" s="9" t="n">
+      <c r="BB16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="BD16" s="12">
+        <f>BC16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BE16" s="9" t="n"/>
+      <c r="BF16" s="9" t="n"/>
+      <c r="BG16" s="12" t="n"/>
+      <c r="BH16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="BF16" s="9" t="n">
+      <c r="BI16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="BG16" s="12">
-        <f>BF16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BH16" s="9" t="n"/>
-      <c r="BI16" s="9" t="n"/>
-      <c r="BJ16" s="12" t="n"/>
+      <c r="BJ16" s="12">
+        <f>BI16/$E$16</f>
+        <v/>
+      </c>
       <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n">
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n"/>
+      <c r="BO16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="BM16" s="12">
-        <f>BL16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n"/>
-      <c r="BP16" s="12" t="n"/>
+      <c r="BP16" s="12">
+        <f>BO16/$E$16</f>
+        <v/>
+      </c>
       <c r="BQ16" s="9" t="n"/>
       <c r="BR16" s="9" t="n"/>
       <c r="BS16" s="12" t="n"/>
@@ -9284,6 +9652,9 @@
       <c r="CF16" s="9" t="n"/>
       <c r="CG16" s="9" t="n"/>
       <c r="CH16" s="12" t="n"/>
+      <c r="CI16" s="9" t="n"/>
+      <c r="CJ16" s="9" t="n"/>
+      <c r="CK16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -9311,24 +9682,24 @@
         <v>1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H17" s="11">
         <f>G17/$E$17</f>
         <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K17" s="12">
         <f>J17/$E$17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
         <v>388</v>
@@ -9338,20 +9709,20 @@
         <v/>
       </c>
       <c r="O17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/$E$17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T17" s="12">
         <f>S17/$E$17</f>
@@ -9368,7 +9739,7 @@
         <v/>
       </c>
       <c r="X17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>385</v>
@@ -9378,108 +9749,115 @@
         <v/>
       </c>
       <c r="AA17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AC17" s="12">
         <f>AB17/$E$17</f>
         <v/>
       </c>
-      <c r="AD17" s="9" t="n"/>
-      <c r="AE17" s="9" t="n"/>
-      <c r="AF17" s="12" t="n"/>
-      <c r="AG17" s="9" t="n">
+      <c r="AD17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AH17" s="9" t="n">
+      <c r="AE17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="AF17" s="12">
+        <f>AE17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n"/>
+      <c r="AI17" s="12" t="n"/>
+      <c r="AJ17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="AI17" s="12">
-        <f>AH17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="AL17" s="12">
         <f>AK17/$E$17</f>
         <v/>
       </c>
       <c r="AM17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AN17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AO17" s="12">
         <f>AN17/$E$17</f>
         <v/>
       </c>
       <c r="AP17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AR17" s="12">
         <f>AQ17/$E$17</f>
         <v/>
       </c>
-      <c r="AS17" s="9" t="n"/>
-      <c r="AT17" s="9" t="n"/>
-      <c r="AU17" s="12" t="n"/>
-      <c r="AV17" s="9" t="n">
+      <c r="AS17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AU17" s="12">
+        <f>AT17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AV17" s="9" t="n"/>
+      <c r="AW17" s="9" t="n"/>
+      <c r="AX17" s="12" t="n"/>
+      <c r="AY17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AW17" s="9" t="n">
+      <c r="AZ17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="AX17" s="12">
-        <f>AW17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AY17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="BA17" s="12">
         <f>AZ17/$E$17</f>
         <v/>
       </c>
-      <c r="BB17" s="9" t="n"/>
-      <c r="BC17" s="9" t="n"/>
-      <c r="BD17" s="12" t="n"/>
-      <c r="BE17" s="9" t="n">
+      <c r="BB17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="BD17" s="12">
+        <f>BC17/$E$17</f>
+        <v/>
+      </c>
+      <c r="BE17" s="9" t="n"/>
+      <c r="BF17" s="9" t="n"/>
+      <c r="BG17" s="12" t="n"/>
+      <c r="BH17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BF17" s="9" t="n">
+      <c r="BI17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="BG17" s="12">
-        <f>BF17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BH17" s="9" t="n"/>
-      <c r="BI17" s="9" t="n"/>
-      <c r="BJ17" s="12" t="n"/>
+      <c r="BJ17" s="12">
+        <f>BI17/$E$17</f>
+        <v/>
+      </c>
       <c r="BK17" s="9" t="n"/>
-      <c r="BL17" s="9" t="n">
+      <c r="BL17" s="9" t="n"/>
+      <c r="BM17" s="12" t="n"/>
+      <c r="BN17" s="9" t="n"/>
+      <c r="BO17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="BM17" s="12">
-        <f>BL17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BN17" s="9" t="n"/>
-      <c r="BO17" s="9" t="n"/>
-      <c r="BP17" s="12" t="n"/>
+      <c r="BP17" s="12">
+        <f>BO17/$E$17</f>
+        <v/>
+      </c>
       <c r="BQ17" s="9" t="n"/>
       <c r="BR17" s="9" t="n"/>
       <c r="BS17" s="12" t="n"/>
@@ -9498,6 +9876,9 @@
       <c r="CF17" s="9" t="n"/>
       <c r="CG17" s="9" t="n"/>
       <c r="CH17" s="12" t="n"/>
+      <c r="CI17" s="9" t="n"/>
+      <c r="CJ17" s="9" t="n"/>
+      <c r="CK17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -9522,20 +9903,20 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
@@ -9572,7 +9953,7 @@
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>292</v>
@@ -9582,118 +9963,125 @@
         <v/>
       </c>
       <c r="X18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z18" s="12">
         <f>Y18/$E$18</f>
         <v/>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AC18" s="12">
         <f>AB18/$E$18</f>
         <v/>
       </c>
-      <c r="AD18" s="9" t="n"/>
-      <c r="AE18" s="9" t="n"/>
-      <c r="AF18" s="12" t="n"/>
-      <c r="AG18" s="9" t="n">
+      <c r="AD18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="AF18" s="12">
+        <f>AE18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="9" t="n"/>
+      <c r="AI18" s="12" t="n"/>
+      <c r="AJ18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AH18" s="9" t="n">
+      <c r="AK18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="AI18" s="12">
-        <f>AH18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="AL18" s="12">
         <f>AK18/$E$18</f>
         <v/>
       </c>
       <c r="AM18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AO18" s="12">
         <f>AN18/$E$18</f>
         <v/>
       </c>
       <c r="AP18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AR18" s="12">
         <f>AQ18/$E$18</f>
         <v/>
       </c>
-      <c r="AS18" s="9" t="n"/>
-      <c r="AT18" s="9" t="n"/>
-      <c r="AU18" s="12" t="n"/>
-      <c r="AV18" s="9" t="n">
+      <c r="AS18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AU18" s="12">
+        <f>AT18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AV18" s="9" t="n"/>
+      <c r="AW18" s="9" t="n"/>
+      <c r="AX18" s="12" t="n"/>
+      <c r="AY18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AW18" s="9" t="n">
+      <c r="AZ18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="AX18" s="12">
-        <f>AW18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AY18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="BA18" s="12">
         <f>AZ18/$E$18</f>
         <v/>
       </c>
-      <c r="BB18" s="9" t="n"/>
-      <c r="BC18" s="9" t="n"/>
-      <c r="BD18" s="12" t="n"/>
-      <c r="BE18" s="9" t="n">
+      <c r="BB18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="BD18" s="12">
+        <f>BC18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BE18" s="9" t="n"/>
+      <c r="BF18" s="9" t="n"/>
+      <c r="BG18" s="12" t="n"/>
+      <c r="BH18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BF18" s="9" t="n">
+      <c r="BI18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="BG18" s="12">
-        <f>BF18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BH18" s="9" t="n"/>
-      <c r="BI18" s="9" t="n"/>
-      <c r="BJ18" s="12" t="n"/>
+      <c r="BJ18" s="12">
+        <f>BI18/$E$18</f>
+        <v/>
+      </c>
       <c r="BK18" s="9" t="n"/>
-      <c r="BL18" s="9" t="n">
+      <c r="BL18" s="9" t="n"/>
+      <c r="BM18" s="12" t="n"/>
+      <c r="BN18" s="9" t="n"/>
+      <c r="BO18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="BM18" s="12">
-        <f>BL18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BN18" s="9" t="n"/>
-      <c r="BO18" s="9" t="n"/>
-      <c r="BP18" s="12" t="n"/>
+      <c r="BP18" s="12">
+        <f>BO18/$E$18</f>
+        <v/>
+      </c>
       <c r="BQ18" s="9" t="n"/>
       <c r="BR18" s="9" t="n"/>
       <c r="BS18" s="12" t="n"/>
@@ -9712,9 +10100,12 @@
       <c r="CF18" s="9" t="n"/>
       <c r="CG18" s="9" t="n"/>
       <c r="CH18" s="12" t="n"/>
+      <c r="CI18" s="9" t="n"/>
+      <c r="CJ18" s="9" t="n"/>
+      <c r="CK18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -9729,6 +10120,7 @@
     <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="CI3:CK3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="CC3:CE3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -591,7 +591,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 20/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 21/08/2026</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 20/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 21/08/2026</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 20/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 21/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,9 @@
     <col width="9" customWidth="1" min="87" max="87"/>
     <col width="9" customWidth="1" min="88" max="88"/>
     <col width="9" customWidth="1" min="89" max="89"/>
+    <col width="9" customWidth="1" min="90" max="90"/>
+    <col width="9" customWidth="1" min="91" max="91"/>
+    <col width="9" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -597,87 +600,90 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1125,6 +1131,21 @@
         </is>
       </c>
       <c r="CK4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CL4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CM4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CN4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1223,7 +1244,7 @@
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="9" t="n">
         <v>43</v>
@@ -1233,17 +1254,17 @@
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="9" t="n">
         <v>42</v>
@@ -1256,49 +1277,56 @@
         <v>1</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
       <c r="AM5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AN5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AO5" s="12">
         <f>AN5/$E$5</f>
         <v/>
       </c>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="12" t="n"/>
-      <c r="AS5" s="9" t="n">
+      <c r="AP5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR5" s="12">
+        <f>AQ5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AS5" s="9" t="n"/>
+      <c r="AT5" s="9" t="n"/>
+      <c r="AU5" s="12" t="n"/>
+      <c r="AV5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AT5" s="9" t="n">
+      <c r="AW5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AU5" s="12">
-        <f>AT5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n"/>
-      <c r="AX5" s="12" t="n"/>
+      <c r="AX5" s="12">
+        <f>AW5/$E$5</f>
+        <v/>
+      </c>
       <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n">
+      <c r="AZ5" s="9" t="n"/>
+      <c r="BA5" s="12" t="n"/>
+      <c r="BB5" s="9" t="n"/>
+      <c r="BC5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="BA5" s="12">
-        <f>AZ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BB5" s="9" t="n"/>
-      <c r="BC5" s="9" t="n"/>
-      <c r="BD5" s="12" t="n"/>
+      <c r="BD5" s="12">
+        <f>BC5/$E$5</f>
+        <v/>
+      </c>
       <c r="BE5" s="9" t="n"/>
       <c r="BF5" s="9" t="n"/>
       <c r="BG5" s="12" t="n"/>
@@ -1332,6 +1360,9 @@
       <c r="CI5" s="9" t="n"/>
       <c r="CJ5" s="9" t="n"/>
       <c r="CK5" s="12" t="n"/>
+      <c r="CL5" s="9" t="n"/>
+      <c r="CM5" s="9" t="n"/>
+      <c r="CN5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1366,7 +1397,7 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>35</v>
@@ -1376,17 +1407,17 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>34</v>
@@ -1396,10 +1427,10 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
@@ -1475,33 +1506,40 @@
         <f>AN6/$E$6</f>
         <v/>
       </c>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="12" t="n"/>
-      <c r="AS6" s="9" t="n">
+      <c r="AP6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AR6" s="12">
+        <f>AQ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AS6" s="9" t="n"/>
+      <c r="AT6" s="9" t="n"/>
+      <c r="AU6" s="12" t="n"/>
+      <c r="AV6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AT6" s="9" t="n">
+      <c r="AW6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AU6" s="12">
-        <f>AT6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
       <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n">
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="12" t="n"/>
+      <c r="BD6" s="12">
+        <f>BC6/$E$6</f>
+        <v/>
+      </c>
       <c r="BE6" s="9" t="n"/>
       <c r="BF6" s="9" t="n"/>
       <c r="BG6" s="12" t="n"/>
@@ -1535,6 +1573,9 @@
       <c r="CI6" s="9" t="n"/>
       <c r="CJ6" s="9" t="n"/>
       <c r="CK6" s="12" t="n"/>
+      <c r="CL6" s="9" t="n"/>
+      <c r="CM6" s="9" t="n"/>
+      <c r="CN6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1569,7 +1610,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>48</v>
@@ -1582,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
@@ -1592,17 +1633,17 @@
         <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
@@ -1639,7 +1680,7 @@
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="9" t="n">
         <v>45</v>
@@ -1649,62 +1690,69 @@
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="9" t="n"/>
-      <c r="AR7" s="12" t="n"/>
-      <c r="AS7" s="9" t="n">
+      <c r="AP7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AR7" s="12">
+        <f>AQ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AS7" s="9" t="n"/>
+      <c r="AT7" s="9" t="n"/>
+      <c r="AU7" s="12" t="n"/>
+      <c r="AV7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AT7" s="9" t="n">
+      <c r="AW7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AU7" s="12">
-        <f>AT7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
       <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n">
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="12" t="n"/>
+      <c r="BD7" s="12">
+        <f>BC7/$E$7</f>
+        <v/>
+      </c>
       <c r="BE7" s="9" t="n"/>
       <c r="BF7" s="9" t="n"/>
       <c r="BG7" s="12" t="n"/>
@@ -1738,6 +1786,9 @@
       <c r="CI7" s="9" t="n"/>
       <c r="CJ7" s="9" t="n"/>
       <c r="CK7" s="12" t="n"/>
+      <c r="CL7" s="9" t="n"/>
+      <c r="CM7" s="9" t="n"/>
+      <c r="CN7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1881,33 +1932,40 @@
         <f>AN8/$E$8</f>
         <v/>
       </c>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="9" t="n"/>
-      <c r="AR8" s="12" t="n"/>
-      <c r="AS8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="9" t="n">
+      <c r="AP8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AU8" s="12">
-        <f>AT8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
+      <c r="AR8" s="12">
+        <f>AQ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AS8" s="9" t="n"/>
+      <c r="AT8" s="9" t="n"/>
+      <c r="AU8" s="12" t="n"/>
+      <c r="AV8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
       <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n">
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="12" t="n"/>
+      <c r="BD8" s="12">
+        <f>BC8/$E$8</f>
+        <v/>
+      </c>
       <c r="BE8" s="9" t="n"/>
       <c r="BF8" s="9" t="n"/>
       <c r="BG8" s="12" t="n"/>
@@ -1941,6 +1999,9 @@
       <c r="CI8" s="9" t="n"/>
       <c r="CJ8" s="9" t="n"/>
       <c r="CK8" s="12" t="n"/>
+      <c r="CL8" s="9" t="n"/>
+      <c r="CM8" s="9" t="n"/>
+      <c r="CN8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2075,7 +2136,7 @@
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="9" t="n">
         <v>1</v>
@@ -2084,33 +2145,40 @@
         <f>AN9/$E$9</f>
         <v/>
       </c>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="12" t="n"/>
-      <c r="AS9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="12">
-        <f>AT9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
+      <c r="AP9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="12">
+        <f>AQ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AS9" s="9" t="n"/>
+      <c r="AT9" s="9" t="n"/>
+      <c r="AU9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
       <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
       <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="12" t="n"/>
+      <c r="BC9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="12">
+        <f>BC9/$E$9</f>
+        <v/>
+      </c>
       <c r="BE9" s="9" t="n"/>
       <c r="BF9" s="9" t="n"/>
       <c r="BG9" s="12" t="n"/>
@@ -2144,6 +2212,9 @@
       <c r="CI9" s="9" t="n"/>
       <c r="CJ9" s="9" t="n"/>
       <c r="CK9" s="12" t="n"/>
+      <c r="CL9" s="9" t="n"/>
+      <c r="CM9" s="9" t="n"/>
+      <c r="CN9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2168,7 +2239,7 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>335</v>
@@ -2181,54 +2252,54 @@
         <v>8</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>311</v>
@@ -2238,69 +2309,76 @@
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="9" t="n"/>
-      <c r="AR10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AR10" s="12">
+        <f>AQ10/$E$10</f>
+        <v/>
+      </c>
       <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n">
+      <c r="AT10" s="9" t="n"/>
+      <c r="AU10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AU10" s="12">
-        <f>AT10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
       <c r="AY10" s="9" t="n"/>
       <c r="AZ10" s="9" t="n"/>
       <c r="BA10" s="12" t="n"/>
@@ -2340,9 +2418,12 @@
       <c r="CI10" s="9" t="n"/>
       <c r="CJ10" s="9" t="n"/>
       <c r="CK10" s="12" t="n"/>
+      <c r="CL10" s="9" t="n"/>
+      <c r="CM10" s="9" t="n"/>
+      <c r="CN10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -2366,6 +2447,7 @@
     <mergeCell ref="BE3:BG3"/>
     <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="CL3:CN3"/>
     <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="F3:H3"/>
@@ -2382,7 +2464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK18"/>
+  <dimension ref="A1:CN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2474,6 +2556,9 @@
     <col width="9" customWidth="1" min="87" max="87"/>
     <col width="9" customWidth="1" min="88" max="88"/>
     <col width="9" customWidth="1" min="89" max="89"/>
+    <col width="9" customWidth="1" min="90" max="90"/>
+    <col width="9" customWidth="1" min="91" max="91"/>
+    <col width="9" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2492,87 +2577,90 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -3020,6 +3108,21 @@
         </is>
       </c>
       <c r="CK4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CL4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CM4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CN4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -3048,7 +3151,7 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>183</v>
@@ -3058,27 +3161,27 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>178</v>
@@ -3088,10 +3191,10 @@
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
@@ -3118,7 +3221,7 @@
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="9" t="n">
         <v>177</v>
@@ -3127,17 +3230,24 @@
         <f>AB5/$E$5</f>
         <v/>
       </c>
-      <c r="AD5" s="9" t="n"/>
+      <c r="AD5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="AE5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
       <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
+      <c r="AH5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
       <c r="AJ5" s="9" t="n"/>
       <c r="AK5" s="9" t="n"/>
       <c r="AL5" s="12" t="n"/>
@@ -3192,6 +3302,9 @@
       <c r="CI5" s="9" t="n"/>
       <c r="CJ5" s="9" t="n"/>
       <c r="CK5" s="12" t="n"/>
+      <c r="CL5" s="9" t="n"/>
+      <c r="CM5" s="9" t="n"/>
+      <c r="CN5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -3216,7 +3329,7 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>344</v>
@@ -3226,40 +3339,40 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
@@ -3276,7 +3389,7 @@
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>335</v>
@@ -3286,183 +3399,193 @@
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
-      <c r="AV6" s="9" t="n">
+      <c r="AS6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="AZ6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
       <c r="BB6" s="9" t="n"/>
       <c r="BC6" s="9" t="n"/>
       <c r="BD6" s="12" t="n"/>
-      <c r="BE6" s="9" t="n">
+      <c r="BE6" s="9" t="n"/>
+      <c r="BF6" s="9" t="n"/>
+      <c r="BG6" s="12" t="n"/>
+      <c r="BH6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BF6" s="9" t="n">
+      <c r="BI6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="BG6" s="12">
-        <f>BF6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n"/>
-      <c r="BJ6" s="12" t="n"/>
-      <c r="BK6" s="9" t="n">
+      <c r="BJ6" s="12">
+        <f>BI6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BK6" s="9" t="n"/>
+      <c r="BL6" s="9" t="n"/>
+      <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BL6" s="9" t="n">
+      <c r="BO6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="BM6" s="12">
-        <f>BL6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BN6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BP6" s="12">
         <f>BO6/$E$6</f>
         <v/>
       </c>
       <c r="BQ6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BR6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
         <v/>
       </c>
       <c r="BT6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BU6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
         <v/>
       </c>
       <c r="BW6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BX6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="BY6" s="12">
         <f>BX6/$E$6</f>
         <v/>
       </c>
       <c r="BZ6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="CA6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="CB6" s="12">
         <f>CA6/$E$6</f>
         <v/>
       </c>
       <c r="CC6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CD6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="CE6" s="12">
         <f>CD6/$E$6</f>
         <v/>
       </c>
       <c r="CF6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CG6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="CH6" s="12">
         <f>CG6/$E$6</f>
         <v/>
       </c>
-      <c r="CI6" s="9" t="n"/>
+      <c r="CI6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="CJ6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="CK6" s="12">
         <f>CJ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="CL6" s="9" t="n"/>
+      <c r="CM6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="CN6" s="12">
+        <f>CM6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -3489,7 +3612,7 @@
         <v>996</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>123</v>
@@ -3499,10 +3622,10 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K7" s="12">
         <f>J7/$E$7</f>
@@ -3529,7 +3652,7 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>120</v>
@@ -3539,10 +3662,10 @@
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
@@ -3559,7 +3682,7 @@
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="9" t="n">
         <v>119</v>
@@ -3572,109 +3695,109 @@
         <v>3</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AF7" s="12">
         <f>AE7/$E$7</f>
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="9" t="n">
+      <c r="AS7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AW7" s="9" t="n">
+      <c r="AZ7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
       <c r="BB7" s="9" t="n"/>
       <c r="BC7" s="9" t="n"/>
       <c r="BD7" s="12" t="n"/>
-      <c r="BE7" s="9" t="n">
+      <c r="BE7" s="9" t="n"/>
+      <c r="BF7" s="9" t="n"/>
+      <c r="BG7" s="12" t="n"/>
+      <c r="BH7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BF7" s="9" t="n">
+      <c r="BI7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="BG7" s="12">
-        <f>BF7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BH7" s="9" t="n"/>
-      <c r="BI7" s="9" t="n"/>
-      <c r="BJ7" s="12" t="n"/>
-      <c r="BK7" s="9" t="n">
+      <c r="BJ7" s="12">
+        <f>BI7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BK7" s="9" t="n"/>
+      <c r="BL7" s="9" t="n"/>
+      <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BL7" s="9" t="n">
+      <c r="BO7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="BM7" s="12">
-        <f>BL7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BN7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BP7" s="12">
         <f>BO7/$E$7</f>
         <v/>
       </c>
       <c r="BQ7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BR7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
@@ -3684,58 +3807,68 @@
         <v>6</v>
       </c>
       <c r="BU7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
         <v/>
       </c>
       <c r="BW7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BX7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="BY7" s="12">
         <f>BX7/$E$7</f>
         <v/>
       </c>
       <c r="BZ7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CA7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="CB7" s="12">
         <f>CA7/$E$7</f>
         <v/>
       </c>
       <c r="CC7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CD7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CE7" s="12">
         <f>CD7/$E$7</f>
         <v/>
       </c>
       <c r="CF7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CG7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CH7" s="12">
         <f>CG7/$E$7</f>
         <v/>
       </c>
-      <c r="CI7" s="9" t="n"/>
+      <c r="CI7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="CJ7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CK7" s="12">
         <f>CJ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="CL7" s="9" t="n"/>
+      <c r="CM7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CN7" s="12">
+        <f>CM7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -3762,7 +3895,7 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1003</v>
@@ -3772,17 +3905,17 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>1000</v>
@@ -3792,10 +3925,10 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
@@ -3822,7 +3955,7 @@
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>998</v>
@@ -3832,112 +3965,112 @@
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AQ8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
-      <c r="AV8" s="9" t="n">
+      <c r="AS8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AW8" s="9" t="n">
+      <c r="AZ8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
       <c r="BB8" s="9" t="n"/>
       <c r="BC8" s="9" t="n"/>
       <c r="BD8" s="12" t="n"/>
-      <c r="BE8" s="9" t="n">
+      <c r="BE8" s="9" t="n"/>
+      <c r="BF8" s="9" t="n"/>
+      <c r="BG8" s="12" t="n"/>
+      <c r="BH8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BF8" s="9" t="n">
+      <c r="BI8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="BG8" s="12">
-        <f>BF8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="9" t="n"/>
-      <c r="BJ8" s="12" t="n"/>
-      <c r="BK8" s="9" t="n">
+      <c r="BJ8" s="12">
+        <f>BI8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BK8" s="9" t="n"/>
+      <c r="BL8" s="9" t="n"/>
+      <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BL8" s="9" t="n">
+      <c r="BO8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="BM8" s="12">
-        <f>BL8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BN8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BP8" s="12">
         <f>BO8/$E$8</f>
@@ -3947,68 +4080,78 @@
         <v>7</v>
       </c>
       <c r="BR8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
         <v/>
       </c>
       <c r="BT8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
         <v/>
       </c>
       <c r="BW8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BX8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="BY8" s="12">
         <f>BX8/$E$8</f>
         <v/>
       </c>
       <c r="BZ8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CA8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="CB8" s="12">
         <f>CA8/$E$8</f>
         <v/>
       </c>
       <c r="CC8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="CD8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="CE8" s="12">
         <f>CD8/$E$8</f>
         <v/>
       </c>
       <c r="CF8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CG8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="CH8" s="12">
         <f>CG8/$E$8</f>
         <v/>
       </c>
-      <c r="CI8" s="9" t="n"/>
+      <c r="CI8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="CJ8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="CK8" s="12">
         <f>CJ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="CL8" s="9" t="n"/>
+      <c r="CM8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="CN8" s="12">
+        <f>CM8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -4105,7 +4248,7 @@
         <v/>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="9" t="n">
         <v>1125</v>
@@ -4115,27 +4258,27 @@
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AF9" s="12">
         <f>AE9/$E$9</f>
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="AI9" s="12">
         <f>AH9/$E$9</f>
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="9" t="n">
         <v>1119</v>
@@ -4145,17 +4288,17 @@
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AO9" s="12">
         <f>AN9/$E$9</f>
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="9" t="n">
         <v>1117</v>
@@ -4164,124 +4307,134 @@
         <f>AQ9/$E$9</f>
         <v/>
       </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
-      <c r="AV9" s="9" t="n">
+      <c r="AS9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AW9" s="9" t="n">
+      <c r="AZ9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
       <c r="BB9" s="9" t="n"/>
       <c r="BC9" s="9" t="n"/>
       <c r="BD9" s="12" t="n"/>
-      <c r="BE9" s="9" t="n">
+      <c r="BE9" s="9" t="n"/>
+      <c r="BF9" s="9" t="n"/>
+      <c r="BG9" s="12" t="n"/>
+      <c r="BH9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BF9" s="9" t="n">
+      <c r="BI9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="BG9" s="12">
-        <f>BF9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n"/>
-      <c r="BJ9" s="12" t="n"/>
-      <c r="BK9" s="9" t="n">
+      <c r="BJ9" s="12">
+        <f>BI9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BK9" s="9" t="n"/>
+      <c r="BL9" s="9" t="n"/>
+      <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BL9" s="9" t="n">
+      <c r="BO9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="BM9" s="12">
-        <f>BL9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BN9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BP9" s="12">
         <f>BO9/$E$9</f>
         <v/>
       </c>
       <c r="BQ9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
         <v/>
       </c>
       <c r="BT9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
         <v/>
       </c>
       <c r="BW9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BX9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="BY9" s="12">
         <f>BX9/$E$9</f>
         <v/>
       </c>
       <c r="BZ9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CA9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="CB9" s="12">
         <f>CA9/$E$9</f>
         <v/>
       </c>
       <c r="CC9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="CD9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="CE9" s="12">
         <f>CD9/$E$9</f>
         <v/>
       </c>
       <c r="CF9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="CG9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="CH9" s="12">
         <f>CG9/$E$9</f>
         <v/>
       </c>
-      <c r="CI9" s="9" t="n"/>
+      <c r="CI9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="CJ9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="CK9" s="12">
         <f>CJ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="CL9" s="9" t="n"/>
+      <c r="CM9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CN9" s="12">
+        <f>CM9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -4308,7 +4461,7 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>509</v>
@@ -4318,27 +4471,27 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>504</v>
@@ -4348,10 +4501,10 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
@@ -4368,7 +4521,7 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>502</v>
@@ -4378,37 +4531,37 @@
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="9" t="n">
         <v>491</v>
@@ -4418,79 +4571,79 @@
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="9" t="n">
+      <c r="AS10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AV10" s="9" t="n"/>
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AW10" s="9" t="n">
+      <c r="AZ10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="AX10" s="12">
-        <f>AW10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
       <c r="BB10" s="9" t="n"/>
       <c r="BC10" s="9" t="n"/>
       <c r="BD10" s="12" t="n"/>
-      <c r="BE10" s="9" t="n">
+      <c r="BE10" s="9" t="n"/>
+      <c r="BF10" s="9" t="n"/>
+      <c r="BG10" s="12" t="n"/>
+      <c r="BH10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BF10" s="9" t="n">
+      <c r="BI10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BG10" s="12">
-        <f>BF10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BH10" s="9" t="n"/>
-      <c r="BI10" s="9" t="n"/>
-      <c r="BJ10" s="12" t="n"/>
-      <c r="BK10" s="9" t="n">
+      <c r="BJ10" s="12">
+        <f>BI10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BK10" s="9" t="n"/>
+      <c r="BL10" s="9" t="n"/>
+      <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BL10" s="9" t="n">
+      <c r="BO10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="BM10" s="12">
-        <f>BL10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BN10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BP10" s="12">
         <f>BO10/$E$10</f>
         <v/>
       </c>
       <c r="BQ10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR10" s="9" t="n">
         <v>462</v>
@@ -4503,58 +4656,68 @@
         <v>2</v>
       </c>
       <c r="BU10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BV10" s="12">
         <f>BU10/$E$10</f>
         <v/>
       </c>
       <c r="BW10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BX10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BY10" s="12">
         <f>BX10/$E$10</f>
         <v/>
       </c>
       <c r="BZ10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CA10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="CB10" s="12">
         <f>CA10/$E$10</f>
         <v/>
       </c>
       <c r="CC10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="CD10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="CE10" s="12">
         <f>CD10/$E$10</f>
         <v/>
       </c>
       <c r="CF10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="CG10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="CH10" s="12">
         <f>CG10/$E$10</f>
         <v/>
       </c>
-      <c r="CI10" s="9" t="n"/>
+      <c r="CI10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="CJ10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="CK10" s="12">
         <f>CJ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="CL10" s="9" t="n"/>
+      <c r="CM10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="CN10" s="12">
+        <f>CM10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -4661,7 +4824,7 @@
         <v/>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="9" t="n">
         <v>467</v>
@@ -4674,17 +4837,17 @@
         <v>1</v>
       </c>
       <c r="AH11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AI11" s="12">
         <f>AH11/$E$11</f>
         <v/>
       </c>
       <c r="AJ11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL11" s="12">
         <f>AK11/$E$11</f>
@@ -4710,60 +4873,60 @@
         <f>AQ11/$E$11</f>
         <v/>
       </c>
-      <c r="AS11" s="9" t="n"/>
-      <c r="AT11" s="9" t="n"/>
-      <c r="AU11" s="12" t="n"/>
-      <c r="AV11" s="9" t="n">
+      <c r="AS11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AU11" s="12">
+        <f>AT11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AV11" s="9" t="n"/>
+      <c r="AW11" s="9" t="n"/>
+      <c r="AX11" s="12" t="n"/>
+      <c r="AY11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AW11" s="9" t="n">
+      <c r="AZ11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AX11" s="12">
-        <f>AW11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n"/>
-      <c r="BA11" s="12" t="n"/>
+      <c r="BA11" s="12">
+        <f>AZ11/$E$11</f>
+        <v/>
+      </c>
       <c r="BB11" s="9" t="n"/>
       <c r="BC11" s="9" t="n"/>
       <c r="BD11" s="12" t="n"/>
-      <c r="BE11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" s="9" t="n">
+      <c r="BE11" s="9" t="n"/>
+      <c r="BF11" s="9" t="n"/>
+      <c r="BG11" s="12" t="n"/>
+      <c r="BH11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BG11" s="12">
-        <f>BF11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BH11" s="9" t="n"/>
-      <c r="BI11" s="9" t="n"/>
-      <c r="BJ11" s="12" t="n"/>
-      <c r="BK11" s="9" t="n">
+      <c r="BJ11" s="12">
+        <f>BI11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BK11" s="9" t="n"/>
+      <c r="BL11" s="9" t="n"/>
+      <c r="BM11" s="12" t="n"/>
+      <c r="BN11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BL11" s="9" t="n">
+      <c r="BO11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="BM11" s="12">
-        <f>BL11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BN11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BP11" s="12">
         <f>BO11/$E$11</f>
         <v/>
       </c>
       <c r="BQ11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR11" s="9" t="n">
         <v>463</v>
@@ -4773,40 +4936,40 @@
         <v/>
       </c>
       <c r="BT11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BV11" s="12">
         <f>BU11/$E$11</f>
         <v/>
       </c>
       <c r="BW11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BX11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="BY11" s="12">
         <f>BX11/$E$11</f>
         <v/>
       </c>
       <c r="BZ11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CA11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CB11" s="12">
         <f>CA11/$E$11</f>
         <v/>
       </c>
       <c r="CC11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="CE11" s="12">
         <f>CD11/$E$11</f>
@@ -4816,18 +4979,28 @@
         <v>2</v>
       </c>
       <c r="CG11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CH11" s="12">
         <f>CG11/$E$11</f>
         <v/>
       </c>
-      <c r="CI11" s="9" t="n"/>
+      <c r="CI11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="CJ11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CK11" s="12">
         <f>CJ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="CL11" s="9" t="n"/>
+      <c r="CM11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="CN11" s="12">
+        <f>CM11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -4934,7 +5107,7 @@
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="9" t="n">
         <v>236</v>
@@ -4944,17 +5117,17 @@
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AI12" s="12">
         <f>AH12/$E$12</f>
         <v/>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="9" t="n">
         <v>235</v>
@@ -4964,10 +5137,10 @@
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO12" s="12">
         <f>AN12/$E$12</f>
@@ -4983,48 +5156,48 @@
         <f>AQ12/$E$12</f>
         <v/>
       </c>
-      <c r="AS12" s="9" t="n"/>
-      <c r="AT12" s="9" t="n"/>
-      <c r="AU12" s="12" t="n"/>
-      <c r="AV12" s="9" t="n">
+      <c r="AS12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AU12" s="12">
+        <f>AT12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="12" t="n"/>
+      <c r="AY12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AW12" s="9" t="n">
+      <c r="AZ12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="AX12" s="12">
-        <f>AW12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n"/>
-      <c r="BA12" s="12" t="n"/>
+      <c r="BA12" s="12">
+        <f>AZ12/$E$12</f>
+        <v/>
+      </c>
       <c r="BB12" s="9" t="n"/>
       <c r="BC12" s="9" t="n"/>
       <c r="BD12" s="12" t="n"/>
-      <c r="BE12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" s="9" t="n">
+      <c r="BE12" s="9" t="n"/>
+      <c r="BF12" s="9" t="n"/>
+      <c r="BG12" s="12" t="n"/>
+      <c r="BH12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="BG12" s="12">
-        <f>BF12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BH12" s="9" t="n"/>
-      <c r="BI12" s="9" t="n"/>
-      <c r="BJ12" s="12" t="n"/>
-      <c r="BK12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="BM12" s="12">
-        <f>BL12/$E$12</f>
-        <v/>
-      </c>
+      <c r="BJ12" s="12">
+        <f>BI12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BK12" s="9" t="n"/>
+      <c r="BL12" s="9" t="n"/>
+      <c r="BM12" s="12" t="n"/>
       <c r="BN12" s="9" t="n">
         <v>0</v>
       </c>
@@ -5066,7 +5239,7 @@
         <v/>
       </c>
       <c r="BZ12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA12" s="9" t="n">
         <v>236</v>
@@ -5076,31 +5249,41 @@
         <v/>
       </c>
       <c r="CC12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="CD12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="CE12" s="12">
         <f>CD12/$E$12</f>
         <v/>
       </c>
       <c r="CF12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="CG12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="CH12" s="12">
         <f>CG12/$E$12</f>
         <v/>
       </c>
-      <c r="CI12" s="9" t="n"/>
+      <c r="CI12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="CJ12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="CK12" s="12">
         <f>CJ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="CL12" s="9" t="n"/>
+      <c r="CM12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="CN12" s="12">
+        <f>CM12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -5127,7 +5310,7 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>626</v>
@@ -5137,27 +5320,27 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>622</v>
@@ -5167,10 +5350,10 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
@@ -5187,7 +5370,7 @@
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>621</v>
@@ -5197,142 +5380,142 @@
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AC13" s="12">
         <f>AB13/$E$13</f>
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
       <c r="AP13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AQ13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
-      <c r="AS13" s="9" t="n"/>
-      <c r="AT13" s="9" t="n"/>
-      <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="9" t="n">
+      <c r="AS13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AU13" s="12">
+        <f>AT13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AV13" s="9" t="n"/>
+      <c r="AW13" s="9" t="n"/>
+      <c r="AX13" s="12" t="n"/>
+      <c r="AY13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AW13" s="9" t="n">
+      <c r="AZ13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="AX13" s="12">
-        <f>AW13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n"/>
-      <c r="BA13" s="12" t="n"/>
+      <c r="BA13" s="12">
+        <f>AZ13/$E$13</f>
+        <v/>
+      </c>
       <c r="BB13" s="9" t="n"/>
       <c r="BC13" s="9" t="n"/>
       <c r="BD13" s="12" t="n"/>
-      <c r="BE13" s="9" t="n">
+      <c r="BE13" s="9" t="n"/>
+      <c r="BF13" s="9" t="n"/>
+      <c r="BG13" s="12" t="n"/>
+      <c r="BH13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="BF13" s="9" t="n">
+      <c r="BI13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="BG13" s="12">
-        <f>BF13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BH13" s="9" t="n"/>
-      <c r="BI13" s="9" t="n"/>
-      <c r="BJ13" s="12" t="n"/>
-      <c r="BK13" s="9" t="n">
+      <c r="BJ13" s="12">
+        <f>BI13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BK13" s="9" t="n"/>
+      <c r="BL13" s="9" t="n"/>
+      <c r="BM13" s="12" t="n"/>
+      <c r="BN13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="BL13" s="9" t="n">
+      <c r="BO13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="BM13" s="12">
-        <f>BL13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BN13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BP13" s="12">
         <f>BO13/$E$13</f>
         <v/>
       </c>
       <c r="BQ13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BR13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
         <v/>
       </c>
       <c r="BT13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
         <v/>
       </c>
       <c r="BW13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BX13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="BY13" s="12">
         <f>BX13/$E$13</f>
@@ -5342,38 +5525,48 @@
         <v>4</v>
       </c>
       <c r="CA13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="CB13" s="12">
         <f>CA13/$E$13</f>
         <v/>
       </c>
       <c r="CC13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="CD13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="CE13" s="12">
         <f>CD13/$E$13</f>
         <v/>
       </c>
       <c r="CF13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="CG13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="CH13" s="12">
         <f>CG13/$E$13</f>
         <v/>
       </c>
-      <c r="CI13" s="9" t="n"/>
+      <c r="CI13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="CJ13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="CK13" s="12">
         <f>CJ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="CL13" s="9" t="n"/>
+      <c r="CM13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="CN13" s="12">
+        <f>CM13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -5400,7 +5593,7 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1151</v>
@@ -5410,27 +5603,27 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>1146</v>
@@ -5440,10 +5633,10 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
@@ -5460,7 +5653,7 @@
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>1145</v>
@@ -5470,17 +5663,17 @@
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="AC14" s="12">
         <f>AB14/$E$14</f>
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="9" t="n">
         <v>1142</v>
@@ -5490,122 +5683,122 @@
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
-      <c r="AS14" s="9" t="n"/>
-      <c r="AT14" s="9" t="n"/>
-      <c r="AU14" s="12" t="n"/>
-      <c r="AV14" s="9" t="n">
+      <c r="AS14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AU14" s="12">
+        <f>AT14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AV14" s="9" t="n"/>
+      <c r="AW14" s="9" t="n"/>
+      <c r="AX14" s="12" t="n"/>
+      <c r="AY14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AW14" s="9" t="n">
+      <c r="AZ14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="AX14" s="12">
-        <f>AW14/$E$14</f>
-        <v/>
-      </c>
-      <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n"/>
-      <c r="BA14" s="12" t="n"/>
+      <c r="BA14" s="12">
+        <f>AZ14/$E$14</f>
+        <v/>
+      </c>
       <c r="BB14" s="9" t="n"/>
       <c r="BC14" s="9" t="n"/>
       <c r="BD14" s="12" t="n"/>
-      <c r="BE14" s="9" t="n">
+      <c r="BE14" s="9" t="n"/>
+      <c r="BF14" s="9" t="n"/>
+      <c r="BG14" s="12" t="n"/>
+      <c r="BH14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="BF14" s="9" t="n">
+      <c r="BI14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="BG14" s="12">
-        <f>BF14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BH14" s="9" t="n"/>
-      <c r="BI14" s="9" t="n"/>
-      <c r="BJ14" s="12" t="n"/>
-      <c r="BK14" s="9" t="n">
+      <c r="BJ14" s="12">
+        <f>BI14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BK14" s="9" t="n"/>
+      <c r="BL14" s="9" t="n"/>
+      <c r="BM14" s="12" t="n"/>
+      <c r="BN14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BL14" s="9" t="n">
+      <c r="BO14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="BM14" s="12">
-        <f>BL14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BN14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BP14" s="12">
         <f>BO14/$E$14</f>
         <v/>
       </c>
       <c r="BQ14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BR14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BS14" s="12">
         <f>BR14/$E$14</f>
         <v/>
       </c>
       <c r="BT14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BU14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BV14" s="12">
         <f>BU14/$E$14</f>
         <v/>
       </c>
       <c r="BW14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BX14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="BY14" s="12">
         <f>BX14/$E$14</f>
@@ -5641,12 +5834,22 @@
         <f>CG14/$E$14</f>
         <v/>
       </c>
-      <c r="CI14" s="9" t="n"/>
+      <c r="CI14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CJ14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CK14" s="12">
         <f>CJ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="CL14" s="9" t="n"/>
+      <c r="CM14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" s="12">
+        <f>CM14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -5673,7 +5876,7 @@
         <v>551</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>127</v>
@@ -5683,10 +5886,10 @@
         <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K15" s="12">
         <f>J15/$E$15</f>
@@ -5733,7 +5936,7 @@
         <v/>
       </c>
       <c r="X15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>126</v>
@@ -5746,17 +5949,17 @@
         <v>1</v>
       </c>
       <c r="AB15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AC15" s="12">
         <f>AB15/$E$15</f>
         <v/>
       </c>
       <c r="AD15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AF15" s="12">
         <f>AE15/$E$15</f>
@@ -5773,7 +5976,7 @@
         <v/>
       </c>
       <c r="AJ15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="9" t="n">
         <v>124</v>
@@ -5783,17 +5986,17 @@
         <v/>
       </c>
       <c r="AM15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AO15" s="12">
         <f>AN15/$E$15</f>
         <v/>
       </c>
       <c r="AP15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="9" t="n">
         <v>121</v>
@@ -5802,53 +6005,53 @@
         <f>AQ15/$E$15</f>
         <v/>
       </c>
-      <c r="AS15" s="9" t="n"/>
-      <c r="AT15" s="9" t="n"/>
-      <c r="AU15" s="12" t="n"/>
-      <c r="AV15" s="9" t="n">
+      <c r="AS15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AU15" s="12">
+        <f>AT15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AV15" s="9" t="n"/>
+      <c r="AW15" s="9" t="n"/>
+      <c r="AX15" s="12" t="n"/>
+      <c r="AY15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AW15" s="9" t="n">
+      <c r="AZ15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="AX15" s="12">
-        <f>AW15/$E$15</f>
-        <v/>
-      </c>
-      <c r="AY15" s="9" t="n"/>
-      <c r="AZ15" s="9" t="n"/>
-      <c r="BA15" s="12" t="n"/>
+      <c r="BA15" s="12">
+        <f>AZ15/$E$15</f>
+        <v/>
+      </c>
       <c r="BB15" s="9" t="n"/>
       <c r="BC15" s="9" t="n"/>
       <c r="BD15" s="12" t="n"/>
-      <c r="BE15" s="9" t="n">
+      <c r="BE15" s="9" t="n"/>
+      <c r="BF15" s="9" t="n"/>
+      <c r="BG15" s="12" t="n"/>
+      <c r="BH15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BF15" s="9" t="n">
+      <c r="BI15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="BG15" s="12">
-        <f>BF15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BH15" s="9" t="n"/>
-      <c r="BI15" s="9" t="n"/>
-      <c r="BJ15" s="12" t="n"/>
-      <c r="BK15" s="9" t="n">
+      <c r="BJ15" s="12">
+        <f>BI15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BK15" s="9" t="n"/>
+      <c r="BL15" s="9" t="n"/>
+      <c r="BM15" s="12" t="n"/>
+      <c r="BN15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BL15" s="9" t="n">
+      <c r="BO15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="BM15" s="12">
-        <f>BL15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BN15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BP15" s="12">
         <f>BO15/$E$15</f>
@@ -5858,24 +6061,24 @@
         <v>3</v>
       </c>
       <c r="BR15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BS15" s="12">
         <f>BR15/$E$15</f>
         <v/>
       </c>
       <c r="BT15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BV15" s="12">
         <f>BU15/$E$15</f>
         <v/>
       </c>
       <c r="BW15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="BX15" s="9" t="n">
         <v>76</v>
@@ -5885,10 +6088,10 @@
         <v/>
       </c>
       <c r="BZ15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="CA15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="CB15" s="12">
         <f>CA15/$E$15</f>
@@ -5914,12 +6117,22 @@
         <f>CG15/$E$15</f>
         <v/>
       </c>
-      <c r="CI15" s="9" t="n"/>
+      <c r="CI15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CJ15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CK15" s="12">
         <f>CJ15/$E$15</f>
+        <v/>
+      </c>
+      <c r="CL15" s="9" t="n"/>
+      <c r="CM15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" s="12">
+        <f>CM15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -6075,51 +6288,58 @@
         <f>AQ16/$E$16</f>
         <v/>
       </c>
-      <c r="AS16" s="9" t="n"/>
-      <c r="AT16" s="9" t="n"/>
-      <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" s="9" t="n">
+      <c r="AS16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AX16" s="12">
-        <f>AW16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
+      <c r="AU16" s="12">
+        <f>AT16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AV16" s="9" t="n"/>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="12" t="n"/>
+      <c r="AY16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
       <c r="BB16" s="9" t="n"/>
       <c r="BC16" s="9" t="n"/>
       <c r="BD16" s="12" t="n"/>
-      <c r="BE16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" s="9" t="n">
+      <c r="BE16" s="9" t="n"/>
+      <c r="BF16" s="9" t="n"/>
+      <c r="BG16" s="12" t="n"/>
+      <c r="BH16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BG16" s="12">
-        <f>BF16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BH16" s="9" t="n"/>
-      <c r="BI16" s="9" t="n"/>
-      <c r="BJ16" s="12" t="n"/>
-      <c r="BK16" s="9" t="n">
+      <c r="BJ16" s="12">
+        <f>BI16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BK16" s="9" t="n"/>
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BL16" s="9" t="n">
+      <c r="BO16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BM16" s="12">
-        <f>BL16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n"/>
-      <c r="BP16" s="12" t="n"/>
+      <c r="BP16" s="12">
+        <f>BO16/$E$16</f>
+        <v/>
+      </c>
       <c r="BQ16" s="9" t="n"/>
       <c r="BR16" s="9" t="n"/>
       <c r="BS16" s="12" t="n"/>
@@ -6139,11 +6359,14 @@
       <c r="CG16" s="9" t="n"/>
       <c r="CH16" s="12" t="n"/>
       <c r="CI16" s="9" t="n"/>
-      <c r="CJ16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK16" s="12">
-        <f>CJ16/$E$16</f>
+      <c r="CJ16" s="9" t="n"/>
+      <c r="CK16" s="12" t="n"/>
+      <c r="CL16" s="9" t="n"/>
+      <c r="CM16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" s="12">
+        <f>CM16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -6253,6 +6476,9 @@
       <c r="CI17" s="9" t="n"/>
       <c r="CJ17" s="9" t="n"/>
       <c r="CK17" s="12" t="n"/>
+      <c r="CL17" s="9" t="n"/>
+      <c r="CM17" s="9" t="n"/>
+      <c r="CN17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6277,7 +6503,7 @@
         <v>830</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>191</v>
@@ -6287,46 +6513,48 @@
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
-      <c r="U18" s="9" t="n"/>
+      <c r="U18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="V18" s="9" t="n">
         <v>139</v>
       </c>
@@ -6335,8 +6563,13 @@
         <v/>
       </c>
       <c r="X18" s="9" t="n"/>
-      <c r="Y18" s="9" t="n"/>
-      <c r="Z18" s="12" t="n"/>
+      <c r="Y18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="Z18" s="12">
+        <f>Y18/$E$18</f>
+        <v/>
+      </c>
       <c r="AA18" s="9" t="n"/>
       <c r="AB18" s="9" t="n"/>
       <c r="AC18" s="12" t="n"/>
@@ -6400,9 +6633,12 @@
       <c r="CI18" s="9" t="n"/>
       <c r="CJ18" s="9" t="n"/>
       <c r="CK18" s="12" t="n"/>
+      <c r="CL18" s="9" t="n"/>
+      <c r="CM18" s="9" t="n"/>
+      <c r="CN18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -6426,6 +6662,7 @@
     <mergeCell ref="BE3:BG3"/>
     <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="CL3:CN3"/>
     <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="F3:H3"/>
@@ -6442,7 +6679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK18"/>
+  <dimension ref="A1:CN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6534,6 +6771,9 @@
     <col width="9" customWidth="1" min="87" max="87"/>
     <col width="9" customWidth="1" min="88" max="88"/>
     <col width="9" customWidth="1" min="89" max="89"/>
+    <col width="9" customWidth="1" min="90" max="90"/>
+    <col width="9" customWidth="1" min="91" max="91"/>
+    <col width="9" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6552,87 +6792,90 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -7080,6 +7323,21 @@
         </is>
       </c>
       <c r="CK4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CL4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CM4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CN4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -7128,7 +7386,7 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>302</v>
@@ -7138,10 +7396,10 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
@@ -7168,7 +7426,7 @@
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>298</v>
@@ -7181,115 +7439,122 @@
         <v>1</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AC5" s="12">
         <f>AB5/$E$5</f>
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="12" t="n"/>
-      <c r="AJ5" s="9" t="n">
+      <c r="AG5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="AI5" s="12">
+        <f>AH5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="9" t="n"/>
+      <c r="AK5" s="9" t="n"/>
+      <c r="AL5" s="12" t="n"/>
+      <c r="AM5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK5" s="9" t="n">
+      <c r="AN5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="AL5" s="12">
-        <f>AK5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AM5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="AO5" s="12">
         <f>AN5/$E$5</f>
         <v/>
       </c>
       <c r="AP5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AQ5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AR5" s="12">
         <f>AQ5/$E$5</f>
         <v/>
       </c>
       <c r="AS5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AT5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AU5" s="12">
         <f>AT5/$E$5</f>
         <v/>
       </c>
-      <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n"/>
-      <c r="AX5" s="12" t="n"/>
-      <c r="AY5" s="9" t="n">
+      <c r="AV5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AW5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="AX5" s="12">
+        <f>AW5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AY5" s="9" t="n"/>
+      <c r="AZ5" s="9" t="n"/>
+      <c r="BA5" s="12" t="n"/>
+      <c r="BB5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AZ5" s="9" t="n">
+      <c r="BC5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="BA5" s="12">
-        <f>AZ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BB5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BC5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="BD5" s="12">
         <f>BC5/$E$5</f>
         <v/>
       </c>
-      <c r="BE5" s="9" t="n"/>
-      <c r="BF5" s="9" t="n"/>
-      <c r="BG5" s="12" t="n"/>
-      <c r="BH5" s="9" t="n">
+      <c r="BE5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BF5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="BG5" s="12">
+        <f>BF5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BH5" s="9" t="n"/>
+      <c r="BI5" s="9" t="n"/>
+      <c r="BJ5" s="12" t="n"/>
+      <c r="BK5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="BI5" s="9" t="n">
+      <c r="BL5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="BJ5" s="12">
-        <f>BI5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BK5" s="9" t="n"/>
-      <c r="BL5" s="9" t="n"/>
-      <c r="BM5" s="12" t="n"/>
+      <c r="BM5" s="12">
+        <f>BL5/$E$5</f>
+        <v/>
+      </c>
       <c r="BN5" s="9" t="n"/>
-      <c r="BO5" s="9" t="n">
+      <c r="BO5" s="9" t="n"/>
+      <c r="BP5" s="12" t="n"/>
+      <c r="BQ5" s="9" t="n"/>
+      <c r="BR5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="BP5" s="12">
-        <f>BO5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BQ5" s="9" t="n"/>
-      <c r="BR5" s="9" t="n"/>
-      <c r="BS5" s="12" t="n"/>
+      <c r="BS5" s="12">
+        <f>BR5/$E$5</f>
+        <v/>
+      </c>
       <c r="BT5" s="9" t="n"/>
       <c r="BU5" s="9" t="n"/>
       <c r="BV5" s="12" t="n"/>
@@ -7308,6 +7573,9 @@
       <c r="CI5" s="9" t="n"/>
       <c r="CJ5" s="9" t="n"/>
       <c r="CK5" s="12" t="n"/>
+      <c r="CL5" s="9" t="n"/>
+      <c r="CM5" s="9" t="n"/>
+      <c r="CN5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -7332,7 +7600,7 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>954</v>
@@ -7342,17 +7610,17 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>953</v>
@@ -7362,20 +7630,20 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
@@ -7392,7 +7660,7 @@
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>950</v>
@@ -7402,118 +7670,125 @@
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="AC6" s="12">
         <f>AB6/$E$6</f>
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="12" t="n"/>
-      <c r="AJ6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="AI6" s="12">
+        <f>AH6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9" t="n"/>
+      <c r="AK6" s="9" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AK6" s="9" t="n">
+      <c r="AN6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="AL6" s="12">
-        <f>AK6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AM6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AN6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
-      <c r="AY6" s="9" t="n">
+      <c r="AV6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="AZ6" s="9" t="n">
+      <c r="BC6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="BD6" s="12">
         <f>BC6/$E$6</f>
         <v/>
       </c>
-      <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="12" t="n"/>
-      <c r="BH6" s="9" t="n">
+      <c r="BE6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="BG6" s="12">
+        <f>BF6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BH6" s="9" t="n"/>
+      <c r="BI6" s="9" t="n"/>
+      <c r="BJ6" s="12" t="n"/>
+      <c r="BK6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BI6" s="9" t="n">
+      <c r="BL6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BJ6" s="12">
-        <f>BI6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BK6" s="9" t="n"/>
-      <c r="BL6" s="9" t="n"/>
-      <c r="BM6" s="12" t="n"/>
+      <c r="BM6" s="12">
+        <f>BL6/$E$6</f>
+        <v/>
+      </c>
       <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n">
+      <c r="BO6" s="9" t="n"/>
+      <c r="BP6" s="12" t="n"/>
+      <c r="BQ6" s="9" t="n"/>
+      <c r="BR6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="BP6" s="12">
-        <f>BO6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BQ6" s="9" t="n"/>
-      <c r="BR6" s="9" t="n"/>
-      <c r="BS6" s="12" t="n"/>
+      <c r="BS6" s="12">
+        <f>BR6/$E$6</f>
+        <v/>
+      </c>
       <c r="BT6" s="9" t="n"/>
       <c r="BU6" s="9" t="n"/>
       <c r="BV6" s="12" t="n"/>
@@ -7532,6 +7807,9 @@
       <c r="CI6" s="9" t="n"/>
       <c r="CJ6" s="9" t="n"/>
       <c r="CK6" s="12" t="n"/>
+      <c r="CL6" s="9" t="n"/>
+      <c r="CM6" s="9" t="n"/>
+      <c r="CN6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -7566,7 +7844,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>48</v>
@@ -7576,10 +7854,10 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
@@ -7645,99 +7923,106 @@
         <f>AE7/$E$7</f>
         <v/>
       </c>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="9" t="n">
+      <c r="AG7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="AI7" s="12">
+        <f>AH7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9" t="n"/>
+      <c r="AK7" s="9" t="n"/>
+      <c r="AL7" s="12" t="n"/>
+      <c r="AM7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="AK7" s="9" t="n">
+      <c r="AN7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="AL7" s="12">
-        <f>AK7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AM7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
-      <c r="AY7" s="9" t="n">
+      <c r="AV7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AZ7" s="9" t="n">
+      <c r="AW7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="BD7" s="12">
         <f>BC7/$E$7</f>
         <v/>
       </c>
-      <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="12" t="n"/>
-      <c r="BH7" s="9" t="n">
+      <c r="BE7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="BG7" s="12">
+        <f>BF7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BH7" s="9" t="n"/>
+      <c r="BI7" s="9" t="n"/>
+      <c r="BJ7" s="12" t="n"/>
+      <c r="BK7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BI7" s="9" t="n">
+      <c r="BL7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="BJ7" s="12">
-        <f>BI7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BK7" s="9" t="n"/>
-      <c r="BL7" s="9" t="n"/>
-      <c r="BM7" s="12" t="n"/>
+      <c r="BM7" s="12">
+        <f>BL7/$E$7</f>
+        <v/>
+      </c>
       <c r="BN7" s="9" t="n"/>
-      <c r="BO7" s="9" t="n">
+      <c r="BO7" s="9" t="n"/>
+      <c r="BP7" s="12" t="n"/>
+      <c r="BQ7" s="9" t="n"/>
+      <c r="BR7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BP7" s="12">
-        <f>BO7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BQ7" s="9" t="n"/>
-      <c r="BR7" s="9" t="n"/>
-      <c r="BS7" s="12" t="n"/>
+      <c r="BS7" s="12">
+        <f>BR7/$E$7</f>
+        <v/>
+      </c>
       <c r="BT7" s="9" t="n"/>
       <c r="BU7" s="9" t="n"/>
       <c r="BV7" s="12" t="n"/>
@@ -7756,6 +8041,9 @@
       <c r="CI7" s="9" t="n"/>
       <c r="CJ7" s="9" t="n"/>
       <c r="CK7" s="12" t="n"/>
+      <c r="CL7" s="9" t="n"/>
+      <c r="CM7" s="9" t="n"/>
+      <c r="CN7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -7780,7 +8068,7 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1058</v>
@@ -7790,17 +8078,17 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>1056</v>
@@ -7810,10 +8098,10 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
@@ -7840,7 +8128,7 @@
         <v/>
       </c>
       <c r="X8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>1054</v>
@@ -7850,17 +8138,17 @@
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="AC8" s="12">
         <f>AB8/$E$8</f>
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="9" t="n">
         <v>1052</v>
@@ -7869,99 +8157,106 @@
         <f>AE8/$E$8</f>
         <v/>
       </c>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="12" t="n"/>
-      <c r="AJ8" s="9" t="n">
+      <c r="AG8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK8" s="9" t="n">
+      <c r="AH8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="AI8" s="12">
+        <f>AH8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9" t="n"/>
+      <c r="AK8" s="9" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="AL8" s="12">
-        <f>AK8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AM8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
-      <c r="AY8" s="9" t="n">
+      <c r="AV8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AZ8" s="9" t="n">
+      <c r="BC8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="BD8" s="12">
         <f>BC8/$E$8</f>
         <v/>
       </c>
-      <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="12" t="n"/>
-      <c r="BH8" s="9" t="n">
+      <c r="BE8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BG8" s="12">
+        <f>BF8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BH8" s="9" t="n"/>
+      <c r="BI8" s="9" t="n"/>
+      <c r="BJ8" s="12" t="n"/>
+      <c r="BK8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BI8" s="9" t="n">
+      <c r="BL8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="BJ8" s="12">
-        <f>BI8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BK8" s="9" t="n"/>
-      <c r="BL8" s="9" t="n"/>
-      <c r="BM8" s="12" t="n"/>
+      <c r="BM8" s="12">
+        <f>BL8/$E$8</f>
+        <v/>
+      </c>
       <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n">
+      <c r="BO8" s="9" t="n"/>
+      <c r="BP8" s="12" t="n"/>
+      <c r="BQ8" s="9" t="n"/>
+      <c r="BR8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="BP8" s="12">
-        <f>BO8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BQ8" s="9" t="n"/>
-      <c r="BR8" s="9" t="n"/>
-      <c r="BS8" s="12" t="n"/>
+      <c r="BS8" s="12">
+        <f>BR8/$E$8</f>
+        <v/>
+      </c>
       <c r="BT8" s="9" t="n"/>
       <c r="BU8" s="9" t="n"/>
       <c r="BV8" s="12" t="n"/>
@@ -7980,6 +8275,9 @@
       <c r="CI8" s="9" t="n"/>
       <c r="CJ8" s="9" t="n"/>
       <c r="CK8" s="12" t="n"/>
+      <c r="CL8" s="9" t="n"/>
+      <c r="CM8" s="9" t="n"/>
+      <c r="CN8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -8093,19 +8391,19 @@
         <f>AE9/$E$9</f>
         <v/>
       </c>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AG9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="AL9" s="12">
-        <f>AK9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AI9" s="12">
+        <f>AH9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9" t="n"/>
+      <c r="AK9" s="9" t="n"/>
+      <c r="AL9" s="12" t="n"/>
       <c r="AM9" s="9" t="n">
         <v>0</v>
       </c>
@@ -8117,7 +8415,7 @@
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="9" t="n">
         <v>845</v>
@@ -8127,28 +8425,28 @@
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AU9" s="12">
         <f>AT9/$E$9</f>
         <v/>
       </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
-      <c r="AY9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="9" t="n">
+      <c r="AV9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
       <c r="BB9" s="9" t="n">
         <v>0</v>
       </c>
@@ -8159,33 +8457,40 @@
         <f>BC9/$E$9</f>
         <v/>
       </c>
-      <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="12" t="n"/>
-      <c r="BH9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" s="9" t="n">
+      <c r="BE9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BJ9" s="12">
-        <f>BI9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BK9" s="9" t="n"/>
-      <c r="BL9" s="9" t="n"/>
-      <c r="BM9" s="12" t="n"/>
+      <c r="BG9" s="12">
+        <f>BF9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BH9" s="9" t="n"/>
+      <c r="BI9" s="9" t="n"/>
+      <c r="BJ9" s="12" t="n"/>
+      <c r="BK9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="BM9" s="12">
+        <f>BL9/$E$9</f>
+        <v/>
+      </c>
       <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n">
+      <c r="BO9" s="9" t="n"/>
+      <c r="BP9" s="12" t="n"/>
+      <c r="BQ9" s="9" t="n"/>
+      <c r="BR9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BP9" s="12">
-        <f>BO9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BQ9" s="9" t="n"/>
-      <c r="BR9" s="9" t="n"/>
-      <c r="BS9" s="12" t="n"/>
+      <c r="BS9" s="12">
+        <f>BR9/$E$9</f>
+        <v/>
+      </c>
       <c r="BT9" s="9" t="n"/>
       <c r="BU9" s="9" t="n"/>
       <c r="BV9" s="12" t="n"/>
@@ -8204,6 +8509,9 @@
       <c r="CI9" s="9" t="n"/>
       <c r="CJ9" s="9" t="n"/>
       <c r="CK9" s="12" t="n"/>
+      <c r="CL9" s="9" t="n"/>
+      <c r="CM9" s="9" t="n"/>
+      <c r="CN9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -8228,7 +8536,7 @@
         <v>3692</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>1421</v>
@@ -8241,7 +8549,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
@@ -8251,17 +8559,17 @@
         <v>1</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
@@ -8288,7 +8596,7 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>1418</v>
@@ -8298,118 +8606,125 @@
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="9" t="n">
+      <c r="AG10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="AI10" s="12">
+        <f>AH10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9" t="n"/>
+      <c r="AK10" s="9" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK10" s="9" t="n">
+      <c r="AN10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="AL10" s="12">
-        <f>AK10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AM10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AN10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AT10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
-      <c r="AY10" s="9" t="n">
+      <c r="AV10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AZ10" s="9" t="n">
+      <c r="BC10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="BA10" s="12">
-        <f>AZ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BB10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="BD10" s="12">
         <f>BC10/$E$10</f>
         <v/>
       </c>
-      <c r="BE10" s="9" t="n"/>
-      <c r="BF10" s="9" t="n"/>
-      <c r="BG10" s="12" t="n"/>
-      <c r="BH10" s="9" t="n">
+      <c r="BE10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BI10" s="9" t="n">
+      <c r="BF10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="BG10" s="12">
+        <f>BF10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BH10" s="9" t="n"/>
+      <c r="BI10" s="9" t="n"/>
+      <c r="BJ10" s="12" t="n"/>
+      <c r="BK10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="BJ10" s="12">
-        <f>BI10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BK10" s="9" t="n"/>
-      <c r="BL10" s="9" t="n"/>
-      <c r="BM10" s="12" t="n"/>
+      <c r="BM10" s="12">
+        <f>BL10/$E$10</f>
+        <v/>
+      </c>
       <c r="BN10" s="9" t="n"/>
-      <c r="BO10" s="9" t="n">
+      <c r="BO10" s="9" t="n"/>
+      <c r="BP10" s="12" t="n"/>
+      <c r="BQ10" s="9" t="n"/>
+      <c r="BR10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="BP10" s="12">
-        <f>BO10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BQ10" s="9" t="n"/>
-      <c r="BR10" s="9" t="n"/>
-      <c r="BS10" s="12" t="n"/>
+      <c r="BS10" s="12">
+        <f>BR10/$E$10</f>
+        <v/>
+      </c>
       <c r="BT10" s="9" t="n"/>
       <c r="BU10" s="9" t="n"/>
       <c r="BV10" s="12" t="n"/>
@@ -8428,6 +8743,9 @@
       <c r="CI10" s="9" t="n"/>
       <c r="CJ10" s="9" t="n"/>
       <c r="CK10" s="12" t="n"/>
+      <c r="CL10" s="9" t="n"/>
+      <c r="CM10" s="9" t="n"/>
+      <c r="CN10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -8452,7 +8770,7 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>1001</v>
@@ -8462,10 +8780,10 @@
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="K11" s="12">
         <f>J11/$E$11</f>
@@ -8475,27 +8793,27 @@
         <v>3</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
         <v/>
       </c>
       <c r="O11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
@@ -8512,7 +8830,7 @@
         <v/>
       </c>
       <c r="X11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>992</v>
@@ -8522,10 +8840,10 @@
         <v/>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="AC11" s="12">
         <f>AB11/$E$11</f>
@@ -8541,99 +8859,106 @@
         <f>AE11/$E$11</f>
         <v/>
       </c>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="9" t="n">
+      <c r="AG11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI11" s="12">
+        <f>AH11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9" t="n"/>
+      <c r="AK11" s="9" t="n"/>
+      <c r="AL11" s="12" t="n"/>
+      <c r="AM11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AN11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="AL11" s="12">
-        <f>AK11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AM11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AN11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="AO11" s="12">
         <f>AN11/$E$11</f>
         <v/>
       </c>
       <c r="AP11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AQ11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AU11" s="12">
         <f>AT11/$E$11</f>
         <v/>
       </c>
-      <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n"/>
-      <c r="AX11" s="12" t="n"/>
-      <c r="AY11" s="9" t="n">
+      <c r="AV11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="AX11" s="12">
+        <f>AW11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="9" t="n"/>
+      <c r="AZ11" s="9" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AZ11" s="9" t="n">
+      <c r="BC11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="BA11" s="12">
-        <f>AZ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BB11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="BD11" s="12">
         <f>BC11/$E$11</f>
         <v/>
       </c>
-      <c r="BE11" s="9" t="n"/>
-      <c r="BF11" s="9" t="n"/>
-      <c r="BG11" s="12" t="n"/>
-      <c r="BH11" s="9" t="n">
+      <c r="BE11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="BG11" s="12">
+        <f>BF11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BH11" s="9" t="n"/>
+      <c r="BI11" s="9" t="n"/>
+      <c r="BJ11" s="12" t="n"/>
+      <c r="BK11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BI11" s="9" t="n">
+      <c r="BL11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="BJ11" s="12">
-        <f>BI11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BK11" s="9" t="n"/>
-      <c r="BL11" s="9" t="n"/>
-      <c r="BM11" s="12" t="n"/>
+      <c r="BM11" s="12">
+        <f>BL11/$E$11</f>
+        <v/>
+      </c>
       <c r="BN11" s="9" t="n"/>
-      <c r="BO11" s="9" t="n">
+      <c r="BO11" s="9" t="n"/>
+      <c r="BP11" s="12" t="n"/>
+      <c r="BQ11" s="9" t="n"/>
+      <c r="BR11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="BP11" s="12">
-        <f>BO11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BQ11" s="9" t="n"/>
-      <c r="BR11" s="9" t="n"/>
-      <c r="BS11" s="12" t="n"/>
+      <c r="BS11" s="12">
+        <f>BR11/$E$11</f>
+        <v/>
+      </c>
       <c r="BT11" s="9" t="n"/>
       <c r="BU11" s="9" t="n"/>
       <c r="BV11" s="12" t="n"/>
@@ -8652,6 +8977,9 @@
       <c r="CI11" s="9" t="n"/>
       <c r="CJ11" s="9" t="n"/>
       <c r="CK11" s="12" t="n"/>
+      <c r="CL11" s="9" t="n"/>
+      <c r="CM11" s="9" t="n"/>
+      <c r="CN11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -8676,7 +9004,7 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>741</v>
@@ -8686,10 +9014,10 @@
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="K12" s="12">
         <f>J12/$E$12</f>
@@ -8699,17 +9027,17 @@
         <v>1</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N12" s="12">
         <f>M12/$E$12</f>
         <v/>
       </c>
       <c r="O12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
@@ -8736,7 +9064,7 @@
         <v/>
       </c>
       <c r="X12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>737</v>
@@ -8746,118 +9074,125 @@
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="AC12" s="12">
         <f>AB12/$E$12</f>
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="12" t="n"/>
-      <c r="AJ12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="AI12" s="12">
+        <f>AH12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9" t="n"/>
+      <c r="AK12" s="9" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AK12" s="9" t="n">
+      <c r="AN12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="AL12" s="12">
-        <f>AK12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AM12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AN12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="AO12" s="12">
         <f>AN12/$E$12</f>
         <v/>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AQ12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="AR12" s="12">
         <f>AQ12/$E$12</f>
         <v/>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AT12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AU12" s="12">
         <f>AT12/$E$12</f>
         <v/>
       </c>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="12" t="n"/>
-      <c r="AY12" s="9" t="n">
+      <c r="AV12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="AX12" s="12">
+        <f>AW12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="12" t="n"/>
+      <c r="BB12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AZ12" s="9" t="n">
+      <c r="BC12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="BA12" s="12">
-        <f>AZ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BB12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="BD12" s="12">
         <f>BC12/$E$12</f>
         <v/>
       </c>
-      <c r="BE12" s="9" t="n"/>
-      <c r="BF12" s="9" t="n"/>
-      <c r="BG12" s="12" t="n"/>
-      <c r="BH12" s="9" t="n">
+      <c r="BE12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="BG12" s="12">
+        <f>BF12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BH12" s="9" t="n"/>
+      <c r="BI12" s="9" t="n"/>
+      <c r="BJ12" s="12" t="n"/>
+      <c r="BK12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BI12" s="9" t="n">
+      <c r="BL12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="BJ12" s="12">
-        <f>BI12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BK12" s="9" t="n"/>
-      <c r="BL12" s="9" t="n"/>
-      <c r="BM12" s="12" t="n"/>
+      <c r="BM12" s="12">
+        <f>BL12/$E$12</f>
+        <v/>
+      </c>
       <c r="BN12" s="9" t="n"/>
-      <c r="BO12" s="9" t="n">
+      <c r="BO12" s="9" t="n"/>
+      <c r="BP12" s="12" t="n"/>
+      <c r="BQ12" s="9" t="n"/>
+      <c r="BR12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="BP12" s="12">
-        <f>BO12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BQ12" s="9" t="n"/>
-      <c r="BR12" s="9" t="n"/>
-      <c r="BS12" s="12" t="n"/>
+      <c r="BS12" s="12">
+        <f>BR12/$E$12</f>
+        <v/>
+      </c>
       <c r="BT12" s="9" t="n"/>
       <c r="BU12" s="9" t="n"/>
       <c r="BV12" s="12" t="n"/>
@@ -8876,6 +9211,9 @@
       <c r="CI12" s="9" t="n"/>
       <c r="CJ12" s="9" t="n"/>
       <c r="CK12" s="12" t="n"/>
+      <c r="CL12" s="9" t="n"/>
+      <c r="CM12" s="9" t="n"/>
+      <c r="CN12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -8920,7 +9258,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>1394</v>
@@ -8930,20 +9268,20 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
@@ -8980,7 +9318,7 @@
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="9" t="n">
         <v>1391</v>
@@ -8989,99 +9327,106 @@
         <f>AE13/$E$13</f>
         <v/>
       </c>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="12" t="n"/>
-      <c r="AJ13" s="9" t="n">
+      <c r="AG13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK13" s="9" t="n">
+      <c r="AH13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="AI13" s="12">
+        <f>AH13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9" t="n"/>
+      <c r="AK13" s="9" t="n"/>
+      <c r="AL13" s="12" t="n"/>
+      <c r="AM13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="AL13" s="12">
-        <f>AK13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AM13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
       <c r="AP13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
-      <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n"/>
-      <c r="AX13" s="12" t="n"/>
-      <c r="AY13" s="9" t="n">
+      <c r="AV13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AX13" s="12">
+        <f>AW13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="AZ13" s="9" t="n">
+      <c r="BC13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="BA13" s="12">
-        <f>AZ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BB13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="BD13" s="12">
         <f>BC13/$E$13</f>
         <v/>
       </c>
-      <c r="BE13" s="9" t="n"/>
-      <c r="BF13" s="9" t="n"/>
-      <c r="BG13" s="12" t="n"/>
-      <c r="BH13" s="9" t="n">
+      <c r="BE13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="BG13" s="12">
+        <f>BF13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BH13" s="9" t="n"/>
+      <c r="BI13" s="9" t="n"/>
+      <c r="BJ13" s="12" t="n"/>
+      <c r="BK13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BI13" s="9" t="n">
+      <c r="BL13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="BJ13" s="12">
-        <f>BI13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BK13" s="9" t="n"/>
-      <c r="BL13" s="9" t="n"/>
-      <c r="BM13" s="12" t="n"/>
+      <c r="BM13" s="12">
+        <f>BL13/$E$13</f>
+        <v/>
+      </c>
       <c r="BN13" s="9" t="n"/>
-      <c r="BO13" s="9" t="n">
+      <c r="BO13" s="9" t="n"/>
+      <c r="BP13" s="12" t="n"/>
+      <c r="BQ13" s="9" t="n"/>
+      <c r="BR13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="BP13" s="12">
-        <f>BO13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BQ13" s="9" t="n"/>
-      <c r="BR13" s="9" t="n"/>
-      <c r="BS13" s="12" t="n"/>
+      <c r="BS13" s="12">
+        <f>BR13/$E$13</f>
+        <v/>
+      </c>
       <c r="BT13" s="9" t="n"/>
       <c r="BU13" s="9" t="n"/>
       <c r="BV13" s="12" t="n"/>
@@ -9100,6 +9445,9 @@
       <c r="CI13" s="9" t="n"/>
       <c r="CJ13" s="9" t="n"/>
       <c r="CK13" s="12" t="n"/>
+      <c r="CL13" s="9" t="n"/>
+      <c r="CM13" s="9" t="n"/>
+      <c r="CN13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -9124,7 +9472,7 @@
         <v>996</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>906</v>
@@ -9137,24 +9485,24 @@
         <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>904</v>
@@ -9164,10 +9512,10 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
@@ -9204,7 +9552,7 @@
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="9" t="n">
         <v>902</v>
@@ -9213,21 +9561,21 @@
         <f>AE14/$E$14</f>
         <v/>
       </c>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="12" t="n"/>
-      <c r="AJ14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="AL14" s="12">
-        <f>AK14/$E$14</f>
-        <v/>
-      </c>
+      <c r="AG14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="AI14" s="12">
+        <f>AH14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="12" t="n"/>
       <c r="AM14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AN14" s="9" t="n">
         <v>898</v>
@@ -9237,75 +9585,82 @@
         <v/>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
-      <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n"/>
-      <c r="AX14" s="12" t="n"/>
-      <c r="AY14" s="9" t="n">
+      <c r="AV14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="AX14" s="12">
+        <f>AW14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="9" t="n"/>
+      <c r="AZ14" s="9" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AZ14" s="9" t="n">
+      <c r="BC14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="BA14" s="12">
-        <f>AZ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BB14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="BD14" s="12">
         <f>BC14/$E$14</f>
         <v/>
       </c>
-      <c r="BE14" s="9" t="n"/>
-      <c r="BF14" s="9" t="n"/>
-      <c r="BG14" s="12" t="n"/>
-      <c r="BH14" s="9" t="n">
+      <c r="BE14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BI14" s="9" t="n">
+      <c r="BF14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="BG14" s="12">
+        <f>BF14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BH14" s="9" t="n"/>
+      <c r="BI14" s="9" t="n"/>
+      <c r="BJ14" s="12" t="n"/>
+      <c r="BK14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="BJ14" s="12">
-        <f>BI14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BK14" s="9" t="n"/>
-      <c r="BL14" s="9" t="n"/>
-      <c r="BM14" s="12" t="n"/>
+      <c r="BM14" s="12">
+        <f>BL14/$E$14</f>
+        <v/>
+      </c>
       <c r="BN14" s="9" t="n"/>
-      <c r="BO14" s="9" t="n">
+      <c r="BO14" s="9" t="n"/>
+      <c r="BP14" s="12" t="n"/>
+      <c r="BQ14" s="9" t="n"/>
+      <c r="BR14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="BP14" s="12">
-        <f>BO14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BQ14" s="9" t="n"/>
-      <c r="BR14" s="9" t="n"/>
-      <c r="BS14" s="12" t="n"/>
+      <c r="BS14" s="12">
+        <f>BR14/$E$14</f>
+        <v/>
+      </c>
       <c r="BT14" s="9" t="n"/>
       <c r="BU14" s="9" t="n"/>
       <c r="BV14" s="12" t="n"/>
@@ -9324,6 +9679,9 @@
       <c r="CI14" s="9" t="n"/>
       <c r="CJ14" s="9" t="n"/>
       <c r="CK14" s="12" t="n"/>
+      <c r="CL14" s="9" t="n"/>
+      <c r="CM14" s="9" t="n"/>
+      <c r="CN14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -9431,6 +9789,9 @@
       <c r="CI15" s="9" t="n"/>
       <c r="CJ15" s="9" t="n"/>
       <c r="CK15" s="12" t="n"/>
+      <c r="CL15" s="9" t="n"/>
+      <c r="CM15" s="9" t="n"/>
+      <c r="CN15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -9455,7 +9816,7 @@
         <v>824</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>720</v>
@@ -9465,27 +9826,27 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="K16" s="12">
         <f>J16/$E$16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="N16" s="12">
         <f>M16/$E$16</f>
         <v/>
       </c>
       <c r="O16" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>717</v>
@@ -9495,10 +9856,10 @@
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="T16" s="12">
         <f>S16/$E$16</f>
@@ -9515,7 +9876,7 @@
         <v/>
       </c>
       <c r="X16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>715</v>
@@ -9525,118 +9886,125 @@
         <v/>
       </c>
       <c r="AA16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AC16" s="12">
         <f>AB16/$E$16</f>
         <v/>
       </c>
       <c r="AD16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="12" t="n"/>
-      <c r="AJ16" s="9" t="n">
+      <c r="AG16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="AI16" s="12">
+        <f>AH16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9" t="n"/>
+      <c r="AK16" s="9" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK16" s="9" t="n">
+      <c r="AN16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="AL16" s="12">
-        <f>AK16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AM16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="AO16" s="12">
         <f>AN16/$E$16</f>
         <v/>
       </c>
       <c r="AP16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AQ16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AR16" s="12">
         <f>AQ16/$E$16</f>
         <v/>
       </c>
       <c r="AS16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AT16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AU16" s="12">
         <f>AT16/$E$16</f>
         <v/>
       </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
-      <c r="AY16" s="9" t="n">
+      <c r="AV16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AZ16" s="9" t="n">
+      <c r="BC16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="BA16" s="12">
-        <f>AZ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BB16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="BD16" s="12">
         <f>BC16/$E$16</f>
         <v/>
       </c>
-      <c r="BE16" s="9" t="n"/>
-      <c r="BF16" s="9" t="n"/>
-      <c r="BG16" s="12" t="n"/>
-      <c r="BH16" s="9" t="n">
+      <c r="BE16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="BG16" s="12">
+        <f>BF16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BH16" s="9" t="n"/>
+      <c r="BI16" s="9" t="n"/>
+      <c r="BJ16" s="12" t="n"/>
+      <c r="BK16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="BI16" s="9" t="n">
+      <c r="BL16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="BJ16" s="12">
-        <f>BI16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n"/>
-      <c r="BM16" s="12" t="n"/>
+      <c r="BM16" s="12">
+        <f>BL16/$E$16</f>
+        <v/>
+      </c>
       <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n">
+      <c r="BO16" s="9" t="n"/>
+      <c r="BP16" s="12" t="n"/>
+      <c r="BQ16" s="9" t="n"/>
+      <c r="BR16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="BP16" s="12">
-        <f>BO16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BQ16" s="9" t="n"/>
-      <c r="BR16" s="9" t="n"/>
-      <c r="BS16" s="12" t="n"/>
+      <c r="BS16" s="12">
+        <f>BR16/$E$16</f>
+        <v/>
+      </c>
       <c r="BT16" s="9" t="n"/>
       <c r="BU16" s="9" t="n"/>
       <c r="BV16" s="12" t="n"/>
@@ -9655,6 +10023,9 @@
       <c r="CI16" s="9" t="n"/>
       <c r="CJ16" s="9" t="n"/>
       <c r="CK16" s="12" t="n"/>
+      <c r="CL16" s="9" t="n"/>
+      <c r="CM16" s="9" t="n"/>
+      <c r="CN16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -9679,7 +10050,7 @@
         <v>1012</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>390</v>
@@ -9692,24 +10063,24 @@
         <v>1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K17" s="12">
         <f>J17/$E$17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N17" s="12">
         <f>M17/$E$17</f>
         <v/>
       </c>
       <c r="O17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="9" t="n">
         <v>388</v>
@@ -9719,20 +10090,20 @@
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="T17" s="12">
         <f>S17/$E$17</f>
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
@@ -9749,7 +10120,7 @@
         <v/>
       </c>
       <c r="AA17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="9" t="n">
         <v>385</v>
@@ -9759,108 +10130,115 @@
         <v/>
       </c>
       <c r="AD17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AF17" s="12">
         <f>AE17/$E$17</f>
         <v/>
       </c>
-      <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="9" t="n"/>
-      <c r="AI17" s="12" t="n"/>
-      <c r="AJ17" s="9" t="n">
+      <c r="AG17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AK17" s="9" t="n">
+      <c r="AH17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="AI17" s="12">
+        <f>AH17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="9" t="n"/>
+      <c r="AK17" s="9" t="n"/>
+      <c r="AL17" s="12" t="n"/>
+      <c r="AM17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="AL17" s="12">
-        <f>AK17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AM17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="AO17" s="12">
         <f>AN17/$E$17</f>
         <v/>
       </c>
       <c r="AP17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AQ17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AR17" s="12">
         <f>AQ17/$E$17</f>
         <v/>
       </c>
       <c r="AS17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AU17" s="12">
         <f>AT17/$E$17</f>
         <v/>
       </c>
-      <c r="AV17" s="9" t="n"/>
-      <c r="AW17" s="9" t="n"/>
-      <c r="AX17" s="12" t="n"/>
-      <c r="AY17" s="9" t="n">
+      <c r="AV17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="AX17" s="12">
+        <f>AW17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AY17" s="9" t="n"/>
+      <c r="AZ17" s="9" t="n"/>
+      <c r="BA17" s="12" t="n"/>
+      <c r="BB17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AZ17" s="9" t="n">
+      <c r="BC17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="BA17" s="12">
-        <f>AZ17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BB17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="BD17" s="12">
         <f>BC17/$E$17</f>
         <v/>
       </c>
-      <c r="BE17" s="9" t="n"/>
-      <c r="BF17" s="9" t="n"/>
-      <c r="BG17" s="12" t="n"/>
-      <c r="BH17" s="9" t="n">
+      <c r="BE17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="BG17" s="12">
+        <f>BF17/$E$17</f>
+        <v/>
+      </c>
+      <c r="BH17" s="9" t="n"/>
+      <c r="BI17" s="9" t="n"/>
+      <c r="BJ17" s="12" t="n"/>
+      <c r="BK17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BI17" s="9" t="n">
+      <c r="BL17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="BJ17" s="12">
-        <f>BI17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BK17" s="9" t="n"/>
-      <c r="BL17" s="9" t="n"/>
-      <c r="BM17" s="12" t="n"/>
+      <c r="BM17" s="12">
+        <f>BL17/$E$17</f>
+        <v/>
+      </c>
       <c r="BN17" s="9" t="n"/>
-      <c r="BO17" s="9" t="n">
+      <c r="BO17" s="9" t="n"/>
+      <c r="BP17" s="12" t="n"/>
+      <c r="BQ17" s="9" t="n"/>
+      <c r="BR17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="BP17" s="12">
-        <f>BO17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BQ17" s="9" t="n"/>
-      <c r="BR17" s="9" t="n"/>
-      <c r="BS17" s="12" t="n"/>
+      <c r="BS17" s="12">
+        <f>BR17/$E$17</f>
+        <v/>
+      </c>
       <c r="BT17" s="9" t="n"/>
       <c r="BU17" s="9" t="n"/>
       <c r="BV17" s="12" t="n"/>
@@ -9879,6 +10257,9 @@
       <c r="CI17" s="9" t="n"/>
       <c r="CJ17" s="9" t="n"/>
       <c r="CK17" s="12" t="n"/>
+      <c r="CL17" s="9" t="n"/>
+      <c r="CM17" s="9" t="n"/>
+      <c r="CN17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -9903,7 +10284,7 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>296</v>
@@ -9913,20 +10294,20 @@
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
@@ -9963,7 +10344,7 @@
         <v/>
       </c>
       <c r="X18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>292</v>
@@ -9973,118 +10354,125 @@
         <v/>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AC18" s="12">
         <f>AB18/$E$18</f>
         <v/>
       </c>
       <c r="AD18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
-      <c r="AG18" s="9" t="n"/>
-      <c r="AH18" s="9" t="n"/>
-      <c r="AI18" s="12" t="n"/>
-      <c r="AJ18" s="9" t="n">
+      <c r="AG18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="AI18" s="12">
+        <f>AH18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="9" t="n"/>
+      <c r="AL18" s="12" t="n"/>
+      <c r="AM18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AK18" s="9" t="n">
+      <c r="AN18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="AL18" s="12">
-        <f>AK18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AM18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="AO18" s="12">
         <f>AN18/$E$18</f>
         <v/>
       </c>
       <c r="AP18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AR18" s="12">
         <f>AQ18/$E$18</f>
         <v/>
       </c>
       <c r="AS18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AU18" s="12">
         <f>AT18/$E$18</f>
         <v/>
       </c>
-      <c r="AV18" s="9" t="n"/>
-      <c r="AW18" s="9" t="n"/>
-      <c r="AX18" s="12" t="n"/>
-      <c r="AY18" s="9" t="n">
+      <c r="AV18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="AX18" s="12">
+        <f>AW18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AY18" s="9" t="n"/>
+      <c r="AZ18" s="9" t="n"/>
+      <c r="BA18" s="12" t="n"/>
+      <c r="BB18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AZ18" s="9" t="n">
+      <c r="BC18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="BA18" s="12">
-        <f>AZ18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BB18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="BD18" s="12">
         <f>BC18/$E$18</f>
         <v/>
       </c>
-      <c r="BE18" s="9" t="n"/>
-      <c r="BF18" s="9" t="n"/>
-      <c r="BG18" s="12" t="n"/>
-      <c r="BH18" s="9" t="n">
+      <c r="BE18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="BG18" s="12">
+        <f>BF18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BH18" s="9" t="n"/>
+      <c r="BI18" s="9" t="n"/>
+      <c r="BJ18" s="12" t="n"/>
+      <c r="BK18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BI18" s="9" t="n">
+      <c r="BL18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="BJ18" s="12">
-        <f>BI18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BK18" s="9" t="n"/>
-      <c r="BL18" s="9" t="n"/>
-      <c r="BM18" s="12" t="n"/>
+      <c r="BM18" s="12">
+        <f>BL18/$E$18</f>
+        <v/>
+      </c>
       <c r="BN18" s="9" t="n"/>
-      <c r="BO18" s="9" t="n">
+      <c r="BO18" s="9" t="n"/>
+      <c r="BP18" s="12" t="n"/>
+      <c r="BQ18" s="9" t="n"/>
+      <c r="BR18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="BP18" s="12">
-        <f>BO18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BQ18" s="9" t="n"/>
-      <c r="BR18" s="9" t="n"/>
-      <c r="BS18" s="12" t="n"/>
+      <c r="BS18" s="12">
+        <f>BR18/$E$18</f>
+        <v/>
+      </c>
       <c r="BT18" s="9" t="n"/>
       <c r="BU18" s="9" t="n"/>
       <c r="BV18" s="12" t="n"/>
@@ -10103,9 +10491,12 @@
       <c r="CI18" s="9" t="n"/>
       <c r="CJ18" s="9" t="n"/>
       <c r="CK18" s="12" t="n"/>
+      <c r="CL18" s="9" t="n"/>
+      <c r="CM18" s="9" t="n"/>
+      <c r="CN18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -10129,6 +10520,7 @@
     <mergeCell ref="BE3:BG3"/>
     <mergeCell ref="AP3:AR3"/>
     <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="CL3:CN3"/>
     <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="F3:H3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -594,7 +594,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 21/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 22/08/2026</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 21/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 22/08/2026</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 21/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 22/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -582,6 +582,9 @@
     <col width="9" customWidth="1" min="90" max="90"/>
     <col width="9" customWidth="1" min="91" max="91"/>
     <col width="9" customWidth="1" min="92" max="92"/>
+    <col width="9" customWidth="1" min="93" max="93"/>
+    <col width="9" customWidth="1" min="94" max="94"/>
+    <col width="9" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,90 +603,93 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CL3" s="4" t="n">
+      <c r="CO3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1146,6 +1152,21 @@
         </is>
       </c>
       <c r="CN4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CO4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CP4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CQ4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1174,10 +1195,10 @@
         <v>146</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
@@ -1254,7 +1275,7 @@
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="9" t="n">
         <v>43</v>
@@ -1264,17 +1285,17 @@
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
       <c r="AJ5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="9" t="n">
         <v>42</v>
@@ -1287,49 +1308,56 @@
         <v>1</v>
       </c>
       <c r="AN5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AO5" s="12">
         <f>AN5/$E$5</f>
         <v/>
       </c>
       <c r="AP5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AQ5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AR5" s="12">
         <f>AQ5/$E$5</f>
         <v/>
       </c>
-      <c r="AS5" s="9" t="n"/>
-      <c r="AT5" s="9" t="n"/>
-      <c r="AU5" s="12" t="n"/>
-      <c r="AV5" s="9" t="n">
+      <c r="AS5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU5" s="12">
+        <f>AT5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="9" t="n"/>
+      <c r="AX5" s="12" t="n"/>
+      <c r="AY5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AW5" s="9" t="n">
+      <c r="AZ5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AX5" s="12">
-        <f>AW5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n"/>
-      <c r="BA5" s="12" t="n"/>
+      <c r="BA5" s="12">
+        <f>AZ5/$E$5</f>
+        <v/>
+      </c>
       <c r="BB5" s="9" t="n"/>
-      <c r="BC5" s="9" t="n">
+      <c r="BC5" s="9" t="n"/>
+      <c r="BD5" s="12" t="n"/>
+      <c r="BE5" s="9" t="n"/>
+      <c r="BF5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="BD5" s="12">
-        <f>BC5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BE5" s="9" t="n"/>
-      <c r="BF5" s="9" t="n"/>
-      <c r="BG5" s="12" t="n"/>
+      <c r="BG5" s="12">
+        <f>BF5/$E$5</f>
+        <v/>
+      </c>
       <c r="BH5" s="9" t="n"/>
       <c r="BI5" s="9" t="n"/>
       <c r="BJ5" s="12" t="n"/>
@@ -1363,6 +1391,9 @@
       <c r="CL5" s="9" t="n"/>
       <c r="CM5" s="9" t="n"/>
       <c r="CN5" s="12" t="n"/>
+      <c r="CO5" s="9" t="n"/>
+      <c r="CP5" s="9" t="n"/>
+      <c r="CQ5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1407,7 +1438,7 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>35</v>
@@ -1417,17 +1448,17 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
         <v>34</v>
@@ -1437,10 +1468,10 @@
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
@@ -1516,33 +1547,40 @@
         <f>AQ6/$E$6</f>
         <v/>
       </c>
-      <c r="AS6" s="9" t="n"/>
-      <c r="AT6" s="9" t="n"/>
-      <c r="AU6" s="12" t="n"/>
-      <c r="AV6" s="9" t="n">
+      <c r="AS6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AU6" s="12">
+        <f>AT6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AV6" s="9" t="n"/>
+      <c r="AW6" s="9" t="n"/>
+      <c r="AX6" s="12" t="n"/>
+      <c r="AY6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AW6" s="9" t="n">
+      <c r="AZ6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AX6" s="12">
-        <f>AW6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
       <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n">
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n"/>
+      <c r="BF6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="BD6" s="12">
-        <f>BC6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="12" t="n"/>
+      <c r="BG6" s="12">
+        <f>BF6/$E$6</f>
+        <v/>
+      </c>
       <c r="BH6" s="9" t="n"/>
       <c r="BI6" s="9" t="n"/>
       <c r="BJ6" s="12" t="n"/>
@@ -1576,6 +1614,9 @@
       <c r="CL6" s="9" t="n"/>
       <c r="CM6" s="9" t="n"/>
       <c r="CN6" s="12" t="n"/>
+      <c r="CO6" s="9" t="n"/>
+      <c r="CP6" s="9" t="n"/>
+      <c r="CQ6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1620,7 +1661,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>48</v>
@@ -1633,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
@@ -1643,17 +1684,17 @@
         <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
@@ -1690,7 +1731,7 @@
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="9" t="n">
         <v>45</v>
@@ -1700,62 +1741,69 @@
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
-      <c r="AS7" s="9" t="n"/>
-      <c r="AT7" s="9" t="n"/>
-      <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="9" t="n">
+      <c r="AS7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AU7" s="12">
+        <f>AT7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AV7" s="9" t="n"/>
+      <c r="AW7" s="9" t="n"/>
+      <c r="AX7" s="12" t="n"/>
+      <c r="AY7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AW7" s="9" t="n">
+      <c r="AZ7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AX7" s="12">
-        <f>AW7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
       <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n">
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n"/>
+      <c r="BF7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="BD7" s="12">
-        <f>BC7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="12" t="n"/>
+      <c r="BG7" s="12">
+        <f>BF7/$E$7</f>
+        <v/>
+      </c>
       <c r="BH7" s="9" t="n"/>
       <c r="BI7" s="9" t="n"/>
       <c r="BJ7" s="12" t="n"/>
@@ -1789,6 +1837,9 @@
       <c r="CL7" s="9" t="n"/>
       <c r="CM7" s="9" t="n"/>
       <c r="CN7" s="12" t="n"/>
+      <c r="CO7" s="9" t="n"/>
+      <c r="CP7" s="9" t="n"/>
+      <c r="CQ7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1942,33 +1993,40 @@
         <f>AQ8/$E$8</f>
         <v/>
       </c>
-      <c r="AS8" s="9" t="n"/>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="12" t="n"/>
-      <c r="AV8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="9" t="n">
+      <c r="AS8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="AX8" s="12">
-        <f>AW8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
+      <c r="AU8" s="12">
+        <f>AT8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AV8" s="9" t="n"/>
+      <c r="AW8" s="9" t="n"/>
+      <c r="AX8" s="12" t="n"/>
+      <c r="AY8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
       <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n">
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n"/>
+      <c r="BF8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="BD8" s="12">
-        <f>BC8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="12" t="n"/>
+      <c r="BG8" s="12">
+        <f>BF8/$E$8</f>
+        <v/>
+      </c>
       <c r="BH8" s="9" t="n"/>
       <c r="BI8" s="9" t="n"/>
       <c r="BJ8" s="12" t="n"/>
@@ -2002,6 +2060,9 @@
       <c r="CL8" s="9" t="n"/>
       <c r="CM8" s="9" t="n"/>
       <c r="CN8" s="12" t="n"/>
+      <c r="CO8" s="9" t="n"/>
+      <c r="CP8" s="9" t="n"/>
+      <c r="CQ8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2146,7 +2207,7 @@
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="9" t="n">
         <v>1</v>
@@ -2155,33 +2216,40 @@
         <f>AQ9/$E$9</f>
         <v/>
       </c>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="12" t="n"/>
-      <c r="AV9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" s="12">
-        <f>AW9/$E$9</f>
-        <v/>
-      </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
+      <c r="AS9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="12">
+        <f>AT9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AV9" s="9" t="n"/>
+      <c r="AW9" s="9" t="n"/>
+      <c r="AX9" s="12" t="n"/>
+      <c r="AY9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
       <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" s="12">
-        <f>BC9/$E$9</f>
-        <v/>
-      </c>
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
       <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="12" t="n"/>
+      <c r="BF9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="12">
+        <f>BF9/$E$9</f>
+        <v/>
+      </c>
       <c r="BH9" s="9" t="n"/>
       <c r="BI9" s="9" t="n"/>
       <c r="BJ9" s="12" t="n"/>
@@ -2215,6 +2283,9 @@
       <c r="CL9" s="9" t="n"/>
       <c r="CM9" s="9" t="n"/>
       <c r="CN9" s="12" t="n"/>
+      <c r="CO9" s="9" t="n"/>
+      <c r="CP9" s="9" t="n"/>
+      <c r="CQ9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2239,17 +2310,17 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>335</v>
@@ -2262,54 +2333,54 @@
         <v>8</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="9" t="n">
         <v>311</v>
@@ -2319,69 +2390,76 @@
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
-      <c r="AS10" s="9" t="n"/>
-      <c r="AT10" s="9" t="n"/>
-      <c r="AU10" s="12" t="n"/>
+      <c r="AS10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AT10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AU10" s="12">
+        <f>AT10/$E$10</f>
+        <v/>
+      </c>
       <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n">
+      <c r="AW10" s="9" t="n"/>
+      <c r="AX10" s="12" t="n"/>
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AX10" s="12">
-        <f>AW10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
       <c r="BB10" s="9" t="n"/>
       <c r="BC10" s="9" t="n"/>
       <c r="BD10" s="12" t="n"/>
@@ -2421,9 +2499,12 @@
       <c r="CL10" s="9" t="n"/>
       <c r="CM10" s="9" t="n"/>
       <c r="CN10" s="12" t="n"/>
+      <c r="CO10" s="9" t="n"/>
+      <c r="CP10" s="9" t="n"/>
+      <c r="CQ10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -2442,6 +2523,7 @@
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="CO3:CQ3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="BE3:BG3"/>
@@ -2464,7 +2546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN18"/>
+  <dimension ref="A1:CQ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2559,6 +2641,9 @@
     <col width="9" customWidth="1" min="90" max="90"/>
     <col width="9" customWidth="1" min="91" max="91"/>
     <col width="9" customWidth="1" min="92" max="92"/>
+    <col width="9" customWidth="1" min="93" max="93"/>
+    <col width="9" customWidth="1" min="94" max="94"/>
+    <col width="9" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2577,90 +2662,93 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CL3" s="4" t="n">
+      <c r="CO3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -3123,6 +3211,21 @@
         </is>
       </c>
       <c r="CN4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CO4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CP4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CQ4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -3151,17 +3254,17 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>183</v>
@@ -3171,27 +3274,27 @@
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N5" s="12">
         <f>M5/$E$5</f>
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="9" t="n">
         <v>178</v>
@@ -3201,10 +3304,10 @@
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W5" s="12">
         <f>V5/$E$5</f>
@@ -3231,7 +3334,7 @@
         <v/>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="9" t="n">
         <v>177</v>
@@ -3240,17 +3343,24 @@
         <f>AE5/$E$5</f>
         <v/>
       </c>
-      <c r="AG5" s="9" t="n"/>
+      <c r="AG5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="AH5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
       <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
+      <c r="AK5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
       <c r="AM5" s="9" t="n"/>
       <c r="AN5" s="9" t="n"/>
       <c r="AO5" s="12" t="n"/>
@@ -3305,6 +3415,9 @@
       <c r="CL5" s="9" t="n"/>
       <c r="CM5" s="9" t="n"/>
       <c r="CN5" s="12" t="n"/>
+      <c r="CO5" s="9" t="n"/>
+      <c r="CP5" s="9" t="n"/>
+      <c r="CQ5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -3329,17 +3442,17 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>344</v>
@@ -3349,40 +3462,40 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
@@ -3399,7 +3512,7 @@
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="9" t="n">
         <v>335</v>
@@ -3409,183 +3522,193 @@
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
-      <c r="AY6" s="9" t="n">
+      <c r="AV6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AZ6" s="9" t="n">
+      <c r="BC6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="12" t="n"/>
+      <c r="BD6" s="12">
+        <f>BC6/$E$6</f>
+        <v/>
+      </c>
       <c r="BE6" s="9" t="n"/>
       <c r="BF6" s="9" t="n"/>
       <c r="BG6" s="12" t="n"/>
-      <c r="BH6" s="9" t="n">
+      <c r="BH6" s="9" t="n"/>
+      <c r="BI6" s="9" t="n"/>
+      <c r="BJ6" s="12" t="n"/>
+      <c r="BK6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BI6" s="9" t="n">
+      <c r="BL6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="BJ6" s="12">
-        <f>BI6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BK6" s="9" t="n"/>
-      <c r="BL6" s="9" t="n"/>
-      <c r="BM6" s="12" t="n"/>
-      <c r="BN6" s="9" t="n">
+      <c r="BM6" s="12">
+        <f>BL6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BN6" s="9" t="n"/>
+      <c r="BO6" s="9" t="n"/>
+      <c r="BP6" s="12" t="n"/>
+      <c r="BQ6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BO6" s="9" t="n">
+      <c r="BR6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="BP6" s="12">
-        <f>BO6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BQ6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BS6" s="12">
         <f>BR6/$E$6</f>
         <v/>
       </c>
       <c r="BT6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BU6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
         <v/>
       </c>
       <c r="BW6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="BX6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="BY6" s="12">
         <f>BX6/$E$6</f>
         <v/>
       </c>
       <c r="BZ6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="CA6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="CB6" s="12">
         <f>CA6/$E$6</f>
         <v/>
       </c>
       <c r="CC6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="CD6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="CE6" s="12">
         <f>CD6/$E$6</f>
         <v/>
       </c>
       <c r="CF6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CG6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="CH6" s="12">
         <f>CG6/$E$6</f>
         <v/>
       </c>
       <c r="CI6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CJ6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="CK6" s="12">
         <f>CJ6/$E$6</f>
         <v/>
       </c>
-      <c r="CL6" s="9" t="n"/>
+      <c r="CL6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="CM6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="CN6" s="12">
         <f>CM6/$E$6</f>
+        <v/>
+      </c>
+      <c r="CO6" s="9" t="n"/>
+      <c r="CP6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="CQ6" s="12">
+        <f>CP6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -3622,7 +3745,7 @@
         <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>123</v>
@@ -3632,10 +3755,10 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N7" s="12">
         <f>M7/$E$7</f>
@@ -3662,7 +3785,7 @@
         <v/>
       </c>
       <c r="U7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>120</v>
@@ -3672,10 +3795,10 @@
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
@@ -3692,7 +3815,7 @@
         <v/>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="9" t="n">
         <v>119</v>
@@ -3705,109 +3828,109 @@
         <v>3</v>
       </c>
       <c r="AH7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AI7" s="12">
         <f>AH7/$E$7</f>
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
-      <c r="AY7" s="9" t="n">
+      <c r="AV7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AZ7" s="9" t="n">
+      <c r="BC7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="12" t="n"/>
+      <c r="BD7" s="12">
+        <f>BC7/$E$7</f>
+        <v/>
+      </c>
       <c r="BE7" s="9" t="n"/>
       <c r="BF7" s="9" t="n"/>
       <c r="BG7" s="12" t="n"/>
-      <c r="BH7" s="9" t="n">
+      <c r="BH7" s="9" t="n"/>
+      <c r="BI7" s="9" t="n"/>
+      <c r="BJ7" s="12" t="n"/>
+      <c r="BK7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BI7" s="9" t="n">
+      <c r="BL7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="BJ7" s="12">
-        <f>BI7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BK7" s="9" t="n"/>
-      <c r="BL7" s="9" t="n"/>
-      <c r="BM7" s="12" t="n"/>
-      <c r="BN7" s="9" t="n">
+      <c r="BM7" s="12">
+        <f>BL7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BN7" s="9" t="n"/>
+      <c r="BO7" s="9" t="n"/>
+      <c r="BP7" s="12" t="n"/>
+      <c r="BQ7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BO7" s="9" t="n">
+      <c r="BR7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="BP7" s="12">
-        <f>BO7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BQ7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BS7" s="12">
         <f>BR7/$E$7</f>
         <v/>
       </c>
       <c r="BT7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
@@ -3817,58 +3940,68 @@
         <v>6</v>
       </c>
       <c r="BX7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BY7" s="12">
         <f>BX7/$E$7</f>
         <v/>
       </c>
       <c r="BZ7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CA7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="CB7" s="12">
         <f>CA7/$E$7</f>
         <v/>
       </c>
       <c r="CC7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CD7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="CE7" s="12">
         <f>CD7/$E$7</f>
         <v/>
       </c>
       <c r="CF7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CG7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CH7" s="12">
         <f>CG7/$E$7</f>
         <v/>
       </c>
       <c r="CI7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CJ7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CK7" s="12">
         <f>CJ7/$E$7</f>
         <v/>
       </c>
-      <c r="CL7" s="9" t="n"/>
+      <c r="CL7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="CM7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CN7" s="12">
         <f>CM7/$E$7</f>
+        <v/>
+      </c>
+      <c r="CO7" s="9" t="n"/>
+      <c r="CP7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CQ7" s="12">
+        <f>CP7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -3895,17 +4028,17 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1003</v>
@@ -3915,17 +4048,17 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>1000</v>
@@ -3935,10 +4068,10 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
@@ -3965,7 +4098,7 @@
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="9" t="n">
         <v>998</v>
@@ -3975,112 +4108,112 @@
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
-      <c r="AY8" s="9" t="n">
+      <c r="AV8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AZ8" s="9" t="n">
+      <c r="BC8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="12" t="n"/>
+      <c r="BD8" s="12">
+        <f>BC8/$E$8</f>
+        <v/>
+      </c>
       <c r="BE8" s="9" t="n"/>
       <c r="BF8" s="9" t="n"/>
       <c r="BG8" s="12" t="n"/>
-      <c r="BH8" s="9" t="n">
+      <c r="BH8" s="9" t="n"/>
+      <c r="BI8" s="9" t="n"/>
+      <c r="BJ8" s="12" t="n"/>
+      <c r="BK8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BI8" s="9" t="n">
+      <c r="BL8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="BJ8" s="12">
-        <f>BI8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BK8" s="9" t="n"/>
-      <c r="BL8" s="9" t="n"/>
-      <c r="BM8" s="12" t="n"/>
-      <c r="BN8" s="9" t="n">
+      <c r="BM8" s="12">
+        <f>BL8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BN8" s="9" t="n"/>
+      <c r="BO8" s="9" t="n"/>
+      <c r="BP8" s="12" t="n"/>
+      <c r="BQ8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BO8" s="9" t="n">
+      <c r="BR8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="BP8" s="12">
-        <f>BO8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BQ8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BS8" s="12">
         <f>BR8/$E$8</f>
@@ -4090,68 +4223,78 @@
         <v>7</v>
       </c>
       <c r="BU8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
         <v/>
       </c>
       <c r="BW8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="BX8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="BY8" s="12">
         <f>BX8/$E$8</f>
         <v/>
       </c>
       <c r="BZ8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="CA8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="CB8" s="12">
         <f>CA8/$E$8</f>
         <v/>
       </c>
       <c r="CC8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CD8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="CE8" s="12">
         <f>CD8/$E$8</f>
         <v/>
       </c>
       <c r="CF8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="CG8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="CH8" s="12">
         <f>CG8/$E$8</f>
         <v/>
       </c>
       <c r="CI8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CJ8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="CK8" s="12">
         <f>CJ8/$E$8</f>
         <v/>
       </c>
-      <c r="CL8" s="9" t="n"/>
+      <c r="CL8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="CM8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="CN8" s="12">
         <f>CM8/$E$8</f>
+        <v/>
+      </c>
+      <c r="CO8" s="9" t="n"/>
+      <c r="CP8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="CQ8" s="12">
+        <f>CP8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -4258,7 +4401,7 @@
         <v/>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="9" t="n">
         <v>1125</v>
@@ -4268,27 +4411,27 @@
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AI9" s="12">
         <f>AH9/$E$9</f>
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="AL9" s="12">
         <f>AK9/$E$9</f>
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="9" t="n">
         <v>1119</v>
@@ -4298,17 +4441,17 @@
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AR9" s="12">
         <f>AQ9/$E$9</f>
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="9" t="n">
         <v>1117</v>
@@ -4317,124 +4460,134 @@
         <f>AT9/$E$9</f>
         <v/>
       </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
-      <c r="AY9" s="9" t="n">
+      <c r="AV9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AZ9" s="9" t="n">
+      <c r="BC9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="12" t="n"/>
+      <c r="BD9" s="12">
+        <f>BC9/$E$9</f>
+        <v/>
+      </c>
       <c r="BE9" s="9" t="n"/>
       <c r="BF9" s="9" t="n"/>
       <c r="BG9" s="12" t="n"/>
-      <c r="BH9" s="9" t="n">
+      <c r="BH9" s="9" t="n"/>
+      <c r="BI9" s="9" t="n"/>
+      <c r="BJ9" s="12" t="n"/>
+      <c r="BK9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BI9" s="9" t="n">
+      <c r="BL9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="BJ9" s="12">
-        <f>BI9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BK9" s="9" t="n"/>
-      <c r="BL9" s="9" t="n"/>
-      <c r="BM9" s="12" t="n"/>
-      <c r="BN9" s="9" t="n">
+      <c r="BM9" s="12">
+        <f>BL9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BN9" s="9" t="n"/>
+      <c r="BO9" s="9" t="n"/>
+      <c r="BP9" s="12" t="n"/>
+      <c r="BQ9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BO9" s="9" t="n">
+      <c r="BR9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="BP9" s="12">
-        <f>BO9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BQ9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BS9" s="12">
         <f>BR9/$E$9</f>
         <v/>
       </c>
       <c r="BT9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
         <v/>
       </c>
       <c r="BW9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BX9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="BY9" s="12">
         <f>BX9/$E$9</f>
         <v/>
       </c>
       <c r="BZ9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CA9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="CB9" s="12">
         <f>CA9/$E$9</f>
         <v/>
       </c>
       <c r="CC9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CD9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="CE9" s="12">
         <f>CD9/$E$9</f>
         <v/>
       </c>
       <c r="CF9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="CG9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="CH9" s="12">
         <f>CG9/$E$9</f>
         <v/>
       </c>
       <c r="CI9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="CJ9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="CK9" s="12">
         <f>CJ9/$E$9</f>
         <v/>
       </c>
-      <c r="CL9" s="9" t="n"/>
+      <c r="CL9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="CM9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="CN9" s="12">
         <f>CM9/$E$9</f>
+        <v/>
+      </c>
+      <c r="CO9" s="9" t="n"/>
+      <c r="CP9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CQ9" s="12">
+        <f>CP9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -4461,17 +4614,17 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H10" s="11">
         <f>G10/$E$10</f>
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>509</v>
@@ -4481,27 +4634,27 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>504</v>
@@ -4511,10 +4664,10 @@
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
@@ -4531,7 +4684,7 @@
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="9" t="n">
         <v>502</v>
@@ -4541,37 +4694,37 @@
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN10" s="9" t="n">
         <v>491</v>
@@ -4581,79 +4734,79 @@
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AT10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
-      <c r="AY10" s="9" t="n">
+      <c r="AV10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AY10" s="9" t="n"/>
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AZ10" s="9" t="n">
+      <c r="BC10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="BA10" s="12">
-        <f>AZ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BB10" s="9" t="n"/>
-      <c r="BC10" s="9" t="n"/>
-      <c r="BD10" s="12" t="n"/>
+      <c r="BD10" s="12">
+        <f>BC10/$E$10</f>
+        <v/>
+      </c>
       <c r="BE10" s="9" t="n"/>
       <c r="BF10" s="9" t="n"/>
       <c r="BG10" s="12" t="n"/>
-      <c r="BH10" s="9" t="n">
+      <c r="BH10" s="9" t="n"/>
+      <c r="BI10" s="9" t="n"/>
+      <c r="BJ10" s="12" t="n"/>
+      <c r="BK10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BI10" s="9" t="n">
+      <c r="BL10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BJ10" s="12">
-        <f>BI10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BK10" s="9" t="n"/>
-      <c r="BL10" s="9" t="n"/>
-      <c r="BM10" s="12" t="n"/>
-      <c r="BN10" s="9" t="n">
+      <c r="BM10" s="12">
+        <f>BL10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BN10" s="9" t="n"/>
+      <c r="BO10" s="9" t="n"/>
+      <c r="BP10" s="12" t="n"/>
+      <c r="BQ10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BO10" s="9" t="n">
+      <c r="BR10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="BP10" s="12">
-        <f>BO10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BQ10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BS10" s="12">
         <f>BR10/$E$10</f>
         <v/>
       </c>
       <c r="BT10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU10" s="9" t="n">
         <v>462</v>
@@ -4666,58 +4819,68 @@
         <v>2</v>
       </c>
       <c r="BX10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BY10" s="12">
         <f>BX10/$E$10</f>
         <v/>
       </c>
       <c r="BZ10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CA10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="CB10" s="12">
         <f>CA10/$E$10</f>
         <v/>
       </c>
       <c r="CC10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CD10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="CE10" s="12">
         <f>CD10/$E$10</f>
         <v/>
       </c>
       <c r="CF10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="CG10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="CH10" s="12">
         <f>CG10/$E$10</f>
         <v/>
       </c>
       <c r="CI10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="CJ10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="CK10" s="12">
         <f>CJ10/$E$10</f>
         <v/>
       </c>
-      <c r="CL10" s="9" t="n"/>
+      <c r="CL10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="CM10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="CN10" s="12">
         <f>CM10/$E$10</f>
+        <v/>
+      </c>
+      <c r="CO10" s="9" t="n"/>
+      <c r="CP10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="CQ10" s="12">
+        <f>CP10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -4834,7 +4997,7 @@
         <v/>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="9" t="n">
         <v>467</v>
@@ -4847,17 +5010,17 @@
         <v>1</v>
       </c>
       <c r="AK11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL11" s="12">
         <f>AK11/$E$11</f>
         <v/>
       </c>
       <c r="AM11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO11" s="12">
         <f>AN11/$E$11</f>
@@ -4883,60 +5046,60 @@
         <f>AT11/$E$11</f>
         <v/>
       </c>
-      <c r="AV11" s="9" t="n"/>
-      <c r="AW11" s="9" t="n"/>
-      <c r="AX11" s="12" t="n"/>
-      <c r="AY11" s="9" t="n">
+      <c r="AV11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="AX11" s="12">
+        <f>AW11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="9" t="n"/>
+      <c r="AZ11" s="9" t="n"/>
+      <c r="BA11" s="12" t="n"/>
+      <c r="BB11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AZ11" s="9" t="n">
+      <c r="BC11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="BA11" s="12">
-        <f>AZ11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BB11" s="9" t="n"/>
-      <c r="BC11" s="9" t="n"/>
-      <c r="BD11" s="12" t="n"/>
+      <c r="BD11" s="12">
+        <f>BC11/$E$11</f>
+        <v/>
+      </c>
       <c r="BE11" s="9" t="n"/>
       <c r="BF11" s="9" t="n"/>
       <c r="BG11" s="12" t="n"/>
-      <c r="BH11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="9" t="n">
+      <c r="BH11" s="9" t="n"/>
+      <c r="BI11" s="9" t="n"/>
+      <c r="BJ11" s="12" t="n"/>
+      <c r="BK11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BJ11" s="12">
-        <f>BI11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BK11" s="9" t="n"/>
-      <c r="BL11" s="9" t="n"/>
-      <c r="BM11" s="12" t="n"/>
-      <c r="BN11" s="9" t="n">
+      <c r="BM11" s="12">
+        <f>BL11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BN11" s="9" t="n"/>
+      <c r="BO11" s="9" t="n"/>
+      <c r="BP11" s="12" t="n"/>
+      <c r="BQ11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BO11" s="9" t="n">
+      <c r="BR11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="BP11" s="12">
-        <f>BO11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BQ11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BS11" s="12">
         <f>BR11/$E$11</f>
         <v/>
       </c>
       <c r="BT11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU11" s="9" t="n">
         <v>463</v>
@@ -4946,40 +5109,40 @@
         <v/>
       </c>
       <c r="BW11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BX11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BY11" s="12">
         <f>BX11/$E$11</f>
         <v/>
       </c>
       <c r="BZ11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CA11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="CB11" s="12">
         <f>CA11/$E$11</f>
         <v/>
       </c>
       <c r="CC11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CE11" s="12">
         <f>CD11/$E$11</f>
         <v/>
       </c>
       <c r="CF11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="CH11" s="12">
         <f>CG11/$E$11</f>
@@ -4989,18 +5152,28 @@
         <v>2</v>
       </c>
       <c r="CJ11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CK11" s="12">
         <f>CJ11/$E$11</f>
         <v/>
       </c>
-      <c r="CL11" s="9" t="n"/>
+      <c r="CL11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="CM11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CN11" s="12">
         <f>CM11/$E$11</f>
+        <v/>
+      </c>
+      <c r="CO11" s="9" t="n"/>
+      <c r="CP11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="CQ11" s="12">
+        <f>CP11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -5117,7 +5290,7 @@
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" s="9" t="n">
         <v>236</v>
@@ -5127,17 +5300,17 @@
         <v/>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL12" s="12">
         <f>AK12/$E$12</f>
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="9" t="n">
         <v>235</v>
@@ -5147,10 +5320,10 @@
         <v/>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AR12" s="12">
         <f>AQ12/$E$12</f>
@@ -5166,48 +5339,48 @@
         <f>AT12/$E$12</f>
         <v/>
       </c>
-      <c r="AV12" s="9" t="n"/>
-      <c r="AW12" s="9" t="n"/>
-      <c r="AX12" s="12" t="n"/>
-      <c r="AY12" s="9" t="n">
+      <c r="AV12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AX12" s="12">
+        <f>AW12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="9" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="12" t="n"/>
+      <c r="BB12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="AZ12" s="9" t="n">
+      <c r="BC12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="BA12" s="12">
-        <f>AZ12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BB12" s="9" t="n"/>
-      <c r="BC12" s="9" t="n"/>
-      <c r="BD12" s="12" t="n"/>
+      <c r="BD12" s="12">
+        <f>BC12/$E$12</f>
+        <v/>
+      </c>
       <c r="BE12" s="9" t="n"/>
       <c r="BF12" s="9" t="n"/>
       <c r="BG12" s="12" t="n"/>
-      <c r="BH12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="9" t="n">
+      <c r="BH12" s="9" t="n"/>
+      <c r="BI12" s="9" t="n"/>
+      <c r="BJ12" s="12" t="n"/>
+      <c r="BK12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="BJ12" s="12">
-        <f>BI12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BK12" s="9" t="n"/>
-      <c r="BL12" s="9" t="n"/>
-      <c r="BM12" s="12" t="n"/>
-      <c r="BN12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="BP12" s="12">
-        <f>BO12/$E$12</f>
-        <v/>
-      </c>
+      <c r="BM12" s="12">
+        <f>BL12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BN12" s="9" t="n"/>
+      <c r="BO12" s="9" t="n"/>
+      <c r="BP12" s="12" t="n"/>
       <c r="BQ12" s="9" t="n">
         <v>0</v>
       </c>
@@ -5249,7 +5422,7 @@
         <v/>
       </c>
       <c r="CC12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD12" s="9" t="n">
         <v>236</v>
@@ -5259,31 +5432,41 @@
         <v/>
       </c>
       <c r="CF12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="CG12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="CH12" s="12">
         <f>CG12/$E$12</f>
         <v/>
       </c>
       <c r="CI12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="CJ12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="CK12" s="12">
         <f>CJ12/$E$12</f>
         <v/>
       </c>
-      <c r="CL12" s="9" t="n"/>
+      <c r="CL12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="CM12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="CN12" s="12">
         <f>CM12/$E$12</f>
+        <v/>
+      </c>
+      <c r="CO12" s="9" t="n"/>
+      <c r="CP12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="CQ12" s="12">
+        <f>CP12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -5310,17 +5493,17 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>626</v>
@@ -5330,27 +5513,27 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="N13" s="12">
         <f>M13/$E$13</f>
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
         <v>622</v>
@@ -5360,10 +5543,10 @@
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
@@ -5380,7 +5563,7 @@
         <v/>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="9" t="n">
         <v>621</v>
@@ -5390,142 +5573,142 @@
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AF13" s="12">
         <f>AE13/$E$13</f>
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AN13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
       <c r="AP13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
-      <c r="AV13" s="9" t="n"/>
-      <c r="AW13" s="9" t="n"/>
-      <c r="AX13" s="12" t="n"/>
-      <c r="AY13" s="9" t="n">
+      <c r="AV13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="AX13" s="12">
+        <f>AW13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="9" t="n"/>
+      <c r="AZ13" s="9" t="n"/>
+      <c r="BA13" s="12" t="n"/>
+      <c r="BB13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="AZ13" s="9" t="n">
+      <c r="BC13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="BA13" s="12">
-        <f>AZ13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BB13" s="9" t="n"/>
-      <c r="BC13" s="9" t="n"/>
-      <c r="BD13" s="12" t="n"/>
+      <c r="BD13" s="12">
+        <f>BC13/$E$13</f>
+        <v/>
+      </c>
       <c r="BE13" s="9" t="n"/>
       <c r="BF13" s="9" t="n"/>
       <c r="BG13" s="12" t="n"/>
-      <c r="BH13" s="9" t="n">
+      <c r="BH13" s="9" t="n"/>
+      <c r="BI13" s="9" t="n"/>
+      <c r="BJ13" s="12" t="n"/>
+      <c r="BK13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="BI13" s="9" t="n">
+      <c r="BL13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="BJ13" s="12">
-        <f>BI13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BK13" s="9" t="n"/>
-      <c r="BL13" s="9" t="n"/>
-      <c r="BM13" s="12" t="n"/>
-      <c r="BN13" s="9" t="n">
+      <c r="BM13" s="12">
+        <f>BL13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BN13" s="9" t="n"/>
+      <c r="BO13" s="9" t="n"/>
+      <c r="BP13" s="12" t="n"/>
+      <c r="BQ13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="BO13" s="9" t="n">
+      <c r="BR13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="BP13" s="12">
-        <f>BO13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BQ13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BS13" s="12">
         <f>BR13/$E$13</f>
         <v/>
       </c>
       <c r="BT13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BU13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
         <v/>
       </c>
       <c r="BW13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="BY13" s="12">
         <f>BX13/$E$13</f>
         <v/>
       </c>
       <c r="BZ13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="CA13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="CB13" s="12">
         <f>CA13/$E$13</f>
@@ -5535,38 +5718,48 @@
         <v>4</v>
       </c>
       <c r="CD13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="CE13" s="12">
         <f>CD13/$E$13</f>
         <v/>
       </c>
       <c r="CF13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="CG13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="CH13" s="12">
         <f>CG13/$E$13</f>
         <v/>
       </c>
       <c r="CI13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="CJ13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="CK13" s="12">
         <f>CJ13/$E$13</f>
         <v/>
       </c>
-      <c r="CL13" s="9" t="n"/>
+      <c r="CL13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="CM13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="CN13" s="12">
         <f>CM13/$E$13</f>
+        <v/>
+      </c>
+      <c r="CO13" s="9" t="n"/>
+      <c r="CP13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="CQ13" s="12">
+        <f>CP13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -5593,17 +5786,17 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H14" s="11">
         <f>G14/$E$14</f>
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>1151</v>
@@ -5613,27 +5806,27 @@
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>1146</v>
@@ -5643,10 +5836,10 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
@@ -5663,7 +5856,7 @@
         <v/>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="9" t="n">
         <v>1145</v>
@@ -5673,17 +5866,17 @@
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="AF14" s="12">
         <f>AE14/$E$14</f>
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="9" t="n">
         <v>1142</v>
@@ -5693,122 +5886,122 @@
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="AL14" s="12">
         <f>AK14/$E$14</f>
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
-      <c r="AV14" s="9" t="n"/>
-      <c r="AW14" s="9" t="n"/>
-      <c r="AX14" s="12" t="n"/>
-      <c r="AY14" s="9" t="n">
+      <c r="AV14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="AX14" s="12">
+        <f>AW14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="9" t="n"/>
+      <c r="AZ14" s="9" t="n"/>
+      <c r="BA14" s="12" t="n"/>
+      <c r="BB14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="AZ14" s="9" t="n">
+      <c r="BC14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="BA14" s="12">
-        <f>AZ14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BB14" s="9" t="n"/>
-      <c r="BC14" s="9" t="n"/>
-      <c r="BD14" s="12" t="n"/>
+      <c r="BD14" s="12">
+        <f>BC14/$E$14</f>
+        <v/>
+      </c>
       <c r="BE14" s="9" t="n"/>
       <c r="BF14" s="9" t="n"/>
       <c r="BG14" s="12" t="n"/>
-      <c r="BH14" s="9" t="n">
+      <c r="BH14" s="9" t="n"/>
+      <c r="BI14" s="9" t="n"/>
+      <c r="BJ14" s="12" t="n"/>
+      <c r="BK14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="BI14" s="9" t="n">
+      <c r="BL14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="BJ14" s="12">
-        <f>BI14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BK14" s="9" t="n"/>
-      <c r="BL14" s="9" t="n"/>
-      <c r="BM14" s="12" t="n"/>
-      <c r="BN14" s="9" t="n">
+      <c r="BM14" s="12">
+        <f>BL14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BN14" s="9" t="n"/>
+      <c r="BO14" s="9" t="n"/>
+      <c r="BP14" s="12" t="n"/>
+      <c r="BQ14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BO14" s="9" t="n">
+      <c r="BR14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="BP14" s="12">
-        <f>BO14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BQ14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BS14" s="12">
         <f>BR14/$E$14</f>
         <v/>
       </c>
       <c r="BT14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BU14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BV14" s="12">
         <f>BU14/$E$14</f>
         <v/>
       </c>
       <c r="BW14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="BX14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="BY14" s="12">
         <f>BX14/$E$14</f>
         <v/>
       </c>
       <c r="BZ14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="CA14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="CB14" s="12">
         <f>CA14/$E$14</f>
@@ -5844,12 +6037,22 @@
         <f>CJ14/$E$14</f>
         <v/>
       </c>
-      <c r="CL14" s="9" t="n"/>
+      <c r="CL14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CM14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CN14" s="12">
         <f>CM14/$E$14</f>
+        <v/>
+      </c>
+      <c r="CO14" s="9" t="n"/>
+      <c r="CP14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" s="12">
+        <f>CP14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -5886,7 +6089,7 @@
         <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>127</v>
@@ -5896,10 +6099,10 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N15" s="12">
         <f>M15/$E$15</f>
@@ -5946,7 +6149,7 @@
         <v/>
       </c>
       <c r="AA15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="9" t="n">
         <v>126</v>
@@ -5959,17 +6162,17 @@
         <v>1</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF15" s="12">
         <f>AE15/$E$15</f>
         <v/>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AI15" s="12">
         <f>AH15/$E$15</f>
@@ -5986,7 +6189,7 @@
         <v/>
       </c>
       <c r="AM15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN15" s="9" t="n">
         <v>124</v>
@@ -5996,17 +6199,17 @@
         <v/>
       </c>
       <c r="AP15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AR15" s="12">
         <f>AQ15/$E$15</f>
         <v/>
       </c>
       <c r="AS15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT15" s="9" t="n">
         <v>121</v>
@@ -6015,53 +6218,53 @@
         <f>AT15/$E$15</f>
         <v/>
       </c>
-      <c r="AV15" s="9" t="n"/>
-      <c r="AW15" s="9" t="n"/>
-      <c r="AX15" s="12" t="n"/>
-      <c r="AY15" s="9" t="n">
+      <c r="AV15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="AX15" s="12">
+        <f>AW15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AY15" s="9" t="n"/>
+      <c r="AZ15" s="9" t="n"/>
+      <c r="BA15" s="12" t="n"/>
+      <c r="BB15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="AZ15" s="9" t="n">
+      <c r="BC15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="BA15" s="12">
-        <f>AZ15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BB15" s="9" t="n"/>
-      <c r="BC15" s="9" t="n"/>
-      <c r="BD15" s="12" t="n"/>
+      <c r="BD15" s="12">
+        <f>BC15/$E$15</f>
+        <v/>
+      </c>
       <c r="BE15" s="9" t="n"/>
       <c r="BF15" s="9" t="n"/>
       <c r="BG15" s="12" t="n"/>
-      <c r="BH15" s="9" t="n">
+      <c r="BH15" s="9" t="n"/>
+      <c r="BI15" s="9" t="n"/>
+      <c r="BJ15" s="12" t="n"/>
+      <c r="BK15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BI15" s="9" t="n">
+      <c r="BL15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="BJ15" s="12">
-        <f>BI15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BK15" s="9" t="n"/>
-      <c r="BL15" s="9" t="n"/>
-      <c r="BM15" s="12" t="n"/>
-      <c r="BN15" s="9" t="n">
+      <c r="BM15" s="12">
+        <f>BL15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BN15" s="9" t="n"/>
+      <c r="BO15" s="9" t="n"/>
+      <c r="BP15" s="12" t="n"/>
+      <c r="BQ15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BO15" s="9" t="n">
+      <c r="BR15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="BP15" s="12">
-        <f>BO15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BQ15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BS15" s="12">
         <f>BR15/$E$15</f>
@@ -6071,24 +6274,24 @@
         <v>3</v>
       </c>
       <c r="BU15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BV15" s="12">
         <f>BU15/$E$15</f>
         <v/>
       </c>
       <c r="BW15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BX15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="BY15" s="12">
         <f>BX15/$E$15</f>
         <v/>
       </c>
       <c r="BZ15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="CA15" s="9" t="n">
         <v>76</v>
@@ -6098,10 +6301,10 @@
         <v/>
       </c>
       <c r="CC15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="CD15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="CE15" s="12">
         <f>CD15/$E$15</f>
@@ -6127,12 +6330,22 @@
         <f>CJ15/$E$15</f>
         <v/>
       </c>
-      <c r="CL15" s="9" t="n"/>
+      <c r="CL15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CM15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CN15" s="12">
         <f>CM15/$E$15</f>
+        <v/>
+      </c>
+      <c r="CO15" s="9" t="n"/>
+      <c r="CP15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" s="12">
+        <f>CP15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -6298,51 +6511,58 @@
         <f>AT16/$E$16</f>
         <v/>
       </c>
-      <c r="AV16" s="9" t="n"/>
-      <c r="AW16" s="9" t="n"/>
-      <c r="AX16" s="12" t="n"/>
-      <c r="AY16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="9" t="n">
+      <c r="AV16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BA16" s="12">
-        <f>AZ16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BB16" s="9" t="n"/>
-      <c r="BC16" s="9" t="n"/>
-      <c r="BD16" s="12" t="n"/>
+      <c r="AX16" s="12">
+        <f>AW16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="9" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="12" t="n"/>
+      <c r="BB16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="BD16" s="12">
+        <f>BC16/$E$16</f>
+        <v/>
+      </c>
       <c r="BE16" s="9" t="n"/>
       <c r="BF16" s="9" t="n"/>
       <c r="BG16" s="12" t="n"/>
-      <c r="BH16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" s="9" t="n">
+      <c r="BH16" s="9" t="n"/>
+      <c r="BI16" s="9" t="n"/>
+      <c r="BJ16" s="12" t="n"/>
+      <c r="BK16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BJ16" s="12">
-        <f>BI16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BK16" s="9" t="n"/>
-      <c r="BL16" s="9" t="n"/>
-      <c r="BM16" s="12" t="n"/>
-      <c r="BN16" s="9" t="n">
+      <c r="BM16" s="12">
+        <f>BL16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BN16" s="9" t="n"/>
+      <c r="BO16" s="9" t="n"/>
+      <c r="BP16" s="12" t="n"/>
+      <c r="BQ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BO16" s="9" t="n">
+      <c r="BR16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BP16" s="12">
-        <f>BO16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BQ16" s="9" t="n"/>
-      <c r="BR16" s="9" t="n"/>
-      <c r="BS16" s="12" t="n"/>
+      <c r="BS16" s="12">
+        <f>BR16/$E$16</f>
+        <v/>
+      </c>
       <c r="BT16" s="9" t="n"/>
       <c r="BU16" s="9" t="n"/>
       <c r="BV16" s="12" t="n"/>
@@ -6362,11 +6582,14 @@
       <c r="CJ16" s="9" t="n"/>
       <c r="CK16" s="12" t="n"/>
       <c r="CL16" s="9" t="n"/>
-      <c r="CM16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN16" s="12">
-        <f>CM16/$E$16</f>
+      <c r="CM16" s="9" t="n"/>
+      <c r="CN16" s="12" t="n"/>
+      <c r="CO16" s="9" t="n"/>
+      <c r="CP16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" s="12">
+        <f>CP16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -6479,6 +6702,9 @@
       <c r="CL17" s="9" t="n"/>
       <c r="CM17" s="9" t="n"/>
       <c r="CN17" s="12" t="n"/>
+      <c r="CO17" s="9" t="n"/>
+      <c r="CP17" s="9" t="n"/>
+      <c r="CQ17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6503,17 +6729,17 @@
         <v>830</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>191</v>
@@ -6523,46 +6749,48 @@
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
-      <c r="X18" s="9" t="n"/>
+      <c r="X18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="Y18" s="9" t="n">
         <v>139</v>
       </c>
@@ -6571,8 +6799,13 @@
         <v/>
       </c>
       <c r="AA18" s="9" t="n"/>
-      <c r="AB18" s="9" t="n"/>
-      <c r="AC18" s="12" t="n"/>
+      <c r="AB18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="AC18" s="12">
+        <f>AB18/$E$18</f>
+        <v/>
+      </c>
       <c r="AD18" s="9" t="n"/>
       <c r="AE18" s="9" t="n"/>
       <c r="AF18" s="12" t="n"/>
@@ -6636,9 +6869,12 @@
       <c r="CL18" s="9" t="n"/>
       <c r="CM18" s="9" t="n"/>
       <c r="CN18" s="12" t="n"/>
+      <c r="CO18" s="9" t="n"/>
+      <c r="CP18" s="9" t="n"/>
+      <c r="CQ18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -6657,6 +6893,7 @@
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="CO3:CQ3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="BE3:BG3"/>
@@ -6679,7 +6916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN18"/>
+  <dimension ref="A1:CQ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6774,6 +7011,9 @@
     <col width="9" customWidth="1" min="90" max="90"/>
     <col width="9" customWidth="1" min="91" max="91"/>
     <col width="9" customWidth="1" min="92" max="92"/>
+    <col width="9" customWidth="1" min="93" max="93"/>
+    <col width="9" customWidth="1" min="94" max="94"/>
+    <col width="9" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6792,90 +7032,93 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CL3" s="4" t="n">
+      <c r="CO3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -7338,6 +7581,21 @@
         </is>
       </c>
       <c r="CN4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CO4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CP4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CQ4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -7366,10 +7624,10 @@
         <v>715</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H5" s="11">
         <f>G5/$E$5</f>
@@ -7396,7 +7654,7 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>302</v>
@@ -7406,10 +7664,10 @@
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
@@ -7436,7 +7694,7 @@
         <v/>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="9" t="n">
         <v>298</v>
@@ -7449,115 +7707,122 @@
         <v>1</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AF5" s="12">
         <f>AE5/$E$5</f>
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AI5" s="12">
         <f>AH5/$E$5</f>
         <v/>
       </c>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="12" t="n"/>
-      <c r="AM5" s="9" t="n">
+      <c r="AJ5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="AL5" s="12">
+        <f>AK5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AM5" s="9" t="n"/>
+      <c r="AN5" s="9" t="n"/>
+      <c r="AO5" s="12" t="n"/>
+      <c r="AP5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN5" s="9" t="n">
+      <c r="AQ5" s="9" t="n">
         <v>293</v>
-      </c>
-      <c r="AO5" s="12">
-        <f>AN5/$E$5</f>
-        <v/>
-      </c>
-      <c r="AP5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ5" s="9" t="n">
-        <v>291</v>
       </c>
       <c r="AR5" s="12">
         <f>AQ5/$E$5</f>
         <v/>
       </c>
       <c r="AS5" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT5" s="9" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AU5" s="12">
         <f>AT5/$E$5</f>
         <v/>
       </c>
       <c r="AV5" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="AW5" s="9" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AX5" s="12">
         <f>AW5/$E$5</f>
         <v/>
       </c>
-      <c r="AY5" s="9" t="n"/>
-      <c r="AZ5" s="9" t="n"/>
-      <c r="BA5" s="12" t="n"/>
-      <c r="BB5" s="9" t="n">
+      <c r="AY5" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AZ5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="BA5" s="12">
+        <f>AZ5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BB5" s="9" t="n"/>
+      <c r="BC5" s="9" t="n"/>
+      <c r="BD5" s="12" t="n"/>
+      <c r="BE5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BC5" s="9" t="n">
+      <c r="BF5" s="9" t="n">
         <v>285</v>
-      </c>
-      <c r="BD5" s="12">
-        <f>BC5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BE5" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BF5" s="9" t="n">
-        <v>283</v>
       </c>
       <c r="BG5" s="12">
         <f>BF5/$E$5</f>
         <v/>
       </c>
-      <c r="BH5" s="9" t="n"/>
-      <c r="BI5" s="9" t="n"/>
-      <c r="BJ5" s="12" t="n"/>
-      <c r="BK5" s="9" t="n">
+      <c r="BH5" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BI5" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="BJ5" s="12">
+        <f>BI5/$E$5</f>
+        <v/>
+      </c>
+      <c r="BK5" s="9" t="n"/>
+      <c r="BL5" s="9" t="n"/>
+      <c r="BM5" s="12" t="n"/>
+      <c r="BN5" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="BL5" s="9" t="n">
+      <c r="BO5" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="BM5" s="12">
-        <f>BL5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BN5" s="9" t="n"/>
-      <c r="BO5" s="9" t="n"/>
-      <c r="BP5" s="12" t="n"/>
+      <c r="BP5" s="12">
+        <f>BO5/$E$5</f>
+        <v/>
+      </c>
       <c r="BQ5" s="9" t="n"/>
-      <c r="BR5" s="9" t="n">
+      <c r="BR5" s="9" t="n"/>
+      <c r="BS5" s="12" t="n"/>
+      <c r="BT5" s="9" t="n"/>
+      <c r="BU5" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="BS5" s="12">
-        <f>BR5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BT5" s="9" t="n"/>
-      <c r="BU5" s="9" t="n"/>
-      <c r="BV5" s="12" t="n"/>
+      <c r="BV5" s="12">
+        <f>BU5/$E$5</f>
+        <v/>
+      </c>
       <c r="BW5" s="9" t="n"/>
       <c r="BX5" s="9" t="n"/>
       <c r="BY5" s="12" t="n"/>
@@ -7576,6 +7841,9 @@
       <c r="CL5" s="9" t="n"/>
       <c r="CM5" s="9" t="n"/>
       <c r="CN5" s="12" t="n"/>
+      <c r="CO5" s="9" t="n"/>
+      <c r="CP5" s="9" t="n"/>
+      <c r="CQ5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -7600,17 +7868,17 @@
         <v>1950</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="H6" s="11">
         <f>G6/$E$6</f>
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>954</v>
@@ -7620,17 +7888,17 @@
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="N6" s="12">
         <f>M6/$E$6</f>
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>953</v>
@@ -7640,20 +7908,20 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
@@ -7670,7 +7938,7 @@
         <v/>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="9" t="n">
         <v>950</v>
@@ -7680,118 +7948,125 @@
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="AF6" s="12">
         <f>AE6/$E$6</f>
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="12" t="n"/>
-      <c r="AM6" s="9" t="n">
+      <c r="AJ6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>938</v>
+      </c>
+      <c r="AL6" s="12">
+        <f>AK6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AM6" s="9" t="n"/>
+      <c r="AN6" s="9" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AN6" s="9" t="n">
+      <c r="AQ6" s="9" t="n">
         <v>935</v>
-      </c>
-      <c r="AO6" s="12">
-        <f>AN6/$E$6</f>
-        <v/>
-      </c>
-      <c r="AP6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ6" s="9" t="n">
-        <v>925</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
-      <c r="BB6" s="9" t="n">
+      <c r="AY6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="BC6" s="9" t="n">
+      <c r="BF6" s="9" t="n">
         <v>901</v>
-      </c>
-      <c r="BD6" s="12">
-        <f>BC6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BE6" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF6" s="9" t="n">
-        <v>853</v>
       </c>
       <c r="BG6" s="12">
         <f>BF6/$E$6</f>
         <v/>
       </c>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n"/>
-      <c r="BJ6" s="12" t="n"/>
-      <c r="BK6" s="9" t="n">
+      <c r="BH6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI6" s="9" t="n">
+        <v>853</v>
+      </c>
+      <c r="BJ6" s="12">
+        <f>BI6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BK6" s="9" t="n"/>
+      <c r="BL6" s="9" t="n"/>
+      <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BL6" s="9" t="n">
+      <c r="BO6" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BM6" s="12">
-        <f>BL6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n"/>
-      <c r="BP6" s="12" t="n"/>
+      <c r="BP6" s="12">
+        <f>BO6/$E$6</f>
+        <v/>
+      </c>
       <c r="BQ6" s="9" t="n"/>
-      <c r="BR6" s="9" t="n">
+      <c r="BR6" s="9" t="n"/>
+      <c r="BS6" s="12" t="n"/>
+      <c r="BT6" s="9" t="n"/>
+      <c r="BU6" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="BS6" s="12">
-        <f>BR6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BT6" s="9" t="n"/>
-      <c r="BU6" s="9" t="n"/>
-      <c r="BV6" s="12" t="n"/>
+      <c r="BV6" s="12">
+        <f>BU6/$E$6</f>
+        <v/>
+      </c>
       <c r="BW6" s="9" t="n"/>
       <c r="BX6" s="9" t="n"/>
       <c r="BY6" s="12" t="n"/>
@@ -7810,6 +8085,9 @@
       <c r="CL6" s="9" t="n"/>
       <c r="CM6" s="9" t="n"/>
       <c r="CN6" s="12" t="n"/>
+      <c r="CO6" s="9" t="n"/>
+      <c r="CP6" s="9" t="n"/>
+      <c r="CQ6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -7854,7 +8132,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>48</v>
@@ -7864,10 +8142,10 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
@@ -7933,99 +8211,106 @@
         <f>AH7/$E$7</f>
         <v/>
       </c>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="12" t="n"/>
-      <c r="AM7" s="9" t="n">
+      <c r="AJ7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="AL7" s="12">
+        <f>AK7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AM7" s="9" t="n"/>
+      <c r="AN7" s="9" t="n"/>
+      <c r="AO7" s="12" t="n"/>
+      <c r="AP7" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="AN7" s="9" t="n">
+      <c r="AQ7" s="9" t="n">
         <v>47</v>
-      </c>
-      <c r="AO7" s="12">
-        <f>AN7/$E$7</f>
-        <v/>
-      </c>
-      <c r="AP7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ7" s="9" t="n">
-        <v>48</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
       <c r="AV7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
-      <c r="BB7" s="9" t="n">
+      <c r="AY7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BC7" s="9" t="n">
+      <c r="AZ7" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF7" s="9" t="n">
         <v>42</v>
-      </c>
-      <c r="BD7" s="12">
-        <f>BC7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BE7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF7" s="9" t="n">
-        <v>39</v>
       </c>
       <c r="BG7" s="12">
         <f>BF7/$E$7</f>
         <v/>
       </c>
-      <c r="BH7" s="9" t="n"/>
-      <c r="BI7" s="9" t="n"/>
-      <c r="BJ7" s="12" t="n"/>
-      <c r="BK7" s="9" t="n">
+      <c r="BH7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI7" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="BJ7" s="12">
+        <f>BI7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BK7" s="9" t="n"/>
+      <c r="BL7" s="9" t="n"/>
+      <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BL7" s="9" t="n">
+      <c r="BO7" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="BM7" s="12">
-        <f>BL7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BN7" s="9" t="n"/>
-      <c r="BO7" s="9" t="n"/>
-      <c r="BP7" s="12" t="n"/>
+      <c r="BP7" s="12">
+        <f>BO7/$E$7</f>
+        <v/>
+      </c>
       <c r="BQ7" s="9" t="n"/>
-      <c r="BR7" s="9" t="n">
+      <c r="BR7" s="9" t="n"/>
+      <c r="BS7" s="12" t="n"/>
+      <c r="BT7" s="9" t="n"/>
+      <c r="BU7" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BS7" s="12">
-        <f>BR7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BT7" s="9" t="n"/>
-      <c r="BU7" s="9" t="n"/>
-      <c r="BV7" s="12" t="n"/>
+      <c r="BV7" s="12">
+        <f>BU7/$E$7</f>
+        <v/>
+      </c>
       <c r="BW7" s="9" t="n"/>
       <c r="BX7" s="9" t="n"/>
       <c r="BY7" s="12" t="n"/>
@@ -8044,6 +8329,9 @@
       <c r="CL7" s="9" t="n"/>
       <c r="CM7" s="9" t="n"/>
       <c r="CN7" s="12" t="n"/>
+      <c r="CO7" s="9" t="n"/>
+      <c r="CP7" s="9" t="n"/>
+      <c r="CQ7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -8068,17 +8356,17 @@
         <v>2156</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H8" s="11">
         <f>G8/$E$8</f>
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1058</v>
@@ -8088,17 +8376,17 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="N8" s="12">
         <f>M8/$E$8</f>
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>1056</v>
@@ -8108,10 +8396,10 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="T8" s="12">
         <f>S8/$E$8</f>
@@ -8138,7 +8426,7 @@
         <v/>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="9" t="n">
         <v>1054</v>
@@ -8148,17 +8436,17 @@
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="AF8" s="12">
         <f>AE8/$E$8</f>
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="9" t="n">
         <v>1052</v>
@@ -8167,99 +8455,106 @@
         <f>AH8/$E$8</f>
         <v/>
       </c>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="12" t="n"/>
-      <c r="AM8" s="9" t="n">
+      <c r="AJ8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN8" s="9" t="n">
+      <c r="AK8" s="9" t="n">
+        <v>1052</v>
+      </c>
+      <c r="AL8" s="12">
+        <f>AK8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AM8" s="9" t="n"/>
+      <c r="AN8" s="9" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="9" t="n">
         <v>1051</v>
-      </c>
-      <c r="AO8" s="12">
-        <f>AN8/$E$8</f>
-        <v/>
-      </c>
-      <c r="AP8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ8" s="9" t="n">
-        <v>1050</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
       <c r="AV8" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
-      <c r="BB8" s="9" t="n">
+      <c r="AY8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" s="9" t="n">
+        <v>1037</v>
+      </c>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BC8" s="9" t="n">
+      <c r="BF8" s="9" t="n">
         <v>1033</v>
-      </c>
-      <c r="BD8" s="12">
-        <f>BC8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BE8" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF8" s="9" t="n">
-        <v>1018</v>
       </c>
       <c r="BG8" s="12">
         <f>BF8/$E$8</f>
         <v/>
       </c>
-      <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="9" t="n"/>
-      <c r="BJ8" s="12" t="n"/>
-      <c r="BK8" s="9" t="n">
+      <c r="BH8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI8" s="9" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BJ8" s="12">
+        <f>BI8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BK8" s="9" t="n"/>
+      <c r="BL8" s="9" t="n"/>
+      <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BL8" s="9" t="n">
+      <c r="BO8" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="BM8" s="12">
-        <f>BL8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n"/>
-      <c r="BP8" s="12" t="n"/>
+      <c r="BP8" s="12">
+        <f>BO8/$E$8</f>
+        <v/>
+      </c>
       <c r="BQ8" s="9" t="n"/>
-      <c r="BR8" s="9" t="n">
+      <c r="BR8" s="9" t="n"/>
+      <c r="BS8" s="12" t="n"/>
+      <c r="BT8" s="9" t="n"/>
+      <c r="BU8" s="9" t="n">
         <v>1010</v>
       </c>
-      <c r="BS8" s="12">
-        <f>BR8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BT8" s="9" t="n"/>
-      <c r="BU8" s="9" t="n"/>
-      <c r="BV8" s="12" t="n"/>
+      <c r="BV8" s="12">
+        <f>BU8/$E$8</f>
+        <v/>
+      </c>
       <c r="BW8" s="9" t="n"/>
       <c r="BX8" s="9" t="n"/>
       <c r="BY8" s="12" t="n"/>
@@ -8278,6 +8573,9 @@
       <c r="CL8" s="9" t="n"/>
       <c r="CM8" s="9" t="n"/>
       <c r="CN8" s="12" t="n"/>
+      <c r="CO8" s="9" t="n"/>
+      <c r="CP8" s="9" t="n"/>
+      <c r="CQ8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -8401,19 +8699,19 @@
         <f>AH9/$E$9</f>
         <v/>
       </c>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="12" t="n"/>
-      <c r="AM9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="9" t="n">
+      <c r="AJ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9" t="n">
         <v>845</v>
       </c>
-      <c r="AO9" s="12">
-        <f>AN9/$E$9</f>
-        <v/>
-      </c>
+      <c r="AL9" s="12">
+        <f>AK9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AM9" s="9" t="n"/>
+      <c r="AN9" s="9" t="n"/>
+      <c r="AO9" s="12" t="n"/>
       <c r="AP9" s="9" t="n">
         <v>0</v>
       </c>
@@ -8425,7 +8723,7 @@
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="9" t="n">
         <v>845</v>
@@ -8435,28 +8733,28 @@
         <v/>
       </c>
       <c r="AV9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW9" s="9" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AX9" s="12">
         <f>AW9/$E$9</f>
         <v/>
       </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
-      <c r="BB9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" s="9" t="n">
+      <c r="AY9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BD9" s="12">
-        <f>BC9/$E$9</f>
-        <v/>
-      </c>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="9" t="n"/>
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
       <c r="BE9" s="9" t="n">
         <v>0</v>
       </c>
@@ -8467,33 +8765,40 @@
         <f>BF9/$E$9</f>
         <v/>
       </c>
-      <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n"/>
-      <c r="BJ9" s="12" t="n"/>
-      <c r="BK9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL9" s="9" t="n">
+      <c r="BH9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BM9" s="12">
-        <f>BL9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n"/>
-      <c r="BP9" s="12" t="n"/>
+      <c r="BJ9" s="12">
+        <f>BI9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BK9" s="9" t="n"/>
+      <c r="BL9" s="9" t="n"/>
+      <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" s="9" t="n">
+        <v>843</v>
+      </c>
+      <c r="BP9" s="12">
+        <f>BO9/$E$9</f>
+        <v/>
+      </c>
       <c r="BQ9" s="9" t="n"/>
-      <c r="BR9" s="9" t="n">
+      <c r="BR9" s="9" t="n"/>
+      <c r="BS9" s="12" t="n"/>
+      <c r="BT9" s="9" t="n"/>
+      <c r="BU9" s="9" t="n">
         <v>843</v>
       </c>
-      <c r="BS9" s="12">
-        <f>BR9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BT9" s="9" t="n"/>
-      <c r="BU9" s="9" t="n"/>
-      <c r="BV9" s="12" t="n"/>
+      <c r="BV9" s="12">
+        <f>BU9/$E$9</f>
+        <v/>
+      </c>
       <c r="BW9" s="9" t="n"/>
       <c r="BX9" s="9" t="n"/>
       <c r="BY9" s="12" t="n"/>
@@ -8512,6 +8817,9 @@
       <c r="CL9" s="9" t="n"/>
       <c r="CM9" s="9" t="n"/>
       <c r="CN9" s="12" t="n"/>
+      <c r="CO9" s="9" t="n"/>
+      <c r="CP9" s="9" t="n"/>
+      <c r="CQ9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -8546,7 +8854,7 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>1421</v>
@@ -8559,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="N10" s="12">
         <f>M10/$E$10</f>
@@ -8569,17 +8877,17 @@
         <v>1</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
@@ -8606,7 +8914,7 @@
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="9" t="n">
         <v>1418</v>
@@ -8616,118 +8924,125 @@
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/$E$10</f>
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="12" t="n"/>
-      <c r="AM10" s="9" t="n">
+      <c r="AJ10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK10" s="9" t="n">
+        <v>1413</v>
+      </c>
+      <c r="AL10" s="12">
+        <f>AK10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AM10" s="9" t="n"/>
+      <c r="AN10" s="9" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AN10" s="9" t="n">
+      <c r="AQ10" s="9" t="n">
         <v>1406</v>
-      </c>
-      <c r="AO10" s="12">
-        <f>AN10/$E$10</f>
-        <v/>
-      </c>
-      <c r="AP10" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ10" s="9" t="n">
-        <v>1403</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AT10" s="9" t="n">
-        <v>1391</v>
+        <v>1403</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
       <c r="AV10" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AW10" s="9" t="n">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
-      <c r="BB10" s="9" t="n">
+      <c r="AY10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" s="9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n"/>
+      <c r="BD10" s="12" t="n"/>
+      <c r="BE10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="BC10" s="9" t="n">
+      <c r="BF10" s="9" t="n">
         <v>1364</v>
-      </c>
-      <c r="BD10" s="12">
-        <f>BC10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BE10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF10" s="9" t="n">
-        <v>1348</v>
       </c>
       <c r="BG10" s="12">
         <f>BF10/$E$10</f>
         <v/>
       </c>
-      <c r="BH10" s="9" t="n"/>
-      <c r="BI10" s="9" t="n"/>
-      <c r="BJ10" s="12" t="n"/>
-      <c r="BK10" s="9" t="n">
+      <c r="BH10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BL10" s="9" t="n">
+      <c r="BI10" s="9" t="n">
+        <v>1348</v>
+      </c>
+      <c r="BJ10" s="12">
+        <f>BI10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BK10" s="9" t="n"/>
+      <c r="BL10" s="9" t="n"/>
+      <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO10" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="BM10" s="12">
-        <f>BL10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BN10" s="9" t="n"/>
-      <c r="BO10" s="9" t="n"/>
-      <c r="BP10" s="12" t="n"/>
+      <c r="BP10" s="12">
+        <f>BO10/$E$10</f>
+        <v/>
+      </c>
       <c r="BQ10" s="9" t="n"/>
-      <c r="BR10" s="9" t="n">
+      <c r="BR10" s="9" t="n"/>
+      <c r="BS10" s="12" t="n"/>
+      <c r="BT10" s="9" t="n"/>
+      <c r="BU10" s="9" t="n">
         <v>1334</v>
       </c>
-      <c r="BS10" s="12">
-        <f>BR10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BT10" s="9" t="n"/>
-      <c r="BU10" s="9" t="n"/>
-      <c r="BV10" s="12" t="n"/>
+      <c r="BV10" s="12">
+        <f>BU10/$E$10</f>
+        <v/>
+      </c>
       <c r="BW10" s="9" t="n"/>
       <c r="BX10" s="9" t="n"/>
       <c r="BY10" s="12" t="n"/>
@@ -8746,6 +9061,9 @@
       <c r="CL10" s="9" t="n"/>
       <c r="CM10" s="9" t="n"/>
       <c r="CN10" s="12" t="n"/>
+      <c r="CO10" s="9" t="n"/>
+      <c r="CP10" s="9" t="n"/>
+      <c r="CQ10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -8770,17 +9088,17 @@
         <v>2743</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="H11" s="11">
         <f>G11/$E$11</f>
         <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>1001</v>
@@ -8790,10 +9108,10 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="N11" s="12">
         <f>M11/$E$11</f>
@@ -8803,27 +9121,27 @@
         <v>3</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="Q11" s="12">
         <f>P11/$E$11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="T11" s="12">
         <f>S11/$E$11</f>
         <v/>
       </c>
       <c r="U11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="W11" s="12">
         <f>V11/$E$11</f>
@@ -8840,7 +9158,7 @@
         <v/>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="9" t="n">
         <v>992</v>
@@ -8850,10 +9168,10 @@
         <v/>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="AF11" s="12">
         <f>AE11/$E$11</f>
@@ -8869,99 +9187,106 @@
         <f>AH11/$E$11</f>
         <v/>
       </c>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="12" t="n"/>
-      <c r="AM11" s="9" t="n">
+      <c r="AJ11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="9" t="n">
+        <v>990</v>
+      </c>
+      <c r="AL11" s="12">
+        <f>AK11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AM11" s="9" t="n"/>
+      <c r="AN11" s="9" t="n"/>
+      <c r="AO11" s="12" t="n"/>
+      <c r="AP11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AN11" s="9" t="n">
+      <c r="AQ11" s="9" t="n">
         <v>990</v>
-      </c>
-      <c r="AO11" s="12">
-        <f>AN11/$E$11</f>
-        <v/>
-      </c>
-      <c r="AP11" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ11" s="9" t="n">
-        <v>989</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
         <v/>
       </c>
       <c r="AS11" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AT11" s="9" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="AU11" s="12">
         <f>AT11/$E$11</f>
         <v/>
       </c>
       <c r="AV11" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW11" s="9" t="n">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="AX11" s="12">
         <f>AW11/$E$11</f>
         <v/>
       </c>
-      <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n"/>
-      <c r="BA11" s="12" t="n"/>
-      <c r="BB11" s="9" t="n">
+      <c r="AY11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="BA11" s="12">
+        <f>AZ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="9" t="n"/>
+      <c r="BC11" s="9" t="n"/>
+      <c r="BD11" s="12" t="n"/>
+      <c r="BE11" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="BC11" s="9" t="n">
+      <c r="BF11" s="9" t="n">
         <v>963</v>
-      </c>
-      <c r="BD11" s="12">
-        <f>BC11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BE11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF11" s="9" t="n">
-        <v>949</v>
       </c>
       <c r="BG11" s="12">
         <f>BF11/$E$11</f>
         <v/>
       </c>
-      <c r="BH11" s="9" t="n"/>
-      <c r="BI11" s="9" t="n"/>
-      <c r="BJ11" s="12" t="n"/>
-      <c r="BK11" s="9" t="n">
+      <c r="BH11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI11" s="9" t="n">
+        <v>949</v>
+      </c>
+      <c r="BJ11" s="12">
+        <f>BI11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BK11" s="9" t="n"/>
+      <c r="BL11" s="9" t="n"/>
+      <c r="BM11" s="12" t="n"/>
+      <c r="BN11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BL11" s="9" t="n">
+      <c r="BO11" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="BM11" s="12">
-        <f>BL11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BN11" s="9" t="n"/>
-      <c r="BO11" s="9" t="n"/>
-      <c r="BP11" s="12" t="n"/>
+      <c r="BP11" s="12">
+        <f>BO11/$E$11</f>
+        <v/>
+      </c>
       <c r="BQ11" s="9" t="n"/>
-      <c r="BR11" s="9" t="n">
+      <c r="BR11" s="9" t="n"/>
+      <c r="BS11" s="12" t="n"/>
+      <c r="BT11" s="9" t="n"/>
+      <c r="BU11" s="9" t="n">
         <v>936</v>
       </c>
-      <c r="BS11" s="12">
-        <f>BR11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BT11" s="9" t="n"/>
-      <c r="BU11" s="9" t="n"/>
-      <c r="BV11" s="12" t="n"/>
+      <c r="BV11" s="12">
+        <f>BU11/$E$11</f>
+        <v/>
+      </c>
       <c r="BW11" s="9" t="n"/>
       <c r="BX11" s="9" t="n"/>
       <c r="BY11" s="12" t="n"/>
@@ -8980,6 +9305,9 @@
       <c r="CL11" s="9" t="n"/>
       <c r="CM11" s="9" t="n"/>
       <c r="CN11" s="12" t="n"/>
+      <c r="CO11" s="9" t="n"/>
+      <c r="CP11" s="9" t="n"/>
+      <c r="CQ11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -9004,17 +9332,17 @@
         <v>1733</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="H12" s="11">
         <f>G12/$E$12</f>
         <v/>
       </c>
       <c r="I12" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>741</v>
@@ -9024,10 +9352,10 @@
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="N12" s="12">
         <f>M12/$E$12</f>
@@ -9037,17 +9365,17 @@
         <v>1</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Q12" s="12">
         <f>P12/$E$12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="T12" s="12">
         <f>S12/$E$12</f>
@@ -9074,7 +9402,7 @@
         <v/>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="9" t="n">
         <v>737</v>
@@ -9084,118 +9412,125 @@
         <v/>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="AF12" s="12">
         <f>AE12/$E$12</f>
         <v/>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH12" s="9" t="n">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AI12" s="12">
         <f>AH12/$E$12</f>
         <v/>
       </c>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="12" t="n"/>
-      <c r="AM12" s="9" t="n">
+      <c r="AJ12" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK12" s="9" t="n">
+        <v>728</v>
+      </c>
+      <c r="AL12" s="12">
+        <f>AK12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AM12" s="9" t="n"/>
+      <c r="AN12" s="9" t="n"/>
+      <c r="AO12" s="12" t="n"/>
+      <c r="AP12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AQ12" s="9" t="n">
         <v>724</v>
-      </c>
-      <c r="AO12" s="12">
-        <f>AN12/$E$12</f>
-        <v/>
-      </c>
-      <c r="AP12" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ12" s="9" t="n">
-        <v>714</v>
       </c>
       <c r="AR12" s="12">
         <f>AQ12/$E$12</f>
         <v/>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AT12" s="9" t="n">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="AU12" s="12">
         <f>AT12/$E$12</f>
         <v/>
       </c>
       <c r="AV12" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AW12" s="9" t="n">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="AX12" s="12">
         <f>AW12/$E$12</f>
         <v/>
       </c>
-      <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n"/>
-      <c r="BA12" s="12" t="n"/>
-      <c r="BB12" s="9" t="n">
+      <c r="AY12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" s="9" t="n">
+        <v>676</v>
+      </c>
+      <c r="BA12" s="12">
+        <f>AZ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="12" t="n"/>
+      <c r="BE12" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="BC12" s="9" t="n">
+      <c r="BF12" s="9" t="n">
         <v>665</v>
-      </c>
-      <c r="BD12" s="12">
-        <f>BC12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BE12" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF12" s="9" t="n">
-        <v>637</v>
       </c>
       <c r="BG12" s="12">
         <f>BF12/$E$12</f>
         <v/>
       </c>
-      <c r="BH12" s="9" t="n"/>
-      <c r="BI12" s="9" t="n"/>
-      <c r="BJ12" s="12" t="n"/>
-      <c r="BK12" s="9" t="n">
+      <c r="BH12" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI12" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="BJ12" s="12">
+        <f>BI12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BK12" s="9" t="n"/>
+      <c r="BL12" s="9" t="n"/>
+      <c r="BM12" s="12" t="n"/>
+      <c r="BN12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BL12" s="9" t="n">
+      <c r="BO12" s="9" t="n">
         <v>616</v>
       </c>
-      <c r="BM12" s="12">
-        <f>BL12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BN12" s="9" t="n"/>
-      <c r="BO12" s="9" t="n"/>
-      <c r="BP12" s="12" t="n"/>
+      <c r="BP12" s="12">
+        <f>BO12/$E$12</f>
+        <v/>
+      </c>
       <c r="BQ12" s="9" t="n"/>
-      <c r="BR12" s="9" t="n">
+      <c r="BR12" s="9" t="n"/>
+      <c r="BS12" s="12" t="n"/>
+      <c r="BT12" s="9" t="n"/>
+      <c r="BU12" s="9" t="n">
         <v>610</v>
       </c>
-      <c r="BS12" s="12">
-        <f>BR12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BT12" s="9" t="n"/>
-      <c r="BU12" s="9" t="n"/>
-      <c r="BV12" s="12" t="n"/>
+      <c r="BV12" s="12">
+        <f>BU12/$E$12</f>
+        <v/>
+      </c>
       <c r="BW12" s="9" t="n"/>
       <c r="BX12" s="9" t="n"/>
       <c r="BY12" s="12" t="n"/>
@@ -9214,6 +9549,9 @@
       <c r="CL12" s="9" t="n"/>
       <c r="CM12" s="9" t="n"/>
       <c r="CN12" s="12" t="n"/>
+      <c r="CO12" s="9" t="n"/>
+      <c r="CP12" s="9" t="n"/>
+      <c r="CQ12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -9238,10 +9576,10 @@
         <v>1623</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H13" s="11">
         <f>G13/$E$13</f>
@@ -9268,7 +9606,7 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
         <v>1394</v>
@@ -9278,20 +9616,20 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="W13" s="12">
         <f>V13/$E$13</f>
@@ -9328,7 +9666,7 @@
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="9" t="n">
         <v>1391</v>
@@ -9337,99 +9675,106 @@
         <f>AH13/$E$13</f>
         <v/>
       </c>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="12" t="n"/>
-      <c r="AM13" s="9" t="n">
+      <c r="AJ13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN13" s="9" t="n">
+      <c r="AK13" s="9" t="n">
+        <v>1391</v>
+      </c>
+      <c r="AL13" s="12">
+        <f>AK13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AM13" s="9" t="n"/>
+      <c r="AN13" s="9" t="n"/>
+      <c r="AO13" s="12" t="n"/>
+      <c r="AP13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ13" s="9" t="n">
         <v>1389</v>
-      </c>
-      <c r="AO13" s="12">
-        <f>AN13/$E$13</f>
-        <v/>
-      </c>
-      <c r="AP13" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ13" s="9" t="n">
-        <v>1387</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
       <c r="AV13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
-      <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n"/>
-      <c r="BA13" s="12" t="n"/>
-      <c r="BB13" s="9" t="n">
+      <c r="AY13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ13" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="BA13" s="12">
+        <f>AZ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="9" t="n"/>
+      <c r="BC13" s="9" t="n"/>
+      <c r="BD13" s="12" t="n"/>
+      <c r="BE13" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="BC13" s="9" t="n">
+      <c r="BF13" s="9" t="n">
         <v>1372</v>
-      </c>
-      <c r="BD13" s="12">
-        <f>BC13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BE13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF13" s="9" t="n">
-        <v>1356</v>
       </c>
       <c r="BG13" s="12">
         <f>BF13/$E$13</f>
         <v/>
       </c>
-      <c r="BH13" s="9" t="n"/>
-      <c r="BI13" s="9" t="n"/>
-      <c r="BJ13" s="12" t="n"/>
-      <c r="BK13" s="9" t="n">
+      <c r="BH13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI13" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="BJ13" s="12">
+        <f>BI13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BK13" s="9" t="n"/>
+      <c r="BL13" s="9" t="n"/>
+      <c r="BM13" s="12" t="n"/>
+      <c r="BN13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BL13" s="9" t="n">
+      <c r="BO13" s="9" t="n">
         <v>1354</v>
       </c>
-      <c r="BM13" s="12">
-        <f>BL13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BN13" s="9" t="n"/>
-      <c r="BO13" s="9" t="n"/>
-      <c r="BP13" s="12" t="n"/>
+      <c r="BP13" s="12">
+        <f>BO13/$E$13</f>
+        <v/>
+      </c>
       <c r="BQ13" s="9" t="n"/>
-      <c r="BR13" s="9" t="n">
+      <c r="BR13" s="9" t="n"/>
+      <c r="BS13" s="12" t="n"/>
+      <c r="BT13" s="9" t="n"/>
+      <c r="BU13" s="9" t="n">
         <v>1351</v>
       </c>
-      <c r="BS13" s="12">
-        <f>BR13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BT13" s="9" t="n"/>
-      <c r="BU13" s="9" t="n"/>
-      <c r="BV13" s="12" t="n"/>
+      <c r="BV13" s="12">
+        <f>BU13/$E$13</f>
+        <v/>
+      </c>
       <c r="BW13" s="9" t="n"/>
       <c r="BX13" s="9" t="n"/>
       <c r="BY13" s="12" t="n"/>
@@ -9448,6 +9793,9 @@
       <c r="CL13" s="9" t="n"/>
       <c r="CM13" s="9" t="n"/>
       <c r="CN13" s="12" t="n"/>
+      <c r="CO13" s="9" t="n"/>
+      <c r="CP13" s="9" t="n"/>
+      <c r="CQ13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -9482,7 +9830,7 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>906</v>
@@ -9495,24 +9843,24 @@
         <v>1</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="N14" s="12">
         <f>M14/$E$14</f>
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>904</v>
@@ -9522,10 +9870,10 @@
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="W14" s="12">
         <f>V14/$E$14</f>
@@ -9562,7 +9910,7 @@
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="9" t="n">
         <v>902</v>
@@ -9571,21 +9919,21 @@
         <f>AH14/$E$14</f>
         <v/>
       </c>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="12" t="n"/>
-      <c r="AM14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="9" t="n">
-        <v>898</v>
-      </c>
-      <c r="AO14" s="12">
-        <f>AN14/$E$14</f>
-        <v/>
-      </c>
+      <c r="AJ14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK14" s="9" t="n">
+        <v>902</v>
+      </c>
+      <c r="AL14" s="12">
+        <f>AK14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AM14" s="9" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="12" t="n"/>
       <c r="AP14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="9" t="n">
         <v>898</v>
@@ -9595,75 +9943,82 @@
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
       <c r="AV14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
-      <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n"/>
-      <c r="BA14" s="12" t="n"/>
-      <c r="BB14" s="9" t="n">
+      <c r="AY14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="BA14" s="12">
+        <f>AZ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="9" t="n"/>
+      <c r="BC14" s="9" t="n"/>
+      <c r="BD14" s="12" t="n"/>
+      <c r="BE14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BC14" s="9" t="n">
+      <c r="BF14" s="9" t="n">
         <v>887</v>
-      </c>
-      <c r="BD14" s="12">
-        <f>BC14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BE14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF14" s="9" t="n">
-        <v>881</v>
       </c>
       <c r="BG14" s="12">
         <f>BF14/$E$14</f>
         <v/>
       </c>
-      <c r="BH14" s="9" t="n"/>
-      <c r="BI14" s="9" t="n"/>
-      <c r="BJ14" s="12" t="n"/>
-      <c r="BK14" s="9" t="n">
+      <c r="BH14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BL14" s="9" t="n">
+      <c r="BI14" s="9" t="n">
+        <v>881</v>
+      </c>
+      <c r="BJ14" s="12">
+        <f>BI14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BK14" s="9" t="n"/>
+      <c r="BL14" s="9" t="n"/>
+      <c r="BM14" s="12" t="n"/>
+      <c r="BN14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO14" s="9" t="n">
         <v>877</v>
       </c>
-      <c r="BM14" s="12">
-        <f>BL14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BN14" s="9" t="n"/>
-      <c r="BO14" s="9" t="n"/>
-      <c r="BP14" s="12" t="n"/>
+      <c r="BP14" s="12">
+        <f>BO14/$E$14</f>
+        <v/>
+      </c>
       <c r="BQ14" s="9" t="n"/>
-      <c r="BR14" s="9" t="n">
+      <c r="BR14" s="9" t="n"/>
+      <c r="BS14" s="12" t="n"/>
+      <c r="BT14" s="9" t="n"/>
+      <c r="BU14" s="9" t="n">
         <v>873</v>
       </c>
-      <c r="BS14" s="12">
-        <f>BR14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BT14" s="9" t="n"/>
-      <c r="BU14" s="9" t="n"/>
-      <c r="BV14" s="12" t="n"/>
+      <c r="BV14" s="12">
+        <f>BU14/$E$14</f>
+        <v/>
+      </c>
       <c r="BW14" s="9" t="n"/>
       <c r="BX14" s="9" t="n"/>
       <c r="BY14" s="12" t="n"/>
@@ -9682,6 +10037,9 @@
       <c r="CL14" s="9" t="n"/>
       <c r="CM14" s="9" t="n"/>
       <c r="CN14" s="12" t="n"/>
+      <c r="CO14" s="9" t="n"/>
+      <c r="CP14" s="9" t="n"/>
+      <c r="CQ14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -9792,6 +10150,9 @@
       <c r="CL15" s="9" t="n"/>
       <c r="CM15" s="9" t="n"/>
       <c r="CN15" s="12" t="n"/>
+      <c r="CO15" s="9" t="n"/>
+      <c r="CP15" s="9" t="n"/>
+      <c r="CQ15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -9826,7 +10187,7 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>720</v>
@@ -9836,27 +10197,27 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N16" s="12">
         <f>M16/$E$16</f>
         <v/>
       </c>
       <c r="O16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/$E$16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S16" s="9" t="n">
         <v>717</v>
@@ -9866,10 +10227,10 @@
         <v/>
       </c>
       <c r="U16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="W16" s="12">
         <f>V16/$E$16</f>
@@ -9886,7 +10247,7 @@
         <v/>
       </c>
       <c r="AA16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="9" t="n">
         <v>715</v>
@@ -9896,118 +10257,125 @@
         <v/>
       </c>
       <c r="AD16" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AF16" s="12">
         <f>AE16/$E$16</f>
         <v/>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH16" s="9" t="n">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="AI16" s="12">
         <f>AH16/$E$16</f>
         <v/>
       </c>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="12" t="n"/>
-      <c r="AM16" s="9" t="n">
+      <c r="AJ16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>711</v>
+      </c>
+      <c r="AL16" s="12">
+        <f>AK16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AM16" s="9" t="n"/>
+      <c r="AN16" s="9" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AN16" s="9" t="n">
+      <c r="AQ16" s="9" t="n">
         <v>710</v>
-      </c>
-      <c r="AO16" s="12">
-        <f>AN16/$E$16</f>
-        <v/>
-      </c>
-      <c r="AP16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ16" s="9" t="n">
-        <v>707</v>
       </c>
       <c r="AR16" s="12">
         <f>AQ16/$E$16</f>
         <v/>
       </c>
       <c r="AS16" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AT16" s="9" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="AU16" s="12">
         <f>AT16/$E$16</f>
         <v/>
       </c>
       <c r="AV16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW16" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AX16" s="12">
         <f>AW16/$E$16</f>
         <v/>
       </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
-      <c r="BB16" s="9" t="n">
+      <c r="AY16" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ16" s="9" t="n">
+        <v>698</v>
+      </c>
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="12" t="n"/>
+      <c r="BE16" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BC16" s="9" t="n">
+      <c r="BF16" s="9" t="n">
         <v>692</v>
-      </c>
-      <c r="BD16" s="12">
-        <f>BC16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BE16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF16" s="9" t="n">
-        <v>685</v>
       </c>
       <c r="BG16" s="12">
         <f>BF16/$E$16</f>
         <v/>
       </c>
-      <c r="BH16" s="9" t="n"/>
-      <c r="BI16" s="9" t="n"/>
-      <c r="BJ16" s="12" t="n"/>
-      <c r="BK16" s="9" t="n">
+      <c r="BH16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI16" s="9" t="n">
+        <v>685</v>
+      </c>
+      <c r="BJ16" s="12">
+        <f>BI16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BK16" s="9" t="n"/>
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="BL16" s="9" t="n">
+      <c r="BO16" s="9" t="n">
         <v>682</v>
       </c>
-      <c r="BM16" s="12">
-        <f>BL16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n"/>
-      <c r="BP16" s="12" t="n"/>
+      <c r="BP16" s="12">
+        <f>BO16/$E$16</f>
+        <v/>
+      </c>
       <c r="BQ16" s="9" t="n"/>
-      <c r="BR16" s="9" t="n">
+      <c r="BR16" s="9" t="n"/>
+      <c r="BS16" s="12" t="n"/>
+      <c r="BT16" s="9" t="n"/>
+      <c r="BU16" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="BS16" s="12">
-        <f>BR16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BT16" s="9" t="n"/>
-      <c r="BU16" s="9" t="n"/>
-      <c r="BV16" s="12" t="n"/>
+      <c r="BV16" s="12">
+        <f>BU16/$E$16</f>
+        <v/>
+      </c>
       <c r="BW16" s="9" t="n"/>
       <c r="BX16" s="9" t="n"/>
       <c r="BY16" s="12" t="n"/>
@@ -10026,6 +10394,9 @@
       <c r="CL16" s="9" t="n"/>
       <c r="CM16" s="9" t="n"/>
       <c r="CN16" s="12" t="n"/>
+      <c r="CO16" s="9" t="n"/>
+      <c r="CP16" s="9" t="n"/>
+      <c r="CQ16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -10060,7 +10431,7 @@
         <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>390</v>
@@ -10073,24 +10444,24 @@
         <v>1</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N17" s="12">
         <f>M17/$E$17</f>
         <v/>
       </c>
       <c r="O17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/$E$17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
         <v>388</v>
@@ -10100,20 +10471,20 @@
         <v/>
       </c>
       <c r="U17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="W17" s="12">
         <f>V17/$E$17</f>
         <v/>
       </c>
       <c r="X17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z17" s="12">
         <f>Y17/$E$17</f>
@@ -10130,7 +10501,7 @@
         <v/>
       </c>
       <c r="AD17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="9" t="n">
         <v>385</v>
@@ -10140,108 +10511,115 @@
         <v/>
       </c>
       <c r="AG17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH17" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AI17" s="12">
         <f>AH17/$E$17</f>
         <v/>
       </c>
-      <c r="AJ17" s="9" t="n"/>
-      <c r="AK17" s="9" t="n"/>
-      <c r="AL17" s="12" t="n"/>
-      <c r="AM17" s="9" t="n">
+      <c r="AJ17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AN17" s="9" t="n">
+      <c r="AK17" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="AL17" s="12">
+        <f>AK17/$E$17</f>
+        <v/>
+      </c>
+      <c r="AM17" s="9" t="n"/>
+      <c r="AN17" s="9" t="n"/>
+      <c r="AO17" s="12" t="n"/>
+      <c r="AP17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ17" s="9" t="n">
         <v>382</v>
-      </c>
-      <c r="AO17" s="12">
-        <f>AN17/$E$17</f>
-        <v/>
-      </c>
-      <c r="AP17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ17" s="9" t="n">
-        <v>380</v>
       </c>
       <c r="AR17" s="12">
         <f>AQ17/$E$17</f>
         <v/>
       </c>
       <c r="AS17" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AT17" s="9" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AU17" s="12">
         <f>AT17/$E$17</f>
         <v/>
       </c>
       <c r="AV17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW17" s="9" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AX17" s="12">
         <f>AW17/$E$17</f>
         <v/>
       </c>
-      <c r="AY17" s="9" t="n"/>
-      <c r="AZ17" s="9" t="n"/>
-      <c r="BA17" s="12" t="n"/>
-      <c r="BB17" s="9" t="n">
+      <c r="AY17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="9" t="n">
+        <v>370</v>
+      </c>
+      <c r="BA17" s="12">
+        <f>AZ17/$E$17</f>
+        <v/>
+      </c>
+      <c r="BB17" s="9" t="n"/>
+      <c r="BC17" s="9" t="n"/>
+      <c r="BD17" s="12" t="n"/>
+      <c r="BE17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="BC17" s="9" t="n">
+      <c r="BF17" s="9" t="n">
         <v>370</v>
-      </c>
-      <c r="BD17" s="12">
-        <f>BC17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BE17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" s="9" t="n">
-        <v>365</v>
       </c>
       <c r="BG17" s="12">
         <f>BF17/$E$17</f>
         <v/>
       </c>
-      <c r="BH17" s="9" t="n"/>
-      <c r="BI17" s="9" t="n"/>
-      <c r="BJ17" s="12" t="n"/>
-      <c r="BK17" s="9" t="n">
+      <c r="BH17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="BJ17" s="12">
+        <f>BI17/$E$17</f>
+        <v/>
+      </c>
+      <c r="BK17" s="9" t="n"/>
+      <c r="BL17" s="9" t="n"/>
+      <c r="BM17" s="12" t="n"/>
+      <c r="BN17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="BL17" s="9" t="n">
+      <c r="BO17" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="BM17" s="12">
-        <f>BL17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BN17" s="9" t="n"/>
-      <c r="BO17" s="9" t="n"/>
-      <c r="BP17" s="12" t="n"/>
+      <c r="BP17" s="12">
+        <f>BO17/$E$17</f>
+        <v/>
+      </c>
       <c r="BQ17" s="9" t="n"/>
-      <c r="BR17" s="9" t="n">
+      <c r="BR17" s="9" t="n"/>
+      <c r="BS17" s="12" t="n"/>
+      <c r="BT17" s="9" t="n"/>
+      <c r="BU17" s="9" t="n">
         <v>358</v>
       </c>
-      <c r="BS17" s="12">
-        <f>BR17/$E$17</f>
-        <v/>
-      </c>
-      <c r="BT17" s="9" t="n"/>
-      <c r="BU17" s="9" t="n"/>
-      <c r="BV17" s="12" t="n"/>
+      <c r="BV17" s="12">
+        <f>BU17/$E$17</f>
+        <v/>
+      </c>
       <c r="BW17" s="9" t="n"/>
       <c r="BX17" s="9" t="n"/>
       <c r="BY17" s="12" t="n"/>
@@ -10260,6 +10638,9 @@
       <c r="CL17" s="9" t="n"/>
       <c r="CM17" s="9" t="n"/>
       <c r="CN17" s="12" t="n"/>
+      <c r="CO17" s="9" t="n"/>
+      <c r="CP17" s="9" t="n"/>
+      <c r="CQ17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -10284,17 +10665,17 @@
         <v>1274</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H18" s="11">
         <f>G18/$E$18</f>
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>296</v>
@@ -10304,20 +10685,20 @@
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="N18" s="12">
         <f>M18/$E$18</f>
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
@@ -10354,7 +10735,7 @@
         <v/>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="9" t="n">
         <v>292</v>
@@ -10364,118 +10745,125 @@
         <v/>
       </c>
       <c r="AD18" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE18" s="9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AF18" s="12">
         <f>AE18/$E$18</f>
         <v/>
       </c>
       <c r="AG18" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH18" s="9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AI18" s="12">
         <f>AH18/$E$18</f>
         <v/>
       </c>
-      <c r="AJ18" s="9" t="n"/>
-      <c r="AK18" s="9" t="n"/>
-      <c r="AL18" s="12" t="n"/>
-      <c r="AM18" s="9" t="n">
+      <c r="AJ18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="AL18" s="12">
+        <f>AK18/$E$18</f>
+        <v/>
+      </c>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="9" t="n"/>
+      <c r="AO18" s="12" t="n"/>
+      <c r="AP18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AN18" s="9" t="n">
+      <c r="AQ18" s="9" t="n">
         <v>284</v>
-      </c>
-      <c r="AO18" s="12">
-        <f>AN18/$E$18</f>
-        <v/>
-      </c>
-      <c r="AP18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ18" s="9" t="n">
-        <v>281</v>
       </c>
       <c r="AR18" s="12">
         <f>AQ18/$E$18</f>
         <v/>
       </c>
       <c r="AS18" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT18" s="9" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AU18" s="12">
         <f>AT18/$E$18</f>
         <v/>
       </c>
       <c r="AV18" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW18" s="9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AX18" s="12">
         <f>AW18/$E$18</f>
         <v/>
       </c>
-      <c r="AY18" s="9" t="n"/>
-      <c r="AZ18" s="9" t="n"/>
-      <c r="BA18" s="12" t="n"/>
-      <c r="BB18" s="9" t="n">
+      <c r="AY18" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ18" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="BA18" s="12">
+        <f>AZ18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BB18" s="9" t="n"/>
+      <c r="BC18" s="9" t="n"/>
+      <c r="BD18" s="12" t="n"/>
+      <c r="BE18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BC18" s="9" t="n">
+      <c r="BF18" s="9" t="n">
         <v>266</v>
-      </c>
-      <c r="BD18" s="12">
-        <f>BC18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BE18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" s="9" t="n">
-        <v>251</v>
       </c>
       <c r="BG18" s="12">
         <f>BF18/$E$18</f>
         <v/>
       </c>
-      <c r="BH18" s="9" t="n"/>
-      <c r="BI18" s="9" t="n"/>
-      <c r="BJ18" s="12" t="n"/>
-      <c r="BK18" s="9" t="n">
+      <c r="BH18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="BJ18" s="12">
+        <f>BI18/$E$18</f>
+        <v/>
+      </c>
+      <c r="BK18" s="9" t="n"/>
+      <c r="BL18" s="9" t="n"/>
+      <c r="BM18" s="12" t="n"/>
+      <c r="BN18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BL18" s="9" t="n">
+      <c r="BO18" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="BM18" s="12">
-        <f>BL18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BN18" s="9" t="n"/>
-      <c r="BO18" s="9" t="n"/>
-      <c r="BP18" s="12" t="n"/>
+      <c r="BP18" s="12">
+        <f>BO18/$E$18</f>
+        <v/>
+      </c>
       <c r="BQ18" s="9" t="n"/>
-      <c r="BR18" s="9" t="n">
+      <c r="BR18" s="9" t="n"/>
+      <c r="BS18" s="12" t="n"/>
+      <c r="BT18" s="9" t="n"/>
+      <c r="BU18" s="9" t="n">
         <v>249</v>
       </c>
-      <c r="BS18" s="12">
-        <f>BR18/$E$18</f>
-        <v/>
-      </c>
-      <c r="BT18" s="9" t="n"/>
-      <c r="BU18" s="9" t="n"/>
-      <c r="BV18" s="12" t="n"/>
+      <c r="BV18" s="12">
+        <f>BU18/$E$18</f>
+        <v/>
+      </c>
       <c r="BW18" s="9" t="n"/>
       <c r="BX18" s="9" t="n"/>
       <c r="BY18" s="12" t="n"/>
@@ -10494,9 +10882,12 @@
       <c r="CL18" s="9" t="n"/>
       <c r="CM18" s="9" t="n"/>
       <c r="CN18" s="12" t="n"/>
+      <c r="CO18" s="9" t="n"/>
+      <c r="CP18" s="9" t="n"/>
+      <c r="CQ18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -10515,6 +10906,7 @@
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="CO3:CQ3"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="BE3:BG3"/>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -597,7 +597,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 22/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 23/08/2026</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 22/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 23/08/2026</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every day the tracker has run, newest first. Generated 22/08/2026</t>
+          <t>Every day the tracker has run, newest first. Generated 23/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Teduh_Daily_Tracker.xlsx
+++ b/docs/downloads/Teduh_Daily_Tracker.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -585,6 +585,9 @@
     <col width="9" customWidth="1" min="93" max="93"/>
     <col width="9" customWidth="1" min="94" max="94"/>
     <col width="9" customWidth="1" min="95" max="95"/>
+    <col width="9" customWidth="1" min="96" max="96"/>
+    <col width="9" customWidth="1" min="97" max="97"/>
+    <col width="9" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -603,93 +606,96 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46257</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CL3" s="4" t="n">
+      <c r="CO3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CO3" s="4" t="n">
+      <c r="CR3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -1167,6 +1173,21 @@
         </is>
       </c>
       <c r="CQ4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CR4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CS4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CT4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1195,7 +1216,7 @@
         <v>146</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>42</v>
@@ -1205,10 +1226,10 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
@@ -1285,7 +1306,7 @@
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="9" t="n">
         <v>43</v>
@@ -1295,17 +1316,17 @@
         <v/>
       </c>
       <c r="AJ5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
       <c r="AM5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="9" t="n">
         <v>42</v>
@@ -1318,49 +1339,56 @@
         <v>1</v>
       </c>
       <c r="AQ5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AR5" s="12">
         <f>AQ5/$E$5</f>
         <v/>
       </c>
       <c r="AS5" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AT5" s="9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU5" s="12">
         <f>AT5/$E$5</f>
         <v/>
       </c>
-      <c r="AV5" s="9" t="n"/>
-      <c r="AW5" s="9" t="n"/>
-      <c r="AX5" s="12" t="n"/>
-      <c r="AY5" s="9" t="n">
+      <c r="AV5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW5" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX5" s="12">
+        <f>AW5/$E$5</f>
+        <v/>
+      </c>
+      <c r="AY5" s="9" t="n"/>
+      <c r="AZ5" s="9" t="n"/>
+      <c r="BA5" s="12" t="n"/>
+      <c r="BB5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AZ5" s="9" t="n">
+      <c r="BC5" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="BA5" s="12">
-        <f>AZ5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BB5" s="9" t="n"/>
-      <c r="BC5" s="9" t="n"/>
-      <c r="BD5" s="12" t="n"/>
+      <c r="BD5" s="12">
+        <f>BC5/$E$5</f>
+        <v/>
+      </c>
       <c r="BE5" s="9" t="n"/>
-      <c r="BF5" s="9" t="n">
+      <c r="BF5" s="9" t="n"/>
+      <c r="BG5" s="12" t="n"/>
+      <c r="BH5" s="9" t="n"/>
+      <c r="BI5" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="BG5" s="12">
-        <f>BF5/$E$5</f>
-        <v/>
-      </c>
-      <c r="BH5" s="9" t="n"/>
-      <c r="BI5" s="9" t="n"/>
-      <c r="BJ5" s="12" t="n"/>
+      <c r="BJ5" s="12">
+        <f>BI5/$E$5</f>
+        <v/>
+      </c>
       <c r="BK5" s="9" t="n"/>
       <c r="BL5" s="9" t="n"/>
       <c r="BM5" s="12" t="n"/>
@@ -1394,6 +1422,9 @@
       <c r="CO5" s="9" t="n"/>
       <c r="CP5" s="9" t="n"/>
       <c r="CQ5" s="12" t="n"/>
+      <c r="CR5" s="9" t="n"/>
+      <c r="CS5" s="9" t="n"/>
+      <c r="CT5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1448,7 +1479,7 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>35</v>
@@ -1458,17 +1489,17 @@
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>34</v>
@@ -1478,10 +1509,10 @@
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
@@ -1557,33 +1588,40 @@
         <f>AT6/$E$6</f>
         <v/>
       </c>
-      <c r="AV6" s="9" t="n"/>
-      <c r="AW6" s="9" t="n"/>
-      <c r="AX6" s="12" t="n"/>
-      <c r="AY6" s="9" t="n">
+      <c r="AV6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AX6" s="12">
+        <f>AW6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="9" t="n"/>
+      <c r="AZ6" s="9" t="n"/>
+      <c r="BA6" s="12" t="n"/>
+      <c r="BB6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AZ6" s="9" t="n">
+      <c r="BC6" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="BA6" s="12">
-        <f>AZ6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BB6" s="9" t="n"/>
-      <c r="BC6" s="9" t="n"/>
-      <c r="BD6" s="12" t="n"/>
+      <c r="BD6" s="12">
+        <f>BC6/$E$6</f>
+        <v/>
+      </c>
       <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n">
+      <c r="BF6" s="9" t="n"/>
+      <c r="BG6" s="12" t="n"/>
+      <c r="BH6" s="9" t="n"/>
+      <c r="BI6" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="BG6" s="12">
-        <f>BF6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n"/>
-      <c r="BJ6" s="12" t="n"/>
+      <c r="BJ6" s="12">
+        <f>BI6/$E$6</f>
+        <v/>
+      </c>
       <c r="BK6" s="9" t="n"/>
       <c r="BL6" s="9" t="n"/>
       <c r="BM6" s="12" t="n"/>
@@ -1617,6 +1655,9 @@
       <c r="CO6" s="9" t="n"/>
       <c r="CP6" s="9" t="n"/>
       <c r="CQ6" s="12" t="n"/>
+      <c r="CR6" s="9" t="n"/>
+      <c r="CS6" s="9" t="n"/>
+      <c r="CT6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1671,7 +1712,7 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>48</v>
@@ -1684,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T7" s="12">
         <f>S7/$E$7</f>
@@ -1694,17 +1735,17 @@
         <v>1</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W7" s="12">
         <f>V7/$E$7</f>
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Z7" s="12">
         <f>Y7/$E$7</f>
@@ -1741,7 +1782,7 @@
         <v/>
       </c>
       <c r="AJ7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="9" t="n">
         <v>45</v>
@@ -1751,62 +1792,69 @@
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
-      <c r="AV7" s="9" t="n"/>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="12" t="n"/>
-      <c r="AY7" s="9" t="n">
+      <c r="AV7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AX7" s="12">
+        <f>AW7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="9" t="n"/>
+      <c r="AZ7" s="9" t="n"/>
+      <c r="BA7" s="12" t="n"/>
+      <c r="BB7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AZ7" s="9" t="n">
+      <c r="BC7" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="BA7" s="12">
-        <f>AZ7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="12" t="n"/>
+      <c r="BD7" s="12">
+        <f>BC7/$E$7</f>
+        <v/>
+      </c>
       <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n">
+      <c r="BF7" s="9" t="n"/>
+      <c r="BG7" s="12" t="n"/>
+      <c r="BH7" s="9" t="n"/>
+      <c r="BI7" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="BG7" s="12">
-        <f>BF7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BH7" s="9" t="n"/>
-      <c r="BI7" s="9" t="n"/>
-      <c r="BJ7" s="12" t="n"/>
+      <c r="BJ7" s="12">
+        <f>BI7/$E$7</f>
+        <v/>
+      </c>
       <c r="BK7" s="9" t="n"/>
       <c r="BL7" s="9" t="n"/>
       <c r="BM7" s="12" t="n"/>
@@ -1840,6 +1888,9 @@
       <c r="CO7" s="9" t="n"/>
       <c r="CP7" s="9" t="n"/>
       <c r="CQ7" s="12" t="n"/>
+      <c r="CR7" s="9" t="n"/>
+      <c r="CS7" s="9" t="n"/>
+      <c r="CT7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -2003,33 +2054,40 @@
         <f>AT8/$E$8</f>
         <v/>
       </c>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="12" t="n"/>
-      <c r="AY8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="9" t="n">
+      <c r="AV8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="BA8" s="12">
-        <f>AZ8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BB8" s="9" t="n"/>
-      <c r="BC8" s="9" t="n"/>
-      <c r="BD8" s="12" t="n"/>
+      <c r="AX8" s="12">
+        <f>AW8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="9" t="n"/>
+      <c r="AZ8" s="9" t="n"/>
+      <c r="BA8" s="12" t="n"/>
+      <c r="BB8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="BD8" s="12">
+        <f>BC8/$E$8</f>
+        <v/>
+      </c>
       <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n">
+      <c r="BF8" s="9" t="n"/>
+      <c r="BG8" s="12" t="n"/>
+      <c r="BH8" s="9" t="n"/>
+      <c r="BI8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="BG8" s="12">
-        <f>BF8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="9" t="n"/>
-      <c r="BJ8" s="12" t="n"/>
+      <c r="BJ8" s="12">
+        <f>BI8/$E$8</f>
+        <v/>
+      </c>
       <c r="BK8" s="9" t="n"/>
       <c r="BL8" s="9" t="n"/>
       <c r="BM8" s="12" t="n"/>
@@ -2063,6 +2121,9 @@
       <c r="CO8" s="9" t="n"/>
       <c r="CP8" s="9" t="n"/>
       <c r="CQ8" s="12" t="n"/>
+      <c r="CR8" s="9" t="n"/>
+      <c r="CS8" s="9" t="n"/>
+      <c r="CT8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2217,7 +2278,7 @@
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="9" t="n">
         <v>1</v>
@@ -2226,33 +2287,40 @@
         <f>AT9/$E$9</f>
         <v/>
       </c>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="12" t="n"/>
-      <c r="AY9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" s="12">
-        <f>AZ9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="12" t="n"/>
+      <c r="AV9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="12">
+        <f>AW9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="9" t="n"/>
+      <c r="AZ9" s="9" t="n"/>
+      <c r="BA9" s="12" t="n"/>
+      <c r="BB9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="12">
+        <f>BC9/$E$9</f>
+        <v/>
+      </c>
       <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" s="12">
-        <f>BF9/$E$9</f>
-        <v/>
-      </c>
+      <c r="BF9" s="9" t="n"/>
+      <c r="BG9" s="12" t="n"/>
       <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n"/>
-      <c r="BJ9" s="12" t="n"/>
+      <c r="BI9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="12">
+        <f>BI9/$E$9</f>
+        <v/>
+      </c>
       <c r="BK9" s="9" t="n"/>
       <c r="BL9" s="9" t="n"/>
       <c r="BM9" s="12" t="n"/>
@@ -2286,6 +2354,9 @@
       <c r="CO9" s="9" t="n"/>
       <c r="CP9" s="9" t="n"/>
       <c r="CQ9" s="12" t="n"/>
+      <c r="CR9" s="9" t="n"/>
+      <c r="CS9" s="9" t="n"/>
+      <c r="CT9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2310,7 +2381,7 @@
         <v>433</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>338</v>
@@ -2320,17 +2391,17 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>335</v>
@@ -2343,54 +2414,54 @@
         <v>8</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="W10" s="12">
         <f>V10/$E$10</f>
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
         <v/>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AC10" s="12">
         <f>AB10/$E$10</f>
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="9" t="n">
         <v>311</v>
@@ -2400,69 +2471,76 @@
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="AQ10" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AR10" s="12">
         <f>AQ10/$E$10</f>
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="AT10" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
-      <c r="AV10" s="9" t="n"/>
-      <c r="AW10" s="9" t="n"/>
-      <c r="AX10" s="12" t="n"/>
+      <c r="AV10" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="AW10" s="9" t="n">
+        <v>214</v>
+      </c>
+      <c r="AX10" s="12">
+        <f>AW10/$E$10</f>
+        <v/>
+      </c>
       <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n">
+      <c r="AZ10" s="9" t="n"/>
+      <c r="BA10" s="12" t="n"/>
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="BA10" s="12">
-        <f>AZ10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BB10" s="9" t="n"/>
-      <c r="BC10" s="9" t="n"/>
-      <c r="BD10" s="12" t="n"/>
+      <c r="BD10" s="12">
+        <f>BC10/$E$10</f>
+        <v/>
+      </c>
       <c r="BE10" s="9" t="n"/>
       <c r="BF10" s="9" t="n"/>
       <c r="BG10" s="12" t="n"/>
@@ -2502,9 +2580,12 @@
       <c r="CO10" s="9" t="n"/>
       <c r="CP10" s="9" t="n"/>
       <c r="CQ10" s="12" t="n"/>
+      <c r="CR10" s="9" t="n"/>
+      <c r="CS10" s="9" t="n"/>
+      <c r="CT10" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -2514,6 +2595,7 @@
     <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="CF3:CH3"/>
+    <mergeCell ref="CR3:CT3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="BW3:BY3"/>
@@ -2546,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ18"/>
+  <dimension ref="A1:CT18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2644,6 +2726,9 @@
     <col width="9" customWidth="1" min="93" max="93"/>
     <col width="9" customWidth="1" min="94" max="94"/>
     <col width="9" customWidth="1" min="95" max="95"/>
+    <col width="9" customWidth="1" min="96" max="96"/>
+    <col width="9" customWidth="1" min="97" max="97"/>
+    <col width="9" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2662,93 +2747,96 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46257</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>46220</v>
       </c>
-      <c r="BB3" s="4" t="n">
+      <c r="BE3" s="4" t="n">
         <v>46219</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BH3" s="4" t="n">
         <v>46213</v>
       </c>
-      <c r="BH3" s="4" t="n">
+      <c r="BK3" s="4" t="n">
         <v>46206</v>
       </c>
-      <c r="BK3" s="4" t="n">
+      <c r="BN3" s="4" t="n">
         <v>46205</v>
       </c>
-      <c r="BN3" s="4" t="n">
+      <c r="BQ3" s="4" t="n">
         <v>46199</v>
       </c>
-      <c r="BQ3" s="4" t="n">
+      <c r="BT3" s="4" t="n">
         <v>46198</v>
       </c>
-      <c r="BT3" s="4" t="n">
+      <c r="BW3" s="4" t="n">
         <v>46192</v>
       </c>
-      <c r="BW3" s="4" t="n">
+      <c r="BZ3" s="4" t="n">
         <v>46184</v>
       </c>
-      <c r="BZ3" s="4" t="n">
+      <c r="CC3" s="4" t="n">
         <v>46170</v>
       </c>
-      <c r="CC3" s="4" t="n">
+      <c r="CF3" s="4" t="n">
         <v>46163</v>
       </c>
-      <c r="CF3" s="4" t="n">
+      <c r="CI3" s="4" t="n">
         <v>46156</v>
       </c>
-      <c r="CI3" s="4" t="n">
+      <c r="CL3" s="4" t="n">
         <v>46149</v>
       </c>
-      <c r="CL3" s="4" t="n">
+      <c r="CO3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="CO3" s="4" t="n">
+      <c r="CR3" s="4" t="n">
         <v>46135</v>
       </c>
     </row>
@@ -3226,6 +3314,21 @@
         </is>
       </c>
       <c r="CQ4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="CR4" s="5" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="CS4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="CT4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -3254,7 +3357,7 @@
         <v>1310</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>184</v>
@@ -3264,17 +3367,17 @@
         <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K5" s="12">
         <f>J5/$E$5</f>
         <v/>
       </c>
       <c r="L5" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>183</v>
@@ -3284,27 +3387,27 @@
         <v/>
       </c>
       <c r="O5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q5" s="12">
         <f>P5/$E$5</f>
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" s="9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="T5" s="12">
         <f>S5/$E$5</f>
         <v/>
       </c>
       <c r="U5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>178</v>
@@ -3314,10 +3417,10 @@
         <v/>
       </c>
       <c r="X5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Z5" s="12">
         <f>Y5/$E$5</f>
@@ -3344,7 +3447,7 @@
         <v/>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="9" t="n">
         <v>177</v>
@@ -3353,17 +3456,24 @@
         <f>AH5/$E$5</f>
         <v/>
       </c>
-      <c r="AJ5" s="9" t="n"/>
+      <c r="AJ5" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="AK5" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AL5" s="12">
         <f>AK5/$E$5</f>
         <v/>
       </c>
       <c r="AM5" s="9" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="12" t="n"/>
+      <c r="AN5" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="AO5" s="12">
+        <f>AN5/$E$5</f>
+        <v/>
+      </c>
       <c r="AP5" s="9" t="n"/>
       <c r="AQ5" s="9" t="n"/>
       <c r="AR5" s="12" t="n"/>
@@ -3418,6 +3528,9 @@
       <c r="CO5" s="9" t="n"/>
       <c r="CP5" s="9" t="n"/>
       <c r="CQ5" s="12" t="n"/>
+      <c r="CR5" s="9" t="n"/>
+      <c r="CS5" s="9" t="n"/>
+      <c r="CT5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -3442,7 +3555,7 @@
         <v>1544</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>347</v>
@@ -3452,17 +3565,17 @@
         <v/>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K6" s="12">
         <f>J6/$E$6</f>
         <v/>
       </c>
       <c r="L6" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>344</v>
@@ -3472,40 +3585,40 @@
         <v/>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q6" s="12">
         <f>P6/$E$6</f>
         <v/>
       </c>
       <c r="R6" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="T6" s="12">
         <f>S6/$E$6</f>
         <v/>
       </c>
       <c r="U6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="W6" s="12">
         <f>V6/$E$6</f>
         <v/>
       </c>
       <c r="X6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Z6" s="12">
         <f>Y6/$E$6</f>
@@ -3522,7 +3635,7 @@
         <v/>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="9" t="n">
         <v>335</v>
@@ -3532,183 +3645,193 @@
         <v/>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6/$E$6</f>
         <v/>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AL6" s="12">
         <f>AK6/$E$6</f>
         <v/>
       </c>
       <c r="AM6" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AN6" s="9" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AO6" s="12">
         <f>AN6/$E$6</f>
         <v/>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AQ6" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AR6" s="12">
         <f>AQ6/$E$6</f>
         <v/>
       </c>
       <c r="AS6" s="9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AT6" s="9" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AU6" s="12">
         <f>AT6/$E$6</f>
         <v/>
       </c>
       <c r="AV6" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AW6" s="9" t="n">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AX6" s="12">
         <f>AW6/$E$6</f>
         <v/>
       </c>
-      <c r="AY6" s="9" t="n"/>
-      <c r="AZ6" s="9" t="n"/>
-      <c r="BA6" s="12" t="n"/>
-      <c r="BB6" s="9" t="n">
+      <c r="AY6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ6" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="BA6" s="12">
+        <f>AZ6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="9" t="n"/>
+      <c r="BC6" s="9" t="n"/>
+      <c r="BD6" s="12" t="n"/>
+      <c r="BE6" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="BC6" s="9" t="n">
+      <c r="BF6" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="BD6" s="12">
-        <f>BC6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BE6" s="9" t="n"/>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="12" t="n"/>
+      <c r="BG6" s="12">
+        <f>BF6/$E$6</f>
+        <v/>
+      </c>
       <c r="BH6" s="9" t="n"/>
       <c r="BI6" s="9" t="n"/>
       <c r="BJ6" s="12" t="n"/>
-      <c r="BK6" s="9" t="n">
+      <c r="BK6" s="9" t="n"/>
+      <c r="BL6" s="9" t="n"/>
+      <c r="BM6" s="12" t="n"/>
+      <c r="BN6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="BL6" s="9" t="n">
+      <c r="BO6" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="BM6" s="12">
-        <f>BL6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n"/>
-      <c r="BP6" s="12" t="n"/>
-      <c r="BQ6" s="9" t="n">
+      <c r="BP6" s="12">
+        <f>BO6/$E$6</f>
+        <v/>
+      </c>
+      <c r="BQ6" s="9" t="n"/>
+      <c r="BR6" s="9" t="n"/>
+      <c r="BS6" s="12" t="n"/>
+      <c r="BT6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BR6" s="9" t="n">
+      <c r="BU6" s="9" t="n">
         <v>241</v>
-      </c>
-      <c r="BS6" s="12">
-        <f>BR6/$E$6</f>
-        <v/>
-      </c>
-      <c r="BT6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU6" s="9" t="n">
-        <v>231</v>
       </c>
       <c r="BV6" s="12">
         <f>BU6/$E$6</f>
         <v/>
       </c>
       <c r="BW6" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BX6" s="9" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="BY6" s="12">
         <f>BX6/$E$6</f>
         <v/>
       </c>
       <c r="BZ6" s="9" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="CA6" s="9" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="CB6" s="12">
         <f>CA6/$E$6</f>
         <v/>
       </c>
       <c r="CC6" s="9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="CD6" s="9" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="CE6" s="12">
         <f>CD6/$E$6</f>
         <v/>
       </c>
       <c r="CF6" s="9" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="CG6" s="9" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="CH6" s="12">
         <f>CG6/$E$6</f>
         <v/>
       </c>
       <c r="CI6" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CJ6" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="CK6" s="12">
         <f>CJ6/$E$6</f>
         <v/>
       </c>
       <c r="CL6" s="9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CM6" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="CN6" s="12">
         <f>CM6/$E$6</f>
         <v/>
       </c>
-      <c r="CO6" s="9" t="n"/>
+      <c r="CO6" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="CP6" s="9" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="CQ6" s="12">
         <f>CP6/$E$6</f>
+        <v/>
+      </c>
+      <c r="CR6" s="9" t="n"/>
+      <c r="CS6" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="CT6" s="12">
+        <f>CS6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -3755,7 +3878,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>123</v>
@@ -3765,10 +3888,10 @@
         <v/>
       </c>
       <c r="O7" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q7" s="12">
         <f>P7/$E$7</f>
@@ -3795,7 +3918,7 @@
         <v/>
       </c>
       <c r="X7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>120</v>
@@ -3805,10 +3928,10 @@
         <v/>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AC7" s="12">
         <f>AB7/$E$7</f>
@@ -3825,7 +3948,7 @@
         <v/>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="9" t="n">
         <v>119</v>
@@ -3838,109 +3961,109 @@
         <v>3</v>
       </c>
       <c r="AK7" s="9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AL7" s="12">
         <f>AK7/$E$7</f>
         <v/>
       </c>
       <c r="AM7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN7" s="9" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AO7" s="12">
         <f>AN7/$E$7</f>
         <v/>
       </c>
       <c r="AP7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AQ7" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AR7" s="12">
         <f>AQ7/$E$7</f>
         <v/>
       </c>
       <c r="AS7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT7" s="9" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AU7" s="12">
         <f>AT7/$E$7</f>
         <v/>
       </c>
       <c r="AV7" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW7" s="9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AX7" s="12">
         <f>AW7/$E$7</f>
         <v/>
       </c>
-      <c r="AY7" s="9" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="12" t="n"/>
-      <c r="BB7" s="9" t="n">
+      <c r="AY7" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="BA7" s="12">
+        <f>AZ7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="9" t="n"/>
+      <c r="BC7" s="9" t="n"/>
+      <c r="BD7" s="12" t="n"/>
+      <c r="BE7" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="BC7" s="9" t="n">
+      <c r="BF7" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="BD7" s="12">
-        <f>BC7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="12" t="n"/>
+      <c r="BG7" s="12">
+        <f>BF7/$E$7</f>
+        <v/>
+      </c>
       <c r="BH7" s="9" t="n"/>
       <c r="BI7" s="9" t="n"/>
       <c r="BJ7" s="12" t="n"/>
-      <c r="BK7" s="9" t="n">
+      <c r="BK7" s="9" t="n"/>
+      <c r="BL7" s="9" t="n"/>
+      <c r="BM7" s="12" t="n"/>
+      <c r="BN7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="BL7" s="9" t="n">
+      <c r="BO7" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="BM7" s="12">
-        <f>BL7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BN7" s="9" t="n"/>
-      <c r="BO7" s="9" t="n"/>
-      <c r="BP7" s="12" t="n"/>
-      <c r="BQ7" s="9" t="n">
+      <c r="BP7" s="12">
+        <f>BO7/$E$7</f>
+        <v/>
+      </c>
+      <c r="BQ7" s="9" t="n"/>
+      <c r="BR7" s="9" t="n"/>
+      <c r="BS7" s="12" t="n"/>
+      <c r="BT7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BR7" s="9" t="n">
+      <c r="BU7" s="9" t="n">
         <v>78</v>
-      </c>
-      <c r="BS7" s="12">
-        <f>BR7/$E$7</f>
-        <v/>
-      </c>
-      <c r="BT7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU7" s="9" t="n">
-        <v>74</v>
       </c>
       <c r="BV7" s="12">
         <f>BU7/$E$7</f>
         <v/>
       </c>
       <c r="BW7" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BX7" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BY7" s="12">
         <f>BX7/$E$7</f>
@@ -3950,58 +4073,68 @@
         <v>6</v>
       </c>
       <c r="CA7" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="CB7" s="12">
         <f>CA7/$E$7</f>
         <v/>
       </c>
       <c r="CC7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CD7" s="9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="CE7" s="12">
         <f>CD7/$E$7</f>
         <v/>
       </c>
       <c r="CF7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CG7" s="9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="CH7" s="12">
         <f>CG7/$E$7</f>
         <v/>
       </c>
       <c r="CI7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CJ7" s="9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="CK7" s="12">
         <f>CJ7/$E$7</f>
         <v/>
       </c>
       <c r="CL7" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CM7" s="9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="CN7" s="12">
         <f>CM7/$E$7</f>
         <v/>
       </c>
-      <c r="CO7" s="9" t="n"/>
+      <c r="CO7" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="CP7" s="9" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="CQ7" s="12">
         <f>CP7/$E$7</f>
+        <v/>
+      </c>
+      <c r="CR7" s="9" t="n"/>
+      <c r="CS7" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="CT7" s="12">
+        <f>CS7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -4028,7 +4161,7 @@
         <v>1618</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1005</v>
@@ -4038,17 +4171,17 @@
         <v/>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K8" s="12">
         <f>J8/$E$8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>1003</v>
@@ -4058,17 +4191,17 @@
         <v/>
       </c>
       <c r="O8" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/$E$8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>1000</v>
@@ -4078,10 +4211,10 @@
         <v/>
       </c>
       <c r="U8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="W8" s="12">
         <f>V8/$E$8</f>
@@ -4108,7 +4241,7 @@
         <v/>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="9" t="n">
         <v>998</v>
@@ -4118,112 +4251,112 @@
         <v/>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH8" s="9" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="AI8" s="12">
         <f>AH8/$E$8</f>
         <v/>
       </c>
       <c r="AJ8" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AK8" s="9" t="n">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="AL8" s="12">
         <f>AK8/$E$8</f>
         <v/>
       </c>
       <c r="AM8" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AN8" s="9" t="n">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="AO8" s="12">
         <f>AN8/$E$8</f>
         <v/>
       </c>
       <c r="AP8" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AQ8" s="9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AR8" s="12">
         <f>AQ8/$E$8</f>
         <v/>
       </c>
       <c r="AS8" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT8" s="9" t="n">
-        <v>976</v>
+        <v>985</v>
       </c>
       <c r="AU8" s="12">
         <f>AT8/$E$8</f>
         <v/>
       </c>
       <c r="AV8" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AW8" s="9" t="n">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="AX8" s="12">
         <f>AW8/$E$8</f>
         <v/>
       </c>
-      <c r="AY8" s="9" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="12" t="n"/>
-      <c r="BB8" s="9" t="n">
+      <c r="AY8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ8" s="9" t="n">
+        <v>965</v>
+      </c>
+      <c r="BA8" s="12">
+        <f>AZ8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="9" t="n"/>
+      <c r="BC8" s="9" t="n"/>
+      <c r="BD8" s="12" t="n"/>
+      <c r="BE8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="BC8" s="9" t="n">
+      <c r="BF8" s="9" t="n">
         <v>951</v>
       </c>
-      <c r="BD8" s="12">
-        <f>BC8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BE8" s="9" t="n"/>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="12" t="n"/>
+      <c r="BG8" s="12">
+        <f>BF8/$E$8</f>
+        <v/>
+      </c>
       <c r="BH8" s="9" t="n"/>
       <c r="BI8" s="9" t="n"/>
       <c r="BJ8" s="12" t="n"/>
-      <c r="BK8" s="9" t="n">
+      <c r="BK8" s="9" t="n"/>
+      <c r="BL8" s="9" t="n"/>
+      <c r="BM8" s="12" t="n"/>
+      <c r="BN8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BL8" s="9" t="n">
+      <c r="BO8" s="9" t="n">
         <v>922</v>
       </c>
-      <c r="BM8" s="12">
-        <f>BL8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n"/>
-      <c r="BP8" s="12" t="n"/>
-      <c r="BQ8" s="9" t="n">
+      <c r="BP8" s="12">
+        <f>BO8/$E$8</f>
+        <v/>
+      </c>
+      <c r="BQ8" s="9" t="n"/>
+      <c r="BR8" s="9" t="n"/>
+      <c r="BS8" s="12" t="n"/>
+      <c r="BT8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="BR8" s="9" t="n">
+      <c r="BU8" s="9" t="n">
         <v>907</v>
-      </c>
-      <c r="BS8" s="12">
-        <f>BR8/$E$8</f>
-        <v/>
-      </c>
-      <c r="BT8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU8" s="9" t="n">
-        <v>892</v>
       </c>
       <c r="BV8" s="12">
         <f>BU8/$E$8</f>
@@ -4233,68 +4366,78 @@
         <v>7</v>
       </c>
       <c r="BX8" s="9" t="n">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="BY8" s="12">
         <f>BX8/$E$8</f>
         <v/>
       </c>
       <c r="BZ8" s="9" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="CA8" s="9" t="n">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="CB8" s="12">
         <f>CA8/$E$8</f>
         <v/>
       </c>
       <c r="CC8" s="9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="CD8" s="9" t="n">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="CE8" s="12">
         <f>CD8/$E$8</f>
         <v/>
       </c>
       <c r="CF8" s="9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CG8" s="9" t="n">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="CH8" s="12">
         <f>CG8/$E$8</f>
         <v/>
       </c>
       <c r="CI8" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="CJ8" s="9" t="n">
-        <v>818</v>
+        <v>837</v>
       </c>
       <c r="CK8" s="12">
         <f>CJ8/$E$8</f>
         <v/>
       </c>
       <c r="CL8" s="9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CM8" s="9" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="CN8" s="12">
         <f>CM8/$E$8</f>
         <v/>
       </c>
-      <c r="CO8" s="9" t="n"/>
+      <c r="CO8" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="CP8" s="9" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="CQ8" s="12">
         <f>CP8/$E$8</f>
+        <v/>
+      </c>
+      <c r="CR8" s="9" t="n"/>
+      <c r="CS8" s="9" t="n">
+        <v>792</v>
+      </c>
+      <c r="CT8" s="12">
+        <f>CS8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -4411,7 +4554,7 @@
         <v/>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="9" t="n">
         <v>1125</v>
@@ -4421,27 +4564,27 @@
         <v/>
       </c>
       <c r="AJ9" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK9" s="9" t="n">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AL9" s="12">
         <f>AK9/$E$9</f>
         <v/>
       </c>
       <c r="AM9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN9" s="9" t="n">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="AO9" s="12">
         <f>AN9/$E$9</f>
         <v/>
       </c>
       <c r="AP9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="9" t="n">
         <v>1119</v>
@@ -4451,17 +4594,17 @@
         <v/>
       </c>
       <c r="AS9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT9" s="9" t="n">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="AU9" s="12">
         <f>AT9/$E$9</f>
         <v/>
       </c>
       <c r="AV9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW9" s="9" t="n">
         <v>1117</v>
@@ -4470,124 +4613,134 @@
         <f>AW9/$E$9</f>
         <v/>
       </c>
-      <c r="AY9" s="9" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="12" t="n"/>
-      <c r="BB9" s="9" t="n">
+      <c r="AY9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="9" t="n">
+        <v>1117</v>
+      </c>
+      <c r="BA9" s="12">
+        <f>AZ9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="9" t="n"/>
+      <c r="BC9" s="9" t="n"/>
+      <c r="BD9" s="12" t="n"/>
+      <c r="BE9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="BC9" s="9" t="n">
+      <c r="BF9" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="BD9" s="12">
-        <f>BC9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="12" t="n"/>
+      <c r="BG9" s="12">
+        <f>BF9/$E$9</f>
+        <v/>
+      </c>
       <c r="BH9" s="9" t="n"/>
       <c r="BI9" s="9" t="n"/>
       <c r="BJ9" s="12" t="n"/>
-      <c r="BK9" s="9" t="n">
+      <c r="BK9" s="9" t="n"/>
+      <c r="BL9" s="9" t="n"/>
+      <c r="BM9" s="12" t="n"/>
+      <c r="BN9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BL9" s="9" t="n">
+      <c r="BO9" s="9" t="n">
         <v>1111</v>
       </c>
-      <c r="BM9" s="12">
-        <f>BL9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n"/>
-      <c r="BP9" s="12" t="n"/>
-      <c r="BQ9" s="9" t="n">
+      <c r="BP9" s="12">
+        <f>BO9/$E$9</f>
+        <v/>
+      </c>
+      <c r="BQ9" s="9" t="n"/>
+      <c r="BR9" s="9" t="n"/>
+      <c r="BS9" s="12" t="n"/>
+      <c r="BT9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="BR9" s="9" t="n">
+      <c r="BU9" s="9" t="n">
         <v>1109</v>
-      </c>
-      <c r="BS9" s="12">
-        <f>BR9/$E$9</f>
-        <v/>
-      </c>
-      <c r="BT9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU9" s="9" t="n">
-        <v>1107</v>
       </c>
       <c r="BV9" s="12">
         <f>BU9/$E$9</f>
         <v/>
       </c>
       <c r="BW9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BX9" s="9" t="n">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="BY9" s="12">
         <f>BX9/$E$9</f>
         <v/>
       </c>
       <c r="BZ9" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CA9" s="9" t="n">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="CB9" s="12">
         <f>CA9/$E$9</f>
         <v/>
       </c>
       <c r="CC9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CD9" s="9" t="n">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="CE9" s="12">
         <f>CD9/$E$9</f>
         <v/>
       </c>
       <c r="CF9" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG9" s="9" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="CH9" s="12">
         <f>CG9/$E$9</f>
         <v/>
       </c>
       <c r="CI9" s="9" t="n">
-        <v>1093</v>
+        <v>2</v>
       </c>
       <c r="CJ9" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="CK9" s="12">
         <f>CJ9/$E$9</f>
         <v/>
       </c>
       <c r="CL9" s="9" t="n">
-        <v>-1091</v>
+        <v>1093</v>
       </c>
       <c r="CM9" s="9" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="CN9" s="12">
         <f>CM9/$E$9</f>
         <v/>
       </c>
-      <c r="CO9" s="9" t="n"/>
+      <c r="CO9" s="9" t="n">
+        <v>-1091</v>
+      </c>
       <c r="CP9" s="9" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="CQ9" s="12">
         <f>CP9/$E$9</f>
+        <v/>
+      </c>
+      <c r="CR9" s="9" t="n"/>
+      <c r="CS9" s="9" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CT9" s="12">
+        <f>CS9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -4614,7 +4767,7 @@
         <v>988</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>513</v>
@@ -4624,17 +4777,17 @@
         <v/>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K10" s="12">
         <f>J10/$E$10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>509</v>
@@ -4644,27 +4797,27 @@
         <v/>
       </c>
       <c r="O10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/$E$10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="T10" s="12">
         <f>S10/$E$10</f>
         <v/>
       </c>
       <c r="U10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>504</v>
@@ -4674,10 +4827,10 @@
         <v/>
       </c>
       <c r="X10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Z10" s="12">
         <f>Y10/$E$10</f>
@@ -4694,7 +4847,7 @@
         <v/>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="9" t="n">
         <v>502</v>
@@ -4704,37 +4857,37 @@
         <v/>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AI10" s="12">
         <f>AH10/$E$10</f>
         <v/>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AL10" s="12">
         <f>AK10/$E$10</f>
         <v/>
       </c>
       <c r="AM10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN10" s="9" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="AO10" s="12">
         <f>AN10/$E$10</f>
         <v/>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="9" t="n">
         <v>491</v>
@@ -4744,79 +4897,79 @@
         <v/>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AT10" s="9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/$E$10</f>
         <v/>
       </c>
       <c r="AV10" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AW10" s="9" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="AX10" s="12">
         <f>AW10/$E$10</f>
         <v/>
       </c>
-      <c r="AY10" s="9" t="n"/>
-      <c r="AZ10" s="9" t="n"/>
-      <c r="BA10" s="12" t="n"/>
-      <c r="BB10" s="9" t="n">
+      <c r="AY10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ10" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="BA10" s="12">
+        <f>AZ10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BB10" s="9" t="n"/>
+      <c r="BC10" s="9" t="n"/>
+      <c r="BD10" s="12" t="n"/>
+      <c r="BE10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="BC10" s="9" t="n">
+      <c r="BF10" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="BD10" s="12">
-        <f>BC10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BE10" s="9" t="n"/>
-      <c r="BF10" s="9" t="n"/>
-      <c r="BG10" s="12" t="n"/>
+      <c r="BG10" s="12">
+        <f>BF10/$E$10</f>
+        <v/>
+      </c>
       <c r="BH10" s="9" t="n"/>
       <c r="BI10" s="9" t="n"/>
       <c r="BJ10" s="12" t="n"/>
-      <c r="BK10" s="9" t="n">
+      <c r="BK10" s="9" t="n"/>
+      <c r="BL10" s="9" t="n"/>
+      <c r="BM10" s="12" t="n"/>
+      <c r="BN10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BL10" s="9" t="n">
+      <c r="BO10" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BM10" s="12">
-        <f>BL10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BN10" s="9" t="n"/>
-      <c r="BO10" s="9" t="n"/>
-      <c r="BP10" s="12" t="n"/>
-      <c r="BQ10" s="9" t="n">
+      <c r="BP10" s="12">
+        <f>BO10/$E$10</f>
+        <v/>
+      </c>
+      <c r="BQ10" s="9" t="n"/>
+      <c r="BR10" s="9" t="n"/>
+      <c r="BS10" s="12" t="n"/>
+      <c r="BT10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BR10" s="9" t="n">
+      <c r="BU10" s="9" t="n">
         <v>463</v>
-      </c>
-      <c r="BS10" s="12">
-        <f>BR10/$E$10</f>
-        <v/>
-      </c>
-      <c r="BT10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU10" s="9" t="n">
-        <v>462</v>
       </c>
       <c r="BV10" s="12">
         <f>BU10/$E$10</f>
         <v/>
       </c>
       <c r="BW10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BX10" s="9" t="n">
         <v>462</v>
@@ -4829,58 +4982,68 @@
         <v>2</v>
       </c>
       <c r="CA10" s="9" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="CB10" s="12">
         <f>CA10/$E$10</f>
         <v/>
       </c>
       <c r="CC10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CD10" s="9" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="CE10" s="12">
         <f>CD10/$E$10</f>
         <v/>
       </c>
       <c r="CF10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CG10" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="CH10" s="12">
         <f>CG10/$E$10</f>
         <v/>
       </c>
       <c r="CI10" s="9" t="n">
-        <v>447</v>
+        <v>10</v>
       </c>
       <c r="CJ10" s="9" t="n">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="CK10" s="12">
         <f>CJ10/$E$10</f>
         <v/>
       </c>
       <c r="CL10" s="9" t="n">
-        <v>-446</v>
+        <v>447</v>
       </c>
       <c r="CM10" s="9" t="n">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="CN10" s="12">
         <f>CM10/$E$10</f>
         <v/>
       </c>
-      <c r="CO10" s="9" t="n"/>
+      <c r="CO10" s="9" t="n">
+        <v>-446</v>
+      </c>
       <c r="CP10" s="9" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="CQ10" s="12">
         <f>CP10/$E$10</f>
+        <v/>
+      </c>
+      <c r="CR10" s="9" t="n"/>
+      <c r="CS10" s="9" t="n">
+        <v>446</v>
+      </c>
+      <c r="CT10" s="12">
+        <f>CS10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -5007,7 +5170,7 @@
         <v/>
       </c>
       <c r="AJ11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="9" t="n">
         <v>467</v>
@@ -5020,17 +5183,17 @@
         <v>1</v>
       </c>
       <c r="AN11" s="9" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO11" s="12">
         <f>AN11/$E$11</f>
         <v/>
       </c>
       <c r="AP11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ11" s="9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AR11" s="12">
         <f>AQ11/$E$11</f>
@@ -5056,60 +5219,60 @@
         <f>AW11/$E$11</f>
         <v/>
       </c>
-      <c r="AY11" s="9" t="n"/>
-      <c r="AZ11" s="9" t="n"/>
-      <c r="BA11" s="12" t="n"/>
-      <c r="BB11" s="9" t="n">
+      <c r="AY11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="BA11" s="12">
+        <f>AZ11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="9" t="n"/>
+      <c r="BC11" s="9" t="n"/>
+      <c r="BD11" s="12" t="n"/>
+      <c r="BE11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BC11" s="9" t="n">
+      <c r="BF11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="BD11" s="12">
-        <f>BC11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BE11" s="9" t="n"/>
-      <c r="BF11" s="9" t="n"/>
-      <c r="BG11" s="12" t="n"/>
+      <c r="BG11" s="12">
+        <f>BF11/$E$11</f>
+        <v/>
+      </c>
       <c r="BH11" s="9" t="n"/>
       <c r="BI11" s="9" t="n"/>
       <c r="BJ11" s="12" t="n"/>
-      <c r="BK11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL11" s="9" t="n">
+      <c r="BK11" s="9" t="n"/>
+      <c r="BL11" s="9" t="n"/>
+      <c r="BM11" s="12" t="n"/>
+      <c r="BN11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" s="9" t="n">
         <v>464</v>
       </c>
-      <c r="BM11" s="12">
-        <f>BL11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BN11" s="9" t="n"/>
-      <c r="BO11" s="9" t="n"/>
-      <c r="BP11" s="12" t="n"/>
-      <c r="BQ11" s="9" t="n">
+      <c r="BP11" s="12">
+        <f>BO11/$E$11</f>
+        <v/>
+      </c>
+      <c r="BQ11" s="9" t="n"/>
+      <c r="BR11" s="9" t="n"/>
+      <c r="BS11" s="12" t="n"/>
+      <c r="BT11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="BR11" s="9" t="n">
+      <c r="BU11" s="9" t="n">
         <v>464</v>
-      </c>
-      <c r="BS11" s="12">
-        <f>BR11/$E$11</f>
-        <v/>
-      </c>
-      <c r="BT11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU11" s="9" t="n">
-        <v>463</v>
       </c>
       <c r="BV11" s="12">
         <f>BU11/$E$11</f>
         <v/>
       </c>
       <c r="BW11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX11" s="9" t="n">
         <v>463</v>
@@ -5119,40 +5282,40 @@
         <v/>
       </c>
       <c r="BZ11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CA11" s="9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="CB11" s="12">
         <f>CA11/$E$11</f>
         <v/>
       </c>
       <c r="CC11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CD11" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="CE11" s="12">
         <f>CD11/$E$11</f>
         <v/>
       </c>
       <c r="CF11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CG11" s="9" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CH11" s="12">
         <f>CG11/$E$11</f>
         <v/>
       </c>
       <c r="CI11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CJ11" s="9" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="CK11" s="12">
         <f>CJ11/$E$11</f>
@@ -5162,18 +5325,28 @@
         <v>2</v>
       </c>
       <c r="CM11" s="9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CN11" s="12">
         <f>CM11/$E$11</f>
         <v/>
       </c>
-      <c r="CO11" s="9" t="n"/>
+      <c r="CO11" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="CP11" s="9" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CQ11" s="12">
         <f>CP11/$E$11</f>
+        <v/>
+      </c>
+      <c r="CR11" s="9" t="n"/>
+      <c r="CS11" s="9" t="n">
+        <v>452</v>
+      </c>
+      <c r="CT11" s="12">
+        <f>CS11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -5300,7 +5473,7 @@
         <v/>
       </c>
       <c r="AJ12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="9" t="n">
         <v>236</v>
@@ -5310,17 +5483,17 @@
         <v/>
       </c>
       <c r="AM12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO12" s="12">
         <f>AN12/$E$12</f>
         <v/>
       </c>
       <c r="AP12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="9" t="n">
         <v>235</v>
@@ -5330,10 +5503,10 @@
         <v/>
       </c>
       <c r="AS12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT12" s="9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AU12" s="12">
         <f>AT12/$E$12</f>
@@ -5349,48 +5522,48 @@
         <f>AW12/$E$12</f>
         <v/>
       </c>
-      <c r="AY12" s="9" t="n"/>
-      <c r="AZ12" s="9" t="n"/>
-      <c r="BA12" s="12" t="n"/>
-      <c r="BB12" s="9" t="n">
+      <c r="AY12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BA12" s="12">
+        <f>AZ12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="12" t="n"/>
+      <c r="BE12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="BC12" s="9" t="n">
+      <c r="BF12" s="9" t="n">
         <v>234</v>
       </c>
-      <c r="BD12" s="12">
-        <f>BC12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BE12" s="9" t="n"/>
-      <c r="BF12" s="9" t="n"/>
-      <c r="BG12" s="12" t="n"/>
+      <c r="BG12" s="12">
+        <f>BF12/$E$12</f>
+        <v/>
+      </c>
       <c r="BH12" s="9" t="n"/>
       <c r="BI12" s="9" t="n"/>
       <c r="BJ12" s="12" t="n"/>
-      <c r="BK12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" s="9" t="n">
+      <c r="BK12" s="9" t="n"/>
+      <c r="BL12" s="9" t="n"/>
+      <c r="BM12" s="12" t="n"/>
+      <c r="BN12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="BM12" s="12">
-        <f>BL12/$E$12</f>
-        <v/>
-      </c>
-      <c r="BN12" s="9" t="n"/>
-      <c r="BO12" s="9" t="n"/>
-      <c r="BP12" s="12" t="n"/>
-      <c r="BQ12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" s="9" t="n">
-        <v>236</v>
-      </c>
-      <c r="BS12" s="12">
-        <f>BR12/$E$12</f>
-        <v/>
-      </c>
+      <c r="BP12" s="12">
+        <f>BO12/$E$12</f>
+        <v/>
+      </c>
+      <c r="BQ12" s="9" t="n"/>
+      <c r="BR12" s="9" t="n"/>
+      <c r="BS12" s="12" t="n"/>
       <c r="BT12" s="9" t="n">
         <v>0</v>
       </c>
@@ -5432,7 +5605,7 @@
         <v/>
       </c>
       <c r="CF12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG12" s="9" t="n">
         <v>236</v>
@@ -5442,31 +5615,41 @@
         <v/>
       </c>
       <c r="CI12" s="9" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="CJ12" s="9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="CK12" s="12">
         <f>CJ12/$E$12</f>
         <v/>
       </c>
       <c r="CL12" s="9" t="n">
-        <v>-234</v>
+        <v>235</v>
       </c>
       <c r="CM12" s="9" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="CN12" s="12">
         <f>CM12/$E$12</f>
         <v/>
       </c>
-      <c r="CO12" s="9" t="n"/>
+      <c r="CO12" s="9" t="n">
+        <v>-234</v>
+      </c>
       <c r="CP12" s="9" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="CQ12" s="12">
         <f>CP12/$E$12</f>
+        <v/>
+      </c>
+      <c r="CR12" s="9" t="n"/>
+      <c r="CS12" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="CT12" s="12">
+        <f>CS12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -5493,7 +5676,7 @@
         <v>1296</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>640</v>
@@ -5503,17 +5686,17 @@
         <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="K13" s="12">
         <f>J13/$E$13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>626</v>
@@ -5523,27 +5706,27 @@
         <v/>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/$E$13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="T13" s="12">
         <f>S13/$E$13</f>
         <v/>
       </c>
       <c r="U13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>622</v>
@@ -5553,10 +5736,10 @@
         <v/>
       </c>
       <c r="X13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="Z13" s="12">
         <f>Y13/$E$13</f>
@@ -5573,7 +5756,7 @@
         <v/>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="9" t="n">
         <v>621</v>
@@ -5583,142 +5766,142 @@
         <v/>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH13" s="9" t="n">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AI13" s="12">
         <f>AH13/$E$13</f>
         <v/>
       </c>
       <c r="AJ13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK13" s="9" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AL13" s="12">
         <f>AK13/$E$13</f>
         <v/>
       </c>
       <c r="AM13" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN13" s="9" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AO13" s="12">
         <f>AN13/$E$13</f>
         <v/>
       </c>
       <c r="AP13" s="9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AQ13" s="9" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AR13" s="12">
         <f>AQ13/$E$13</f>
         <v/>
       </c>
       <c r="AS13" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT13" s="9" t="n">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="AU13" s="12">
         <f>AT13/$E$13</f>
         <v/>
       </c>
       <c r="AV13" s="9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AW13" s="9" t="n">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AX13" s="12">
         <f>AW13/$E$13</f>
         <v/>
       </c>
-      <c r="AY13" s="9" t="n"/>
-      <c r="AZ13" s="9" t="n"/>
-      <c r="BA13" s="12" t="n"/>
-      <c r="BB13" s="9" t="n">
+      <c r="AY13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ13" s="9" t="n">
+        <v>573</v>
+      </c>
+      <c r="BA13" s="12">
+        <f>AZ13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="9" t="n"/>
+      <c r="BC13" s="9" t="n"/>
+      <c r="BD13" s="12" t="n"/>
+      <c r="BE13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="BC13" s="9" t="n">
+      <c r="BF13" s="9" t="n">
         <v>544</v>
       </c>
-      <c r="BD13" s="12">
-        <f>BC13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BE13" s="9" t="n"/>
-      <c r="BF13" s="9" t="n"/>
-      <c r="BG13" s="12" t="n"/>
+      <c r="BG13" s="12">
+        <f>BF13/$E$13</f>
+        <v/>
+      </c>
       <c r="BH13" s="9" t="n"/>
       <c r="BI13" s="9" t="n"/>
       <c r="BJ13" s="12" t="n"/>
-      <c r="BK13" s="9" t="n">
+      <c r="BK13" s="9" t="n"/>
+      <c r="BL13" s="9" t="n"/>
+      <c r="BM13" s="12" t="n"/>
+      <c r="BN13" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="BL13" s="9" t="n">
+      <c r="BO13" s="9" t="n">
         <v>460</v>
       </c>
-      <c r="BM13" s="12">
-        <f>BL13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BN13" s="9" t="n"/>
-      <c r="BO13" s="9" t="n"/>
-      <c r="BP13" s="12" t="n"/>
-      <c r="BQ13" s="9" t="n">
+      <c r="BP13" s="12">
+        <f>BO13/$E$13</f>
+        <v/>
+      </c>
+      <c r="BQ13" s="9" t="n"/>
+      <c r="BR13" s="9" t="n"/>
+      <c r="BS13" s="12" t="n"/>
+      <c r="BT13" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="BR13" s="9" t="n">
+      <c r="BU13" s="9" t="n">
         <v>433</v>
-      </c>
-      <c r="BS13" s="12">
-        <f>BR13/$E$13</f>
-        <v/>
-      </c>
-      <c r="BT13" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU13" s="9" t="n">
-        <v>421</v>
       </c>
       <c r="BV13" s="12">
         <f>BU13/$E$13</f>
         <v/>
       </c>
       <c r="BW13" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BX13" s="9" t="n">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="BY13" s="12">
         <f>BX13/$E$13</f>
         <v/>
       </c>
       <c r="BZ13" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA13" s="9" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="CB13" s="12">
         <f>CA13/$E$13</f>
         <v/>
       </c>
       <c r="CC13" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="CD13" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="CE13" s="12">
         <f>CD13/$E$13</f>
@@ -5728,38 +5911,48 @@
         <v>4</v>
       </c>
       <c r="CG13" s="9" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="CH13" s="12">
         <f>CG13/$E$13</f>
         <v/>
       </c>
       <c r="CI13" s="9" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="CJ13" s="9" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="CK13" s="12">
         <f>CJ13/$E$13</f>
         <v/>
       </c>
       <c r="CL13" s="9" t="n">
-        <v>-379</v>
+        <v>381</v>
       </c>
       <c r="CM13" s="9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="CN13" s="12">
         <f>CM13/$E$13</f>
         <v/>
       </c>
-      <c r="CO13" s="9" t="n"/>
+      <c r="CO13" s="9" t="n">
+        <v>-379</v>
+      </c>
       <c r="CP13" s="9" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="CQ13" s="12">
         <f>CP13/$E$13</f>
+        <v/>
+      </c>
+      <c r="CR13" s="9" t="n"/>
+      <c r="CS13" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="CT13" s="12">
+        <f>CS13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -5786,7 +5979,7 @@
         <v>1500</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1152</v>
@@ -5796,17 +5989,17 @@
         <v/>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="K14" s="12">
         <f>J14/$E$14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>1151</v>
@@ -5816,27 +6009,27 @@
         <v/>
       </c>
       <c r="O14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/$E$14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="T14" s="12">
         <f>S14/$E$14</f>
         <v/>
       </c>
       <c r="U14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>1146</v>
@@ -5846,10 +6039,10 @@
         <v/>
       </c>
       <c r="X14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="Z14" s="12">
         <f>Y14/$E$14</f>
@@ -5866,7 +6059,7 @@
         <v/>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="9" t="n">
         <v>1145</v>
@@ -5876,17 +6069,17 @@
         <v/>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH14" s="9" t="n">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="AI14" s="12">
         <f>AH14/$E$14</f>
         <v/>
       </c>
       <c r="AJ14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="9" t="n">
         <v>1142</v>
@@ -5896,122 +6089,122 @@
         <v/>
       </c>
       <c r="AM14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN14" s="9" t="n">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="AO14" s="12">
         <f>AN14/$E$14</f>
         <v/>
       </c>
       <c r="AP14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AQ14" s="9" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AR14" s="12">
         <f>AQ14/$E$14</f>
         <v/>
       </c>
       <c r="AS14" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT14" s="9" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="AU14" s="12">
         <f>AT14/$E$14</f>
         <v/>
       </c>
       <c r="AV14" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW14" s="9" t="n">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="AX14" s="12">
         <f>AW14/$E$14</f>
         <v/>
       </c>
-      <c r="AY14" s="9" t="n"/>
-      <c r="AZ14" s="9" t="n"/>
-      <c r="BA14" s="12" t="n"/>
-      <c r="BB14" s="9" t="n">
+      <c r="AY14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ14" s="9" t="n">
+        <v>1129</v>
+      </c>
+      <c r="BA14" s="12">
+        <f>AZ14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="9" t="n"/>
+      <c r="BC14" s="9" t="n"/>
+      <c r="BD14" s="12" t="n"/>
+      <c r="BE14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="BC14" s="9" t="n">
+      <c r="BF14" s="9" t="n">
         <v>1126</v>
       </c>
-      <c r="BD14" s="12">
-        <f>BC14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BE14" s="9" t="n"/>
-      <c r="BF14" s="9" t="n"/>
-      <c r="BG14" s="12" t="n"/>
+      <c r="BG14" s="12">
+        <f>BF14/$E$14</f>
+        <v/>
+      </c>
       <c r="BH14" s="9" t="n"/>
       <c r="BI14" s="9" t="n"/>
       <c r="BJ14" s="12" t="n"/>
-      <c r="BK14" s="9" t="n">
+      <c r="BK14" s="9" t="n"/>
+      <c r="BL14" s="9" t="n"/>
+      <c r="BM14" s="12" t="n"/>
+      <c r="BN14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="BL14" s="9" t="n">
+      <c r="BO14" s="9" t="n">
         <v>1115</v>
       </c>
-      <c r="BM14" s="12">
-        <f>BL14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BN14" s="9" t="n"/>
-      <c r="BO14" s="9" t="n"/>
-      <c r="BP14" s="12" t="n"/>
-      <c r="BQ14" s="9" t="n">
+      <c r="BP14" s="12">
+        <f>BO14/$E$14</f>
+        <v/>
+      </c>
+      <c r="BQ14" s="9" t="n"/>
+      <c r="BR14" s="9" t="n"/>
+      <c r="BS14" s="12" t="n"/>
+      <c r="BT14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BR14" s="9" t="n">
+      <c r="BU14" s="9" t="n">
         <v>1110</v>
-      </c>
-      <c r="BS14" s="12">
-        <f>BR14/$E$14</f>
-        <v/>
-      </c>
-      <c r="BT14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU14" s="9" t="n">
-        <v>1100</v>
       </c>
       <c r="BV14" s="12">
         <f>BU14/$E$14</f>
         <v/>
       </c>
       <c r="BW14" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BX14" s="9" t="n">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="BY14" s="12">
         <f>BX14/$E$14</f>
         <v/>
       </c>
       <c r="BZ14" s="9" t="n">
-        <v>1086</v>
+        <v>10</v>
       </c>
       <c r="CA14" s="9" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="CB14" s="12">
         <f>CA14/$E$14</f>
         <v/>
       </c>
       <c r="CC14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="CD14" s="9" t="n">
-        <v>0</v>
+        <v>1086</v>
       </c>
       <c r="CE14" s="12">
         <f>CD14/$E$14</f>
@@ -6047,12 +6240,22 @@
         <f>CM14/$E$14</f>
         <v/>
       </c>
-      <c r="CO14" s="9" t="n"/>
+      <c r="CO14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CP14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CQ14" s="12">
         <f>CP14/$E$14</f>
+        <v/>
+      </c>
+      <c r="CR14" s="9" t="n"/>
+      <c r="CS14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" s="12">
+        <f>CS14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -6099,7 +6302,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="9" t="n">
         <v>127</v>
@@ -6109,10 +6312,10 @@
         <v/>
       </c>
       <c r="O15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/$E$15</f>
@@ -6159,7 +6362,7 @@
         <v/>
       </c>
       <c r="AD15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="9" t="n">
         <v>126</v>
@@ -6172,17 +6375,17 @@
         <v>1</v>
       </c>
       <c r="AH15" s="9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AI15" s="12">
         <f>AH15/$E$15</f>
         <v/>
       </c>
       <c r="AJ15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AL15" s="12">
         <f>AK15/$E$15</f>
@@ -6199,7 +6402,7 @@
         <v/>
       </c>
       <c r="AP15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="9" t="n">
         <v>124</v>
@@ -6209,17 +6412,17 @@
         <v/>
       </c>
       <c r="AS15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT15" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AU15" s="12">
         <f>AT15/$E$15</f>
         <v/>
       </c>
       <c r="AV15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW15" s="9" t="n">
         <v>121</v>
@@ -6228,53 +6431,53 @@
         <f>AW15/$E$15</f>
         <v/>
       </c>
-      <c r="AY15" s="9" t="n"/>
-      <c r="AZ15" s="9" t="n"/>
-      <c r="BA15" s="12" t="n"/>
-      <c r="BB15" s="9" t="n">
+      <c r="AY15" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ15" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="BA15" s="12">
+        <f>AZ15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BB15" s="9" t="n"/>
+      <c r="BC15" s="9" t="n"/>
+      <c r="BD15" s="12" t="n"/>
+      <c r="BE15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="BC15" s="9" t="n">
+      <c r="BF15" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="BD15" s="12">
-        <f>BC15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BE15" s="9" t="n"/>
-      <c r="BF15" s="9" t="n"/>
-      <c r="BG15" s="12" t="n"/>
+      <c r="BG15" s="12">
+        <f>BF15/$E$15</f>
+        <v/>
+      </c>
       <c r="BH15" s="9" t="n"/>
       <c r="BI15" s="9" t="n"/>
       <c r="BJ15" s="12" t="n"/>
-      <c r="BK15" s="9" t="n">
+      <c r="BK15" s="9" t="n"/>
+      <c r="BL15" s="9" t="n"/>
+      <c r="BM15" s="12" t="n"/>
+      <c r="BN15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="BL15" s="9" t="n">
+      <c r="BO15" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="BM15" s="12">
-        <f>BL15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BN15" s="9" t="n"/>
-      <c r="BO15" s="9" t="n"/>
-      <c r="BP15" s="12" t="n"/>
-      <c r="BQ15" s="9" t="n">
+      <c r="BP15" s="12">
+        <f>BO15/$E$15</f>
+        <v/>
+      </c>
+      <c r="BQ15" s="9" t="n"/>
+      <c r="BR15" s="9" t="n"/>
+      <c r="BS15" s="12" t="n"/>
+      <c r="BT15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="BR15" s="9" t="n">
+      <c r="BU15" s="9" t="n">
         <v>86</v>
-      </c>
-      <c r="BS15" s="12">
-        <f>BR15/$E$15</f>
-        <v/>
-      </c>
-      <c r="BT15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU15" s="9" t="n">
-        <v>82</v>
       </c>
       <c r="BV15" s="12">
         <f>BU15/$E$15</f>
@@ -6284,24 +6487,24 @@
         <v>3</v>
       </c>
       <c r="BX15" s="9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="BY15" s="12">
         <f>BX15/$E$15</f>
         <v/>
       </c>
       <c r="BZ15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CA15" s="9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="CB15" s="12">
         <f>CA15/$E$15</f>
         <v/>
       </c>
       <c r="CC15" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="CD15" s="9" t="n">
         <v>76</v>
@@ -6311,10 +6514,10 @@
         <v/>
       </c>
       <c r="CF15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="CG15" s="9" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="CH15" s="12">
         <f>CG15/$E$15</f>
@@ -6340,12 +6543,22 @@
         <f>CM15/$E$15</f>
         <v/>
       </c>
-      <c r="CO15" s="9" t="n"/>
+      <c r="CO15" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="CP15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="CQ15" s="12">
         <f>CP15/$E$15</f>
+        <v/>
+      </c>
+      <c r="CR15" s="9" t="n"/>
+      <c r="CS15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" s="12">
+        <f>CS15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -6521,51 +6734,58 @@
         <f>AW16/$E$16</f>
         <v/>
       </c>
-      <c r="AY16" s="9" t="n"/>
-      <c r="AZ16" s="9" t="n"/>
-      <c r="BA16" s="12" t="n"/>
-      <c r="BB16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" s="9" t="n">
+      <c r="AY16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BD16" s="12">
-        <f>BC16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BE16" s="9" t="n"/>
-      <c r="BF16" s="9" t="n"/>
-      <c r="BG16" s="12" t="n"/>
+      <c r="BA16" s="12">
+        <f>AZ16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="12" t="n"/>
+      <c r="BE16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="9" t="n">
+        <v>659</v>
+      </c>
+      <c r="BG16" s="12">
+        <f>BF16/$E$16</f>
+        <v/>
+      </c>
       <c r="BH16" s="9" t="n"/>
       <c r="BI16" s="9" t="n"/>
       <c r="BJ16" s="12" t="n"/>
-      <c r="BK16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" s="9" t="n">
+      <c r="BK16" s="9" t="n"/>
+      <c r="BL16" s="9" t="n"/>
+      <c r="BM16" s="12" t="n"/>
+      <c r="BN16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BM16" s="12">
-        <f>BL16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BN16" s="9" t="n"/>
-      <c r="BO16" s="9" t="n"/>
-      <c r="BP16" s="12" t="n"/>
-      <c r="BQ16" s="9" t="n">
+      <c r="BP16" s="12">
+        <f>BO16/$E$16</f>
+        <v/>
+      </c>
+      <c r="BQ16" s="9" t="n"/>
+      <c r="BR16" s="9" t="n"/>
+      <c r="BS16" s="12" t="n"/>
+      <c r="BT16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BR16" s="9" t="n">
+      <c r="BU16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="BS16" s="12">
-        <f>BR16/$E$16</f>
-        <v/>
-      </c>
-      <c r="BT16" s="9" t="n"/>
-      <c r="BU16" s="9" t="n"/>
-      <c r="BV16" s="12" t="n"/>
+      <c r="BV16" s="12">
+        <f>BU16/$E$16</f>
+        <v/>
+      </c>
       <c r="BW16" s="9" t="n"/>
       <c r="BX16" s="9" t="n"/>
       <c r="BY16" s="12" t="n"/>
@@ -6585,11 +6805,14 @@
       <c r="CM16" s="9" t="n"/>
       <c r="CN16" s="12" t="n"/>
       <c r="CO16" s="9" t="n"/>
-      <c r="CP16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ16" s="12">
-        <f>CP16/$E$16</f>
+      <c r="CP16" s="9" t="n"/>
+      <c r="CQ16" s="12" t="n"/>
+      <c r="CR16" s="9" t="n"/>
+      <c r="CS16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" s="12">
+        <f>CS16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -6705,6 +6928,9 @@
       <c r="CO17" s="9" t="n"/>
       <c r="CP17" s="9" t="n"/>
       <c r="CQ17" s="12" t="n"/>
+      <c r="CR17" s="9" t="n"/>
+      <c r="CS17" s="9" t="n"/>
+      <c r="CT17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -6729,7 +6955,7 @@
         <v>830</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>202</v>
@@ -6739,17 +6965,17 @@
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="K18" s="12">
         <f>J18/$E$18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
         <v>191</v>
@@ -6759,46 +6985,48 @@
         <v/>
       </c>
       <c r="O18" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="Q18" s="12">
         <f>P18/$E$18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S18" s="9" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="T18" s="12">
         <f>S18/$E$18</f>
         <v/>
       </c>
       <c r="U18" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="W18" s="12">
         <f>V18/$E$18</f>
         <v/>
       </c>
       <c r="X18" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Z18" s="12">
         <f>Y18/$E$18</f>
         <v/>
       </c>
-      <c r="AA18" s="9" t="n"/>
+      <c r="AA18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB18" s="9" t="n">
         <v>139</v>
       </c>
@@ -6807,8 +7035,13 @@
         <v/>
       </c>
       <c r="AD18" s="9" t="n"/>
-      <c r="AE18" s="9" t="n"/>
-      <c r="AF18" s="12" t="n"/>
+      <c r="AE18" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="AF18" s="12">
+        <f>AE18/$E$18</f>
+        <v/>
+      </c>
       <c r="AG18" s="9" t="n"/>
       <c r="AH18" s="9" t="n"/>
       <c r="AI18" s="12" t="n"/>
@@ -6872,9 +7105,12 @@
       <c r="CO18" s="9" t="n"/>
       <c r="CP18" s="9" t="n"/>
       <c r="CQ18" s="12" t="n"/>
+      <c r="CR18" s="9" t="n"/>
+      <c r="CS18" s="9" t="n"/>
+      <c r="CT18" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="X3:Z3"/>
@@ -6884,6 +7120,7 @@
     <mergeCell ref="BT3:BV3"/>
     <mergeCell ref="BK3:BM3"/>
     <mergeCell ref="CF3:CH3"/>
+    <mergeCell ref="CR3:CT3"/>
     <mergeCell ref="BQ3:BS3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="BW3:BY3"/>
@@ -6916,7 +7153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ18"/>
+  <dimension ref="A1:CT18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7014,6 +7251,9 @@
     <col width="9" customWidth="1" min="93" max="93"/>
     <col width="9" customWidth="1" min="94" max="94"/>
     <col width="9" customWidth="1" min="95" max="95"/>
+    <col width="9" customWidth="1" min="96" max="96"/>
+    <col width="9" customWidth="1" min="97" max="97"/>
+    <col width="9" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7032,93 +7272,96 @@
     </row>
     <row r="3">
       <c r="F3" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>46257</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>46256</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>46255</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>46254</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>46253</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>46252</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>46251</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>46250</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AG3" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AM3" s="4" t="n">
         <v>46247</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AP3" s="4" t="n">
         <v>46242</v>
       </c>
-      <c r="AP3" s="4" t="n">
+      <c r="AS3" s="4" t="n">
         <v>46241</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AV3" s="4" t="n">
         <v>46234</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AY3" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="BB3" s="4" t="n">
         <v>462